--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -14064,9 +14064,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BP65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -14118,7 +14118,7 @@
     <col min="67" max="67" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:68" ht="27.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="100" t="s">
         <v>0</v>
       </c>
@@ -14171,7 +14171,7 @@
       <c r="AV1" s="96"/>
       <c r="AW1" s="96"/>
     </row>
-    <row r="2" spans="1:68" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:68" ht="21.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A2" s="103" t="s">
         <v>1</v>
       </c>
@@ -14257,7 +14257,7 @@
       <c r="BO2" s="96"/>
       <c r="BP2" s="96"/>
     </row>
-    <row r="3" spans="1:68" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="45" customHeight="1" ns3:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -14461,7 +14461,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A4" s="86" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -14683,17 +14683,23 @@
         <f t="shared" ref="BM4:BM35" ca="1" si="20">(BK4/G4)^(1/4)-1</f>
         <v>0.34329692568943093</v>
       </c>
-      <c r="BN4" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO4" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="BP4" s="93" t="s">
-        <v>83</v>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A5" s="86" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -14925,7 +14931,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A6" s="86" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -15157,7 +15163,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A7" s="86" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
@@ -15379,17 +15385,23 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.25007229949436627</v>
       </c>
-      <c r="BN7" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO7" s="94" t="s">
-        <v>98</v>
-      </c>
-      <c r="BP7" s="93" t="s">
-        <v>99</v>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A8" s="86" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
@@ -15611,17 +15623,23 @@
         <f t="shared" ca="1" si="20"/>
         <v>-1.6089199691735612E-2</v>
       </c>
-      <c r="BN8" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO8" s="93" t="s">
-        <v>103</v>
-      </c>
-      <c r="BP8" s="93" t="s">
-        <v>104</v>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A9" s="86" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
@@ -15843,17 +15861,23 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.22845688983290469</v>
       </c>
-      <c r="BN9" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO9" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="BP9" s="93" t="s">
-        <v>108</v>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A10" s="86" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
@@ -16085,7 +16109,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A11" s="86" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
@@ -16307,17 +16331,23 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.23909386335572558</v>
       </c>
-      <c r="BN11" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO11" s="93" t="s">
-        <v>118</v>
-      </c>
-      <c r="BP11" s="93" t="s">
-        <v>104</v>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
       </c>
     </row>
-    <row r="12" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A12" s="86" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
@@ -16549,7 +16579,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="86" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -16781,7 +16811,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A14" s="86" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
@@ -17013,7 +17043,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="15" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A15" s="86" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
@@ -17235,17 +17265,23 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.16540754702958971</v>
       </c>
-      <c r="BN15" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO15" s="93" t="s">
-        <v>134</v>
-      </c>
-      <c r="BP15" s="93" t="s">
-        <v>108</v>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
       </c>
     </row>
-    <row r="16" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A16" s="86" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
@@ -17477,7 +17513,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A17" s="86" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
@@ -17709,7 +17745,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="18" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A18" s="86" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
@@ -17941,7 +17977,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="19" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A19" s="86" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
@@ -18173,7 +18209,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="20" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A20" s="86" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
@@ -18395,17 +18431,23 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.35157533189574863</v>
       </c>
-      <c r="BN20" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO20" s="93" t="s">
-        <v>123</v>
-      </c>
-      <c r="BP20" s="93" t="s">
-        <v>104</v>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
       </c>
     </row>
-    <row r="21" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A21" s="86" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
@@ -18637,7 +18679,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A22" s="86" t="e" vm="19">
         <v>#VALUE!</v>
       </c>
@@ -18869,7 +18911,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="23" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A23" s="86" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
@@ -19091,17 +19133,23 @@
         <f t="shared" ca="1" si="20"/>
         <v>6.3700785282530648E-2</v>
       </c>
-      <c r="BN23" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO23" s="93" t="s">
-        <v>123</v>
-      </c>
-      <c r="BP23" s="93" t="s">
-        <v>99</v>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>13/08/2026</t>
+        </is>
       </c>
     </row>
-    <row r="24" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A24" s="86" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
@@ -19333,7 +19381,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="25" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A25" s="86" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
@@ -19565,7 +19613,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A26" s="86" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
@@ -19797,7 +19845,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="27" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A27" s="86" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
@@ -20029,7 +20077,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A28" s="86" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
@@ -20261,7 +20309,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A29" s="86" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
@@ -20493,7 +20541,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A30" s="86" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
@@ -20725,7 +20773,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A31" s="86" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
@@ -20947,17 +20995,23 @@
         <f t="shared" ca="1" si="20"/>
         <v>-7.0078191617545804E-2</v>
       </c>
-      <c r="BN31" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO31" s="93" t="s">
-        <v>186</v>
-      </c>
-      <c r="BP31" s="93" t="s">
-        <v>187</v>
+      <c r="BN31" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO31" t="inlineStr">
+        <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="BP31" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
       </c>
     </row>
-    <row r="32" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A32" s="86" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
@@ -21189,7 +21243,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A33" s="86" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
@@ -21421,7 +21475,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A34" s="86" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
@@ -21653,7 +21707,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A35" s="86" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
@@ -21885,7 +21939,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A36" s="86" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
@@ -22107,17 +22161,23 @@
         <f t="shared" ref="BM36:BM65" ca="1" si="44">(BK36/G36)^(1/4)-1</f>
         <v>0.19198564331280221</v>
       </c>
-      <c r="BN36" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO36" s="93" t="s">
-        <v>206</v>
-      </c>
-      <c r="BP36" s="93" t="s">
-        <v>207</v>
+      <c r="BN36" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO36" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="BP36" t="inlineStr">
+        <is>
+          <t>27/07/2026</t>
+        </is>
       </c>
     </row>
-    <row r="37" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A37" s="86" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -22349,7 +22409,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A38" s="86" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
@@ -22571,17 +22631,23 @@
         <f t="shared" ca="1" si="44"/>
         <v>7.7459442978258242E-2</v>
       </c>
-      <c r="BN38" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO38" s="93" t="s">
-        <v>213</v>
-      </c>
-      <c r="BP38" s="93" t="s">
-        <v>214</v>
+      <c r="BN38" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO38" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="BP38" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
       </c>
     </row>
-    <row r="39" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A39" s="86" t="e" vm="36">
         <v>#VALUE!</v>
       </c>
@@ -22813,7 +22879,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A40" s="86" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
@@ -23045,7 +23111,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="41" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A41" s="86" t="e" vm="38">
         <v>#VALUE!</v>
       </c>
@@ -23277,7 +23343,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="42" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A42" s="86" t="e" vm="39">
         <v>#VALUE!</v>
       </c>
@@ -23509,7 +23575,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="43" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A43" s="86" t="e" vm="40">
         <v>#VALUE!</v>
       </c>
@@ -23741,7 +23807,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="44" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A44" s="86" t="e" vm="41">
         <v>#VALUE!</v>
       </c>
@@ -23973,7 +24039,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="45" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A45" s="86" t="e" vm="42">
         <v>#VALUE!</v>
       </c>
@@ -24205,7 +24271,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="46" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A46" s="86" t="e" vm="43">
         <v>#VALUE!</v>
       </c>
@@ -24437,7 +24503,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="47" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A47" s="86" t="e" vm="44">
         <v>#VALUE!</v>
       </c>
@@ -24669,7 +24735,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A48" s="86" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
@@ -24901,7 +24967,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A49" s="86" t="e" vm="46">
         <v>#VALUE!</v>
       </c>
@@ -25133,7 +25199,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A50" s="86" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
@@ -25367,7 +25433,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="51" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A51" s="86" t="e" vm="48">
         <v>#VALUE!</v>
       </c>
@@ -25599,7 +25665,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="52" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A52" s="86" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
@@ -25831,7 +25897,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="53" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A53" s="86" t="e" vm="50">
         <v>#VALUE!</v>
       </c>
@@ -26063,7 +26129,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="54" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A54" s="86" t="e" vm="51">
         <v>#VALUE!</v>
       </c>
@@ -26285,17 +26351,23 @@
         <f t="shared" ca="1" si="44"/>
         <v>-2.1023309776532217E-3</v>
       </c>
-      <c r="BN54" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO54" s="93" t="s">
-        <v>261</v>
-      </c>
-      <c r="BP54" s="93" t="s">
-        <v>83</v>
+      <c r="BN54" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO54" t="inlineStr">
+        <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="BP54" t="inlineStr">
+        <is>
+          <t>27/08/2026</t>
+        </is>
       </c>
     </row>
-    <row r="55" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A55" s="86" t="e" vm="52">
         <v>#VALUE!</v>
       </c>
@@ -26527,7 +26599,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A56" s="86" t="e" vm="53">
         <v>#VALUE!</v>
       </c>
@@ -26759,7 +26831,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="57" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A57" s="86" t="e" vm="54">
         <v>#VALUE!</v>
       </c>
@@ -26991,7 +27063,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="58" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A58" s="86" t="e" vm="55">
         <v>#VALUE!</v>
       </c>
@@ -27213,17 +27285,23 @@
         <f t="shared" ca="1" si="44"/>
         <v>0.26657523111483949</v>
       </c>
-      <c r="BN58" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO58" s="93" t="s">
-        <v>118</v>
-      </c>
-      <c r="BP58" s="93" t="s">
-        <v>207</v>
+      <c r="BN58" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO58" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="BP58" t="inlineStr">
+        <is>
+          <t>06/08/2026</t>
+        </is>
       </c>
     </row>
-    <row r="59" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A59" s="86" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
@@ -27455,7 +27533,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="60" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A60" s="86" t="e" vm="57">
         <v>#VALUE!</v>
       </c>
@@ -27687,7 +27765,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="61" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A61" s="86" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
@@ -27921,7 +27999,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="62" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A62" s="86" t="e" vm="59">
         <v>#VALUE!</v>
       </c>
@@ -28143,17 +28221,23 @@
         <f t="shared" ca="1" si="44"/>
         <v>0.1042738829072658</v>
       </c>
-      <c r="BN62" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO62" s="94" t="s">
-        <v>275</v>
-      </c>
-      <c r="BP62" s="93" t="s">
-        <v>276</v>
+      <c r="BN62" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="BO62" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="BP62" t="inlineStr">
+        <is>
+          <t>02/07/2026</t>
+        </is>
       </c>
     </row>
-    <row r="63" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A63" s="86" t="e" vm="60">
         <v>#VALUE!</v>
       </c>
@@ -28385,7 +28469,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="64" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:68" ht="15" customHeight="1" ns3:dyDescent="0.25">
       <c r="A64" s="86" t="e" vm="61">
         <v>#VALUE!</v>
       </c>
@@ -28617,7 +28701,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="65" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:68" ns3:dyDescent="0.25">
       <c r="A65" s="86" t="e" vm="62">
         <v>#VALUE!</v>
       </c>
@@ -28858,7 +28942,7 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing ns4:id="rId1"/>
 </worksheet>
 </file>
 
@@ -32970,9 +33054,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" ns3:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.85546875" customWidth="1"/>
@@ -32980,7 +33064,7 @@
     <col min="5" max="5" width="192.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ns3:dyDescent="0.25">
       <c r="A1" t="s">
         <v>358</v>
       </c>
@@ -32997,7 +33081,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ns3:dyDescent="0.25">
       <c r="A2" t="s">
         <v>431</v>
       </c>
@@ -33014,7 +33098,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ns3:dyDescent="0.25">
       <c r="A3" t="s">
         <v>396</v>
       </c>
@@ -33031,7 +33115,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ns3:dyDescent="0.25">
       <c r="A4" t="s">
         <v>438</v>
       </c>
@@ -33048,7 +33132,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ns3:dyDescent="0.25">
       <c r="A5" t="s">
         <v>442</v>
       </c>
@@ -33065,7 +33149,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ns3:dyDescent="0.25">
       <c r="A6" t="s">
         <v>282</v>
       </c>
@@ -33080,6 +33164,384 @@
       </c>
       <c r="E6" t="s">
         <v>448</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Q1 FY27 press release + CNBC (20/05/2026)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Q1 FY27: rev $81.6B (+85%), Data Center $75.2B (+92%), EPS adj $1.87 beat; guía Q2 $91B; dividendo x25 a $0.25/trim. Vigilar digestión de expectativas (acción cayó pese al beat).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Q1 FY27 press release + transcript (03/06/2026)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Q1 FY27: ARR $5.51B, NNARR $256M (+32%), FCF $469M récord; sube guía NNARR FY27 +$50M; split 4:1 (jul). AIDR ARR +250% QoQ. Tesis de plataforma intacta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VEEV</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Q1 FY27 press release + IR (03/06/2026)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Q1 FY27: rev $882.9M (+16%), subs +15%, EPS adj $2.24 beat; sube guía FY27. Pivot estratégico a AI agents (Vault CRM 150+ live). Vigilar ejecución Veeva AI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>COST</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Q3 FY26 press release (28/05/2026)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Q3 FY26: ventas $69.2B (+11.6%), comps +9.8% (+6.6% adj), EPS $4.93 (+15%), e-comm +21.5%, renovación US/CA 92.2%. Calidad operativa intacta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ZS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Q3 FY26 press release (28/05/2026)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Q3 FY26: rev $850.5M (+25%), ARR $3.525B (+25%), NNARR $166M, margen op. non-GAAP récord 23%; guía FY26 ARR ~$3.74B (+24%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Q1 FY27 press release (28/05/2026)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Q1 FY27: aceleración rev +21% ($277M), ARR $1.163B (+23%), NNARR récord $44M (+55%), margen op. +550bps a 4%. Inflexión crecimiento+rentabilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ITX</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Q1 2026 results + IR (09/06/2026)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Q1: ventas €8.75B (+5.8%; +8.8% cc), margen bruto 61.2% (+67bps), BN €1.4B (+5.4%); 1may-1jun +11.5% vs ~8% esperado; caja neta €10.8B. Momentum fuerte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Q1 2026 report (14/05/2026)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Q1: rev PLN 8.9B (+14.8%), LFL +4.4%, EBITDA beat consenso +9%; 62 tiendas nuevas; margen EBITDA 6.7% (-50bps). Acción +13.7% el día.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Q1 2026 press release (14/05/2026)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Q1: DE pre-realizaciones $0.59/sh (+7%), FRE +11%, capital fee-bearing +12%; $1B+ recompras YTD; avanza combinación BN+BNT. Tesis compounding intacta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KSPI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1Q 2026 results + transcript (11/05/2026)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Q1: rev +31% (KZT1.1T), GMV e-comm +41%, pero net income -1% (KZT252B); div KZT850/ADS (payout 64%); amortizó $600M notes. Vigilar compresión de márgenes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EVD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Q1 2026 results (28/05/2026)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Q1: rev €630M (+23%), aEBITDA €119M (+18.5%); Live Ent +38.3%; EPS €0.66 (+38%). Guidance reafirmado; ticketing algo débil por cambio de partner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DSGX</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Q1 FY27 press release (03/06/2026)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Q1 FY27: rev $193.6M (+15%), aEBITDA récord, net income $48.5M. Récords en márgenes y cash flow pese a mercado freight débil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WOSG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FY26 Trading Update RNS (14/05/2026)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>FY26 (53 sem): rev récord £1.83B (+13% cc); US +24% ($1.24B, &gt;50% grupo); aEBIT £152-155M sobre guía; FY27 +5-10% cc. Resultados completos 02/07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CELH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BN Última actualización; BO Últimos resultados; BP Próximos resultados (est.)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Q1 2026 press release (07/05/2026)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Q1: rev $782.6M (+138% con Alani Nu/Rockstar), EPS $0.41 beat; cuota ~20.9%; margen bruto 48.3% (-400bps por mix adquisiciones). Vigilar integración.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Downloads\watchlist-dashboard\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7F887A-EE24-4D4C-9E98-14F40BD60250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F179AC-28C1-48A6-8C1F-63087ECB91FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Watchlist Ratings" sheetId="1" r:id="rId1"/>
@@ -2403,7 +2403,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="578">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -2874,9 +2874,6 @@
     <t>8,331</t>
   </si>
   <si>
-    <t>24/04/2026</t>
-  </si>
-  <si>
     <t>14/07/2026</t>
   </si>
   <si>
@@ -3054,9 +3051,6 @@
     <t>94,595</t>
   </si>
   <si>
-    <t>15/04/2026</t>
-  </si>
-  <si>
     <t>4,637</t>
   </si>
   <si>
@@ -3135,24 +3129,15 @@
     <t>473</t>
   </si>
   <si>
-    <t>16/04/2026</t>
-  </si>
-  <si>
     <t>5,000</t>
   </si>
   <si>
     <t>7,693</t>
   </si>
   <si>
-    <t>25/06/2026</t>
-  </si>
-  <si>
     <t>121</t>
   </si>
   <si>
-    <t>23/04/2026</t>
-  </si>
-  <si>
     <t>2,522</t>
   </si>
   <si>
@@ -3201,9 +3186,6 @@
     <t>173</t>
   </si>
   <si>
-    <t>02/07/2026</t>
-  </si>
-  <si>
     <t>178</t>
   </si>
   <si>
@@ -3949,6 +3931,249 @@
   </si>
   <si>
     <t>OTLY</t>
+  </si>
+  <si>
+    <t>2026-07-18</t>
+  </si>
+  <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>19/08/2026</t>
+  </si>
+  <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
+    <t>23/07/2026</t>
+  </si>
+  <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
+    <t>30/06/2026</t>
+  </si>
+  <si>
+    <t>30/09/2026</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
+  </si>
+  <si>
+    <t>08/07/2026</t>
+  </si>
+  <si>
+    <t>30/01/2027</t>
+  </si>
+  <si>
+    <t>26/06/2026</t>
+  </si>
+  <si>
+    <t>02/12/2026</t>
+  </si>
+  <si>
+    <t>22/07/2026</t>
+  </si>
+  <si>
+    <t>BN; BO; BP</t>
+  </si>
+  <si>
+    <t>Q2 2026 (16/07/2026)</t>
+  </si>
+  <si>
+    <t>Q2: ingresos $40,2B (+36% i.a., sobre guia), margen bruto 67,7%, HPC +20% t/t. Sube guia FY26 a &gt;30% en USD por demanda IA (2nm/3nm). Prox Q3 ~15-oct (est).</t>
+  </si>
+  <si>
+    <t>Q2: rev $12,56B (+13%), margen op 33%, BPA $0,80, BN $3,40B. Estrecha guia FY26 a $51,0-51,4B (margen op 31,5%); Q3 +12%. Reduce reporte de metricas de engagement; accion cayo tras publicar.</t>
+  </si>
+  <si>
+    <t>ABBNE</t>
+  </si>
+  <si>
+    <t>Q2: pedidos record $12B, ventas comparables +12%, margen EBITA op 20,2% (+90pb); Electrificacion pedidos $7,2B (+70%). OPA sobre Rotork £503p (~$5,5B) recomendada; desinversion Robotics ~$4,8B caja (cierre 2S26). Buyback $2B, ND/EBITDA 0,3.</t>
+  </si>
+  <si>
+    <t>Interim Q2/H1 2026 (14/07/2026)</t>
+  </si>
+  <si>
+    <t>Q2: ventas +11% (organico +5%, M&amp;A +7%), margen EBITA 23,1% (vs 22,5%), BN/BPA +18%. 4 adquisiciones en 1S (Ethoss, Glass Umbrella, Karl Kaps, Metalltech ~500M SEK); Boscaro consolidada en jul. Vuelta a la normalidad tras un 2025 dificil.</t>
+  </si>
+  <si>
+    <t>NKE</t>
+  </si>
+  <si>
+    <t>Q4/FY26 (30/06/2026)</t>
+  </si>
+  <si>
+    <t>Q4 FY26 (cierre 31-may): ventas $10,97B (-1%; -4% cc) sobre est., BPA aj $0,20 vs $0,13e; margen bruto 49,2% (+890pb por recuperacion aranceles IEEPA). FY26 ventas $46,4B (planas). Guia: BPA 'plano' en 1S FY27. Prox ~30-sep (est).</t>
+  </si>
+  <si>
+    <t>Interim Q2 2026 (16/07/2026)</t>
+  </si>
+  <si>
+    <t>Q2: ventas +72% (SEK 232M), organico +42%, margen op 41% (aj 47%). Resuelto litigio de patentes con BrainGuard (paga USD 3,25M, se contabiliza en Q3). Fuerte recuperacion en todas las categorias.</t>
+  </si>
+  <si>
+    <t>FY26 Results (14/07/2026)</t>
+  </si>
+  <si>
+    <t>FY26 (53 sem, cierre 3-may): ingresos record £1,83B (+11%; +13% cc), EBIT aj +6% a £155M, PBT +76% a £133M. EEUU +24% cc (ya 1er mercado, £927M); FCF £162M, deuda neta baja a £57M. Guia FY27: ventas +5-10% cc. Rumores de posible venta.</t>
+  </si>
+  <si>
+    <t>TFF</t>
+  </si>
+  <si>
+    <t>Resultats annuels 2025/26 (08/07/2026)</t>
+  </si>
+  <si>
+    <t>FY (cierre 30-abr): CA €312,75M (-26,5%; -23,4% cc); Alcools -36,7% (Bourbon -35,4%, volumenes -28%), Vin -14,1%. EBITDA €48,2M (15,4%, -40%), BN €9,2M (-71%). Deuda neta baja a €285M; caja €97M por desdstock. Dividendo €0,40, AG 28-oct.</t>
+  </si>
+  <si>
+    <t>FY2025 Full Year Results (26/06/2026)</t>
+  </si>
+  <si>
+    <t>FY25: ingresos $212,9M, produccion 8.940 boepd (tope de guia), EBITDA aj $97M. Guia FY26 proforma 19-21k boepd. Adquisicion Oman (Bloques 3&amp;4 y 9, +25,6 mmboe 2P); FID Balder Next (86 mmboe, primer crudo 4T27); bono $300M al 9,875% sobresuscrito. Caja ~$268M.</t>
+  </si>
+  <si>
+    <t>BN; BP</t>
+  </si>
+  <si>
+    <t>Preanuncio Q2 2026 + guia (jul-2026)</t>
+  </si>
+  <si>
+    <t>Preliminar Q2: ventas ~$418M (sobre guia $388-403M), EBITDA aj ~$112M. SUBE guia FY26 a ventas $1.215-1.250M y EBITDA aj $335-350M. Termina distribucion con Boise Cascade (12-ago) y amplia con SBP. Resultados completos ~4-ago.</t>
+  </si>
+  <si>
+    <t>Prensa (jul-2026)</t>
+  </si>
+  <si>
+    <t>6-jul: recorta ~4.800 empleos (~2,1%) reestructurando comercial y Xbox mientras eleva el capex record en IA; accion -23% en 1S26. Sin resultados nuevos; Q4 FY26 el 29-jul.</t>
+  </si>
+  <si>
+    <t>Prensa (jun-jul 2026)</t>
+  </si>
+  <si>
+    <t>Jun: paga $14,3B por el 49% de Scale AI e incorpora a Alexandr Wang para liderar Meta Superintelligence Labs; fichajes de primer nivel (Nat Friedman, Daniel Gross, +11 ingenieros de OpenAI/Google/Anthropic, fundadores de Virtue AI). Fuerte gasto en talento IA. Q2 el 29-jul.</t>
+  </si>
+  <si>
+    <t>16.000+ despidos en 2026 (AWS, Alexa, Prime Video); nueva unidad AWS 'Forward Deployed Engineering' ($1B); capex 2026 ~$200B en IA; emision de bonos ~$25B para infraestructura. Q2 el 30-jul.</t>
+  </si>
+  <si>
+    <t>DOJ/Prensa (2026)</t>
+  </si>
+  <si>
+    <t>Remedios antitrust finalizados (abr-26): conductuales (sin contratos exclusivos, compartir datos/sindicacion), sin ruptura estructural; Google y DOJ+35 estados han apelado. Gemini 750M MAU; capex 2026 $175-185B. Q2 el 28-jul.</t>
+  </si>
+  <si>
+    <t>30-jun: acuerdo para comprar las operaciones norteamericanas de EDF power solutions ($4,2B, renovables). Cierra fondo buyout NA de $23B y $2,5B de credito privado en Asia; monetizaciones &gt;$900M (mar-jun). Q2 el 30-jul.</t>
+  </si>
+  <si>
+    <t>Junta/RNS (16-17 jul 2026)</t>
+  </si>
+  <si>
+    <t>16-17-jul: la junta aprueba la simplificacion de la estructura corporativa; nueva matriz 'Brookfield Corporation Ltd.' cotizara en TSX/NYSE como BN, cierre previsto para fin de ano. Q2 el 13-ago.</t>
+  </si>
+  <si>
+    <t>Prensa (jun-2026)</t>
+  </si>
+  <si>
+    <t>Fusion de MWI Animal Health con Covetrus (plataforma salud animal) y compra del negocio de retina de EyeSouth; relevo de CFO (Cleary sale 30-jun, entra Eva Boratto). Guia FY26 BPA aj $17,65-17,90, buyback $1B. Q3 FY26 el 4-ago.</t>
+  </si>
+  <si>
+    <t>Prensa (30-jun-2026)</t>
+  </si>
+  <si>
+    <t>30-jun: acuerdo para comprar el 100% de Cognite (software IA industrial) por $3,1B en efectivo (refuerza AVEVA); colaboracion con Foxconn en centros de datos IA. Mantiene objetivo EBITA aj +10-15% organico. S1 el 30-jul.</t>
+  </si>
+  <si>
+    <t>SGO</t>
+  </si>
+  <si>
+    <t>Rotacion de cartera: compra Xypex (quimicos de construccion, 6-jul); vende Dahl (distribucion nordica, €1,5B, 15-jun), HKO (1-jun) y distribucion de azulejos nordica (26-may). Objetivo: rotar &gt;20% de ventas via M&amp;A/desinversiones hasta 2030. S1 el 30-jul.</t>
+  </si>
+  <si>
+    <t>Adquisiciones en centros de datos: Girtz Industries (EEUU, ~$80M ventas) y SRS Power Engineering (Malasia, ~€90M). Reafirma guia FY26 (ventas +2-6%, margen op aj 20-21%); guia data center al alto de 10-20%. Varias mejoras de rating. S1 el 6-ago.</t>
+  </si>
+  <si>
+    <t>Ambicion M&amp;A ~€4B (posible operacion tamano Encore Wire en 12m) y cerca de contratos a largo plazo con hyperscalers (capacidad optica +40-50%). Confia en batir con holgura el punto medio de la guia EBITDA FY26 (€2.625-2.775M); adquirio Xtera (subsea). S1 el 30-jul.</t>
+  </si>
+  <si>
+    <t>Prensa/IR (jun-jul 2026)</t>
+  </si>
+  <si>
+    <t>11-jun: adquisicion de Orb (billing para software). Reafirma guia FY26 (ingresos +20-22% cc, margen EBITDA 55%). Resultados S1 2026 el 13-ago.</t>
+  </si>
+  <si>
+    <t>Ad-hoc (17-jun-2026)</t>
+  </si>
+  <si>
+    <t>17-jun: SUBE guia de rentabilidad FY26 - expansion de margen core EBIT ahora 140-170pb (antes 30-60pb) por eficiencias de fabricacion, mix geografico y menores aranceles. Resultados S1 el 19-ago.</t>
+  </si>
+  <si>
+    <t>Presion competitiva: VantageScore 4.0 aprobado para Fannie/Freddie/FHA; FICO baja el score hipotecario 10T a $0,99 (aunque sube el score base a $10). Accion ~-50% desde maximos. Sube guia FY26 (~$2,45B ingresos). Q3 FY26 ~28-jul. VIGILAR tesis.</t>
+  </si>
+  <si>
+    <t>Prensa (01-jul-2026)</t>
+  </si>
+  <si>
+    <t>1-jul: nueva politica 'Pay Per Use' - desde 15-sept bloquea por defecto crawlers de IA de uso mixto en paginas con publicidad y paga a editores cuando su contenido alimenta respuestas IA. Q2 el 6-ago.</t>
+  </si>
+  <si>
+    <t>Prensa (may-jul 2026)</t>
+  </si>
+  <si>
+    <t>19-may: adquiere Deepchecks (~$20M, seguridad IA). Reorganizacion comercial (nuevo CRO, cambios GTM) que ha pesado en la percepcion de la guia. Q2 el 30-jul.</t>
+  </si>
+  <si>
+    <t>Summer Release (20-may-2026)</t>
+  </si>
+  <si>
+    <t>20-may: 'Summer Release 2026' - nuevos Servicios (comida via Instacart, recogidas aeropuerto, alquiler de coche, consigna), +3.000 experiencias, hoteles boutique, mejoras IA y experiencias del Mundial 2026. Q2 el 6-ago.</t>
+  </si>
+  <si>
+    <t>Lanza FLRT (energetica enfocada a mujeres, vs Alani Nu/Bloom) y planea subida de precios en EEUU; la subida de Red Bull (1-ago) se ve positiva. Presion de costes de aluminio. Q2 el 6-ago.</t>
+  </si>
+  <si>
+    <t>Prensa (25-jun-2026)</t>
+  </si>
+  <si>
+    <t>25-jun: completa el stream de oro de Ravenswood (Australia) por US$440M; sube el objetivo 2030 a 150-160k GEOs. Primera entrega en Q3. Q2 el 4-ago.</t>
+  </si>
+  <si>
+    <t>Adquisicion de FloWorks ($1,6B, control de flujo industrial; data centers/semis; ~10x EBITDA, cierre Q3). Cancela su cotizacion secundaria en el LSE (efectivo 20-jul). Mantiene guia FY. Q4 FY26 el 4-ago.</t>
+  </si>
+  <si>
+    <t>Jun: primer crudo en Blackrod Fase 1 (hito). Produccion Q1 43k boepd; guia FY 44-47k con fuerte rampa en 2S. Recompras ralentizadas para priorizar Blackrod; perdida de cobertura ~$30M en Q2. Q2 el 4-ago.</t>
+  </si>
+  <si>
+    <t>Se reanudan (muy pocos) envios de H200 a China tras licencias; sigue practicamente fuera del mercado de data center chino. Sin resultados nuevos desde Q1 FY27 (20-may). Q2 FY27 el 26-ago.</t>
+  </si>
+  <si>
+    <t>Ad-hoc Jungfraubahn (jun-2026)</t>
+  </si>
+  <si>
+    <t>Advertencia: caida de visitantes en los primeros 4 meses (Jungfraujoch -12,3%, Experience Mountains -9,6%, total -5,7%) por el conflicto en Oriente Medio, restricciones de espacio aereo y menor demanda asiatica; la tendencia se acentua y pesara en el resultado 2026. Fuertes reservas futuras como colchon. S1 el 28-ago.</t>
+  </si>
+  <si>
+    <t>Calendario/IR (jul-2026)</t>
+  </si>
+  <si>
+    <t>Sin novedad material desde may; resultados S1 2026 el 23-jul. Q1: rev €368M/EBITDA €104M; guia FY EBITDA &gt;€450M, BPA +5%.</t>
+  </si>
+  <si>
+    <t>Sin novedad material; resultados Q2 2026 el 22-jul. Q1: rev $228,3M (+15,6%), EBITDA aj +$5,0M (positivo). Revision estrategica de China en curso.</t>
+  </si>
+  <si>
+    <t>VARIOS</t>
+  </si>
+  <si>
+    <t>Revision sin cambios de celda</t>
+  </si>
+  <si>
+    <t>Barrido de noticias 18-may -&gt; 18-jul</t>
+  </si>
+  <si>
+    <t>Revisados sin novedad material (resultados ya capturados en jun o proximos en ago-sep): VEEV, COST, DSGX, ZS, S, CRWD, ITX, DNP, EVD, KSPI, CELH, HLMA (Q1/anteriores ya analizados en jun); RAA (Rational, Q1 6-may), NTO (Nintendo, FY 8-may), SPOT, VLTO, GRMN, KRX (Kingspan), CPR (Campari), JDG, BFIT, VRLA (Verallia, OPA BWGI fue 2025), LOTB, CBAV (Clinica Baviera), SIKA, TGYM (Technogym). No se ha modificado su celda BN.</t>
   </si>
 </sst>
 </file>
@@ -5147,37 +5372,155 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5195,129 +5538,11 @@
     <xf numFmtId="0" fontId="15" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14885,13 +15110,13 @@
         <v>0.35404498597134726</v>
       </c>
       <c r="BN4" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO4" t="s">
         <v>103</v>
       </c>
       <c r="BP4" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15117,13 +15342,13 @@
         <v>0.13667813232291248</v>
       </c>
       <c r="BN5" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO5" s="93" t="s">
         <v>85</v>
       </c>
       <c r="BP5" s="93" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="6" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15349,7 +15574,7 @@
         <v>0.33962554586669502</v>
       </c>
       <c r="BN6" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO6" s="93" t="s">
         <v>90</v>
@@ -15581,13 +15806,13 @@
         <v>0.25482976969404003</v>
       </c>
       <c r="BN7" t="s">
-        <v>425</v>
+        <v>497</v>
       </c>
       <c r="BO7" t="s">
         <v>95</v>
       </c>
       <c r="BP7" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15813,13 +16038,13 @@
         <v>1.7035846360751394E-2</v>
       </c>
       <c r="BN8" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO8" t="s">
         <v>99</v>
       </c>
       <c r="BP8" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16045,13 +16270,13 @@
         <v>0.24553423525971096</v>
       </c>
       <c r="BN9" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO9" t="s">
         <v>103</v>
       </c>
       <c r="BP9" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16277,13 +16502,13 @@
         <v>0.15723005465088957</v>
       </c>
       <c r="BN10" s="93" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="BO10" s="93" t="s">
         <v>108</v>
       </c>
       <c r="BP10" s="93" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16509,13 +16734,13 @@
         <v>0.34414353629850369</v>
       </c>
       <c r="BN11" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO11" t="s">
         <v>99</v>
       </c>
       <c r="BP11" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16741,7 +16966,7 @@
         <v>0.1501292474376974</v>
       </c>
       <c r="BN12" s="93" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="BO12" s="94" t="s">
         <v>118</v>
@@ -16973,7 +17198,7 @@
         <v>6.9229397135512238E-2</v>
       </c>
       <c r="BN13" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO13" s="93" t="s">
         <v>85</v>
@@ -17205,7 +17430,7 @@
         <v>5.0833735875018826E-2</v>
       </c>
       <c r="BN14" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO14" s="93" t="s">
         <v>113</v>
@@ -17437,13 +17662,13 @@
         <v>0.13663154593919979</v>
       </c>
       <c r="BN15" t="s">
+        <v>419</v>
+      </c>
+      <c r="BO15" t="s">
+        <v>174</v>
+      </c>
+      <c r="BP15" t="s">
         <v>425</v>
-      </c>
-      <c r="BO15" t="s">
-        <v>175</v>
-      </c>
-      <c r="BP15" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="16" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17901,13 +18126,13 @@
         <v>8.6208283772470695E-2</v>
       </c>
       <c r="BN17" s="93" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="BO17" s="94" t="s">
         <v>136</v>
       </c>
       <c r="BP17" s="93" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="18" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18133,13 +18358,13 @@
         <v>0.12760665021194706</v>
       </c>
       <c r="BN18" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO18" s="93" t="s">
         <v>139</v>
       </c>
       <c r="BP18" s="93" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18365,13 +18590,13 @@
         <v>0.12340083605171048</v>
       </c>
       <c r="BN19" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO19" s="93" t="s">
         <v>144</v>
       </c>
       <c r="BP19" s="93" t="s">
-        <v>145</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18561,14 +18786,14 @@
         <v>0.21875</v>
       </c>
       <c r="BD20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BE20" s="23">
         <f t="shared" si="15"/>
         <v>3.9812328944305531E-2</v>
       </c>
       <c r="BF20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="BG20" s="23">
         <f t="shared" si="16"/>
@@ -18597,13 +18822,13 @@
         <v>0.39406104363416494</v>
       </c>
       <c r="BN20" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO20" t="s">
         <v>99</v>
       </c>
       <c r="BP20" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="21" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18793,14 +19018,14 @@
         <v>0.59375</v>
       </c>
       <c r="BD21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BE21" s="23">
         <f t="shared" si="15"/>
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BG21" s="23">
         <f t="shared" si="16"/>
@@ -18829,13 +19054,13 @@
         <v>-6.75258992372334E-2</v>
       </c>
       <c r="BN21" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO21" s="93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BP21" s="93" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="22" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19025,14 +19250,14 @@
         <v>0.375</v>
       </c>
       <c r="BD22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BE22" s="23">
         <f t="shared" si="15"/>
         <v>4.9985012185677746E-2</v>
       </c>
       <c r="BF22" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BG22" s="23">
         <f t="shared" si="16"/>
@@ -19061,13 +19286,13 @@
         <v>0.26608928109004548</v>
       </c>
       <c r="BN22" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO22" s="93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BP22" s="93" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="23" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19205,7 +19430,7 @@
         <v>7.44</v>
       </c>
       <c r="AO23" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AP23" s="19">
         <v>500</v>
@@ -19257,14 +19482,14 @@
         <v>0.2615384615384615</v>
       </c>
       <c r="BD23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BE23" s="23">
         <f t="shared" si="15"/>
         <v>0.12006550912241742</v>
       </c>
       <c r="BF23" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BG23" s="23">
         <f t="shared" si="16"/>
@@ -19293,13 +19518,13 @@
         <v>9.6454580014539326E-2</v>
       </c>
       <c r="BN23" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO23" t="s">
         <v>95</v>
       </c>
       <c r="BP23" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="24" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19489,14 +19714,14 @@
         <v>0.15384615384615385</v>
       </c>
       <c r="BD24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BE24" s="23">
         <f t="shared" si="15"/>
         <v>3.9950542132181077E-2</v>
       </c>
       <c r="BF24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BG24" s="23">
         <f t="shared" si="16"/>
@@ -19525,13 +19750,13 @@
         <v>0.15736302613130304</v>
       </c>
       <c r="BN24" s="93" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="BO24" s="93" t="s">
         <v>139</v>
       </c>
       <c r="BP24" s="93" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19721,14 +19946,14 @@
         <v>0.15263157894736842</v>
       </c>
       <c r="BD25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BE25" s="23">
         <f t="shared" si="15"/>
         <v>6.003737798448272E-2</v>
       </c>
       <c r="BF25" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BG25" s="23">
         <f t="shared" si="16"/>
@@ -19757,13 +19982,13 @@
         <v>0.11996589429293425</v>
       </c>
       <c r="BN25" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO25" s="93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BP25" s="93" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19953,14 +20178,14 @@
         <v>0.15</v>
       </c>
       <c r="BD26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BE26" s="23">
         <f t="shared" si="15"/>
         <v>6.1858758794934632E-2</v>
       </c>
       <c r="BF26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BG26" s="23">
         <f t="shared" si="16"/>
@@ -19992,10 +20217,10 @@
         <v>81</v>
       </c>
       <c r="BO26" s="93" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BP26" s="93" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20133,7 +20358,7 @@
         <v>6.7</v>
       </c>
       <c r="AO27" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AP27" s="19">
         <v>300</v>
@@ -20185,14 +20410,14 @@
         <v>0.13571428571428573</v>
       </c>
       <c r="BD27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BE27" s="23">
         <f t="shared" si="15"/>
         <v>5.9828421260577302E-2</v>
       </c>
       <c r="BF27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BG27" s="23">
         <f t="shared" si="16"/>
@@ -20221,13 +20446,13 @@
         <v>2.3314845145717245E-2</v>
       </c>
       <c r="BN27" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO27" s="94" t="s">
         <v>85</v>
       </c>
       <c r="BP27" s="93" t="s">
-        <v>428</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20417,14 +20642,14 @@
         <v>0.28947368421052633</v>
       </c>
       <c r="BD28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BE28" s="23">
         <f t="shared" si="15"/>
         <v>4.9999742905350697E-2</v>
       </c>
       <c r="BF28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="BG28" s="23">
         <f t="shared" si="16"/>
@@ -20453,13 +20678,13 @@
         <v>0.18017157019865659</v>
       </c>
       <c r="BN28" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO28" s="93" t="s">
         <v>85</v>
       </c>
       <c r="BP28" s="93" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="29" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20649,14 +20874,14 @@
         <v>5.6249999999999994E-2</v>
       </c>
       <c r="BD29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="BE29" s="23">
         <f t="shared" si="15"/>
         <v>7.0010270953862141E-2</v>
       </c>
       <c r="BF29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BG29" s="23">
         <f t="shared" si="16"/>
@@ -20685,13 +20910,13 @@
         <v>0.25952098858972428</v>
       </c>
       <c r="BN29" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO29" s="93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BP29" s="93" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="30" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20881,14 +21106,14 @@
         <v>1.4285714285714287E-2</v>
       </c>
       <c r="BD30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BE30" s="23">
         <f t="shared" si="15"/>
         <v>0.13995090255865472</v>
       </c>
       <c r="BF30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BG30" s="23">
         <f t="shared" si="16"/>
@@ -20917,13 +21142,13 @@
         <v>-0.2212757014175647</v>
       </c>
       <c r="BN30" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO30" s="93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BP30" s="93" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="31" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21113,14 +21338,14 @@
         <v>0.19999999999999998</v>
       </c>
       <c r="BD31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="BE31" s="23">
         <f t="shared" si="15"/>
         <v>0.12002012191466971</v>
       </c>
       <c r="BF31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BG31" s="23">
         <f t="shared" si="16"/>
@@ -21149,13 +21374,13 @@
         <v>-9.1701728940705274E-2</v>
       </c>
       <c r="BN31" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO31" t="s">
         <v>103</v>
       </c>
       <c r="BP31" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="32" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21345,14 +21570,14 @@
         <v>0.27142857142857141</v>
       </c>
       <c r="BD32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BE32" s="23">
         <f t="shared" si="15"/>
         <v>4.9999742905350697E-2</v>
       </c>
       <c r="BF32" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BG32" s="23">
         <f t="shared" si="16"/>
@@ -21381,13 +21606,13 @@
         <v>2.3331185931335874E-2</v>
       </c>
       <c r="BN32" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO32" s="93" t="s">
         <v>85</v>
       </c>
       <c r="BP32" s="93" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21577,14 +21802,14 @@
         <v>0.20454545454545453</v>
       </c>
       <c r="BD33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BE33" s="23">
         <f t="shared" si="15"/>
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF33" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="BG33" s="23">
         <f t="shared" si="16"/>
@@ -21613,13 +21838,13 @@
         <v>-1.6917988403060247E-2</v>
       </c>
       <c r="BN33" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO33" s="93" t="s">
         <v>180</v>
       </c>
       <c r="BP33" s="93" t="s">
-        <v>181</v>
+        <v>498</v>
       </c>
     </row>
     <row r="34" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21631,7 +21856,7 @@
         <v>GRMN</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D34" s="88" t="s">
         <v>77</v>
@@ -21809,14 +22034,14 @@
         <v>0.25</v>
       </c>
       <c r="BD34" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BE34" s="23">
         <f t="shared" si="15"/>
         <v>4.004618516068903E-2</v>
       </c>
       <c r="BF34" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BG34" s="23">
         <f t="shared" si="16"/>
@@ -21845,13 +22070,13 @@
         <v>9.5928190485545128E-2</v>
       </c>
       <c r="BN34" s="93" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="BO34" s="93" t="s">
         <v>85</v>
       </c>
       <c r="BP34" s="93" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="35" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21863,7 +22088,7 @@
         <v>KRX</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D35" s="88" t="s">
         <v>77</v>
@@ -22041,14 +22266,14 @@
         <v>0.1076923076923077</v>
       </c>
       <c r="BD35" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BE35" s="23">
         <f t="shared" si="15"/>
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF35" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="BG35" s="23">
         <f t="shared" si="16"/>
@@ -22080,7 +22305,7 @@
         <v>81</v>
       </c>
       <c r="BO35" s="93" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BP35" s="93" t="s">
         <v>131</v>
@@ -22221,7 +22446,7 @@
         <v>6</v>
       </c>
       <c r="AO36" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AP36" s="19">
         <v>900000</v>
@@ -22273,14 +22498,14 @@
         <v>0.23333333333333334</v>
       </c>
       <c r="BD36" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BE36" s="23">
         <f t="shared" ref="BE36:BE65" si="41">(BD36/AS36)^(1/5)-1</f>
         <v>6.9999922003442849E-2</v>
       </c>
       <c r="BF36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="BG36" s="23">
         <f t="shared" ref="BG36:BG65" si="42">(BF36/AS36)^(1/5)-1</f>
@@ -22309,13 +22534,13 @@
         <v>0.2031572378387061</v>
       </c>
       <c r="BN36" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO36" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BP36" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="37" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22505,14 +22730,14 @@
         <v>0.15909090909090909</v>
       </c>
       <c r="BD37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BE37" s="23">
         <f t="shared" si="41"/>
         <v>5.9223841048812176E-2</v>
       </c>
       <c r="BF37" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BG37" s="23">
         <f t="shared" si="42"/>
@@ -22547,7 +22772,7 @@
         <v>113</v>
       </c>
       <c r="BP37" s="93" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="38" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22559,7 +22784,7 @@
         <v>NVDA</v>
       </c>
       <c r="C38" s="88" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D38" s="88" t="s">
         <v>110</v>
@@ -22737,14 +22962,14 @@
         <v>0.83333333333333326</v>
       </c>
       <c r="BD38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BE38" s="23">
         <f t="shared" si="41"/>
         <v>8.0000772740678627E-2</v>
       </c>
       <c r="BF38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BG38" s="23">
         <f t="shared" si="42"/>
@@ -22773,13 +22998,13 @@
         <v>0.10599500048899735</v>
       </c>
       <c r="BN38" t="s">
-        <v>425</v>
+        <v>497</v>
       </c>
       <c r="BO38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BP38" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="39" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22791,7 +23016,7 @@
         <v>COR</v>
       </c>
       <c r="C39" s="88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>96</v>
@@ -22969,14 +23194,14 @@
         <v>0.13333333333333333</v>
       </c>
       <c r="BD39" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BE39" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BG39" s="23">
         <f t="shared" si="42"/>
@@ -23005,13 +23230,13 @@
         <v>0.1297914061329597</v>
       </c>
       <c r="BN39" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO39" s="94" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BP39" s="93" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="40" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23023,7 +23248,7 @@
         <v>TSM</v>
       </c>
       <c r="C40" s="88" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>77</v>
@@ -23201,14 +23426,14 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="BD40" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="BE40" s="23">
         <f t="shared" si="41"/>
         <v>7.9997972620447833E-2</v>
       </c>
       <c r="BF40" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BG40" s="23">
         <f t="shared" si="42"/>
@@ -23237,13 +23462,13 @@
         <v>-1.7257046861950176E-2</v>
       </c>
       <c r="BN40" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO40" s="93" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="BP40" s="93" t="s">
-        <v>181</v>
+        <v>500</v>
       </c>
     </row>
     <row r="41" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23433,14 +23658,14 @@
         <v>0.18</v>
       </c>
       <c r="BD41" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="BE41" s="23">
         <f t="shared" si="41"/>
         <v>2.9995722023716587E-2</v>
       </c>
       <c r="BF41" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="BG41" s="23">
         <f t="shared" si="42"/>
@@ -23469,13 +23694,13 @@
         <v>0.17255762415461096</v>
       </c>
       <c r="BN41" s="93" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="BO41" s="93" t="s">
         <v>139</v>
       </c>
       <c r="BP41" s="93" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23665,14 +23890,14 @@
         <v>0.11052631578947368</v>
       </c>
       <c r="BD42" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="BE42" s="23">
         <f t="shared" si="41"/>
         <v>5.9929050622556934E-2</v>
       </c>
       <c r="BF42" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="BG42" s="23">
         <f t="shared" si="42"/>
@@ -23701,10 +23926,10 @@
         <v>-1.3636073866254428E-2</v>
       </c>
       <c r="BN42" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO42" s="93" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BP42" s="93" t="s">
         <v>124</v>
@@ -23719,7 +23944,7 @@
         <v>JFN</v>
       </c>
       <c r="C43" s="88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D43" s="88" t="s">
         <v>96</v>
@@ -23845,7 +24070,7 @@
         <v>5.24</v>
       </c>
       <c r="AO43" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AP43" s="19">
         <v>75</v>
@@ -23897,14 +24122,14 @@
         <v>0.17333333333333334</v>
       </c>
       <c r="BD43" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="BE43" s="23">
         <f t="shared" si="41"/>
         <v>-6.0146235650011426E-2</v>
       </c>
       <c r="BF43" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="BG43" s="23">
         <f t="shared" si="42"/>
@@ -23933,13 +24158,13 @@
         <v>4.8865524260605975E-2</v>
       </c>
       <c r="BN43" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO43" s="93" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="BP43" s="93" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23951,7 +24176,7 @@
         <v>CPR</v>
       </c>
       <c r="C44" s="88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D44" s="88" t="s">
         <v>96</v>
@@ -24129,14 +24354,14 @@
         <v>7.636363636363637E-2</v>
       </c>
       <c r="BD44" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="BE44" s="23">
         <f t="shared" si="41"/>
         <v>3.0128962818398941E-2</v>
       </c>
       <c r="BF44" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="BG44" s="23">
         <f t="shared" si="42"/>
@@ -24165,13 +24390,13 @@
         <v>4.4886395959320424E-4</v>
       </c>
       <c r="BN44" s="93" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="BO44" s="93" t="s">
         <v>108</v>
       </c>
       <c r="BP44" s="93" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="45" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24183,7 +24408,7 @@
         <v>SIKA</v>
       </c>
       <c r="C45" s="88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D45" s="88" t="s">
         <v>77</v>
@@ -24309,7 +24534,7 @@
         <v>5.13</v>
       </c>
       <c r="AO45" s="18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AP45" s="19">
         <v>1200</v>
@@ -24361,14 +24586,14 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="BD45" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="BE45" s="23">
         <f t="shared" si="41"/>
         <v>2.9967449959592329E-2</v>
       </c>
       <c r="BF45" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="BG45" s="23">
         <f t="shared" si="42"/>
@@ -24400,10 +24625,10 @@
         <v>81</v>
       </c>
       <c r="BO45" s="93" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="BP45" s="93" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24418,7 +24643,7 @@
         <v>109</v>
       </c>
       <c r="D46" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E46" s="11" t="str">
         <f t="array" aca="1" ref="E46" ca="1">_FV(A46,"Abreviatura de intercambio",TRUE())</f>
@@ -24593,14 +24818,14 @@
         <v>0.83333333333333326</v>
       </c>
       <c r="BD46" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="BE46" s="23">
         <f t="shared" si="41"/>
         <v>1.9956640367314815E-2</v>
       </c>
       <c r="BF46" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="BG46" s="23">
         <f t="shared" si="42"/>
@@ -24629,10 +24854,10 @@
         <v>0.27827634265152379</v>
       </c>
       <c r="BN46" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO46" s="93" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BP46" s="93" t="s">
         <v>124</v>
@@ -24647,7 +24872,7 @@
         <v>TGYM</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D47" s="88" t="s">
         <v>77</v>
@@ -24825,14 +25050,14 @@
         <v>0.19999999999999998</v>
       </c>
       <c r="BD47" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="BE47" s="23">
         <f t="shared" si="41"/>
         <v>4.0751095710728658E-2</v>
       </c>
       <c r="BF47" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="BG47" s="23">
         <f t="shared" si="42"/>
@@ -24879,7 +25104,7 @@
         <v>VID</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D48" s="88" t="s">
         <v>96</v>
@@ -25057,14 +25282,14 @@
         <v>0.17500000000000002</v>
       </c>
       <c r="BD48" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="BE48" s="23">
         <f t="shared" si="41"/>
         <v>9.805797673485328E-3</v>
       </c>
       <c r="BF48" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="BG48" s="23">
         <f t="shared" si="42"/>
@@ -25093,13 +25318,13 @@
         <v>0.17994078083050535</v>
       </c>
       <c r="BN48" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO48" s="94" t="s">
         <v>85</v>
       </c>
       <c r="BP48" s="93" t="s">
-        <v>428</v>
+        <v>501</v>
       </c>
     </row>
     <row r="49" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25111,10 +25336,10 @@
         <v>TFPM</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E49" s="11" t="str">
         <f t="array" aca="1" ref="E49" ca="1">_FV(A49,"Abreviatura de intercambio",TRUE())</f>
@@ -25289,14 +25514,14 @@
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="BD49" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="BE49" s="23">
         <f t="shared" si="41"/>
         <v>4.957228210048803E-2</v>
       </c>
       <c r="BF49" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="BG49" s="23">
         <f t="shared" si="42"/>
@@ -25325,13 +25550,13 @@
         <v>0.15245224094281129</v>
       </c>
       <c r="BN49" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO49" s="93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BP49" s="93" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="50" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25559,13 +25784,13 @@
         <v>0.12883269664335661</v>
       </c>
       <c r="BN50" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO50" s="93" t="s">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="BP50" s="93" t="s">
-        <v>181</v>
+        <v>502</v>
       </c>
     </row>
     <row r="51" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25580,7 +25805,7 @@
         <v>125</v>
       </c>
       <c r="D51" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E51" s="11" t="str">
         <f t="array" aca="1" ref="E51" ca="1">_FV(A51,"Abreviatura de intercambio",TRUE())</f>
@@ -25755,14 +25980,14 @@
         <v>0.24</v>
       </c>
       <c r="BD51" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="BE51" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF51" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="BG51" s="23">
         <f t="shared" si="42"/>
@@ -25791,13 +26016,13 @@
         <v>0.26370364004104818</v>
       </c>
       <c r="BN51" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO51" s="93" t="s">
-        <v>212</v>
+        <v>503</v>
       </c>
       <c r="BP51" s="93" t="s">
-        <v>234</v>
+        <v>504</v>
       </c>
     </row>
     <row r="52" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25987,7 +26212,7 @@
         <v>0.40857142857142859</v>
       </c>
       <c r="BD52" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="BE52" s="23">
         <f t="shared" si="41"/>
@@ -26023,13 +26248,13 @@
         <v>-2.4636655998681367E-2</v>
       </c>
       <c r="BN52" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO52" s="93" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="BP52" s="93" t="s">
-        <v>181</v>
+        <v>505</v>
       </c>
     </row>
     <row r="53" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26041,7 +26266,7 @@
         <v>FERG</v>
       </c>
       <c r="C53" s="88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D53" s="88" t="s">
         <v>96</v>
@@ -26219,14 +26444,14 @@
         <v>0.23333333333333334</v>
       </c>
       <c r="BD53" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="BE53" s="23">
         <f t="shared" si="41"/>
         <v>9.966033447608158E-3</v>
       </c>
       <c r="BF53" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="BG53" s="23">
         <f t="shared" si="42"/>
@@ -26255,13 +26480,13 @@
         <v>0.11134685123661803</v>
       </c>
       <c r="BN53" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO53" s="93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BP53" s="93" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26451,14 +26676,14 @@
         <v>-1.3333333333333334E-2</v>
       </c>
       <c r="BD54" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="BE54" s="23">
         <f t="shared" si="41"/>
         <v>7.8625221439269977E-2</v>
       </c>
       <c r="BF54" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="BG54" s="23">
         <f t="shared" si="42"/>
@@ -26487,13 +26712,13 @@
         <v>3.431391125000971E-2</v>
       </c>
       <c r="BN54" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO54" t="s">
         <v>99</v>
       </c>
       <c r="BP54" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="55" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26505,7 +26730,7 @@
         <v>TREX</v>
       </c>
       <c r="C55" s="88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D55" s="88" t="s">
         <v>77</v>
@@ -26683,14 +26908,14 @@
         <v>0.21111111111111114</v>
       </c>
       <c r="BD55" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="BE55" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF55" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="BG55" s="23">
         <f t="shared" si="42"/>
@@ -26719,13 +26944,13 @@
         <v>8.3315115618449731E-2</v>
       </c>
       <c r="BN55" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO55" s="93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BP55" s="93" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26737,10 +26962,10 @@
         <v>SGO</v>
       </c>
       <c r="C56" s="88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D56" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E56" s="11" t="str">
         <f t="array" aca="1" ref="E56" ca="1">_FV(A56,"Abreviatura de intercambio",TRUE())</f>
@@ -26915,14 +27140,14 @@
         <v>0.10714285714285714</v>
       </c>
       <c r="BD56" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="BE56" s="23">
         <f t="shared" si="41"/>
         <v>9.966033447608158E-3</v>
       </c>
       <c r="BF56" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="BG56" s="23">
         <f t="shared" si="42"/>
@@ -26951,7 +27176,7 @@
         <v>7.0454949447204207E-2</v>
       </c>
       <c r="BN56" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO56" s="93" t="s">
         <v>113</v>
@@ -26969,10 +27194,10 @@
         <v>TFF</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E57" s="11" t="str">
         <f t="array" aca="1" ref="E57" ca="1">_FV(A57,"Abreviatura de intercambio",TRUE())</f>
@@ -27147,14 +27372,14 @@
         <v>0.04</v>
       </c>
       <c r="BD57" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="BE57" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF57" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="BG57" s="23">
         <f t="shared" si="42"/>
@@ -27183,13 +27408,13 @@
         <v>-0.12010740028521605</v>
       </c>
       <c r="BN57" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO57" s="93" t="s">
-        <v>162</v>
+        <v>506</v>
       </c>
       <c r="BP57" s="93" t="s">
-        <v>162</v>
+        <v>507</v>
       </c>
     </row>
     <row r="58" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27379,14 +27604,14 @@
         <v>0.3</v>
       </c>
       <c r="BD58" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="BE58" s="23">
         <f t="shared" si="41"/>
         <v>7.9831440532173836E-2</v>
       </c>
       <c r="BF58" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="BG58" s="23">
         <f t="shared" si="42"/>
@@ -27415,13 +27640,13 @@
         <v>0.27964014265382842</v>
       </c>
       <c r="BN58" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="BO58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BP58" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="59" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27433,7 +27658,7 @@
         <v>BFIT</v>
       </c>
       <c r="C59" s="88" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D59" s="88" t="s">
         <v>110</v>
@@ -27611,14 +27836,14 @@
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="BD59" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="BE59" s="23">
         <f t="shared" si="41"/>
         <v>1.9244876491456564E-2</v>
       </c>
       <c r="BF59" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="BG59" s="23">
         <f t="shared" si="42"/>
@@ -27653,7 +27878,7 @@
         <v>102</v>
       </c>
       <c r="BP59" s="93" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="60" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27665,10 +27890,10 @@
         <v>VRLA</v>
       </c>
       <c r="C60" s="88" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D60" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E60" s="11" t="str">
         <f t="array" aca="1" ref="E60" ca="1">_FV(A60,"Abreviatura de intercambio",TRUE())</f>
@@ -27882,10 +28107,10 @@
         <v>81</v>
       </c>
       <c r="BO60" s="93" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BP60" s="93" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="61" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27897,10 +28122,10 @@
         <v>KIST</v>
       </c>
       <c r="C61" s="88" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D61" s="88" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E61" s="11" t="str">
         <f t="array" aca="1" ref="E61" ca="1">_FV(A61,"Abreviatura de intercambio",TRUE())</f>
@@ -28113,13 +28338,13 @@
         <v>0.37985089166123109</v>
       </c>
       <c r="BN61" s="93" t="s">
-        <v>81</v>
+        <v>497</v>
       </c>
       <c r="BO61" s="93" t="s">
-        <v>162</v>
+        <v>508</v>
       </c>
       <c r="BP61" s="93" t="s">
-        <v>162</v>
+        <v>504</v>
       </c>
     </row>
     <row r="62" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28134,7 +28359,7 @@
         <v>125</v>
       </c>
       <c r="D62" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E62" s="11" t="str">
         <f t="array" aca="1" ref="E62" ca="1">_FV(A62,"Abreviatura de intercambio",TRUE())</f>
@@ -28309,14 +28534,14 @@
         <v>8.8888888888888878E-2</v>
       </c>
       <c r="BD62" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="BE62" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF62" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="BG62" s="23">
         <f t="shared" si="42"/>
@@ -28345,13 +28570,13 @@
         <v>8.1957952078739016E-2</v>
       </c>
       <c r="BN62" t="s">
-        <v>425</v>
+        <v>497</v>
       </c>
       <c r="BO62" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="BP62" t="s">
-        <v>253</v>
+        <v>509</v>
       </c>
     </row>
     <row r="63" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28363,10 +28588,10 @@
         <v>IPCO</v>
       </c>
       <c r="C63" s="88" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D63" s="88" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E63" s="11" t="str">
         <f t="array" aca="1" ref="E63" ca="1">_FV(A63,"Abreviatura de intercambio",TRUE())</f>
@@ -28541,14 +28766,14 @@
         <v>9.4444444444444442E-2</v>
       </c>
       <c r="BD63" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="BE63" s="23">
         <f t="shared" si="41"/>
         <v>-4.9967563918014046E-2</v>
       </c>
       <c r="BF63" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="BG63" s="23">
         <f t="shared" si="42"/>
@@ -28577,13 +28802,13 @@
         <v>0.12024588148725956</v>
       </c>
       <c r="BN63" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO63" s="93" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BP63" s="93" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="64" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28598,7 +28823,7 @@
         <v>125</v>
       </c>
       <c r="D64" s="88" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E64" s="11" t="str">
         <f t="array" aca="1" ref="E64" ca="1">_FV(A64,"Abreviatura de intercambio",TRUE())</f>
@@ -28773,14 +28998,14 @@
         <v>-0.15384615384615383</v>
       </c>
       <c r="BD64" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="BE64" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF64" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="BG64" s="23">
         <f t="shared" si="42"/>
@@ -28809,13 +29034,13 @@
         <v>0.60646057206184456</v>
       </c>
       <c r="BN64" s="93" t="s">
-        <v>427</v>
+        <v>497</v>
       </c>
       <c r="BO64" s="93" t="s">
         <v>85</v>
       </c>
       <c r="BP64" s="93" t="s">
-        <v>428</v>
+        <v>510</v>
       </c>
     </row>
     <row r="65" spans="1:68" x14ac:dyDescent="0.25">
@@ -28823,7 +29048,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C65" s="88" t="s">
         <v>76</v>
@@ -28832,10 +29057,10 @@
         <v>77</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G65" s="12">
         <v>2600</v>
@@ -29036,13 +29261,13 @@
         <v>0.45488435118754245</v>
       </c>
       <c r="BN65" s="93" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="BO65" s="93" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="BP65" s="93" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -29075,7 +29300,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="100" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -29085,12 +29310,12 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D4" t="e" vm="63">
         <v>#VALUE!</v>
@@ -29102,7 +29327,7 @@
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D5" t="e" vm="64">
         <v>#VALUE!</v>
@@ -29114,7 +29339,7 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D6" t="e" vm="65">
         <v>#VALUE!</v>
@@ -29135,7 +29360,7 @@
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D8" t="e" vm="67">
         <v>#VALUE!</v>
@@ -29147,197 +29372,197 @@
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="28" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="28" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="28" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="28" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -29366,8 +29591,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="162" t="s">
-        <v>309</v>
+      <c r="A1" s="107" t="s">
+        <v>303</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -29388,276 +29613,276 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="150" t="s">
-        <v>310</v>
-      </c>
-      <c r="B2" s="151"/>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="151"/>
-      <c r="K2" s="151"/>
-      <c r="L2" s="151"/>
+      <c r="A2" s="124" t="s">
+        <v>304</v>
+      </c>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
     </row>
     <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="155" t="s">
-        <v>311</v>
-      </c>
-      <c r="B3" s="126"/>
-      <c r="C3" s="125" t="s">
-        <v>312</v>
-      </c>
-      <c r="D3" s="126"/>
-      <c r="E3" s="127" t="s">
-        <v>313</v>
-      </c>
-      <c r="F3" s="126"/>
-      <c r="G3" s="170" t="s">
-        <v>314</v>
-      </c>
-      <c r="H3" s="126"/>
-      <c r="I3" s="171" t="s">
-        <v>315</v>
-      </c>
-      <c r="J3" s="126"/>
-      <c r="K3" s="134" t="s">
-        <v>316</v>
-      </c>
-      <c r="L3" s="135"/>
+      <c r="A3" s="130" t="s">
+        <v>305</v>
+      </c>
+      <c r="B3" s="119"/>
+      <c r="C3" s="151" t="s">
+        <v>306</v>
+      </c>
+      <c r="D3" s="119"/>
+      <c r="E3" s="152" t="s">
+        <v>307</v>
+      </c>
+      <c r="F3" s="119"/>
+      <c r="G3" s="118" t="s">
+        <v>308</v>
+      </c>
+      <c r="H3" s="119"/>
+      <c r="I3" s="120" t="s">
+        <v>309</v>
+      </c>
+      <c r="J3" s="119"/>
+      <c r="K3" s="156" t="s">
+        <v>310</v>
+      </c>
+      <c r="L3" s="157"/>
     </row>
     <row r="4" spans="1:47" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="159">
+      <c r="A4" s="137">
         <f ca="1">COUNTA('Watchlist Ratings'!B4:B64)</f>
         <v>61</v>
       </c>
-      <c r="B4" s="129"/>
-      <c r="C4" s="130">
+      <c r="B4" s="122"/>
+      <c r="C4" s="153">
         <f>ROUND(AVERAGE('Watchlist Ratings'!AN4:AN64),2)</f>
         <v>5.94</v>
       </c>
-      <c r="D4" s="129"/>
-      <c r="E4" s="131" t="str">
+      <c r="D4" s="122"/>
+      <c r="E4" s="123" t="str">
         <f>TEXT(AVERAGE('Watchlist Ratings'!BC4:BC64),"0.0%")</f>
         <v>22.3%</v>
       </c>
-      <c r="F4" s="129"/>
-      <c r="G4" s="131" t="str">
+      <c r="F4" s="122"/>
+      <c r="G4" s="123" t="str">
         <f ca="1">TEXT(AVERAGE('Watchlist Ratings'!AW4:AW64),"0.0x")</f>
         <v>36.4x</v>
       </c>
-      <c r="H4" s="129"/>
-      <c r="I4" s="131">
+      <c r="H4" s="122"/>
+      <c r="I4" s="123">
         <f ca="1">COUNTIF('Watchlist Ratings'!BM4:BM64,"&gt;0")</f>
         <v>53</v>
       </c>
-      <c r="J4" s="129"/>
-      <c r="K4" s="163">
+      <c r="J4" s="122"/>
+      <c r="K4" s="108">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN64,"&gt;7.5")</f>
         <v>15</v>
       </c>
-      <c r="L4" s="137"/>
+      <c r="L4" s="109"/>
     </row>
     <row r="5" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="157" t="s">
-        <v>317</v>
-      </c>
-      <c r="B5" s="129"/>
-      <c r="C5" s="128" t="s">
-        <v>318</v>
-      </c>
-      <c r="D5" s="129"/>
-      <c r="E5" s="128" t="s">
-        <v>319</v>
-      </c>
-      <c r="F5" s="129"/>
-      <c r="G5" s="128" t="s">
-        <v>320</v>
-      </c>
-      <c r="H5" s="129"/>
-      <c r="I5" s="128" t="s">
-        <v>321</v>
-      </c>
-      <c r="J5" s="129"/>
-      <c r="K5" s="136" t="s">
-        <v>322</v>
-      </c>
-      <c r="L5" s="137"/>
+      <c r="A5" s="133" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5" s="122"/>
+      <c r="C5" s="121" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="122"/>
+      <c r="E5" s="121" t="s">
+        <v>313</v>
+      </c>
+      <c r="F5" s="122"/>
+      <c r="G5" s="121" t="s">
+        <v>314</v>
+      </c>
+      <c r="H5" s="122"/>
+      <c r="I5" s="121" t="s">
+        <v>315</v>
+      </c>
+      <c r="J5" s="122"/>
+      <c r="K5" s="158" t="s">
+        <v>316</v>
+      </c>
+      <c r="L5" s="109"/>
     </row>
     <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="167" t="s">
+      <c r="A6" s="114" t="s">
+        <v>317</v>
+      </c>
+      <c r="B6" s="115"/>
+      <c r="C6" s="131" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6" s="115"/>
+      <c r="E6" s="131" t="s">
+        <v>319</v>
+      </c>
+      <c r="F6" s="115"/>
+      <c r="G6" s="117" t="s">
+        <v>320</v>
+      </c>
+      <c r="H6" s="115"/>
+      <c r="I6" s="131" t="s">
+        <v>321</v>
+      </c>
+      <c r="J6" s="115"/>
+      <c r="K6" s="154" t="s">
+        <v>322</v>
+      </c>
+      <c r="L6" s="155"/>
+      <c r="O6" t="s">
         <v>323</v>
       </c>
-      <c r="B6" s="108"/>
-      <c r="C6" s="107" t="s">
+      <c r="S6" t="s">
         <v>324</v>
       </c>
-      <c r="D6" s="108"/>
-      <c r="E6" s="107" t="s">
+      <c r="V6" t="s">
         <v>325</v>
       </c>
-      <c r="F6" s="108"/>
-      <c r="G6" s="169" t="s">
+      <c r="Y6" t="s">
         <v>326</v>
       </c>
-      <c r="H6" s="108"/>
-      <c r="I6" s="107" t="s">
+      <c r="AA6" t="s">
         <v>327</v>
       </c>
-      <c r="J6" s="108"/>
-      <c r="K6" s="132" t="s">
+      <c r="AE6" t="s">
         <v>328</v>
       </c>
-      <c r="L6" s="133"/>
-      <c r="O6" t="s">
+      <c r="AF6" t="s">
         <v>329</v>
       </c>
-      <c r="S6" t="s">
+      <c r="AH6" t="s">
+        <v>328</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>329</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>328</v>
+      </c>
+      <c r="AK6" t="s">
         <v>330</v>
       </c>
-      <c r="V6" t="s">
+      <c r="AL6" t="s">
         <v>331</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AM6" t="s">
+        <v>328</v>
+      </c>
+      <c r="AN6" t="s">
         <v>332</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AO6" t="s">
+        <v>328</v>
+      </c>
+      <c r="AP6" t="s">
         <v>333</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AQ6" t="s">
         <v>334</v>
       </c>
-      <c r="AF6" t="s">
-        <v>335</v>
-      </c>
-      <c r="AH6" t="s">
+      <c r="AS6" t="s">
+        <v>328</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>332</v>
+      </c>
+      <c r="AU6" t="s">
         <v>334</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>335</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>334</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>336</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>337</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>334</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>338</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>334</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>339</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>340</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>334</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>338</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="I7" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="K7" s="36"/>
       <c r="O7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="P7" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="Q7" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="S7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="T7" t="s">
         <v>62</v>
       </c>
       <c r="V7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="W7" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="X7" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="Y7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="Z7" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="AA7" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="AB7" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="AC7" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="AE7" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AF7">
         <v>83.3333333333333</v>
       </c>
       <c r="AH7" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="AI7">
         <v>83.3</v>
       </c>
       <c r="AJ7" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AK7">
         <v>8</v>
@@ -29666,13 +29891,13 @@
         <v>3</v>
       </c>
       <c r="AM7" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AN7">
         <v>52.2</v>
       </c>
       <c r="AO7" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AP7">
         <v>4.5</v>
@@ -29681,7 +29906,7 @@
         <v>33.6</v>
       </c>
       <c r="AS7" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AT7">
         <v>20.173600073636401</v>
@@ -29691,8 +29916,8 @@
       </c>
     </row>
     <row r="8" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="168" t="s">
-        <v>352</v>
+      <c r="A8" s="116" t="s">
+        <v>346</v>
       </c>
       <c r="B8" s="96"/>
       <c r="C8" s="96"/>
@@ -29758,19 +29983,19 @@
         <v>0.35404498597134726</v>
       </c>
       <c r="AE8" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AF8">
         <v>83.3333333333333</v>
       </c>
       <c r="AH8" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AI8">
         <v>83.3</v>
       </c>
       <c r="AJ8" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -29779,13 +30004,13 @@
         <v>3</v>
       </c>
       <c r="AM8" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AN8">
         <v>51.1</v>
       </c>
       <c r="AO8" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AP8">
         <v>3.7</v>
@@ -29794,7 +30019,7 @@
         <v>32.4</v>
       </c>
       <c r="AS8" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AT8">
         <v>44.5724369425714</v>
@@ -29896,19 +30121,19 @@
         <v>0.13667813232291248</v>
       </c>
       <c r="AE9" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="AF9">
         <v>59.375</v>
       </c>
       <c r="AH9" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="AI9">
         <v>59.4</v>
       </c>
       <c r="AJ9" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AK9">
         <v>8</v>
@@ -29917,13 +30142,13 @@
         <v>1</v>
       </c>
       <c r="AM9" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AN9">
         <v>45.6</v>
       </c>
       <c r="AO9" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AP9">
         <v>1.1000000000000001</v>
@@ -29932,7 +30157,7 @@
         <v>28.4</v>
       </c>
       <c r="AS9" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AT9">
         <v>28.571278521519002</v>
@@ -30034,19 +30259,19 @@
         <v>0.33962554586669502</v>
       </c>
       <c r="AE10" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AF10">
         <v>54</v>
       </c>
       <c r="AH10" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="AI10">
         <v>54</v>
       </c>
       <c r="AJ10" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AK10">
         <v>8</v>
@@ -30055,13 +30280,13 @@
         <v>3</v>
       </c>
       <c r="AM10" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AN10">
         <v>44.8</v>
       </c>
       <c r="AO10" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AP10">
         <v>1.8</v>
@@ -30070,7 +30295,7 @@
         <v>25</v>
       </c>
       <c r="AS10" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AT10">
         <v>24.369253736000001</v>
@@ -30172,19 +30397,19 @@
         <v>0.25482976969404003</v>
       </c>
       <c r="AE11" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AF11">
         <v>41.6666666666667</v>
       </c>
       <c r="AH11" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="AI11">
         <v>41.7</v>
       </c>
       <c r="AJ11" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AK11">
         <v>8</v>
@@ -30193,13 +30418,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AN11">
         <v>43.6</v>
       </c>
       <c r="AO11" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AP11">
         <v>0.6</v>
@@ -30208,7 +30433,7 @@
         <v>23.3</v>
       </c>
       <c r="AS11" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="AT11">
         <v>51.179748126470599</v>
@@ -30310,19 +30535,19 @@
         <v>1.7035846360751394E-2</v>
       </c>
       <c r="AE12" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AF12">
         <v>38.3333333333333</v>
       </c>
       <c r="AH12" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AI12">
         <v>38.299999999999997</v>
       </c>
       <c r="AJ12" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="AK12">
         <v>7</v>
@@ -30331,13 +30556,13 @@
         <v>3</v>
       </c>
       <c r="AM12" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="AN12">
         <v>40.299999999999997</v>
       </c>
       <c r="AO12" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="AP12">
         <v>-0.1</v>
@@ -30346,7 +30571,7 @@
         <v>20.8</v>
       </c>
       <c r="AS12" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="AT12">
         <v>25.7039266520833</v>
@@ -30396,10 +30621,10 @@
         <v>22.692192080416664</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="M13" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -30454,19 +30679,19 @@
         <v>0.24553423525971096</v>
       </c>
       <c r="AE13" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AF13">
         <v>37.5</v>
       </c>
       <c r="AH13" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="AI13">
         <v>37.5</v>
       </c>
       <c r="AJ13" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="AK13">
         <v>7</v>
@@ -30475,13 +30700,13 @@
         <v>3</v>
       </c>
       <c r="AM13" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="AN13">
         <v>38.9</v>
       </c>
       <c r="AO13" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="AP13">
         <v>4.7</v>
@@ -30490,7 +30715,7 @@
         <v>32.9</v>
       </c>
       <c r="AS13" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AT13">
         <v>29.589673076923098</v>
@@ -30540,7 +30765,7 @@
         <v>27.293807692307691</v>
       </c>
       <c r="L14" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="M14">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN64,"&gt;=8")</f>
@@ -30599,19 +30824,19 @@
         <v>0.15723005465088957</v>
       </c>
       <c r="AE14" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AF14">
         <v>37.142857142857103</v>
       </c>
       <c r="AH14" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="AI14">
         <v>37.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="AK14">
         <v>7</v>
@@ -30620,13 +30845,13 @@
         <v>2</v>
       </c>
       <c r="AM14" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AN14">
         <v>38.5</v>
       </c>
       <c r="AO14" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AP14">
         <v>-4.2</v>
@@ -30635,7 +30860,7 @@
         <v>13.7</v>
       </c>
       <c r="AS14" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="AT14">
         <v>26.244954871232899</v>
@@ -30685,7 +30910,7 @@
         <v>24.661489883561643</v>
       </c>
       <c r="L15" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="M15">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN64,"&gt;=7",'Watchlist Ratings'!AN4:AN64,"&lt;8")</f>
@@ -30744,19 +30969,19 @@
         <v>0.34414353629850369</v>
       </c>
       <c r="AE15" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AF15">
         <v>36.1111111111111</v>
       </c>
       <c r="AH15" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AI15">
         <v>36.1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AK15">
         <v>7</v>
@@ -30765,13 +30990,13 @@
         <v>2</v>
       </c>
       <c r="AM15" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AN15">
         <v>37.700000000000003</v>
       </c>
       <c r="AO15" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AP15">
         <v>-8</v>
@@ -30780,7 +31005,7 @@
         <v>13.5</v>
       </c>
       <c r="AS15" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AT15">
         <v>27.905545425233299</v>
@@ -30830,7 +31055,7 @@
         <v>21.185176984260604</v>
       </c>
       <c r="L16" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="M16">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN64,"&gt;=6",'Watchlist Ratings'!AN4:AN64,"&lt;7")</f>
@@ -30889,19 +31114,19 @@
         <v>0.1501292474376974</v>
       </c>
       <c r="AE16" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AF16">
         <v>32.142857142857103</v>
       </c>
       <c r="AH16" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="AI16">
         <v>32.1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="AK16">
         <v>7</v>
@@ -30910,13 +31135,13 @@
         <v>3</v>
       </c>
       <c r="AM16" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="AN16">
         <v>29.6</v>
       </c>
       <c r="AO16" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AP16">
         <v>-7.9</v>
@@ -30925,7 +31150,7 @@
         <v>12.3</v>
       </c>
       <c r="AS16" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="AT16">
         <v>52.2229498644231</v>
@@ -30975,7 +31200,7 @@
         <v>48.141288886538462</v>
       </c>
       <c r="L17" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="M17">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN64,"&lt;6")</f>
@@ -31034,7 +31259,7 @@
         <v>6.9229397135512238E-2</v>
       </c>
       <c r="AS17" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="AT17">
         <v>37.736707694444398</v>
@@ -31128,7 +31353,7 @@
         <v>5.0833735875018826E-2</v>
       </c>
       <c r="AS18" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="AT18">
         <v>24.612029698461502</v>
@@ -31222,7 +31447,7 @@
         <v>0.13663154593919979</v>
       </c>
       <c r="AS19" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="AT19">
         <v>45.617441111111098</v>
@@ -31316,7 +31541,7 @@
         <v>5.2655928593337009E-3</v>
       </c>
       <c r="AS20" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="AT20">
         <v>43.630936634999998</v>
@@ -31410,7 +31635,7 @@
         <v>8.6208283772470695E-2</v>
       </c>
       <c r="AS21" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="AT21">
         <v>38.120501266027397</v>
@@ -31519,8 +31744,8 @@
       </c>
     </row>
     <row r="24" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="161" t="s">
-        <v>379</v>
+      <c r="A24" s="106" t="s">
+        <v>373</v>
       </c>
       <c r="B24" s="96"/>
       <c r="C24" s="96"/>
@@ -31595,7 +31820,7 @@
     <row r="38" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L40" s="109"/>
+      <c r="L40" s="169"/>
       <c r="M40" s="96"/>
       <c r="N40" s="96"/>
       <c r="O40" s="96"/>
@@ -31612,7 +31837,7 @@
       <c r="Q41" s="57"/>
     </row>
     <row r="42" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J42" s="116"/>
+      <c r="J42" s="171"/>
       <c r="K42" s="96"/>
       <c r="L42" s="96"/>
       <c r="M42" s="96"/>
@@ -31697,8 +31922,8 @@
     <row r="60" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="142" t="s">
-        <v>380</v>
+      <c r="A62" s="141" t="s">
+        <v>374</v>
       </c>
       <c r="B62" s="96"/>
       <c r="C62" s="96"/>
@@ -31707,8 +31932,8 @@
       <c r="F62" s="96"/>
       <c r="G62" s="96"/>
       <c r="H62" s="96"/>
-      <c r="J62" s="147" t="s">
-        <v>381</v>
+      <c r="J62" s="148" t="s">
+        <v>375</v>
       </c>
       <c r="K62" s="96"/>
       <c r="L62" s="96"/>
@@ -31720,52 +31945,52 @@
     </row>
     <row r="63" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="61" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B63" s="61" t="s">
+        <v>376</v>
+      </c>
+      <c r="C63" s="61" t="s">
+        <v>377</v>
+      </c>
+      <c r="D63" s="61" t="s">
+        <v>378</v>
+      </c>
+      <c r="E63" s="61" t="s">
+        <v>342</v>
+      </c>
+      <c r="F63" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="G63" s="61" t="s">
+        <v>379</v>
+      </c>
+      <c r="H63" s="61" t="s">
+        <v>380</v>
+      </c>
+      <c r="J63" s="62" t="s">
+        <v>328</v>
+      </c>
+      <c r="K63" s="62" t="s">
+        <v>381</v>
+      </c>
+      <c r="L63" s="62" t="s">
         <v>382</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="M63" s="62" t="s">
         <v>383</v>
       </c>
-      <c r="D63" s="61" t="s">
+      <c r="N63" s="62" t="s">
         <v>384</v>
       </c>
-      <c r="E63" s="61" t="s">
-        <v>348</v>
-      </c>
-      <c r="F63" s="61" t="s">
-        <v>347</v>
-      </c>
-      <c r="G63" s="61" t="s">
+      <c r="O63" s="62" t="s">
+        <v>330</v>
+      </c>
+      <c r="P63" s="62" t="s">
         <v>385</v>
       </c>
-      <c r="H63" s="61" t="s">
+      <c r="Q63" s="62" t="s">
         <v>386</v>
-      </c>
-      <c r="J63" s="62" t="s">
-        <v>334</v>
-      </c>
-      <c r="K63" s="62" t="s">
-        <v>387</v>
-      </c>
-      <c r="L63" s="62" t="s">
-        <v>388</v>
-      </c>
-      <c r="M63" s="62" t="s">
-        <v>389</v>
-      </c>
-      <c r="N63" s="62" t="s">
-        <v>390</v>
-      </c>
-      <c r="O63" s="62" t="s">
-        <v>336</v>
-      </c>
-      <c r="P63" s="62" t="s">
-        <v>391</v>
-      </c>
-      <c r="Q63" s="62" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -32297,29 +32522,29 @@
       </c>
     </row>
     <row r="72" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="138" t="str">
+      <c r="A72" s="159" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="B72" s="111"/>
-      <c r="C72" s="111"/>
-      <c r="D72" s="111"/>
-      <c r="E72" s="111"/>
-      <c r="F72" s="111"/>
-      <c r="G72" s="111"/>
-      <c r="H72" s="111"/>
-      <c r="I72" s="112"/>
-      <c r="J72" s="110" t="str">
+      <c r="B72" s="160"/>
+      <c r="C72" s="160"/>
+      <c r="D72" s="160"/>
+      <c r="E72" s="160"/>
+      <c r="F72" s="160"/>
+      <c r="G72" s="160"/>
+      <c r="H72" s="160"/>
+      <c r="I72" s="161"/>
+      <c r="J72" s="170" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="K72" s="111"/>
-      <c r="L72" s="111"/>
-      <c r="M72" s="111"/>
-      <c r="N72" s="111"/>
-      <c r="O72" s="111"/>
-      <c r="P72" s="111"/>
-      <c r="Q72" s="112"/>
+      <c r="K72" s="160"/>
+      <c r="L72" s="160"/>
+      <c r="M72" s="160"/>
+      <c r="N72" s="160"/>
+      <c r="O72" s="160"/>
+      <c r="P72" s="160"/>
+      <c r="Q72" s="161"/>
     </row>
     <row r="73" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="68" t="str">
@@ -32389,7 +32614,7 @@
     </row>
     <row r="74" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="75" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B74" s="76" t="str">
         <f ca="1">VLOOKUP(A74,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32420,7 +32645,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J74" s="78" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="K74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -32453,7 +32678,7 @@
     </row>
     <row r="75" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="79" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B75" s="80" t="str">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32484,7 +32709,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J75" s="79" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="K75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -32516,8 +32741,8 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="158" t="s">
-        <v>393</v>
+      <c r="A76" s="134" t="s">
+        <v>387</v>
       </c>
       <c r="B76" s="96"/>
       <c r="C76" s="96"/>
@@ -32538,7 +32763,7 @@
     </row>
     <row r="77" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="79" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B77" s="80" t="str">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32569,7 +32794,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J77" s="79" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="K77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -32601,130 +32826,130 @@
       </c>
     </row>
     <row r="78" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="105" t="s">
+      <c r="A78" s="126" t="s">
+        <v>388</v>
+      </c>
+      <c r="B78" s="111"/>
+      <c r="C78" s="110" t="s">
+        <v>389</v>
+      </c>
+      <c r="D78" s="111"/>
+      <c r="E78" s="129" t="s">
+        <v>390</v>
+      </c>
+      <c r="F78" s="111"/>
+      <c r="G78" s="129" t="s">
+        <v>391</v>
+      </c>
+      <c r="H78" s="111"/>
+      <c r="I78" s="162" t="s">
+        <v>392</v>
+      </c>
+      <c r="J78" s="96"/>
+      <c r="K78" s="126" t="s">
+        <v>393</v>
+      </c>
+      <c r="L78" s="111"/>
+      <c r="M78" s="126" t="s">
         <v>394</v>
       </c>
-      <c r="B78" s="106"/>
-      <c r="C78" s="164" t="s">
+      <c r="N78" s="111"/>
+      <c r="O78" s="126" t="s">
         <v>395</v>
       </c>
-      <c r="D78" s="106"/>
-      <c r="E78" s="154" t="s">
-        <v>396</v>
-      </c>
-      <c r="F78" s="106"/>
-      <c r="G78" s="154" t="s">
-        <v>397</v>
-      </c>
-      <c r="H78" s="106"/>
-      <c r="I78" s="139" t="s">
-        <v>398</v>
-      </c>
-      <c r="J78" s="96"/>
-      <c r="K78" s="105" t="s">
-        <v>399</v>
-      </c>
-      <c r="L78" s="106"/>
-      <c r="M78" s="105" t="s">
-        <v>400</v>
-      </c>
-      <c r="N78" s="106"/>
-      <c r="O78" s="105" t="s">
-        <v>401</v>
-      </c>
-      <c r="P78" s="106"/>
+      <c r="P78" s="111"/>
       <c r="Q78" s="82" t="str">
         <f>IF(K78&gt;=8.5,"🟢 ALTO",IF(K78&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="118" t="str">
+      <c r="A79" s="135" t="str">
         <f>INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AN:AN),'Watchlist Ratings'!AN:AN,0))</f>
         <v>CSU</v>
       </c>
-      <c r="B79" s="106"/>
-      <c r="C79" s="117" t="str">
+      <c r="B79" s="111"/>
+      <c r="C79" s="163" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM:BM),'Watchlist Ratings'!BM:BM,0))</f>
         <v>OTLY</v>
       </c>
-      <c r="D79" s="106"/>
-      <c r="E79" s="119" t="str">
+      <c r="D79" s="111"/>
+      <c r="E79" s="136" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BC:BC),'Watchlist Ratings'!BC:BC,0))</f>
         <v>NVDA</v>
       </c>
-      <c r="F79" s="106"/>
-      <c r="G79" s="119" t="str">
+      <c r="F79" s="111"/>
+      <c r="G79" s="136" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!K:K),'Watchlist Ratings'!K:K,0))</f>
         <v>VEEV</v>
       </c>
-      <c r="H79" s="106"/>
-      <c r="I79" s="146" t="str">
+      <c r="H79" s="111"/>
+      <c r="I79" s="147" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!L:L),'Watchlist Ratings'!L:L,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J79" s="96"/>
-      <c r="K79" s="118" t="str">
+      <c r="K79" s="135" t="str">
         <f>INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AM:AM),'Watchlist Ratings'!AM:AM,0))</f>
         <v>CSU</v>
       </c>
-      <c r="L79" s="106"/>
-      <c r="M79" s="118" t="str">
+      <c r="L79" s="111"/>
+      <c r="M79" s="135" t="str">
         <f t="array" aca="1" ref="M79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MIN('Watchlist Ratings'!AW4:AW64),'Watchlist Ratings'!AW4:AW64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="N79" s="106"/>
-      <c r="O79" s="118" t="str">
+      <c r="N79" s="111"/>
+      <c r="O79" s="135" t="str">
         <f t="array" aca="1" ref="O79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),'Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="P79" s="106"/>
+      <c r="P79" s="111"/>
       <c r="Q79" s="79" t="str">
         <f>IF(K79&gt;=8.5,"🟢 ALTO",IF(K79&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="152">
+      <c r="A80" s="127">
         <f>MAX('Watchlist Ratings'!AN:AN)</f>
         <v>8.5500000000000007</v>
       </c>
-      <c r="B80" s="106"/>
-      <c r="C80" s="153">
+      <c r="B80" s="111"/>
+      <c r="C80" s="128">
         <f ca="1">MAX('Watchlist Ratings'!BM:BM)</f>
         <v>0.60646057206184456</v>
       </c>
-      <c r="D80" s="106"/>
-      <c r="E80" s="156">
+      <c r="D80" s="111"/>
+      <c r="E80" s="132">
         <f>MAX('Watchlist Ratings'!BC:BC)</f>
         <v>0.83333333333333326</v>
       </c>
-      <c r="F80" s="106"/>
-      <c r="G80" s="156" t="str">
+      <c r="F80" s="111"/>
+      <c r="G80" s="132" t="str">
         <f>MAX('Watchlist Ratings'!K:K)&amp;"/8"</f>
         <v>8/8</v>
       </c>
-      <c r="H80" s="106"/>
-      <c r="I80" s="121" t="str">
+      <c r="H80" s="111"/>
+      <c r="I80" s="165" t="str">
         <f>MAX('Watchlist Ratings'!L:L)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J80" s="96"/>
-      <c r="K80" s="122">
+      <c r="K80" s="166">
         <f>MAX('Watchlist Ratings'!AM:AM)</f>
         <v>8.86</v>
       </c>
-      <c r="L80" s="106"/>
-      <c r="M80" s="122" t="str">
+      <c r="L80" s="111"/>
+      <c r="M80" s="166" t="str">
         <f ca="1">MIN('Watchlist Ratings'!AW4:AW64)&amp;"x"</f>
         <v>-7.177105x</v>
       </c>
-      <c r="N80" s="106"/>
-      <c r="O80" s="122" t="str">
+      <c r="N80" s="111"/>
+      <c r="O80" s="166" t="str">
         <f t="array" ref="O80" ca="1">TEXT(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),"0.0%")</f>
         <v>282.7%</v>
       </c>
-      <c r="P80" s="106"/>
+      <c r="P80" s="111"/>
       <c r="Q80" s="82" t="str">
         <f>IF(K80&gt;=8.5,"🟢 ALTO",IF(K80&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
@@ -32732,7 +32957,7 @@
     </row>
     <row r="81" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="79" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B81" s="80" t="str">
         <f ca="1">VLOOKUP(A81,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32763,7 +32988,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J81" s="79" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="K81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -32795,8 +33020,8 @@
       </c>
     </row>
     <row r="82" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="123" t="s">
-        <v>402</v>
+      <c r="A82" s="167" t="s">
+        <v>396</v>
       </c>
       <c r="B82" s="96"/>
       <c r="C82" s="96"/>
@@ -32817,7 +33042,7 @@
     </row>
     <row r="83" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="83" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B83" s="84" t="str">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32848,7 +33073,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J83" s="83" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="K83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -32881,8 +33106,8 @@
     </row>
     <row r="84" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="85" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="145" t="s">
-        <v>393</v>
+      <c r="A85" s="146" t="s">
+        <v>387</v>
       </c>
       <c r="B85" s="96"/>
       <c r="C85" s="96"/>
@@ -32903,118 +33128,118 @@
     </row>
     <row r="86" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="124" t="s">
+      <c r="A87" s="168" t="s">
+        <v>388</v>
+      </c>
+      <c r="B87" s="96"/>
+      <c r="C87" s="113" t="s">
+        <v>389</v>
+      </c>
+      <c r="D87" s="96"/>
+      <c r="E87" s="164" t="s">
+        <v>390</v>
+      </c>
+      <c r="F87" s="96"/>
+      <c r="G87" s="142" t="s">
+        <v>391</v>
+      </c>
+      <c r="H87" s="96"/>
+      <c r="I87" s="143" t="s">
+        <v>392</v>
+      </c>
+      <c r="J87" s="96"/>
+      <c r="K87" s="112" t="s">
+        <v>393</v>
+      </c>
+      <c r="L87" s="96"/>
+      <c r="M87" s="139" t="s">
         <v>394</v>
       </c>
-      <c r="B87" s="96"/>
-      <c r="C87" s="166" t="s">
+      <c r="N87" s="96"/>
+      <c r="O87" s="149" t="s">
         <v>395</v>
-      </c>
-      <c r="D87" s="96"/>
-      <c r="E87" s="120" t="s">
-        <v>396</v>
-      </c>
-      <c r="F87" s="96"/>
-      <c r="G87" s="143" t="s">
-        <v>397</v>
-      </c>
-      <c r="H87" s="96"/>
-      <c r="I87" s="144" t="s">
-        <v>398</v>
-      </c>
-      <c r="J87" s="96"/>
-      <c r="K87" s="165" t="s">
-        <v>399</v>
-      </c>
-      <c r="L87" s="96"/>
-      <c r="M87" s="141" t="s">
-        <v>400</v>
-      </c>
-      <c r="N87" s="96"/>
-      <c r="O87" s="148" t="s">
-        <v>401</v>
       </c>
       <c r="P87" s="96"/>
     </row>
     <row r="88" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="115" t="str">
+      <c r="A88" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!AN$4:AN$64),'Watchlist Ratings'!AN$4:AN$64,0))</f>
         <v>VEEV</v>
       </c>
       <c r="B88" s="96"/>
-      <c r="C88" s="149" t="str">
+      <c r="C88" s="150" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!BM$4:BM$64),'Watchlist Ratings'!BM$4:BM$64,0))</f>
         <v>OTLY</v>
       </c>
       <c r="D88" s="96"/>
-      <c r="E88" s="115" t="str">
+      <c r="E88" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!BC$4:BC$64),'Watchlist Ratings'!BC$4:BC$64,0))</f>
         <v>NVDA</v>
       </c>
       <c r="F88" s="96"/>
-      <c r="G88" s="115" t="str">
+      <c r="G88" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!K$4:K$64),'Watchlist Ratings'!K$4:K$64,0))</f>
         <v>VEEV</v>
       </c>
       <c r="H88" s="96"/>
-      <c r="I88" s="115" t="str">
+      <c r="I88" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!L$4:L$64),'Watchlist Ratings'!L$4:L$64,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J88" s="96"/>
-      <c r="K88" s="115" t="str">
+      <c r="K88" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!AM$4:AM$64),'Watchlist Ratings'!AM$4:AM$64,0))</f>
         <v>DSGX</v>
       </c>
       <c r="L88" s="96"/>
-      <c r="M88" s="115" t="str">
+      <c r="M88" s="140" t="str">
         <f t="array" aca="1" ref="M88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64)),IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64),0))</f>
         <v>CHKP</v>
       </c>
       <c r="N88" s="96"/>
-      <c r="O88" s="115" t="str">
+      <c r="O88" s="140" t="str">
         <f t="array" aca="1" ref="O88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64),'Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64,0))</f>
         <v>OTLY</v>
       </c>
       <c r="P88" s="96"/>
     </row>
     <row r="89" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="140">
+      <c r="A89" s="138">
         <f>MAX('Watchlist Ratings'!AN$4:AN$64)</f>
         <v>8.2799999999999994</v>
       </c>
       <c r="B89" s="96"/>
-      <c r="C89" s="114">
+      <c r="C89" s="145">
         <f ca="1">MAX('Watchlist Ratings'!BM$4:BM$64)</f>
         <v>0.60646057206184456</v>
       </c>
       <c r="D89" s="96"/>
-      <c r="E89" s="114">
+      <c r="E89" s="145">
         <f>MAX('Watchlist Ratings'!BC$4:BC$64)</f>
         <v>0.83333333333333326</v>
       </c>
       <c r="F89" s="96"/>
-      <c r="G89" s="113" t="str">
+      <c r="G89" s="144" t="str">
         <f>MAX('Watchlist Ratings'!K$4:K$64)&amp;"/8"</f>
         <v>8/8</v>
       </c>
       <c r="H89" s="96"/>
-      <c r="I89" s="113" t="str">
+      <c r="I89" s="144" t="str">
         <f>MAX('Watchlist Ratings'!L$4:L$64)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J89" s="96"/>
-      <c r="K89" s="113">
+      <c r="K89" s="144">
         <f>MAX('Watchlist Ratings'!AM$4:AM$64)</f>
         <v>8.7100000000000009</v>
       </c>
       <c r="L89" s="96"/>
-      <c r="M89" s="113" t="str">
+      <c r="M89" s="144" t="str">
         <f t="array" aca="1" ref="M89" ca="1">MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64))&amp;"x"</f>
         <v>7.60615703230769x</v>
       </c>
       <c r="N89" s="96"/>
-      <c r="O89" s="113">
+      <c r="O89" s="144">
         <f t="array" ref="O89" ca="1">MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64)</f>
         <v>2.8265964915753719</v>
       </c>
@@ -33022,8 +33247,8 @@
     </row>
     <row r="90" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="160" t="s">
-        <v>402</v>
+      <c r="A91" s="105" t="s">
+        <v>396</v>
       </c>
       <c r="B91" s="96"/>
       <c r="C91" s="96"/>
@@ -33044,6 +33269,76 @@
     </row>
   </sheetData>
   <mergeCells count="86">
+    <mergeCell ref="O78:P78"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="L40:R40"/>
+    <mergeCell ref="J72:Q72"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="O88:P88"/>
+    <mergeCell ref="J42:Q42"/>
+    <mergeCell ref="O89:P89"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="A82:Q82"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="O80:P80"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="A85:Q85"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="J62:Q62"/>
+    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="A76:Q76"/>
+    <mergeCell ref="O79:P79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A91:Q91"/>
     <mergeCell ref="A24:R24"/>
     <mergeCell ref="A1:L1"/>
@@ -33060,76 +33355,6 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="A76:Q76"/>
-    <mergeCell ref="O79:P79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="M87:N87"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="A85:Q85"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="J62:Q62"/>
-    <mergeCell ref="O87:P87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="A82:Q82"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="O80:P80"/>
-    <mergeCell ref="O78:P78"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="L40:R40"/>
-    <mergeCell ref="J72:Q72"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="O88:P88"/>
-    <mergeCell ref="J42:Q42"/>
-    <mergeCell ref="O89:P89"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:F22">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -33172,7 +33397,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -33183,801 +33408,1413 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B2" t="s">
         <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D2" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="E2" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="B3" t="s">
         <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D3" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E3" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D4" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="E4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D5" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="E5" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C6" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D6" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="E6" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B7" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C7" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D7" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E7" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B8" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C8" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D8" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="E8" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B9" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C9" t="s">
+        <v>432</v>
+      </c>
+      <c r="D9" t="s">
         <v>438</v>
       </c>
-      <c r="D9" t="s">
-        <v>444</v>
-      </c>
       <c r="E9" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="B10" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C10" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D10" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E10" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B11" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C11" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D11" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E11" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B12" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C12" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D12" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="E12" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B13" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C13" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D13" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E13" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="B14" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C14" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D14" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="E14" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B15" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C15" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D15" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="E15" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B16" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C16" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D16" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="E16" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B17" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C17" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D17" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="E17" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="B18" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C18" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D18" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E18" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B19" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C19" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="D19" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="E19" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="B20" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C20" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D20" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E20" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B21" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C21" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D21" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E21" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="B22" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C22" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D22" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E22" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B23" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C23" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D23" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E23" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B24" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C24" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D24" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E24" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B25" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C25" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D25" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E25" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B26" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C26" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D26" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E26" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B27" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C27" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D27" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E27" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B28" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C28" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D28" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E28" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B29" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C29" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D29" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E29" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B30" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C30" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D30" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E30" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B31" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C31" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D31" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E31" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B32" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C32" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D32" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E32" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B33" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C33" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D33" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E33" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="B34" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C34" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D34" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E34" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="B35" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C35" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D35" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E35" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B36" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C36" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D36" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E36" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B37" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C37" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D37" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E37" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B38" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C38" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D38" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E38" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B39" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C39" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D39" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E39" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="B40" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C40" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D40" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E40" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C41" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D41" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E41" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="B42" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C42" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D42" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E42" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B43" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C43" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D43" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E43" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="B44" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C44" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D44" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E44" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="B45" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C45" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D45" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E45" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="B46" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C46" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D46" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E46" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="B47" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C47" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="D47" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E47" t="s">
-        <v>474</v>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>356</v>
+      </c>
+      <c r="B48" t="s">
+        <v>497</v>
+      </c>
+      <c r="C48" t="s">
+        <v>511</v>
+      </c>
+      <c r="D48" t="s">
+        <v>512</v>
+      </c>
+      <c r="E48" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>401</v>
+      </c>
+      <c r="B49" t="s">
+        <v>497</v>
+      </c>
+      <c r="C49" t="s">
+        <v>511</v>
+      </c>
+      <c r="D49" t="s">
+        <v>512</v>
+      </c>
+      <c r="E49" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>515</v>
+      </c>
+      <c r="B50" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" t="s">
+        <v>511</v>
+      </c>
+      <c r="D50" t="s">
+        <v>512</v>
+      </c>
+      <c r="E50" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>363</v>
+      </c>
+      <c r="B51" t="s">
+        <v>497</v>
+      </c>
+      <c r="C51" t="s">
+        <v>511</v>
+      </c>
+      <c r="D51" t="s">
+        <v>517</v>
+      </c>
+      <c r="E51" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>519</v>
+      </c>
+      <c r="B52" t="s">
+        <v>497</v>
+      </c>
+      <c r="C52" t="s">
+        <v>511</v>
+      </c>
+      <c r="D52" t="s">
+        <v>520</v>
+      </c>
+      <c r="E52" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>366</v>
+      </c>
+      <c r="B53" t="s">
+        <v>497</v>
+      </c>
+      <c r="C53" t="s">
+        <v>511</v>
+      </c>
+      <c r="D53" t="s">
+        <v>522</v>
+      </c>
+      <c r="E53" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>460</v>
+      </c>
+      <c r="B54" t="s">
+        <v>497</v>
+      </c>
+      <c r="C54" t="s">
+        <v>511</v>
+      </c>
+      <c r="D54" t="s">
+        <v>524</v>
+      </c>
+      <c r="E54" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>526</v>
+      </c>
+      <c r="B55" t="s">
+        <v>497</v>
+      </c>
+      <c r="C55" t="s">
+        <v>511</v>
+      </c>
+      <c r="D55" t="s">
+        <v>527</v>
+      </c>
+      <c r="E55" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>412</v>
+      </c>
+      <c r="B56" t="s">
+        <v>497</v>
+      </c>
+      <c r="C56" t="s">
+        <v>511</v>
+      </c>
+      <c r="D56" t="s">
+        <v>529</v>
+      </c>
+      <c r="E56" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>494</v>
+      </c>
+      <c r="B57" t="s">
+        <v>497</v>
+      </c>
+      <c r="C57" t="s">
+        <v>531</v>
+      </c>
+      <c r="D57" t="s">
+        <v>532</v>
+      </c>
+      <c r="E57" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>348</v>
+      </c>
+      <c r="B58" t="s">
+        <v>497</v>
+      </c>
+      <c r="C58" t="s">
+        <v>355</v>
+      </c>
+      <c r="D58" t="s">
+        <v>534</v>
+      </c>
+      <c r="E58" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>479</v>
+      </c>
+      <c r="B59" t="s">
+        <v>497</v>
+      </c>
+      <c r="C59" t="s">
+        <v>355</v>
+      </c>
+      <c r="D59" t="s">
+        <v>536</v>
+      </c>
+      <c r="E59" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>345</v>
+      </c>
+      <c r="B60" t="s">
+        <v>497</v>
+      </c>
+      <c r="C60" t="s">
+        <v>355</v>
+      </c>
+      <c r="D60" t="s">
+        <v>536</v>
+      </c>
+      <c r="E60" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>483</v>
+      </c>
+      <c r="B61" t="s">
+        <v>497</v>
+      </c>
+      <c r="C61" t="s">
+        <v>355</v>
+      </c>
+      <c r="D61" t="s">
+        <v>539</v>
+      </c>
+      <c r="E61" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>480</v>
+      </c>
+      <c r="B62" t="s">
+        <v>497</v>
+      </c>
+      <c r="C62" t="s">
+        <v>355</v>
+      </c>
+      <c r="D62" t="s">
+        <v>536</v>
+      </c>
+      <c r="E62" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>355</v>
+      </c>
+      <c r="B63" t="s">
+        <v>497</v>
+      </c>
+      <c r="C63" t="s">
+        <v>355</v>
+      </c>
+      <c r="D63" t="s">
+        <v>542</v>
+      </c>
+      <c r="E63" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>486</v>
+      </c>
+      <c r="B64" t="s">
+        <v>497</v>
+      </c>
+      <c r="C64" t="s">
+        <v>355</v>
+      </c>
+      <c r="D64" t="s">
+        <v>544</v>
+      </c>
+      <c r="E64" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>369</v>
+      </c>
+      <c r="B65" t="s">
+        <v>497</v>
+      </c>
+      <c r="C65" t="s">
+        <v>355</v>
+      </c>
+      <c r="D65" t="s">
+        <v>546</v>
+      </c>
+      <c r="E65" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>548</v>
+      </c>
+      <c r="B66" t="s">
+        <v>497</v>
+      </c>
+      <c r="C66" t="s">
+        <v>355</v>
+      </c>
+      <c r="D66" t="s">
+        <v>536</v>
+      </c>
+      <c r="E66" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>477</v>
+      </c>
+      <c r="B67" t="s">
+        <v>497</v>
+      </c>
+      <c r="C67" t="s">
+        <v>355</v>
+      </c>
+      <c r="D67" t="s">
+        <v>544</v>
+      </c>
+      <c r="E67" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>488</v>
+      </c>
+      <c r="B68" t="s">
+        <v>497</v>
+      </c>
+      <c r="C68" t="s">
+        <v>355</v>
+      </c>
+      <c r="D68" t="s">
+        <v>536</v>
+      </c>
+      <c r="E68" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>353</v>
+      </c>
+      <c r="B69" t="s">
+        <v>497</v>
+      </c>
+      <c r="C69" t="s">
+        <v>355</v>
+      </c>
+      <c r="D69" t="s">
+        <v>552</v>
+      </c>
+      <c r="E69" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>478</v>
+      </c>
+      <c r="B70" t="s">
+        <v>497</v>
+      </c>
+      <c r="C70" t="s">
+        <v>531</v>
+      </c>
+      <c r="D70" t="s">
+        <v>554</v>
+      </c>
+      <c r="E70" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>357</v>
+      </c>
+      <c r="B71" t="s">
+        <v>497</v>
+      </c>
+      <c r="C71" t="s">
+        <v>355</v>
+      </c>
+      <c r="D71" t="s">
+        <v>536</v>
+      </c>
+      <c r="E71" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>482</v>
+      </c>
+      <c r="B72" t="s">
+        <v>497</v>
+      </c>
+      <c r="C72" t="s">
+        <v>355</v>
+      </c>
+      <c r="D72" t="s">
+        <v>557</v>
+      </c>
+      <c r="E72" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>347</v>
+      </c>
+      <c r="B73" t="s">
+        <v>497</v>
+      </c>
+      <c r="C73" t="s">
+        <v>355</v>
+      </c>
+      <c r="D73" t="s">
+        <v>559</v>
+      </c>
+      <c r="E73" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>354</v>
+      </c>
+      <c r="B74" t="s">
+        <v>497</v>
+      </c>
+      <c r="C74" t="s">
+        <v>355</v>
+      </c>
+      <c r="D74" t="s">
+        <v>561</v>
+      </c>
+      <c r="E74" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>351</v>
+      </c>
+      <c r="B75" t="s">
+        <v>497</v>
+      </c>
+      <c r="C75" t="s">
+        <v>355</v>
+      </c>
+      <c r="D75" t="s">
+        <v>544</v>
+      </c>
+      <c r="E75" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>492</v>
+      </c>
+      <c r="B76" t="s">
+        <v>497</v>
+      </c>
+      <c r="C76" t="s">
+        <v>355</v>
+      </c>
+      <c r="D76" t="s">
+        <v>564</v>
+      </c>
+      <c r="E76" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>493</v>
+      </c>
+      <c r="B77" t="s">
+        <v>497</v>
+      </c>
+      <c r="C77" t="s">
+        <v>355</v>
+      </c>
+      <c r="D77" t="s">
+        <v>536</v>
+      </c>
+      <c r="E77" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>495</v>
+      </c>
+      <c r="B78" t="s">
+        <v>497</v>
+      </c>
+      <c r="C78" t="s">
+        <v>355</v>
+      </c>
+      <c r="D78" t="s">
+        <v>544</v>
+      </c>
+      <c r="E78" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>343</v>
+      </c>
+      <c r="B79" t="s">
+        <v>497</v>
+      </c>
+      <c r="C79" t="s">
+        <v>355</v>
+      </c>
+      <c r="D79" t="s">
+        <v>534</v>
+      </c>
+      <c r="E79" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>408</v>
+      </c>
+      <c r="B80" t="s">
+        <v>497</v>
+      </c>
+      <c r="C80" t="s">
+        <v>355</v>
+      </c>
+      <c r="D80" t="s">
+        <v>569</v>
+      </c>
+      <c r="E80" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>491</v>
+      </c>
+      <c r="B81" t="s">
+        <v>497</v>
+      </c>
+      <c r="C81" t="s">
+        <v>531</v>
+      </c>
+      <c r="D81" t="s">
+        <v>571</v>
+      </c>
+      <c r="E81" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>496</v>
+      </c>
+      <c r="B82" t="s">
+        <v>497</v>
+      </c>
+      <c r="C82" t="s">
+        <v>531</v>
+      </c>
+      <c r="D82" t="s">
+        <v>571</v>
+      </c>
+      <c r="E82" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>574</v>
+      </c>
+      <c r="B83" t="s">
+        <v>497</v>
+      </c>
+      <c r="C83" t="s">
+        <v>575</v>
+      </c>
+      <c r="D83" t="s">
+        <v>576</v>
+      </c>
+      <c r="E83" t="s">
+        <v>577</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Downloads\watchlist-dashboard\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F179AC-28C1-48A6-8C1F-63087ECB91FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F22447-90F5-44C1-A105-BDA3251AF2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Watchlist Ratings" sheetId="1" r:id="rId1"/>
@@ -2403,7 +2403,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="610">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -2748,9 +2748,6 @@
     <t>504</t>
   </si>
   <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
     <t>03/06/2026</t>
   </si>
   <si>
@@ -2979,9 +2976,6 @@
     <t>7,402</t>
   </si>
   <si>
-    <t>22/04/2026</t>
-  </si>
-  <si>
     <t>16/07/2026</t>
   </si>
   <si>
@@ -3090,12 +3084,6 @@
     <t>1,854</t>
   </si>
   <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>27/07/2026</t>
-  </si>
-  <si>
     <t>Special situation</t>
   </si>
   <si>
@@ -4174,6 +4162,114 @@
   </si>
   <si>
     <t>Revisados sin novedad material (resultados ya capturados en jun o proximos en ago-sep): VEEV, COST, DSGX, ZS, S, CRWD, ITX, DNP, EVD, KSPI, CELH, HLMA (Q1/anteriores ya analizados en jun); RAA (Rational, Q1 6-may), NTO (Nintendo, FY 8-may), SPOT, VLTO, GRMN, KRX (Kingspan), CPR (Campari), JDG, BFIT, VRLA (Verallia, OPA BWGI fue 2025), LOTB, CBAV (Clinica Baviera), SIKA, TGYM (Technogym). No se ha modificado su celda BN.</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>27/10/2026</t>
+  </si>
+  <si>
+    <t>29/10/2026</t>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
+    <t>05/11/2026</t>
+  </si>
+  <si>
+    <t>28/10/2026</t>
+  </si>
+  <si>
+    <t>04/11/2026</t>
+  </si>
+  <si>
+    <t>BN; BO; BP (est.)</t>
+  </si>
+  <si>
+    <t>H1 2026 results (29/07/2026) - amorim.com/investidores + prensa (Sapo/ECO)</t>
+  </si>
+  <si>
+    <t>OJO: ticker = Corticeira Amorim (Lisboa/cortica), NO Cencora -- logs de 24-jun/18-jul documentaron por error noticias de Cencora. H1 2026: ventas EUR445,8M (-5,8%; -4,6% ex-USD), BN EUR25,2M (-31,7%) por reestructuracion de suelos (ACS) y dolar debil. Q2 BN -51,9% a EUR9,8M; ACS mejora secuencial +5,3% (aeroespacial/sellado/deportes). Vigilar recuperacion de suelos.</t>
+  </si>
+  <si>
+    <t>VRLA</t>
+  </si>
+  <si>
+    <t>Resultats S1 2026 (28/07/2026) - verallia.com/investisseurs</t>
+  </si>
+  <si>
+    <t>S1: ingresos EUR1.698,8M (-1,4%), BN EUR27M (EUR0,21/acc.) vs EUR68M en S1 2025 por cargos excepcionales de adaptacion industrial en Europa (-EUR43M neto); ex-excepcionales BN EUR70M (EUR0,59/acc.). Mantiene objetivos FY26. Capex EUR91M (-12%); nuevo horno hibrido en Saint-Romain en 2S26.</t>
+  </si>
+  <si>
+    <t>Q2 2026 press release (28/07/2026) - investors.veralto.com</t>
+  </si>
+  <si>
+    <t>Q2: ventas $1.474M (+7,6%), BN $241M (BPA $0,98), BPA aj. $1,11 bate estimacion ($1,00e); margen op. aj. 24,6%. FCF aj. $328M. Sube guia FY26: core sales +4,0-4,5%, BPA aj. $4,35-4,43 (incl. $0,05 por reembolsos arancelarios IEEPA).</t>
+  </si>
+  <si>
+    <t>Q2 2026 results (22/07/2026) - abc.xyz / CNBC</t>
+  </si>
+  <si>
+    <t>Q2: ingresos $119,8B (+24%, bate $116,9B e.), Cloud +82% a $24,8B (vs +63% en Q1); BPA $9,11 vs $2,89e (incluye ganancias no operativas). Emite $49,6B en acciones (jun) + $20,3B en bonos para capex IA; dividendo $0,22/acc. Accion cayo por subida de capex.</t>
+  </si>
+  <si>
+    <t>Q2 2026 press release (29/07/2026) - garmin.com/newsroom</t>
+  </si>
+  <si>
+    <t>Q2 record: ingresos $2,02B (+11,4%, bate $1,94B e.), BPA $2,81 vs $2,30e; margen bruto 62,4%, margen op. 30,4% (+30%). Fitness lidera (+25%, 37% ventas); Outdoor -2%. Sube guia FY26 a ~$8,05B ingresos y BPA ~$10.</t>
+  </si>
+  <si>
+    <t>SIKA</t>
+  </si>
+  <si>
+    <t>H1 2026 results (28/07/2026) - sika.com</t>
+  </si>
+  <si>
+    <t>H1: ventas CHF5,59B (+4,0% en moneda local, -1,5% reportado por FX -5,5%); BN CHF552,1M (-0,4%); EBITDA CHF1.063M (-0,7%), margen bruto 55,7% (+60pb). Sube guia FY26: ventas +3-6% LC, margen EBITDA 19,0-19,5%. Fast Forward: CHF80M ahorro 2026.</t>
+  </si>
+  <si>
+    <t>Resultados S1 2026 (23/07/2026) - vidrala.com / CNMV</t>
+  </si>
+  <si>
+    <t>S1: ventas EUR754M (+0,5%), BN EUR117,4M (+8,9%) impulsado por Sudamerica; EBITDA EUR225,5M (+4,4%, margen 29,9%, +110pb); BPA EUR3,36 (+9,9%). Deuda neta EUR252,3M (0,6x EBITDA). Guia FY: EBITDA &gt;EUR450M, BPA +5%, caja ~EUR200M.</t>
+  </si>
+  <si>
+    <t>BFIT</t>
+  </si>
+  <si>
+    <t>Half-Year Report 2026 (28/07/2026) - corporate.basic-fit.com</t>
+  </si>
+  <si>
+    <t>H1: ingresos EUR800M (+18%), EBITDA aj. (menos alquiler) EUR204M (+36%); BN +EUR23,6M vs -EUR7,9M en H1 2025. Clubes +35% a 2.192 (consolidacion Clever Fit), socios +34% a 6,1M. Sube guia FY26 EBITDA-menos-alquiler a EUR430-460M (antes EUR415-455M).</t>
+  </si>
+  <si>
+    <t>Q2 2026 financial results (22/07/2026) - investors.oatly.com</t>
+  </si>
+  <si>
+    <t>Q2: ingresos $240,1M (+15,2%; +12,7% cc, bate $220,1M e.), perdida aj. BPA -$0,99 (mejor que -$1,02e). Margen bruto 33,9% (+140pb); EBITDA aj. positivo +$0,4M (primer trimestre rentable a nivel aj.). Sube guia FY26 crecimiento cc a 8-10% (antes 3-5%).</t>
+  </si>
+  <si>
+    <t>BN; BP (confirmado, sin cambios en BO)</t>
+  </si>
+  <si>
+    <t>FICO confirma fecha de publicacion - biggo/marketbeat (jul-2026)</t>
+  </si>
+  <si>
+    <t>Confirma publicacion de Q3 FY26 hoy 29-jul tras cierre (antes estimado 28-jul); aun sin resultados publicados a la hora de este barrido. Consenso: ingresos $679,3M (+26,6%), BPA $12,02 (+40,3%).</t>
+  </si>
+  <si>
+    <t>Kaspi.kz confirma fecha - globenewswire (14/07/2026)</t>
+  </si>
+  <si>
+    <t>Confirma publicacion de Q2/S1 2026 el 10-ago (antes estimado 27-jul); aun sin resultados.</t>
+  </si>
+  <si>
+    <t>Spotify confirma fecha - stocktitan (jul-2026)</t>
+  </si>
+  <si>
+    <t>Confirma publicacion de Q2 2026 el 4-ago antes de apertura (antes estimado 28-jul); aun sin resultados. Guia: ingresos ~EUR4,8B (+15%), MAU 778M, suscriptores 299M.</t>
   </si>
 </sst>
 </file>
@@ -15110,13 +15206,13 @@
         <v>0.35404498597134726</v>
       </c>
       <c r="BN4" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BP4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15341,14 +15437,20 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.13667813232291248</v>
       </c>
-      <c r="BN5" s="93" t="s">
-        <v>497</v>
-      </c>
-      <c r="BO5" s="93" t="s">
-        <v>85</v>
-      </c>
-      <c r="BP5" s="93" t="s">
-        <v>422</v>
+      <c r="BN5" s="93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="BO5" s="93" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="BP5" s="93" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -15574,7 +15676,7 @@
         <v>0.33962554586669502</v>
       </c>
       <c r="BN6" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO6" s="93" t="s">
         <v>90</v>
@@ -15806,13 +15908,13 @@
         <v>0.25482976969404003</v>
       </c>
       <c r="BN7" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO7" t="s">
         <v>95</v>
       </c>
       <c r="BP7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16038,13 +16140,13 @@
         <v>1.7035846360751394E-2</v>
       </c>
       <c r="BN8" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO8" t="s">
         <v>99</v>
       </c>
       <c r="BP8" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16270,13 +16372,13 @@
         <v>0.24553423525971096</v>
       </c>
       <c r="BN9" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BP9" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16288,7 +16390,7 @@
         <v>RAA</v>
       </c>
       <c r="C10" s="88" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D10" s="88" t="s">
         <v>77</v>
@@ -16466,14 +16568,14 @@
         <v>0.38333333333333336</v>
       </c>
       <c r="BD10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="BE10" s="23">
         <f t="shared" si="15"/>
         <v>5.0105533884466924E-2</v>
       </c>
       <c r="BF10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="BG10" s="23">
         <f t="shared" si="16"/>
@@ -16502,13 +16604,13 @@
         <v>0.15723005465088957</v>
       </c>
       <c r="BN10" s="93" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="BO10" s="93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="BP10" s="93" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16520,10 +16622,10 @@
         <v>ZS</v>
       </c>
       <c r="C11" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="88" t="s">
         <v>109</v>
-      </c>
-      <c r="D11" s="88" t="s">
-        <v>110</v>
       </c>
       <c r="E11" s="11" t="str">
         <f t="array" aca="1" ref="E11" ca="1">_FV(A11,"Abreviatura de intercambio",TRUE())</f>
@@ -16698,14 +16800,14 @@
         <v>0.15</v>
       </c>
       <c r="BD11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BE11" s="23">
         <f t="shared" si="15"/>
         <v>0.10006131467358759</v>
       </c>
       <c r="BF11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="BG11" s="23">
         <f t="shared" si="16"/>
@@ -16734,13 +16836,13 @@
         <v>0.34414353629850369</v>
       </c>
       <c r="BN11" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO11" t="s">
         <v>99</v>
       </c>
       <c r="BP11" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16752,7 +16854,7 @@
         <v>NTO</v>
       </c>
       <c r="C12" s="88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" s="88" t="s">
         <v>77</v>
@@ -16878,7 +16980,7 @@
         <v>7.92</v>
       </c>
       <c r="AO12" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AP12" s="19">
         <v>1950000</v>
@@ -16930,14 +17032,14 @@
         <v>0.21875</v>
       </c>
       <c r="BD12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BE12" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="BF12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="BG12" s="23">
         <f t="shared" si="16"/>
@@ -16966,13 +17068,13 @@
         <v>0.1501292474376974</v>
       </c>
       <c r="BN12" s="93" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="BO12" s="94" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="BP12" s="93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17162,14 +17264,14 @@
         <v>0.18333333333333335</v>
       </c>
       <c r="BD13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="BE13" s="23">
         <f t="shared" si="15"/>
         <v>7.0000909614846396E-2</v>
       </c>
       <c r="BF13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BG13" s="23">
         <f t="shared" si="16"/>
@@ -17198,13 +17300,13 @@
         <v>6.9229397135512238E-2</v>
       </c>
       <c r="BN13" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO13" s="93" t="s">
         <v>85</v>
       </c>
       <c r="BP13" s="93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17216,7 +17318,7 @@
         <v>SU</v>
       </c>
       <c r="C14" s="88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D14" s="88" t="s">
         <v>77</v>
@@ -17394,14 +17496,14 @@
         <v>0.12631578947368421</v>
       </c>
       <c r="BD14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="BE14" s="23">
         <f t="shared" si="15"/>
         <v>4.9990235939731065E-2</v>
       </c>
       <c r="BF14" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="BG14" s="23">
         <f t="shared" si="16"/>
@@ -17429,14 +17531,20 @@
         <f t="shared" ca="1" si="20"/>
         <v>5.0833735875018826E-2</v>
       </c>
-      <c r="BN14" s="93" t="s">
-        <v>497</v>
-      </c>
-      <c r="BO14" s="93" t="s">
-        <v>113</v>
-      </c>
-      <c r="BP14" s="93" t="s">
-        <v>124</v>
+      <c r="BN14" s="93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="BO14" s="93" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="BP14" s="93" t="inlineStr">
+        <is>
+          <t>29/10/2026</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17448,7 +17556,7 @@
         <v>ITX</v>
       </c>
       <c r="C15" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D15" s="88" t="s">
         <v>77</v>
@@ -17626,14 +17734,14 @@
         <v>0.36111111111111105</v>
       </c>
       <c r="BD15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BE15" s="23">
         <f t="shared" si="15"/>
         <v>3.9993585848977053E-2</v>
       </c>
       <c r="BF15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="BG15" s="23">
         <f t="shared" si="16"/>
@@ -17662,13 +17770,13 @@
         <v>0.13663154593919979</v>
       </c>
       <c r="BN15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BP15" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17680,7 +17788,7 @@
         <v>LOTB</v>
       </c>
       <c r="C16" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" s="88" t="s">
         <v>77</v>
@@ -17858,14 +17966,14 @@
         <v>0.20625000000000002</v>
       </c>
       <c r="BD16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BE16" s="23">
         <f t="shared" si="15"/>
         <v>6.9610375725068785E-2</v>
       </c>
       <c r="BF16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="BG16" s="23">
         <f t="shared" si="16"/>
@@ -17897,10 +18005,10 @@
         <v>81</v>
       </c>
       <c r="BO16" s="93" t="s">
+        <v>129</v>
+      </c>
+      <c r="BP16" s="93" t="s">
         <v>130</v>
-      </c>
-      <c r="BP16" s="93" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -17912,7 +18020,7 @@
         <v>HLMA</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D17" s="88" t="s">
         <v>77</v>
@@ -18038,7 +18146,7 @@
         <v>7.88</v>
       </c>
       <c r="AO17" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AP17" s="19">
         <v>100</v>
@@ -18090,14 +18198,14 @@
         <v>0.1761904761904762</v>
       </c>
       <c r="BD17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="BE17" s="23">
         <f t="shared" si="15"/>
         <v>5.0200405794756708E-2</v>
       </c>
       <c r="BF17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BG17" s="23">
         <f t="shared" si="16"/>
@@ -18126,13 +18234,13 @@
         <v>8.6208283772470695E-2</v>
       </c>
       <c r="BN17" s="93" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="BO17" s="94" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BP17" s="93" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18322,14 +18430,14 @@
         <v>0.29090909090909089</v>
       </c>
       <c r="BD18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="BE18" s="23">
         <f t="shared" si="15"/>
         <v>8.0078627468473051E-2</v>
       </c>
       <c r="BF18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BG18" s="23">
         <f t="shared" si="16"/>
@@ -18357,14 +18465,20 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.12760665021194706</v>
       </c>
-      <c r="BN18" s="93" t="s">
-        <v>497</v>
-      </c>
-      <c r="BO18" s="93" t="s">
-        <v>139</v>
-      </c>
-      <c r="BP18" s="93" t="s">
-        <v>245</v>
+      <c r="BN18" s="93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="BO18" s="93" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="BP18" s="93" t="inlineStr">
+        <is>
+          <t>18/11/2026</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18376,7 +18490,7 @@
         <v>LIFCO B</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D19" s="88" t="s">
         <v>77</v>
@@ -18502,7 +18616,7 @@
         <v>7.9</v>
       </c>
       <c r="AO19" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AP19" s="19">
         <v>3000</v>
@@ -18554,14 +18668,14 @@
         <v>0.15454545454545454</v>
       </c>
       <c r="BD19" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="BE19" s="23">
         <f t="shared" si="15"/>
         <v>7.001218289169242E-2</v>
       </c>
       <c r="BF19" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BG19" s="23">
         <f t="shared" si="16"/>
@@ -18590,13 +18704,13 @@
         <v>0.12340083605171048</v>
       </c>
       <c r="BN19" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO19" s="93" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BP19" s="93" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="20" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18608,7 +18722,7 @@
         <v>EVD</v>
       </c>
       <c r="C20" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D20" s="88" t="s">
         <v>77</v>
@@ -18786,14 +18900,14 @@
         <v>0.21875</v>
       </c>
       <c r="BD20" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BE20" s="23">
         <f t="shared" si="15"/>
         <v>3.9812328944305531E-2</v>
       </c>
       <c r="BF20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BG20" s="23">
         <f t="shared" si="16"/>
@@ -18822,13 +18936,13 @@
         <v>0.39406104363416494</v>
       </c>
       <c r="BN20" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO20" t="s">
         <v>99</v>
       </c>
       <c r="BP20" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="21" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -18840,7 +18954,7 @@
         <v>MNST</v>
       </c>
       <c r="C21" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D21" s="88" t="s">
         <v>77</v>
@@ -19018,14 +19132,14 @@
         <v>0.59375</v>
       </c>
       <c r="BD21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="BE21" s="23">
         <f t="shared" si="15"/>
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BG21" s="23">
         <f t="shared" si="16"/>
@@ -19054,13 +19168,13 @@
         <v>-6.75258992372334E-2</v>
       </c>
       <c r="BN21" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO21" s="93" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BP21" s="93" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="22" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19072,10 +19186,10 @@
         <v>ABNB</v>
       </c>
       <c r="C22" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D22" s="88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E22" s="11" t="str">
         <f t="array" aca="1" ref="E22" ca="1">_FV(A22,"Abreviatura de intercambio",TRUE())</f>
@@ -19250,14 +19364,14 @@
         <v>0.375</v>
       </c>
       <c r="BD22" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BE22" s="23">
         <f t="shared" si="15"/>
         <v>4.9985012185677746E-2</v>
       </c>
       <c r="BF22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BG22" s="23">
         <f t="shared" si="16"/>
@@ -19286,13 +19400,13 @@
         <v>0.26608928109004548</v>
       </c>
       <c r="BN22" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO22" s="93" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BP22" s="93" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="23" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19430,7 +19544,7 @@
         <v>7.44</v>
       </c>
       <c r="AO23" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AP23" s="19">
         <v>500</v>
@@ -19482,14 +19596,14 @@
         <v>0.2615384615384615</v>
       </c>
       <c r="BD23" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BE23" s="23">
         <f t="shared" si="15"/>
         <v>0.12006550912241742</v>
       </c>
       <c r="BF23" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="BG23" s="23">
         <f t="shared" si="16"/>
@@ -19518,13 +19632,13 @@
         <v>9.6454580014539326E-2</v>
       </c>
       <c r="BN23" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO23" t="s">
         <v>95</v>
       </c>
       <c r="BP23" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19536,7 +19650,7 @@
         <v>VLTO</v>
       </c>
       <c r="C24" s="88" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D24" s="88" t="s">
         <v>77</v>
@@ -19714,14 +19828,14 @@
         <v>0.15384615384615385</v>
       </c>
       <c r="BD24" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BE24" s="23">
         <f t="shared" si="15"/>
         <v>3.9950542132181077E-2</v>
       </c>
       <c r="BF24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BG24" s="23">
         <f t="shared" si="16"/>
@@ -19750,13 +19864,13 @@
         <v>0.15736302613130304</v>
       </c>
       <c r="BN24" s="93" t="s">
-        <v>421</v>
+        <v>574</v>
       </c>
       <c r="BO24" s="93" t="s">
-        <v>139</v>
+        <v>241</v>
       </c>
       <c r="BP24" s="93" t="s">
-        <v>245</v>
+        <v>575</v>
       </c>
     </row>
     <row r="25" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19768,7 +19882,7 @@
         <v>LR</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D25" s="88" t="s">
         <v>77</v>
@@ -19946,14 +20060,14 @@
         <v>0.15263157894736842</v>
       </c>
       <c r="BD25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BE25" s="23">
         <f t="shared" si="15"/>
         <v>6.003737798448272E-2</v>
       </c>
       <c r="BF25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BG25" s="23">
         <f t="shared" si="16"/>
@@ -19982,13 +20096,13 @@
         <v>0.11996589429293425</v>
       </c>
       <c r="BN25" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO25" s="93" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BP25" s="93" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="26" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20000,7 +20114,7 @@
         <v>JDG</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D26" s="88" t="s">
         <v>77</v>
@@ -20126,7 +20240,7 @@
         <v>6.74</v>
       </c>
       <c r="AO26" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AP26" s="19">
         <v>10</v>
@@ -20178,14 +20292,14 @@
         <v>0.15</v>
       </c>
       <c r="BD26" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="BE26" s="23">
         <f t="shared" si="15"/>
         <v>6.1858758794934632E-2</v>
       </c>
       <c r="BF26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="BG26" s="23">
         <f t="shared" si="16"/>
@@ -20217,10 +20331,10 @@
         <v>81</v>
       </c>
       <c r="BO26" s="93" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BP26" s="93" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20232,7 +20346,7 @@
         <v>STMN</v>
       </c>
       <c r="C27" s="88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D27" s="88" t="s">
         <v>77</v>
@@ -20358,7 +20472,7 @@
         <v>6.7</v>
       </c>
       <c r="AO27" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AP27" s="19">
         <v>300</v>
@@ -20410,14 +20524,14 @@
         <v>0.13571428571428573</v>
       </c>
       <c r="BD27" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BE27" s="23">
         <f t="shared" si="15"/>
         <v>5.9828421260577302E-2</v>
       </c>
       <c r="BF27" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BG27" s="23">
         <f t="shared" si="16"/>
@@ -20446,13 +20560,13 @@
         <v>2.3314845145717245E-2</v>
       </c>
       <c r="BN27" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO27" s="94" t="s">
         <v>85</v>
       </c>
       <c r="BP27" s="93" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="28" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20642,14 +20756,14 @@
         <v>0.28947368421052633</v>
       </c>
       <c r="BD28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BE28" s="23">
         <f t="shared" si="15"/>
         <v>4.9999742905350697E-2</v>
       </c>
       <c r="BF28" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BG28" s="23">
         <f t="shared" si="16"/>
@@ -20677,14 +20791,20 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.18017157019865659</v>
       </c>
-      <c r="BN28" s="93" t="s">
-        <v>497</v>
-      </c>
-      <c r="BO28" s="93" t="s">
-        <v>85</v>
-      </c>
-      <c r="BP28" s="93" t="s">
-        <v>422</v>
+      <c r="BN28" s="93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="BO28" s="93" t="inlineStr">
+        <is>
+          <t>29/07/2026</t>
+        </is>
+      </c>
+      <c r="BP28" s="93" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20874,14 +20994,14 @@
         <v>5.6249999999999994E-2</v>
       </c>
       <c r="BD29" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="BE29" s="23">
         <f t="shared" si="15"/>
         <v>7.0010270953862141E-2</v>
       </c>
       <c r="BF29" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="BG29" s="23">
         <f t="shared" si="16"/>
@@ -20910,13 +21030,13 @@
         <v>0.25952098858972428</v>
       </c>
       <c r="BN29" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO29" s="93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BP29" s="93" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="30" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -20928,10 +21048,10 @@
         <v>NET</v>
       </c>
       <c r="C30" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" s="88" t="s">
         <v>109</v>
-      </c>
-      <c r="D30" s="88" t="s">
-        <v>110</v>
       </c>
       <c r="E30" s="11" t="str">
         <f t="array" aca="1" ref="E30" ca="1">_FV(A30,"Abreviatura de intercambio",TRUE())</f>
@@ -21106,14 +21226,14 @@
         <v>1.4285714285714287E-2</v>
       </c>
       <c r="BD30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BE30" s="23">
         <f t="shared" si="15"/>
         <v>0.13995090255865472</v>
       </c>
       <c r="BF30" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BG30" s="23">
         <f t="shared" si="16"/>
@@ -21142,13 +21262,13 @@
         <v>-0.2212757014175647</v>
       </c>
       <c r="BN30" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO30" s="93" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BP30" s="93" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="31" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21160,10 +21280,10 @@
         <v>CRWD</v>
       </c>
       <c r="C31" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="88" t="s">
         <v>109</v>
-      </c>
-      <c r="D31" s="88" t="s">
-        <v>110</v>
       </c>
       <c r="E31" s="11" t="str">
         <f t="array" aca="1" ref="E31" ca="1">_FV(A31,"Abreviatura de intercambio",TRUE())</f>
@@ -21338,14 +21458,14 @@
         <v>0.19999999999999998</v>
       </c>
       <c r="BD31" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BE31" s="23">
         <f t="shared" si="15"/>
         <v>0.12002012191466971</v>
       </c>
       <c r="BF31" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="BG31" s="23">
         <f t="shared" si="16"/>
@@ -21374,13 +21494,13 @@
         <v>-9.1701728940705274E-2</v>
       </c>
       <c r="BN31" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BP31" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21570,14 +21690,14 @@
         <v>0.27142857142857141</v>
       </c>
       <c r="BD32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BE32" s="23">
         <f t="shared" si="15"/>
         <v>4.9999742905350697E-2</v>
       </c>
       <c r="BF32" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BG32" s="23">
         <f t="shared" si="16"/>
@@ -21606,13 +21726,13 @@
         <v>2.3331185931335874E-2</v>
       </c>
       <c r="BN32" s="93" t="s">
-        <v>497</v>
+        <v>574</v>
       </c>
       <c r="BO32" s="93" t="s">
-        <v>85</v>
+        <v>506</v>
       </c>
       <c r="BP32" s="93" t="s">
-        <v>245</v>
+        <v>575</v>
       </c>
     </row>
     <row r="33" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21624,7 +21744,7 @@
         <v>ABBNE</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D33" s="88" t="s">
         <v>77</v>
@@ -21802,14 +21922,14 @@
         <v>0.20454545454545453</v>
       </c>
       <c r="BD33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BE33" s="23">
         <f t="shared" si="15"/>
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BG33" s="23">
         <f t="shared" si="16"/>
@@ -21838,13 +21958,13 @@
         <v>-1.6917988403060247E-2</v>
       </c>
       <c r="BN33" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO33" s="93" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="BP33" s="93" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="34" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21856,7 +21976,7 @@
         <v>GRMN</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D34" s="88" t="s">
         <v>77</v>
@@ -22034,14 +22154,14 @@
         <v>0.25</v>
       </c>
       <c r="BD34" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="BE34" s="23">
         <f t="shared" si="15"/>
         <v>4.004618516068903E-2</v>
       </c>
       <c r="BF34" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="BG34" s="23">
         <f t="shared" si="16"/>
@@ -22070,13 +22190,13 @@
         <v>9.5928190485545128E-2</v>
       </c>
       <c r="BN34" s="93" t="s">
-        <v>421</v>
+        <v>574</v>
       </c>
       <c r="BO34" s="93" t="s">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="BP34" s="93" t="s">
-        <v>422</v>
+        <v>576</v>
       </c>
     </row>
     <row r="35" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22088,7 +22208,7 @@
         <v>KRX</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D35" s="88" t="s">
         <v>77</v>
@@ -22266,14 +22386,14 @@
         <v>0.1076923076923077</v>
       </c>
       <c r="BD35" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="BE35" s="23">
         <f t="shared" si="15"/>
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF35" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="BG35" s="23">
         <f t="shared" si="16"/>
@@ -22305,10 +22425,10 @@
         <v>81</v>
       </c>
       <c r="BO35" s="93" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="BP35" s="93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22323,7 +22443,7 @@
         <v>86</v>
       </c>
       <c r="D36" s="88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36" s="11" t="str">
         <f t="array" aca="1" ref="E36" ca="1">_FV(A36,"Abreviatura de intercambio",TRUE())</f>
@@ -22446,7 +22566,7 @@
         <v>6</v>
       </c>
       <c r="AO36" s="18" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AP36" s="19">
         <v>900000</v>
@@ -22498,14 +22618,14 @@
         <v>0.23333333333333334</v>
       </c>
       <c r="BD36" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="BE36" s="23">
         <f t="shared" ref="BE36:BE65" si="41">(BD36/AS36)^(1/5)-1</f>
         <v>6.9999922003442849E-2</v>
       </c>
       <c r="BF36" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="BG36" s="23">
         <f t="shared" ref="BG36:BG65" si="42">(BF36/AS36)^(1/5)-1</f>
@@ -22534,13 +22654,13 @@
         <v>0.2031572378387061</v>
       </c>
       <c r="BN36" t="s">
-        <v>419</v>
+        <v>574</v>
       </c>
       <c r="BO36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="BP36" t="s">
-        <v>217</v>
+        <v>577</v>
       </c>
     </row>
     <row r="37" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22552,7 +22672,7 @@
         <v>CBAV</v>
       </c>
       <c r="C37" s="88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>77</v>
@@ -22730,14 +22850,14 @@
         <v>0.15909090909090909</v>
       </c>
       <c r="BD37" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="BE37" s="23">
         <f t="shared" si="41"/>
         <v>5.9223841048812176E-2</v>
       </c>
       <c r="BF37" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BG37" s="23">
         <f t="shared" si="42"/>
@@ -22769,10 +22889,10 @@
         <v>81</v>
       </c>
       <c r="BO37" s="94" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BP37" s="93" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -22784,10 +22904,10 @@
         <v>NVDA</v>
       </c>
       <c r="C38" s="88" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D38" s="88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E38" s="11" t="str">
         <f t="array" aca="1" ref="E38" ca="1">_FV(A38,"Abreviatura de intercambio",TRUE())</f>
@@ -22962,14 +23082,14 @@
         <v>0.83333333333333326</v>
       </c>
       <c r="BD38" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="BE38" s="23">
         <f t="shared" si="41"/>
         <v>8.0000772740678627E-2</v>
       </c>
       <c r="BF38" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="BG38" s="23">
         <f t="shared" si="42"/>
@@ -22998,13 +23118,13 @@
         <v>0.10599500048899735</v>
       </c>
       <c r="BN38" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="BP38" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="39" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23016,7 +23136,7 @@
         <v>COR</v>
       </c>
       <c r="C39" s="88" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>96</v>
@@ -23194,14 +23314,14 @@
         <v>0.13333333333333333</v>
       </c>
       <c r="BD39" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="BE39" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="BG39" s="23">
         <f t="shared" si="42"/>
@@ -23230,13 +23350,13 @@
         <v>0.1297914061329597</v>
       </c>
       <c r="BN39" s="93" t="s">
-        <v>497</v>
+        <v>574</v>
       </c>
       <c r="BO39" s="94" t="s">
-        <v>169</v>
+        <v>418</v>
       </c>
       <c r="BP39" s="93" t="s">
-        <v>430</v>
+        <v>578</v>
       </c>
     </row>
     <row r="40" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23248,7 +23368,7 @@
         <v>TSM</v>
       </c>
       <c r="C40" s="88" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>77</v>
@@ -23426,14 +23546,14 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="BD40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="BE40" s="23">
         <f t="shared" si="41"/>
         <v>7.9997972620447833E-2</v>
       </c>
       <c r="BF40" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="BG40" s="23">
         <f t="shared" si="42"/>
@@ -23462,13 +23582,13 @@
         <v>-1.7257046861950176E-2</v>
       </c>
       <c r="BN40" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO40" s="93" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="BP40" s="93" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="41" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23480,10 +23600,10 @@
         <v>SPOT</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E41" s="11" t="str">
         <f t="array" aca="1" ref="E41" ca="1">_FV(A41,"Abreviatura de intercambio",TRUE())</f>
@@ -23658,14 +23778,14 @@
         <v>0.18</v>
       </c>
       <c r="BD41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="BE41" s="23">
         <f t="shared" si="41"/>
         <v>2.9995722023716587E-2</v>
       </c>
       <c r="BF41" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="BG41" s="23">
         <f t="shared" si="42"/>
@@ -23694,13 +23814,13 @@
         <v>0.17255762415461096</v>
       </c>
       <c r="BN41" s="93" t="s">
-        <v>421</v>
+        <v>574</v>
       </c>
       <c r="BO41" s="93" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="BP41" s="93" t="s">
-        <v>245</v>
+        <v>426</v>
       </c>
     </row>
     <row r="42" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23712,7 +23832,7 @@
         <v>PRY</v>
       </c>
       <c r="C42" s="88" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D42" s="88" t="s">
         <v>77</v>
@@ -23890,14 +24010,14 @@
         <v>0.11052631578947368</v>
       </c>
       <c r="BD42" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="BE42" s="23">
         <f t="shared" si="41"/>
         <v>5.9929050622556934E-2</v>
       </c>
       <c r="BF42" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="BG42" s="23">
         <f t="shared" si="42"/>
@@ -23925,14 +24045,20 @@
         <f t="shared" ca="1" si="44"/>
         <v>-1.3636073866254428E-2</v>
       </c>
-      <c r="BN42" s="93" t="s">
-        <v>497</v>
-      </c>
-      <c r="BO42" s="93" t="s">
-        <v>207</v>
-      </c>
-      <c r="BP42" s="93" t="s">
-        <v>124</v>
+      <c r="BN42" s="93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="BO42" s="93" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="BP42" s="93" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
       </c>
     </row>
     <row r="43" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -23944,7 +24070,7 @@
         <v>JFN</v>
       </c>
       <c r="C43" s="88" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D43" s="88" t="s">
         <v>96</v>
@@ -24070,7 +24196,7 @@
         <v>5.24</v>
       </c>
       <c r="AO43" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AP43" s="19">
         <v>75</v>
@@ -24122,14 +24248,14 @@
         <v>0.17333333333333334</v>
       </c>
       <c r="BD43" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="BE43" s="23">
         <f t="shared" si="41"/>
         <v>-6.0146235650011426E-2</v>
       </c>
       <c r="BF43" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BG43" s="23">
         <f t="shared" si="42"/>
@@ -24158,13 +24284,13 @@
         <v>4.8865524260605975E-2</v>
       </c>
       <c r="BN43" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO43" s="93" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="BP43" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24176,7 +24302,7 @@
         <v>CPR</v>
       </c>
       <c r="C44" s="88" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D44" s="88" t="s">
         <v>96</v>
@@ -24354,14 +24480,14 @@
         <v>7.636363636363637E-2</v>
       </c>
       <c r="BD44" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="BE44" s="23">
         <f t="shared" si="41"/>
         <v>3.0128962818398941E-2</v>
       </c>
       <c r="BF44" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="BG44" s="23">
         <f t="shared" si="42"/>
@@ -24390,13 +24516,13 @@
         <v>4.4886395959320424E-4</v>
       </c>
       <c r="BN44" s="93" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="BO44" s="93" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="BP44" s="93" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="45" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24408,7 +24534,7 @@
         <v>SIKA</v>
       </c>
       <c r="C45" s="88" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D45" s="88" t="s">
         <v>77</v>
@@ -24534,7 +24660,7 @@
         <v>5.13</v>
       </c>
       <c r="AO45" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AP45" s="19">
         <v>1200</v>
@@ -24586,14 +24712,14 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="BD45" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="BE45" s="23">
         <f t="shared" si="41"/>
         <v>2.9967449959592329E-2</v>
       </c>
       <c r="BF45" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="BG45" s="23">
         <f t="shared" si="42"/>
@@ -24622,13 +24748,13 @@
         <v>0.10084068627750553</v>
       </c>
       <c r="BN45" s="93" t="s">
-        <v>81</v>
+        <v>574</v>
       </c>
       <c r="BO45" s="93" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="BP45" s="93" t="s">
-        <v>217</v>
+        <v>494</v>
       </c>
     </row>
     <row r="46" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24640,10 +24766,10 @@
         <v>CHKP</v>
       </c>
       <c r="C46" s="88" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D46" s="88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E46" s="11" t="str">
         <f t="array" aca="1" ref="E46" ca="1">_FV(A46,"Abreviatura de intercambio",TRUE())</f>
@@ -24818,14 +24944,14 @@
         <v>0.83333333333333326</v>
       </c>
       <c r="BD46" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="BE46" s="23">
         <f t="shared" si="41"/>
         <v>1.9956640367314815E-2</v>
       </c>
       <c r="BF46" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="BG46" s="23">
         <f t="shared" si="42"/>
@@ -24853,14 +24979,20 @@
         <f t="shared" ca="1" si="44"/>
         <v>0.27827634265152379</v>
       </c>
-      <c r="BN46" s="93" t="s">
-        <v>497</v>
-      </c>
-      <c r="BO46" s="93" t="s">
-        <v>207</v>
-      </c>
-      <c r="BP46" s="93" t="s">
-        <v>124</v>
+      <c r="BN46" s="93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="BO46" s="93" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="BP46" s="93" t="inlineStr">
+        <is>
+          <t>28/10/2026</t>
+        </is>
       </c>
     </row>
     <row r="47" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -24872,7 +25004,7 @@
         <v>TGYM</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D47" s="88" t="s">
         <v>77</v>
@@ -25050,14 +25182,14 @@
         <v>0.19999999999999998</v>
       </c>
       <c r="BD47" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="BE47" s="23">
         <f t="shared" si="41"/>
         <v>4.0751095710728658E-2</v>
       </c>
       <c r="BF47" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="BG47" s="23">
         <f t="shared" si="42"/>
@@ -25085,14 +25217,20 @@
         <f t="shared" ca="1" si="44"/>
         <v>7.6047153433324466E-2</v>
       </c>
-      <c r="BN47" s="93" t="s">
-        <v>81</v>
-      </c>
-      <c r="BO47" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="BP47" s="93" t="s">
-        <v>124</v>
+      <c r="BN47" s="93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="BO47" s="93" t="inlineStr">
+        <is>
+          <t>30/07/2026</t>
+        </is>
+      </c>
+      <c r="BP47" s="93" t="inlineStr">
+        <is>
+          <t>05/11/2026</t>
+        </is>
       </c>
     </row>
     <row r="48" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25104,7 +25242,7 @@
         <v>VID</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D48" s="88" t="s">
         <v>96</v>
@@ -25282,14 +25420,14 @@
         <v>0.17500000000000002</v>
       </c>
       <c r="BD48" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="BE48" s="23">
         <f t="shared" si="41"/>
         <v>9.805797673485328E-3</v>
       </c>
       <c r="BF48" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="BG48" s="23">
         <f t="shared" si="42"/>
@@ -25318,13 +25456,13 @@
         <v>0.17994078083050535</v>
       </c>
       <c r="BN48" s="93" t="s">
+        <v>574</v>
+      </c>
+      <c r="BO48" s="94" t="s">
         <v>497</v>
       </c>
-      <c r="BO48" s="94" t="s">
-        <v>85</v>
-      </c>
       <c r="BP48" s="93" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
     </row>
     <row r="49" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25336,10 +25474,10 @@
         <v>TFPM</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E49" s="11" t="str">
         <f t="array" aca="1" ref="E49" ca="1">_FV(A49,"Abreviatura de intercambio",TRUE())</f>
@@ -25514,14 +25652,14 @@
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="BD49" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="BE49" s="23">
         <f t="shared" si="41"/>
         <v>4.957228210048803E-2</v>
       </c>
       <c r="BF49" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="BG49" s="23">
         <f t="shared" si="42"/>
@@ -25550,13 +25688,13 @@
         <v>0.15245224094281129</v>
       </c>
       <c r="BN49" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO49" s="93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BP49" s="93" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="50" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25568,10 +25706,10 @@
         <v>NFLX</v>
       </c>
       <c r="C50" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D50" s="88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E50" s="11" t="str">
         <f t="array" aca="1" ref="E50" ca="1">_FV(A50,"Abreviatura de intercambio",TRUE())</f>
@@ -25784,13 +25922,13 @@
         <v>0.12883269664335661</v>
       </c>
       <c r="BN50" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO50" s="93" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="BP50" s="93" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="51" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -25802,10 +25940,10 @@
         <v>NKE</v>
       </c>
       <c r="C51" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D51" s="88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E51" s="11" t="str">
         <f t="array" aca="1" ref="E51" ca="1">_FV(A51,"Abreviatura de intercambio",TRUE())</f>
@@ -25980,14 +26118,14 @@
         <v>0.24</v>
       </c>
       <c r="BD51" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="BE51" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF51" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="BG51" s="23">
         <f t="shared" si="42"/>
@@ -26016,13 +26154,13 @@
         <v>0.26370364004104818</v>
       </c>
       <c r="BN51" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO51" s="93" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="BP51" s="93" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26034,7 +26172,7 @@
         <v>MIPS</v>
       </c>
       <c r="C52" s="88" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D52" s="88" t="s">
         <v>77</v>
@@ -26160,7 +26298,7 @@
         <v>4.68</v>
       </c>
       <c r="AO52" s="18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AP52" s="19">
         <v>180</v>
@@ -26212,14 +26350,14 @@
         <v>0.40857142857142859</v>
       </c>
       <c r="BD52" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="BE52" s="23">
         <f t="shared" si="41"/>
         <v>5.0338114975041481E-3</v>
       </c>
       <c r="BF52" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BG52" s="23">
         <f t="shared" si="42"/>
@@ -26248,13 +26386,13 @@
         <v>-2.4636655998681367E-2</v>
       </c>
       <c r="BN52" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO52" s="93" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="BP52" s="93" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
     </row>
     <row r="53" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26266,7 +26404,7 @@
         <v>FERG</v>
       </c>
       <c r="C53" s="88" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D53" s="88" t="s">
         <v>96</v>
@@ -26444,14 +26582,14 @@
         <v>0.23333333333333334</v>
       </c>
       <c r="BD53" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="BE53" s="23">
         <f t="shared" si="41"/>
         <v>9.966033447608158E-3</v>
       </c>
       <c r="BF53" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="BG53" s="23">
         <f t="shared" si="42"/>
@@ -26480,13 +26618,13 @@
         <v>0.11134685123661803</v>
       </c>
       <c r="BN53" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO53" s="93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BP53" s="93" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="54" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26498,10 +26636,10 @@
         <v>S</v>
       </c>
       <c r="C54" s="88" t="s">
+        <v>108</v>
+      </c>
+      <c r="D54" s="88" t="s">
         <v>109</v>
-      </c>
-      <c r="D54" s="88" t="s">
-        <v>110</v>
       </c>
       <c r="E54" s="11" t="str">
         <f t="array" aca="1" ref="E54" ca="1">_FV(A54,"Abreviatura de intercambio",TRUE())</f>
@@ -26676,14 +26814,14 @@
         <v>-1.3333333333333334E-2</v>
       </c>
       <c r="BD54" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="BE54" s="23">
         <f t="shared" si="41"/>
         <v>7.8625221439269977E-2</v>
       </c>
       <c r="BF54" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="BG54" s="23">
         <f t="shared" si="42"/>
@@ -26712,13 +26850,13 @@
         <v>3.431391125000971E-2</v>
       </c>
       <c r="BN54" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO54" t="s">
         <v>99</v>
       </c>
       <c r="BP54" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="55" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26730,7 +26868,7 @@
         <v>TREX</v>
       </c>
       <c r="C55" s="88" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D55" s="88" t="s">
         <v>77</v>
@@ -26908,14 +27046,14 @@
         <v>0.21111111111111114</v>
       </c>
       <c r="BD55" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="BE55" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF55" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="BG55" s="23">
         <f t="shared" si="42"/>
@@ -26944,13 +27082,13 @@
         <v>8.3315115618449731E-2</v>
       </c>
       <c r="BN55" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO55" s="93" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BP55" s="93" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26962,10 +27100,10 @@
         <v>SGO</v>
       </c>
       <c r="C56" s="88" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D56" s="88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E56" s="11" t="str">
         <f t="array" aca="1" ref="E56" ca="1">_FV(A56,"Abreviatura de intercambio",TRUE())</f>
@@ -27140,14 +27278,14 @@
         <v>0.10714285714285714</v>
       </c>
       <c r="BD56" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="BE56" s="23">
         <f t="shared" si="41"/>
         <v>9.966033447608158E-3</v>
       </c>
       <c r="BF56" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="BG56" s="23">
         <f t="shared" si="42"/>
@@ -27176,13 +27314,13 @@
         <v>7.0454949447204207E-2</v>
       </c>
       <c r="BN56" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO56" s="93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="BP56" s="93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27194,10 +27332,10 @@
         <v>TFF</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E57" s="11" t="str">
         <f t="array" aca="1" ref="E57" ca="1">_FV(A57,"Abreviatura de intercambio",TRUE())</f>
@@ -27372,14 +27510,14 @@
         <v>0.04</v>
       </c>
       <c r="BD57" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="BE57" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF57" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="BG57" s="23">
         <f t="shared" si="42"/>
@@ -27408,13 +27546,13 @@
         <v>-0.12010740028521605</v>
       </c>
       <c r="BN57" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO57" s="93" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="BP57" s="93" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="58" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27426,10 +27564,10 @@
         <v>CELH</v>
       </c>
       <c r="C58" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D58" s="88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E58" s="11" t="str">
         <f t="array" aca="1" ref="E58" ca="1">_FV(A58,"Abreviatura de intercambio",TRUE())</f>
@@ -27604,14 +27742,14 @@
         <v>0.3</v>
       </c>
       <c r="BD58" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="BE58" s="23">
         <f t="shared" si="41"/>
         <v>7.9831440532173836E-2</v>
       </c>
       <c r="BF58" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="BG58" s="23">
         <f t="shared" si="42"/>
@@ -27640,13 +27778,13 @@
         <v>0.27964014265382842</v>
       </c>
       <c r="BN58" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="BO58" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="BP58" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27658,10 +27796,10 @@
         <v>BFIT</v>
       </c>
       <c r="C59" s="88" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D59" s="88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E59" s="11" t="str">
         <f t="array" aca="1" ref="E59" ca="1">_FV(A59,"Abreviatura de intercambio",TRUE())</f>
@@ -27836,14 +27974,14 @@
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="BD59" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="BE59" s="23">
         <f t="shared" si="41"/>
         <v>1.9244876491456564E-2</v>
       </c>
       <c r="BF59" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="BG59" s="23">
         <f t="shared" si="42"/>
@@ -27872,13 +28010,13 @@
         <v>2.9387839645351965E-2</v>
       </c>
       <c r="BN59" s="93" t="s">
-        <v>81</v>
+        <v>574</v>
       </c>
       <c r="BO59" s="93" t="s">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="BP59" s="93" t="s">
-        <v>245</v>
+        <v>575</v>
       </c>
     </row>
     <row r="60" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -27890,10 +28028,10 @@
         <v>VRLA</v>
       </c>
       <c r="C60" s="88" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D60" s="88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E60" s="11" t="str">
         <f t="array" aca="1" ref="E60" ca="1">_FV(A60,"Abreviatura de intercambio",TRUE())</f>
@@ -28104,13 +28242,13 @@
         <v>0.21139783699780201</v>
       </c>
       <c r="BN60" s="93" t="s">
-        <v>81</v>
+        <v>574</v>
       </c>
       <c r="BO60" s="93" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="BP60" s="93" t="s">
-        <v>245</v>
+        <v>579</v>
       </c>
     </row>
     <row r="61" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28122,10 +28260,10 @@
         <v>KIST</v>
       </c>
       <c r="C61" s="88" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D61" s="88" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E61" s="11" t="str">
         <f t="array" aca="1" ref="E61" ca="1">_FV(A61,"Abreviatura de intercambio",TRUE())</f>
@@ -28248,7 +28386,7 @@
         <v>2.14</v>
       </c>
       <c r="AO61" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AP61" s="19">
         <v>215</v>
@@ -28338,13 +28476,13 @@
         <v>0.37985089166123109</v>
       </c>
       <c r="BN61" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO61" s="93" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="BP61" s="93" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="62" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28356,10 +28494,10 @@
         <v>WOSG</v>
       </c>
       <c r="C62" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D62" s="88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E62" s="11" t="str">
         <f t="array" aca="1" ref="E62" ca="1">_FV(A62,"Abreviatura de intercambio",TRUE())</f>
@@ -28482,7 +28620,7 @@
         <v>2.08</v>
       </c>
       <c r="AO62" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AP62" s="19">
         <v>70</v>
@@ -28534,14 +28672,14 @@
         <v>8.8888888888888878E-2</v>
       </c>
       <c r="BD62" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="BE62" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF62" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="BG62" s="23">
         <f t="shared" si="42"/>
@@ -28570,13 +28708,13 @@
         <v>8.1957952078739016E-2</v>
       </c>
       <c r="BN62" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BP62" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="63" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28588,10 +28726,10 @@
         <v>IPCO</v>
       </c>
       <c r="C63" s="88" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D63" s="88" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E63" s="11" t="str">
         <f t="array" aca="1" ref="E63" ca="1">_FV(A63,"Abreviatura de intercambio",TRUE())</f>
@@ -28766,14 +28904,14 @@
         <v>9.4444444444444442E-2</v>
       </c>
       <c r="BD63" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="BE63" s="23">
         <f t="shared" si="41"/>
         <v>-4.9967563918014046E-2</v>
       </c>
       <c r="BF63" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="BG63" s="23">
         <f t="shared" si="42"/>
@@ -28802,13 +28940,13 @@
         <v>0.12024588148725956</v>
       </c>
       <c r="BN63" s="93" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="BO63" s="93" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BP63" s="93" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="64" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28820,10 +28958,10 @@
         <v>OTLY</v>
       </c>
       <c r="C64" s="88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D64" s="88" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E64" s="11" t="str">
         <f t="array" aca="1" ref="E64" ca="1">_FV(A64,"Abreviatura de intercambio",TRUE())</f>
@@ -28998,14 +29136,14 @@
         <v>-0.15384615384615383</v>
       </c>
       <c r="BD64" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="BE64" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="BF64" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="BG64" s="23">
         <f t="shared" si="42"/>
@@ -29034,13 +29172,13 @@
         <v>0.60646057206184456</v>
       </c>
       <c r="BN64" s="93" t="s">
-        <v>497</v>
+        <v>574</v>
       </c>
       <c r="BO64" s="93" t="s">
-        <v>85</v>
+        <v>506</v>
       </c>
       <c r="BP64" s="93" t="s">
-        <v>510</v>
+        <v>580</v>
       </c>
     </row>
     <row r="65" spans="1:68" x14ac:dyDescent="0.25">
@@ -29048,7 +29186,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C65" s="88" t="s">
         <v>76</v>
@@ -29057,20 +29195,22 @@
         <v>77</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G65" s="12">
-        <v>2600</v>
+        <f t="array" aca="1" ref="G65" ca="1">_FV(A65,"Precio")</f>
+        <v>2790.88</v>
       </c>
       <c r="H65" s="13">
-        <v>21.2</v>
+        <f t="array" aca="1" ref="H65" ca="1">_FV(A65,"Acciones en circulación",TRUE())/1000000</f>
+        <v>21.19153</v>
       </c>
       <c r="I65" s="14">
-        <f>G65*H65</f>
-        <v>55120</v>
+        <f ca="1">G65*H65</f>
+        <v>59143.017246400006</v>
       </c>
       <c r="J65" s="90">
         <v>2</v>
@@ -29182,8 +29322,8 @@
         <v>4131</v>
       </c>
       <c r="AR65" s="19">
-        <f>I65-AP65+AQ65</f>
-        <v>56162</v>
+        <f ca="1">I65-AP65+AQ65</f>
+        <v>60185.017246400006</v>
       </c>
       <c r="AS65" s="19">
         <v>2700</v>
@@ -29198,16 +29338,16 @@
         <v>12149</v>
       </c>
       <c r="AW65" s="20">
-        <f t="shared" si="35"/>
-        <v>20.800740740740739</v>
+        <f t="shared" ca="1" si="35"/>
+        <v>22.290747128296299</v>
       </c>
       <c r="AX65" s="20">
-        <f t="shared" si="36"/>
-        <v>16.38331388564761</v>
+        <f t="shared" ca="1" si="36"/>
+        <v>17.5568895117853</v>
       </c>
       <c r="AY65" s="20">
-        <f t="shared" si="37"/>
-        <v>4.6227673059511067</v>
+        <f t="shared" ca="1" si="37"/>
+        <v>4.9539070908222902</v>
       </c>
       <c r="AZ65" s="21">
         <v>5000</v>
@@ -29245,29 +29385,29 @@
         <v>40</v>
       </c>
       <c r="BJ65" s="25">
-        <f>(BD65*BH65+AP65-AQ65)/H65</f>
-        <v>5080.566037735849</v>
+        <f ca="1">(BD65*BH65+AP65-AQ65)/H65</f>
+        <v>5082.596678956168</v>
       </c>
       <c r="BK65" s="25">
-        <f>(BF65*BI65+AP65-AQ65)/H65</f>
-        <v>11648.962264150943</v>
+        <f ca="1">(BF65*BI65+AP65-AQ65)/H65</f>
+        <v>11653.618214446999</v>
       </c>
       <c r="BL65" s="23">
-        <f>(BJ65/G65)^(1/5)-1</f>
-        <v>0.14337252119652866</v>
+        <f ca="1">(BJ65/G65)^(1/5)-1</f>
+        <v>0.12737629027296715</v>
       </c>
       <c r="BM65" s="23">
-        <f t="shared" si="44"/>
-        <v>0.45488435118754245</v>
+        <f t="shared" ca="1" si="44"/>
+        <v>0.42948599766279716</v>
       </c>
       <c r="BN65" s="93" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="BO65" s="93" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="BP65" s="93" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -29300,7 +29440,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="100" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -29310,12 +29450,12 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D4" t="e" vm="63">
         <v>#VALUE!</v>
@@ -29327,7 +29467,7 @@
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D5" t="e" vm="64">
         <v>#VALUE!</v>
@@ -29339,7 +29479,7 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D6" t="e" vm="65">
         <v>#VALUE!</v>
@@ -29360,7 +29500,7 @@
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="27" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D8" t="e" vm="67">
         <v>#VALUE!</v>
@@ -29372,197 +29512,197 @@
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="28" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="27" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="28" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="28" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="28" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="28" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="28" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="27" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="28" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="28" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="28" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="28" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="28" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="27" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="28" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="28" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="27" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="28" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="28" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="28" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="28" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="27" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="28" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="28" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="28" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -29592,7 +29732,7 @@
   <sheetData>
     <row r="1" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="107" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B1" s="96"/>
       <c r="C1" s="96"/>
@@ -29614,7 +29754,7 @@
     </row>
     <row r="2" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="124" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B2" s="125"/>
       <c r="C2" s="125"/>
@@ -29630,27 +29770,27 @@
     </row>
     <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="130" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B3" s="119"/>
       <c r="C3" s="151" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D3" s="119"/>
       <c r="E3" s="152" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F3" s="119"/>
       <c r="G3" s="118" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="H3" s="119"/>
       <c r="I3" s="120" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J3" s="119"/>
       <c r="K3" s="156" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="L3" s="157"/>
     </row>
@@ -29688,201 +29828,201 @@
     </row>
     <row r="5" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="133" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B5" s="122"/>
       <c r="C5" s="121" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D5" s="122"/>
       <c r="E5" s="121" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F5" s="122"/>
       <c r="G5" s="121" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H5" s="122"/>
       <c r="I5" s="121" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J5" s="122"/>
       <c r="K5" s="158" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="L5" s="109"/>
     </row>
     <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="114" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B6" s="115"/>
       <c r="C6" s="131" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D6" s="115"/>
       <c r="E6" s="131" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F6" s="115"/>
       <c r="G6" s="117" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="H6" s="115"/>
       <c r="I6" s="131" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J6" s="115"/>
       <c r="K6" s="154" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="L6" s="155"/>
       <c r="O6" t="s">
+        <v>319</v>
+      </c>
+      <c r="S6" t="s">
+        <v>320</v>
+      </c>
+      <c r="V6" t="s">
+        <v>321</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>322</v>
+      </c>
+      <c r="AA6" t="s">
         <v>323</v>
       </c>
-      <c r="S6" t="s">
+      <c r="AE6" t="s">
         <v>324</v>
       </c>
-      <c r="V6" t="s">
+      <c r="AF6" t="s">
         <v>325</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AH6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>325</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AK6" t="s">
         <v>326</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AL6" t="s">
         <v>327</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AM6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AN6" t="s">
         <v>328</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AO6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AP6" t="s">
         <v>329</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AQ6" t="s">
+        <v>330</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>324</v>
+      </c>
+      <c r="AT6" t="s">
         <v>328</v>
       </c>
-      <c r="AI6" t="s">
-        <v>329</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>328</v>
-      </c>
-      <c r="AK6" t="s">
+      <c r="AU6" t="s">
         <v>330</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>331</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>328</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>332</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>328</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>333</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>334</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>328</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>332</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="F7" s="34" t="s">
         <v>335</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="C7" s="34" t="s">
+      <c r="G7" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="H7" s="34" t="s">
         <v>336</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>338</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>339</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>340</v>
       </c>
       <c r="I7" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K7" s="36"/>
       <c r="O7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="P7" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="Q7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="S7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="T7" t="s">
         <v>62</v>
       </c>
       <c r="V7" t="s">
+        <v>324</v>
+      </c>
+      <c r="W7" t="s">
+        <v>326</v>
+      </c>
+      <c r="X7" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>324</v>
+      </c>
+      <c r="Z7" t="s">
         <v>328</v>
       </c>
-      <c r="W7" t="s">
-        <v>330</v>
-      </c>
-      <c r="X7" t="s">
-        <v>331</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>328</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>332</v>
-      </c>
       <c r="AA7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="AB7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AC7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AE7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AF7">
         <v>83.3333333333333</v>
       </c>
       <c r="AH7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AI7">
         <v>83.3</v>
       </c>
       <c r="AJ7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AK7">
         <v>8</v>
@@ -29891,13 +30031,13 @@
         <v>3</v>
       </c>
       <c r="AM7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AN7">
         <v>52.2</v>
       </c>
       <c r="AO7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AP7">
         <v>4.5</v>
@@ -29906,7 +30046,7 @@
         <v>33.6</v>
       </c>
       <c r="AS7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AT7">
         <v>20.173600073636401</v>
@@ -29917,7 +30057,7 @@
     </row>
     <row r="8" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="116" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B8" s="96"/>
       <c r="C8" s="96"/>
@@ -29983,19 +30123,19 @@
         <v>0.35404498597134726</v>
       </c>
       <c r="AE8" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AF8">
         <v>83.3333333333333</v>
       </c>
       <c r="AH8" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AI8">
         <v>83.3</v>
       </c>
       <c r="AJ8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -30004,13 +30144,13 @@
         <v>3</v>
       </c>
       <c r="AM8" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AN8">
         <v>51.1</v>
       </c>
       <c r="AO8" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AP8">
         <v>3.7</v>
@@ -30019,7 +30159,7 @@
         <v>32.4</v>
       </c>
       <c r="AS8" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AT8">
         <v>44.5724369425714</v>
@@ -30121,19 +30261,19 @@
         <v>0.13667813232291248</v>
       </c>
       <c r="AE9" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AF9">
         <v>59.375</v>
       </c>
       <c r="AH9" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AI9">
         <v>59.4</v>
       </c>
       <c r="AJ9" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AK9">
         <v>8</v>
@@ -30142,13 +30282,13 @@
         <v>1</v>
       </c>
       <c r="AM9" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AN9">
         <v>45.6</v>
       </c>
       <c r="AO9" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AP9">
         <v>1.1000000000000001</v>
@@ -30157,7 +30297,7 @@
         <v>28.4</v>
       </c>
       <c r="AS9" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AT9">
         <v>28.571278521519002</v>
@@ -30259,19 +30399,19 @@
         <v>0.33962554586669502</v>
       </c>
       <c r="AE10" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AF10">
         <v>54</v>
       </c>
       <c r="AH10" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AI10">
         <v>54</v>
       </c>
       <c r="AJ10" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AK10">
         <v>8</v>
@@ -30280,13 +30420,13 @@
         <v>3</v>
       </c>
       <c r="AM10" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AN10">
         <v>44.8</v>
       </c>
       <c r="AO10" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AP10">
         <v>1.8</v>
@@ -30295,7 +30435,7 @@
         <v>25</v>
       </c>
       <c r="AS10" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AT10">
         <v>24.369253736000001</v>
@@ -30397,19 +30537,19 @@
         <v>0.25482976969404003</v>
       </c>
       <c r="AE11" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="AF11">
         <v>41.6666666666667</v>
       </c>
       <c r="AH11" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="AI11">
         <v>41.7</v>
       </c>
       <c r="AJ11" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AK11">
         <v>8</v>
@@ -30418,13 +30558,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AN11">
         <v>43.6</v>
       </c>
       <c r="AO11" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AP11">
         <v>0.6</v>
@@ -30433,7 +30573,7 @@
         <v>23.3</v>
       </c>
       <c r="AS11" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="AT11">
         <v>51.179748126470599</v>
@@ -30535,19 +30675,19 @@
         <v>1.7035846360751394E-2</v>
       </c>
       <c r="AE12" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AF12">
         <v>38.3333333333333</v>
       </c>
       <c r="AH12" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AI12">
         <v>38.299999999999997</v>
       </c>
       <c r="AJ12" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="AK12">
         <v>7</v>
@@ -30556,13 +30696,13 @@
         <v>3</v>
       </c>
       <c r="AM12" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="AN12">
         <v>40.299999999999997</v>
       </c>
       <c r="AO12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AP12">
         <v>-0.1</v>
@@ -30571,7 +30711,7 @@
         <v>20.8</v>
       </c>
       <c r="AS12" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AT12">
         <v>25.7039266520833</v>
@@ -30621,10 +30761,10 @@
         <v>22.692192080416664</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="M13" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -30679,19 +30819,19 @@
         <v>0.24553423525971096</v>
       </c>
       <c r="AE13" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AF13">
         <v>37.5</v>
       </c>
       <c r="AH13" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="AI13">
         <v>37.5</v>
       </c>
       <c r="AJ13" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="AK13">
         <v>7</v>
@@ -30700,13 +30840,13 @@
         <v>3</v>
       </c>
       <c r="AM13" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="AN13">
         <v>38.9</v>
       </c>
       <c r="AO13" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="AP13">
         <v>4.7</v>
@@ -30715,7 +30855,7 @@
         <v>32.9</v>
       </c>
       <c r="AS13" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AT13">
         <v>29.589673076923098</v>
@@ -30765,7 +30905,7 @@
         <v>27.293807692307691</v>
       </c>
       <c r="L14" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="M14">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN64,"&gt;=8")</f>
@@ -30824,19 +30964,19 @@
         <v>0.15723005465088957</v>
       </c>
       <c r="AE14" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AF14">
         <v>37.142857142857103</v>
       </c>
       <c r="AH14" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="AI14">
         <v>37.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="AK14">
         <v>7</v>
@@ -30845,13 +30985,13 @@
         <v>2</v>
       </c>
       <c r="AM14" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AN14">
         <v>38.5</v>
       </c>
       <c r="AO14" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AP14">
         <v>-4.2</v>
@@ -30860,7 +31000,7 @@
         <v>13.7</v>
       </c>
       <c r="AS14" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AT14">
         <v>26.244954871232899</v>
@@ -30910,7 +31050,7 @@
         <v>24.661489883561643</v>
       </c>
       <c r="L15" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="M15">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN64,"&gt;=7",'Watchlist Ratings'!AN4:AN64,"&lt;8")</f>
@@ -30969,19 +31109,19 @@
         <v>0.34414353629850369</v>
       </c>
       <c r="AE15" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AF15">
         <v>36.1111111111111</v>
       </c>
       <c r="AH15" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AI15">
         <v>36.1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AK15">
         <v>7</v>
@@ -30990,13 +31130,13 @@
         <v>2</v>
       </c>
       <c r="AM15" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AN15">
         <v>37.700000000000003</v>
       </c>
       <c r="AO15" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AP15">
         <v>-8</v>
@@ -31005,7 +31145,7 @@
         <v>13.5</v>
       </c>
       <c r="AS15" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AT15">
         <v>27.905545425233299</v>
@@ -31055,7 +31195,7 @@
         <v>21.185176984260604</v>
       </c>
       <c r="L16" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="M16">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN64,"&gt;=6",'Watchlist Ratings'!AN4:AN64,"&lt;7")</f>
@@ -31114,19 +31254,19 @@
         <v>0.1501292474376974</v>
       </c>
       <c r="AE16" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AF16">
         <v>32.142857142857103</v>
       </c>
       <c r="AH16" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AI16">
         <v>32.1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AK16">
         <v>7</v>
@@ -31135,13 +31275,13 @@
         <v>3</v>
       </c>
       <c r="AM16" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="AN16">
         <v>29.6</v>
       </c>
       <c r="AO16" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AP16">
         <v>-7.9</v>
@@ -31150,7 +31290,7 @@
         <v>12.3</v>
       </c>
       <c r="AS16" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="AT16">
         <v>52.2229498644231</v>
@@ -31200,7 +31340,7 @@
         <v>48.141288886538462</v>
       </c>
       <c r="L17" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="M17">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN64,"&lt;6")</f>
@@ -31259,7 +31399,7 @@
         <v>6.9229397135512238E-2</v>
       </c>
       <c r="AS17" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="AT17">
         <v>37.736707694444398</v>
@@ -31353,7 +31493,7 @@
         <v>5.0833735875018826E-2</v>
       </c>
       <c r="AS18" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="AT18">
         <v>24.612029698461502</v>
@@ -31447,7 +31587,7 @@
         <v>0.13663154593919979</v>
       </c>
       <c r="AS19" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="AT19">
         <v>45.617441111111098</v>
@@ -31541,7 +31681,7 @@
         <v>5.2655928593337009E-3</v>
       </c>
       <c r="AS20" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="AT20">
         <v>43.630936634999998</v>
@@ -31635,7 +31775,7 @@
         <v>8.6208283772470695E-2</v>
       </c>
       <c r="AS21" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="AT21">
         <v>38.120501266027397</v>
@@ -31745,7 +31885,7 @@
     </row>
     <row r="24" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="106" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B24" s="96"/>
       <c r="C24" s="96"/>
@@ -31923,7 +32063,7 @@
     <row r="61" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="141" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B62" s="96"/>
       <c r="C62" s="96"/>
@@ -31933,7 +32073,7 @@
       <c r="G62" s="96"/>
       <c r="H62" s="96"/>
       <c r="J62" s="148" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="K62" s="96"/>
       <c r="L62" s="96"/>
@@ -31945,52 +32085,52 @@
     </row>
     <row r="63" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="61" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B63" s="61" t="s">
+        <v>372</v>
+      </c>
+      <c r="C63" s="61" t="s">
+        <v>373</v>
+      </c>
+      <c r="D63" s="61" t="s">
+        <v>374</v>
+      </c>
+      <c r="E63" s="61" t="s">
+        <v>338</v>
+      </c>
+      <c r="F63" s="61" t="s">
+        <v>337</v>
+      </c>
+      <c r="G63" s="61" t="s">
+        <v>375</v>
+      </c>
+      <c r="H63" s="61" t="s">
         <v>376</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="J63" s="62" t="s">
+        <v>324</v>
+      </c>
+      <c r="K63" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="D63" s="61" t="s">
+      <c r="L63" s="62" t="s">
         <v>378</v>
       </c>
-      <c r="E63" s="61" t="s">
-        <v>342</v>
-      </c>
-      <c r="F63" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="G63" s="61" t="s">
+      <c r="M63" s="62" t="s">
         <v>379</v>
       </c>
-      <c r="H63" s="61" t="s">
+      <c r="N63" s="62" t="s">
         <v>380</v>
       </c>
-      <c r="J63" s="62" t="s">
-        <v>328</v>
-      </c>
-      <c r="K63" s="62" t="s">
+      <c r="O63" s="62" t="s">
+        <v>326</v>
+      </c>
+      <c r="P63" s="62" t="s">
         <v>381</v>
       </c>
-      <c r="L63" s="62" t="s">
+      <c r="Q63" s="62" t="s">
         <v>382</v>
-      </c>
-      <c r="M63" s="62" t="s">
-        <v>383</v>
-      </c>
-      <c r="N63" s="62" t="s">
-        <v>384</v>
-      </c>
-      <c r="O63" s="62" t="s">
-        <v>330</v>
-      </c>
-      <c r="P63" s="62" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q63" s="62" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -32614,7 +32754,7 @@
     </row>
     <row r="74" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="75" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B74" s="76" t="str">
         <f ca="1">VLOOKUP(A74,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32645,7 +32785,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J74" s="78" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -32678,7 +32818,7 @@
     </row>
     <row r="75" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="79" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B75" s="80" t="str">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32709,7 +32849,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J75" s="79" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="K75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -32742,7 +32882,7 @@
     </row>
     <row r="76" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="134" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B76" s="96"/>
       <c r="C76" s="96"/>
@@ -32763,7 +32903,7 @@
     </row>
     <row r="77" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="79" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B77" s="80" t="str">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32794,7 +32934,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J77" s="79" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -32827,35 +32967,35 @@
     </row>
     <row r="78" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="126" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B78" s="111"/>
       <c r="C78" s="110" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D78" s="111"/>
       <c r="E78" s="129" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F78" s="111"/>
       <c r="G78" s="129" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H78" s="111"/>
       <c r="I78" s="162" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="J78" s="96"/>
       <c r="K78" s="126" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="L78" s="111"/>
       <c r="M78" s="126" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="N78" s="111"/>
       <c r="O78" s="126" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="P78" s="111"/>
       <c r="Q78" s="82" t="str">
@@ -32957,7 +33097,7 @@
     </row>
     <row r="81" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="79" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B81" s="80" t="str">
         <f ca="1">VLOOKUP(A81,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -32988,7 +33128,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J81" s="79" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="K81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -33021,7 +33161,7 @@
     </row>
     <row r="82" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="167" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B82" s="96"/>
       <c r="C82" s="96"/>
@@ -33042,7 +33182,7 @@
     </row>
     <row r="83" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="83" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B83" s="84" t="str">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$64,4,FALSE())</f>
@@ -33073,7 +33213,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J83" s="83" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="K83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$64,36,FALSE())</f>
@@ -33107,7 +33247,7 @@
     <row r="84" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="85" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="146" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B85" s="96"/>
       <c r="C85" s="96"/>
@@ -33129,35 +33269,35 @@
     <row r="86" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="168" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B87" s="96"/>
       <c r="C87" s="113" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D87" s="96"/>
       <c r="E87" s="164" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F87" s="96"/>
       <c r="G87" s="142" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H87" s="96"/>
       <c r="I87" s="143" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="J87" s="96"/>
       <c r="K87" s="112" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="L87" s="96"/>
       <c r="M87" s="139" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="N87" s="96"/>
       <c r="O87" s="149" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="P87" s="96"/>
     </row>
@@ -33248,7 +33388,7 @@
     <row r="90" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="105" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B91" s="96"/>
       <c r="C91" s="96"/>
@@ -33397,7 +33537,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -33408,1413 +33548,1806 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B2" t="s">
         <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B3" t="s">
         <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="D3" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E3" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B4" t="s">
         <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D4" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D5" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E5" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C6" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D6" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="E6" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B7" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D7" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E7" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B8" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C8" t="s">
+        <v>428</v>
+      </c>
+      <c r="D8" t="s">
         <v>432</v>
       </c>
-      <c r="D8" t="s">
-        <v>436</v>
-      </c>
       <c r="E8" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B9" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C9" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D9" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E9" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B10" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C10" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D10" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E10" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B11" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C11" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D11" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E11" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B12" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C12" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D12" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E12" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B13" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="E13" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B14" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C14" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D14" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="E14" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B15" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D15" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E15" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B16" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C16" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D16" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E16" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B17" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C17" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D17" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="E17" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B18" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C18" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D18" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E18" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B19" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C19" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D19" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E19" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B20" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C20" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D20" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E20" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B21" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C21" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D21" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E21" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B22" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C22" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D22" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E22" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B23" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C23" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D23" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E23" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B24" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C24" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D24" t="s">
+        <v>463</v>
+      </c>
+      <c r="E24" t="s">
         <v>467</v>
-      </c>
-      <c r="E24" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B25" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C25" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D25" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E25" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B26" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C26" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D26" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E26" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B27" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C27" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D27" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E27" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B28" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C28" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D28" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E28" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B29" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C29" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D29" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E29" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B30" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C30" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D30" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E30" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B31" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C31" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D31" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E31" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B32" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C32" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D32" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E32" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B33" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C33" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D33" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E33" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B34" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C34" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D34" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E34" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B35" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C35" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D35" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E35" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B36" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C36" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D36" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E36" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B37" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C37" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D37" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E37" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B38" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C38" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D38" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E38" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B39" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C39" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D39" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E39" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B40" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C40" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D40" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E40" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C41" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D41" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E41" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B42" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C42" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D42" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E42" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B43" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C43" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D43" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E43" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B44" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C44" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D44" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E44" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B45" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C45" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D45" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E45" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B46" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C46" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D46" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E46" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B47" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C47" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D47" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E47" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C48" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D48" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E48" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B49" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C49" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D49" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E49" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B50" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C50" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D50" t="s">
+        <v>508</v>
+      </c>
+      <c r="E50" t="s">
         <v>512</v>
-      </c>
-      <c r="E50" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C51" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D51" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="E51" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B52" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C52" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D52" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="E52" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C53" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D53" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E53" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C54" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D54" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E54" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B55" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C55" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D55" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E55" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C56" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D56" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E56" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B57" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C57" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D57" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E57" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B58" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C58" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D58" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E58" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B59" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C59" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D59" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E59" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B60" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C60" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D60" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E60" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B61" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C61" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D61" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E61" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B62" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C62" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D62" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E62" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B63" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C63" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D63" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E63" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C64" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D64" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E64" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B65" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C65" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D65" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E65" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B66" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C66" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D66" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E66" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C67" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D67" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E67" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B68" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C68" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D68" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E68" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B69" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C69" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D69" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="E69" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B70" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C70" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D70" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="E70" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B71" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C71" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D71" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E71" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B72" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C72" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D72" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="E72" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B73" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C73" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D73" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E73" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B74" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C74" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D74" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="E74" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>347</v>
+      </c>
+      <c r="B75" t="s">
+        <v>493</v>
+      </c>
+      <c r="C75" t="s">
         <v>351</v>
       </c>
-      <c r="B75" t="s">
-        <v>497</v>
-      </c>
-      <c r="C75" t="s">
-        <v>355</v>
-      </c>
       <c r="D75" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E75" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B76" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C76" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D76" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="E76" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>489</v>
+      </c>
+      <c r="B77" t="s">
         <v>493</v>
       </c>
-      <c r="B77" t="s">
-        <v>497</v>
-      </c>
       <c r="C77" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D77" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E77" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B78" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C78" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D78" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="E78" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B79" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C79" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D79" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="E79" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B80" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C80" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D80" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="E80" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B81" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C81" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D81" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E81" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B82" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C82" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D82" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="E82" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>570</v>
+      </c>
+      <c r="B83" t="s">
+        <v>493</v>
+      </c>
+      <c r="C83" t="s">
+        <v>571</v>
+      </c>
+      <c r="D83" t="s">
+        <v>572</v>
+      </c>
+      <c r="E83" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>482</v>
+      </c>
+      <c r="B84" t="s">
         <v>574</v>
       </c>
-      <c r="B83" t="s">
-        <v>497</v>
-      </c>
-      <c r="C83" t="s">
-        <v>575</v>
-      </c>
-      <c r="D83" t="s">
-        <v>576</v>
-      </c>
-      <c r="E83" t="s">
-        <v>577</v>
+      <c r="C84" t="s">
+        <v>581</v>
+      </c>
+      <c r="D84" t="s">
+        <v>582</v>
+      </c>
+      <c r="E84" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>584</v>
+      </c>
+      <c r="B85" t="s">
+        <v>574</v>
+      </c>
+      <c r="C85" t="s">
+        <v>581</v>
+      </c>
+      <c r="D85" t="s">
+        <v>585</v>
+      </c>
+      <c r="E85" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>472</v>
+      </c>
+      <c r="B86" t="s">
+        <v>574</v>
+      </c>
+      <c r="C86" t="s">
+        <v>581</v>
+      </c>
+      <c r="D86" t="s">
+        <v>587</v>
+      </c>
+      <c r="E86" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>479</v>
+      </c>
+      <c r="B87" t="s">
+        <v>574</v>
+      </c>
+      <c r="C87" t="s">
+        <v>581</v>
+      </c>
+      <c r="D87" t="s">
+        <v>589</v>
+      </c>
+      <c r="E87" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>481</v>
+      </c>
+      <c r="B88" t="s">
+        <v>574</v>
+      </c>
+      <c r="C88" t="s">
+        <v>581</v>
+      </c>
+      <c r="D88" t="s">
+        <v>591</v>
+      </c>
+      <c r="E88" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>593</v>
+      </c>
+      <c r="B89" t="s">
+        <v>574</v>
+      </c>
+      <c r="C89" t="s">
+        <v>581</v>
+      </c>
+      <c r="D89" t="s">
+        <v>594</v>
+      </c>
+      <c r="E89" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>487</v>
+      </c>
+      <c r="B90" t="s">
+        <v>574</v>
+      </c>
+      <c r="C90" t="s">
+        <v>581</v>
+      </c>
+      <c r="D90" t="s">
+        <v>596</v>
+      </c>
+      <c r="E90" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>598</v>
+      </c>
+      <c r="B91" t="s">
+        <v>574</v>
+      </c>
+      <c r="C91" t="s">
+        <v>581</v>
+      </c>
+      <c r="D91" t="s">
+        <v>599</v>
+      </c>
+      <c r="E91" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>492</v>
+      </c>
+      <c r="B92" t="s">
+        <v>574</v>
+      </c>
+      <c r="C92" t="s">
+        <v>581</v>
+      </c>
+      <c r="D92" t="s">
+        <v>601</v>
+      </c>
+      <c r="E92" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>353</v>
+      </c>
+      <c r="B93" t="s">
+        <v>574</v>
+      </c>
+      <c r="C93" t="s">
+        <v>603</v>
+      </c>
+      <c r="D93" t="s">
+        <v>604</v>
+      </c>
+      <c r="E93" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>449</v>
+      </c>
+      <c r="B94" t="s">
+        <v>574</v>
+      </c>
+      <c r="C94" t="s">
+        <v>603</v>
+      </c>
+      <c r="D94" t="s">
+        <v>606</v>
+      </c>
+      <c r="E94" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>483</v>
+      </c>
+      <c r="B95" t="s">
+        <v>574</v>
+      </c>
+      <c r="C95" t="s">
+        <v>603</v>
+      </c>
+      <c r="D95" t="s">
+        <v>608</v>
+      </c>
+      <c r="E95" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>BN; BO; BP (est.)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Q4 FY26 press release (29/07/2026) - microsoft.com/investor</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Q4 FY26: ingresos $90,0B (+18%, bate $87,7B e.), BPA aj. $4,74 (bate $4,24e). Azure +43% (Intelligent Cloud $39,3B, +32%). FY26 completo: ingresos $331,8B (+18%), BN $133,7B (+31%); Azure supera $100B (+41%) por primera vez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BN; BO; BP (est.)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Q2 2026 results (29/07/2026) - investor.atmeta.com</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Q2: ingresos $60,8B (+28%, bate estimacion) por impresiones +14% y precio/anuncio +12%; pero BPA $6,18 vs $7,22e (-13% i.a.) por gastos +55% a $42,0B (capex IA). FCF se desploma a $784M. Accion -9,6% tras publicar. Guia Q3 hasta $64B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>FICO</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BN; BO; BP (est.)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Q3 FY26 results (29/07/2026) - SEC 8-K</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Q3 FY26: ingresos $674M (+26% i.a.), BPA GAAP $10,45 (BN $237,2M) vs $7,40 ano anterior; BPA aj. $12,18 bate $12,02e (+42%). Sube guia FY26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SU</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BN; BO; BP (est.)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Resultats S1 2026 (30/07/2026) - se.com</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>S1 record: ingresos EUR21,23B (+9,8% reportado, +14% organico); EBITA aj. EUR4,09B (+16,6%/+22,1% organico), margen 19,3% (+1,2pt). Sube guia FY26: EBITA organico +14-19% (antes +10-15%), ventas organicas +10-13%. Impulsado por demanda de centros de datos (Norteamerica, China).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BN; BO; BP (est.)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Risultati H1 2026 (30/07/2026) - prysmian.com</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>S1: ingresos EUR11,24B (+7,2% organico); EBITDA EUR1,33B (+17,6%); BN EUR569M (+34,2% desde EUR424M). Sube guia FY26: EBITDA EUR2,8-2,9B (antes EUR2,63-2,78B), caja generada EUR1,65-1,75B (antes EUR1,3-1,4B). Digital Solutions +18%, Power Grid +13%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CHKP</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BN; BO; BP (est.)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Q2 2026 financial results (30/07/2026) - checkpoint.com</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Q2: ingresos $673,6M (+1% i.a., miss de $689,9Me); BPA no-GAAP $2,55 bate $2,50e (+8%); BPA GAAP $1,87 (+2%). Suscripciones de seguridad $332,6M (+12%). Accion cayo pese al beat de BPA por el miss de ingresos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TGYM</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>BN; BO; BP (est.)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Risultati H1 2026 (30/07/2026) - corporate.technogym.com</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>S1: ingresos EUR493M (+7,4%, +9% a tipos de cambio constantes); EBITDA aj. EUR85,7M (+1%); BN aj. EUR43,8M (estable). Posicion financiera neta positiva +EUR89M. CEO: 2026 ano de transicion hacia 'Vision 2031' (nuevo Healthness Lab, nueva planta, inversion en IA).</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Cosas Roger\BOLSA E INVERSIÓN\repos\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519282A0-CAB6-4F49-ACBF-E38E5FBCC42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F99D64-7EF0-41C5-8E9A-ED9C89461194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Watchlist Ratings" sheetId="1" r:id="rId1"/>
@@ -2448,7 +2448,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1459" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="686">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -2862,9 +2862,6 @@
     <t>2026-04-26</t>
   </si>
   <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
     <t>Healthcare</t>
   </si>
   <si>
@@ -4501,6 +4498,51 @@
   </si>
   <si>
     <t>Codigos de mercado: Verallia XWBO-&gt;XPAR (Euronext Paris) y Kingspan XFRA-&gt;XDUB (Euronext Dublin). Nuevo tipo de cambio en Framework Notes E9 = 1,3641 USD/GBP. AVISO: los tipos E4:E8 estan congelados porque la columna D, que deberia traerlos en vivo, esta en #VALUE! en las cinco filas.</t>
+  </si>
+  <si>
+    <t>AV; AS; AP; AQ; AU; AT; BN</t>
+  </si>
+  <si>
+    <t>Verificacion del top 10 contra investor relations - FY2026 (29-jul-2026)</t>
+  </si>
+  <si>
+    <t>El ejercicio cerro el 30-jun-2026, asi que el ano fiscal ES el LTM. Ingresos 270.000 -&gt; 331.839 (+18%). FCF 70.000 -&gt; 66.987 (flujo de operaciones 182.935 menos capex 115.948). Caja 78.000 -&gt; 76.843. Deuda 45.000 -&gt; 40.294. EBITDA 144.000 -&gt; 193.771 (resultado operativo 155.237 + D&amp;A y otros 38.534). NOPAT 90.000 -&gt; 125.127 (EBIT por 1 menos la tasa fiscal efectiva del 19,4%). AVISO: el FCF del Q4 cayo un 23% y la guia de capex del ano natural 2026 es de unos 190.000 M$, asi que este FCF es la ultima foto antes de la caida.</t>
+  </si>
+  <si>
+    <t>AV; AS; AP; AQ; BO; BN</t>
+  </si>
+  <si>
+    <t>Verificacion del top 10 contra investor relations - Q2 2026 (30-jul-2026)</t>
+  </si>
+  <si>
+    <t>Ingresos 637.000 -&gt; 775.656 TTM (FY2025 716.900 menos 1S2025 323.369 mas 1S2026 382.125). FCF 52.000 -&gt; -7.604: el flujo de caja libre TTM es NEGATIVO porque el capex TTM (169.007) supera al flujo de operaciones (161.403), tras subir 66.100 M$ interanuales. No es deterioro sino inversion en infraestructura de IA, y el flujo de operaciones crece un 33%. El EV/FCF queda negativo a proposito: el multiplo no aplica en un ciclo de capex, y la valoracion se apoya en las columnas FCF@5y, que son la vision forward. Caja 80.000 -&gt; 78.213 (aparte hay 44.775 de valores negociables). Deuda 65.000 -&gt; 128.894 (deuda a largo plazo reportada). EBITDA y NOPAT NO se tocan: no hay cifras TTM exactas publicadas.</t>
+  </si>
+  <si>
+    <t>AV; AU; BO; BN</t>
+  </si>
+  <si>
+    <t>Verificacion del top 10 contra investor relations - 1S2026 (7-ago-2026)</t>
+  </si>
+  <si>
+    <t>La fila llevaba sin actualizarse desde el 26-abr y se habia perdido el semestre. Ingresos 1.200 -&gt; 1.446,8 LTM (FY2025 1.355,0 menos 1S2025 657,3 mas 1S2026 749,1). EBITDA subyacente 260 -&gt; 300,4 (273,4 menos 129,3 mas 156,3). Biscoff crecio mas del 20% en volumen y en ingresos a la vez; EBIT subyacente del semestre 131,0 (17,5%) y beneficio neto +23,5%. NOPAT no se toca: falta el EBIT subyacente de 2025.</t>
+  </si>
+  <si>
+    <t>BP; BN</t>
+  </si>
+  <si>
+    <t>Verificacion del top 10 contra investor relations - Calendario</t>
+  </si>
+  <si>
+    <t>Los resultados del Q2 FY2027 son el 10-sep-2026, no el 9. El resto de la fila esta al dia: el Q1 FY2027 del 3-jun ya estaba recogido.</t>
+  </si>
+  <si>
+    <t>AZ (Capital Employed)</t>
+  </si>
+  <si>
+    <t>Verificacion del top 10 - coherencia del ROIC</t>
+  </si>
+  <si>
+    <t>Capital empleado 280.000 -&gt; 589.551 (activo total 758.376 menos pasivo corriente 168.825 a 30-jun-2026). Era necesario porque al actualizar el NOPAT a 125.127 con el capital empleado viejo el ROIC saltaba al 44,7%, imposible para Microsoft. Con la cifra correcta queda en 21,2%. AVISO IMPORTANTE: la columna Capital Employed son estimaciones manuales redondeadas en las otras 67 filas (Veeva 1.500, Costco 40.000, Amazon 300.000, Lotus 800...) y no siguen ninguna definicion homogenea, asi que el ROIC NO es comparable entre empresas hasta que esa columna tenga una sola definicion. Esta fila es ahora la unica con la definicion de libro.</t>
   </si>
 </sst>
 </file>
@@ -5431,7 +5473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5677,6 +5719,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -6671,7 +6716,7 @@
                   <c:v>0.2716311384364436</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.6428327251210062E-2</c:v>
+                  <c:v>6.6632314867387743E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.27406080160124957</c:v>
@@ -6695,7 +6740,7 @@
                   <c:v>9.0098171806134886E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>4.2346765118855378E-2</c:v>
+                  <c:v>3.7107521210228311E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>3.658617807367448E-2</c:v>
@@ -15325,14 +15370,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BP71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
@@ -15356,167 +15401,167 @@
     <col min="38" max="38" width="8" customWidth="1"/>
     <col min="39" max="39" width="10" customWidth="1"/>
     <col min="40" max="40" width="11" customWidth="1"/>
-    <col min="41" max="41" width="7.85546875" customWidth="1"/>
-    <col min="42" max="42" width="9.140625" customWidth="1"/>
-    <col min="43" max="43" width="7.5703125" customWidth="1"/>
-    <col min="44" max="44" width="10.28515625" customWidth="1"/>
-    <col min="46" max="47" width="7.5703125" customWidth="1"/>
-    <col min="48" max="48" width="9.140625" customWidth="1"/>
-    <col min="49" max="49" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="11.85546875" customWidth="1"/>
-    <col min="52" max="52" width="9.140625" customWidth="1"/>
+    <col min="41" max="41" width="7.81640625" customWidth="1"/>
+    <col min="42" max="42" width="9.1796875" customWidth="1"/>
+    <col min="43" max="43" width="7.54296875" customWidth="1"/>
+    <col min="44" max="44" width="10.26953125" customWidth="1"/>
+    <col min="46" max="47" width="7.54296875" customWidth="1"/>
+    <col min="48" max="48" width="9.1796875" customWidth="1"/>
+    <col min="49" max="49" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="11.81640625" customWidth="1"/>
+    <col min="52" max="52" width="9.1796875" customWidth="1"/>
     <col min="56" max="56" width="10" customWidth="1"/>
-    <col min="57" max="57" width="7.85546875" customWidth="1"/>
-    <col min="58" max="58" width="9.140625" customWidth="1"/>
-    <col min="59" max="59" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="60" max="61" width="11.28515625" customWidth="1"/>
-    <col min="62" max="62" width="9.5703125" customWidth="1"/>
-    <col min="63" max="63" width="10.5703125" customWidth="1"/>
-    <col min="64" max="65" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="9.5703125" customWidth="1"/>
-    <col min="67" max="67" width="11.85546875" customWidth="1"/>
+    <col min="57" max="57" width="7.81640625" customWidth="1"/>
+    <col min="58" max="58" width="9.1796875" customWidth="1"/>
+    <col min="59" max="59" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="60" max="61" width="11.26953125" customWidth="1"/>
+    <col min="62" max="62" width="9.54296875" customWidth="1"/>
+    <col min="63" max="63" width="10.54296875" customWidth="1"/>
+    <col min="64" max="65" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="9.54296875" customWidth="1"/>
+    <col min="67" max="67" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:68" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="100"/>
-      <c r="T1" s="100"/>
-      <c r="U1" s="100"/>
-      <c r="V1" s="100"/>
-      <c r="W1" s="100"/>
-      <c r="X1" s="100"/>
-      <c r="Y1" s="100"/>
-      <c r="Z1" s="100"/>
-      <c r="AA1" s="100"/>
-      <c r="AB1" s="100"/>
-      <c r="AC1" s="100"/>
-      <c r="AD1" s="100"/>
-      <c r="AE1" s="100"/>
-      <c r="AF1" s="100"/>
-      <c r="AG1" s="100"/>
-      <c r="AH1" s="100"/>
-      <c r="AI1" s="100"/>
-      <c r="AJ1" s="100"/>
-      <c r="AK1" s="100"/>
-      <c r="AL1" s="100"/>
-      <c r="AM1" s="100"/>
-      <c r="AN1" s="100"/>
-      <c r="AO1" s="100"/>
-      <c r="AP1" s="100"/>
-      <c r="AQ1" s="100"/>
-      <c r="AR1" s="100"/>
-      <c r="AS1" s="100"/>
-      <c r="AT1" s="100"/>
-      <c r="AU1" s="100"/>
-      <c r="AV1" s="100"/>
-      <c r="AW1" s="100"/>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="101"/>
+      <c r="T1" s="101"/>
+      <c r="U1" s="101"/>
+      <c r="V1" s="101"/>
+      <c r="W1" s="101"/>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="101"/>
+      <c r="AC1" s="101"/>
+      <c r="AD1" s="101"/>
+      <c r="AE1" s="101"/>
+      <c r="AF1" s="101"/>
+      <c r="AG1" s="101"/>
+      <c r="AH1" s="101"/>
+      <c r="AI1" s="101"/>
+      <c r="AJ1" s="101"/>
+      <c r="AK1" s="101"/>
+      <c r="AL1" s="101"/>
+      <c r="AM1" s="101"/>
+      <c r="AN1" s="101"/>
+      <c r="AO1" s="101"/>
+      <c r="AP1" s="101"/>
+      <c r="AQ1" s="101"/>
+      <c r="AR1" s="101"/>
+      <c r="AS1" s="101"/>
+      <c r="AT1" s="101"/>
+      <c r="AU1" s="101"/>
+      <c r="AV1" s="101"/>
+      <c r="AW1" s="101"/>
     </row>
-    <row r="2" spans="1:68" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="107" t="s">
+    <row r="2" spans="1:68" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="108" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="102" t="s">
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="100"/>
-      <c r="R2" s="100"/>
-      <c r="S2" s="100"/>
-      <c r="T2" s="101" t="s">
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+      <c r="S2" s="101"/>
+      <c r="T2" s="102" t="s">
         <v>3</v>
       </c>
-      <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="100"/>
-      <c r="Y2" s="100"/>
-      <c r="Z2" s="100"/>
-      <c r="AA2" s="100"/>
-      <c r="AB2" s="100"/>
-      <c r="AC2" s="100"/>
-      <c r="AD2" s="105" t="s">
+      <c r="U2" s="101"/>
+      <c r="V2" s="101"/>
+      <c r="W2" s="101"/>
+      <c r="X2" s="101"/>
+      <c r="Y2" s="101"/>
+      <c r="Z2" s="101"/>
+      <c r="AA2" s="101"/>
+      <c r="AB2" s="101"/>
+      <c r="AC2" s="101"/>
+      <c r="AD2" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="AE2" s="100"/>
-      <c r="AF2" s="100"/>
-      <c r="AG2" s="100"/>
-      <c r="AH2" s="100"/>
-      <c r="AI2" s="100"/>
-      <c r="AJ2" s="100"/>
-      <c r="AK2" s="100"/>
-      <c r="AL2" s="100"/>
-      <c r="AM2" s="100"/>
-      <c r="AN2" s="103" t="s">
+      <c r="AE2" s="101"/>
+      <c r="AF2" s="101"/>
+      <c r="AG2" s="101"/>
+      <c r="AH2" s="101"/>
+      <c r="AI2" s="101"/>
+      <c r="AJ2" s="101"/>
+      <c r="AK2" s="101"/>
+      <c r="AL2" s="101"/>
+      <c r="AM2" s="101"/>
+      <c r="AN2" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="AO2" s="108" t="s">
+      <c r="AO2" s="109" t="s">
         <v>6</v>
       </c>
-      <c r="AP2" s="100"/>
-      <c r="AQ2" s="100"/>
-      <c r="AR2" s="100"/>
-      <c r="AS2" s="100"/>
-      <c r="AT2" s="100"/>
-      <c r="AU2" s="100"/>
-      <c r="AV2" s="100"/>
-      <c r="AW2" s="100"/>
-      <c r="AX2" s="100"/>
-      <c r="AY2" s="100"/>
-      <c r="AZ2" s="100"/>
-      <c r="BA2" s="100"/>
-      <c r="BB2" s="100"/>
-      <c r="BC2" s="100"/>
-      <c r="BD2" s="100"/>
-      <c r="BE2" s="100"/>
-      <c r="BF2" s="100"/>
+      <c r="AP2" s="101"/>
+      <c r="AQ2" s="101"/>
+      <c r="AR2" s="101"/>
+      <c r="AS2" s="101"/>
+      <c r="AT2" s="101"/>
+      <c r="AU2" s="101"/>
+      <c r="AV2" s="101"/>
+      <c r="AW2" s="101"/>
+      <c r="AX2" s="101"/>
+      <c r="AY2" s="101"/>
+      <c r="AZ2" s="101"/>
+      <c r="BA2" s="101"/>
+      <c r="BB2" s="101"/>
+      <c r="BC2" s="101"/>
+      <c r="BD2" s="101"/>
+      <c r="BE2" s="101"/>
+      <c r="BF2" s="101"/>
       <c r="BG2" s="1"/>
       <c r="BH2" s="1"/>
       <c r="BI2" s="1"/>
-      <c r="BJ2" s="106" t="s">
+      <c r="BJ2" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="BK2" s="100"/>
-      <c r="BL2" s="100"/>
-      <c r="BM2" s="100"/>
-      <c r="BN2" s="99" t="s">
+      <c r="BK2" s="101"/>
+      <c r="BL2" s="101"/>
+      <c r="BM2" s="101"/>
+      <c r="BN2" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="BO2" s="100"/>
-      <c r="BP2" s="100"/>
+      <c r="BO2" s="101"/>
+      <c r="BP2" s="101"/>
     </row>
-    <row r="3" spans="1:68" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:68" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -15634,7 +15679,7 @@
       <c r="AM3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AN3" s="100"/>
+      <c r="AN3" s="101"/>
       <c r="AO3" s="7" t="s">
         <v>48</v>
       </c>
@@ -15720,7 +15765,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="4" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="86" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -15952,7 +15997,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="86" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -16090,67 +16135,67 @@
         <v>78</v>
       </c>
       <c r="AP5" s="19">
-        <v>78000</v>
+        <v>76843</v>
       </c>
       <c r="AQ5" s="19">
-        <v>45000</v>
+        <v>40294</v>
       </c>
       <c r="AR5" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>3552275.8923499999</v>
+        <v>3548726.8923499999</v>
       </c>
       <c r="AS5" s="19">
-        <v>70000</v>
+        <v>66987</v>
       </c>
       <c r="AT5" s="19">
-        <v>90000</v>
+        <v>125127</v>
       </c>
       <c r="AU5" s="19">
-        <v>144000</v>
+        <v>193771</v>
       </c>
       <c r="AV5" s="19">
-        <v>270000</v>
+        <v>331839</v>
       </c>
       <c r="AW5" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>50.746798462142856</v>
+        <v>52.976352013823579</v>
       </c>
       <c r="AX5" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>24.66858258576389</v>
+        <v>18.31402476299343</v>
       </c>
       <c r="AY5" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>13.156577379074074</v>
+        <v>10.69412242789425</v>
       </c>
       <c r="AZ5" s="21">
-        <v>280000</v>
+        <v>589551</v>
       </c>
       <c r="BA5" s="22">
         <f t="shared" si="12"/>
-        <v>0.33333333333333331</v>
+        <v>0.37707141113612325</v>
       </c>
       <c r="BB5" s="22">
         <f t="shared" si="13"/>
-        <v>0.9642857142857143</v>
+        <v>0.56286733463262717</v>
       </c>
       <c r="BC5" s="23">
         <f t="shared" si="14"/>
-        <v>0.3214285714285714</v>
+        <v>0.21224118015235321</v>
       </c>
       <c r="BD5" s="98">
         <v>102853</v>
       </c>
       <c r="BE5" s="23">
         <f t="shared" si="15"/>
-        <v>8.0000072713343418E-2</v>
+        <v>8.9545288544927937E-2</v>
       </c>
       <c r="BF5" t="s">
         <v>83</v>
       </c>
       <c r="BG5" s="23">
         <f t="shared" si="16"/>
-        <v>0.1699994472920241</v>
+        <v>0.18034009219511105</v>
       </c>
       <c r="BH5" s="24">
         <v>20</v>
@@ -16160,22 +16205,22 @@
       </c>
       <c r="BJ5" s="25">
         <f t="shared" ca="1" si="17"/>
-        <v>281.46890228259338</v>
+        <v>281.94684699910914</v>
       </c>
       <c r="BK5" s="25">
         <f t="shared" ca="1" si="18"/>
-        <v>624.48345542313723</v>
+        <v>624.96140013965305</v>
       </c>
       <c r="BL5" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-0.10230824869655464</v>
+        <v>-0.10200359272389903</v>
       </c>
       <c r="BM5" s="23">
         <f t="shared" ca="1" si="20"/>
-        <v>6.6428327251210062E-2</v>
-      </c>
-      <c r="BN5" s="93" t="s">
-        <v>84</v>
+        <v>6.6632314867387743E-2</v>
+      </c>
+      <c r="BN5" s="99">
+        <v>46256</v>
       </c>
       <c r="BO5" s="93" t="s">
         <v>85</v>
@@ -16184,7 +16229,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="86" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -16416,7 +16461,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="86" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
@@ -16648,7 +16693,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="86" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
@@ -16880,7 +16925,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="86" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
@@ -17102,17 +17147,17 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.20330830951269752</v>
       </c>
-      <c r="BN9" t="s">
-        <v>93</v>
+      <c r="BN9" s="97">
+        <v>46256</v>
       </c>
       <c r="BO9" t="s">
         <v>80</v>
       </c>
-      <c r="BP9" t="s">
-        <v>97</v>
+      <c r="BP9" s="97">
+        <v>46304</v>
       </c>
     </row>
-    <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="86" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
@@ -17344,7 +17389,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="86" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
@@ -17576,7 +17621,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="86" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
@@ -17808,7 +17853,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="86" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -17946,17 +17991,17 @@
         <v>78</v>
       </c>
       <c r="AP13" s="19">
-        <v>80000</v>
+        <v>78213</v>
       </c>
       <c r="AQ13" s="19">
-        <v>65000</v>
+        <v>128894</v>
       </c>
       <c r="AR13" s="19">
         <f t="shared" ref="AR13:AR32" ca="1" si="21">I13-AP13+AQ13</f>
-        <v>2773368.9981</v>
+        <v>2839049.9981</v>
       </c>
       <c r="AS13" s="19">
-        <v>52000</v>
+        <v>-7604</v>
       </c>
       <c r="AT13" s="19">
         <v>55000</v>
@@ -17965,48 +18010,48 @@
         <v>138000</v>
       </c>
       <c r="AV13" s="19">
-        <v>637000</v>
+        <v>775656</v>
       </c>
       <c r="AW13" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>53.33401919423077</v>
+        <v>-373.36270359021569</v>
       </c>
       <c r="AX13" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>20.096876797826088</v>
+        <v>20.572826073188406</v>
       </c>
       <c r="AY13" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>4.3537974852433283</v>
+        <v>3.660192144584713</v>
       </c>
       <c r="AZ13" s="21">
         <v>300000</v>
       </c>
       <c r="BA13" s="22">
         <f t="shared" si="12"/>
-        <v>8.6342229199372053E-2</v>
+        <v>7.0907721979846738E-2</v>
       </c>
       <c r="BB13" s="22">
         <f t="shared" si="13"/>
-        <v>2.1233333333333335</v>
+        <v>2.5855199999999998</v>
       </c>
       <c r="BC13" s="23">
         <f t="shared" si="14"/>
-        <v>0.18333333333333335</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="BD13" s="98">
         <v>72933</v>
       </c>
       <c r="BE13" s="23">
         <f t="shared" si="15"/>
-        <v>7.0000909614846396E-2</v>
+        <v>-2.5717243949720334</v>
       </c>
       <c r="BF13" t="s">
         <v>112</v>
       </c>
       <c r="BG13" s="23">
         <f t="shared" si="16"/>
-        <v>0.16000049664691973</v>
+        <v>-2.7039247933124759</v>
       </c>
       <c r="BH13" s="24">
         <v>22.5</v>
@@ -18016,31 +18061,31 @@
       </c>
       <c r="BJ13" s="25">
         <f ca="1">(BD13*BH13+$AP13-$AQ13)/$H13</f>
-        <v>153.52724889234597</v>
+        <v>147.4379560758035</v>
       </c>
       <c r="BK13" s="25">
         <f ca="1">(BF13*BI13+$AP13-$AQ13)/$H13</f>
-        <v>305.15903956033156</v>
+        <v>299.06974674378915</v>
       </c>
       <c r="BL13" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-9.8965077025216064E-2</v>
+        <v>-0.10622872895036783</v>
       </c>
       <c r="BM13" s="23">
         <f t="shared" ca="1" si="20"/>
-        <v>4.2346765118855378E-2</v>
-      </c>
-      <c r="BN13" s="93" t="s">
-        <v>113</v>
+        <v>3.7107521210228311E-2</v>
+      </c>
+      <c r="BN13" s="99">
+        <v>46256</v>
       </c>
       <c r="BO13" s="93" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BP13" s="93" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="86" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
@@ -18272,7 +18317,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="86" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
@@ -18504,7 +18549,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="86" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
@@ -18658,10 +18703,10 @@
         <v>165</v>
       </c>
       <c r="AU16" s="19">
-        <v>260</v>
+        <v>300.39999999999998</v>
       </c>
       <c r="AV16" s="19">
-        <v>1200</v>
+        <v>1446.8</v>
       </c>
       <c r="AW16" s="20">
         <f t="shared" ca="1" si="9"/>
@@ -18669,22 +18714,22 @@
       </c>
       <c r="AX16" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>40.620185384615382</v>
+        <v>35.157284287616513</v>
       </c>
       <c r="AY16" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>8.8010401666666667</v>
+        <v>7.2997291954658561</v>
       </c>
       <c r="AZ16" s="21">
         <v>800</v>
       </c>
       <c r="BA16" s="22">
         <f t="shared" si="12"/>
-        <v>0.13750000000000001</v>
+        <v>0.11404478849875588</v>
       </c>
       <c r="BB16" s="22">
         <f t="shared" si="13"/>
-        <v>1.5</v>
+        <v>1.8085</v>
       </c>
       <c r="BC16" s="23">
         <f t="shared" si="14"/>
@@ -18726,17 +18771,17 @@
         <f t="shared" ca="1" si="20"/>
         <v>-2.7684909382092893E-2</v>
       </c>
-      <c r="BN16" s="93" t="s">
-        <v>124</v>
-      </c>
-      <c r="BO16" s="93" t="s">
-        <v>125</v>
+      <c r="BN16" s="99">
+        <v>46256</v>
+      </c>
+      <c r="BO16" s="99">
+        <v>46211</v>
       </c>
       <c r="BP16" s="93" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="86" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
@@ -18745,7 +18790,7 @@
         <v>HLMA</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D17" s="88" t="s">
         <v>77</v>
@@ -18871,7 +18916,7 @@
         <v>7.82</v>
       </c>
       <c r="AO17" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AP17" s="19">
         <v>100</v>
@@ -18930,7 +18975,7 @@
         <v>5.0200405794756708E-2</v>
       </c>
       <c r="BF17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="BG17" s="23">
         <f t="shared" si="16"/>
@@ -18962,13 +19007,13 @@
         <v>100</v>
       </c>
       <c r="BO17" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="BP17" s="93" t="s">
         <v>129</v>
       </c>
-      <c r="BP17" s="93" t="s">
-        <v>130</v>
-      </c>
     </row>
-    <row r="18" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="86" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
@@ -19162,7 +19207,7 @@
         <v>8.0078627468473051E-2</v>
       </c>
       <c r="BF18" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BG18" s="23">
         <f t="shared" si="16"/>
@@ -19197,10 +19242,10 @@
         <v>85</v>
       </c>
       <c r="BP18" s="93" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="86" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
@@ -19209,7 +19254,7 @@
         <v>LIFCO B</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D19" s="88" t="s">
         <v>77</v>
@@ -19335,7 +19380,7 @@
         <v>7.94</v>
       </c>
       <c r="AO19" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AP19" s="19">
         <v>3000</v>
@@ -19394,7 +19439,7 @@
         <v>7.001218289169242E-2</v>
       </c>
       <c r="BF19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BG19" s="23">
         <f t="shared" si="16"/>
@@ -19426,13 +19471,13 @@
         <v>113</v>
       </c>
       <c r="BO19" s="93" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP19" s="93" t="s">
         <v>136</v>
       </c>
-      <c r="BP19" s="93" t="s">
-        <v>137</v>
-      </c>
     </row>
-    <row r="20" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="86" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
@@ -19626,7 +19671,7 @@
         <v>3.9812328944305531E-2</v>
       </c>
       <c r="BF20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BG20" s="23">
         <f t="shared" si="16"/>
@@ -19661,10 +19706,10 @@
         <v>94</v>
       </c>
       <c r="BP20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="86" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
@@ -19858,7 +19903,7 @@
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BG21" s="23">
         <f t="shared" si="16"/>
@@ -19890,13 +19935,13 @@
         <v>79</v>
       </c>
       <c r="BO21" s="93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BP21" s="93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="86" t="e" vm="19">
         <v>#VALUE!</v>
       </c>
@@ -20090,7 +20135,7 @@
         <v>4.9985012185677746E-2</v>
       </c>
       <c r="BF22" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="BG22" s="23">
         <f t="shared" si="16"/>
@@ -20122,13 +20167,13 @@
         <v>113</v>
       </c>
       <c r="BO22" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BP22" s="93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="86" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
@@ -20263,7 +20308,7 @@
         <v>7.48</v>
       </c>
       <c r="AO23" s="18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AP23" s="19">
         <v>500</v>
@@ -20322,7 +20367,7 @@
         <v>0.12006550912241742</v>
       </c>
       <c r="BF23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="BG23" s="23">
         <f t="shared" si="16"/>
@@ -20354,13 +20399,13 @@
         <v>93</v>
       </c>
       <c r="BO23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BP23" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="86" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
@@ -20369,7 +20414,7 @@
         <v>VLTO</v>
       </c>
       <c r="C24" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D24" s="88" t="s">
         <v>77</v>
@@ -20554,7 +20599,7 @@
         <v>3.9950542132181077E-2</v>
       </c>
       <c r="BF24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="BG24" s="23">
         <f t="shared" si="16"/>
@@ -20583,16 +20628,16 @@
         <v>0.11371071980891823</v>
       </c>
       <c r="BN24" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="BO24" s="93" t="s">
         <v>148</v>
       </c>
-      <c r="BO24" s="93" t="s">
+      <c r="BP24" s="93" t="s">
         <v>149</v>
       </c>
-      <c r="BP24" s="93" t="s">
-        <v>150</v>
-      </c>
     </row>
-    <row r="25" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="86" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
@@ -20786,7 +20831,7 @@
         <v>6.003737798448272E-2</v>
       </c>
       <c r="BF25" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BG25" s="23">
         <f t="shared" si="16"/>
@@ -20818,13 +20863,13 @@
         <v>113</v>
       </c>
       <c r="BO25" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BP25" s="93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="86" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
@@ -20833,7 +20878,7 @@
         <v>JDG</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D26" s="88" t="s">
         <v>77</v>
@@ -20959,7 +21004,7 @@
         <v>6.75</v>
       </c>
       <c r="AO26" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AP26" s="19">
         <v>10</v>
@@ -21018,7 +21063,7 @@
         <v>6.1858758794934632E-2</v>
       </c>
       <c r="BF26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BG26" s="23">
         <f t="shared" si="16"/>
@@ -21050,13 +21095,13 @@
         <v>124</v>
       </c>
       <c r="BO26" s="93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BP26" s="93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
-    <row r="27" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="86" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
@@ -21065,7 +21110,7 @@
         <v>STMN</v>
       </c>
       <c r="C27" s="88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" s="88" t="s">
         <v>77</v>
@@ -21191,7 +21236,7 @@
         <v>6.71</v>
       </c>
       <c r="AO27" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AP27" s="19">
         <v>300</v>
@@ -21250,7 +21295,7 @@
         <v>5.9828421260577302E-2</v>
       </c>
       <c r="BF27" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="BG27" s="23">
         <f t="shared" si="16"/>
@@ -21285,10 +21330,10 @@
         <v>114</v>
       </c>
       <c r="BP27" s="93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
-    <row r="28" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="86" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
@@ -21482,7 +21527,7 @@
         <v>4.9999742905350697E-2</v>
       </c>
       <c r="BF28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BG28" s="23">
         <f t="shared" si="16"/>
@@ -21520,7 +21565,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="86" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
@@ -21714,7 +21759,7 @@
         <v>7.0010270953862141E-2</v>
       </c>
       <c r="BF29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="BG29" s="23">
         <f t="shared" si="16"/>
@@ -21746,13 +21791,13 @@
         <v>113</v>
       </c>
       <c r="BO29" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP29" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="BP29" s="93" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="30" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="86" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
@@ -21946,7 +21991,7 @@
         <v>0.13995090255865472</v>
       </c>
       <c r="BF30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BG30" s="23">
         <f t="shared" si="16"/>
@@ -21978,13 +22023,13 @@
         <v>113</v>
       </c>
       <c r="BO30" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BP30" s="93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="86" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
@@ -22178,7 +22223,7 @@
         <v>0.12002012191466971</v>
       </c>
       <c r="BF31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BG31" s="23">
         <f t="shared" si="16"/>
@@ -22216,7 +22261,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="86" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
@@ -22410,7 +22455,7 @@
         <v>4.9999742905350697E-2</v>
       </c>
       <c r="BF32" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="BG32" s="23">
         <f t="shared" si="16"/>
@@ -22439,16 +22484,16 @@
         <v>2.5077159575637831E-2</v>
       </c>
       <c r="BN32" s="93" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BO32" s="93" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BP32" s="93" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="86" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
@@ -22642,7 +22687,7 @@
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="BG33" s="23">
         <f t="shared" si="16"/>
@@ -22674,13 +22719,13 @@
         <v>113</v>
       </c>
       <c r="BO33" s="93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BP33" s="93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="86" t="e" vm="31">
         <v>#VALUE!</v>
       </c>
@@ -22689,7 +22734,7 @@
         <v>GRMN</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D34" s="88" t="s">
         <v>77</v>
@@ -22874,7 +22919,7 @@
         <v>4.004618516068903E-2</v>
       </c>
       <c r="BF34" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="BG34" s="23">
         <f t="shared" si="16"/>
@@ -22903,7 +22948,7 @@
         <v>3.6972461656187283E-2</v>
       </c>
       <c r="BN34" s="93" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BO34" s="93" t="s">
         <v>85</v>
@@ -22912,7 +22957,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="86" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
@@ -22921,13 +22966,13 @@
         <v>KRX</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D35" s="88" t="s">
         <v>77</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F35" s="11" t="str">
         <f t="array" aca="1" ref="F35" ca="1">_FV(A35,"Moneda")</f>
@@ -23105,7 +23150,7 @@
         <v>4.0002353139918068E-2</v>
       </c>
       <c r="BF35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BG35" s="23">
         <f t="shared" si="16"/>
@@ -23137,13 +23182,13 @@
         <v>124</v>
       </c>
       <c r="BO35" s="93" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BP35" s="93" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="36" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="86" t="e" vm="33">
         <v>#VALUE!</v>
       </c>
@@ -23278,7 +23323,7 @@
         <v>5.81</v>
       </c>
       <c r="AO36" s="18" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AP36" s="19">
         <v>900000</v>
@@ -23369,13 +23414,13 @@
         <v>79</v>
       </c>
       <c r="BO36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="BP36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="86" t="e" vm="34">
         <v>#VALUE!</v>
       </c>
@@ -23384,7 +23429,7 @@
         <v>CBAV</v>
       </c>
       <c r="C37" s="88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>77</v>
@@ -23569,7 +23614,7 @@
         <v>5.9223841048812176E-2</v>
       </c>
       <c r="BF37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="BG37" s="23">
         <f t="shared" si="42"/>
@@ -23601,13 +23646,13 @@
         <v>124</v>
       </c>
       <c r="BO37" s="94" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BP37" s="93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
-    <row r="38" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="86" t="e" vm="35">
         <v>#VALUE!</v>
       </c>
@@ -23616,7 +23661,7 @@
         <v>NVDA</v>
       </c>
       <c r="C38" s="88" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D38" s="88" t="s">
         <v>104</v>
@@ -23801,7 +23846,7 @@
         <v>8.0000772740678627E-2</v>
       </c>
       <c r="BF38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BG38" s="23">
         <f t="shared" si="42"/>
@@ -23833,13 +23878,13 @@
         <v>113</v>
       </c>
       <c r="BO38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="BP38" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="39" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="86" t="e" vm="36">
         <v>#VALUE!</v>
       </c>
@@ -23848,7 +23893,7 @@
         <v>COR</v>
       </c>
       <c r="C39" s="88" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>91</v>
@@ -24033,7 +24078,7 @@
         <v>0</v>
       </c>
       <c r="BF39" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BG39" s="23">
         <f t="shared" si="42"/>
@@ -24062,16 +24107,16 @@
         <v>0.10299210611655019</v>
       </c>
       <c r="BN39" s="93" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BO39" s="94" t="s">
         <v>85</v>
       </c>
       <c r="BP39" s="93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="40" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="86" t="e" vm="37">
         <v>#VALUE!</v>
       </c>
@@ -24080,7 +24125,7 @@
         <v>TSM</v>
       </c>
       <c r="C40" s="88" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>77</v>
@@ -24265,7 +24310,7 @@
         <v>7.9997972620447833E-2</v>
       </c>
       <c r="BF40" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BG40" s="23">
         <f t="shared" si="42"/>
@@ -24297,13 +24342,13 @@
         <v>113</v>
       </c>
       <c r="BO40" s="93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BP40" s="93" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
-    <row r="41" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="86" t="e" vm="38">
         <v>#VALUE!</v>
       </c>
@@ -24497,7 +24542,7 @@
         <v>2.9995722023716587E-2</v>
       </c>
       <c r="BF41" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BG41" s="23">
         <f t="shared" si="42"/>
@@ -24526,16 +24571,16 @@
         <v>0.13461354792856439</v>
       </c>
       <c r="BN41" s="93" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BO41" s="93" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BP41" s="93" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="42" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="86" t="e" vm="39">
         <v>#VALUE!</v>
       </c>
@@ -24758,16 +24803,16 @@
         <v>0.19507135627029171</v>
       </c>
       <c r="BN42" s="95" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="BO42" s="93" t="s">
         <v>115</v>
       </c>
       <c r="BP42" s="93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="43" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="86" t="e" vm="40">
         <v>#VALUE!</v>
       </c>
@@ -24776,7 +24821,7 @@
         <v>JFN</v>
       </c>
       <c r="C43" s="88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D43" s="88" t="s">
         <v>91</v>
@@ -24902,7 +24947,7 @@
         <v>5.52</v>
       </c>
       <c r="AO43" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AP43" s="19">
         <v>75</v>
@@ -24961,7 +25006,7 @@
         <v>-6.0146235650011426E-2</v>
       </c>
       <c r="BF43" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="BG43" s="23">
         <f t="shared" si="42"/>
@@ -24993,13 +25038,13 @@
         <v>113</v>
       </c>
       <c r="BO43" s="93" t="s">
+        <v>186</v>
+      </c>
+      <c r="BP43" s="93" t="s">
         <v>187</v>
       </c>
-      <c r="BP43" s="93" t="s">
-        <v>188</v>
-      </c>
     </row>
-    <row r="44" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="86" t="e" vm="41">
         <v>#VALUE!</v>
       </c>
@@ -25008,7 +25053,7 @@
         <v>CPR</v>
       </c>
       <c r="C44" s="88" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D44" s="88" t="s">
         <v>91</v>
@@ -25193,7 +25238,7 @@
         <v>3.0128962818398941E-2</v>
       </c>
       <c r="BF44" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BG44" s="23">
         <f t="shared" si="42"/>
@@ -25231,7 +25276,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="45" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="86" t="e" vm="42">
         <v>#VALUE!</v>
       </c>
@@ -25240,7 +25285,7 @@
         <v>SIKA</v>
       </c>
       <c r="C45" s="88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D45" s="88" t="s">
         <v>77</v>
@@ -25366,7 +25411,7 @@
         <v>5.51</v>
       </c>
       <c r="AO45" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AP45" s="19">
         <v>1200</v>
@@ -25425,7 +25470,7 @@
         <v>2.9967449959592329E-2</v>
       </c>
       <c r="BF45" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BG45" s="23">
         <f t="shared" si="42"/>
@@ -25454,16 +25499,16 @@
         <v>6.4001605398879668E-2</v>
       </c>
       <c r="BN45" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="BO45" s="93" t="s">
         <v>148</v>
       </c>
-      <c r="BO45" s="93" t="s">
-        <v>149</v>
-      </c>
       <c r="BP45" s="93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="46" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="86" t="e" vm="43">
         <v>#VALUE!</v>
       </c>
@@ -25475,7 +25520,7 @@
         <v>103</v>
       </c>
       <c r="D46" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E46" s="11" t="str">
         <f t="array" aca="1" ref="E46" ca="1">_FV(A46,"Abreviatura de intercambio",TRUE())</f>
@@ -25657,7 +25702,7 @@
         <v>1.9956640367314815E-2</v>
       </c>
       <c r="BF46" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BG46" s="23">
         <f t="shared" si="42"/>
@@ -25695,7 +25740,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="47" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="86" t="e" vm="44">
         <v>#VALUE!</v>
       </c>
@@ -25704,7 +25749,7 @@
         <v>TGYM</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D47" s="88" t="s">
         <v>77</v>
@@ -25889,7 +25934,7 @@
         <v>4.0751095710728658E-2</v>
       </c>
       <c r="BF47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="BG47" s="23">
         <f t="shared" si="42"/>
@@ -25924,10 +25969,10 @@
         <v>115</v>
       </c>
       <c r="BP47" s="93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
-    <row r="48" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="86" t="e" vm="45">
         <v>#VALUE!</v>
       </c>
@@ -25936,7 +25981,7 @@
         <v>VID</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D48" s="88" t="s">
         <v>91</v>
@@ -26121,7 +26166,7 @@
         <v>9.805797673485328E-3</v>
       </c>
       <c r="BF48" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BG48" s="23">
         <f t="shared" si="42"/>
@@ -26150,16 +26195,16 @@
         <v>0.14462746999133813</v>
       </c>
       <c r="BN48" s="93" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BO48" s="94" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BP48" s="93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="86" t="e" vm="46">
         <v>#VALUE!</v>
       </c>
@@ -26168,10 +26213,10 @@
         <v>TFPM</v>
       </c>
       <c r="C49" s="88" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" s="88" t="s">
         <v>196</v>
-      </c>
-      <c r="D49" s="88" t="s">
-        <v>197</v>
       </c>
       <c r="E49" s="11" t="str">
         <f t="array" aca="1" ref="E49" ca="1">_FV(A49,"Abreviatura de intercambio",TRUE())</f>
@@ -26353,7 +26398,7 @@
         <v>4.957228210048803E-2</v>
       </c>
       <c r="BF49" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="BG49" s="23">
         <f t="shared" si="42"/>
@@ -26385,13 +26430,13 @@
         <v>113</v>
       </c>
       <c r="BO49" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP49" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="BP49" s="93" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="50" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="86" t="e" vm="47">
         <v>#VALUE!</v>
       </c>
@@ -26619,13 +26664,13 @@
         <v>113</v>
       </c>
       <c r="BO50" s="93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BP50" s="93" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
-    <row r="51" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="86" t="e" vm="48">
         <v>#VALUE!</v>
       </c>
@@ -26637,7 +26682,7 @@
         <v>119</v>
       </c>
       <c r="D51" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E51" s="11" t="str">
         <f t="array" aca="1" ref="E51" ca="1">_FV(A51,"Abreviatura de intercambio",TRUE())</f>
@@ -26819,7 +26864,7 @@
         <v>0</v>
       </c>
       <c r="BF51" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BG51" s="23">
         <f t="shared" si="42"/>
@@ -26851,13 +26896,13 @@
         <v>113</v>
       </c>
       <c r="BO51" s="93" t="s">
+        <v>200</v>
+      </c>
+      <c r="BP51" s="93" t="s">
         <v>201</v>
       </c>
-      <c r="BP51" s="93" t="s">
-        <v>202</v>
-      </c>
     </row>
-    <row r="52" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="86" t="e" vm="49">
         <v>#VALUE!</v>
       </c>
@@ -26992,7 +27037,7 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="AO52" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AP52" s="19">
         <v>180</v>
@@ -27083,13 +27128,13 @@
         <v>113</v>
       </c>
       <c r="BO52" s="93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BP52" s="93" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="86" t="e" vm="50">
         <v>#VALUE!</v>
       </c>
@@ -27098,7 +27143,7 @@
         <v>FERG</v>
       </c>
       <c r="C53" s="88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D53" s="88" t="s">
         <v>91</v>
@@ -27283,7 +27328,7 @@
         <v>9.966033447608158E-3</v>
       </c>
       <c r="BF53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="BG53" s="23">
         <f t="shared" si="42"/>
@@ -27315,13 +27360,13 @@
         <v>113</v>
       </c>
       <c r="BO53" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP53" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="BP53" s="93" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="54" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="86" t="e" vm="51">
         <v>#VALUE!</v>
       </c>
@@ -27515,7 +27560,7 @@
         <v>7.8625221439269977E-2</v>
       </c>
       <c r="BF54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BG54" s="23">
         <f t="shared" si="42"/>
@@ -27550,10 +27595,10 @@
         <v>94</v>
       </c>
       <c r="BP54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
-    <row r="55" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="86" t="e" vm="52">
         <v>#VALUE!</v>
       </c>
@@ -27562,7 +27607,7 @@
         <v>TREX</v>
       </c>
       <c r="C55" s="88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D55" s="88" t="s">
         <v>77</v>
@@ -27747,7 +27792,7 @@
         <v>0</v>
       </c>
       <c r="BF55" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BG55" s="23">
         <f t="shared" si="42"/>
@@ -27779,13 +27824,13 @@
         <v>113</v>
       </c>
       <c r="BO55" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BP55" s="93" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
-    <row r="56" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="86" t="e" vm="53">
         <v>#VALUE!</v>
       </c>
@@ -27794,10 +27839,10 @@
         <v>SGO</v>
       </c>
       <c r="C56" s="88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D56" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E56" s="11" t="str">
         <f t="array" aca="1" ref="E56" ca="1">_FV(A56,"Abreviatura de intercambio",TRUE())</f>
@@ -27979,7 +28024,7 @@
         <v>9.966033447608158E-3</v>
       </c>
       <c r="BF56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="BG56" s="23">
         <f t="shared" si="42"/>
@@ -28011,13 +28056,13 @@
         <v>113</v>
       </c>
       <c r="BO56" s="93" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="BP56" s="93" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="86" t="e" vm="54">
         <v>#VALUE!</v>
       </c>
@@ -28026,10 +28071,10 @@
         <v>TFF</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E57" s="11" t="str">
         <f t="array" aca="1" ref="E57" ca="1">_FV(A57,"Abreviatura de intercambio",TRUE())</f>
@@ -28211,7 +28256,7 @@
         <v>0</v>
       </c>
       <c r="BF57" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BG57" s="23">
         <f t="shared" si="42"/>
@@ -28243,13 +28288,13 @@
         <v>113</v>
       </c>
       <c r="BO57" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="BP57" s="93" t="s">
         <v>209</v>
       </c>
-      <c r="BP57" s="93" t="s">
-        <v>210</v>
-      </c>
     </row>
-    <row r="58" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="86" t="e" vm="55">
         <v>#VALUE!</v>
       </c>
@@ -28475,13 +28520,13 @@
         <v>79</v>
       </c>
       <c r="BO58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BP58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="86" t="e" vm="56">
         <v>#VALUE!</v>
       </c>
@@ -28490,7 +28535,7 @@
         <v>BFIT</v>
       </c>
       <c r="C59" s="88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D59" s="88" t="s">
         <v>104</v>
@@ -28675,7 +28720,7 @@
         <v>1.9244876491456564E-2</v>
       </c>
       <c r="BF59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="BG59" s="23">
         <f t="shared" si="42"/>
@@ -28704,16 +28749,16 @@
         <v>8.7959215950159653E-3</v>
       </c>
       <c r="BN59" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="BO59" s="93" t="s">
         <v>148</v>
       </c>
-      <c r="BO59" s="93" t="s">
+      <c r="BP59" s="93" t="s">
         <v>149</v>
       </c>
-      <c r="BP59" s="93" t="s">
-        <v>150</v>
-      </c>
     </row>
-    <row r="60" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="86" t="e" vm="57">
         <v>#VALUE!</v>
       </c>
@@ -28722,13 +28767,13 @@
         <v>VRLA</v>
       </c>
       <c r="C60" s="88" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D60" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F60" s="11" t="str">
         <f t="array" aca="1" ref="F60" ca="1">_FV(A60,"Moneda")</f>
@@ -28935,16 +28980,16 @@
         <v>0.23475697847426313</v>
       </c>
       <c r="BN60" s="93" t="s">
+        <v>147</v>
+      </c>
+      <c r="BO60" s="93" t="s">
         <v>148</v>
-      </c>
-      <c r="BO60" s="93" t="s">
-        <v>149</v>
       </c>
       <c r="BP60" s="93" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="61" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="86" t="e" vm="58">
         <v>#VALUE!</v>
       </c>
@@ -28953,10 +28998,10 @@
         <v>KIST</v>
       </c>
       <c r="C61" s="88" t="s">
+        <v>195</v>
+      </c>
+      <c r="D61" s="88" t="s">
         <v>196</v>
-      </c>
-      <c r="D61" s="88" t="s">
-        <v>197</v>
       </c>
       <c r="E61" s="11" t="str">
         <f t="array" aca="1" ref="E61" ca="1">_FV(A61,"Abreviatura de intercambio",TRUE())</f>
@@ -29172,13 +29217,13 @@
         <v>113</v>
       </c>
       <c r="BO61" s="93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="BP61" s="93" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
-    <row r="62" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="86" t="e" vm="59">
         <v>#VALUE!</v>
       </c>
@@ -29190,7 +29235,7 @@
         <v>119</v>
       </c>
       <c r="D62" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E62" s="11" t="str">
         <f t="array" aca="1" ref="E62" ca="1">_FV(A62,"Abreviatura de intercambio",TRUE())</f>
@@ -29313,7 +29358,7 @@
         <v>2.33</v>
       </c>
       <c r="AO62" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AP62" s="19">
         <v>70</v>
@@ -29372,7 +29417,7 @@
         <v>0</v>
       </c>
       <c r="BF62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BG62" s="23">
         <f t="shared" si="42"/>
@@ -29404,13 +29449,13 @@
         <v>113</v>
       </c>
       <c r="BO62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BP62" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="63" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="86" t="e" vm="60">
         <v>#VALUE!</v>
       </c>
@@ -29419,10 +29464,10 @@
         <v>IPCO</v>
       </c>
       <c r="C63" s="88" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" s="88" t="s">
         <v>196</v>
-      </c>
-      <c r="D63" s="88" t="s">
-        <v>197</v>
       </c>
       <c r="E63" s="11" t="str">
         <f t="array" aca="1" ref="E63" ca="1">_FV(A63,"Abreviatura de intercambio",TRUE())</f>
@@ -29604,7 +29649,7 @@
         <v>-4.9967563918014046E-2</v>
       </c>
       <c r="BF63" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BG63" s="23">
         <f t="shared" si="42"/>
@@ -29636,13 +29681,13 @@
         <v>113</v>
       </c>
       <c r="BO63" s="93" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP63" s="93" t="s">
         <v>159</v>
       </c>
-      <c r="BP63" s="93" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="64" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="86" t="e" vm="61">
         <v>#VALUE!</v>
       </c>
@@ -29654,7 +29699,7 @@
         <v>119</v>
       </c>
       <c r="D64" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E64" s="11" t="str">
         <f t="array" aca="1" ref="E64" ca="1">_FV(A64,"Abreviatura de intercambio",TRUE())</f>
@@ -29836,7 +29881,7 @@
         <v>0</v>
       </c>
       <c r="BF64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="BG64" s="23">
         <f t="shared" si="42"/>
@@ -29868,13 +29913,13 @@
         <v>79</v>
       </c>
       <c r="BO64" s="93" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BP64" s="93" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="65" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A65" s="86" t="e" vm="62">
         <v>#VALUE!</v>
       </c>
@@ -30097,16 +30142,16 @@
         <v>0.50867711810090377</v>
       </c>
       <c r="BN65" s="93" t="s">
+        <v>218</v>
+      </c>
+      <c r="BO65" s="93" t="s">
         <v>219</v>
       </c>
-      <c r="BO65" s="93" t="s">
+      <c r="BP65" s="93" t="s">
         <v>220</v>
       </c>
-      <c r="BP65" s="93" t="s">
-        <v>221</v>
-      </c>
     </row>
-    <row r="66" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A66" s="86" t="e" vm="63">
         <v>#VALUE!</v>
       </c>
@@ -30115,7 +30160,7 @@
         <v>UBER</v>
       </c>
       <c r="C66" s="88" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D66" s="88" t="s">
         <v>77</v>
@@ -30332,13 +30377,13 @@
         <v>79</v>
       </c>
       <c r="BO66" s="93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="BP66" s="93" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
-    <row r="67" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A67" s="86" t="e" vm="64">
         <v>#VALUE!</v>
       </c>
@@ -30347,10 +30392,10 @@
         <v>SOM</v>
       </c>
       <c r="C67" s="88" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D67" s="88" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E67" s="11" t="str">
         <f ca="1">_FV(A67,"Abreviatura de intercambio",TRUE)</f>
@@ -30561,16 +30606,16 @@
         <v>0.37789220301948356</v>
       </c>
       <c r="BN67" s="96" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="BO67" s="96" t="s">
+        <v>588</v>
+      </c>
+      <c r="BP67" s="96" t="s">
         <v>589</v>
       </c>
-      <c r="BP67" s="96" t="s">
-        <v>590</v>
-      </c>
     </row>
-    <row r="68" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A68" s="86" t="e" vm="65">
         <v>#VALUE!</v>
       </c>
@@ -30579,7 +30624,7 @@
         <v>IP</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D68" s="88" t="s">
         <v>77</v>
@@ -30793,16 +30838,16 @@
         <v>0.24079940137721412</v>
       </c>
       <c r="BN68" s="96" t="s">
+        <v>597</v>
+      </c>
+      <c r="BO68" s="96" t="s">
+        <v>140</v>
+      </c>
+      <c r="BP68" s="96" t="s">
         <v>598</v>
       </c>
-      <c r="BO68" s="96" t="s">
-        <v>141</v>
-      </c>
-      <c r="BP68" s="96" t="s">
-        <v>599</v>
-      </c>
     </row>
-    <row r="69" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A69" s="86" t="e" vm="66">
         <v>#VALUE!</v>
       </c>
@@ -31025,16 +31070,16 @@
         <v>0.20879027721969323</v>
       </c>
       <c r="BN69" s="96" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="BO69" s="96" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BP69" s="96" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
-    <row r="70" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A70" s="86" t="e" vm="67">
         <v>#VALUE!</v>
       </c>
@@ -31043,7 +31088,7 @@
         <v>ROKO B</v>
       </c>
       <c r="C70" s="88" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D70" s="88" t="s">
         <v>77</v>
@@ -31169,7 +31214,7 @@
         <v>6.2</v>
       </c>
       <c r="AO70" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AP70" s="19">
         <v>500</v>
@@ -31257,16 +31302,16 @@
         <v>0.23558226327105958</v>
       </c>
       <c r="BN70" s="96" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="BO70" s="96" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="BP70" s="96" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="71" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:68" x14ac:dyDescent="0.35">
       <c r="A71" s="86" t="e" vm="68">
         <v>#VALUE!</v>
       </c>
@@ -31275,7 +31320,7 @@
         <v>USPH</v>
       </c>
       <c r="C71" s="88" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D71" s="88" t="s">
         <v>77</v>
@@ -31489,13 +31534,13 @@
         <v>0.19051809473296477</v>
       </c>
       <c r="BN71" s="96" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="BO71" s="96" t="s">
         <v>102</v>
       </c>
       <c r="BP71" s="96" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -31519,31 +31564,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" customWidth="1"/>
+    <col min="5" max="5" width="9.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="105" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+    </row>
+    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
     </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="28" t="s">
         <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
-        <v>226</v>
       </c>
       <c r="D4" t="e" vm="69">
         <v>#VALUE!</v>
@@ -31553,9 +31598,9 @@
         <v>185.7</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D5" t="e" vm="70">
         <v>#VALUE!</v>
@@ -31565,9 +31610,9 @@
         <v>1.2481</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D6" t="e" vm="71">
         <v>#VALUE!</v>
@@ -31577,7 +31622,7 @@
         <v>458.38</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D7" t="e" vm="72">
         <v>#VALUE!</v>
       </c>
@@ -31586,9 +31631,9 @@
         <v>0.7268</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="27" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D8" t="e" vm="73">
         <v>#VALUE!</v>
@@ -31598,210 +31643,210 @@
         <v>0.85589999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E9">
         <v>1.3641000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="28" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="28" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="28" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
+    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="28" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="28" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="28" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="27" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="28" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="28" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="28" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="28" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="28" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="28" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="28" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="28" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="27" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="28" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="28" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="28" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="28" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="28" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="28" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="28" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="28" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="27" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="28" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
-        <v>234</v>
+    <row r="40" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="28" t="s">
+        <v>651</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28" t="s">
-        <v>235</v>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>652</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
-        <v>236</v>
+    <row r="42" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="27" t="s">
+        <v>254</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
-        <v>237</v>
+    <row r="43" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="28" t="s">
+        <v>255</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28" t="s">
-        <v>238</v>
+    <row r="44" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="28" t="s">
+        <v>256</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28" t="s">
-        <v>239</v>
+    <row r="45" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="28" t="s">
+        <v>257</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
-        <v>240</v>
+    <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="28" t="s">
+        <v>258</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28" t="s">
-        <v>241</v>
+    <row r="47" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="28" t="s">
+        <v>259</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
-        <v>242</v>
+    <row r="49" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="27" t="s">
+        <v>260</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
-        <v>243</v>
+    <row r="50" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="28" t="s">
+        <v>261</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
-        <v>244</v>
+    <row r="51" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="28" t="s">
+        <v>262</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="28" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="28" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="28" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="28" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="28" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="28" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="27" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="28" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="28" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="28" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="28" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="28" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="27" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="28" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="28" t="s">
+    <row r="52" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="28" t="s">
         <v>263</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="28" t="s">
-        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -31816,34 +31861,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AU91"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="14" width="13.28515625" customWidth="1"/>
-    <col min="15" max="16" width="10.7109375" customWidth="1"/>
+    <col min="1" max="14" width="13.26953125" customWidth="1"/>
+    <col min="15" max="16" width="10.7265625" customWidth="1"/>
     <col min="17" max="17" width="16" customWidth="1"/>
-    <col min="18" max="29" width="13.28515625" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="2.85546875" customWidth="1"/>
-    <col min="31" max="31" width="4.7109375" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="13.28515625" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="10.42578125" customWidth="1"/>
-    <col min="34" max="43" width="0.140625" customWidth="1"/>
+    <col min="18" max="29" width="13.26953125" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="2.81640625" customWidth="1"/>
+    <col min="31" max="31" width="4.7265625" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="13.26953125" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="10.453125" customWidth="1"/>
+    <col min="34" max="43" width="0.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="111" t="s">
-        <v>265</v>
-      </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
+    <row r="1" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="112" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="101"/>
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="101"/>
+      <c r="I1" s="101"/>
+      <c r="J1" s="101"/>
+      <c r="K1" s="101"/>
+      <c r="L1" s="101"/>
       <c r="M1" s="32"/>
       <c r="N1" s="32"/>
       <c r="O1" s="32"/>
@@ -31851,277 +31896,277 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="32"/>
     </row>
-    <row r="2" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="128" t="s">
+    <row r="2" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="129" t="s">
+        <v>265</v>
+      </c>
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+    </row>
+    <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="135" t="s">
         <v>266</v>
       </c>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="156" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" s="124"/>
+      <c r="E3" s="157" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" s="124"/>
+      <c r="G3" s="123" t="s">
+        <v>269</v>
+      </c>
+      <c r="H3" s="124"/>
+      <c r="I3" s="125" t="s">
+        <v>270</v>
+      </c>
+      <c r="J3" s="124"/>
+      <c r="K3" s="161" t="s">
+        <v>271</v>
+      </c>
+      <c r="L3" s="162"/>
     </row>
-    <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="134" t="s">
-        <v>267</v>
-      </c>
-      <c r="B3" s="123"/>
-      <c r="C3" s="155" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3" s="123"/>
-      <c r="E3" s="156" t="s">
-        <v>269</v>
-      </c>
-      <c r="F3" s="123"/>
-      <c r="G3" s="122" t="s">
-        <v>270</v>
-      </c>
-      <c r="H3" s="123"/>
-      <c r="I3" s="124" t="s">
-        <v>271</v>
-      </c>
-      <c r="J3" s="123"/>
-      <c r="K3" s="160" t="s">
-        <v>272</v>
-      </c>
-      <c r="L3" s="161"/>
-    </row>
-    <row r="4" spans="1:47" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="141">
+    <row r="4" spans="1:47" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="142">
         <f ca="1">COUNTA('Watchlist Ratings'!B4:B71)</f>
         <v>68</v>
       </c>
-      <c r="B4" s="126"/>
-      <c r="C4" s="157">
+      <c r="B4" s="127"/>
+      <c r="C4" s="158">
         <f>ROUND(AVERAGE('Watchlist Ratings'!AN4:AN71),2)</f>
         <v>5.98</v>
       </c>
-      <c r="D4" s="126"/>
-      <c r="E4" s="127" t="str">
+      <c r="D4" s="127"/>
+      <c r="E4" s="128" t="str">
         <f>TEXT(AVERAGE('Watchlist Ratings'!BC4:BC71),"0.0%")</f>
-        <v>21.1%</v>
-      </c>
-      <c r="F4" s="126"/>
-      <c r="G4" s="127" t="str">
+        <v>20.9%</v>
+      </c>
+      <c r="F4" s="127"/>
+      <c r="G4" s="128" t="str">
         <f ca="1">TEXT(AVERAGE('Watchlist Ratings'!AW4:AW71),"0.0x")</f>
-        <v>38.0x</v>
-      </c>
-      <c r="H4" s="126"/>
-      <c r="I4" s="127">
+        <v>31.7x</v>
+      </c>
+      <c r="H4" s="127"/>
+      <c r="I4" s="128">
         <f ca="1">COUNTIF('Watchlist Ratings'!BM4:BM71,"&gt;0")</f>
         <v>58</v>
       </c>
-      <c r="J4" s="126"/>
-      <c r="K4" s="112">
+      <c r="J4" s="127"/>
+      <c r="K4" s="113">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&gt;7.5")</f>
         <v>16</v>
       </c>
-      <c r="L4" s="113"/>
+      <c r="L4" s="114"/>
     </row>
-    <row r="5" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="137" t="s">
+    <row r="5" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="138" t="s">
+        <v>272</v>
+      </c>
+      <c r="B5" s="127"/>
+      <c r="C5" s="126" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="126"/>
-      <c r="C5" s="125" t="s">
+      <c r="D5" s="127"/>
+      <c r="E5" s="126" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="126"/>
-      <c r="E5" s="125" t="s">
+      <c r="F5" s="127"/>
+      <c r="G5" s="126" t="s">
         <v>275</v>
       </c>
-      <c r="F5" s="126"/>
-      <c r="G5" s="125" t="s">
+      <c r="H5" s="127"/>
+      <c r="I5" s="126" t="s">
         <v>276</v>
       </c>
-      <c r="H5" s="126"/>
-      <c r="I5" s="125" t="s">
+      <c r="J5" s="127"/>
+      <c r="K5" s="163" t="s">
         <v>277</v>
       </c>
-      <c r="J5" s="126"/>
-      <c r="K5" s="162" t="s">
+      <c r="L5" s="114"/>
+    </row>
+    <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="119" t="s">
         <v>278</v>
       </c>
-      <c r="L5" s="113"/>
+      <c r="B6" s="120"/>
+      <c r="C6" s="136" t="s">
+        <v>279</v>
+      </c>
+      <c r="D6" s="120"/>
+      <c r="E6" s="136" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="120"/>
+      <c r="G6" s="122" t="s">
+        <v>281</v>
+      </c>
+      <c r="H6" s="120"/>
+      <c r="I6" s="136" t="s">
+        <v>282</v>
+      </c>
+      <c r="J6" s="120"/>
+      <c r="K6" s="159" t="s">
+        <v>283</v>
+      </c>
+      <c r="L6" s="160"/>
+      <c r="O6" t="s">
+        <v>284</v>
+      </c>
+      <c r="S6" t="s">
+        <v>285</v>
+      </c>
+      <c r="V6" t="s">
+        <v>286</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>287</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>289</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>290</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>289</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>290</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>289</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>291</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>292</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>289</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>293</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>289</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>294</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>295</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>289</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>293</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>295</v>
+      </c>
     </row>
-    <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="118" t="s">
-        <v>279</v>
-      </c>
-      <c r="B6" s="119"/>
-      <c r="C6" s="135" t="s">
-        <v>280</v>
-      </c>
-      <c r="D6" s="119"/>
-      <c r="E6" s="135" t="s">
-        <v>281</v>
-      </c>
-      <c r="F6" s="119"/>
-      <c r="G6" s="121" t="s">
-        <v>282</v>
-      </c>
-      <c r="H6" s="119"/>
-      <c r="I6" s="135" t="s">
-        <v>283</v>
-      </c>
-      <c r="J6" s="119"/>
-      <c r="K6" s="158" t="s">
-        <v>284</v>
-      </c>
-      <c r="L6" s="159"/>
-      <c r="O6" t="s">
-        <v>285</v>
-      </c>
-      <c r="S6" t="s">
-        <v>286</v>
-      </c>
-      <c r="V6" t="s">
-        <v>287</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>288</v>
-      </c>
-      <c r="AA6" t="s">
+    <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="AE6" t="s">
-        <v>290</v>
-      </c>
-      <c r="AF6" t="s">
+      <c r="C7" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="G7" s="34" t="s">
         <v>291</v>
       </c>
-      <c r="AH6" t="s">
-        <v>290</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>291</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>290</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>292</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>293</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>290</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>294</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>290</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>295</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>296</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>290</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>294</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>290</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="F7" s="34" t="s">
+      <c r="H7" s="34" t="s">
         <v>301</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>292</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>302</v>
       </c>
       <c r="I7" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="K7" s="36"/>
       <c r="O7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="Q7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="S7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="T7" t="s">
         <v>62</v>
       </c>
       <c r="V7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="W7" t="s">
+        <v>291</v>
+      </c>
+      <c r="X7" t="s">
         <v>292</v>
       </c>
-      <c r="X7" t="s">
+      <c r="Y7" t="s">
+        <v>289</v>
+      </c>
+      <c r="Z7" t="s">
         <v>293</v>
       </c>
-      <c r="Y7" t="s">
-        <v>290</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>294</v>
-      </c>
       <c r="AA7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AB7" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>302</v>
+      </c>
+      <c r="AE7" t="s">
         <v>304</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>303</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>305</v>
       </c>
       <c r="AF7">
         <v>83.3333333333333</v>
       </c>
       <c r="AH7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AI7">
         <v>83.3</v>
       </c>
       <c r="AJ7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AK7">
         <v>8</v>
@@ -32130,13 +32175,13 @@
         <v>3</v>
       </c>
       <c r="AM7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AN7">
         <v>52.2</v>
       </c>
       <c r="AO7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AP7">
         <v>4.5</v>
@@ -32145,7 +32190,7 @@
         <v>33.6</v>
       </c>
       <c r="AS7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AT7">
         <v>20.173600073636401</v>
@@ -32154,21 +32199,21 @@
         <v>33.701681153345</v>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="120" t="s">
-        <v>308</v>
-      </c>
-      <c r="B8" s="100"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100"/>
-      <c r="J8" s="100"/>
-      <c r="K8" s="100"/>
-      <c r="L8" s="100"/>
+    <row r="8" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="121" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
+      <c r="J8" s="101"/>
+      <c r="K8" s="101"/>
+      <c r="L8" s="101"/>
       <c r="O8" t="str">
         <f ca="1">'Watchlist Ratings'!B4</f>
         <v>VEEV</v>
@@ -32222,19 +32267,19 @@
         <v>0.2716311384364436</v>
       </c>
       <c r="AE8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AF8">
         <v>83.3333333333333</v>
       </c>
       <c r="AH8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AI8">
         <v>83.3</v>
       </c>
       <c r="AJ8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -32243,13 +32288,13 @@
         <v>3</v>
       </c>
       <c r="AM8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AN8">
         <v>51.1</v>
       </c>
       <c r="AO8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AP8">
         <v>3.7</v>
@@ -32258,7 +32303,7 @@
         <v>32.4</v>
       </c>
       <c r="AS8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AT8">
         <v>44.5724369425714</v>
@@ -32267,7 +32312,7 @@
         <v>10.123218193895701</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="39">
         <v>2</v>
       </c>
@@ -32301,11 +32346,11 @@
       </c>
       <c r="I9" s="43">
         <f>'Watchlist Ratings'!BC5</f>
-        <v>0.3214285714285714</v>
+        <v>0.21224118015235321</v>
       </c>
       <c r="J9" s="44">
         <f ca="1">'Watchlist Ratings'!AW5</f>
-        <v>50.746798462142856</v>
+        <v>52.976352013823579</v>
       </c>
       <c r="O9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32317,7 +32362,7 @@
       </c>
       <c r="Q9" s="23">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>6.6428327251210062E-2</v>
+        <v>6.6632314867387743E-2</v>
       </c>
       <c r="S9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32325,7 +32370,7 @@
       </c>
       <c r="T9" s="23">
         <f>'Watchlist Ratings'!BC5</f>
-        <v>0.3214285714285714</v>
+        <v>0.21224118015235321</v>
       </c>
       <c r="V9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32345,7 +32390,7 @@
       </c>
       <c r="Z9">
         <f ca="1">'Watchlist Ratings'!AW5</f>
-        <v>50.746798462142856</v>
+        <v>52.976352013823579</v>
       </c>
       <c r="AA9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32353,26 +32398,26 @@
       </c>
       <c r="AB9">
         <f ca="1">'Watchlist Ratings'!BL5</f>
-        <v>-0.10230824869655464</v>
+        <v>-0.10200359272389903</v>
       </c>
       <c r="AC9">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>6.6428327251210062E-2</v>
+        <v>6.6632314867387743E-2</v>
       </c>
       <c r="AE9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AF9">
         <v>59.375</v>
       </c>
       <c r="AH9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AI9">
         <v>59.4</v>
       </c>
       <c r="AJ9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AK9">
         <v>8</v>
@@ -32381,13 +32426,13 @@
         <v>1</v>
       </c>
       <c r="AM9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AN9">
         <v>45.6</v>
       </c>
       <c r="AO9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AP9">
         <v>1.1000000000000001</v>
@@ -32396,7 +32441,7 @@
         <v>28.4</v>
       </c>
       <c r="AS9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AT9">
         <v>28.571278521519002</v>
@@ -32405,7 +32450,7 @@
         <v>28.414482662692301</v>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="45">
         <v>3</v>
       </c>
@@ -32498,19 +32543,19 @@
         <v>0.27406080160124957</v>
       </c>
       <c r="AE10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AF10">
         <v>54</v>
       </c>
       <c r="AH10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AI10">
         <v>54</v>
       </c>
       <c r="AJ10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AK10">
         <v>8</v>
@@ -32519,13 +32564,13 @@
         <v>3</v>
       </c>
       <c r="AM10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AN10">
         <v>44.8</v>
       </c>
       <c r="AO10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AP10">
         <v>1.8</v>
@@ -32534,7 +32579,7 @@
         <v>25</v>
       </c>
       <c r="AS10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AT10">
         <v>24.369253736000001</v>
@@ -32543,7 +32588,7 @@
         <v>23.4863412384314</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39">
         <v>4</v>
       </c>
@@ -32636,19 +32681,19 @@
         <v>0.348330191162048</v>
       </c>
       <c r="AE11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AF11">
         <v>41.6666666666667</v>
       </c>
       <c r="AH11" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AI11">
         <v>41.7</v>
       </c>
       <c r="AJ11" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AK11">
         <v>8</v>
@@ -32657,13 +32702,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AN11">
         <v>43.6</v>
       </c>
       <c r="AO11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AP11">
         <v>0.6</v>
@@ -32672,7 +32717,7 @@
         <v>23.3</v>
       </c>
       <c r="AS11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AT11">
         <v>51.179748126470599</v>
@@ -32681,7 +32726,7 @@
         <v>0.80673234994763598</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="45">
         <v>5</v>
       </c>
@@ -32774,19 +32819,19 @@
         <v>1.9388396424438792E-2</v>
       </c>
       <c r="AE12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AF12">
         <v>38.3333333333333</v>
       </c>
       <c r="AH12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AI12">
         <v>38.299999999999997</v>
       </c>
       <c r="AJ12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AK12">
         <v>7</v>
@@ -32795,13 +32840,13 @@
         <v>3</v>
       </c>
       <c r="AM12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AN12">
         <v>40.299999999999997</v>
       </c>
       <c r="AO12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AP12">
         <v>-0.1</v>
@@ -32810,7 +32855,7 @@
         <v>20.8</v>
       </c>
       <c r="AS12" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AT12">
         <v>25.7039266520833</v>
@@ -32819,7 +32864,7 @@
         <v>20.9506730863196</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="39">
         <v>6</v>
       </c>
@@ -32860,10 +32905,10 @@
         <v>26.268452506666669</v>
       </c>
       <c r="L13" s="36" t="s">
+        <v>322</v>
+      </c>
+      <c r="M13" t="s">
         <v>323</v>
-      </c>
-      <c r="M13" t="s">
-        <v>324</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -32918,19 +32963,19 @@
         <v>0.20330830951269752</v>
       </c>
       <c r="AE13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AF13">
         <v>37.5</v>
       </c>
       <c r="AH13" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AI13">
         <v>37.5</v>
       </c>
       <c r="AJ13" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AK13">
         <v>7</v>
@@ -32939,13 +32984,13 @@
         <v>3</v>
       </c>
       <c r="AM13" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AN13">
         <v>38.9</v>
       </c>
       <c r="AO13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AP13">
         <v>4.7</v>
@@ -32954,7 +32999,7 @@
         <v>32.9</v>
       </c>
       <c r="AS13" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AT13">
         <v>29.589673076923098</v>
@@ -32963,7 +33008,7 @@
         <v>13.4877131347373</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="45">
         <v>7</v>
       </c>
@@ -33004,7 +33049,7 @@
         <v>26.484788461538457</v>
       </c>
       <c r="L14" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="M14">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&gt;=8")</f>
@@ -33063,19 +33108,19 @@
         <v>0.16565345141495191</v>
       </c>
       <c r="AE14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AF14">
         <v>37.142857142857103</v>
       </c>
       <c r="AH14" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AI14">
         <v>37.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AK14">
         <v>7</v>
@@ -33084,13 +33129,13 @@
         <v>2</v>
       </c>
       <c r="AM14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AN14">
         <v>38.5</v>
       </c>
       <c r="AO14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AP14">
         <v>-4.2</v>
@@ -33099,7 +33144,7 @@
         <v>13.7</v>
       </c>
       <c r="AS14" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AT14">
         <v>26.244954871232899</v>
@@ -33108,7 +33153,7 @@
         <v>32.575210542620198</v>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="39">
         <v>8</v>
       </c>
@@ -33149,7 +33194,7 @@
         <v>36.376567839041094</v>
       </c>
       <c r="L15" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="M15">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN71,"&gt;=7",'Watchlist Ratings'!AN4:AN71,"&lt;8")</f>
@@ -33208,19 +33253,19 @@
         <v>0.23151033398140308</v>
       </c>
       <c r="AE15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AF15">
         <v>36.1111111111111</v>
       </c>
       <c r="AH15" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AI15">
         <v>36.1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AK15">
         <v>7</v>
@@ -33229,13 +33274,13 @@
         <v>2</v>
       </c>
       <c r="AM15" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AN15">
         <v>37.700000000000003</v>
       </c>
       <c r="AO15" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AP15">
         <v>-8</v>
@@ -33244,7 +33289,7 @@
         <v>13.5</v>
       </c>
       <c r="AS15" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AT15">
         <v>27.905545425233299</v>
@@ -33253,7 +33298,7 @@
         <v>8.8031472249346301</v>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="45">
         <v>9</v>
       </c>
@@ -33294,7 +33339,7 @@
         <v>27.650297565424239</v>
       </c>
       <c r="L16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="M16">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN71,"&gt;=6",'Watchlist Ratings'!AN4:AN71,"&lt;7")</f>
@@ -33353,19 +33398,19 @@
         <v>9.0098171806134886E-2</v>
       </c>
       <c r="AE16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AF16">
         <v>32.142857142857103</v>
       </c>
       <c r="AH16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AI16">
         <v>32.1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AK16">
         <v>7</v>
@@ -33374,13 +33419,13 @@
         <v>3</v>
       </c>
       <c r="AM16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AN16">
         <v>29.6</v>
       </c>
       <c r="AO16" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AP16">
         <v>-7.9</v>
@@ -33389,7 +33434,7 @@
         <v>12.3</v>
       </c>
       <c r="AS16" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AT16">
         <v>52.2229498644231</v>
@@ -33398,7 +33443,7 @@
         <v>4.7817205741696798</v>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="39">
         <v>10</v>
       </c>
@@ -33432,14 +33477,14 @@
       </c>
       <c r="I17" s="43">
         <f>'Watchlist Ratings'!BC13</f>
-        <v>0.18333333333333335</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="J17" s="44">
         <f ca="1">'Watchlist Ratings'!AW13</f>
-        <v>53.33401919423077</v>
+        <v>-373.36270359021569</v>
       </c>
       <c r="L17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M17">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&lt;6")</f>
@@ -33455,7 +33500,7 @@
       </c>
       <c r="Q17" s="23">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>4.2346765118855378E-2</v>
+        <v>3.7107521210228311E-2</v>
       </c>
       <c r="S17" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
@@ -33463,7 +33508,7 @@
       </c>
       <c r="T17" s="23">
         <f>'Watchlist Ratings'!BC13</f>
-        <v>0.18333333333333335</v>
+        <v>0.18333333333333332</v>
       </c>
       <c r="V17" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
@@ -33483,7 +33528,7 @@
       </c>
       <c r="Z17">
         <f ca="1">'Watchlist Ratings'!AW13</f>
-        <v>53.33401919423077</v>
+        <v>-373.36270359021569</v>
       </c>
       <c r="AA17" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
@@ -33491,14 +33536,14 @@
       </c>
       <c r="AB17">
         <f ca="1">'Watchlist Ratings'!BL13</f>
-        <v>-9.8965077025216064E-2</v>
+        <v>-0.10622872895036783</v>
       </c>
       <c r="AC17">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>4.2346765118855378E-2</v>
+        <v>3.7107521210228311E-2</v>
       </c>
       <c r="AS17" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AT17">
         <v>37.736707694444398</v>
@@ -33507,7 +33552,7 @@
         <v>5.3744270407932504</v>
       </c>
     </row>
-    <row r="18" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="45">
         <v>11</v>
       </c>
@@ -33592,7 +33637,7 @@
         <v>3.658617807367448E-2</v>
       </c>
       <c r="AS18" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AT18">
         <v>24.612029698461502</v>
@@ -33601,7 +33646,7 @@
         <v>13.683807480135</v>
       </c>
     </row>
-    <row r="19" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="39">
         <v>12</v>
       </c>
@@ -33686,7 +33731,7 @@
         <v>0.12088409505027364</v>
       </c>
       <c r="AS19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AT19">
         <v>45.617441111111098</v>
@@ -33695,7 +33740,7 @@
         <v>3.6173393375436902</v>
       </c>
     </row>
-    <row r="20" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="45">
         <v>13</v>
       </c>
@@ -33780,7 +33825,7 @@
         <v>-2.7684909382092893E-2</v>
       </c>
       <c r="AS20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AT20">
         <v>43.630936634999998</v>
@@ -33789,7 +33834,7 @@
         <v>4.3482859737552504</v>
       </c>
     </row>
-    <row r="21" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="39">
         <v>14</v>
       </c>
@@ -33874,7 +33919,7 @@
         <v>0.11146322371597783</v>
       </c>
       <c r="AS21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AT21">
         <v>38.120501266027397</v>
@@ -33883,7 +33928,7 @@
         <v>12.615575978128</v>
       </c>
     </row>
-    <row r="22" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="51">
         <v>15</v>
       </c>
@@ -33968,7 +34013,7 @@
         <v>0.12939371313220138</v>
       </c>
     </row>
-    <row r="23" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O23" t="str">
         <f ca="1">'Watchlist Ratings'!B19</f>
         <v>LIFCO B</v>
@@ -33982,29 +34027,29 @@
         <v>0.114780755491519</v>
       </c>
     </row>
-    <row r="24" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="166" t="s">
-        <v>335</v>
-      </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="100"/>
-      <c r="D24" s="100"/>
-      <c r="E24" s="100"/>
-      <c r="F24" s="100"/>
-      <c r="G24" s="100"/>
-      <c r="H24" s="100"/>
-      <c r="I24" s="100"/>
-      <c r="J24" s="100"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="100"/>
-      <c r="N24" s="100"/>
-      <c r="O24" s="100"/>
-      <c r="P24" s="100"/>
-      <c r="Q24" s="100"/>
-      <c r="R24" s="100"/>
+    <row r="24" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="167" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" s="101"/>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="101"/>
+      <c r="N24" s="101"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="101"/>
+      <c r="Q24" s="101"/>
+      <c r="R24" s="101"/>
     </row>
-    <row r="25" spans="1:47" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:47" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O25" t="str">
         <f ca="1">'Watchlist Ratings'!B21</f>
         <v>MNST</v>
@@ -34018,7 +34063,7 @@
         <v>-6.8004414305380734E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O26" t="str">
         <f ca="1">'Watchlist Ratings'!B22</f>
         <v>ABNB</v>
@@ -34032,7 +34077,7 @@
         <v>0.17758798307282797</v>
       </c>
     </row>
-    <row r="27" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="O27" t="str">
         <f ca="1">'Watchlist Ratings'!B23</f>
         <v>DNP</v>
@@ -34046,28 +34091,28 @@
         <v>4.4209682767559988E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L40" s="174"/>
-      <c r="M40" s="100"/>
-      <c r="N40" s="100"/>
-      <c r="O40" s="100"/>
-      <c r="P40" s="100"/>
-      <c r="Q40" s="100"/>
-      <c r="R40" s="100"/>
+    <row r="28" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="33" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="L40" s="175"/>
+      <c r="M40" s="101"/>
+      <c r="N40" s="101"/>
+      <c r="O40" s="101"/>
+      <c r="P40" s="101"/>
+      <c r="Q40" s="101"/>
+      <c r="R40" s="101"/>
     </row>
-    <row r="41" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="L41" s="57"/>
       <c r="M41" s="57"/>
       <c r="N41" s="57"/>
@@ -34075,17 +34120,17 @@
       <c r="P41" s="57"/>
       <c r="Q41" s="57"/>
     </row>
-    <row r="42" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J42" s="176"/>
-      <c r="K42" s="100"/>
-      <c r="L42" s="100"/>
-      <c r="M42" s="100"/>
-      <c r="N42" s="100"/>
-      <c r="O42" s="100"/>
-      <c r="P42" s="100"/>
-      <c r="Q42" s="100"/>
+    <row r="42" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J42" s="177"/>
+      <c r="K42" s="101"/>
+      <c r="L42" s="101"/>
+      <c r="M42" s="101"/>
+      <c r="N42" s="101"/>
+      <c r="O42" s="101"/>
+      <c r="P42" s="101"/>
+      <c r="Q42" s="101"/>
     </row>
-    <row r="43" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="58"/>
       <c r="C43" s="58"/>
       <c r="D43" s="58"/>
@@ -34102,137 +34147,137 @@
       <c r="P43" s="59"/>
       <c r="Q43" s="59"/>
     </row>
-    <row r="44" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E44" s="60"/>
       <c r="F44" s="60"/>
       <c r="G44" s="60"/>
     </row>
-    <row r="45" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E45" s="60"/>
       <c r="F45" s="60"/>
       <c r="G45" s="60"/>
     </row>
-    <row r="46" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E46" s="60"/>
       <c r="F46" s="60"/>
       <c r="G46" s="60"/>
     </row>
-    <row r="47" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E47" s="60"/>
       <c r="F47" s="60"/>
       <c r="G47" s="60"/>
     </row>
-    <row r="48" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E48" s="60"/>
       <c r="F48" s="60"/>
       <c r="G48" s="60"/>
     </row>
-    <row r="49" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E49" s="60"/>
       <c r="F49" s="60"/>
       <c r="G49" s="60"/>
     </row>
-    <row r="50" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E50" s="60"/>
       <c r="F50" s="60"/>
       <c r="G50" s="60"/>
     </row>
-    <row r="51" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E51" s="60"/>
       <c r="F51" s="60"/>
       <c r="G51" s="60"/>
     </row>
-    <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E52" s="60"/>
       <c r="F52" s="60"/>
       <c r="G52" s="60"/>
     </row>
-    <row r="53" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E53" s="60"/>
       <c r="F53" s="60"/>
       <c r="G53" s="60"/>
     </row>
-    <row r="54" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="145" t="s">
+    <row r="54" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="55" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="146" t="s">
+        <v>335</v>
+      </c>
+      <c r="B62" s="101"/>
+      <c r="C62" s="101"/>
+      <c r="D62" s="101"/>
+      <c r="E62" s="101"/>
+      <c r="F62" s="101"/>
+      <c r="G62" s="101"/>
+      <c r="H62" s="101"/>
+      <c r="J62" s="153" t="s">
         <v>336</v>
       </c>
-      <c r="B62" s="100"/>
-      <c r="C62" s="100"/>
-      <c r="D62" s="100"/>
-      <c r="E62" s="100"/>
-      <c r="F62" s="100"/>
-      <c r="G62" s="100"/>
-      <c r="H62" s="100"/>
-      <c r="J62" s="152" t="s">
+      <c r="K62" s="101"/>
+      <c r="L62" s="101"/>
+      <c r="M62" s="101"/>
+      <c r="N62" s="101"/>
+      <c r="O62" s="101"/>
+      <c r="P62" s="101"/>
+      <c r="Q62" s="101"/>
+    </row>
+    <row r="63" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="61" t="s">
+        <v>289</v>
+      </c>
+      <c r="B63" s="61" t="s">
         <v>337</v>
       </c>
-      <c r="K62" s="100"/>
-      <c r="L62" s="100"/>
-      <c r="M62" s="100"/>
-      <c r="N62" s="100"/>
-      <c r="O62" s="100"/>
-      <c r="P62" s="100"/>
-      <c r="Q62" s="100"/>
+      <c r="C63" s="61" t="s">
+        <v>338</v>
+      </c>
+      <c r="D63" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="E63" s="61" t="s">
+        <v>303</v>
+      </c>
+      <c r="F63" s="61" t="s">
+        <v>302</v>
+      </c>
+      <c r="G63" s="61" t="s">
+        <v>340</v>
+      </c>
+      <c r="H63" s="61" t="s">
+        <v>341</v>
+      </c>
+      <c r="J63" s="62" t="s">
+        <v>289</v>
+      </c>
+      <c r="K63" s="62" t="s">
+        <v>342</v>
+      </c>
+      <c r="L63" s="62" t="s">
+        <v>343</v>
+      </c>
+      <c r="M63" s="62" t="s">
+        <v>344</v>
+      </c>
+      <c r="N63" s="62" t="s">
+        <v>345</v>
+      </c>
+      <c r="O63" s="62" t="s">
+        <v>291</v>
+      </c>
+      <c r="P63" s="62" t="s">
+        <v>346</v>
+      </c>
+      <c r="Q63" s="62" t="s">
+        <v>347</v>
+      </c>
     </row>
-    <row r="63" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="61" t="s">
-        <v>290</v>
-      </c>
-      <c r="B63" s="61" t="s">
-        <v>338</v>
-      </c>
-      <c r="C63" s="61" t="s">
-        <v>339</v>
-      </c>
-      <c r="D63" s="61" t="s">
-        <v>340</v>
-      </c>
-      <c r="E63" s="61" t="s">
-        <v>304</v>
-      </c>
-      <c r="F63" s="61" t="s">
-        <v>303</v>
-      </c>
-      <c r="G63" s="61" t="s">
-        <v>341</v>
-      </c>
-      <c r="H63" s="61" t="s">
-        <v>342</v>
-      </c>
-      <c r="J63" s="62" t="s">
-        <v>290</v>
-      </c>
-      <c r="K63" s="62" t="s">
-        <v>343</v>
-      </c>
-      <c r="L63" s="62" t="s">
-        <v>344</v>
-      </c>
-      <c r="M63" s="62" t="s">
-        <v>345</v>
-      </c>
-      <c r="N63" s="62" t="s">
-        <v>346</v>
-      </c>
-      <c r="O63" s="62" t="s">
-        <v>292</v>
-      </c>
-      <c r="P63" s="62" t="s">
-        <v>347</v>
-      </c>
-      <c r="Q63" s="62" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B4</f>
         <v>VEEV</v>
@@ -34298,7 +34343,7 @@
         <v>🟢 ALTO</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
         <v>MSFT</v>
@@ -34309,23 +34354,23 @@
       </c>
       <c r="C65" s="64">
         <f ca="1">'Watchlist Ratings'!BJ5</f>
-        <v>281.46890228259338</v>
+        <v>281.94684699910914</v>
       </c>
       <c r="D65" s="64">
         <f ca="1">'Watchlist Ratings'!BK5</f>
-        <v>624.48345542313723</v>
+        <v>624.96140013965305</v>
       </c>
       <c r="E65" s="65">
         <f ca="1">'Watchlist Ratings'!BL5</f>
-        <v>-0.10230824869655464</v>
+        <v>-0.10200359272389903</v>
       </c>
       <c r="F65" s="65">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>6.6428327251210062E-2</v>
+        <v>6.6632314867387743E-2</v>
       </c>
       <c r="G65" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.1687365759477647</v>
+        <v>0.16863590759128677</v>
       </c>
       <c r="H65" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -34364,7 +34409,7 @@
         <v>🟡 MEDIO</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B6</f>
         <v>ADYEN</v>
@@ -34430,7 +34475,7 @@
         <v>🟢 ALTO</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
         <v>BN</v>
@@ -34496,7 +34541,7 @@
         <v>🟡 MEDIO</v>
       </c>
     </row>
-    <row r="68" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B8</f>
         <v>COST</v>
@@ -34562,7 +34607,7 @@
         <v>🟢 ALTO</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
         <v>DSGX</v>
@@ -34628,7 +34673,7 @@
         <v>🟢 ALTO</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B10</f>
         <v>RAA</v>
@@ -34694,7 +34739,7 @@
         <v>🟢 ALTO</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B11</f>
         <v>ZS</v>
@@ -34760,32 +34805,32 @@
         <v>🟡 MEDIO</v>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="163" t="str">
+    <row r="72" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="164" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="B72" s="164"/>
-      <c r="C72" s="164"/>
-      <c r="D72" s="164"/>
-      <c r="E72" s="164"/>
-      <c r="F72" s="164"/>
-      <c r="G72" s="164"/>
-      <c r="H72" s="164"/>
-      <c r="I72" s="165"/>
-      <c r="J72" s="173" t="str">
+      <c r="B72" s="165"/>
+      <c r="C72" s="165"/>
+      <c r="D72" s="165"/>
+      <c r="E72" s="165"/>
+      <c r="F72" s="165"/>
+      <c r="G72" s="165"/>
+      <c r="H72" s="165"/>
+      <c r="I72" s="166"/>
+      <c r="J72" s="174" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="K72" s="164"/>
-      <c r="L72" s="164"/>
-      <c r="M72" s="164"/>
-      <c r="N72" s="164"/>
-      <c r="O72" s="164"/>
-      <c r="P72" s="164"/>
-      <c r="Q72" s="165"/>
+      <c r="K72" s="165"/>
+      <c r="L72" s="165"/>
+      <c r="M72" s="165"/>
+      <c r="N72" s="165"/>
+      <c r="O72" s="165"/>
+      <c r="P72" s="165"/>
+      <c r="Q72" s="166"/>
     </row>
-    <row r="73" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="68" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
         <v>AMZN</v>
@@ -34796,23 +34841,23 @@
       </c>
       <c r="C73" s="69">
         <f ca="1">'Watchlist Ratings'!BJ13</f>
-        <v>153.52724889234597</v>
+        <v>147.4379560758035</v>
       </c>
       <c r="D73" s="69">
         <f ca="1">'Watchlist Ratings'!BK13</f>
-        <v>305.15903956033156</v>
+        <v>299.06974674378915</v>
       </c>
       <c r="E73" s="70">
         <f ca="1">'Watchlist Ratings'!BL13</f>
-        <v>-9.8965077025216064E-2</v>
+        <v>-0.10622872895036783</v>
       </c>
       <c r="F73" s="70">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>4.2346765118855378E-2</v>
+        <v>3.7107521210228311E-2</v>
       </c>
       <c r="G73" s="70">
         <f ca="1">F73-E73</f>
-        <v>0.14131184214407144</v>
+        <v>0.14333625016059615</v>
       </c>
       <c r="H73" s="71" t="str">
         <f ca="1">IF(E73&gt;0,"🟢 BUY",IF(E73&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -34851,9 +34896,9 @@
         <v>🟡 MEDIO</v>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="75" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B74" s="76" t="str">
         <f ca="1">VLOOKUP(A74,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -34884,7 +34929,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J74" s="78" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -34915,9 +34960,9 @@
         <v>🔴 BAJO</v>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="79" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B75" s="80" t="str">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -34933,22 +34978,22 @@
       </c>
       <c r="E75" s="81">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$71,61,FALSE())</f>
-        <v>281.46890228259338</v>
+        <v>281.94684699910914</v>
       </c>
       <c r="F75" s="81">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>6.6428327251210062E-2</v>
+        <v>6.6632314867387743E-2</v>
       </c>
       <c r="G75" s="81">
         <f ca="1">F75-E75</f>
-        <v>-281.40247395534215</v>
+        <v>-281.88021468424176</v>
       </c>
       <c r="H75" s="79" t="str">
         <f ca="1">IF(E75&gt;0,"🟢 BUY",IF(E75&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
         <v>🟢 BUY</v>
       </c>
       <c r="J75" s="79" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="K75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -34979,30 +35024,30 @@
         <v>🔴 BAJO</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="138" t="s">
-        <v>349</v>
-      </c>
-      <c r="B76" s="100"/>
-      <c r="C76" s="100"/>
-      <c r="D76" s="100"/>
-      <c r="E76" s="100"/>
-      <c r="F76" s="100"/>
-      <c r="G76" s="100"/>
-      <c r="H76" s="100"/>
-      <c r="I76" s="100"/>
-      <c r="J76" s="100"/>
-      <c r="K76" s="100"/>
-      <c r="L76" s="100"/>
-      <c r="M76" s="100"/>
-      <c r="N76" s="100"/>
-      <c r="O76" s="100"/>
-      <c r="P76" s="100"/>
-      <c r="Q76" s="100"/>
+    <row r="76" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="139" t="s">
+        <v>348</v>
+      </c>
+      <c r="B76" s="101"/>
+      <c r="C76" s="101"/>
+      <c r="D76" s="101"/>
+      <c r="E76" s="101"/>
+      <c r="F76" s="101"/>
+      <c r="G76" s="101"/>
+      <c r="H76" s="101"/>
+      <c r="I76" s="101"/>
+      <c r="J76" s="101"/>
+      <c r="K76" s="101"/>
+      <c r="L76" s="101"/>
+      <c r="M76" s="101"/>
+      <c r="N76" s="101"/>
+      <c r="O76" s="101"/>
+      <c r="P76" s="101"/>
+      <c r="Q76" s="101"/>
     </row>
-    <row r="77" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B77" s="80" t="str">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35033,7 +35078,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J77" s="79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35064,139 +35109,139 @@
         <v>🔴 BAJO</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="130" t="s">
+    <row r="78" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="131" t="s">
+        <v>349</v>
+      </c>
+      <c r="B78" s="116"/>
+      <c r="C78" s="115" t="s">
         <v>350</v>
       </c>
-      <c r="B78" s="115"/>
-      <c r="C78" s="114" t="s">
+      <c r="D78" s="116"/>
+      <c r="E78" s="134" t="s">
         <v>351</v>
       </c>
-      <c r="D78" s="115"/>
-      <c r="E78" s="133" t="s">
+      <c r="F78" s="116"/>
+      <c r="G78" s="134" t="s">
         <v>352</v>
       </c>
-      <c r="F78" s="115"/>
-      <c r="G78" s="133" t="s">
+      <c r="H78" s="116"/>
+      <c r="I78" s="111" t="s">
         <v>353</v>
       </c>
-      <c r="H78" s="115"/>
-      <c r="I78" s="110" t="s">
+      <c r="J78" s="101"/>
+      <c r="K78" s="131" t="s">
         <v>354</v>
       </c>
-      <c r="J78" s="100"/>
-      <c r="K78" s="130" t="s">
+      <c r="L78" s="116"/>
+      <c r="M78" s="131" t="s">
         <v>355</v>
       </c>
-      <c r="L78" s="115"/>
-      <c r="M78" s="130" t="s">
+      <c r="N78" s="116"/>
+      <c r="O78" s="131" t="s">
         <v>356</v>
       </c>
-      <c r="N78" s="115"/>
-      <c r="O78" s="130" t="s">
-        <v>357</v>
-      </c>
-      <c r="P78" s="115"/>
+      <c r="P78" s="116"/>
       <c r="Q78" s="82" t="str">
         <f>IF(K78&gt;=8.5,"🟢 ALTO",IF(K78&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="139" t="str">
+    <row r="79" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AN:AN),'Watchlist Ratings'!AN:AN,0))</f>
         <v>CSU</v>
       </c>
-      <c r="B79" s="115"/>
-      <c r="C79" s="167" t="str">
+      <c r="B79" s="116"/>
+      <c r="C79" s="168" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM:BM),'Watchlist Ratings'!BM:BM,0))</f>
         <v>CSU</v>
       </c>
-      <c r="D79" s="115"/>
-      <c r="E79" s="140" t="str">
+      <c r="D79" s="116"/>
+      <c r="E79" s="141" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BC:BC),'Watchlist Ratings'!BC:BC,0))</f>
         <v>NVDA</v>
       </c>
-      <c r="F79" s="115"/>
-      <c r="G79" s="140" t="str">
+      <c r="F79" s="116"/>
+      <c r="G79" s="141" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!K:K),'Watchlist Ratings'!K:K,0))</f>
         <v>VEEV</v>
       </c>
-      <c r="H79" s="115"/>
-      <c r="I79" s="151" t="str">
+      <c r="H79" s="116"/>
+      <c r="I79" s="152" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!L:L),'Watchlist Ratings'!L:L,0))</f>
         <v>MSFT</v>
       </c>
-      <c r="J79" s="100"/>
-      <c r="K79" s="139" t="str">
+      <c r="J79" s="101"/>
+      <c r="K79" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AM:AM),'Watchlist Ratings'!AM:AM,0))</f>
         <v>CSU</v>
       </c>
-      <c r="L79" s="115"/>
-      <c r="M79" s="139" t="str">
+      <c r="L79" s="116"/>
+      <c r="M79" s="140" t="str">
         <f t="array" aca="1" ref="M79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MIN('Watchlist Ratings'!AW4:AW64),'Watchlist Ratings'!AW4:AW64,0)+3)</f>
-        <v>OTLY</v>
-      </c>
-      <c r="N79" s="115"/>
-      <c r="O79" s="139" t="str">
+        <v>AMZN</v>
+      </c>
+      <c r="N79" s="116"/>
+      <c r="O79" s="140" t="str">
         <f t="array" aca="1" ref="O79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),'Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="P79" s="115"/>
+      <c r="P79" s="116"/>
       <c r="Q79" s="79" t="str">
         <f ca="1">IF(K79&gt;=8.5,"🟢 ALTO",IF(K79&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="131">
+    <row r="80" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="132">
         <f>MAX('Watchlist Ratings'!AN:AN)</f>
         <v>8.57</v>
       </c>
-      <c r="B80" s="115"/>
-      <c r="C80" s="132">
+      <c r="B80" s="116"/>
+      <c r="C80" s="133">
         <f ca="1">MAX('Watchlist Ratings'!BM:BM)</f>
         <v>0.50867711810090377</v>
       </c>
-      <c r="D80" s="115"/>
-      <c r="E80" s="136">
+      <c r="D80" s="116"/>
+      <c r="E80" s="137">
         <f>MAX('Watchlist Ratings'!BC:BC)</f>
         <v>0.83333333333333326</v>
       </c>
-      <c r="F80" s="115"/>
-      <c r="G80" s="136" t="str">
+      <c r="F80" s="116"/>
+      <c r="G80" s="137" t="str">
         <f>MAX('Watchlist Ratings'!K:K)&amp;"/8"</f>
         <v>8/8</v>
       </c>
-      <c r="H80" s="115"/>
-      <c r="I80" s="169" t="str">
+      <c r="H80" s="116"/>
+      <c r="I80" s="170" t="str">
         <f>MAX('Watchlist Ratings'!L:L)&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="J80" s="100"/>
-      <c r="K80" s="170">
+      <c r="J80" s="101"/>
+      <c r="K80" s="171">
         <f>MAX('Watchlist Ratings'!AM:AM)</f>
         <v>8.86</v>
       </c>
-      <c r="L80" s="115"/>
-      <c r="M80" s="170" t="str">
+      <c r="L80" s="116"/>
+      <c r="M80" s="171" t="str">
         <f ca="1">MIN('Watchlist Ratings'!AW4:AW64)&amp;"x"</f>
-        <v>-18.59090636x</v>
-      </c>
-      <c r="N80" s="115"/>
-      <c r="O80" s="170" t="str">
+        <v>-373.362703590216x</v>
+      </c>
+      <c r="N80" s="116"/>
+      <c r="O80" s="171" t="str">
         <f t="array" aca="1" ref="O80" ca="1">TEXT(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),"0.0%")</f>
         <v>249.8%</v>
       </c>
-      <c r="P80" s="115"/>
+      <c r="P80" s="116"/>
       <c r="Q80" s="82" t="str">
         <f>IF(K80&gt;=8.5,"🟢 ALTO",IF(K80&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="79" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B81" s="80" t="str">
         <f ca="1">VLOOKUP(A81,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35227,7 +35272,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J81" s="79" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35258,30 +35303,30 @@
         <v>🔴 BAJO</v>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="171" t="s">
-        <v>358</v>
-      </c>
-      <c r="B82" s="100"/>
-      <c r="C82" s="100"/>
-      <c r="D82" s="100"/>
-      <c r="E82" s="100"/>
-      <c r="F82" s="100"/>
-      <c r="G82" s="100"/>
-      <c r="H82" s="100"/>
-      <c r="I82" s="100"/>
-      <c r="J82" s="100"/>
-      <c r="K82" s="100"/>
-      <c r="L82" s="100"/>
-      <c r="M82" s="100"/>
-      <c r="N82" s="100"/>
-      <c r="O82" s="100"/>
-      <c r="P82" s="100"/>
-      <c r="Q82" s="100"/>
+    <row r="82" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="172" t="s">
+        <v>357</v>
+      </c>
+      <c r="B82" s="101"/>
+      <c r="C82" s="101"/>
+      <c r="D82" s="101"/>
+      <c r="E82" s="101"/>
+      <c r="F82" s="101"/>
+      <c r="G82" s="101"/>
+      <c r="H82" s="101"/>
+      <c r="I82" s="101"/>
+      <c r="J82" s="101"/>
+      <c r="K82" s="101"/>
+      <c r="L82" s="101"/>
+      <c r="M82" s="101"/>
+      <c r="N82" s="101"/>
+      <c r="O82" s="101"/>
+      <c r="P82" s="101"/>
+      <c r="Q82" s="101"/>
     </row>
-    <row r="83" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="83" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B83" s="84" t="str">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35297,22 +35342,22 @@
       </c>
       <c r="E83" s="85">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$71,61,FALSE())</f>
-        <v>153.52724889234597</v>
+        <v>147.4379560758035</v>
       </c>
       <c r="F83" s="85">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>4.2346765118855378E-2</v>
+        <v>3.7107521210228311E-2</v>
       </c>
       <c r="G83" s="85">
         <f ca="1">F83-E83</f>
-        <v>-153.48490212722712</v>
+        <v>-147.40084855459327</v>
       </c>
       <c r="H83" s="83" t="str">
         <f ca="1">IF(E83&gt;0,"🟢 BUY",IF(E83&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
         <v>🟢 BUY</v>
       </c>
       <c r="J83" s="83" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35343,168 +35388,168 @@
         <v>🔴 BAJO</v>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="150" t="s">
+    <row r="84" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="151" t="s">
+        <v>348</v>
+      </c>
+      <c r="B85" s="101"/>
+      <c r="C85" s="101"/>
+      <c r="D85" s="101"/>
+      <c r="E85" s="101"/>
+      <c r="F85" s="101"/>
+      <c r="G85" s="101"/>
+      <c r="H85" s="101"/>
+      <c r="I85" s="101"/>
+      <c r="J85" s="101"/>
+      <c r="K85" s="101"/>
+      <c r="L85" s="101"/>
+      <c r="M85" s="101"/>
+      <c r="N85" s="101"/>
+      <c r="O85" s="101"/>
+      <c r="P85" s="101"/>
+      <c r="Q85" s="101"/>
+    </row>
+    <row r="86" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="173" t="s">
         <v>349</v>
       </c>
-      <c r="B85" s="100"/>
-      <c r="C85" s="100"/>
-      <c r="D85" s="100"/>
-      <c r="E85" s="100"/>
-      <c r="F85" s="100"/>
-      <c r="G85" s="100"/>
-      <c r="H85" s="100"/>
-      <c r="I85" s="100"/>
-      <c r="J85" s="100"/>
-      <c r="K85" s="100"/>
-      <c r="L85" s="100"/>
-      <c r="M85" s="100"/>
-      <c r="N85" s="100"/>
-      <c r="O85" s="100"/>
-      <c r="P85" s="100"/>
-      <c r="Q85" s="100"/>
+      <c r="B87" s="101"/>
+      <c r="C87" s="118" t="s">
+        <v>350</v>
+      </c>
+      <c r="D87" s="101"/>
+      <c r="E87" s="169" t="s">
+        <v>351</v>
+      </c>
+      <c r="F87" s="101"/>
+      <c r="G87" s="147" t="s">
+        <v>352</v>
+      </c>
+      <c r="H87" s="101"/>
+      <c r="I87" s="148" t="s">
+        <v>353</v>
+      </c>
+      <c r="J87" s="101"/>
+      <c r="K87" s="117" t="s">
+        <v>354</v>
+      </c>
+      <c r="L87" s="101"/>
+      <c r="M87" s="144" t="s">
+        <v>355</v>
+      </c>
+      <c r="N87" s="101"/>
+      <c r="O87" s="154" t="s">
+        <v>356</v>
+      </c>
+      <c r="P87" s="101"/>
     </row>
-    <row r="86" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="172" t="s">
-        <v>350</v>
-      </c>
-      <c r="B87" s="100"/>
-      <c r="C87" s="117" t="s">
-        <v>351</v>
-      </c>
-      <c r="D87" s="100"/>
-      <c r="E87" s="168" t="s">
-        <v>352</v>
-      </c>
-      <c r="F87" s="100"/>
-      <c r="G87" s="146" t="s">
-        <v>353</v>
-      </c>
-      <c r="H87" s="100"/>
-      <c r="I87" s="147" t="s">
-        <v>354</v>
-      </c>
-      <c r="J87" s="100"/>
-      <c r="K87" s="116" t="s">
-        <v>355</v>
-      </c>
-      <c r="L87" s="100"/>
-      <c r="M87" s="143" t="s">
-        <v>356</v>
-      </c>
-      <c r="N87" s="100"/>
-      <c r="O87" s="153" t="s">
-        <v>357</v>
-      </c>
-      <c r="P87" s="100"/>
-    </row>
-    <row r="88" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="144" t="str">
+    <row r="88" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AN$4:AN$71),'Watchlist Ratings'!AN$4:AN$71,0))</f>
         <v>CSU</v>
       </c>
-      <c r="B88" s="100"/>
-      <c r="C88" s="154" t="str">
+      <c r="B88" s="101"/>
+      <c r="C88" s="155" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!BM$4:BM$71),'Watchlist Ratings'!BM$4:BM$71,0))</f>
         <v>CSU</v>
       </c>
-      <c r="D88" s="100"/>
-      <c r="E88" s="144" t="str">
+      <c r="D88" s="101"/>
+      <c r="E88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!BC$4:BC$71),'Watchlist Ratings'!BC$4:BC$71,0))</f>
         <v>NVDA</v>
       </c>
-      <c r="F88" s="100"/>
-      <c r="G88" s="144" t="str">
+      <c r="F88" s="101"/>
+      <c r="G88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!K$4:K$71),'Watchlist Ratings'!K$4:K$71,0))</f>
         <v>VEEV</v>
       </c>
-      <c r="H88" s="100"/>
-      <c r="I88" s="144" t="str">
+      <c r="H88" s="101"/>
+      <c r="I88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!L$4:L$71),'Watchlist Ratings'!L$4:L$71,0))</f>
         <v>MSFT</v>
       </c>
-      <c r="J88" s="100"/>
-      <c r="K88" s="144" t="str">
+      <c r="J88" s="101"/>
+      <c r="K88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AM$4:AM$71),'Watchlist Ratings'!AM$4:AM$71,0))</f>
         <v>CSU</v>
       </c>
-      <c r="L88" s="100"/>
-      <c r="M88" s="144" t="str">
+      <c r="L88" s="101"/>
+      <c r="M88" s="145" t="str">
         <f t="array" aca="1" ref="M88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64)),IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64),0))</f>
         <v>CHKP</v>
       </c>
-      <c r="N88" s="100"/>
-      <c r="O88" s="144" t="str">
+      <c r="N88" s="101"/>
+      <c r="O88" s="145" t="str">
         <f t="array" aca="1" ref="O88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64),'Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64,0))</f>
         <v>OTLY</v>
       </c>
-      <c r="P88" s="100"/>
+      <c r="P88" s="101"/>
     </row>
-    <row r="89" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="142">
+    <row r="89" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="143">
         <f>MAX('Watchlist Ratings'!AN$4:AN$71)</f>
         <v>8.57</v>
       </c>
-      <c r="B89" s="100"/>
-      <c r="C89" s="149">
+      <c r="B89" s="101"/>
+      <c r="C89" s="150">
         <f ca="1">MAX('Watchlist Ratings'!BM$4:BM$64)</f>
         <v>0.46257448883098218</v>
       </c>
-      <c r="D89" s="100"/>
-      <c r="E89" s="149">
+      <c r="D89" s="101"/>
+      <c r="E89" s="150">
         <f>MAX('Watchlist Ratings'!BC$4:BC$71)</f>
         <v>0.83333333333333326</v>
       </c>
-      <c r="F89" s="100"/>
-      <c r="G89" s="148" t="str">
+      <c r="F89" s="101"/>
+      <c r="G89" s="149" t="str">
         <f>MAX('Watchlist Ratings'!K$4:K$71)&amp;"/8"</f>
         <v>8/8</v>
       </c>
-      <c r="H89" s="100"/>
-      <c r="I89" s="148" t="str">
+      <c r="H89" s="101"/>
+      <c r="I89" s="149" t="str">
         <f>MAX('Watchlist Ratings'!L$4:L$71)&amp;"/3"</f>
         <v>3/3</v>
       </c>
-      <c r="J89" s="100"/>
-      <c r="K89" s="175">
+      <c r="J89" s="101"/>
+      <c r="K89" s="176">
         <f>MAX('Watchlist Ratings'!AM$4:AM$71)</f>
         <v>8.86</v>
       </c>
-      <c r="L89" s="100"/>
-      <c r="M89" s="148" t="str">
+      <c r="L89" s="101"/>
+      <c r="M89" s="149" t="str">
         <f t="array" aca="1" ref="M89" ca="1">MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64))&amp;"x"</f>
         <v>7.94399332153846x</v>
       </c>
-      <c r="N89" s="100"/>
-      <c r="O89" s="148">
+      <c r="N89" s="101"/>
+      <c r="O89" s="149">
         <f t="array" aca="1" ref="O89" ca="1">MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64)</f>
         <v>2.4981957482457289</v>
       </c>
-      <c r="P89" s="100"/>
+      <c r="P89" s="101"/>
     </row>
-    <row r="90" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="B91" s="100"/>
-      <c r="C91" s="100"/>
-      <c r="D91" s="100"/>
-      <c r="E91" s="100"/>
-      <c r="F91" s="100"/>
-      <c r="G91" s="100"/>
-      <c r="H91" s="100"/>
-      <c r="I91" s="100"/>
-      <c r="J91" s="100"/>
-      <c r="K91" s="100"/>
-      <c r="L91" s="100"/>
-      <c r="M91" s="100"/>
-      <c r="N91" s="100"/>
-      <c r="O91" s="100"/>
-      <c r="P91" s="100"/>
-      <c r="Q91" s="100"/>
+    <row r="90" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="110" t="s">
+        <v>357</v>
+      </c>
+      <c r="B91" s="101"/>
+      <c r="C91" s="101"/>
+      <c r="D91" s="101"/>
+      <c r="E91" s="101"/>
+      <c r="F91" s="101"/>
+      <c r="G91" s="101"/>
+      <c r="H91" s="101"/>
+      <c r="I91" s="101"/>
+      <c r="J91" s="101"/>
+      <c r="K91" s="101"/>
+      <c r="L91" s="101"/>
+      <c r="M91" s="101"/>
+      <c r="N91" s="101"/>
+      <c r="O91" s="101"/>
+      <c r="P91" s="101"/>
+      <c r="Q91" s="101"/>
     </row>
   </sheetData>
   <mergeCells count="86">
@@ -35636,2478 +35681,2563 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E145"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E150"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
-    <col min="4" max="4" width="52.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="192.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
+    <col min="4" max="4" width="52.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="192.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1" t="s">
         <v>359</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>360</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>361</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>362</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>363</v>
       </c>
       <c r="B2" t="s">
         <v>124</v>
       </c>
       <c r="C2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D2" t="s">
         <v>364</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>365</v>
       </c>
-      <c r="E2" t="s">
-        <v>366</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B3" t="s">
         <v>124</v>
       </c>
       <c r="C3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D3" t="s">
         <v>367</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>368</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>369</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>370</v>
       </c>
       <c r="B4" t="s">
         <v>124</v>
       </c>
       <c r="C4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" t="s">
         <v>371</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>372</v>
       </c>
-      <c r="E4" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>373</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>374</v>
       </c>
       <c r="B5" t="s">
         <v>124</v>
       </c>
       <c r="C5" t="s">
+        <v>374</v>
+      </c>
+      <c r="D5" t="s">
         <v>375</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>376</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" t="s">
         <v>377</v>
       </c>
+      <c r="D6" t="s">
+        <v>378</v>
+      </c>
+      <c r="E6" t="s">
+        <v>379</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C6" t="s">
-        <v>378</v>
-      </c>
-      <c r="D6" t="s">
-        <v>379</v>
-      </c>
-      <c r="E6" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B7" t="s">
         <v>93</v>
       </c>
       <c r="C7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D7" t="s">
         <v>381</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>382</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>383</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>384</v>
       </c>
       <c r="B8" t="s">
         <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D8" t="s">
+        <v>384</v>
+      </c>
+      <c r="E8" t="s">
         <v>385</v>
       </c>
-      <c r="E8" t="s">
-        <v>386</v>
-      </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B9" t="s">
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E9" t="s">
         <v>387</v>
       </c>
-      <c r="E9" t="s">
-        <v>388</v>
-      </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B10" t="s">
         <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D10" t="s">
+        <v>388</v>
+      </c>
+      <c r="E10" t="s">
         <v>389</v>
       </c>
-      <c r="E10" t="s">
-        <v>390</v>
-      </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B11" t="s">
         <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E11" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
         <v>391</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>392</v>
       </c>
       <c r="B12" t="s">
         <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D12" t="s">
+        <v>392</v>
+      </c>
+      <c r="E12" t="s">
         <v>393</v>
       </c>
-      <c r="E12" t="s">
-        <v>394</v>
-      </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B13" t="s">
         <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D13" t="s">
+        <v>394</v>
+      </c>
+      <c r="E13" t="s">
         <v>395</v>
       </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>397</v>
       </c>
       <c r="B14" t="s">
         <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D14" t="s">
+        <v>397</v>
+      </c>
+      <c r="E14" t="s">
         <v>398</v>
       </c>
-      <c r="E14" t="s">
-        <v>399</v>
-      </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B15" t="s">
         <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D15" t="s">
+        <v>399</v>
+      </c>
+      <c r="E15" t="s">
         <v>400</v>
       </c>
-      <c r="E15" t="s">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
         <v>401</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>402</v>
       </c>
       <c r="B16" t="s">
         <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D16" t="s">
+        <v>402</v>
+      </c>
+      <c r="E16" t="s">
         <v>403</v>
       </c>
-      <c r="E16" t="s">
-        <v>404</v>
-      </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B17" t="s">
         <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D17" t="s">
+        <v>404</v>
+      </c>
+      <c r="E17" t="s">
         <v>405</v>
       </c>
-      <c r="E17" t="s">
-        <v>406</v>
-      </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B18" t="s">
         <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D18" t="s">
+        <v>406</v>
+      </c>
+      <c r="E18" t="s">
         <v>407</v>
       </c>
-      <c r="E18" t="s">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
         <v>408</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>409</v>
       </c>
       <c r="B19" t="s">
         <v>93</v>
       </c>
       <c r="C19" t="s">
+        <v>409</v>
+      </c>
+      <c r="D19" t="s">
         <v>410</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>411</v>
       </c>
-      <c r="E19" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
         <v>412</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>413</v>
       </c>
       <c r="B20" t="s">
         <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D20" t="s">
+        <v>413</v>
+      </c>
+      <c r="E20" t="s">
         <v>414</v>
       </c>
-      <c r="E20" t="s">
-        <v>415</v>
-      </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B21" t="s">
         <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D21" t="s">
+        <v>415</v>
+      </c>
+      <c r="E21" t="s">
         <v>416</v>
       </c>
-      <c r="E21" t="s">
-        <v>417</v>
-      </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B22" t="s">
         <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D22" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E22" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B23" t="s">
         <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E23" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B24" t="s">
         <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D24" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E24" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B25" t="s">
         <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D25" t="s">
+        <v>420</v>
+      </c>
+      <c r="E25" t="s">
         <v>421</v>
       </c>
-      <c r="E25" t="s">
-        <v>422</v>
-      </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B26" t="s">
         <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D26" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E26" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B27" t="s">
         <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D27" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E27" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B28" t="s">
         <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D28" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E28" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
         <v>424</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>425</v>
       </c>
       <c r="B29" t="s">
         <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D29" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E29" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B30" t="s">
         <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D30" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E30" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B31" t="s">
         <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D31" t="s">
+        <v>415</v>
+      </c>
+      <c r="E31" t="s">
         <v>416</v>
       </c>
-      <c r="E31" t="s">
-        <v>417</v>
-      </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B32" t="s">
         <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D32" t="s">
+        <v>415</v>
+      </c>
+      <c r="E32" t="s">
         <v>416</v>
       </c>
-      <c r="E32" t="s">
-        <v>417</v>
-      </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B33" t="s">
         <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D33" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E33" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>430</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>431</v>
       </c>
       <c r="B34" t="s">
         <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D34" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E34" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B35" t="s">
         <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D35" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E35" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>433</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>434</v>
       </c>
       <c r="B36" t="s">
         <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D36" t="s">
+        <v>415</v>
+      </c>
+      <c r="E36" t="s">
         <v>416</v>
       </c>
-      <c r="E36" t="s">
-        <v>417</v>
-      </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B37" t="s">
         <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D37" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E37" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B38" t="s">
         <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D38" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E38" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B39" t="s">
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D39" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E39" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>438</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>439</v>
       </c>
       <c r="B40" t="s">
         <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D40" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E40" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B41" t="s">
         <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D41" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E41" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B42" t="s">
         <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D42" t="s">
+        <v>415</v>
+      </c>
+      <c r="E42" t="s">
         <v>416</v>
       </c>
-      <c r="E42" t="s">
-        <v>417</v>
-      </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B43" t="s">
         <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D43" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E43" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B44" t="s">
         <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D44" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E44" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B45" t="s">
         <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D45" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E45" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B46" t="s">
         <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D46" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E46" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s">
         <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D47" t="s">
+        <v>415</v>
+      </c>
+      <c r="E47" t="s">
         <v>416</v>
       </c>
-      <c r="E47" t="s">
-        <v>417</v>
-      </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B48" t="s">
         <v>113</v>
       </c>
       <c r="C48" t="s">
+        <v>445</v>
+      </c>
+      <c r="D48" t="s">
         <v>446</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>447</v>
       </c>
-      <c r="E48" t="s">
-        <v>448</v>
-      </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s">
         <v>113</v>
       </c>
       <c r="C49" t="s">
+        <v>445</v>
+      </c>
+      <c r="D49" t="s">
         <v>446</v>
       </c>
-      <c r="D49" t="s">
-        <v>447</v>
-      </c>
       <c r="E49" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>449</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>450</v>
       </c>
       <c r="B50" t="s">
         <v>113</v>
       </c>
       <c r="C50" t="s">
+        <v>445</v>
+      </c>
+      <c r="D50" t="s">
         <v>446</v>
       </c>
-      <c r="D50" t="s">
-        <v>447</v>
-      </c>
       <c r="E50" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s">
         <v>113</v>
       </c>
       <c r="C51" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D51" t="s">
+        <v>451</v>
+      </c>
+      <c r="E51" t="s">
         <v>452</v>
       </c>
-      <c r="E51" t="s">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>453</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>454</v>
       </c>
       <c r="B52" t="s">
         <v>113</v>
       </c>
       <c r="C52" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D52" t="s">
+        <v>454</v>
+      </c>
+      <c r="E52" t="s">
         <v>455</v>
       </c>
-      <c r="E52" t="s">
-        <v>456</v>
-      </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B53" t="s">
         <v>113</v>
       </c>
       <c r="C53" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D53" t="s">
+        <v>456</v>
+      </c>
+      <c r="E53" t="s">
         <v>457</v>
       </c>
-      <c r="E53" t="s">
-        <v>458</v>
-      </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s">
         <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D54" t="s">
+        <v>458</v>
+      </c>
+      <c r="E54" t="s">
         <v>459</v>
       </c>
-      <c r="E54" t="s">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>460</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>461</v>
       </c>
       <c r="B55" t="s">
         <v>113</v>
       </c>
       <c r="C55" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D55" t="s">
+        <v>461</v>
+      </c>
+      <c r="E55" t="s">
         <v>462</v>
       </c>
-      <c r="E55" t="s">
-        <v>463</v>
-      </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B56" t="s">
         <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D56" t="s">
+        <v>463</v>
+      </c>
+      <c r="E56" t="s">
         <v>464</v>
       </c>
-      <c r="E56" t="s">
-        <v>465</v>
-      </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s">
         <v>113</v>
       </c>
       <c r="C57" t="s">
+        <v>465</v>
+      </c>
+      <c r="D57" t="s">
         <v>466</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>467</v>
       </c>
-      <c r="E57" t="s">
-        <v>468</v>
-      </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B58" t="s">
         <v>113</v>
       </c>
       <c r="C58" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D58" t="s">
+        <v>468</v>
+      </c>
+      <c r="E58" t="s">
         <v>469</v>
       </c>
-      <c r="E58" t="s">
-        <v>470</v>
-      </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s">
         <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D59" t="s">
+        <v>470</v>
+      </c>
+      <c r="E59" t="s">
         <v>471</v>
       </c>
-      <c r="E59" t="s">
-        <v>472</v>
-      </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B60" t="s">
         <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D60" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E60" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B61" t="s">
         <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D61" t="s">
+        <v>473</v>
+      </c>
+      <c r="E61" t="s">
         <v>474</v>
       </c>
-      <c r="E61" t="s">
-        <v>475</v>
-      </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s">
         <v>113</v>
       </c>
       <c r="C62" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D62" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E62" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B63" t="s">
         <v>113</v>
       </c>
       <c r="C63" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D63" t="s">
+        <v>476</v>
+      </c>
+      <c r="E63" t="s">
         <v>477</v>
       </c>
-      <c r="E63" t="s">
-        <v>478</v>
-      </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B64" t="s">
         <v>113</v>
       </c>
       <c r="C64" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D64" t="s">
+        <v>478</v>
+      </c>
+      <c r="E64" t="s">
         <v>479</v>
       </c>
-      <c r="E64" t="s">
-        <v>480</v>
-      </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B65" t="s">
         <v>113</v>
       </c>
       <c r="C65" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D65" t="s">
+        <v>480</v>
+      </c>
+      <c r="E65" t="s">
         <v>481</v>
       </c>
-      <c r="E65" t="s">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>482</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>483</v>
       </c>
       <c r="B66" t="s">
         <v>113</v>
       </c>
       <c r="C66" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D66" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E66" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B67" t="s">
         <v>113</v>
       </c>
       <c r="C67" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D67" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E67" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s">
         <v>113</v>
       </c>
       <c r="C68" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D68" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E68" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B69" t="s">
         <v>113</v>
       </c>
       <c r="C69" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D69" t="s">
+        <v>486</v>
+      </c>
+      <c r="E69" t="s">
         <v>487</v>
       </c>
-      <c r="E69" t="s">
-        <v>488</v>
-      </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B70" t="s">
         <v>113</v>
       </c>
       <c r="C70" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D70" t="s">
+        <v>488</v>
+      </c>
+      <c r="E70" t="s">
         <v>489</v>
       </c>
-      <c r="E70" t="s">
-        <v>490</v>
-      </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B71" t="s">
         <v>113</v>
       </c>
       <c r="C71" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D71" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E71" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B72" t="s">
         <v>113</v>
       </c>
       <c r="C72" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D72" t="s">
+        <v>491</v>
+      </c>
+      <c r="E72" t="s">
         <v>492</v>
       </c>
-      <c r="E72" t="s">
-        <v>493</v>
-      </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B73" t="s">
         <v>113</v>
       </c>
       <c r="C73" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D73" t="s">
+        <v>493</v>
+      </c>
+      <c r="E73" t="s">
         <v>494</v>
       </c>
-      <c r="E73" t="s">
-        <v>495</v>
-      </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B74" t="s">
         <v>113</v>
       </c>
       <c r="C74" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D74" t="s">
+        <v>495</v>
+      </c>
+      <c r="E74" t="s">
         <v>496</v>
       </c>
-      <c r="E74" t="s">
-        <v>497</v>
-      </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B75" t="s">
         <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D75" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E75" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B76" t="s">
         <v>113</v>
       </c>
       <c r="C76" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D76" t="s">
+        <v>498</v>
+      </c>
+      <c r="E76" t="s">
         <v>499</v>
       </c>
-      <c r="E76" t="s">
-        <v>500</v>
-      </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B77" t="s">
         <v>113</v>
       </c>
       <c r="C77" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D77" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E77" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B78" t="s">
         <v>113</v>
       </c>
       <c r="C78" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D78" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E78" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s">
         <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D79" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E79" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B80" t="s">
         <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D80" t="s">
+        <v>503</v>
+      </c>
+      <c r="E80" t="s">
         <v>504</v>
       </c>
-      <c r="E80" t="s">
-        <v>505</v>
-      </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B81" t="s">
         <v>113</v>
       </c>
       <c r="C81" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D81" t="s">
+        <v>505</v>
+      </c>
+      <c r="E81" t="s">
         <v>506</v>
       </c>
-      <c r="E81" t="s">
-        <v>507</v>
-      </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B82" t="s">
         <v>113</v>
       </c>
       <c r="C82" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D82" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="E82" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>508</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>509</v>
       </c>
       <c r="B83" t="s">
         <v>113</v>
       </c>
       <c r="C83" t="s">
+        <v>509</v>
+      </c>
+      <c r="D83" t="s">
         <v>510</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>511</v>
       </c>
-      <c r="E83" t="s">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>434</v>
+      </c>
+      <c r="B84" t="s">
+        <v>147</v>
+      </c>
+      <c r="C84" t="s">
         <v>512</v>
       </c>
+      <c r="D84" t="s">
+        <v>513</v>
+      </c>
+      <c r="E84" t="s">
+        <v>514</v>
+      </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>515</v>
+      </c>
+      <c r="B85" t="s">
+        <v>147</v>
+      </c>
+      <c r="C85" t="s">
+        <v>512</v>
+      </c>
+      <c r="D85" t="s">
+        <v>516</v>
+      </c>
+      <c r="E85" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>424</v>
+      </c>
+      <c r="B86" t="s">
+        <v>147</v>
+      </c>
+      <c r="C86" t="s">
+        <v>512</v>
+      </c>
+      <c r="D86" t="s">
+        <v>518</v>
+      </c>
+      <c r="E86" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>431</v>
+      </c>
+      <c r="B87" t="s">
+        <v>147</v>
+      </c>
+      <c r="C87" t="s">
+        <v>512</v>
+      </c>
+      <c r="D87" t="s">
+        <v>520</v>
+      </c>
+      <c r="E87" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>433</v>
+      </c>
+      <c r="B88" t="s">
+        <v>147</v>
+      </c>
+      <c r="C88" t="s">
+        <v>512</v>
+      </c>
+      <c r="D88" t="s">
+        <v>522</v>
+      </c>
+      <c r="E88" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>524</v>
+      </c>
+      <c r="B89" t="s">
+        <v>147</v>
+      </c>
+      <c r="C89" t="s">
+        <v>512</v>
+      </c>
+      <c r="D89" t="s">
+        <v>525</v>
+      </c>
+      <c r="E89" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>439</v>
+      </c>
+      <c r="B90" t="s">
+        <v>147</v>
+      </c>
+      <c r="C90" t="s">
+        <v>512</v>
+      </c>
+      <c r="D90" t="s">
+        <v>527</v>
+      </c>
+      <c r="E90" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>529</v>
+      </c>
+      <c r="B91" t="s">
+        <v>147</v>
+      </c>
+      <c r="C91" t="s">
+        <v>512</v>
+      </c>
+      <c r="D91" t="s">
+        <v>530</v>
+      </c>
+      <c r="E91" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>444</v>
+      </c>
+      <c r="B92" t="s">
+        <v>147</v>
+      </c>
+      <c r="C92" t="s">
+        <v>512</v>
+      </c>
+      <c r="D92" t="s">
+        <v>532</v>
+      </c>
+      <c r="E92" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>318</v>
+      </c>
+      <c r="B93" t="s">
+        <v>147</v>
+      </c>
+      <c r="C93" t="s">
+        <v>534</v>
+      </c>
+      <c r="D93" t="s">
+        <v>535</v>
+      </c>
+      <c r="E93" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>401</v>
+      </c>
+      <c r="B94" t="s">
+        <v>147</v>
+      </c>
+      <c r="C94" t="s">
+        <v>534</v>
+      </c>
+      <c r="D94" t="s">
+        <v>537</v>
+      </c>
+      <c r="E94" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>435</v>
       </c>
-      <c r="B84" t="s">
-        <v>148</v>
-      </c>
-      <c r="C84" t="s">
-        <v>513</v>
-      </c>
-      <c r="D84" t="s">
-        <v>514</v>
-      </c>
-      <c r="E84" t="s">
-        <v>515</v>
+      <c r="B95" t="s">
+        <v>147</v>
+      </c>
+      <c r="C95" t="s">
+        <v>534</v>
+      </c>
+      <c r="D95" t="s">
+        <v>539</v>
+      </c>
+      <c r="E95" t="s">
+        <v>540</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>516</v>
-      </c>
-      <c r="B85" t="s">
-        <v>148</v>
-      </c>
-      <c r="C85" t="s">
-        <v>513</v>
-      </c>
-      <c r="D85" t="s">
-        <v>517</v>
-      </c>
-      <c r="E85" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>425</v>
-      </c>
-      <c r="B86" t="s">
-        <v>148</v>
-      </c>
-      <c r="C86" t="s">
-        <v>513</v>
-      </c>
-      <c r="D86" t="s">
-        <v>519</v>
-      </c>
-      <c r="E86" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>432</v>
-      </c>
-      <c r="B87" t="s">
-        <v>148</v>
-      </c>
-      <c r="C87" t="s">
-        <v>513</v>
-      </c>
-      <c r="D87" t="s">
-        <v>521</v>
-      </c>
-      <c r="E87" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>434</v>
-      </c>
-      <c r="B88" t="s">
-        <v>148</v>
-      </c>
-      <c r="C88" t="s">
-        <v>513</v>
-      </c>
-      <c r="D88" t="s">
-        <v>523</v>
-      </c>
-      <c r="E88" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>525</v>
-      </c>
-      <c r="B89" t="s">
-        <v>148</v>
-      </c>
-      <c r="C89" t="s">
-        <v>513</v>
-      </c>
-      <c r="D89" t="s">
-        <v>526</v>
-      </c>
-      <c r="E89" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>440</v>
-      </c>
-      <c r="B90" t="s">
-        <v>148</v>
-      </c>
-      <c r="C90" t="s">
-        <v>513</v>
-      </c>
-      <c r="D90" t="s">
-        <v>528</v>
-      </c>
-      <c r="E90" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>530</v>
-      </c>
-      <c r="B91" t="s">
-        <v>148</v>
-      </c>
-      <c r="C91" t="s">
-        <v>513</v>
-      </c>
-      <c r="D91" t="s">
-        <v>531</v>
-      </c>
-      <c r="E91" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>445</v>
-      </c>
-      <c r="B92" t="s">
-        <v>148</v>
-      </c>
-      <c r="C92" t="s">
-        <v>513</v>
-      </c>
-      <c r="D92" t="s">
-        <v>533</v>
-      </c>
-      <c r="E92" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>319</v>
-      </c>
-      <c r="B93" t="s">
-        <v>148</v>
-      </c>
-      <c r="C93" t="s">
-        <v>535</v>
-      </c>
-      <c r="D93" t="s">
-        <v>536</v>
-      </c>
-      <c r="E93" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>402</v>
-      </c>
-      <c r="B94" t="s">
-        <v>148</v>
-      </c>
-      <c r="C94" t="s">
-        <v>535</v>
-      </c>
-      <c r="D94" t="s">
-        <v>538</v>
-      </c>
-      <c r="E94" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>436</v>
-      </c>
-      <c r="B95" t="s">
-        <v>148</v>
-      </c>
-      <c r="C95" t="s">
-        <v>535</v>
-      </c>
-      <c r="D95" t="s">
-        <v>540</v>
-      </c>
-      <c r="E95" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B96" t="s">
         <v>84</v>
       </c>
       <c r="C96" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D96" t="s">
+        <v>541</v>
+      </c>
+      <c r="E96" t="s">
         <v>542</v>
       </c>
-      <c r="E96" t="s">
-        <v>543</v>
-      </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B97" t="s">
         <v>84</v>
       </c>
       <c r="C97" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D97" t="s">
+        <v>543</v>
+      </c>
+      <c r="E97" t="s">
         <v>544</v>
       </c>
-      <c r="E97" t="s">
-        <v>545</v>
-      </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B98" t="s">
         <v>84</v>
       </c>
       <c r="C98" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D98" t="s">
+        <v>545</v>
+      </c>
+      <c r="E98" t="s">
         <v>546</v>
       </c>
-      <c r="E98" t="s">
-        <v>547</v>
-      </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B99" t="s">
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D99" t="s">
+        <v>547</v>
+      </c>
+      <c r="E99" t="s">
         <v>548</v>
       </c>
-      <c r="E99" t="s">
-        <v>549</v>
-      </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B100" t="s">
         <v>84</v>
       </c>
       <c r="C100" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D100" t="s">
+        <v>549</v>
+      </c>
+      <c r="E100" t="s">
         <v>550</v>
       </c>
-      <c r="E100" t="s">
-        <v>551</v>
-      </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B101" t="s">
         <v>84</v>
       </c>
       <c r="C101" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D101" t="s">
+        <v>551</v>
+      </c>
+      <c r="E101" t="s">
         <v>552</v>
       </c>
-      <c r="E101" t="s">
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>553</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>554</v>
       </c>
       <c r="B102" t="s">
         <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D102" t="s">
+        <v>554</v>
+      </c>
+      <c r="E102" t="s">
         <v>555</v>
       </c>
-      <c r="E102" t="s">
-        <v>556</v>
-      </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B103" t="s">
         <v>79</v>
       </c>
       <c r="C103" t="s">
+        <v>556</v>
+      </c>
+      <c r="D103" t="s">
         <v>557</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
         <v>558</v>
       </c>
-      <c r="E103" t="s">
-        <v>559</v>
-      </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B104" t="s">
         <v>79</v>
       </c>
       <c r="C104" t="s">
+        <v>559</v>
+      </c>
+      <c r="D104" t="s">
         <v>560</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
         <v>561</v>
       </c>
-      <c r="E104" t="s">
-        <v>562</v>
-      </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B105" t="s">
         <v>79</v>
       </c>
       <c r="C105" t="s">
+        <v>562</v>
+      </c>
+      <c r="D105" t="s">
         <v>563</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
         <v>564</v>
       </c>
-      <c r="E105" t="s">
-        <v>565</v>
-      </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B106" t="s">
         <v>79</v>
       </c>
       <c r="C106" t="s">
+        <v>565</v>
+      </c>
+      <c r="D106" t="s">
         <v>566</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
         <v>567</v>
       </c>
-      <c r="E106" t="s">
-        <v>568</v>
-      </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B107" t="s">
         <v>79</v>
       </c>
       <c r="C107" t="s">
+        <v>568</v>
+      </c>
+      <c r="D107" t="s">
         <v>569</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
         <v>570</v>
       </c>
-      <c r="E107" t="s">
-        <v>571</v>
-      </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B108" t="s">
         <v>79</v>
       </c>
       <c r="C108" t="s">
+        <v>571</v>
+      </c>
+      <c r="D108" t="s">
         <v>572</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>573</v>
       </c>
-      <c r="E108" t="s">
-        <v>574</v>
-      </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B109" t="s">
         <v>79</v>
       </c>
       <c r="C109" t="s">
+        <v>574</v>
+      </c>
+      <c r="D109" t="s">
         <v>575</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>576</v>
       </c>
-      <c r="E109" t="s">
-        <v>577</v>
-      </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B110" t="s">
         <v>79</v>
       </c>
       <c r="C110" t="s">
+        <v>577</v>
+      </c>
+      <c r="D110" t="s">
         <v>578</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
         <v>579</v>
       </c>
-      <c r="E110" t="s">
-        <v>580</v>
-      </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B111" s="97">
         <v>46254</v>
       </c>
       <c r="C111" t="s">
+        <v>582</v>
+      </c>
+      <c r="D111" t="s">
         <v>583</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
         <v>584</v>
       </c>
-      <c r="E111" t="s">
-        <v>585</v>
-      </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B112" s="97">
         <v>46254</v>
       </c>
       <c r="C112" t="s">
+        <v>585</v>
+      </c>
+      <c r="D112" t="s">
         <v>586</v>
       </c>
-      <c r="D112" t="s">
+      <c r="E112" t="s">
         <v>587</v>
       </c>
-      <c r="E112" t="s">
-        <v>588</v>
-      </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B113" s="97">
         <v>46254</v>
       </c>
       <c r="C113" t="s">
+        <v>590</v>
+      </c>
+      <c r="D113" t="s">
         <v>591</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
         <v>592</v>
       </c>
-      <c r="E113" t="s">
-        <v>593</v>
-      </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B114" s="97">
         <v>46254</v>
       </c>
       <c r="C114" t="s">
+        <v>593</v>
+      </c>
+      <c r="D114" t="s">
         <v>594</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>595</v>
       </c>
-      <c r="E114" t="s">
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>596</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>597</v>
       </c>
       <c r="B115" s="97">
         <v>46255</v>
       </c>
       <c r="C115" t="s">
+        <v>604</v>
+      </c>
+      <c r="D115" t="s">
         <v>605</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
         <v>606</v>
       </c>
-      <c r="E115" t="s">
-        <v>607</v>
-      </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B116" s="97">
         <v>46255</v>
       </c>
       <c r="C116" t="s">
+        <v>607</v>
+      </c>
+      <c r="D116" t="s">
         <v>608</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
         <v>609</v>
       </c>
-      <c r="E116" t="s">
-        <v>610</v>
-      </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B117" s="97">
         <v>46255</v>
       </c>
       <c r="C117" t="s">
+        <v>610</v>
+      </c>
+      <c r="D117" t="s">
         <v>611</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
         <v>612</v>
       </c>
-      <c r="E117" t="s">
-        <v>613</v>
-      </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B118" s="97">
         <v>46255</v>
       </c>
       <c r="C118" t="s">
+        <v>613</v>
+      </c>
+      <c r="D118" t="s">
         <v>614</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
         <v>615</v>
       </c>
-      <c r="E118" t="s">
-        <v>616</v>
-      </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B119" s="97">
         <v>46255</v>
       </c>
       <c r="C119" t="s">
+        <v>616</v>
+      </c>
+      <c r="D119" t="s">
         <v>617</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
         <v>618</v>
       </c>
-      <c r="E119" t="s">
-        <v>619</v>
-      </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B120" s="97">
         <v>46255</v>
       </c>
       <c r="C120" t="s">
+        <v>619</v>
+      </c>
+      <c r="D120" t="s">
+        <v>617</v>
+      </c>
+      <c r="E120" t="s">
         <v>620</v>
       </c>
-      <c r="D120" t="s">
-        <v>618</v>
-      </c>
-      <c r="E120" t="s">
-        <v>621</v>
-      </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B121" s="97">
         <v>46255</v>
       </c>
       <c r="C121" t="s">
+        <v>621</v>
+      </c>
+      <c r="D121" t="s">
+        <v>617</v>
+      </c>
+      <c r="E121" t="s">
         <v>622</v>
       </c>
-      <c r="D121" t="s">
-        <v>618</v>
-      </c>
-      <c r="E121" t="s">
-        <v>623</v>
-      </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B122" s="97">
         <v>46255</v>
       </c>
       <c r="C122" t="s">
+        <v>623</v>
+      </c>
+      <c r="D122" t="s">
+        <v>617</v>
+      </c>
+      <c r="E122" t="s">
         <v>624</v>
       </c>
-      <c r="D122" t="s">
-        <v>618</v>
-      </c>
-      <c r="E122" t="s">
-        <v>625</v>
-      </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B123" s="97">
         <v>46255</v>
       </c>
       <c r="C123" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D123" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E123" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B124" s="97">
         <v>46255</v>
       </c>
       <c r="C124" t="s">
+        <v>626</v>
+      </c>
+      <c r="D124" t="s">
+        <v>617</v>
+      </c>
+      <c r="E124" t="s">
         <v>627</v>
       </c>
-      <c r="D124" t="s">
-        <v>618</v>
-      </c>
-      <c r="E124" t="s">
-        <v>628</v>
-      </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B125" s="97">
         <v>46255</v>
       </c>
       <c r="C125" t="s">
+        <v>628</v>
+      </c>
+      <c r="D125" t="s">
+        <v>617</v>
+      </c>
+      <c r="E125" t="s">
         <v>629</v>
       </c>
-      <c r="D125" t="s">
-        <v>618</v>
-      </c>
-      <c r="E125" t="s">
-        <v>630</v>
-      </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B126" s="97">
         <v>46255</v>
       </c>
       <c r="C126" t="s">
+        <v>630</v>
+      </c>
+      <c r="D126" t="s">
+        <v>617</v>
+      </c>
+      <c r="E126" t="s">
         <v>631</v>
       </c>
-      <c r="D126" t="s">
-        <v>618</v>
-      </c>
-      <c r="E126" t="s">
-        <v>632</v>
-      </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B127" s="97">
         <v>46255</v>
       </c>
       <c r="C127" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D127" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E127" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B128" s="97">
         <v>46255</v>
       </c>
       <c r="C128" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D128" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E128" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B129" s="97">
         <v>46255</v>
       </c>
       <c r="C129" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D129" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E129" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B130" s="97">
         <v>46255</v>
       </c>
       <c r="C130" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D130" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E130" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B131" s="97">
         <v>46255</v>
       </c>
       <c r="C131" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D131" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E131" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B132" s="97">
         <v>46255</v>
       </c>
       <c r="C132" t="s">
+        <v>637</v>
+      </c>
+      <c r="D132" t="s">
+        <v>617</v>
+      </c>
+      <c r="E132" t="s">
         <v>638</v>
       </c>
-      <c r="D132" t="s">
-        <v>618</v>
-      </c>
-      <c r="E132" t="s">
-        <v>639</v>
-      </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B133" s="97">
         <v>46255</v>
       </c>
       <c r="C133" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D133" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E133" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B134" s="97">
         <v>46255</v>
       </c>
       <c r="C134" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D134" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E134" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B135" s="97">
         <v>46255</v>
       </c>
       <c r="C135" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D135" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E135" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B136" s="97">
         <v>46255</v>
       </c>
       <c r="C136" t="s">
+        <v>642</v>
+      </c>
+      <c r="D136" t="s">
+        <v>617</v>
+      </c>
+      <c r="E136" t="s">
         <v>643</v>
       </c>
-      <c r="D136" t="s">
-        <v>618</v>
-      </c>
-      <c r="E136" t="s">
-        <v>644</v>
-      </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B137" s="97">
         <v>46255</v>
       </c>
       <c r="C137" t="s">
+        <v>644</v>
+      </c>
+      <c r="D137" t="s">
+        <v>617</v>
+      </c>
+      <c r="E137" t="s">
         <v>645</v>
       </c>
-      <c r="D137" t="s">
-        <v>618</v>
-      </c>
-      <c r="E137" t="s">
-        <v>646</v>
-      </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B138" s="97">
         <v>46255</v>
       </c>
       <c r="C138" t="s">
+        <v>646</v>
+      </c>
+      <c r="D138" t="s">
+        <v>617</v>
+      </c>
+      <c r="E138" t="s">
         <v>647</v>
       </c>
-      <c r="D138" t="s">
-        <v>618</v>
-      </c>
-      <c r="E138" t="s">
-        <v>648</v>
-      </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B139" s="97">
         <v>46255</v>
       </c>
       <c r="C139" t="s">
+        <v>653</v>
+      </c>
+      <c r="D139" t="s">
         <v>654</v>
       </c>
-      <c r="D139" t="s">
+      <c r="E139" t="s">
         <v>655</v>
       </c>
-      <c r="E139" t="s">
-        <v>656</v>
-      </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B140" s="97">
         <v>46255</v>
       </c>
       <c r="C140" t="s">
+        <v>659</v>
+      </c>
+      <c r="D140" t="s">
         <v>660</v>
       </c>
-      <c r="D140" t="s">
+      <c r="E140" t="s">
         <v>661</v>
       </c>
-      <c r="E140" t="s">
-        <v>662</v>
-      </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B141" s="97">
         <v>46255</v>
       </c>
       <c r="C141" t="s">
+        <v>662</v>
+      </c>
+      <c r="D141" t="s">
+        <v>660</v>
+      </c>
+      <c r="E141" t="s">
         <v>663</v>
       </c>
-      <c r="D141" t="s">
-        <v>661</v>
-      </c>
-      <c r="E141" t="s">
-        <v>664</v>
-      </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B142" s="97">
         <v>46255</v>
       </c>
       <c r="C142" t="s">
+        <v>664</v>
+      </c>
+      <c r="D142" t="s">
+        <v>660</v>
+      </c>
+      <c r="E142" t="s">
         <v>665</v>
       </c>
-      <c r="D142" t="s">
-        <v>661</v>
-      </c>
-      <c r="E142" t="s">
-        <v>666</v>
-      </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B143" s="97">
         <v>46255</v>
       </c>
       <c r="C143" t="s">
+        <v>666</v>
+      </c>
+      <c r="D143" t="s">
+        <v>660</v>
+      </c>
+      <c r="E143" t="s">
         <v>667</v>
       </c>
-      <c r="D143" t="s">
-        <v>661</v>
-      </c>
-      <c r="E143" t="s">
-        <v>668</v>
-      </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B144" s="97">
         <v>46255</v>
       </c>
       <c r="C144" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D144" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E144" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B145" s="97">
         <v>46255</v>
       </c>
       <c r="C145" t="s">
+        <v>669</v>
+      </c>
+      <c r="D145" t="s">
+        <v>660</v>
+      </c>
+      <c r="E145" t="s">
         <v>670</v>
       </c>
-      <c r="D145" t="s">
-        <v>661</v>
-      </c>
-      <c r="E145" t="s">
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>309</v>
+      </c>
+      <c r="B146" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C146" t="s">
         <v>671</v>
+      </c>
+      <c r="D146" t="s">
+        <v>672</v>
+      </c>
+      <c r="E146" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>306</v>
+      </c>
+      <c r="B147" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C147" t="s">
+        <v>674</v>
+      </c>
+      <c r="D147" t="s">
+        <v>675</v>
+      </c>
+      <c r="E147" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>313</v>
+      </c>
+      <c r="B148" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C148" t="s">
+        <v>677</v>
+      </c>
+      <c r="D148" t="s">
+        <v>678</v>
+      </c>
+      <c r="E148" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>321</v>
+      </c>
+      <c r="B149" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C149" t="s">
+        <v>680</v>
+      </c>
+      <c r="D149" t="s">
+        <v>681</v>
+      </c>
+      <c r="E149" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>309</v>
+      </c>
+      <c r="B150" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C150" t="s">
+        <v>683</v>
+      </c>
+      <c r="D150" t="s">
+        <v>684</v>
+      </c>
+      <c r="E150" t="s">
+        <v>685</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Cosas Roger\BOLSA E INVERSIÓN\repos\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F99D64-7EF0-41C5-8E9A-ED9C89461194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2097B1B5-F75D-4026-AAC5-BAEBF9700907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2448,7 +2448,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="697">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -3144,9 +3144,6 @@
     <t>2026-05-18</t>
   </si>
   <si>
-    <t>12/05/2026</t>
-  </si>
-  <si>
     <t>08/2026</t>
   </si>
   <si>
@@ -3267,18 +3264,6 @@
     <t>&lt;5.0 : Lower quality. Special situations only or avoid.</t>
   </si>
   <si>
-    <t>IMPORTANT</t>
-  </si>
-  <si>
-    <t>Ratings do not include valuation. A 9.0-rated company may be priced to perfection.</t>
-  </si>
-  <si>
-    <t>Cross-reference with Monte Carlo asymmetry data in companion files.</t>
-  </si>
-  <si>
-    <t>Ratings reflect analyst judgment as of April 2026 and should be re-tested quarterly.</t>
-  </si>
-  <si>
     <t>📊 INVESTMENT COMMAND CENTER — Portfolio Analytics Dashboard</t>
   </si>
   <si>
@@ -4543,6 +4528,54 @@
   </si>
   <si>
     <t>Capital empleado 280.000 -&gt; 589.551 (activo total 758.376 menos pasivo corriente 168.825 a 30-jun-2026). Era necesario porque al actualizar el NOPAT a 125.127 con el capital empleado viejo el ROIC saltaba al 44,7%, imposible para Microsoft. Con la cifra correcta queda en 21,2%. AVISO IMPORTANTE: la columna Capital Employed son estimaciones manuales redondeadas en las otras 67 filas (Veeva 1.500, Costco 40.000, Amazon 300.000, Lotus 800...) y no siguen ninguna definicion homogenea, asi que el ROIC NO es comparable entre empresas hasta que esa columna tenga una sola definicion. Esta fila es ahora la unica con la definicion de libro.</t>
+  </si>
+  <si>
+    <t>FCF NORMALIZADO - metodo para empresas en ciclo de capex de crecimiento</t>
+  </si>
+  <si>
+    <t>Problema: cuando una empresa multiplica su capex para construir capacidad nueva, el FCF reportado deja de medir la capacidad de generar caja del negocio y pasa a medir el ritmo de inversion. Amazon cerro los doce meses a jun-2026 con FCF de -7.604 M$ y a la vez con el flujo de operaciones creciendo un 33%.</t>
+  </si>
+  <si>
+    <t>Regla:  capex de mantenimiento = MAX( D&amp;A del periodo ; 50% del capex del periodo )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        FCF normalizado = flujo de caja de operaciones - capex de mantenimiento</t>
+  </si>
+  <si>
+    <t>Por que el maximo de dos cosas: el D&amp;A es la medida contable de la capacidad consumida y es el punto de partida correcto (owner earnings), pero se queda corto cuando el activo crece deprisa, porque refleja un parque de activos mas pequeno que el actual. El suelo del 50% del capex recoge que en infraestructura de nube y logistica buena parte del gasto es reposicion: la propia Microsoft dice que dos tercios de su capex son activos de vida corta, CPU y GPU.</t>
+  </si>
+  <si>
+    <t>Cuando aplicarlo: solo si el capex del periodo supera el doble del D&amp;A, o si el FCF reportado es negativo con flujo de operaciones positivo. Si no se cumple ninguna de las dos, se usa el FCF reportado.</t>
+  </si>
+  <si>
+    <t>Como anotarlo: dejar el FCF normalizado en la columna AS y registrar en el Updates Log los tres numeros de partida (flujo de operaciones, D&amp;A y capex) para que el calculo sea reproducible.</t>
+  </si>
+  <si>
+    <t>Precision: el objetivo es estar aproximadamente acertado, no exactamente equivocado. Un error del 10% en el capex de mantenimiento mueve el FCF normalizado mucho menos que la diferencia entre usar el FCF reportado o no usarlo.</t>
+  </si>
+  <si>
+    <t>Filas normalizadas a 22-ago-2026: AMZN (fila 13) y MSFT (fila 5). El resto usa FCF reportado.</t>
+  </si>
+  <si>
+    <t>OJO: el FCF normalizado NO sustituye a las columnas FCF@5y, que siguen siendo la vision forward y la base de la valoracion. El normalizado solo sirve para que el EV/FCF de cribado signifique algo durante el ciclo de inversion.</t>
+  </si>
+  <si>
+    <t>AS (FCF); AF (R3 Capital Intensity)</t>
+  </si>
+  <si>
+    <t>FCF normalizado + revision de ratings tras resultados</t>
+  </si>
+  <si>
+    <t>FCF pasa de -7.604 reportado a 76.899 normalizado. Partida: flujo de operaciones TTM 161.403, D&amp;A TTM 75.200 (65.756 de 2025 menos 29.489 del 1S25 mas 38.933 del 1S26), capex TTM 169.007. Capex de mantenimiento = max(75.200 ; 84.504) = 84.504. El EV/FCF queda en 36,9x en vez de -373x. Capital Intensity 4-&gt;3: el capex es el 21,8% de las ventas y el FCF reportado es negativo; un 4 sobre 10, donde 10 es asset-light, era generoso.</t>
+  </si>
+  <si>
+    <t>FCF pasa de 66.987 reportado a 124.961 normalizado. Partida: flujo de operaciones 182.935, D&amp;A y otros 38.534, capex 115.948. Capex de mantenimiento = max(38.534 ; 57.974) = 57.974. El EV/FCF queda en 28,4x en vez de 53x. Capital Intensity 5-&gt;4: el capex es el 34,9% de las ventas del ejercicio, y la guia del ano natural 2026 son unos 190.000 M$.</t>
+  </si>
+  <si>
+    <t>AV (Ingresos); AG (R3 Capital Allocation); BO; BN</t>
+  </si>
+  <si>
+    <t>Ingresos 12.149 -&gt; 12.641 LTM (FY2025 11.623 menos 1S25 5.498 mas 1S26 6.516). Capital Allocation 15 -&gt; 13: era la unica nota perfecta del libro y el Q2 2026 muestra crecimiento organico del 3% en el trimestre y del 1% quitando divisa, frente a un +17% de titular. Practicamente todo el crecimiento viene de comprar companias (732 M$ en un solo trimestre) y un 15/15 dice que cada euro reinvertido genera spread positivo, lo cual con el organico al 1% ya no se sostiene solo. Un 13 sigue diciendo excelente. El FCF de 2.700 no se toca: el FCFA2S LTM es 2.031 pero la columna pide FCF sin apalancar y no tengo el desglose para convertirlo.</t>
   </si>
 </sst>
 </file>
@@ -5750,155 +5783,33 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5916,14 +5827,136 @@
     <xf numFmtId="0" fontId="15" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6662,7 +6695,7 @@
                   <c:v>8.33</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.87</c:v>
+                  <c:v>7.82</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>7.8</c:v>
@@ -6686,7 +6719,7 @@
                   <c:v>7.76</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.87</c:v>
+                  <c:v>7.81</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>7.79</c:v>
@@ -16102,7 +16135,7 @@
         <v>0</v>
       </c>
       <c r="AF5" s="91">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG5" s="91">
         <v>14</v>
@@ -16121,15 +16154,15 @@
       </c>
       <c r="AL5" s="26">
         <f t="shared" si="5"/>
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AM5" s="16">
         <f t="shared" si="6"/>
-        <v>7.71</v>
+        <v>7.57</v>
       </c>
       <c r="AN5" s="17">
         <f t="shared" si="7"/>
-        <v>7.87</v>
+        <v>7.82</v>
       </c>
       <c r="AO5" s="18" t="s">
         <v>78</v>
@@ -16145,7 +16178,7 @@
         <v>3548726.8923499999</v>
       </c>
       <c r="AS5" s="19">
-        <v>66987</v>
+        <v>124961</v>
       </c>
       <c r="AT5" s="19">
         <v>125127</v>
@@ -16158,7 +16191,7 @@
       </c>
       <c r="AW5" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>52.976352013823579</v>
+        <v>28.398675525563974</v>
       </c>
       <c r="AX5" s="20">
         <f t="shared" ca="1" si="10"/>
@@ -16188,14 +16221,14 @@
       </c>
       <c r="BE5" s="23">
         <f t="shared" si="15"/>
-        <v>8.9545288544927937E-2</v>
+        <v>-3.8191758023769062E-2</v>
       </c>
       <c r="BF5" t="s">
         <v>83</v>
       </c>
       <c r="BG5" s="23">
         <f t="shared" si="16"/>
-        <v>0.18034009219511105</v>
+        <v>4.1958366434099004E-2</v>
       </c>
       <c r="BH5" s="24">
         <v>20</v>
@@ -17958,7 +17991,7 @@
         <v>-1</v>
       </c>
       <c r="AF13" s="91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG13" s="91">
         <v>13</v>
@@ -17977,15 +18010,15 @@
       </c>
       <c r="AL13" s="26">
         <f t="shared" si="5"/>
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM13" s="16">
         <f t="shared" si="6"/>
-        <v>7.29</v>
+        <v>7.14</v>
       </c>
       <c r="AN13" s="17">
         <f t="shared" si="7"/>
-        <v>7.87</v>
+        <v>7.81</v>
       </c>
       <c r="AO13" s="18" t="s">
         <v>78</v>
@@ -18001,7 +18034,7 @@
         <v>2839049.9981</v>
       </c>
       <c r="AS13" s="19">
-        <v>-7604</v>
+        <v>76899</v>
       </c>
       <c r="AT13" s="19">
         <v>55000</v>
@@ -18014,7 +18047,7 @@
       </c>
       <c r="AW13" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>-373.36270359021569</v>
+        <v>36.919205686679931</v>
       </c>
       <c r="AX13" s="20">
         <f t="shared" ca="1" si="10"/>
@@ -18044,14 +18077,14 @@
       </c>
       <c r="BE13" s="23">
         <f t="shared" si="15"/>
-        <v>-2.5717243949720334</v>
+        <v>-1.0534452076982226E-2</v>
       </c>
       <c r="BF13" t="s">
         <v>112</v>
       </c>
       <c r="BG13" s="23">
         <f t="shared" si="16"/>
-        <v>-2.7039247933124759</v>
+        <v>7.2691169411125189E-2</v>
       </c>
       <c r="BH13" s="24">
         <v>22.5</v>
@@ -22972,7 +23005,7 @@
         <v>77</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="F35" s="11" t="str">
         <f t="array" aca="1" ref="F35" ca="1">_FV(A35,"Moneda")</f>
@@ -24803,7 +24836,7 @@
         <v>0.19507135627029171</v>
       </c>
       <c r="BN42" s="95" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="BO42" s="93" t="s">
         <v>115</v>
@@ -28773,7 +28806,7 @@
         <v>190</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="F60" s="11" t="str">
         <f t="array" aca="1" ref="F60" ca="1">_FV(A60,"Moneda")</f>
@@ -30027,7 +30060,7 @@
         <v>9</v>
       </c>
       <c r="AG65" s="90">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH65" s="90">
         <v>3</v>
@@ -30043,15 +30076,15 @@
       </c>
       <c r="AL65" s="15">
         <f t="shared" si="32"/>
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AM65" s="16">
         <f t="shared" si="33"/>
-        <v>8.86</v>
+        <v>8.57</v>
       </c>
       <c r="AN65" s="17">
         <f t="shared" si="34"/>
-        <v>8.57</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="AO65" s="18" t="s">
         <v>78</v>
@@ -30076,7 +30109,7 @@
         <v>3428</v>
       </c>
       <c r="AV65" s="19">
-        <v>12149</v>
+        <v>12641</v>
       </c>
       <c r="AW65" s="20">
         <f t="shared" ca="1" si="35"/>
@@ -30088,22 +30121,22 @@
       </c>
       <c r="AY65" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>4.009482458834472</v>
+        <v>3.8534295065564432</v>
       </c>
       <c r="AZ65" s="21">
         <v>5000</v>
       </c>
       <c r="BA65" s="22">
         <f t="shared" si="38"/>
-        <v>0.1152358218783439</v>
+        <v>0.11075073174590618</v>
       </c>
       <c r="BB65" s="22">
         <f t="shared" si="39"/>
-        <v>2.4298000000000002</v>
+        <v>2.5282</v>
       </c>
       <c r="BC65" s="23">
         <f t="shared" si="40"/>
-        <v>0.28000000000000003</v>
+        <v>0.27999999999999997</v>
       </c>
       <c r="BD65" s="98">
         <v>4350</v>
@@ -30141,14 +30174,14 @@
         <f t="shared" ca="1" si="44"/>
         <v>0.50867711810090377</v>
       </c>
-      <c r="BN65" s="93" t="s">
-        <v>218</v>
-      </c>
-      <c r="BO65" s="93" t="s">
+      <c r="BN65" s="99">
+        <v>46256</v>
+      </c>
+      <c r="BO65" s="99">
+        <v>46334</v>
+      </c>
+      <c r="BP65" s="93" t="s">
         <v>219</v>
-      </c>
-      <c r="BP65" s="93" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:68" x14ac:dyDescent="0.35">
@@ -30160,7 +30193,7 @@
         <v>UBER</v>
       </c>
       <c r="C66" s="88" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D66" s="88" t="s">
         <v>77</v>
@@ -30606,13 +30639,13 @@
         <v>0.37789220301948356</v>
       </c>
       <c r="BN67" s="96" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="BO67" s="96" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="BP67" s="96" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="68" spans="1:68" x14ac:dyDescent="0.35">
@@ -30838,13 +30871,13 @@
         <v>0.24079940137721412</v>
       </c>
       <c r="BN68" s="96" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="BO68" s="96" t="s">
         <v>140</v>
       </c>
       <c r="BP68" s="96" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
     </row>
     <row r="69" spans="1:68" x14ac:dyDescent="0.35">
@@ -31070,13 +31103,13 @@
         <v>0.20879027721969323</v>
       </c>
       <c r="BN69" s="96" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="BO69" s="96" t="s">
         <v>140</v>
       </c>
       <c r="BP69" s="96" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
     <row r="70" spans="1:68" x14ac:dyDescent="0.35">
@@ -31302,10 +31335,10 @@
         <v>0.23558226327105958</v>
       </c>
       <c r="BN70" s="96" t="s">
+        <v>592</v>
+      </c>
+      <c r="BO70" s="96" t="s">
         <v>597</v>
-      </c>
-      <c r="BO70" s="96" t="s">
-        <v>602</v>
       </c>
       <c r="BP70" s="96" t="s">
         <v>136</v>
@@ -31534,7 +31567,7 @@
         <v>0.19051809473296477</v>
       </c>
       <c r="BN71" s="96" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="BO71" s="96" t="s">
         <v>102</v>
@@ -31563,7 +31596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -31573,7 +31606,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="105" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B1" s="101"/>
       <c r="C1" s="101"/>
@@ -31583,12 +31616,12 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D4" t="e" vm="69">
         <v>#VALUE!</v>
@@ -31600,7 +31633,7 @@
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D5" t="e" vm="70">
         <v>#VALUE!</v>
@@ -31612,7 +31645,7 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D6" t="e" vm="71">
         <v>#VALUE!</v>
@@ -31633,7 +31666,7 @@
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="27" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="D8" t="e" vm="73">
         <v>#VALUE!</v>
@@ -31645,10 +31678,10 @@
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C9" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="E9">
         <v>1.3641000000000001</v>
@@ -31656,197 +31689,230 @@
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="28" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="28" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="28" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="28" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="28" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="28" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="28" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="28" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="28" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="28" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="27" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="28" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="27" t="s">
-        <v>260</v>
-      </c>
+      <c r="A49" s="27"/>
     </row>
     <row r="50" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="28" t="s">
-        <v>261</v>
+        <v>681</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="28" t="s">
-        <v>262</v>
+        <v>682</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="28" t="s">
-        <v>263</v>
+        <v>683</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>690</v>
       </c>
     </row>
   </sheetData>
@@ -31875,8 +31941,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="112" t="s">
-        <v>264</v>
+      <c r="A1" s="168" t="s">
+        <v>259</v>
       </c>
       <c r="B1" s="101"/>
       <c r="C1" s="101"/>
@@ -31897,276 +31963,276 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="129" t="s">
-        <v>265</v>
-      </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
+      <c r="A2" s="156" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
     </row>
     <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="135" t="s">
+      <c r="A3" s="161" t="s">
+        <v>261</v>
+      </c>
+      <c r="B3" s="129"/>
+      <c r="C3" s="128" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3" s="129"/>
+      <c r="E3" s="130" t="s">
+        <v>263</v>
+      </c>
+      <c r="F3" s="129"/>
+      <c r="G3" s="176" t="s">
+        <v>264</v>
+      </c>
+      <c r="H3" s="129"/>
+      <c r="I3" s="177" t="s">
+        <v>265</v>
+      </c>
+      <c r="J3" s="129"/>
+      <c r="K3" s="140" t="s">
         <v>266</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="156" t="s">
-        <v>267</v>
-      </c>
-      <c r="D3" s="124"/>
-      <c r="E3" s="157" t="s">
-        <v>268</v>
-      </c>
-      <c r="F3" s="124"/>
-      <c r="G3" s="123" t="s">
-        <v>269</v>
-      </c>
-      <c r="H3" s="124"/>
-      <c r="I3" s="125" t="s">
-        <v>270</v>
-      </c>
-      <c r="J3" s="124"/>
-      <c r="K3" s="161" t="s">
-        <v>271</v>
-      </c>
-      <c r="L3" s="162"/>
+      <c r="L3" s="141"/>
     </row>
     <row r="4" spans="1:47" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="142">
+      <c r="A4" s="165">
         <f ca="1">COUNTA('Watchlist Ratings'!B4:B71)</f>
         <v>68</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="158">
+      <c r="B4" s="135"/>
+      <c r="C4" s="136">
         <f>ROUND(AVERAGE('Watchlist Ratings'!AN4:AN71),2)</f>
         <v>5.98</v>
       </c>
-      <c r="D4" s="127"/>
-      <c r="E4" s="128" t="str">
+      <c r="D4" s="135"/>
+      <c r="E4" s="137" t="str">
         <f>TEXT(AVERAGE('Watchlist Ratings'!BC4:BC71),"0.0%")</f>
         <v>20.9%</v>
       </c>
-      <c r="F4" s="127"/>
-      <c r="G4" s="128" t="str">
+      <c r="F4" s="135"/>
+      <c r="G4" s="137" t="str">
         <f ca="1">TEXT(AVERAGE('Watchlist Ratings'!AW4:AW71),"0.0x")</f>
-        <v>31.7x</v>
-      </c>
-      <c r="H4" s="127"/>
-      <c r="I4" s="128">
+        <v>37.4x</v>
+      </c>
+      <c r="H4" s="135"/>
+      <c r="I4" s="137">
         <f ca="1">COUNTIF('Watchlist Ratings'!BM4:BM71,"&gt;0")</f>
         <v>58</v>
       </c>
-      <c r="J4" s="127"/>
-      <c r="K4" s="113">
+      <c r="J4" s="135"/>
+      <c r="K4" s="169">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&gt;7.5")</f>
         <v>16</v>
       </c>
-      <c r="L4" s="114"/>
+      <c r="L4" s="143"/>
     </row>
     <row r="5" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="138" t="s">
+      <c r="A5" s="163" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="135"/>
+      <c r="C5" s="134" t="s">
+        <v>268</v>
+      </c>
+      <c r="D5" s="135"/>
+      <c r="E5" s="134" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="135"/>
+      <c r="G5" s="134" t="s">
+        <v>270</v>
+      </c>
+      <c r="H5" s="135"/>
+      <c r="I5" s="134" t="s">
+        <v>271</v>
+      </c>
+      <c r="J5" s="135"/>
+      <c r="K5" s="142" t="s">
         <v>272</v>
       </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="126" t="s">
-        <v>273</v>
-      </c>
-      <c r="D5" s="127"/>
-      <c r="E5" s="126" t="s">
-        <v>274</v>
-      </c>
-      <c r="F5" s="127"/>
-      <c r="G5" s="126" t="s">
-        <v>275</v>
-      </c>
-      <c r="H5" s="127"/>
-      <c r="I5" s="126" t="s">
-        <v>276</v>
-      </c>
-      <c r="J5" s="127"/>
-      <c r="K5" s="163" t="s">
-        <v>277</v>
-      </c>
-      <c r="L5" s="114"/>
+      <c r="L5" s="143"/>
     </row>
     <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="173" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="133"/>
+      <c r="C6" s="132" t="s">
+        <v>274</v>
+      </c>
+      <c r="D6" s="133"/>
+      <c r="E6" s="132" t="s">
+        <v>275</v>
+      </c>
+      <c r="F6" s="133"/>
+      <c r="G6" s="175" t="s">
+        <v>276</v>
+      </c>
+      <c r="H6" s="133"/>
+      <c r="I6" s="132" t="s">
+        <v>277</v>
+      </c>
+      <c r="J6" s="133"/>
+      <c r="K6" s="138" t="s">
         <v>278</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="136" t="s">
+      <c r="L6" s="139"/>
+      <c r="O6" t="s">
         <v>279</v>
       </c>
-      <c r="D6" s="120"/>
-      <c r="E6" s="136" t="s">
+      <c r="S6" t="s">
         <v>280</v>
       </c>
-      <c r="F6" s="120"/>
-      <c r="G6" s="122" t="s">
+      <c r="V6" t="s">
         <v>281</v>
       </c>
-      <c r="H6" s="120"/>
-      <c r="I6" s="136" t="s">
+      <c r="Y6" t="s">
         <v>282</v>
       </c>
-      <c r="J6" s="120"/>
-      <c r="K6" s="159" t="s">
+      <c r="AA6" t="s">
         <v>283</v>
       </c>
-      <c r="L6" s="160"/>
-      <c r="O6" t="s">
+      <c r="AE6" t="s">
         <v>284</v>
       </c>
-      <c r="S6" t="s">
+      <c r="AF6" t="s">
         <v>285</v>
       </c>
-      <c r="V6" t="s">
+      <c r="AH6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>285</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AK6" t="s">
         <v>286</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AL6" t="s">
         <v>287</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AM6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN6" t="s">
         <v>288</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AO6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AP6" t="s">
         <v>289</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AQ6" t="s">
         <v>290</v>
       </c>
-      <c r="AH6" t="s">
-        <v>289</v>
-      </c>
-      <c r="AI6" t="s">
+      <c r="AS6" t="s">
+        <v>284</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AU6" t="s">
         <v>290</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>289</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>291</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>292</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>289</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>293</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>289</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>294</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>295</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>289</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>293</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" s="34" t="s">
         <v>296</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>289</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>298</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>299</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>301</v>
       </c>
       <c r="I7" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="K7" s="36"/>
       <c r="O7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="P7" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="Q7" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="S7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="T7" t="s">
         <v>62</v>
       </c>
       <c r="V7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="W7" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="X7" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="Y7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="Z7" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AA7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AB7" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AC7" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AE7" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AF7">
         <v>83.3333333333333</v>
       </c>
       <c r="AH7" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AI7">
         <v>83.3</v>
       </c>
       <c r="AJ7" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AK7">
         <v>8</v>
@@ -32175,13 +32241,13 @@
         <v>3</v>
       </c>
       <c r="AM7" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AN7">
         <v>52.2</v>
       </c>
       <c r="AO7" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AP7">
         <v>4.5</v>
@@ -32190,7 +32256,7 @@
         <v>33.6</v>
       </c>
       <c r="AS7" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AT7">
         <v>20.173600073636401</v>
@@ -32200,8 +32266,8 @@
       </c>
     </row>
     <row r="8" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="121" t="s">
-        <v>307</v>
+      <c r="A8" s="174" t="s">
+        <v>302</v>
       </c>
       <c r="B8" s="101"/>
       <c r="C8" s="101"/>
@@ -32267,19 +32333,19 @@
         <v>0.2716311384364436</v>
       </c>
       <c r="AE8" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AF8">
         <v>83.3333333333333</v>
       </c>
       <c r="AH8" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AI8">
         <v>83.3</v>
       </c>
       <c r="AJ8" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -32288,13 +32354,13 @@
         <v>3</v>
       </c>
       <c r="AM8" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AN8">
         <v>51.1</v>
       </c>
       <c r="AO8" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AP8">
         <v>3.7</v>
@@ -32303,7 +32369,7 @@
         <v>32.4</v>
       </c>
       <c r="AS8" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AT8">
         <v>44.5724369425714</v>
@@ -32330,11 +32396,11 @@
       </c>
       <c r="E9" s="41">
         <f>'Watchlist Ratings'!AM5</f>
-        <v>7.71</v>
+        <v>7.57</v>
       </c>
       <c r="F9" s="41">
         <f>'Watchlist Ratings'!AN5</f>
-        <v>7.87</v>
+        <v>7.82</v>
       </c>
       <c r="G9" s="42">
         <f>'Watchlist Ratings'!K5</f>
@@ -32350,7 +32416,7 @@
       </c>
       <c r="J9" s="44">
         <f ca="1">'Watchlist Ratings'!AW5</f>
-        <v>52.976352013823579</v>
+        <v>28.398675525563974</v>
       </c>
       <c r="O9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32358,7 +32424,7 @@
       </c>
       <c r="P9" s="37">
         <f>'Watchlist Ratings'!AN5</f>
-        <v>7.87</v>
+        <v>7.82</v>
       </c>
       <c r="Q9" s="23">
         <f ca="1">'Watchlist Ratings'!BM5</f>
@@ -32390,7 +32456,7 @@
       </c>
       <c r="Z9">
         <f ca="1">'Watchlist Ratings'!AW5</f>
-        <v>52.976352013823579</v>
+        <v>28.398675525563974</v>
       </c>
       <c r="AA9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32405,19 +32471,19 @@
         <v>6.6632314867387743E-2</v>
       </c>
       <c r="AE9" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AF9">
         <v>59.375</v>
       </c>
       <c r="AH9" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AI9">
         <v>59.4</v>
       </c>
       <c r="AJ9" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AK9">
         <v>8</v>
@@ -32426,13 +32492,13 @@
         <v>1</v>
       </c>
       <c r="AM9" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AN9">
         <v>45.6</v>
       </c>
       <c r="AO9" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AP9">
         <v>1.1000000000000001</v>
@@ -32441,7 +32507,7 @@
         <v>28.4</v>
       </c>
       <c r="AS9" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AT9">
         <v>28.571278521519002</v>
@@ -32543,19 +32609,19 @@
         <v>0.27406080160124957</v>
       </c>
       <c r="AE10" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AF10">
         <v>54</v>
       </c>
       <c r="AH10" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="AI10">
         <v>54</v>
       </c>
       <c r="AJ10" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AK10">
         <v>8</v>
@@ -32564,13 +32630,13 @@
         <v>3</v>
       </c>
       <c r="AM10" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AN10">
         <v>44.8</v>
       </c>
       <c r="AO10" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AP10">
         <v>1.8</v>
@@ -32579,7 +32645,7 @@
         <v>25</v>
       </c>
       <c r="AS10" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AT10">
         <v>24.369253736000001</v>
@@ -32681,19 +32747,19 @@
         <v>0.348330191162048</v>
       </c>
       <c r="AE11" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AF11">
         <v>41.6666666666667</v>
       </c>
       <c r="AH11" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="AI11">
         <v>41.7</v>
       </c>
       <c r="AJ11" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AK11">
         <v>8</v>
@@ -32702,13 +32768,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AN11">
         <v>43.6</v>
       </c>
       <c r="AO11" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AP11">
         <v>0.6</v>
@@ -32717,7 +32783,7 @@
         <v>23.3</v>
       </c>
       <c r="AS11" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AT11">
         <v>51.179748126470599</v>
@@ -32819,19 +32885,19 @@
         <v>1.9388396424438792E-2</v>
       </c>
       <c r="AE12" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AF12">
         <v>38.3333333333333</v>
       </c>
       <c r="AH12" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AI12">
         <v>38.299999999999997</v>
       </c>
       <c r="AJ12" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="AK12">
         <v>7</v>
@@ -32840,13 +32906,13 @@
         <v>3</v>
       </c>
       <c r="AM12" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AN12">
         <v>40.299999999999997</v>
       </c>
       <c r="AO12" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AP12">
         <v>-0.1</v>
@@ -32855,7 +32921,7 @@
         <v>20.8</v>
       </c>
       <c r="AS12" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AT12">
         <v>25.7039266520833</v>
@@ -32905,10 +32971,10 @@
         <v>26.268452506666669</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="M13" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -32963,19 +33029,19 @@
         <v>0.20330830951269752</v>
       </c>
       <c r="AE13" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AF13">
         <v>37.5</v>
       </c>
       <c r="AH13" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AI13">
         <v>37.5</v>
       </c>
       <c r="AJ13" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="AK13">
         <v>7</v>
@@ -32984,13 +33050,13 @@
         <v>3</v>
       </c>
       <c r="AM13" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="AN13">
         <v>38.9</v>
       </c>
       <c r="AO13" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="AP13">
         <v>4.7</v>
@@ -32999,7 +33065,7 @@
         <v>32.9</v>
       </c>
       <c r="AS13" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AT13">
         <v>29.589673076923098</v>
@@ -33049,7 +33115,7 @@
         <v>26.484788461538457</v>
       </c>
       <c r="L14" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M14">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&gt;=8")</f>
@@ -33108,19 +33174,19 @@
         <v>0.16565345141495191</v>
       </c>
       <c r="AE14" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AF14">
         <v>37.142857142857103</v>
       </c>
       <c r="AH14" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AI14">
         <v>37.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AK14">
         <v>7</v>
@@ -33129,13 +33195,13 @@
         <v>2</v>
       </c>
       <c r="AM14" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AN14">
         <v>38.5</v>
       </c>
       <c r="AO14" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AP14">
         <v>-4.2</v>
@@ -33144,7 +33210,7 @@
         <v>13.7</v>
       </c>
       <c r="AS14" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AT14">
         <v>26.244954871232899</v>
@@ -33194,7 +33260,7 @@
         <v>36.376567839041094</v>
       </c>
       <c r="L15" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="M15">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN71,"&gt;=7",'Watchlist Ratings'!AN4:AN71,"&lt;8")</f>
@@ -33253,19 +33319,19 @@
         <v>0.23151033398140308</v>
       </c>
       <c r="AE15" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AF15">
         <v>36.1111111111111</v>
       </c>
       <c r="AH15" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AI15">
         <v>36.1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AK15">
         <v>7</v>
@@ -33274,13 +33340,13 @@
         <v>2</v>
       </c>
       <c r="AM15" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AN15">
         <v>37.700000000000003</v>
       </c>
       <c r="AO15" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AP15">
         <v>-8</v>
@@ -33289,7 +33355,7 @@
         <v>13.5</v>
       </c>
       <c r="AS15" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AT15">
         <v>27.905545425233299</v>
@@ -33339,7 +33405,7 @@
         <v>27.650297565424239</v>
       </c>
       <c r="L16" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="M16">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN71,"&gt;=6",'Watchlist Ratings'!AN4:AN71,"&lt;7")</f>
@@ -33398,19 +33464,19 @@
         <v>9.0098171806134886E-2</v>
       </c>
       <c r="AE16" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AF16">
         <v>32.142857142857103</v>
       </c>
       <c r="AH16" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AI16">
         <v>32.1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AK16">
         <v>7</v>
@@ -33419,13 +33485,13 @@
         <v>3</v>
       </c>
       <c r="AM16" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AN16">
         <v>29.6</v>
       </c>
       <c r="AO16" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AP16">
         <v>-7.9</v>
@@ -33434,7 +33500,7 @@
         <v>12.3</v>
       </c>
       <c r="AS16" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="AT16">
         <v>52.2229498644231</v>
@@ -33461,11 +33527,11 @@
       </c>
       <c r="E17" s="41">
         <f>'Watchlist Ratings'!AM13</f>
-        <v>7.29</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="41">
         <f>'Watchlist Ratings'!AN13</f>
-        <v>7.87</v>
+        <v>7.81</v>
       </c>
       <c r="G17" s="42">
         <f>'Watchlist Ratings'!K13</f>
@@ -33481,10 +33547,10 @@
       </c>
       <c r="J17" s="44">
         <f ca="1">'Watchlist Ratings'!AW13</f>
-        <v>-373.36270359021569</v>
+        <v>36.919205686679931</v>
       </c>
       <c r="L17" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="M17">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&lt;6")</f>
@@ -33496,7 +33562,7 @@
       </c>
       <c r="P17" s="37">
         <f>'Watchlist Ratings'!AN13</f>
-        <v>7.87</v>
+        <v>7.81</v>
       </c>
       <c r="Q17" s="23">
         <f ca="1">'Watchlist Ratings'!BM13</f>
@@ -33528,7 +33594,7 @@
       </c>
       <c r="Z17">
         <f ca="1">'Watchlist Ratings'!AW13</f>
-        <v>-373.36270359021569</v>
+        <v>36.919205686679931</v>
       </c>
       <c r="AA17" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
@@ -33543,7 +33609,7 @@
         <v>3.7107521210228311E-2</v>
       </c>
       <c r="AS17" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AT17">
         <v>37.736707694444398</v>
@@ -33637,7 +33703,7 @@
         <v>3.658617807367448E-2</v>
       </c>
       <c r="AS18" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AT18">
         <v>24.612029698461502</v>
@@ -33731,7 +33797,7 @@
         <v>0.12088409505027364</v>
       </c>
       <c r="AS19" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AT19">
         <v>45.617441111111098</v>
@@ -33825,7 +33891,7 @@
         <v>-2.7684909382092893E-2</v>
       </c>
       <c r="AS20" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AT20">
         <v>43.630936634999998</v>
@@ -33919,7 +33985,7 @@
         <v>0.11146322371597783</v>
       </c>
       <c r="AS21" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AT21">
         <v>38.120501266027397</v>
@@ -34028,8 +34094,8 @@
       </c>
     </row>
     <row r="24" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="167" t="s">
-        <v>334</v>
+      <c r="A24" s="145" t="s">
+        <v>329</v>
       </c>
       <c r="B24" s="101"/>
       <c r="C24" s="101"/>
@@ -34104,7 +34170,7 @@
     <row r="38" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L40" s="175"/>
+      <c r="L40" s="114"/>
       <c r="M40" s="101"/>
       <c r="N40" s="101"/>
       <c r="O40" s="101"/>
@@ -34121,7 +34187,7 @@
       <c r="Q41" s="57"/>
     </row>
     <row r="42" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J42" s="177"/>
+      <c r="J42" s="118"/>
       <c r="K42" s="101"/>
       <c r="L42" s="101"/>
       <c r="M42" s="101"/>
@@ -34206,8 +34272,8 @@
     <row r="60" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="61" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="62" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="146" t="s">
-        <v>335</v>
+      <c r="A62" s="148" t="s">
+        <v>330</v>
       </c>
       <c r="B62" s="101"/>
       <c r="C62" s="101"/>
@@ -34217,7 +34283,7 @@
       <c r="G62" s="101"/>
       <c r="H62" s="101"/>
       <c r="J62" s="153" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="K62" s="101"/>
       <c r="L62" s="101"/>
@@ -34229,52 +34295,52 @@
     </row>
     <row r="63" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="61" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B63" s="61" t="s">
+        <v>332</v>
+      </c>
+      <c r="C63" s="61" t="s">
+        <v>333</v>
+      </c>
+      <c r="D63" s="61" t="s">
+        <v>334</v>
+      </c>
+      <c r="E63" s="61" t="s">
+        <v>298</v>
+      </c>
+      <c r="F63" s="61" t="s">
+        <v>297</v>
+      </c>
+      <c r="G63" s="61" t="s">
+        <v>335</v>
+      </c>
+      <c r="H63" s="61" t="s">
+        <v>336</v>
+      </c>
+      <c r="J63" s="62" t="s">
+        <v>284</v>
+      </c>
+      <c r="K63" s="62" t="s">
         <v>337</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="L63" s="62" t="s">
         <v>338</v>
       </c>
-      <c r="D63" s="61" t="s">
+      <c r="M63" s="62" t="s">
         <v>339</v>
       </c>
-      <c r="E63" s="61" t="s">
-        <v>303</v>
-      </c>
-      <c r="F63" s="61" t="s">
-        <v>302</v>
-      </c>
-      <c r="G63" s="61" t="s">
+      <c r="N63" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="H63" s="61" t="s">
+      <c r="O63" s="62" t="s">
+        <v>286</v>
+      </c>
+      <c r="P63" s="62" t="s">
         <v>341</v>
       </c>
-      <c r="J63" s="62" t="s">
-        <v>289</v>
-      </c>
-      <c r="K63" s="62" t="s">
+      <c r="Q63" s="62" t="s">
         <v>342</v>
-      </c>
-      <c r="L63" s="62" t="s">
-        <v>343</v>
-      </c>
-      <c r="M63" s="62" t="s">
-        <v>344</v>
-      </c>
-      <c r="N63" s="62" t="s">
-        <v>345</v>
-      </c>
-      <c r="O63" s="62" t="s">
-        <v>291</v>
-      </c>
-      <c r="P63" s="62" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q63" s="62" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -34382,11 +34448,11 @@
       </c>
       <c r="K65" s="66">
         <f>'Watchlist Ratings'!AM5</f>
-        <v>7.71</v>
+        <v>7.57</v>
       </c>
       <c r="L65" s="67">
         <f>'Watchlist Ratings'!AF5</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M65" s="67">
         <f>'Watchlist Ratings'!AG5</f>
@@ -34806,29 +34872,29 @@
       </c>
     </row>
     <row r="72" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="164" t="str">
+      <c r="A72" s="144" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="B72" s="165"/>
-      <c r="C72" s="165"/>
-      <c r="D72" s="165"/>
-      <c r="E72" s="165"/>
-      <c r="F72" s="165"/>
-      <c r="G72" s="165"/>
-      <c r="H72" s="165"/>
-      <c r="I72" s="166"/>
-      <c r="J72" s="174" t="str">
+      <c r="B72" s="112"/>
+      <c r="C72" s="112"/>
+      <c r="D72" s="112"/>
+      <c r="E72" s="112"/>
+      <c r="F72" s="112"/>
+      <c r="G72" s="112"/>
+      <c r="H72" s="112"/>
+      <c r="I72" s="113"/>
+      <c r="J72" s="111" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="K72" s="165"/>
-      <c r="L72" s="165"/>
-      <c r="M72" s="165"/>
-      <c r="N72" s="165"/>
-      <c r="O72" s="165"/>
-      <c r="P72" s="165"/>
-      <c r="Q72" s="166"/>
+      <c r="K72" s="112"/>
+      <c r="L72" s="112"/>
+      <c r="M72" s="112"/>
+      <c r="N72" s="112"/>
+      <c r="O72" s="112"/>
+      <c r="P72" s="112"/>
+      <c r="Q72" s="113"/>
     </row>
     <row r="73" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="68" t="str">
@@ -34869,11 +34935,11 @@
       </c>
       <c r="K73" s="73">
         <f>'Watchlist Ratings'!AM13</f>
-        <v>7.29</v>
+        <v>7.14</v>
       </c>
       <c r="L73" s="74">
         <f>'Watchlist Ratings'!AF13</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M73" s="74">
         <f>'Watchlist Ratings'!AG13</f>
@@ -34898,7 +34964,7 @@
     </row>
     <row r="74" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="75" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B74" s="76" t="str">
         <f ca="1">VLOOKUP(A74,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -34929,7 +34995,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J74" s="78" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="K74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -34962,7 +35028,7 @@
     </row>
     <row r="75" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="79" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B75" s="80" t="str">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -34993,7 +35059,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J75" s="79" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="K75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35025,8 +35091,8 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="139" t="s">
-        <v>348</v>
+      <c r="A76" s="164" t="s">
+        <v>343</v>
       </c>
       <c r="B76" s="101"/>
       <c r="C76" s="101"/>
@@ -35047,7 +35113,7 @@
     </row>
     <row r="77" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="79" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B77" s="80" t="str">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35078,7 +35144,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J77" s="79" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="K77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35111,129 +35177,129 @@
     </row>
     <row r="78" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="131" t="s">
-        <v>349</v>
-      </c>
-      <c r="B78" s="116"/>
-      <c r="C78" s="115" t="s">
-        <v>350</v>
-      </c>
-      <c r="D78" s="116"/>
-      <c r="E78" s="134" t="s">
-        <v>351</v>
-      </c>
-      <c r="F78" s="116"/>
-      <c r="G78" s="134" t="s">
-        <v>352</v>
-      </c>
-      <c r="H78" s="116"/>
-      <c r="I78" s="111" t="s">
-        <v>353</v>
+        <v>344</v>
+      </c>
+      <c r="B78" s="120"/>
+      <c r="C78" s="170" t="s">
+        <v>345</v>
+      </c>
+      <c r="D78" s="120"/>
+      <c r="E78" s="160" t="s">
+        <v>346</v>
+      </c>
+      <c r="F78" s="120"/>
+      <c r="G78" s="160" t="s">
+        <v>347</v>
+      </c>
+      <c r="H78" s="120"/>
+      <c r="I78" s="167" t="s">
+        <v>348</v>
       </c>
       <c r="J78" s="101"/>
       <c r="K78" s="131" t="s">
-        <v>354</v>
-      </c>
-      <c r="L78" s="116"/>
+        <v>349</v>
+      </c>
+      <c r="L78" s="120"/>
       <c r="M78" s="131" t="s">
-        <v>355</v>
-      </c>
-      <c r="N78" s="116"/>
+        <v>350</v>
+      </c>
+      <c r="N78" s="120"/>
       <c r="O78" s="131" t="s">
-        <v>356</v>
-      </c>
-      <c r="P78" s="116"/>
+        <v>351</v>
+      </c>
+      <c r="P78" s="120"/>
       <c r="Q78" s="82" t="str">
         <f>IF(K78&gt;=8.5,"🟢 ALTO",IF(K78&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="140" t="str">
+      <c r="A79" s="119" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AN:AN),'Watchlist Ratings'!AN:AN,0))</f>
         <v>CSU</v>
       </c>
-      <c r="B79" s="116"/>
-      <c r="C79" s="168" t="str">
+      <c r="B79" s="120"/>
+      <c r="C79" s="121" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM:BM),'Watchlist Ratings'!BM:BM,0))</f>
         <v>CSU</v>
       </c>
-      <c r="D79" s="116"/>
-      <c r="E79" s="141" t="str">
+      <c r="D79" s="120"/>
+      <c r="E79" s="122" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BC:BC),'Watchlist Ratings'!BC:BC,0))</f>
         <v>NVDA</v>
       </c>
-      <c r="F79" s="116"/>
-      <c r="G79" s="141" t="str">
+      <c r="F79" s="120"/>
+      <c r="G79" s="122" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!K:K),'Watchlist Ratings'!K:K,0))</f>
         <v>VEEV</v>
       </c>
-      <c r="H79" s="116"/>
+      <c r="H79" s="120"/>
       <c r="I79" s="152" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!L:L),'Watchlist Ratings'!L:L,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J79" s="101"/>
-      <c r="K79" s="140" t="str">
+      <c r="K79" s="119" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AM:AM),'Watchlist Ratings'!AM:AM,0))</f>
-        <v>CSU</v>
-      </c>
-      <c r="L79" s="116"/>
-      <c r="M79" s="140" t="str">
+        <v>DSGX</v>
+      </c>
+      <c r="L79" s="120"/>
+      <c r="M79" s="119" t="str">
         <f t="array" aca="1" ref="M79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MIN('Watchlist Ratings'!AW4:AW64),'Watchlist Ratings'!AW4:AW64,0)+3)</f>
-        <v>AMZN</v>
-      </c>
-      <c r="N79" s="116"/>
-      <c r="O79" s="140" t="str">
+        <v>OTLY</v>
+      </c>
+      <c r="N79" s="120"/>
+      <c r="O79" s="119" t="str">
         <f t="array" aca="1" ref="O79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),'Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="P79" s="116"/>
+      <c r="P79" s="120"/>
       <c r="Q79" s="79" t="str">
         <f ca="1">IF(K79&gt;=8.5,"🟢 ALTO",IF(K79&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="132">
+      <c r="A80" s="158">
         <f>MAX('Watchlist Ratings'!AN:AN)</f>
-        <v>8.57</v>
-      </c>
-      <c r="B80" s="116"/>
-      <c r="C80" s="133">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="B80" s="120"/>
+      <c r="C80" s="159">
         <f ca="1">MAX('Watchlist Ratings'!BM:BM)</f>
         <v>0.50867711810090377</v>
       </c>
-      <c r="D80" s="116"/>
-      <c r="E80" s="137">
+      <c r="D80" s="120"/>
+      <c r="E80" s="162">
         <f>MAX('Watchlist Ratings'!BC:BC)</f>
         <v>0.83333333333333326</v>
       </c>
-      <c r="F80" s="116"/>
-      <c r="G80" s="137" t="str">
+      <c r="F80" s="120"/>
+      <c r="G80" s="162" t="str">
         <f>MAX('Watchlist Ratings'!K:K)&amp;"/8"</f>
         <v>8/8</v>
       </c>
-      <c r="H80" s="116"/>
-      <c r="I80" s="170" t="str">
+      <c r="H80" s="120"/>
+      <c r="I80" s="124" t="str">
         <f>MAX('Watchlist Ratings'!L:L)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J80" s="101"/>
-      <c r="K80" s="171">
+      <c r="K80" s="125">
         <f>MAX('Watchlist Ratings'!AM:AM)</f>
-        <v>8.86</v>
-      </c>
-      <c r="L80" s="116"/>
-      <c r="M80" s="171" t="str">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="L80" s="120"/>
+      <c r="M80" s="125" t="str">
         <f ca="1">MIN('Watchlist Ratings'!AW4:AW64)&amp;"x"</f>
-        <v>-373.362703590216x</v>
-      </c>
-      <c r="N80" s="116"/>
-      <c r="O80" s="171" t="str">
+        <v>-18.59090636x</v>
+      </c>
+      <c r="N80" s="120"/>
+      <c r="O80" s="125" t="str">
         <f t="array" aca="1" ref="O80" ca="1">TEXT(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),"0.0%")</f>
         <v>249.8%</v>
       </c>
-      <c r="P80" s="116"/>
+      <c r="P80" s="120"/>
       <c r="Q80" s="82" t="str">
         <f>IF(K80&gt;=8.5,"🟢 ALTO",IF(K80&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
@@ -35241,7 +35307,7 @@
     </row>
     <row r="81" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="79" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B81" s="80" t="str">
         <f ca="1">VLOOKUP(A81,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35272,7 +35338,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J81" s="79" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="K81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35304,8 +35370,8 @@
       </c>
     </row>
     <row r="82" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="172" t="s">
-        <v>357</v>
+      <c r="A82" s="126" t="s">
+        <v>352</v>
       </c>
       <c r="B82" s="101"/>
       <c r="C82" s="101"/>
@@ -35326,7 +35392,7 @@
     </row>
     <row r="83" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="83" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B83" s="84" t="str">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35357,7 +35423,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J83" s="83" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35391,7 +35457,7 @@
     <row r="84" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="85" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="151" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B85" s="101"/>
       <c r="C85" s="101"/>
@@ -35412,41 +35478,41 @@
     </row>
     <row r="86" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="173" t="s">
+      <c r="A87" s="127" t="s">
+        <v>344</v>
+      </c>
+      <c r="B87" s="101"/>
+      <c r="C87" s="172" t="s">
+        <v>345</v>
+      </c>
+      <c r="D87" s="101"/>
+      <c r="E87" s="123" t="s">
+        <v>346</v>
+      </c>
+      <c r="F87" s="101"/>
+      <c r="G87" s="149" t="s">
+        <v>347</v>
+      </c>
+      <c r="H87" s="101"/>
+      <c r="I87" s="150" t="s">
+        <v>348</v>
+      </c>
+      <c r="J87" s="101"/>
+      <c r="K87" s="171" t="s">
         <v>349</v>
       </c>
-      <c r="B87" s="101"/>
-      <c r="C87" s="118" t="s">
+      <c r="L87" s="101"/>
+      <c r="M87" s="147" t="s">
         <v>350</v>
-      </c>
-      <c r="D87" s="101"/>
-      <c r="E87" s="169" t="s">
-        <v>351</v>
-      </c>
-      <c r="F87" s="101"/>
-      <c r="G87" s="147" t="s">
-        <v>352</v>
-      </c>
-      <c r="H87" s="101"/>
-      <c r="I87" s="148" t="s">
-        <v>353</v>
-      </c>
-      <c r="J87" s="101"/>
-      <c r="K87" s="117" t="s">
-        <v>354</v>
-      </c>
-      <c r="L87" s="101"/>
-      <c r="M87" s="144" t="s">
-        <v>355</v>
       </c>
       <c r="N87" s="101"/>
       <c r="O87" s="154" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="P87" s="101"/>
     </row>
     <row r="88" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="145" t="str">
+      <c r="A88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AN$4:AN$71),'Watchlist Ratings'!AN$4:AN$71,0))</f>
         <v>CSU</v>
       </c>
@@ -35456,74 +35522,74 @@
         <v>CSU</v>
       </c>
       <c r="D88" s="101"/>
-      <c r="E88" s="145" t="str">
+      <c r="E88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!BC$4:BC$71),'Watchlist Ratings'!BC$4:BC$71,0))</f>
         <v>NVDA</v>
       </c>
       <c r="F88" s="101"/>
-      <c r="G88" s="145" t="str">
+      <c r="G88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!K$4:K$71),'Watchlist Ratings'!K$4:K$71,0))</f>
         <v>VEEV</v>
       </c>
       <c r="H88" s="101"/>
-      <c r="I88" s="145" t="str">
+      <c r="I88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!L$4:L$71),'Watchlist Ratings'!L$4:L$71,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J88" s="101"/>
-      <c r="K88" s="145" t="str">
+      <c r="K88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AM$4:AM$71),'Watchlist Ratings'!AM$4:AM$71,0))</f>
-        <v>CSU</v>
+        <v>DSGX</v>
       </c>
       <c r="L88" s="101"/>
-      <c r="M88" s="145" t="str">
+      <c r="M88" s="117" t="str">
         <f t="array" aca="1" ref="M88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64)),IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64),0))</f>
         <v>CHKP</v>
       </c>
       <c r="N88" s="101"/>
-      <c r="O88" s="145" t="str">
+      <c r="O88" s="117" t="str">
         <f t="array" aca="1" ref="O88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64),'Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64,0))</f>
         <v>OTLY</v>
       </c>
       <c r="P88" s="101"/>
     </row>
     <row r="89" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="143">
+      <c r="A89" s="146">
         <f>MAX('Watchlist Ratings'!AN$4:AN$71)</f>
-        <v>8.57</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="B89" s="101"/>
-      <c r="C89" s="150">
+      <c r="C89" s="116">
         <f ca="1">MAX('Watchlist Ratings'!BM$4:BM$64)</f>
         <v>0.46257448883098218</v>
       </c>
       <c r="D89" s="101"/>
-      <c r="E89" s="150">
+      <c r="E89" s="116">
         <f>MAX('Watchlist Ratings'!BC$4:BC$71)</f>
         <v>0.83333333333333326</v>
       </c>
       <c r="F89" s="101"/>
-      <c r="G89" s="149" t="str">
+      <c r="G89" s="110" t="str">
         <f>MAX('Watchlist Ratings'!K$4:K$71)&amp;"/8"</f>
         <v>8/8</v>
       </c>
       <c r="H89" s="101"/>
-      <c r="I89" s="149" t="str">
+      <c r="I89" s="110" t="str">
         <f>MAX('Watchlist Ratings'!L$4:L$71)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J89" s="101"/>
-      <c r="K89" s="176">
+      <c r="K89" s="115">
         <f>MAX('Watchlist Ratings'!AM$4:AM$71)</f>
-        <v>8.86</v>
+        <v>8.7100000000000009</v>
       </c>
       <c r="L89" s="101"/>
-      <c r="M89" s="149" t="str">
+      <c r="M89" s="110" t="str">
         <f t="array" aca="1" ref="M89" ca="1">MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64))&amp;"x"</f>
         <v>7.94399332153846x</v>
       </c>
       <c r="N89" s="101"/>
-      <c r="O89" s="149">
+      <c r="O89" s="110">
         <f t="array" aca="1" ref="O89" ca="1">MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64)</f>
         <v>2.4981957482457289</v>
       </c>
@@ -35531,8 +35597,8 @@
     </row>
     <row r="90" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="110" t="s">
-        <v>357</v>
+      <c r="A91" s="166" t="s">
+        <v>352</v>
       </c>
       <c r="B91" s="101"/>
       <c r="C91" s="101"/>
@@ -35553,44 +35619,38 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="J72:Q72"/>
-    <mergeCell ref="L40:R40"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="O88:P88"/>
-    <mergeCell ref="J42:Q42"/>
-    <mergeCell ref="O89:P89"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="A82:Q82"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="O80:P80"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A24:R24"/>
-    <mergeCell ref="O78:P78"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A91:Q91"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="A76:Q76"/>
+    <mergeCell ref="O79:P79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="M87:N87"/>
     <mergeCell ref="G88:H88"/>
@@ -35607,38 +35667,44 @@
     <mergeCell ref="O87:P87"/>
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="E88:F88"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="A76:Q76"/>
-    <mergeCell ref="O79:P79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A91:Q91"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A24:R24"/>
+    <mergeCell ref="O78:P78"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="A82:Q82"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="O80:P80"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="J72:Q72"/>
+    <mergeCell ref="L40:R40"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="O88:P88"/>
+    <mergeCell ref="J42:Q42"/>
+    <mergeCell ref="O89:P89"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:F22">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -35681,7 +35747,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -35692,87 +35758,87 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B1" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="D1" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E1" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B2" t="s">
         <v>124</v>
       </c>
       <c r="C2" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="E2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B3" t="s">
         <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="E3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B4" t="s">
         <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D4" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B5" t="s">
         <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D5" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E5" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -35783,2308 +35849,2308 @@
         <v>218</v>
       </c>
       <c r="C6" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D6" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="E6" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s">
         <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D7" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E7" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B8" t="s">
         <v>93</v>
       </c>
       <c r="C8" t="s">
+        <v>375</v>
+      </c>
+      <c r="D8" t="s">
+        <v>379</v>
+      </c>
+      <c r="E8" t="s">
         <v>380</v>
-      </c>
-      <c r="D8" t="s">
-        <v>384</v>
-      </c>
-      <c r="E8" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B9" t="s">
         <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D9" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E9" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B10" t="s">
         <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D10" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E10" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B11" t="s">
         <v>93</v>
       </c>
       <c r="C11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D11" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E11" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B12" t="s">
         <v>93</v>
       </c>
       <c r="C12" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D12" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E12" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="B13" t="s">
         <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D13" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E13" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B14" t="s">
         <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D14" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E14" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B15" t="s">
         <v>93</v>
       </c>
       <c r="C15" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D15" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E15" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B16" t="s">
         <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D16" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="E16" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B17" t="s">
         <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D17" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E17" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B18" t="s">
         <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D18" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="E18" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B19" t="s">
         <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D19" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="E19" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B20" t="s">
         <v>93</v>
       </c>
       <c r="C20" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D20" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="E20" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B21" t="s">
         <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D21" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E21" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B22" t="s">
         <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D22" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E22" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B23" t="s">
         <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D23" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E23" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B24" t="s">
         <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D24" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E24" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B25" t="s">
         <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D25" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="E25" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B26" t="s">
         <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D26" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E26" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B27" t="s">
         <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D27" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E27" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B28" t="s">
         <v>100</v>
       </c>
       <c r="C28" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D28" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E28" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B29" t="s">
         <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D29" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E29" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B30" t="s">
         <v>100</v>
       </c>
       <c r="C30" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D30" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E30" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B31" t="s">
         <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D31" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E31" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B32" t="s">
         <v>100</v>
       </c>
       <c r="C32" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D32" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E32" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B33" t="s">
         <v>100</v>
       </c>
       <c r="C33" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D33" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E33" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B34" t="s">
         <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D34" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E34" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B35" t="s">
         <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D35" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E35" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B36" t="s">
         <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D36" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E36" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B37" t="s">
         <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D37" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E37" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B38" t="s">
         <v>100</v>
       </c>
       <c r="C38" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D38" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E38" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B39" t="s">
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D39" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E39" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B40" t="s">
         <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D40" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E40" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B41" t="s">
         <v>100</v>
       </c>
       <c r="C41" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D41" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E41" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B42" t="s">
         <v>100</v>
       </c>
       <c r="C42" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D42" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E42" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B43" t="s">
         <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D43" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E43" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B44" t="s">
         <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D44" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E44" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s">
         <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D45" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E45" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s">
         <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D46" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E46" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B47" t="s">
         <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D47" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E47" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B48" t="s">
         <v>113</v>
       </c>
       <c r="C48" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D48" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E48" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s">
         <v>113</v>
       </c>
       <c r="C49" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D49" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="E49" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s">
         <v>113</v>
       </c>
       <c r="C50" t="s">
+        <v>440</v>
+      </c>
+      <c r="D50" t="s">
+        <v>441</v>
+      </c>
+      <c r="E50" t="s">
         <v>445</v>
-      </c>
-      <c r="D50" t="s">
-        <v>446</v>
-      </c>
-      <c r="E50" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s">
         <v>113</v>
       </c>
       <c r="C51" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D51" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="E51" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B52" t="s">
         <v>113</v>
       </c>
       <c r="C52" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D52" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="E52" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B53" t="s">
         <v>113</v>
       </c>
       <c r="C53" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D53" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="E53" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B54" t="s">
         <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D54" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="E54" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s">
         <v>113</v>
       </c>
       <c r="C55" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D55" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E55" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B56" t="s">
         <v>113</v>
       </c>
       <c r="C56" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="D56" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="E56" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B57" t="s">
         <v>113</v>
       </c>
       <c r="C57" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D57" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="E57" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B58" t="s">
         <v>113</v>
       </c>
       <c r="C58" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D58" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="E58" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B59" t="s">
         <v>113</v>
       </c>
       <c r="C59" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D59" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E59" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B60" t="s">
         <v>113</v>
       </c>
       <c r="C60" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D60" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E60" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B61" t="s">
         <v>113</v>
       </c>
       <c r="C61" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D61" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="E61" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s">
         <v>113</v>
       </c>
       <c r="C62" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D62" t="s">
+        <v>465</v>
+      </c>
+      <c r="E62" t="s">
         <v>470</v>
-      </c>
-      <c r="E62" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B63" t="s">
         <v>113</v>
       </c>
       <c r="C63" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D63" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="E63" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B64" t="s">
         <v>113</v>
       </c>
       <c r="C64" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D64" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E64" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B65" t="s">
         <v>113</v>
       </c>
       <c r="C65" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D65" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="E65" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B66" t="s">
         <v>113</v>
       </c>
       <c r="C66" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D66" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E66" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B67" t="s">
         <v>113</v>
       </c>
       <c r="C67" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D67" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E67" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B68" t="s">
         <v>113</v>
       </c>
       <c r="C68" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D68" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E68" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B69" t="s">
         <v>113</v>
       </c>
       <c r="C69" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D69" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="E69" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="B70" t="s">
         <v>113</v>
       </c>
       <c r="C70" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D70" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="E70" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B71" t="s">
         <v>113</v>
       </c>
       <c r="C71" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D71" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E71" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B72" t="s">
         <v>113</v>
       </c>
       <c r="C72" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D72" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E72" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B73" t="s">
         <v>113</v>
       </c>
       <c r="C73" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D73" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E73" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B74" t="s">
         <v>113</v>
       </c>
       <c r="C74" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D74" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="E74" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B75" t="s">
         <v>113</v>
       </c>
       <c r="C75" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D75" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E75" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B76" t="s">
         <v>113</v>
       </c>
       <c r="C76" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D76" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E76" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B77" t="s">
         <v>113</v>
       </c>
       <c r="C77" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D77" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="E77" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B78" t="s">
         <v>113</v>
       </c>
       <c r="C78" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D78" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="E78" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B79" t="s">
         <v>113</v>
       </c>
       <c r="C79" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D79" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="E79" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B80" t="s">
         <v>113</v>
       </c>
       <c r="C80" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D80" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="E80" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B81" t="s">
         <v>113</v>
       </c>
       <c r="C81" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D81" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="E81" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B82" t="s">
         <v>113</v>
       </c>
       <c r="C82" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D82" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="E82" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B83" t="s">
         <v>113</v>
       </c>
       <c r="C83" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D83" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E83" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="B84" t="s">
         <v>147</v>
       </c>
       <c r="C84" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D84" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E84" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B85" t="s">
         <v>147</v>
       </c>
       <c r="C85" t="s">
+        <v>507</v>
+      </c>
+      <c r="D85" t="s">
+        <v>511</v>
+      </c>
+      <c r="E85" t="s">
         <v>512</v>
-      </c>
-      <c r="D85" t="s">
-        <v>516</v>
-      </c>
-      <c r="E85" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B86" t="s">
         <v>147</v>
       </c>
       <c r="C86" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D86" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E86" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B87" t="s">
         <v>147</v>
       </c>
       <c r="C87" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D87" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E87" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="B88" t="s">
         <v>147</v>
       </c>
       <c r="C88" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D88" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E88" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B89" t="s">
         <v>147</v>
       </c>
       <c r="C89" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D89" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E89" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B90" t="s">
         <v>147</v>
       </c>
       <c r="C90" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D90" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="E90" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B91" t="s">
         <v>147</v>
       </c>
       <c r="C91" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D91" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="E91" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B92" t="s">
         <v>147</v>
       </c>
       <c r="C92" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D92" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E92" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B93" t="s">
         <v>147</v>
       </c>
       <c r="C93" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="D93" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E93" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B94" t="s">
         <v>147</v>
       </c>
       <c r="C94" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="D94" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="E94" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B95" t="s">
         <v>147</v>
       </c>
       <c r="C95" t="s">
+        <v>529</v>
+      </c>
+      <c r="D95" t="s">
         <v>534</v>
       </c>
-      <c r="D95" t="s">
-        <v>539</v>
-      </c>
       <c r="E95" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B96" t="s">
         <v>84</v>
       </c>
       <c r="C96" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D96" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="E96" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="B97" t="s">
         <v>84</v>
       </c>
       <c r="C97" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D97" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="E97" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B98" t="s">
         <v>84</v>
       </c>
       <c r="C98" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D98" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="E98" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B99" t="s">
         <v>84</v>
       </c>
       <c r="C99" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D99" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E99" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B100" t="s">
         <v>84</v>
       </c>
       <c r="C100" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D100" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="E100" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B101" t="s">
         <v>84</v>
       </c>
       <c r="C101" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D101" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="E101" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B102" t="s">
         <v>84</v>
       </c>
       <c r="C102" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D102" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="E102" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B103" t="s">
         <v>79</v>
       </c>
       <c r="C103" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D103" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E103" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B104" t="s">
         <v>79</v>
       </c>
       <c r="C104" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D104" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="E104" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B105" t="s">
         <v>79</v>
       </c>
       <c r="C105" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="D105" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="E105" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B106" t="s">
         <v>79</v>
       </c>
       <c r="C106" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D106" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="E106" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B107" t="s">
         <v>79</v>
       </c>
       <c r="C107" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="D107" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="E107" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B108" t="s">
         <v>79</v>
       </c>
       <c r="C108" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="D108" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E108" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B109" t="s">
         <v>79</v>
       </c>
       <c r="C109" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="D109" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="E109" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B110" t="s">
         <v>79</v>
       </c>
       <c r="C110" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="D110" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="E110" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B111" s="97">
         <v>46254</v>
       </c>
       <c r="C111" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D111" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="E111" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B112" s="97">
         <v>46254</v>
       </c>
       <c r="C112" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="D112" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="E112" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B113" s="97">
         <v>46254</v>
       </c>
       <c r="C113" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="D113" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="E113" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B114" s="97">
         <v>46254</v>
       </c>
       <c r="C114" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D114" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="E114" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="B115" s="97">
         <v>46255</v>
       </c>
       <c r="C115" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D115" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="E115" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B116" s="97">
         <v>46255</v>
       </c>
       <c r="C116" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="D116" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="E116" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B117" s="97">
         <v>46255</v>
       </c>
       <c r="C117" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="D117" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="E117" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B118" s="97">
         <v>46255</v>
       </c>
       <c r="C118" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="D118" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="E118" t="s">
-        <v>615</v>
+        <v>610</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="B119" s="97">
         <v>46255</v>
       </c>
       <c r="C119" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="D119" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E119" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B120" s="97">
         <v>46255</v>
       </c>
       <c r="C120" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D120" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E120" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B121" s="97">
         <v>46255</v>
       </c>
       <c r="C121" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="D121" t="s">
+        <v>612</v>
+      </c>
+      <c r="E121" t="s">
         <v>617</v>
-      </c>
-      <c r="E121" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B122" s="97">
         <v>46255</v>
       </c>
       <c r="C122" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D122" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E122" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B123" s="97">
         <v>46255</v>
       </c>
       <c r="C123" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="D123" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E123" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B124" s="97">
         <v>46255</v>
       </c>
       <c r="C124" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="D124" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E124" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B125" s="97">
         <v>46255</v>
       </c>
       <c r="C125" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="D125" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E125" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B126" s="97">
         <v>46255</v>
       </c>
       <c r="C126" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D126" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E126" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="B127" s="97">
         <v>46255</v>
       </c>
       <c r="C127" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D127" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E127" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B128" s="97">
         <v>46255</v>
       </c>
       <c r="C128" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D128" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E128" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="B129" s="97">
         <v>46255</v>
       </c>
       <c r="C129" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D129" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E129" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B130" s="97">
         <v>46255</v>
       </c>
       <c r="C130" t="s">
+        <v>625</v>
+      </c>
+      <c r="D130" t="s">
+        <v>612</v>
+      </c>
+      <c r="E130" t="s">
         <v>630</v>
-      </c>
-      <c r="D130" t="s">
-        <v>617</v>
-      </c>
-      <c r="E130" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B131" s="97">
         <v>46255</v>
       </c>
       <c r="C131" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="D131" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E131" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B132" s="97">
         <v>46255</v>
       </c>
       <c r="C132" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D132" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E132" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B133" s="97">
         <v>46255</v>
       </c>
       <c r="C133" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D133" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E133" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B134" s="97">
         <v>46255</v>
       </c>
       <c r="C134" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D134" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E134" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B135" s="97">
         <v>46255</v>
       </c>
       <c r="C135" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="D135" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E135" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B136" s="97">
         <v>46255</v>
       </c>
       <c r="C136" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D136" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E136" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B137" s="97">
         <v>46255</v>
       </c>
       <c r="C137" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="D137" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E137" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B138" s="97">
         <v>46255</v>
       </c>
       <c r="C138" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="D138" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E138" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B139" s="97">
         <v>46255</v>
       </c>
       <c r="C139" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="D139" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="E139" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B140" s="97">
         <v>46255</v>
       </c>
       <c r="C140" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="D140" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E140" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B141" s="97">
         <v>46255</v>
       </c>
       <c r="C141" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="D141" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E141" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
@@ -38095,149 +38161,200 @@
         <v>46255</v>
       </c>
       <c r="C142" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="D142" t="s">
+        <v>655</v>
+      </c>
+      <c r="E142" t="s">
         <v>660</v>
-      </c>
-      <c r="E142" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B143" s="97">
         <v>46255</v>
       </c>
       <c r="C143" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="D143" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E143" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="B144" s="97">
         <v>46255</v>
       </c>
       <c r="C144" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="D144" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E144" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B145" s="97">
         <v>46255</v>
       </c>
       <c r="C145" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="D145" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="E145" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B146" s="97">
         <v>46256</v>
       </c>
       <c r="C146" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="D146" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="E146" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B147" s="97">
         <v>46256</v>
       </c>
       <c r="C147" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D147" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="E147" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B148" s="97">
         <v>46256</v>
       </c>
       <c r="C148" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D148" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="E148" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B149" s="97">
         <v>46256</v>
       </c>
       <c r="C149" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="D149" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="E149" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B150" s="97">
         <v>46256</v>
       </c>
       <c r="C150" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="D150" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="E150" t="s">
-        <v>685</v>
+        <v>680</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>301</v>
+      </c>
+      <c r="B151" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C151" t="s">
+        <v>691</v>
+      </c>
+      <c r="D151" t="s">
+        <v>692</v>
+      </c>
+      <c r="E151" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>304</v>
+      </c>
+      <c r="B152" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C152" t="s">
+        <v>691</v>
+      </c>
+      <c r="D152" t="s">
+        <v>692</v>
+      </c>
+      <c r="E152" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>217</v>
+      </c>
+      <c r="B153" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C153" t="s">
+        <v>695</v>
+      </c>
+      <c r="D153" t="s">
+        <v>692</v>
+      </c>
+      <c r="E153" t="s">
+        <v>696</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Cosas Roger\BOLSA E INVERSIÓN\repos\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2097B1B5-F75D-4026-AAC5-BAEBF9700907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FE987F-4449-47BD-A5C5-EC12131360BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2448,7 +2448,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="705">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -4576,6 +4576,30 @@
   </si>
   <si>
     <t>Ingresos 12.149 -&gt; 12.641 LTM (FY2025 11.623 menos 1S25 5.498 mas 1S26 6.516). Capital Allocation 15 -&gt; 13: era la unica nota perfecta del libro y el Q2 2026 muestra crecimiento organico del 3% en el trimestre y del 1% quitando divisa, frente a un +17% de titular. Practicamente todo el crecimiento viene de comprar companias (732 M$ en un solo trimestre) y un 15/15 dice que cada euro reinvertido genera spread positivo, lo cual con el organico al 1% ya no se sostiene solo. Un 13 sigue diciendo excelente. El FCF de 2.700 no se toca: el FCFA2S LTM es 2.031 pero la columna pide FCF sin apalancar y no tengo el desglose para convertirlo.</t>
+  </si>
+  <si>
+    <t>AV; BN</t>
+  </si>
+  <si>
+    <t>Verificacion del top 10 contra investor relations</t>
+  </si>
+  <si>
+    <t>Ingresos 262.000 -&gt; 287.790 LTM (FY2025 de 52 semanas 269.900, menos las 36 semanas comparables de 185.480, mas las 36 semanas del FY2026 de 203.370). El Q3 FY26 cerro con ventas de 69,15 MM$ (+11,6%) y comparables del +9,8%, del +6,6% sin gasolina ni divisa. NOPAT no se toca: falta el resultado operativo. Sin cambios de rating: los resultados confirman la nota.</t>
+  </si>
+  <si>
+    <t>AS; BN</t>
+  </si>
+  <si>
+    <t>FCF 6.936 -&gt; 6.200, que es el beneficio distribuible total de los ultimos doce meses reportado en el Q2 2026 (2,61 $/accion). El trimestre trajo un record de 77.000 M$ captados, 100.000 M$ en el semestre, capital con comisiones +19% hasta 672.000 M$ y 210.000 M$ de capital desplegable. Sin cambios de rating. PENDIENTE: la celda de proximos resultados sigue en 13/08/2026, que es la fecha de los ultimos.</t>
+  </si>
+  <si>
+    <t>Ingresos 1.200 -&gt; 1.296 LTM (FY2025 1.260,0 menos 1S25 605,7 mas 1S26 642,0). EBITDA 320 -&gt; 350: el 320 era imposible porque quedaba POR DEBAJO del EBIT LTM de 349,8; se pone el EBIT como suelo hasta tener el D&amp;A exacto, asi que el EV/EBITDA real es algo menor. Contexto: margen EBIT del 26% en 2025 pese a aranceles de EE.UU. y divisa en contra, 50% de cuota mundial y ratio de fondos propios del 80%. El 26,5% del 1S26 incluye 14 M EUR de devolucion de aranceles: sin eso es 24,3%. El Q2 se freno al +4% por China. Sin cambios de rating: la concentracion de producto ya se bajo a -1 el 21-ago.</t>
+  </si>
+  <si>
+    <t>AV; AU; BN</t>
+  </si>
+  <si>
+    <t>Ingresos 26.500 -&gt; 29.251 MSEK LTM (FY2025 28.251 menos 1S25 13.881 mas 1S26 14.881). EBITDA 5.800 -&gt; 6.627: igual que en Rational, el 5.800 quedaba por debajo del EBITA LTM, asi que se pone el EBITA como suelo. Margen EBITA del 22,6% en el semestre, +60 pb. Crecimiento organico del 4,2% en 2025 y del 2,9% en el 1S26, con 16 negocios consolidados en 2025. Sin cambios de rating: su mezcla de organico y M&amp;A es mas sana que la de Constellation y su Capital Allocation de 14 sobre 15 se sostiene.</t>
   </si>
 </sst>
 </file>
@@ -5783,33 +5807,155 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5827,136 +5973,14 @@
     <xf numFmtId="0" fontId="15" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16642,7 +16666,7 @@
         <v>110182.45125</v>
       </c>
       <c r="AS7" s="19">
-        <v>6936</v>
+        <v>6200</v>
       </c>
       <c r="AT7" s="19">
         <v>5500</v>
@@ -16655,7 +16679,7 @@
       </c>
       <c r="AW7" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>15.885589857266435</v>
+        <v>17.771363104838709</v>
       </c>
       <c r="AX7" s="20">
         <f t="shared" ca="1" si="10"/>
@@ -16685,14 +16709,14 @@
       </c>
       <c r="BE7" s="23">
         <f t="shared" si="15"/>
-        <v>6.8983984752092997E-2</v>
+        <v>9.3237896239710016E-2</v>
       </c>
       <c r="BF7">
         <v>13846</v>
       </c>
       <c r="BG7" s="23">
         <f t="shared" si="16"/>
-        <v>0.14826743554130828</v>
+        <v>0.17432018950486827</v>
       </c>
       <c r="BH7" s="24">
         <v>18</v>
@@ -16716,8 +16740,8 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.348330191162048</v>
       </c>
-      <c r="BN7" t="s">
-        <v>79</v>
+      <c r="BN7" s="97">
+        <v>46256</v>
       </c>
       <c r="BO7" t="s">
         <v>89</v>
@@ -16883,7 +16907,7 @@
         <v>11800</v>
       </c>
       <c r="AV8" s="19">
-        <v>262000</v>
+        <v>287790</v>
       </c>
       <c r="AW8" s="20">
         <f t="shared" ca="1" si="9"/>
@@ -16895,18 +16919,18 @@
       </c>
       <c r="AY8" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>1.5870371334198474</v>
+        <v>1.4448164597658015</v>
       </c>
       <c r="AZ8" s="21">
         <v>40000</v>
       </c>
       <c r="BA8" s="22">
         <f t="shared" si="12"/>
-        <v>2.8625954198473282E-2</v>
+        <v>2.6060669237986032E-2</v>
       </c>
       <c r="BB8" s="22">
         <f t="shared" si="13"/>
-        <v>6.55</v>
+        <v>7.19475</v>
       </c>
       <c r="BC8" s="23">
         <f t="shared" si="14"/>
@@ -16948,8 +16972,8 @@
         <f t="shared" ca="1" si="20"/>
         <v>1.9388396424438792E-2</v>
       </c>
-      <c r="BN8" t="s">
-        <v>93</v>
+      <c r="BN8" s="97">
+        <v>46256</v>
       </c>
       <c r="BO8" t="s">
         <v>94</v>
@@ -17344,10 +17368,10 @@
         <v>230</v>
       </c>
       <c r="AU10" s="19">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AV10" s="19">
-        <v>1200</v>
+        <v>1296</v>
       </c>
       <c r="AW10" s="20">
         <f t="shared" ca="1" si="9"/>
@@ -17355,22 +17379,22 @@
       </c>
       <c r="AX10" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>21.518890624999997</v>
+        <v>19.674414285714285</v>
       </c>
       <c r="AY10" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>5.7383708333333328</v>
+        <v>5.3133063271604932</v>
       </c>
       <c r="AZ10" s="21">
         <v>600</v>
       </c>
       <c r="BA10" s="22">
         <f t="shared" si="12"/>
-        <v>0.19166666666666668</v>
+        <v>0.17746913580246915</v>
       </c>
       <c r="BB10" s="22">
         <f t="shared" si="13"/>
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="BC10" s="23">
         <f t="shared" si="14"/>
@@ -17412,11 +17436,11 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.16565345141495191</v>
       </c>
-      <c r="BN10" s="93" t="s">
-        <v>100</v>
-      </c>
-      <c r="BO10" s="93" t="s">
-        <v>101</v>
+      <c r="BN10" s="99">
+        <v>46256</v>
+      </c>
+      <c r="BO10" s="99">
+        <v>46181</v>
       </c>
       <c r="BP10" s="93" t="s">
         <v>102</v>
@@ -19432,10 +19456,10 @@
         <v>3400</v>
       </c>
       <c r="AU19" s="19">
-        <v>5800</v>
+        <v>6627</v>
       </c>
       <c r="AV19" s="19">
-        <v>26500</v>
+        <v>29251</v>
       </c>
       <c r="AW19" s="20">
         <f t="shared" ca="1" si="9"/>
@@ -19443,22 +19467,22 @@
       </c>
       <c r="AX19" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>24.758942862068963</v>
+        <v>21.669212102006938</v>
       </c>
       <c r="AY19" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>5.4189384377358483</v>
+        <v>4.9092977539229423</v>
       </c>
       <c r="AZ19" s="21">
         <v>22000</v>
       </c>
       <c r="BA19" s="22">
         <f t="shared" si="12"/>
-        <v>0.12830188679245283</v>
+        <v>0.11623534238145704</v>
       </c>
       <c r="BB19" s="22">
         <f t="shared" si="13"/>
-        <v>1.2045454545454546</v>
+        <v>1.329590909090909</v>
       </c>
       <c r="BC19" s="23">
         <f t="shared" si="14"/>
@@ -19500,8 +19524,8 @@
         <f t="shared" ca="1" si="20"/>
         <v>0.114780755491519</v>
       </c>
-      <c r="BN19" s="93" t="s">
-        <v>113</v>
+      <c r="BN19" s="99">
+        <v>46256</v>
       </c>
       <c r="BO19" s="93" t="s">
         <v>135</v>
@@ -31941,7 +31965,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="112" t="s">
         <v>259</v>
       </c>
       <c r="B1" s="101"/>
@@ -31963,130 +31987,130 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="156" t="s">
+      <c r="A2" s="129" t="s">
         <v>260</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
     </row>
     <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="161" t="s">
+      <c r="A3" s="135" t="s">
         <v>261</v>
       </c>
-      <c r="B3" s="129"/>
-      <c r="C3" s="128" t="s">
+      <c r="B3" s="124"/>
+      <c r="C3" s="156" t="s">
         <v>262</v>
       </c>
-      <c r="D3" s="129"/>
-      <c r="E3" s="130" t="s">
+      <c r="D3" s="124"/>
+      <c r="E3" s="157" t="s">
         <v>263</v>
       </c>
-      <c r="F3" s="129"/>
-      <c r="G3" s="176" t="s">
+      <c r="F3" s="124"/>
+      <c r="G3" s="123" t="s">
         <v>264</v>
       </c>
-      <c r="H3" s="129"/>
-      <c r="I3" s="177" t="s">
+      <c r="H3" s="124"/>
+      <c r="I3" s="125" t="s">
         <v>265</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="140" t="s">
+      <c r="J3" s="124"/>
+      <c r="K3" s="161" t="s">
         <v>266</v>
       </c>
-      <c r="L3" s="141"/>
+      <c r="L3" s="162"/>
     </row>
     <row r="4" spans="1:47" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="165">
+      <c r="A4" s="142">
         <f ca="1">COUNTA('Watchlist Ratings'!B4:B71)</f>
         <v>68</v>
       </c>
-      <c r="B4" s="135"/>
-      <c r="C4" s="136">
+      <c r="B4" s="127"/>
+      <c r="C4" s="158">
         <f>ROUND(AVERAGE('Watchlist Ratings'!AN4:AN71),2)</f>
         <v>5.98</v>
       </c>
-      <c r="D4" s="135"/>
-      <c r="E4" s="137" t="str">
+      <c r="D4" s="127"/>
+      <c r="E4" s="128" t="str">
         <f>TEXT(AVERAGE('Watchlist Ratings'!BC4:BC71),"0.0%")</f>
         <v>20.9%</v>
       </c>
-      <c r="F4" s="135"/>
-      <c r="G4" s="137" t="str">
+      <c r="F4" s="127"/>
+      <c r="G4" s="128" t="str">
         <f ca="1">TEXT(AVERAGE('Watchlist Ratings'!AW4:AW71),"0.0x")</f>
         <v>37.4x</v>
       </c>
-      <c r="H4" s="135"/>
-      <c r="I4" s="137">
+      <c r="H4" s="127"/>
+      <c r="I4" s="128">
         <f ca="1">COUNTIF('Watchlist Ratings'!BM4:BM71,"&gt;0")</f>
         <v>58</v>
       </c>
-      <c r="J4" s="135"/>
-      <c r="K4" s="169">
+      <c r="J4" s="127"/>
+      <c r="K4" s="113">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&gt;7.5")</f>
         <v>16</v>
       </c>
-      <c r="L4" s="143"/>
+      <c r="L4" s="114"/>
     </row>
     <row r="5" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="163" t="s">
+      <c r="A5" s="138" t="s">
         <v>267</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="134" t="s">
+      <c r="B5" s="127"/>
+      <c r="C5" s="126" t="s">
         <v>268</v>
       </c>
-      <c r="D5" s="135"/>
-      <c r="E5" s="134" t="s">
+      <c r="D5" s="127"/>
+      <c r="E5" s="126" t="s">
         <v>269</v>
       </c>
-      <c r="F5" s="135"/>
-      <c r="G5" s="134" t="s">
+      <c r="F5" s="127"/>
+      <c r="G5" s="126" t="s">
         <v>270</v>
       </c>
-      <c r="H5" s="135"/>
-      <c r="I5" s="134" t="s">
+      <c r="H5" s="127"/>
+      <c r="I5" s="126" t="s">
         <v>271</v>
       </c>
-      <c r="J5" s="135"/>
-      <c r="K5" s="142" t="s">
+      <c r="J5" s="127"/>
+      <c r="K5" s="163" t="s">
         <v>272</v>
       </c>
-      <c r="L5" s="143"/>
+      <c r="L5" s="114"/>
     </row>
     <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="173" t="s">
+      <c r="A6" s="119" t="s">
         <v>273</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="132" t="s">
+      <c r="B6" s="120"/>
+      <c r="C6" s="136" t="s">
         <v>274</v>
       </c>
-      <c r="D6" s="133"/>
-      <c r="E6" s="132" t="s">
+      <c r="D6" s="120"/>
+      <c r="E6" s="136" t="s">
         <v>275</v>
       </c>
-      <c r="F6" s="133"/>
-      <c r="G6" s="175" t="s">
+      <c r="F6" s="120"/>
+      <c r="G6" s="122" t="s">
         <v>276</v>
       </c>
-      <c r="H6" s="133"/>
-      <c r="I6" s="132" t="s">
+      <c r="H6" s="120"/>
+      <c r="I6" s="136" t="s">
         <v>277</v>
       </c>
-      <c r="J6" s="133"/>
-      <c r="K6" s="138" t="s">
+      <c r="J6" s="120"/>
+      <c r="K6" s="159" t="s">
         <v>278</v>
       </c>
-      <c r="L6" s="139"/>
+      <c r="L6" s="160"/>
       <c r="O6" t="s">
         <v>279</v>
       </c>
@@ -32266,7 +32290,7 @@
       </c>
     </row>
     <row r="8" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="174" t="s">
+      <c r="A8" s="121" t="s">
         <v>302</v>
       </c>
       <c r="B8" s="101"/>
@@ -32692,7 +32716,7 @@
       </c>
       <c r="J11" s="44">
         <f ca="1">'Watchlist Ratings'!AW7</f>
-        <v>15.885589857266435</v>
+        <v>17.771363104838709</v>
       </c>
       <c r="O11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -32732,7 +32756,7 @@
       </c>
       <c r="Z11">
         <f ca="1">'Watchlist Ratings'!AW7</f>
-        <v>15.885589857266435</v>
+        <v>17.771363104838709</v>
       </c>
       <c r="AA11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -34094,7 +34118,7 @@
       </c>
     </row>
     <row r="24" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="145" t="s">
+      <c r="A24" s="167" t="s">
         <v>329</v>
       </c>
       <c r="B24" s="101"/>
@@ -34170,7 +34194,7 @@
     <row r="38" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L40" s="114"/>
+      <c r="L40" s="175"/>
       <c r="M40" s="101"/>
       <c r="N40" s="101"/>
       <c r="O40" s="101"/>
@@ -34187,7 +34211,7 @@
       <c r="Q41" s="57"/>
     </row>
     <row r="42" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J42" s="118"/>
+      <c r="J42" s="177"/>
       <c r="K42" s="101"/>
       <c r="L42" s="101"/>
       <c r="M42" s="101"/>
@@ -34272,7 +34296,7 @@
     <row r="60" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="61" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="62" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="148" t="s">
+      <c r="A62" s="146" t="s">
         <v>330</v>
       </c>
       <c r="B62" s="101"/>
@@ -34872,29 +34896,29 @@
       </c>
     </row>
     <row r="72" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="144" t="str">
+      <c r="A72" s="164" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="B72" s="112"/>
-      <c r="C72" s="112"/>
-      <c r="D72" s="112"/>
-      <c r="E72" s="112"/>
-      <c r="F72" s="112"/>
-      <c r="G72" s="112"/>
-      <c r="H72" s="112"/>
-      <c r="I72" s="113"/>
-      <c r="J72" s="111" t="str">
+      <c r="B72" s="165"/>
+      <c r="C72" s="165"/>
+      <c r="D72" s="165"/>
+      <c r="E72" s="165"/>
+      <c r="F72" s="165"/>
+      <c r="G72" s="165"/>
+      <c r="H72" s="165"/>
+      <c r="I72" s="166"/>
+      <c r="J72" s="174" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="K72" s="112"/>
-      <c r="L72" s="112"/>
-      <c r="M72" s="112"/>
-      <c r="N72" s="112"/>
-      <c r="O72" s="112"/>
-      <c r="P72" s="112"/>
-      <c r="Q72" s="113"/>
+      <c r="K72" s="165"/>
+      <c r="L72" s="165"/>
+      <c r="M72" s="165"/>
+      <c r="N72" s="165"/>
+      <c r="O72" s="165"/>
+      <c r="P72" s="165"/>
+      <c r="Q72" s="166"/>
     </row>
     <row r="73" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="68" t="str">
@@ -35091,7 +35115,7 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="164" t="s">
+      <c r="A76" s="139" t="s">
         <v>343</v>
       </c>
       <c r="B76" s="101"/>
@@ -35179,127 +35203,127 @@
       <c r="A78" s="131" t="s">
         <v>344</v>
       </c>
-      <c r="B78" s="120"/>
-      <c r="C78" s="170" t="s">
+      <c r="B78" s="116"/>
+      <c r="C78" s="115" t="s">
         <v>345</v>
       </c>
-      <c r="D78" s="120"/>
-      <c r="E78" s="160" t="s">
+      <c r="D78" s="116"/>
+      <c r="E78" s="134" t="s">
         <v>346</v>
       </c>
-      <c r="F78" s="120"/>
-      <c r="G78" s="160" t="s">
+      <c r="F78" s="116"/>
+      <c r="G78" s="134" t="s">
         <v>347</v>
       </c>
-      <c r="H78" s="120"/>
-      <c r="I78" s="167" t="s">
+      <c r="H78" s="116"/>
+      <c r="I78" s="111" t="s">
         <v>348</v>
       </c>
       <c r="J78" s="101"/>
       <c r="K78" s="131" t="s">
         <v>349</v>
       </c>
-      <c r="L78" s="120"/>
+      <c r="L78" s="116"/>
       <c r="M78" s="131" t="s">
         <v>350</v>
       </c>
-      <c r="N78" s="120"/>
+      <c r="N78" s="116"/>
       <c r="O78" s="131" t="s">
         <v>351</v>
       </c>
-      <c r="P78" s="120"/>
+      <c r="P78" s="116"/>
       <c r="Q78" s="82" t="str">
         <f>IF(K78&gt;=8.5,"🟢 ALTO",IF(K78&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="119" t="str">
+      <c r="A79" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AN:AN),'Watchlist Ratings'!AN:AN,0))</f>
         <v>CSU</v>
       </c>
-      <c r="B79" s="120"/>
-      <c r="C79" s="121" t="str">
+      <c r="B79" s="116"/>
+      <c r="C79" s="168" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM:BM),'Watchlist Ratings'!BM:BM,0))</f>
         <v>CSU</v>
       </c>
-      <c r="D79" s="120"/>
-      <c r="E79" s="122" t="str">
+      <c r="D79" s="116"/>
+      <c r="E79" s="141" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BC:BC),'Watchlist Ratings'!BC:BC,0))</f>
         <v>NVDA</v>
       </c>
-      <c r="F79" s="120"/>
-      <c r="G79" s="122" t="str">
+      <c r="F79" s="116"/>
+      <c r="G79" s="141" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!K:K),'Watchlist Ratings'!K:K,0))</f>
         <v>VEEV</v>
       </c>
-      <c r="H79" s="120"/>
+      <c r="H79" s="116"/>
       <c r="I79" s="152" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!L:L),'Watchlist Ratings'!L:L,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J79" s="101"/>
-      <c r="K79" s="119" t="str">
+      <c r="K79" s="140" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AM:AM),'Watchlist Ratings'!AM:AM,0))</f>
         <v>DSGX</v>
       </c>
-      <c r="L79" s="120"/>
-      <c r="M79" s="119" t="str">
+      <c r="L79" s="116"/>
+      <c r="M79" s="140" t="str">
         <f t="array" aca="1" ref="M79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MIN('Watchlist Ratings'!AW4:AW64),'Watchlist Ratings'!AW4:AW64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="N79" s="120"/>
-      <c r="O79" s="119" t="str">
+      <c r="N79" s="116"/>
+      <c r="O79" s="140" t="str">
         <f t="array" aca="1" ref="O79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),'Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="P79" s="120"/>
+      <c r="P79" s="116"/>
       <c r="Q79" s="79" t="str">
         <f ca="1">IF(K79&gt;=8.5,"🟢 ALTO",IF(K79&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="158">
+      <c r="A80" s="132">
         <f>MAX('Watchlist Ratings'!AN:AN)</f>
         <v>8.4499999999999993</v>
       </c>
-      <c r="B80" s="120"/>
-      <c r="C80" s="159">
+      <c r="B80" s="116"/>
+      <c r="C80" s="133">
         <f ca="1">MAX('Watchlist Ratings'!BM:BM)</f>
         <v>0.50867711810090377</v>
       </c>
-      <c r="D80" s="120"/>
-      <c r="E80" s="162">
+      <c r="D80" s="116"/>
+      <c r="E80" s="137">
         <f>MAX('Watchlist Ratings'!BC:BC)</f>
         <v>0.83333333333333326</v>
       </c>
-      <c r="F80" s="120"/>
-      <c r="G80" s="162" t="str">
+      <c r="F80" s="116"/>
+      <c r="G80" s="137" t="str">
         <f>MAX('Watchlist Ratings'!K:K)&amp;"/8"</f>
         <v>8/8</v>
       </c>
-      <c r="H80" s="120"/>
-      <c r="I80" s="124" t="str">
+      <c r="H80" s="116"/>
+      <c r="I80" s="170" t="str">
         <f>MAX('Watchlist Ratings'!L:L)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J80" s="101"/>
-      <c r="K80" s="125">
+      <c r="K80" s="171">
         <f>MAX('Watchlist Ratings'!AM:AM)</f>
         <v>8.7100000000000009</v>
       </c>
-      <c r="L80" s="120"/>
-      <c r="M80" s="125" t="str">
+      <c r="L80" s="116"/>
+      <c r="M80" s="171" t="str">
         <f ca="1">MIN('Watchlist Ratings'!AW4:AW64)&amp;"x"</f>
         <v>-18.59090636x</v>
       </c>
-      <c r="N80" s="120"/>
-      <c r="O80" s="125" t="str">
+      <c r="N80" s="116"/>
+      <c r="O80" s="171" t="str">
         <f t="array" aca="1" ref="O80" ca="1">TEXT(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),"0.0%")</f>
         <v>249.8%</v>
       </c>
-      <c r="P80" s="120"/>
+      <c r="P80" s="116"/>
       <c r="Q80" s="82" t="str">
         <f>IF(K80&gt;=8.5,"🟢 ALTO",IF(K80&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
@@ -35370,7 +35394,7 @@
       </c>
     </row>
     <row r="82" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="126" t="s">
+      <c r="A82" s="172" t="s">
         <v>352</v>
       </c>
       <c r="B82" s="101"/>
@@ -35478,31 +35502,31 @@
     </row>
     <row r="86" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="127" t="s">
+      <c r="A87" s="173" t="s">
         <v>344</v>
       </c>
       <c r="B87" s="101"/>
-      <c r="C87" s="172" t="s">
+      <c r="C87" s="118" t="s">
         <v>345</v>
       </c>
       <c r="D87" s="101"/>
-      <c r="E87" s="123" t="s">
+      <c r="E87" s="169" t="s">
         <v>346</v>
       </c>
       <c r="F87" s="101"/>
-      <c r="G87" s="149" t="s">
+      <c r="G87" s="147" t="s">
         <v>347</v>
       </c>
       <c r="H87" s="101"/>
-      <c r="I87" s="150" t="s">
+      <c r="I87" s="148" t="s">
         <v>348</v>
       </c>
       <c r="J87" s="101"/>
-      <c r="K87" s="171" t="s">
+      <c r="K87" s="117" t="s">
         <v>349</v>
       </c>
       <c r="L87" s="101"/>
-      <c r="M87" s="147" t="s">
+      <c r="M87" s="144" t="s">
         <v>350</v>
       </c>
       <c r="N87" s="101"/>
@@ -35512,7 +35536,7 @@
       <c r="P87" s="101"/>
     </row>
     <row r="88" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="117" t="str">
+      <c r="A88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AN$4:AN$71),'Watchlist Ratings'!AN$4:AN$71,0))</f>
         <v>CSU</v>
       </c>
@@ -35522,74 +35546,74 @@
         <v>CSU</v>
       </c>
       <c r="D88" s="101"/>
-      <c r="E88" s="117" t="str">
+      <c r="E88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!BC$4:BC$71),'Watchlist Ratings'!BC$4:BC$71,0))</f>
         <v>NVDA</v>
       </c>
       <c r="F88" s="101"/>
-      <c r="G88" s="117" t="str">
+      <c r="G88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!K$4:K$71),'Watchlist Ratings'!K$4:K$71,0))</f>
         <v>VEEV</v>
       </c>
       <c r="H88" s="101"/>
-      <c r="I88" s="117" t="str">
+      <c r="I88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!L$4:L$71),'Watchlist Ratings'!L$4:L$71,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J88" s="101"/>
-      <c r="K88" s="117" t="str">
+      <c r="K88" s="145" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AM$4:AM$71),'Watchlist Ratings'!AM$4:AM$71,0))</f>
         <v>DSGX</v>
       </c>
       <c r="L88" s="101"/>
-      <c r="M88" s="117" t="str">
+      <c r="M88" s="145" t="str">
         <f t="array" aca="1" ref="M88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64)),IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64),0))</f>
         <v>CHKP</v>
       </c>
       <c r="N88" s="101"/>
-      <c r="O88" s="117" t="str">
+      <c r="O88" s="145" t="str">
         <f t="array" aca="1" ref="O88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64),'Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64,0))</f>
         <v>OTLY</v>
       </c>
       <c r="P88" s="101"/>
     </row>
     <row r="89" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="146">
+      <c r="A89" s="143">
         <f>MAX('Watchlist Ratings'!AN$4:AN$71)</f>
         <v>8.4499999999999993</v>
       </c>
       <c r="B89" s="101"/>
-      <c r="C89" s="116">
+      <c r="C89" s="150">
         <f ca="1">MAX('Watchlist Ratings'!BM$4:BM$64)</f>
         <v>0.46257448883098218</v>
       </c>
       <c r="D89" s="101"/>
-      <c r="E89" s="116">
+      <c r="E89" s="150">
         <f>MAX('Watchlist Ratings'!BC$4:BC$71)</f>
         <v>0.83333333333333326</v>
       </c>
       <c r="F89" s="101"/>
-      <c r="G89" s="110" t="str">
+      <c r="G89" s="149" t="str">
         <f>MAX('Watchlist Ratings'!K$4:K$71)&amp;"/8"</f>
         <v>8/8</v>
       </c>
       <c r="H89" s="101"/>
-      <c r="I89" s="110" t="str">
+      <c r="I89" s="149" t="str">
         <f>MAX('Watchlist Ratings'!L$4:L$71)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J89" s="101"/>
-      <c r="K89" s="115">
+      <c r="K89" s="176">
         <f>MAX('Watchlist Ratings'!AM$4:AM$71)</f>
         <v>8.7100000000000009</v>
       </c>
       <c r="L89" s="101"/>
-      <c r="M89" s="110" t="str">
+      <c r="M89" s="149" t="str">
         <f t="array" aca="1" ref="M89" ca="1">MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64))&amp;"x"</f>
         <v>7.94399332153846x</v>
       </c>
       <c r="N89" s="101"/>
-      <c r="O89" s="110">
+      <c r="O89" s="149">
         <f t="array" aca="1" ref="O89" ca="1">MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64)</f>
         <v>2.4981957482457289</v>
       </c>
@@ -35597,7 +35621,7 @@
     </row>
     <row r="90" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="166" t="s">
+      <c r="A91" s="110" t="s">
         <v>352</v>
       </c>
       <c r="B91" s="101"/>
@@ -35619,6 +35643,76 @@
     </row>
   </sheetData>
   <mergeCells count="86">
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="J72:Q72"/>
+    <mergeCell ref="L40:R40"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="O88:P88"/>
+    <mergeCell ref="J42:Q42"/>
+    <mergeCell ref="O89:P89"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="A82:Q82"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="O80:P80"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A24:R24"/>
+    <mergeCell ref="O78:P78"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="G88:H88"/>
+    <mergeCell ref="I88:J88"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="E89:F89"/>
+    <mergeCell ref="G89:H89"/>
+    <mergeCell ref="A85:Q85"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="J62:Q62"/>
+    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="E88:F88"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="A76:Q76"/>
+    <mergeCell ref="O79:P79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A91:Q91"/>
     <mergeCell ref="I78:J78"/>
     <mergeCell ref="A1:L1"/>
@@ -35635,76 +35729,6 @@
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="A76:Q76"/>
-    <mergeCell ref="O79:P79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="M87:N87"/>
-    <mergeCell ref="G88:H88"/>
-    <mergeCell ref="I88:J88"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="M89:N89"/>
-    <mergeCell ref="E89:F89"/>
-    <mergeCell ref="G89:H89"/>
-    <mergeCell ref="A85:Q85"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="J62:Q62"/>
-    <mergeCell ref="O87:P87"/>
-    <mergeCell ref="C88:D88"/>
-    <mergeCell ref="E88:F88"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A24:R24"/>
-    <mergeCell ref="O78:P78"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="A82:Q82"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="O80:P80"/>
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="J72:Q72"/>
-    <mergeCell ref="L40:R40"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="O88:P88"/>
-    <mergeCell ref="J42:Q42"/>
-    <mergeCell ref="O89:P89"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:F22">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -35747,7 +35771,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -38357,6 +38381,74 @@
         <v>696</v>
       </c>
     </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>305</v>
+      </c>
+      <c r="B154" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C154" t="s">
+        <v>697</v>
+      </c>
+      <c r="D154" t="s">
+        <v>698</v>
+      </c>
+      <c r="E154" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>311</v>
+      </c>
+      <c r="B155" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C155" t="s">
+        <v>700</v>
+      </c>
+      <c r="D155" t="s">
+        <v>698</v>
+      </c>
+      <c r="E155" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>315</v>
+      </c>
+      <c r="B156" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C156" t="s">
+        <v>672</v>
+      </c>
+      <c r="D156" t="s">
+        <v>698</v>
+      </c>
+      <c r="E156" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>319</v>
+      </c>
+      <c r="B157" s="97">
+        <v>46256</v>
+      </c>
+      <c r="C157" t="s">
+        <v>703</v>
+      </c>
+      <c r="D157" t="s">
+        <v>698</v>
+      </c>
+      <c r="E157" t="s">
+        <v>704</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Cosas Roger\BOLSA E INVERSIÓN\repos\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE73480-7667-4FE2-A271-F657789D3504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D54772-2AA0-4AD2-AA0F-0DB6FD9DACA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5876,155 +5876,33 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6042,14 +5920,136 @@
     <xf numFmtId="0" fontId="15" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6848,7 +6848,7 @@
                   <c:v>0.27406080160124957</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.24224417295338063</c:v>
+                  <c:v>0.28381894079882097</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1.9692117436700851E-2</c:v>
@@ -17059,26 +17059,26 @@
         <v>0.12993869883637732</v>
       </c>
       <c r="BH7" s="24">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BI7" s="24">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BJ7" s="25">
         <f t="shared" ca="1" si="17"/>
-        <v>33.104736501877106</v>
+        <v>45.66736611995114</v>
       </c>
       <c r="BK7" s="25">
         <f t="shared" ca="1" si="18"/>
-        <v>99.279542724768191</v>
+        <v>113.25229463500978</v>
       </c>
       <c r="BL7" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-4.5069756479004019E-2</v>
+        <v>1.8391612561389437E-2</v>
       </c>
       <c r="BM7" s="23">
         <f t="shared" ca="1" si="20"/>
-        <v>0.24224417295338063</v>
+        <v>0.28381894079882097</v>
       </c>
       <c r="BN7" s="97">
         <v>46256</v>
@@ -32360,7 +32360,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="168" t="s">
         <v>257</v>
       </c>
       <c r="B1" s="101"/>
@@ -32382,130 +32382,130 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="129" t="s">
+      <c r="A2" s="156" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="157"/>
+      <c r="H2" s="157"/>
+      <c r="I2" s="157"/>
+      <c r="J2" s="157"/>
+      <c r="K2" s="157"/>
+      <c r="L2" s="157"/>
     </row>
     <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="135" t="s">
+      <c r="A3" s="161" t="s">
         <v>259</v>
       </c>
-      <c r="B3" s="124"/>
-      <c r="C3" s="156" t="s">
+      <c r="B3" s="129"/>
+      <c r="C3" s="128" t="s">
         <v>260</v>
       </c>
-      <c r="D3" s="124"/>
-      <c r="E3" s="157" t="s">
+      <c r="D3" s="129"/>
+      <c r="E3" s="130" t="s">
         <v>261</v>
       </c>
-      <c r="F3" s="124"/>
-      <c r="G3" s="123" t="s">
+      <c r="F3" s="129"/>
+      <c r="G3" s="176" t="s">
         <v>262</v>
       </c>
-      <c r="H3" s="124"/>
-      <c r="I3" s="125" t="s">
+      <c r="H3" s="129"/>
+      <c r="I3" s="177" t="s">
         <v>263</v>
       </c>
-      <c r="J3" s="124"/>
-      <c r="K3" s="161" t="s">
+      <c r="J3" s="129"/>
+      <c r="K3" s="140" t="s">
         <v>264</v>
       </c>
-      <c r="L3" s="162"/>
+      <c r="L3" s="141"/>
     </row>
     <row r="4" spans="1:47" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="142">
+      <c r="A4" s="165">
         <f ca="1">COUNTA('Watchlist Ratings'!B4:B71)</f>
         <v>68</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="158">
+      <c r="B4" s="135"/>
+      <c r="C4" s="136">
         <f>ROUND(AVERAGE('Watchlist Ratings'!AN4:AN71),2)</f>
         <v>5.98</v>
       </c>
-      <c r="D4" s="127"/>
-      <c r="E4" s="128" t="str">
+      <c r="D4" s="135"/>
+      <c r="E4" s="137" t="str">
         <f>TEXT(AVERAGE('Watchlist Ratings'!BC4:BC71),"0.0%")</f>
         <v>20.9%</v>
       </c>
-      <c r="F4" s="127"/>
-      <c r="G4" s="128" t="str">
+      <c r="F4" s="135"/>
+      <c r="G4" s="137" t="str">
         <f ca="1">TEXT(AVERAGE('Watchlist Ratings'!AW4:AW71),"0.0x")</f>
         <v>37.5x</v>
       </c>
-      <c r="H4" s="127"/>
-      <c r="I4" s="128">
+      <c r="H4" s="135"/>
+      <c r="I4" s="137">
         <f ca="1">COUNTIF('Watchlist Ratings'!BM4:BM71,"&gt;0")</f>
         <v>58</v>
       </c>
-      <c r="J4" s="127"/>
-      <c r="K4" s="113">
+      <c r="J4" s="135"/>
+      <c r="K4" s="169">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&gt;7.5")</f>
         <v>16</v>
       </c>
-      <c r="L4" s="114"/>
+      <c r="L4" s="143"/>
     </row>
     <row r="5" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="138" t="s">
+      <c r="A5" s="163" t="s">
         <v>265</v>
       </c>
-      <c r="B5" s="127"/>
-      <c r="C5" s="126" t="s">
+      <c r="B5" s="135"/>
+      <c r="C5" s="134" t="s">
         <v>266</v>
       </c>
-      <c r="D5" s="127"/>
-      <c r="E5" s="126" t="s">
+      <c r="D5" s="135"/>
+      <c r="E5" s="134" t="s">
         <v>267</v>
       </c>
-      <c r="F5" s="127"/>
-      <c r="G5" s="126" t="s">
+      <c r="F5" s="135"/>
+      <c r="G5" s="134" t="s">
         <v>268</v>
       </c>
-      <c r="H5" s="127"/>
-      <c r="I5" s="126" t="s">
+      <c r="H5" s="135"/>
+      <c r="I5" s="134" t="s">
         <v>269</v>
       </c>
-      <c r="J5" s="127"/>
-      <c r="K5" s="163" t="s">
+      <c r="J5" s="135"/>
+      <c r="K5" s="142" t="s">
         <v>270</v>
       </c>
-      <c r="L5" s="114"/>
+      <c r="L5" s="143"/>
     </row>
     <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="173" t="s">
         <v>271</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="136" t="s">
+      <c r="B6" s="133"/>
+      <c r="C6" s="132" t="s">
         <v>272</v>
       </c>
-      <c r="D6" s="120"/>
-      <c r="E6" s="136" t="s">
+      <c r="D6" s="133"/>
+      <c r="E6" s="132" t="s">
         <v>273</v>
       </c>
-      <c r="F6" s="120"/>
-      <c r="G6" s="122" t="s">
+      <c r="F6" s="133"/>
+      <c r="G6" s="175" t="s">
         <v>274</v>
       </c>
-      <c r="H6" s="120"/>
-      <c r="I6" s="136" t="s">
+      <c r="H6" s="133"/>
+      <c r="I6" s="132" t="s">
         <v>275</v>
       </c>
-      <c r="J6" s="120"/>
-      <c r="K6" s="159" t="s">
+      <c r="J6" s="133"/>
+      <c r="K6" s="138" t="s">
         <v>276</v>
       </c>
-      <c r="L6" s="160"/>
+      <c r="L6" s="139"/>
       <c r="O6" t="s">
         <v>277</v>
       </c>
@@ -32685,7 +32685,7 @@
       </c>
     </row>
     <row r="8" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="121" t="s">
+      <c r="A8" s="174" t="s">
         <v>300</v>
       </c>
       <c r="B8" s="101"/>
@@ -33123,7 +33123,7 @@
       </c>
       <c r="Q11" s="23">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.24224417295338063</v>
+        <v>0.28381894079882097</v>
       </c>
       <c r="S11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -33159,11 +33159,11 @@
       </c>
       <c r="AB11">
         <f ca="1">'Watchlist Ratings'!BL7</f>
-        <v>-4.5069756479004019E-2</v>
+        <v>1.8391612561389437E-2</v>
       </c>
       <c r="AC11">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.24224417295338063</v>
+        <v>0.28381894079882097</v>
       </c>
       <c r="AE11" t="s">
         <v>310</v>
@@ -34513,7 +34513,7 @@
       </c>
     </row>
     <row r="24" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="167" t="s">
+      <c r="A24" s="145" t="s">
         <v>327</v>
       </c>
       <c r="B24" s="101"/>
@@ -34589,7 +34589,7 @@
     <row r="38" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L40" s="175"/>
+      <c r="L40" s="114"/>
       <c r="M40" s="101"/>
       <c r="N40" s="101"/>
       <c r="O40" s="101"/>
@@ -34606,7 +34606,7 @@
       <c r="Q41" s="57"/>
     </row>
     <row r="42" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J42" s="177"/>
+      <c r="J42" s="118"/>
       <c r="K42" s="101"/>
       <c r="L42" s="101"/>
       <c r="M42" s="101"/>
@@ -34691,7 +34691,7 @@
     <row r="60" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="61" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="62" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="146" t="s">
+      <c r="A62" s="148" t="s">
         <v>328</v>
       </c>
       <c r="B62" s="101"/>
@@ -34971,27 +34971,27 @@
       </c>
       <c r="C67" s="64">
         <f ca="1">'Watchlist Ratings'!BJ7</f>
-        <v>33.104736501877106</v>
+        <v>45.66736611995114</v>
       </c>
       <c r="D67" s="64">
         <f ca="1">'Watchlist Ratings'!BK7</f>
-        <v>99.279542724768191</v>
+        <v>113.25229463500978</v>
       </c>
       <c r="E67" s="65">
         <f ca="1">'Watchlist Ratings'!BL7</f>
-        <v>-4.5069756479004019E-2</v>
+        <v>1.8391612561389437E-2</v>
       </c>
       <c r="F67" s="65">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.24224417295338063</v>
+        <v>0.28381894079882097</v>
       </c>
       <c r="G67" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.28731392943238465</v>
+        <v>0.26542732823743154</v>
       </c>
       <c r="H67" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>🟡 HOLD</v>
+        <v>🟢 BUY</v>
       </c>
       <c r="J67" s="63" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -35291,29 +35291,29 @@
       </c>
     </row>
     <row r="72" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="164" t="str">
+      <c r="A72" s="144" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="B72" s="165"/>
-      <c r="C72" s="165"/>
-      <c r="D72" s="165"/>
-      <c r="E72" s="165"/>
-      <c r="F72" s="165"/>
-      <c r="G72" s="165"/>
-      <c r="H72" s="165"/>
-      <c r="I72" s="166"/>
-      <c r="J72" s="174" t="str">
+      <c r="B72" s="112"/>
+      <c r="C72" s="112"/>
+      <c r="D72" s="112"/>
+      <c r="E72" s="112"/>
+      <c r="F72" s="112"/>
+      <c r="G72" s="112"/>
+      <c r="H72" s="112"/>
+      <c r="I72" s="113"/>
+      <c r="J72" s="111" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="K72" s="165"/>
-      <c r="L72" s="165"/>
-      <c r="M72" s="165"/>
-      <c r="N72" s="165"/>
-      <c r="O72" s="165"/>
-      <c r="P72" s="165"/>
-      <c r="Q72" s="166"/>
+      <c r="K72" s="112"/>
+      <c r="L72" s="112"/>
+      <c r="M72" s="112"/>
+      <c r="N72" s="112"/>
+      <c r="O72" s="112"/>
+      <c r="P72" s="112"/>
+      <c r="Q72" s="113"/>
     </row>
     <row r="73" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="68" t="str">
@@ -35510,7 +35510,7 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="139" t="s">
+      <c r="A76" s="164" t="s">
         <v>341</v>
       </c>
       <c r="B76" s="101"/>
@@ -35540,23 +35540,23 @@
       </c>
       <c r="C77" s="80">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,59,FALSE())</f>
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="D77" s="80">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,60,FALSE())</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E77" s="81">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,61,FALSE())</f>
-        <v>33.104736501877106</v>
+        <v>45.66736611995114</v>
       </c>
       <c r="F77" s="81">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.24224417295338063</v>
+        <v>0.28381894079882097</v>
       </c>
       <c r="G77" s="81">
         <f ca="1">F77-E77</f>
-        <v>-32.862492328923729</v>
+        <v>-45.383547179152316</v>
       </c>
       <c r="H77" s="79" t="str">
         <f ca="1">IF(E77&gt;0,"🟢 BUY",IF(E77&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -35598,127 +35598,127 @@
       <c r="A78" s="131" t="s">
         <v>342</v>
       </c>
-      <c r="B78" s="116"/>
-      <c r="C78" s="115" t="s">
+      <c r="B78" s="120"/>
+      <c r="C78" s="170" t="s">
         <v>343</v>
       </c>
-      <c r="D78" s="116"/>
-      <c r="E78" s="134" t="s">
+      <c r="D78" s="120"/>
+      <c r="E78" s="160" t="s">
         <v>344</v>
       </c>
-      <c r="F78" s="116"/>
-      <c r="G78" s="134" t="s">
+      <c r="F78" s="120"/>
+      <c r="G78" s="160" t="s">
         <v>345</v>
       </c>
-      <c r="H78" s="116"/>
-      <c r="I78" s="111" t="s">
+      <c r="H78" s="120"/>
+      <c r="I78" s="167" t="s">
         <v>346</v>
       </c>
       <c r="J78" s="101"/>
       <c r="K78" s="131" t="s">
         <v>347</v>
       </c>
-      <c r="L78" s="116"/>
+      <c r="L78" s="120"/>
       <c r="M78" s="131" t="s">
         <v>348</v>
       </c>
-      <c r="N78" s="116"/>
+      <c r="N78" s="120"/>
       <c r="O78" s="131" t="s">
         <v>349</v>
       </c>
-      <c r="P78" s="116"/>
+      <c r="P78" s="120"/>
       <c r="Q78" s="82" t="str">
         <f>IF(K78&gt;=8.5,"🟢 ALTO",IF(K78&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="140" t="str">
+      <c r="A79" s="119" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AN:AN),'Watchlist Ratings'!AN:AN,0))</f>
         <v>CSU</v>
       </c>
-      <c r="B79" s="116"/>
-      <c r="C79" s="168" t="str">
+      <c r="B79" s="120"/>
+      <c r="C79" s="121" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM:BM),'Watchlist Ratings'!BM:BM,0))</f>
         <v>KSPI</v>
       </c>
-      <c r="D79" s="116"/>
-      <c r="E79" s="141" t="str">
+      <c r="D79" s="120"/>
+      <c r="E79" s="122" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BC:BC),'Watchlist Ratings'!BC:BC,0))</f>
         <v>NVDA</v>
       </c>
-      <c r="F79" s="116"/>
-      <c r="G79" s="141" t="str">
+      <c r="F79" s="120"/>
+      <c r="G79" s="122" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!K:K),'Watchlist Ratings'!K:K,0))</f>
         <v>VEEV</v>
       </c>
-      <c r="H79" s="116"/>
+      <c r="H79" s="120"/>
       <c r="I79" s="152" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!L:L),'Watchlist Ratings'!L:L,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J79" s="101"/>
-      <c r="K79" s="140" t="str">
+      <c r="K79" s="119" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AM:AM),'Watchlist Ratings'!AM:AM,0))</f>
         <v>DSGX</v>
       </c>
-      <c r="L79" s="116"/>
-      <c r="M79" s="140" t="str">
+      <c r="L79" s="120"/>
+      <c r="M79" s="119" t="str">
         <f t="array" aca="1" ref="M79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MIN('Watchlist Ratings'!AW4:AW64),'Watchlist Ratings'!AW4:AW64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="N79" s="116"/>
-      <c r="O79" s="140" t="str">
+      <c r="N79" s="120"/>
+      <c r="O79" s="119" t="str">
         <f t="array" aca="1" ref="O79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),'Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="P79" s="116"/>
+      <c r="P79" s="120"/>
       <c r="Q79" s="79" t="str">
         <f ca="1">IF(K79&gt;=8.5,"🟢 ALTO",IF(K79&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="132">
+      <c r="A80" s="158">
         <f>MAX('Watchlist Ratings'!AN:AN)</f>
         <v>8.4499999999999993</v>
       </c>
-      <c r="B80" s="116"/>
-      <c r="C80" s="133">
+      <c r="B80" s="120"/>
+      <c r="C80" s="159">
         <f ca="1">MAX('Watchlist Ratings'!BM:BM)</f>
         <v>0.46183288973934067</v>
       </c>
-      <c r="D80" s="116"/>
-      <c r="E80" s="137">
+      <c r="D80" s="120"/>
+      <c r="E80" s="162">
         <f>MAX('Watchlist Ratings'!BC:BC)</f>
         <v>0.83333333333333326</v>
       </c>
-      <c r="F80" s="116"/>
-      <c r="G80" s="137" t="str">
+      <c r="F80" s="120"/>
+      <c r="G80" s="162" t="str">
         <f>MAX('Watchlist Ratings'!K:K)&amp;"/8"</f>
         <v>8/8</v>
       </c>
-      <c r="H80" s="116"/>
-      <c r="I80" s="170" t="str">
+      <c r="H80" s="120"/>
+      <c r="I80" s="124" t="str">
         <f>MAX('Watchlist Ratings'!L:L)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J80" s="101"/>
-      <c r="K80" s="171">
+      <c r="K80" s="125">
         <f>MAX('Watchlist Ratings'!AM:AM)</f>
         <v>8.7100000000000009</v>
       </c>
-      <c r="L80" s="116"/>
-      <c r="M80" s="171" t="str">
+      <c r="L80" s="120"/>
+      <c r="M80" s="125" t="str">
         <f ca="1">MIN('Watchlist Ratings'!AW4:AW64)&amp;"x"</f>
         <v>-18.7185554x</v>
       </c>
-      <c r="N80" s="116"/>
-      <c r="O80" s="171" t="str">
+      <c r="N80" s="120"/>
+      <c r="O80" s="125" t="str">
         <f t="array" aca="1" ref="O80" ca="1">TEXT(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),"0.0%")</f>
         <v>249.0%</v>
       </c>
-      <c r="P80" s="116"/>
+      <c r="P80" s="120"/>
       <c r="Q80" s="82" t="str">
         <f>IF(K80&gt;=8.5,"🟢 ALTO",IF(K80&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
@@ -35789,7 +35789,7 @@
       </c>
     </row>
     <row r="82" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="172" t="s">
+      <c r="A82" s="126" t="s">
         <v>350</v>
       </c>
       <c r="B82" s="101"/>
@@ -35897,31 +35897,31 @@
     </row>
     <row r="86" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="173" t="s">
+      <c r="A87" s="127" t="s">
         <v>342</v>
       </c>
       <c r="B87" s="101"/>
-      <c r="C87" s="118" t="s">
+      <c r="C87" s="172" t="s">
         <v>343</v>
       </c>
       <c r="D87" s="101"/>
-      <c r="E87" s="169" t="s">
+      <c r="E87" s="123" t="s">
         <v>344</v>
       </c>
       <c r="F87" s="101"/>
-      <c r="G87" s="147" t="s">
+      <c r="G87" s="149" t="s">
         <v>345</v>
       </c>
       <c r="H87" s="101"/>
-      <c r="I87" s="148" t="s">
+      <c r="I87" s="150" t="s">
         <v>346</v>
       </c>
       <c r="J87" s="101"/>
-      <c r="K87" s="117" t="s">
+      <c r="K87" s="171" t="s">
         <v>347</v>
       </c>
       <c r="L87" s="101"/>
-      <c r="M87" s="144" t="s">
+      <c r="M87" s="147" t="s">
         <v>348</v>
       </c>
       <c r="N87" s="101"/>
@@ -35931,7 +35931,7 @@
       <c r="P87" s="101"/>
     </row>
     <row r="88" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="145" t="str">
+      <c r="A88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AN$4:AN$71),'Watchlist Ratings'!AN$4:AN$71,0))</f>
         <v>CSU</v>
       </c>
@@ -35941,74 +35941,74 @@
         <v>KSPI</v>
       </c>
       <c r="D88" s="101"/>
-      <c r="E88" s="145" t="str">
+      <c r="E88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!BC$4:BC$71),'Watchlist Ratings'!BC$4:BC$71,0))</f>
         <v>NVDA</v>
       </c>
       <c r="F88" s="101"/>
-      <c r="G88" s="145" t="str">
+      <c r="G88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!K$4:K$71),'Watchlist Ratings'!K$4:K$71,0))</f>
         <v>VEEV</v>
       </c>
       <c r="H88" s="101"/>
-      <c r="I88" s="145" t="str">
+      <c r="I88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!L$4:L$71),'Watchlist Ratings'!L$4:L$71,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J88" s="101"/>
-      <c r="K88" s="145" t="str">
+      <c r="K88" s="117" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AM$4:AM$71),'Watchlist Ratings'!AM$4:AM$71,0))</f>
         <v>DSGX</v>
       </c>
       <c r="L88" s="101"/>
-      <c r="M88" s="145" t="str">
+      <c r="M88" s="117" t="str">
         <f t="array" aca="1" ref="M88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64)),IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64),0))</f>
         <v>CHKP</v>
       </c>
       <c r="N88" s="101"/>
-      <c r="O88" s="145" t="str">
+      <c r="O88" s="117" t="str">
         <f t="array" aca="1" ref="O88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64),'Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64,0))</f>
         <v>OTLY</v>
       </c>
       <c r="P88" s="101"/>
     </row>
     <row r="89" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="143">
+      <c r="A89" s="146">
         <f>MAX('Watchlist Ratings'!AN$4:AN$71)</f>
         <v>8.4499999999999993</v>
       </c>
       <c r="B89" s="101"/>
-      <c r="C89" s="150">
+      <c r="C89" s="116">
         <f ca="1">MAX('Watchlist Ratings'!BM$4:BM$64)</f>
         <v>0.46183288973934067</v>
       </c>
       <c r="D89" s="101"/>
-      <c r="E89" s="150">
+      <c r="E89" s="116">
         <f>MAX('Watchlist Ratings'!BC$4:BC$71)</f>
         <v>0.83333333333333326</v>
       </c>
       <c r="F89" s="101"/>
-      <c r="G89" s="149" t="str">
+      <c r="G89" s="110" t="str">
         <f>MAX('Watchlist Ratings'!K$4:K$71)&amp;"/8"</f>
         <v>8/8</v>
       </c>
       <c r="H89" s="101"/>
-      <c r="I89" s="149" t="str">
+      <c r="I89" s="110" t="str">
         <f>MAX('Watchlist Ratings'!L$4:L$71)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J89" s="101"/>
-      <c r="K89" s="176">
+      <c r="K89" s="115">
         <f>MAX('Watchlist Ratings'!AM$4:AM$71)</f>
         <v>8.7100000000000009</v>
       </c>
       <c r="L89" s="101"/>
-      <c r="M89" s="149" t="str">
+      <c r="M89" s="110" t="str">
         <f t="array" aca="1" ref="M89" ca="1">MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64))&amp;"x"</f>
         <v>7.9455641x</v>
       </c>
       <c r="N89" s="101"/>
-      <c r="O89" s="149">
+      <c r="O89" s="110">
         <f t="array" aca="1" ref="O89" ca="1">MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64)</f>
         <v>2.4903577795625393</v>
       </c>
@@ -36016,7 +36016,7 @@
     </row>
     <row r="90" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="110" t="s">
+      <c r="A91" s="166" t="s">
         <v>350</v>
       </c>
       <c r="B91" s="101"/>
@@ -36038,44 +36038,38 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="J72:Q72"/>
-    <mergeCell ref="L40:R40"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="O88:P88"/>
-    <mergeCell ref="J42:Q42"/>
-    <mergeCell ref="O89:P89"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="A82:Q82"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="O80:P80"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A24:R24"/>
-    <mergeCell ref="O78:P78"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A91:Q91"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="A76:Q76"/>
+    <mergeCell ref="O79:P79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="M87:N87"/>
     <mergeCell ref="G88:H88"/>
@@ -36092,38 +36086,44 @@
     <mergeCell ref="O87:P87"/>
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="E88:F88"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="A76:Q76"/>
-    <mergeCell ref="O79:P79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A91:Q91"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A24:R24"/>
+    <mergeCell ref="O78:P78"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="A82:Q82"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="O80:P80"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="J72:Q72"/>
+    <mergeCell ref="L40:R40"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="O88:P88"/>
+    <mergeCell ref="J42:Q42"/>
+    <mergeCell ref="O89:P89"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:F22">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Cosas Roger\BOLSA E INVERSIÓN\repos\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360FB1B9-4543-4D70-98FF-6C3987BA9D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1A780B-12A6-4BD2-8FAF-83690C08BF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2463,7 +2463,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="800">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -2835,12 +2835,6 @@
     <t>09/06/2026</t>
   </si>
   <si>
-    <t>252</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
     <t>2026-04-26</t>
   </si>
   <si>
@@ -2883,9 +2877,6 @@
     <t>27/08/2026</t>
   </si>
   <si>
-    <t>3,033</t>
-  </si>
-  <si>
     <t>06/08/2026</t>
   </si>
   <si>
@@ -2991,12 +2982,6 @@
     <t>4,044</t>
   </si>
   <si>
-    <t>186</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
     <t>08/07/2026</t>
   </si>
   <si>
@@ -3018,9 +3003,6 @@
     <t>405</t>
   </si>
   <si>
-    <t>114</t>
-  </si>
-  <si>
     <t>04/11/2026</t>
   </si>
   <si>
@@ -4854,10 +4836,70 @@
     <t>Somero no ha publicado el semestre: los resultados del 1S2026 son el 8-sep-2026, la fecha que ya tenia la hoja. AVISO PARA ENTONCES: los ingresos LTM de la hoja son 64,9 M$ y la actualizacion de trading de julio situa las expectativas de mercado para 2026 en 86,0 M$ de ingresos y 15,9 M$ de EBITDA ajustado; la cifra de la hoja parece corta. Su caso bajista asume el FCF creciendo un 6,5% anual para un ciclico puro de construccion no residencial en EE.UU., lo que tambien habra que endurecer.</t>
   </si>
   <si>
-    <t>Filas normalizadas a 25-ago-2026 (doce): MSFT (5), COST (8), AMZN (13), DNP (23), META (28), GOOG (32), NVDA (38), TSM (40), CPR (44), NFLX (50), TREX (55) e IPCO (63). El resto usa FCF reportado. NVDA y NFLX cumplen el disparador por poco (efecto del 2,8% y el 3,7%) y se aplican igual para no elegir a dedo. EXCEPCIONES documentadas: TFPM (49) lo activa mecanicamente pero NO se normaliza, porque ese capex son compras de streams -M&amp;A de crecimiento- y en una royalty el capex de sostenimiento es cero; EVD (20) tampoco, porque el D&amp;A de la fuente es implausible y el capex derivado no es fiable.</t>
-  </si>
-  <si>
     <t>Estado a 25-ago-2026: los cuatro pasos hechos en AMZN, MSFT, CSU, BN, COST, LIFCO B, RAA y LOTB (22-ago); en NTO, ABNB, DNP, LR, STMN, KKR, KRX, SPOT, CPR, TFPM, TREX y SGO (25-ago, resultados nuevos); y en COST, DSGX, ZS, SU, ITX, EVD, VLTO, JDG, META, GOOG, ABBNE, GRMN, NVDA, TSM, SIKA, CHKP, NFLX, NKE, IP, RBT y ROKO B (25-ago, refresco de LTM). Con los pasos 1-3 hechos y el 4 pendiente a proposito: FERG, IPCO, NET y CRWD (estas dos con EV/FCF de 303x y 127x, los multiplos de salida no pueden capturar el precio). Pendientes de publicar: VEEV y NVDA el 26-ago, EVD y S el 27-ago, SOM el 8-sep, DSGX el 10-sep, JDG el 22-sep.</t>
+  </si>
+  <si>
+    <t>T (R2 Financials)</t>
+  </si>
+  <si>
+    <t>Deep dive 25-ago-2026</t>
+  </si>
+  <si>
+    <t>Cloudflare. R2 Financials 8 -&gt; 7. El 8 se puso el 21-ago justificandolo con un ROIC del 1,4% que no esta en las cuentas: en GAAP el margen operativo LTM es -7,8% y el ROIC -5,1%. Aun quitando los hasta 165 M$ de cargos de reestructuracion (125 en caja, 35 en SBC), el margen seria -2,6%. El SBC son 508 M$, el 20% de los ingresos, y ES el FCF. A favor: ingresos +36% en el Q2 y caja neta de 634 M$. A vigilar: el recorte del 20% de la plantilla del 7-may es una apuesta por un modelo operativo agentic-AI que toca soporte y no la fuerza comercial. VALORACION: con un EV/FCF de 285x, para que el caso alcista solo EMPATE con el precio de hoy hace falta un FCF a 5 anos de 3.253 M$, un 56,9% anual. Los multiplos de salida (20x/30x) ya son los mas altos del libro, los mismos que Microsoft y Costco. No es un problema de multiplo: el precio esta fuera del marco.</t>
+  </si>
+  <si>
+    <t>CrowdStrike. R2 Potential 15 -&gt; 16. Hecho nuevo del Q1 FY2027 (3-jun-2026): ARR 5.510 M$ +24%, net new ARR record de 256 M$ +32%, ingresos +26% con CUATRO trimestres consecutivos de aceleracion y guia de net new ARR subida 520 pb. La recuperacion del apagon de 2024 esta completa y la consolidacion de plataforma funciona. FCF record de 468 M$ en el trimestre, 1.510 LTM con margen del 29,7%. En GAAP sigue en perdidas (-160 M$ operativo) por el SBC; R2 Financials se deja en 12 porque un margen FCF del 29,7% lo justifica. VALORACION: EV/FCF de 121x. Para que el alcista empate hace falta un FCF a 5 anos de 6.098 M$, un 32,2% anual, que es justo lo que crece hoy el net new ARR: a diferencia de Cloudflare NO es imposible, pero exige que se cumpla el escenario bueno entero solo para no perder dinero.</t>
+  </si>
+  <si>
+    <t>T (R2 Financials); AH (R3 Financing Source); AP; AQ; AS; AT; AU; AV; AZ; BD; BF</t>
+  </si>
+  <si>
+    <t>SentinelOne. R2 Financials 6 -&gt; 7 y R3 Financing Source 0 -&gt; 1. Inflexion real en el Q1 FY2027 (28-may-2026): primer resultado operativo NON-GAAP positivo de su historia (+10,5 M$ frente a -3,9), guia de margen operativo FY27 del 10% (+650 pb), ARR 1.163 M$ +23% y net new ARR record de 44 M$ +55%. Ya no necesita levantar capital: 657 M$ de caja e inversiones a corto mas 156 a largo, sin deuda, y FCF LTM positivo de 62 M$. En contra: en GAAP el resultado operativo LTM es -301 M$, el 29% de los ingresos, y recortaron un 8% de plantilla. Financials corregidos: caja 1.100 -&gt; 657 (el 1.100 incluia inversiones a largo), ingresos 815 -&gt; 1.050, EBITDA 10 -&gt; -259, NOPAT -20 -&gt; -301. VALORACION: EV/FCF de 101x sobre una base de FCF de solo 62 M$. Para que el alcista empate hacen falta 241 M$ a cinco anos, un 31,2% anual, alcanzable con ingresos al 21% y el margen yendo del 6% al 15%. Es la unica de las tres de ciber cuyo caso alcista casi cuadra: -4%.</t>
+  </si>
+  <si>
+    <t>V (R2 Potential); AA (R2 Risks); AP; AQ; AS; AT; AU; AV; AZ; BD; BF</t>
+  </si>
+  <si>
+    <t>Mips AB. R2 Potential 10 -&gt; 12 y R2 Risks -12 -&gt; -13. El Q2 2026 (16-jul) cambia la tesis: ventas +72% (organico +42%), margen EBIT ajustado del 46,7% frente al 40,4% y sobre todo el segmento Safety +604% (organico +80%) por la compra de KOROYD y los cascos de ala completa. Deja de ser una historia de un solo ciclo (bici y nieve) y gana una segunda pata industrial: por eso sube Potential. Baja Risks porque aparece la primera grieta en el foso: pagan 3,25 M$ a BrainGuard para cerrar un pleito de infraccion de patente, con unos 35 MSEK de impacto en el Q3. En un negocio que ES una patente, perder un pleito no es un gasto, es informacion. Financials: aparece deuda de 331 MSEK (Koroyd) donde la hoja tenia cero, capital empleado 350 -&gt; 1.185 y el ROIC baja del 40,9% al 16,1%. VALORACION: EV/FCF 58,7x. Para empatar hace falta un 21,1% anual durante cinco anos; el alcista se fija en el 18%, ya agresivo para un licenciador de IP expuesto al ciclo del casco.</t>
+  </si>
+  <si>
+    <t>AF (R3 Capital Intensity); AP; AQ; AS; AT; AU; AV; AZ; BD; BF</t>
+  </si>
+  <si>
+    <t>Lotus Bakeries. R3 Capital Intensity 7 -&gt; 6. El 1S2026 (7-ago) confirma la calidad -ingresos 749,1 M EUR +14%, EBITDA subyacente 156,3 +20,9%, beneficio neto 98,1 +23,5%, Biscoff creciendo mas del 20% en VOLUMEN y no solo en precio, y la planta de Tailandia en la parte alta de las expectativas- y a la vez que el negocio se vuelve mas intensivo en capital: capex de 2026 y 2027 por encima de 250 M EUR combinados y compromiso de al menos 500 M EUR a cinco anos entre Mebane, Lembeke y Chonburi. El capex LTM (101,8) es 2,7 veces el D&amp;A (37,7). FCF NORMALIZADO: mantenimiento = max(37,7 ; 50,9) = 50,9 y FCF = 233,5 - 50,9 = 182,6 en vez de los 131,7 reportados. Financials corregidos: caja 100 -&gt; 274, deuda 200 -&gt; 409 (deuda neta 115,4, o sea 0,3x EBITDA), capital empleado 800 -&gt; 1.309. VALORACION: EV/FCF de 59,2x, la mas cara del libro entre las de calidad alta. El alcista se rebasa al 18% anual desde el negocio; para EMPATAR harian falta 433, un 18,8% anual. Lotus a este precio descuenta exactamente lo que esta entregando hoy, sin margen.</t>
+  </si>
+  <si>
+    <t>V (R2 Potential); AP; AQ; AS; AT; AU; AV; AZ; BD; BF</t>
+  </si>
+  <si>
+    <t>Monster Beverage. R2 Potential 11 -&gt; 12. Hecho nuevo del Q2 2026 (6-ago): ventas 2.540 M$ +20,2%, primera vez por encima de 2.500; margen bruto 55,9%; y sobre todo INTERNACIONAL 1.160 M$ +34,6%, ya el 46% del negocio frente al 41% de hace un ano. El motor de crecimiento ya no es Estados Unidos y eso alarga el recorrido. En contra: el segmento de alcohol cae un 15,2%, o sea que la diversificacion fuera de la bebida energetica no funciona. Split 2:1 el 11-ago. Financials corregidos: caja 4.201 -&gt; 3.419, aparece deuda de 93, FCF 1.800 -&gt; 2.100, capital empleado 5.164 -&gt; 9.665 (ROIC 22,3%). VALORACION: el EV/FCF baja de 50,5x a 43,7x con el dato correcto. Alcista rebasado al 14% anual desde el negocio; para empatar harian falta 4.171, un 14,7% anual. Se queda a un pelo, y la razon es el multiplo de salida alcista de 22x contra un EV/FCF de 43,7x: es la unica fila del grupo donde lo que rompe el caso es el multiplo y no el crecimiento.</t>
+  </si>
+  <si>
+    <t>AA (R2 Risks); AP; AQ; AS; AT; AU; AV; AZ; BD; BF</t>
+  </si>
+  <si>
+    <t>TFF Group. R2 Risks -13 -&gt; -14. El ejercicio cerrado el 30-abr-2026 (publicado el 16-jul) es un desplome: ingresos 312,75 M EUR frente a 425,43, un -26,5% publicado y -23,4% a tipo constante; EBITDA 48,2 -40%; beneficio neto 9,20 -71,1%, el 2,9% de las ventas; dividendo recortado de 0,50 a 0,40 EUR. La amplitud del ciclo es mayor de lo que asumia el rating. LO IMPORTANTE, Y ES BUENA NOTICIA: la fila estaba MAL. La caja real son 97,2 M EUR y no 25 (subio 17,5 en el ano) y el FCF LTM es 59,1 y no 25, porque al frenar la produccion liberan el circulante inmovilizado en madera. La deuda neta baja a 285,2 desde 314. Con los datos correctos el EV/FCF pasa de 28,1x a 11,0x y el FVE minimo DEJA DE SER NEGATIVO: ese defecto era un error de datos, no de formula. VALORACION: bajista -81% y alcista +180%. El bajista es tan duro porque el multiplo de salida de 6x es solo el 55% del actual, punitivo para un ciclico en el suelo. Ver la recomendacion de subirlo a 8x.</t>
+  </si>
+  <si>
+    <t>AE (R3 Risk of Disappearance); AP; AQ; AS; AT; AU; AV; AZ; BD; BF</t>
+  </si>
+  <si>
+    <t>Oatly. R3 Risk of Disappearance -10 -&gt; -12. La revision del 21-ago recogio bien la mejora operativa (Q2 del 22-jul: ingresos +15,2%, margen bruto 33,9%, adj EBITDA +0,4 M$ frente a -3,6, guia subida al 8-10%) pero no miro el balance en detalle. Al hacerlo: pasivo corriente de 574,9 M$ contra un activo total de 744, deuda de 549,1 contra 44,6 de caja, capital empleado de solo 169 y Altman Z de -1,9. El FCF LTM sigue negativo (-21,9) aunque mejorando desde -50. La operativa mejora de verdad; la estructura de capital es lo que puede matarla antes de que la mejora llegue. Financials corregidos: ingresos 830 -&gt; 925, EBITDA -10 -&gt; -13,6, NOPAT -100 -&gt; -49,2, capital empleado 650 -&gt; 169. VALORACION: el FVE minimo negativo NO es aqui un error de datos: con un FCF terminal cercano a cero y 504 M$ de deuda neta, en el caso bajista la accion vale cero. Lo que si es un defecto de formula es que la TIR lo exprese como -200% anual en vez de topar en -100%. BD se pone en 0 y BF se deja en 114.</t>
+  </si>
+  <si>
+    <t>AT (NOPAT); AU (EBITDA)</t>
+  </si>
+  <si>
+    <t>Metricas non-GAAP por indicacion de Roger</t>
+  </si>
+  <si>
+    <t>Brookfield. Se sustituyen las cifras de relleno por las metricas que la compania reporta y que son las que tienen sentido en una gestora: NOPAT 5.500 -&gt; 5.700, que es el DISTRIBUTABLE EARNINGS ANTES DE REALIZACIONES de los ultimos doce meses (2,39 $/accion), la parte recurrente y no grumosa; y EBITDA 15.000 -&gt; 5.700, porque en Brookfield no existe analogo de EBITDA y la columna AX debe leerse como EV / DE antes de realizaciones (19,5x). El FCF sigue en 6.200, el DE TOTAL incluyendo realizaciones (2,61 $/accion). El Q2 2026 fue record: DE antes de realizaciones 1.400 M$ +15% y DE total 1.500. AVISO: no se tocan caja ni deuda, que son de perimetro CORPORATIVO a proposito (10.000 y 17.815); el consolidado GAAP trae 268.910 M$ de deuda de Global Atlantic y de los vehiculos y daria un EV sin sentido. AZ (90.000) sigue sin base publicada.</t>
+  </si>
+  <si>
+    <t>Se anade LOTB (16) a la lista de filas con FCF normalizado: capex LTM 101,8 frente a un D&amp;A de 37,7, con un compromiso publicado de al menos 500 M EUR de capacidad Biscoff a cinco anos. Con ella son trece.</t>
+  </si>
+  <si>
+    <t>Filas normalizadas a 25-ago-2026 (trece): MSFT (5), COST (8), AMZN (13), LOTB (16), DNP (23), META (28), GOOG (32), NVDA (38), TSM (40), CPR (44), NFLX (50), TREX (55) e IPCO (63). El resto usa FCF reportado. NVDA y NFLX cumplen el disparador por poco (efecto del 2,8% y el 3,7%) y se aplican igual para no elegir a dedo. EXCEPCIONES documentadas: TFPM (49) lo activa mecanicamente pero NO se normaliza, porque ese capex son compras de streams -M&amp;A de crecimiento- y en una royalty el capex de sostenimiento es cero; EVD (20) tampoco, porque el D&amp;A de la fuente es implausible y el capex derivado no es fiable.</t>
   </si>
 </sst>
 </file>
@@ -6068,155 +6110,33 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="29" fillId="25" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6234,14 +6154,136 @@
     <xf numFmtId="0" fontId="15" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="23" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="33" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="32" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="37" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="30" fillId="37" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="44" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="28" fillId="40" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7013,7 +7055,7 @@
                   <c:v>7.77</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.9</c:v>
+                  <c:v>7.84</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>7.82</c:v>
@@ -7067,7 +7109,7 @@
                   <c:v>0.10741088468091919</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-2.6426000842472375E-2</c:v>
+                  <c:v>-6.630657915443261E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>8.4171531047791737E-2</c:v>
@@ -16664,10 +16706,10 @@
         <v>6200</v>
       </c>
       <c r="AT7" s="19">
-        <v>5500</v>
+        <v>5700</v>
       </c>
       <c r="AU7" s="19">
-        <v>15000</v>
+        <v>5700</v>
       </c>
       <c r="AV7" s="19">
         <v>80690</v>
@@ -16678,7 +16720,7 @@
       </c>
       <c r="AX7" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>7.398621575</v>
+        <v>19.47005677631579</v>
       </c>
       <c r="AY7" s="20">
         <f t="shared" ca="1" si="11"/>
@@ -16689,7 +16731,7 @@
       </c>
       <c r="BA7" s="22">
         <f t="shared" si="12"/>
-        <v>6.8162101871359529E-2</v>
+        <v>7.0640723757590784E-2</v>
       </c>
       <c r="BB7" s="22">
         <f t="shared" si="13"/>
@@ -16697,7 +16739,7 @@
       </c>
       <c r="BC7" s="23">
         <f t="shared" si="14"/>
-        <v>6.1111111111111116E-2</v>
+        <v>6.3333333333333339E-2</v>
       </c>
       <c r="BD7" s="98">
         <v>6845</v>
@@ -16736,13 +16778,13 @@
         <v>0.21900244611200459</v>
       </c>
       <c r="BN7" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO7" t="s">
         <v>88</v>
       </c>
       <c r="BP7" s="96" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -16968,7 +17010,7 @@
         <v>8.4916787387159243E-2</v>
       </c>
       <c r="BN8" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO8" t="s">
         <v>92</v>
@@ -17200,13 +17242,13 @@
         <v>0.19745985531708032</v>
       </c>
       <c r="BN9" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO9" t="s">
         <v>80</v>
       </c>
       <c r="BP9" s="96" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
     </row>
     <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -17432,13 +17474,13 @@
         <v>0.12867081613737774</v>
       </c>
       <c r="BN10" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO10" s="95" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP10" s="95" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -17664,7 +17706,7 @@
         <v>0.25949207403006769</v>
       </c>
       <c r="BN11" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO11" t="s">
         <v>92</v>
@@ -17896,13 +17938,13 @@
         <v>2.2808301254799268E-2</v>
       </c>
       <c r="BN12" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO12" s="100" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP12" s="95" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18128,7 +18170,7 @@
         <v>0.11301923910271405</v>
       </c>
       <c r="BN13" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO13" s="93" t="s">
         <v>106</v>
@@ -18360,7 +18402,7 @@
         <v>9.4174490275463096E-2</v>
       </c>
       <c r="BN14" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO14" s="93" t="s">
         <v>106</v>
@@ -18592,7 +18634,7 @@
         <v>0.10741088468091919</v>
       </c>
       <c r="BN15" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO15" t="s">
         <v>110</v>
@@ -18706,7 +18748,7 @@
         <v>-1</v>
       </c>
       <c r="AF16" s="90">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG16" s="90">
         <v>13</v>
@@ -18725,81 +18767,81 @@
       </c>
       <c r="AL16" s="15">
         <f t="shared" si="5"/>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AM16" s="16">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="AN16" s="17">
         <f t="shared" si="7"/>
-        <v>7.9</v>
+        <v>7.84</v>
       </c>
       <c r="AO16" s="18" t="s">
         <v>87</v>
       </c>
       <c r="AP16" s="19">
-        <v>100</v>
+        <v>274</v>
       </c>
       <c r="AQ16" s="19">
-        <v>200</v>
+        <v>409</v>
       </c>
       <c r="AR16" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>10789.731</v>
+        <v>10824.731</v>
       </c>
       <c r="AS16" s="19">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="AT16" s="19">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="AU16" s="19">
-        <v>300.39999999999998</v>
+        <v>291</v>
       </c>
       <c r="AV16" s="19">
-        <v>1446.8</v>
+        <v>1450</v>
       </c>
       <c r="AW16" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>59.942949999999996</v>
+        <v>59.15153551912568</v>
       </c>
       <c r="AX16" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>35.917879494007991</v>
+        <v>37.198388316151203</v>
       </c>
       <c r="AY16" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>7.457652059717998</v>
+        <v>7.4653317241379309</v>
       </c>
       <c r="AZ16" s="21">
-        <v>800</v>
+        <v>1309</v>
       </c>
       <c r="BA16" s="22">
         <f t="shared" si="12"/>
-        <v>0.11404478849875588</v>
+        <v>0.1310344827586207</v>
       </c>
       <c r="BB16" s="22">
         <f t="shared" si="13"/>
-        <v>1.8085</v>
+        <v>1.1077158135981666</v>
       </c>
       <c r="BC16" s="23">
         <f t="shared" si="14"/>
-        <v>0.20625000000000002</v>
+        <v>0.14514896867838048</v>
       </c>
       <c r="BD16" s="98">
-        <v>252</v>
+        <v>256.2</v>
       </c>
       <c r="BE16" s="23">
         <f t="shared" si="15"/>
         <v>6.9610375725068785E-2</v>
       </c>
-      <c r="BF16" t="s">
-        <v>112</v>
+      <c r="BF16">
+        <v>419</v>
       </c>
       <c r="BG16" s="23">
         <f t="shared" si="16"/>
-        <v>0.15996225865400127</v>
+        <v>0.18019178321090878</v>
       </c>
       <c r="BH16" s="24">
         <v>15</v>
@@ -18809,28 +18851,28 @@
       </c>
       <c r="BJ16" s="25">
         <f ca="1">(BD16*BH16+$AP16-$AQ16)/$H16</f>
-        <v>4509.7486550409922</v>
+        <v>4544.0619600249993</v>
       </c>
       <c r="BK16" s="25">
         <f ca="1">(BF16*BI16+$AP16-$AQ16)/$H16</f>
-        <v>11458.192914302521</v>
+        <v>12671.413340522788</v>
       </c>
       <c r="BL16" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.19206539792849897</v>
+        <v>-0.19083965708991213</v>
       </c>
       <c r="BM16" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-2.6426000842472375E-2</v>
+        <v>-6.630657915443261E-3</v>
       </c>
       <c r="BN16" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO16" s="95" t="s">
         <v>104</v>
       </c>
       <c r="BP16" s="95" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18842,7 +18884,7 @@
         <v>HLMA</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D17" s="88" t="s">
         <v>77</v>
@@ -18968,7 +19010,7 @@
         <v>7.82</v>
       </c>
       <c r="AO17" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AP17" s="19">
         <v>100</v>
@@ -19027,7 +19069,7 @@
         <v>5.0200405794756708E-2</v>
       </c>
       <c r="BF17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="BG17" s="23">
         <f t="shared" si="16"/>
@@ -19059,10 +19101,10 @@
         <v>97</v>
       </c>
       <c r="BO17" s="94" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="BP17" s="93" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19259,7 +19301,7 @@
         <v>8.0078627468473051E-2</v>
       </c>
       <c r="BF18" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="BG18" s="23">
         <f t="shared" si="16"/>
@@ -19294,7 +19336,7 @@
         <v>84</v>
       </c>
       <c r="BP18" s="93" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19306,7 +19348,7 @@
         <v>LIFCO B</v>
       </c>
       <c r="C19" s="88" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D19" s="88" t="s">
         <v>77</v>
@@ -19432,7 +19474,7 @@
         <v>7.94</v>
       </c>
       <c r="AO19" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AP19" s="19">
         <v>3000</v>
@@ -19491,7 +19533,7 @@
         <v>7.001218289169242E-2</v>
       </c>
       <c r="BF19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="BG19" s="23">
         <f t="shared" si="16"/>
@@ -19523,10 +19565,10 @@
         <v>46256</v>
       </c>
       <c r="BO19" s="93" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="BP19" s="93" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19752,13 +19794,13 @@
         <v>0.15549957158625838</v>
       </c>
       <c r="BN20" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO20" t="s">
         <v>92</v>
       </c>
       <c r="BP20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19834,7 +19876,7 @@
         <v>17</v>
       </c>
       <c r="V21" s="91">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W21" s="91">
         <v>9</v>
@@ -19853,11 +19895,11 @@
       </c>
       <c r="AB21" s="26">
         <f t="shared" si="3"/>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AC21" s="16">
         <f t="shared" si="4"/>
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AD21" s="91">
         <v>13</v>
@@ -19893,73 +19935,73 @@
       </c>
       <c r="AN21" s="17">
         <f t="shared" si="7"/>
-        <v>7.54</v>
+        <v>7.58</v>
       </c>
       <c r="AO21" s="18" t="s">
         <v>78</v>
       </c>
       <c r="AP21" s="19">
-        <v>4201</v>
+        <v>3419</v>
       </c>
       <c r="AQ21" s="19">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="AR21" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>90880.937760000001</v>
+        <v>91755.937760000001</v>
       </c>
       <c r="AS21" s="19">
-        <v>1800</v>
+        <v>2100</v>
       </c>
       <c r="AT21" s="19">
-        <v>2043</v>
+        <v>2154</v>
       </c>
       <c r="AU21" s="19">
-        <v>2688</v>
+        <v>2930</v>
       </c>
       <c r="AV21" s="19">
-        <v>9219</v>
+        <v>9220</v>
       </c>
       <c r="AW21" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>50.489409866666669</v>
+        <v>43.693303695238093</v>
       </c>
       <c r="AX21" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>33.809872678571431</v>
+        <v>31.316019713310581</v>
       </c>
       <c r="AY21" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>9.8580038789456559</v>
+        <v>9.9518370672451191</v>
       </c>
       <c r="AZ21" s="21">
-        <v>5164</v>
+        <v>9665</v>
       </c>
       <c r="BA21" s="22">
         <f t="shared" si="12"/>
-        <v>0.22160754962577286</v>
+        <v>0.23362255965292841</v>
       </c>
       <c r="BB21" s="22">
         <f t="shared" si="13"/>
-        <v>1.7852439969016267</v>
+        <v>0.95395757889291255</v>
       </c>
       <c r="BC21" s="23">
         <f t="shared" si="14"/>
-        <v>0.39562354763749036</v>
+        <v>0.22286601138127263</v>
       </c>
       <c r="BD21" s="98">
-        <v>2190</v>
+        <v>2555</v>
       </c>
       <c r="BE21" s="23">
         <f t="shared" si="15"/>
         <v>4.0002353139918068E-2</v>
       </c>
-      <c r="BF21" t="s">
-        <v>127</v>
+      <c r="BF21">
+        <v>4043</v>
       </c>
       <c r="BG21" s="23">
         <f t="shared" si="16"/>
-        <v>0.10999233818109388</v>
+        <v>0.1399791003201496</v>
       </c>
       <c r="BH21" s="24">
         <v>18</v>
@@ -19969,28 +20011,28 @@
       </c>
       <c r="BJ21" s="25">
         <f t="shared" ca="1" si="23"/>
-        <v>22.300942323580173</v>
+        <v>25.212472699609819</v>
       </c>
       <c r="BK21" s="25">
         <f t="shared" ca="1" si="24"/>
-        <v>36.260950830668051</v>
+        <v>47.173438254083813</v>
       </c>
       <c r="BL21" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.14430396685011082</v>
+        <v>-0.12304367658880577</v>
       </c>
       <c r="BM21" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-5.6932641321074229E-2</v>
+        <v>-5.9816951414956021E-3</v>
       </c>
       <c r="BN21" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO21" s="93" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP21" s="95" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -20216,13 +20258,13 @@
         <v>0.16592790507589994</v>
       </c>
       <c r="BN22" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO22" s="95" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP22" s="95" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -20360,7 +20402,7 @@
         <v>7.48</v>
       </c>
       <c r="AO23" s="18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="AP23" s="19">
         <v>771</v>
@@ -20448,13 +20490,13 @@
         <v>0.13746109747208712</v>
       </c>
       <c r="BN23" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO23" s="96" t="s">
         <v>88</v>
       </c>
       <c r="BP23" s="96" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
     </row>
     <row r="24" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -20466,7 +20508,7 @@
         <v>VLTO</v>
       </c>
       <c r="C24" s="88" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D24" s="88" t="s">
         <v>77</v>
@@ -20680,13 +20722,13 @@
         <v>8.2282923728493218E-2</v>
       </c>
       <c r="BN24" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO24" s="93" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BP24" s="93" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -20912,13 +20954,13 @@
         <v>0.10491795222211375</v>
       </c>
       <c r="BN25" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO25" s="95" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP25" s="95" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -20930,7 +20972,7 @@
         <v>JDG</v>
       </c>
       <c r="C26" s="88" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D26" s="88" t="s">
         <v>77</v>
@@ -21056,7 +21098,7 @@
         <v>6.75</v>
       </c>
       <c r="AO26" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AP26" s="19">
         <v>19.399999999999999</v>
@@ -21144,13 +21186,13 @@
         <v>0.31684805256802173</v>
       </c>
       <c r="BN26" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO26" s="95" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="BP26" s="95" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
     </row>
     <row r="27" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21162,7 +21204,7 @@
         <v>STMN</v>
       </c>
       <c r="C27" s="88" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D27" s="88" t="s">
         <v>77</v>
@@ -21288,7 +21330,7 @@
         <v>6.71</v>
       </c>
       <c r="AO27" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AP27" s="19">
         <v>415</v>
@@ -21376,10 +21418,10 @@
         <v>6.6237833093061527E-2</v>
       </c>
       <c r="BN27" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO27" s="100" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="BP27" s="95" t="s">
         <v>108</v>
@@ -21608,7 +21650,7 @@
         <v>0.26454787038117189</v>
       </c>
       <c r="BN28" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO28" s="93" t="s">
         <v>84</v>
@@ -21840,13 +21882,13 @@
         <v>0.23368644814706618</v>
       </c>
       <c r="BN29" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO29" s="95" t="s">
         <v>106</v>
       </c>
       <c r="BP29" s="95" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21916,7 +21958,7 @@
         <v>6.25</v>
       </c>
       <c r="T30" s="90">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30" s="90">
         <v>13</v>
@@ -21941,11 +21983,11 @@
       </c>
       <c r="AB30" s="15">
         <f t="shared" si="3"/>
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AC30" s="16">
         <f t="shared" si="4"/>
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AD30" s="90">
         <v>13</v>
@@ -21981,7 +22023,7 @@
       </c>
       <c r="AN30" s="17">
         <f t="shared" si="7"/>
-        <v>6.24</v>
+        <v>6.2</v>
       </c>
       <c r="AO30" s="18" t="s">
         <v>78</v>
@@ -22072,13 +22114,13 @@
         <v>-0.18238523641727311</v>
       </c>
       <c r="BN30" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO30" s="95" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP30" s="95" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -22154,7 +22196,7 @@
         <v>16</v>
       </c>
       <c r="V31" s="91">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W31" s="91">
         <v>8</v>
@@ -22173,11 +22215,11 @@
       </c>
       <c r="AB31" s="26">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AC31" s="16">
         <f t="shared" si="4"/>
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="AD31" s="91">
         <v>12</v>
@@ -22213,7 +22255,7 @@
       </c>
       <c r="AN31" s="17">
         <f t="shared" si="7"/>
-        <v>6.53</v>
+        <v>6.57</v>
       </c>
       <c r="AO31" s="18" t="s">
         <v>78</v>
@@ -22304,7 +22346,7 @@
         <v>-4.5877313596097258E-2</v>
       </c>
       <c r="BN31" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO31" t="s">
         <v>80</v>
@@ -22536,13 +22578,13 @@
         <v>0.11790528475856199</v>
       </c>
       <c r="BN32" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO32" s="93" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BP32" s="93" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -22768,13 +22810,13 @@
         <v>3.0933296240593267E-2</v>
       </c>
       <c r="BN33" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO33" s="93" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="BP33" s="93" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -22786,7 +22828,7 @@
         <v>GRMN</v>
       </c>
       <c r="C34" s="88" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D34" s="88" t="s">
         <v>77</v>
@@ -23000,7 +23042,7 @@
         <v>7.2435514956375791E-2</v>
       </c>
       <c r="BN34" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO34" s="93" t="s">
         <v>84</v>
@@ -23018,13 +23060,13 @@
         <v>KRX</v>
       </c>
       <c r="C35" s="88" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D35" s="88" t="s">
         <v>77</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="F35" s="11" t="str">
         <f t="array" aca="1" ref="F35" ca="1">_FV(A35,"Moneda")</f>
@@ -23231,13 +23273,13 @@
         <v>5.7941616311690369E-2</v>
       </c>
       <c r="BN35" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO35" s="95" t="s">
         <v>104</v>
       </c>
       <c r="BP35" s="95" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
     </row>
     <row r="36" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -23375,7 +23417,7 @@
         <v>5.81</v>
       </c>
       <c r="AO36" s="18" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="AP36" s="19">
         <v>900000</v>
@@ -23463,13 +23505,13 @@
         <v>0.34861805110601995</v>
       </c>
       <c r="BN36" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO36" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="BP36" s="96" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
     </row>
     <row r="37" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -23481,7 +23523,7 @@
         <v>CBAV</v>
       </c>
       <c r="C37" s="88" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D37" s="88" t="s">
         <v>77</v>
@@ -23666,7 +23708,7 @@
         <v>5.9223841048812176E-2</v>
       </c>
       <c r="BF37" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="BG37" s="23">
         <f t="shared" si="42"/>
@@ -23695,13 +23737,13 @@
         <v>9.2815334580940823E-2</v>
       </c>
       <c r="BN37" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO37" s="100" t="s">
         <v>84</v>
       </c>
       <c r="BP37" s="95" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
     </row>
     <row r="38" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -23713,7 +23755,7 @@
         <v>NVDA</v>
       </c>
       <c r="C38" s="88" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D38" s="88" t="s">
         <v>100</v>
@@ -23927,10 +23969,10 @@
         <v>0.1043703183777529</v>
       </c>
       <c r="BN38" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO38" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="BP38" t="s">
         <v>81</v>
@@ -23945,7 +23987,7 @@
         <v>COR</v>
       </c>
       <c r="C39" s="88" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D39" s="88" t="s">
         <v>90</v>
@@ -24130,7 +24172,7 @@
         <v>0</v>
       </c>
       <c r="BF39" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="BG39" s="23">
         <f t="shared" si="42"/>
@@ -24159,13 +24201,13 @@
         <v>7.9424865939422329E-2</v>
       </c>
       <c r="BN39" s="93" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BO39" s="94" t="s">
         <v>84</v>
       </c>
       <c r="BP39" s="93" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24177,7 +24219,7 @@
         <v>TSM</v>
       </c>
       <c r="C40" s="88" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D40" s="88" t="s">
         <v>77</v>
@@ -24391,13 +24433,13 @@
         <v>5.4817197673405094E-2</v>
       </c>
       <c r="BN40" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO40" s="93" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="BP40" s="93" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24623,7 +24665,7 @@
         <v>7.2771031468262803E-2</v>
       </c>
       <c r="BN41" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO41" s="95" t="s">
         <v>84</v>
@@ -24855,13 +24897,13 @@
         <v>0.15889031327299175</v>
       </c>
       <c r="BN42" s="95" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="BO42" s="93" t="s">
         <v>106</v>
       </c>
       <c r="BP42" s="93" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24873,7 +24915,7 @@
         <v>JFN</v>
       </c>
       <c r="C43" s="88" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D43" s="88" t="s">
         <v>90</v>
@@ -24999,7 +25041,7 @@
         <v>5.52</v>
       </c>
       <c r="AO43" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AP43" s="19">
         <v>75</v>
@@ -25058,7 +25100,7 @@
         <v>-6.0146235650011426E-2</v>
       </c>
       <c r="BF43" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="BG43" s="23">
         <f t="shared" si="42"/>
@@ -25090,10 +25132,10 @@
         <v>105</v>
       </c>
       <c r="BO43" s="93" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="BP43" s="93" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="44" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25105,7 +25147,7 @@
         <v>CPR</v>
       </c>
       <c r="C44" s="88" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D44" s="88" t="s">
         <v>90</v>
@@ -25319,7 +25361,7 @@
         <v>0.11502649565910006</v>
       </c>
       <c r="BN44" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO44" s="95" t="s">
         <v>84</v>
@@ -25337,7 +25379,7 @@
         <v>SIKA</v>
       </c>
       <c r="C45" s="88" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D45" s="88" t="s">
         <v>77</v>
@@ -25463,7 +25505,7 @@
         <v>5.51</v>
       </c>
       <c r="AO45" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AP45" s="19">
         <v>625</v>
@@ -25551,13 +25593,13 @@
         <v>7.8644748935160935E-2</v>
       </c>
       <c r="BN45" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO45" s="93" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BP45" s="93" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25572,7 +25614,7 @@
         <v>99</v>
       </c>
       <c r="D46" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E46" s="11" t="str">
         <f t="array" aca="1" ref="E46" ca="1">_FV(A46,"Abreviatura de intercambio",TRUE())</f>
@@ -25783,7 +25825,7 @@
         <v>0.15475894702900495</v>
       </c>
       <c r="BN46" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO46" s="93" t="s">
         <v>106</v>
@@ -25801,7 +25843,7 @@
         <v>TGYM</v>
       </c>
       <c r="C47" s="88" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D47" s="88" t="s">
         <v>77</v>
@@ -25986,7 +26028,7 @@
         <v>4.0751095710728658E-2</v>
       </c>
       <c r="BF47" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="BG47" s="23">
         <f t="shared" si="42"/>
@@ -26021,7 +26063,7 @@
         <v>106</v>
       </c>
       <c r="BP47" s="93" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26033,7 +26075,7 @@
         <v>VID</v>
       </c>
       <c r="C48" s="88" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D48" s="88" t="s">
         <v>90</v>
@@ -26218,7 +26260,7 @@
         <v>9.805797673485328E-3</v>
       </c>
       <c r="BF48" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="BG48" s="23">
         <f t="shared" si="42"/>
@@ -26247,13 +26289,13 @@
         <v>0.11190339617094747</v>
       </c>
       <c r="BN48" s="93" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BO48" s="94" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="BP48" s="93" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26265,10 +26307,10 @@
         <v>TFPM</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E49" s="11" t="str">
         <f t="array" aca="1" ref="E49" ca="1">_FV(A49,"Abreviatura de intercambio",TRUE())</f>
@@ -26479,13 +26521,13 @@
         <v>0.12508464727548008</v>
       </c>
       <c r="BN49" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO49" s="95" t="s">
         <v>98</v>
       </c>
       <c r="BP49" s="95" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26713,13 +26755,13 @@
         <v>7.0737265216964884E-2</v>
       </c>
       <c r="BN50" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO50" s="93" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="BP50" s="93" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26734,7 +26776,7 @@
         <v>109</v>
       </c>
       <c r="D51" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E51" s="11" t="str">
         <f t="array" aca="1" ref="E51" ca="1">_FV(A51,"Abreviatura de intercambio",TRUE())</f>
@@ -26945,13 +26987,13 @@
         <v>3.0610269988418981E-2</v>
       </c>
       <c r="BN51" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO51" s="93" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="BP51" s="93" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27027,7 +27069,7 @@
         <v>11</v>
       </c>
       <c r="V52" s="90">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W52" s="90">
         <v>6</v>
@@ -27042,15 +27084,15 @@
         <v>4</v>
       </c>
       <c r="AA52" s="90">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="AB52" s="15">
         <f t="shared" si="30"/>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AC52" s="16">
         <f t="shared" si="31"/>
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AD52" s="90">
         <v>10</v>
@@ -27086,73 +27128,73 @@
       </c>
       <c r="AN52" s="17">
         <f t="shared" si="34"/>
-        <v>4.8499999999999996</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="AO52" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AP52" s="19">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AQ52" s="19">
-        <v>0</v>
+        <v>331</v>
       </c>
       <c r="AR52" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>9531.6445920000006</v>
+        <v>9855.6445920000006</v>
       </c>
       <c r="AS52" s="19">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="AT52" s="19">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="AU52" s="19">
-        <v>182</v>
+        <v>259</v>
       </c>
       <c r="AV52" s="19">
-        <v>485</v>
+        <v>664</v>
       </c>
       <c r="AW52" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>80.77664908474577</v>
+        <v>58.66455114285715</v>
       </c>
       <c r="AX52" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>52.371673582417586</v>
+        <v>38.052681822393822</v>
       </c>
       <c r="AY52" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>19.65287544742268</v>
+        <v>14.842838240963856</v>
       </c>
       <c r="AZ52" s="21">
-        <v>350</v>
+        <v>1185</v>
       </c>
       <c r="BA52" s="22">
         <f t="shared" si="38"/>
-        <v>0.29484536082474228</v>
+        <v>0.28765060240963858</v>
       </c>
       <c r="BB52" s="22">
         <f t="shared" si="39"/>
-        <v>1.3857142857142857</v>
+        <v>0.56033755274261599</v>
       </c>
       <c r="BC52" s="23">
         <f t="shared" si="40"/>
-        <v>0.40857142857142859</v>
+        <v>0.16118143459915613</v>
       </c>
       <c r="BD52" s="98">
-        <v>121</v>
+        <v>172.3</v>
       </c>
       <c r="BE52" s="23">
         <f t="shared" si="41"/>
-        <v>5.0338114975041481E-3</v>
-      </c>
-      <c r="BF52" t="s">
-        <v>111</v>
+        <v>5.0674290335872563E-3</v>
+      </c>
+      <c r="BF52">
+        <v>384</v>
       </c>
       <c r="BG52" s="23">
         <f t="shared" si="42"/>
-        <v>0.16386794389255699</v>
+        <v>0.17978912471277986</v>
       </c>
       <c r="BH52" s="24">
         <v>17.5</v>
@@ -27162,28 +27204,28 @@
       </c>
       <c r="BJ52" s="25">
         <f t="shared" ca="1" si="49"/>
-        <v>86.727174992978789</v>
+        <v>108.38537592974552</v>
       </c>
       <c r="BK52" s="25">
         <f t="shared" ca="1" si="50"/>
-        <v>220.82871543370007</v>
+        <v>320.71124210678903</v>
       </c>
       <c r="BL52" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.25046391167669246</v>
+        <v>-0.21628953585513977</v>
       </c>
       <c r="BM52" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>-9.6407500885144048E-2</v>
-      </c>
-      <c r="BN52" s="93" t="s">
-        <v>105</v>
+        <v>-2.6391527282287108E-2</v>
+      </c>
+      <c r="BN52" s="95" t="s">
+        <v>679</v>
       </c>
       <c r="BO52" s="93" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="BP52" s="93" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27195,7 +27237,7 @@
         <v>FERG</v>
       </c>
       <c r="C53" s="88" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D53" s="88" t="s">
         <v>90</v>
@@ -27380,7 +27422,7 @@
         <v>0.17668618806379421</v>
       </c>
       <c r="BF53" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="BG53" s="23">
         <f t="shared" si="42"/>
@@ -27409,13 +27451,13 @@
         <v>7.9083214732629026E-2</v>
       </c>
       <c r="BN53" s="95" t="s">
+        <v>679</v>
+      </c>
+      <c r="BO53" s="95" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP53" s="95" t="s">
         <v>685</v>
-      </c>
-      <c r="BO53" s="95" t="s">
-        <v>135</v>
-      </c>
-      <c r="BP53" s="95" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="54" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27485,7 +27527,7 @@
         <v>4.38</v>
       </c>
       <c r="T54" s="90">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U54" s="90">
         <v>10</v>
@@ -27510,11 +27552,11 @@
       </c>
       <c r="AB54" s="15">
         <f t="shared" si="30"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AC54" s="16">
         <f t="shared" si="31"/>
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="AD54" s="90">
         <v>9</v>
@@ -27532,7 +27574,7 @@
         <v>0</v>
       </c>
       <c r="AI54" s="90">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AJ54" s="90">
         <v>9</v>
@@ -27542,81 +27584,81 @@
       </c>
       <c r="AL54" s="15">
         <f t="shared" si="32"/>
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AM54" s="16">
         <f t="shared" si="33"/>
-        <v>3.57</v>
+        <v>2.86</v>
       </c>
       <c r="AN54" s="17">
         <f t="shared" si="34"/>
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="AO54" s="18" t="s">
         <v>78</v>
       </c>
       <c r="AP54" s="19">
-        <v>1100</v>
+        <v>657</v>
       </c>
       <c r="AQ54" s="19">
         <v>0</v>
       </c>
       <c r="AR54" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>5826.7258425699993</v>
+        <v>6269.7258425699993</v>
       </c>
       <c r="AS54" s="19">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="AT54" s="19">
-        <v>-20</v>
+        <v>-301</v>
       </c>
       <c r="AU54" s="19">
-        <v>10</v>
+        <v>-259</v>
       </c>
       <c r="AV54" s="19">
-        <v>815</v>
+        <v>1050</v>
       </c>
       <c r="AW54" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>116.53451685139999</v>
+        <v>101.12461036403225</v>
       </c>
       <c r="AX54" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>582.67258425699993</v>
+        <v>-24.207435685598451</v>
       </c>
       <c r="AY54" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>7.1493568620490793</v>
+        <v>5.9711674691142846</v>
       </c>
       <c r="AZ54" s="21">
-        <v>1500</v>
+        <v>1684</v>
       </c>
       <c r="BA54" s="22">
         <f t="shared" si="38"/>
-        <v>-2.4539877300613498E-2</v>
+        <v>-0.28666666666666668</v>
       </c>
       <c r="BB54" s="22">
         <f t="shared" si="39"/>
-        <v>0.54333333333333333</v>
+        <v>0.62351543942992871</v>
       </c>
       <c r="BC54" s="23">
         <f t="shared" si="40"/>
-        <v>-1.3333333333333334E-2</v>
+        <v>-0.17874109263657958</v>
       </c>
       <c r="BD54" s="98">
-        <v>73</v>
+        <v>90.5</v>
       </c>
       <c r="BE54" s="23">
         <f t="shared" si="41"/>
-        <v>7.8625221439269977E-2</v>
-      </c>
-      <c r="BF54" t="s">
-        <v>163</v>
+        <v>7.8577553716729254E-2</v>
+      </c>
+      <c r="BF54">
+        <v>230.6</v>
       </c>
       <c r="BG54" s="23">
         <f t="shared" si="42"/>
-        <v>0.30049470405023282</v>
+        <v>0.3004495918431016</v>
       </c>
       <c r="BH54" s="24">
         <v>18</v>
@@ -27626,28 +27668,28 @@
       </c>
       <c r="BJ54" s="25">
         <f t="shared" ca="1" si="49"/>
-        <v>7.0419309943270738</v>
+        <v>6.6685394585881079</v>
       </c>
       <c r="BK54" s="25">
         <f t="shared" ca="1" si="50"/>
-        <v>17.31603246989458</v>
+        <v>19.4064416457582</v>
       </c>
       <c r="BL54" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.19008050366721119</v>
+        <v>-0.19885773220635861</v>
       </c>
       <c r="BM54" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>-3.0398723223409752E-2</v>
-      </c>
-      <c r="BN54" t="s">
-        <v>91</v>
+        <v>-8.043374446389806E-3</v>
+      </c>
+      <c r="BN54" s="96" t="s">
+        <v>679</v>
       </c>
       <c r="BO54" t="s">
         <v>92</v>
       </c>
       <c r="BP54" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27659,7 +27701,7 @@
         <v>TREX</v>
       </c>
       <c r="C55" s="88" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D55" s="88" t="s">
         <v>77</v>
@@ -27873,13 +27915,13 @@
         <v>0.14794472574933581</v>
       </c>
       <c r="BN55" s="95" t="s">
+        <v>679</v>
+      </c>
+      <c r="BO55" s="95" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP55" s="95" t="s">
         <v>685</v>
-      </c>
-      <c r="BO55" s="95" t="s">
-        <v>135</v>
-      </c>
-      <c r="BP55" s="95" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="56" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27891,10 +27933,10 @@
         <v>SGO</v>
       </c>
       <c r="C56" s="88" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D56" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E56" s="11" t="str">
         <f t="array" aca="1" ref="E56" ca="1">_FV(A56,"Abreviatura de intercambio",TRUE())</f>
@@ -28105,7 +28147,7 @@
         <v>0.12247003636339482</v>
       </c>
       <c r="BN56" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO56" s="95" t="s">
         <v>106</v>
@@ -28123,10 +28165,10 @@
         <v>TFF</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E57" s="11" t="str">
         <f t="array" aca="1" ref="E57" ca="1">_FV(A57,"Abreviatura de intercambio",TRUE())</f>
@@ -28202,15 +28244,15 @@
         <v>8</v>
       </c>
       <c r="AA57" s="91">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="AB57" s="26">
         <f t="shared" si="30"/>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AC57" s="16">
         <f t="shared" si="31"/>
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD57" s="91">
         <v>9</v>
@@ -28246,73 +28288,73 @@
       </c>
       <c r="AN57" s="17">
         <f t="shared" si="34"/>
-        <v>3.53</v>
+        <v>3.49</v>
       </c>
       <c r="AO57" s="18" t="s">
         <v>87</v>
       </c>
       <c r="AP57" s="19">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="AQ57" s="19">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="AR57" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>701.62239999999997</v>
+        <v>646.62239999999997</v>
       </c>
       <c r="AS57" s="19">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="AT57" s="19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU57" s="19">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AV57" s="19">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="AW57" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>28.064895999999997</v>
+        <v>10.959701694915253</v>
       </c>
       <c r="AX57" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>12.756770909090909</v>
+        <v>13.471299999999999</v>
       </c>
       <c r="AY57" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>2.1925699999999999</v>
+        <v>2.0658862619808307</v>
       </c>
       <c r="AZ57" s="21">
-        <v>500</v>
+        <v>624</v>
       </c>
       <c r="BA57" s="22">
         <f t="shared" si="38"/>
-        <v>6.25E-2</v>
+        <v>6.7092651757188496E-2</v>
       </c>
       <c r="BB57" s="22">
         <f t="shared" si="39"/>
-        <v>0.64</v>
+        <v>0.5016025641025641</v>
       </c>
       <c r="BC57" s="23">
         <f t="shared" si="40"/>
-        <v>0.04</v>
+        <v>3.3653846153846152E-2</v>
       </c>
       <c r="BD57" s="98">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="BE57" s="23">
         <f t="shared" si="41"/>
         <v>0</v>
       </c>
-      <c r="BF57" t="s">
-        <v>164</v>
+      <c r="BF57">
+        <v>103.8</v>
       </c>
       <c r="BG57" s="23">
         <f t="shared" si="42"/>
-        <v>0.11970220528043152</v>
+        <v>0.11961592833339973</v>
       </c>
       <c r="BH57" s="24">
         <v>6</v>
@@ -28322,28 +28364,28 @@
       </c>
       <c r="BJ57" s="25">
         <f t="shared" ca="1" si="49"/>
-        <v>-8.7638376383763834</v>
+        <v>3.1826568265682655</v>
       </c>
       <c r="BK57" s="25">
         <f t="shared" ca="1" si="50"/>
-        <v>9.6863468634686356</v>
+        <v>46.702029520295206</v>
       </c>
       <c r="BL57" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-1.8792242448232659</v>
+        <v>-0.28200940850053402</v>
       </c>
       <c r="BM57" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>-0.10299927489502325</v>
-      </c>
-      <c r="BN57" s="93" t="s">
-        <v>105</v>
+        <v>0.22864931127815757</v>
+      </c>
+      <c r="BN57" s="95" t="s">
+        <v>679</v>
       </c>
       <c r="BO57" s="93" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="BP57" s="93" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28569,13 +28611,13 @@
         <v>0.29785192981163666</v>
       </c>
       <c r="BN58" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO58" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP58" s="96" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28587,7 +28629,7 @@
         <v>BFIT</v>
       </c>
       <c r="C59" s="88" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D59" s="88" t="s">
         <v>100</v>
@@ -28772,7 +28814,7 @@
         <v>1.9244876491456564E-2</v>
       </c>
       <c r="BF59" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="BG59" s="23">
         <f t="shared" si="42"/>
@@ -28801,13 +28843,13 @@
         <v>9.176758778506322E-3</v>
       </c>
       <c r="BN59" s="93" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BO59" s="93" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BP59" s="93" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28819,13 +28861,13 @@
         <v>VRLA</v>
       </c>
       <c r="C60" s="88" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D60" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="F60" s="11" t="str">
         <f t="array" aca="1" ref="F60" ca="1">_FV(A60,"Moneda")</f>
@@ -29032,10 +29074,10 @@
         <v>0.18376417218175689</v>
       </c>
       <c r="BN60" s="93" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BO60" s="93" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="BP60" s="93" t="s">
         <v>85</v>
@@ -29050,10 +29092,10 @@
         <v>KIST</v>
       </c>
       <c r="C61" s="88" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D61" s="88" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E61" s="11" t="str">
         <f t="array" aca="1" ref="E61" ca="1">_FV(A61,"Abreviatura de intercambio",TRUE())</f>
@@ -29269,10 +29311,10 @@
         <v>105</v>
       </c>
       <c r="BO61" s="93" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="BP61" s="93" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="62" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29287,7 +29329,7 @@
         <v>109</v>
       </c>
       <c r="D62" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E62" s="11" t="str">
         <f t="array" aca="1" ref="E62" ca="1">_FV(A62,"Abreviatura de intercambio",TRUE())</f>
@@ -29410,7 +29452,7 @@
         <v>2.33</v>
       </c>
       <c r="AO62" s="18" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AP62" s="19">
         <v>70</v>
@@ -29469,7 +29511,7 @@
         <v>0</v>
       </c>
       <c r="BF62" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="BG62" s="23">
         <f t="shared" si="42"/>
@@ -29501,10 +29543,10 @@
         <v>105</v>
       </c>
       <c r="BO62" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="BP62" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="63" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29516,10 +29558,10 @@
         <v>IPCO</v>
       </c>
       <c r="C63" s="88" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D63" s="88" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E63" s="11" t="str">
         <f t="array" aca="1" ref="E63" ca="1">_FV(A63,"Abreviatura de intercambio",TRUE())</f>
@@ -29701,7 +29743,7 @@
         <v>0.57101890653493736</v>
       </c>
       <c r="BF63" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="BG63" s="23">
         <f t="shared" si="42"/>
@@ -29730,13 +29772,13 @@
         <v>0.14248204562663958</v>
       </c>
       <c r="BN63" s="95" t="s">
+        <v>679</v>
+      </c>
+      <c r="BO63" s="95" t="s">
+        <v>132</v>
+      </c>
+      <c r="BP63" s="95" t="s">
         <v>685</v>
-      </c>
-      <c r="BO63" s="95" t="s">
-        <v>135</v>
-      </c>
-      <c r="BP63" s="95" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="64" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29751,7 +29793,7 @@
         <v>109</v>
       </c>
       <c r="D64" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E64" s="11" t="str">
         <f t="array" aca="1" ref="E64" ca="1">_FV(A64,"Abreviatura de intercambio",TRUE())</f>
@@ -29841,7 +29883,7 @@
         <v>8</v>
       </c>
       <c r="AE64" s="90">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AF64" s="90">
         <v>4</v>
@@ -29863,15 +29905,15 @@
       </c>
       <c r="AL64" s="15">
         <f t="shared" si="32"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM64" s="16">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="AN64" s="17">
         <f t="shared" si="34"/>
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AO64" s="18" t="s">
         <v>78</v>
@@ -29880,64 +29922,64 @@
         <v>44.6</v>
       </c>
       <c r="AQ64" s="19">
-        <v>517.79999999999995</v>
+        <v>549</v>
       </c>
       <c r="AR64" s="19">
         <f t="shared" ref="AR64:AR71" ca="1" si="51">I64-AP64+AQ64</f>
-        <v>976.13721759999999</v>
+        <v>1007.3372176</v>
       </c>
       <c r="AS64" s="19">
-        <v>-50</v>
+        <v>-21.9</v>
       </c>
       <c r="AT64" s="19">
-        <v>-100</v>
+        <v>-49</v>
       </c>
       <c r="AU64" s="19">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="AV64" s="19">
-        <v>830</v>
+        <v>925</v>
       </c>
       <c r="AW64" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>-19.522744352</v>
+        <v>-45.997133223744299</v>
       </c>
       <c r="AX64" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>-97.613721760000004</v>
+        <v>-71.952658400000004</v>
       </c>
       <c r="AY64" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>1.1760689368674699</v>
+        <v>1.0890132082162163</v>
       </c>
       <c r="AZ64" s="21">
-        <v>650</v>
+        <v>169</v>
       </c>
       <c r="BA64" s="22">
         <f t="shared" si="38"/>
-        <v>-0.12048192771084337</v>
+        <v>-5.2972972972972973E-2</v>
       </c>
       <c r="BB64" s="22">
         <f t="shared" si="39"/>
-        <v>1.2769230769230768</v>
+        <v>5.4733727810650885</v>
       </c>
       <c r="BC64" s="23">
         <f t="shared" si="40"/>
-        <v>-0.15384615384615383</v>
+        <v>-0.28994082840236685</v>
       </c>
       <c r="BD64" s="98">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="BE64" s="23">
         <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="BF64" t="s">
-        <v>172</v>
+        <v>-1</v>
+      </c>
+      <c r="BF64">
+        <v>114</v>
       </c>
       <c r="BG64" s="23">
         <f t="shared" si="42"/>
-        <v>-2.179198639369468</v>
+        <v>-2.3908879585905485</v>
       </c>
       <c r="BH64" s="24">
         <v>12</v>
@@ -29947,28 +29989,28 @@
       </c>
       <c r="BJ64" s="25">
         <f ca="1">(BD64*BH64+$AP64-$AQ64)/$H64</f>
-        <v>-33.629708456875186</v>
+        <v>-15.805837631054647</v>
       </c>
       <c r="BK64" s="25">
         <f ca="1">(BF64*BI64+$AP64-$AQ64)/$H64</f>
-        <v>42.328559619406462</v>
+        <v>41.350878941196889</v>
       </c>
       <c r="BL64" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-2.1636794844959226</v>
+        <v>-2.0005810202640713</v>
       </c>
       <c r="BM64" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.21847172422912342</v>
-      </c>
-      <c r="BN64" s="93" t="s">
-        <v>79</v>
+        <v>0.21279027663802674</v>
+      </c>
+      <c r="BN64" s="95" t="s">
+        <v>679</v>
       </c>
       <c r="BO64" s="93" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="BP64" s="93" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="65" spans="1:68" x14ac:dyDescent="0.35">
@@ -30194,13 +30236,13 @@
         <v>0.19382646615642507</v>
       </c>
       <c r="BN65" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO65" s="95" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="BP65" s="95" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:68" x14ac:dyDescent="0.35">
@@ -30212,7 +30254,7 @@
         <v>UBER</v>
       </c>
       <c r="C66" s="88" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D66" s="88" t="s">
         <v>77</v>
@@ -30426,13 +30468,13 @@
         <v>0.31304768252822446</v>
       </c>
       <c r="BN66" s="95" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO66" s="95" t="s">
         <v>98</v>
       </c>
       <c r="BP66" s="95" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
     </row>
     <row r="67" spans="1:68" x14ac:dyDescent="0.35">
@@ -30444,10 +30486,10 @@
         <v>SOM</v>
       </c>
       <c r="C67" s="88" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D67" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E67" s="11" t="str">
         <f ca="1">_FV(A67,"Abreviatura de intercambio",TRUE)</f>
@@ -30658,13 +30700,13 @@
         <v>0.29447306727229905</v>
       </c>
       <c r="BN67" s="96" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="BO67" s="96" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="BP67" s="96" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="68" spans="1:68" x14ac:dyDescent="0.35">
@@ -30676,7 +30718,7 @@
         <v>IP</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D68" s="88" t="s">
         <v>77</v>
@@ -30890,13 +30932,13 @@
         <v>0.21585925378268067</v>
       </c>
       <c r="BN68" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO68" s="96" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP68" s="96" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
     </row>
     <row r="69" spans="1:68" x14ac:dyDescent="0.35">
@@ -31122,13 +31164,13 @@
         <v>0.16393540749423563</v>
       </c>
       <c r="BN69" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO69" s="96" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="BP69" s="96" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
     </row>
     <row r="70" spans="1:68" x14ac:dyDescent="0.35">
@@ -31140,7 +31182,7 @@
         <v>ROKO B</v>
       </c>
       <c r="C70" s="88" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D70" s="88" t="s">
         <v>77</v>
@@ -31266,7 +31308,7 @@
         <v>6.2</v>
       </c>
       <c r="AO70" s="18" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AP70" s="19">
         <v>435</v>
@@ -31354,13 +31396,13 @@
         <v>0.18934774904737917</v>
       </c>
       <c r="BN70" s="96" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="BO70" s="96" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="BP70" s="96" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:68" x14ac:dyDescent="0.35">
@@ -31372,7 +31414,7 @@
         <v>USPH</v>
       </c>
       <c r="C71" s="88" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D71" s="88" t="s">
         <v>77</v>
@@ -31586,13 +31628,13 @@
         <v>0.15403674413348489</v>
       </c>
       <c r="BN71" s="96" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="BO71" s="96" t="s">
         <v>98</v>
       </c>
       <c r="BP71" s="96" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -31625,7 +31667,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="106" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="102"/>
@@ -31635,12 +31677,12 @@
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="27" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D4" t="e" vm="69">
         <v>#VALUE!</v>
@@ -31652,7 +31694,7 @@
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D5" t="e" vm="70">
         <v>#VALUE!</v>
@@ -31664,7 +31706,7 @@
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D6" t="e" vm="71">
         <v>#VALUE!</v>
@@ -31685,7 +31727,7 @@
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="27" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="D8" t="e" vm="73">
         <v>#VALUE!</v>
@@ -31697,10 +31739,10 @@
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="28" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C9" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="E9">
         <v>1.3641000000000001</v>
@@ -31708,177 +31750,177 @@
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="28" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="28" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="28" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="28" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="28" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="28" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="27" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="28" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="28" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="28" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="28" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="28" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="28" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="28" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="28" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="27" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="28" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="28" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="28" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="28" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="28" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="28" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="28" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="28" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="27" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="28" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="28" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="27" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="28" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="28" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="28" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="28" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="28" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31886,107 +31928,107 @@
     </row>
     <row r="50" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="28" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="28" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="28" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>784</v>
+        <v>799</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
     </row>
   </sheetData>
@@ -32015,8 +32057,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="45" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="113" t="s">
-        <v>215</v>
+      <c r="A1" s="169" t="s">
+        <v>209</v>
       </c>
       <c r="B1" s="102"/>
       <c r="C1" s="102"/>
@@ -32037,276 +32079,276 @@
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="130" t="s">
+      <c r="A2" s="157" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
+      <c r="G2" s="158"/>
+      <c r="H2" s="158"/>
+      <c r="I2" s="158"/>
+      <c r="J2" s="158"/>
+      <c r="K2" s="158"/>
+      <c r="L2" s="158"/>
+    </row>
+    <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="162" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="130"/>
+      <c r="C3" s="129" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" s="130"/>
+      <c r="E3" s="131" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="130"/>
+      <c r="G3" s="177" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="130"/>
+      <c r="I3" s="178" t="s">
+        <v>215</v>
+      </c>
+      <c r="J3" s="130"/>
+      <c r="K3" s="141" t="s">
         <v>216</v>
       </c>
-      <c r="B2" s="131"/>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-    </row>
-    <row r="3" spans="1:47" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="136" t="s">
-        <v>217</v>
-      </c>
-      <c r="B3" s="125"/>
-      <c r="C3" s="157" t="s">
-        <v>218</v>
-      </c>
-      <c r="D3" s="125"/>
-      <c r="E3" s="158" t="s">
-        <v>219</v>
-      </c>
-      <c r="F3" s="125"/>
-      <c r="G3" s="124" t="s">
-        <v>220</v>
-      </c>
-      <c r="H3" s="125"/>
-      <c r="I3" s="126" t="s">
-        <v>221</v>
-      </c>
-      <c r="J3" s="125"/>
-      <c r="K3" s="162" t="s">
-        <v>222</v>
-      </c>
-      <c r="L3" s="163"/>
+      <c r="L3" s="142"/>
     </row>
     <row r="4" spans="1:47" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="143">
+      <c r="A4" s="166">
         <f ca="1">COUNTA('Watchlist Ratings'!B4:B71)</f>
         <v>68</v>
       </c>
-      <c r="B4" s="128"/>
-      <c r="C4" s="159">
+      <c r="B4" s="136"/>
+      <c r="C4" s="137">
         <f>ROUND(AVERAGE('Watchlist Ratings'!AN4:AN71),2)</f>
         <v>5.98</v>
       </c>
-      <c r="D4" s="128"/>
-      <c r="E4" s="129" t="str">
+      <c r="D4" s="136"/>
+      <c r="E4" s="138" t="str">
         <f>TEXT(AVERAGE('Watchlist Ratings'!BC4:BC71),"0.0%")</f>
-        <v>16.8%</v>
-      </c>
-      <c r="F4" s="128"/>
-      <c r="G4" s="129" t="str">
+        <v>15.6%</v>
+      </c>
+      <c r="F4" s="136"/>
+      <c r="G4" s="138" t="str">
         <f ca="1">TEXT(AVERAGE('Watchlist Ratings'!AW4:AW71),"0.0x")</f>
-        <v>35.3x</v>
-      </c>
-      <c r="H4" s="128"/>
-      <c r="I4" s="129">
+        <v>34.0x</v>
+      </c>
+      <c r="H4" s="136"/>
+      <c r="I4" s="138">
         <f ca="1">COUNTIF('Watchlist Ratings'!BM4:BM71,"&gt;0")</f>
-        <v>61</v>
-      </c>
-      <c r="J4" s="128"/>
-      <c r="K4" s="114">
+        <v>62</v>
+      </c>
+      <c r="J4" s="136"/>
+      <c r="K4" s="170">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&gt;7.5")</f>
         <v>16</v>
       </c>
-      <c r="L4" s="115"/>
+      <c r="L4" s="144"/>
     </row>
     <row r="5" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="139" t="s">
+      <c r="A5" s="164" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="136"/>
+      <c r="C5" s="135" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="136"/>
+      <c r="E5" s="135" t="s">
+        <v>219</v>
+      </c>
+      <c r="F5" s="136"/>
+      <c r="G5" s="135" t="s">
+        <v>220</v>
+      </c>
+      <c r="H5" s="136"/>
+      <c r="I5" s="135" t="s">
+        <v>221</v>
+      </c>
+      <c r="J5" s="136"/>
+      <c r="K5" s="143" t="s">
+        <v>222</v>
+      </c>
+      <c r="L5" s="144"/>
+    </row>
+    <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="174" t="s">
         <v>223</v>
       </c>
-      <c r="B5" s="128"/>
-      <c r="C5" s="127" t="s">
+      <c r="B6" s="134"/>
+      <c r="C6" s="133" t="s">
         <v>224</v>
       </c>
-      <c r="D5" s="128"/>
-      <c r="E5" s="127" t="s">
+      <c r="D6" s="134"/>
+      <c r="E6" s="133" t="s">
         <v>225</v>
       </c>
-      <c r="F5" s="128"/>
-      <c r="G5" s="127" t="s">
+      <c r="F6" s="134"/>
+      <c r="G6" s="176" t="s">
         <v>226</v>
       </c>
-      <c r="H5" s="128"/>
-      <c r="I5" s="127" t="s">
+      <c r="H6" s="134"/>
+      <c r="I6" s="133" t="s">
         <v>227</v>
       </c>
-      <c r="J5" s="128"/>
-      <c r="K5" s="164" t="s">
+      <c r="J6" s="134"/>
+      <c r="K6" s="139" t="s">
         <v>228</v>
       </c>
-      <c r="L5" s="115"/>
-    </row>
-    <row r="6" spans="1:47" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="120" t="s">
+      <c r="L6" s="140"/>
+      <c r="O6" t="s">
         <v>229</v>
       </c>
-      <c r="B6" s="121"/>
-      <c r="C6" s="137" t="s">
+      <c r="S6" t="s">
         <v>230</v>
       </c>
-      <c r="D6" s="121"/>
-      <c r="E6" s="137" t="s">
+      <c r="V6" t="s">
         <v>231</v>
       </c>
-      <c r="F6" s="121"/>
-      <c r="G6" s="123" t="s">
+      <c r="Y6" t="s">
         <v>232</v>
       </c>
-      <c r="H6" s="121"/>
-      <c r="I6" s="137" t="s">
+      <c r="AA6" t="s">
         <v>233</v>
       </c>
-      <c r="J6" s="121"/>
-      <c r="K6" s="160" t="s">
+      <c r="AE6" t="s">
         <v>234</v>
       </c>
-      <c r="L6" s="161"/>
-      <c r="O6" t="s">
+      <c r="AF6" t="s">
         <v>235</v>
       </c>
-      <c r="S6" t="s">
+      <c r="AH6" t="s">
+        <v>234</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>235</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>234</v>
+      </c>
+      <c r="AK6" t="s">
         <v>236</v>
       </c>
-      <c r="V6" t="s">
+      <c r="AL6" t="s">
         <v>237</v>
       </c>
-      <c r="Y6" t="s">
+      <c r="AM6" t="s">
+        <v>234</v>
+      </c>
+      <c r="AN6" t="s">
         <v>238</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AO6" t="s">
+        <v>234</v>
+      </c>
+      <c r="AP6" t="s">
         <v>239</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AQ6" t="s">
         <v>240</v>
       </c>
-      <c r="AF6" t="s">
-        <v>241</v>
-      </c>
-      <c r="AH6" t="s">
+      <c r="AS6" t="s">
+        <v>234</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>238</v>
+      </c>
+      <c r="AU6" t="s">
         <v>240</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>241</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>240</v>
-      </c>
-      <c r="AK6" t="s">
-        <v>242</v>
-      </c>
-      <c r="AL6" t="s">
-        <v>243</v>
-      </c>
-      <c r="AM6" t="s">
-        <v>240</v>
-      </c>
-      <c r="AN6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AO6" t="s">
-        <v>240</v>
-      </c>
-      <c r="AP6" t="s">
-        <v>245</v>
-      </c>
-      <c r="AQ6" t="s">
-        <v>246</v>
-      </c>
-      <c r="AS6" t="s">
-        <v>240</v>
-      </c>
-      <c r="AT6" t="s">
-        <v>244</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="33" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C7" s="34" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="H7" s="34" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="I7" s="34" t="s">
         <v>62</v>
       </c>
       <c r="J7" s="35" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="K7" s="36"/>
       <c r="O7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="P7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="Q7" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="S7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="T7" t="s">
         <v>62</v>
       </c>
       <c r="V7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="W7" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="X7" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="Y7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="Z7" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AA7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AB7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AC7" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AE7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AF7">
         <v>83.3333333333333</v>
       </c>
       <c r="AH7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AI7">
         <v>83.3</v>
       </c>
       <c r="AJ7" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AK7">
         <v>8</v>
@@ -32315,13 +32357,13 @@
         <v>3</v>
       </c>
       <c r="AM7" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AN7">
         <v>52.2</v>
       </c>
       <c r="AO7" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AP7">
         <v>4.5</v>
@@ -32330,7 +32372,7 @@
         <v>33.6</v>
       </c>
       <c r="AS7" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AT7">
         <v>20.173600073636401</v>
@@ -32340,8 +32382,8 @@
       </c>
     </row>
     <row r="8" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="122" t="s">
-        <v>258</v>
+      <c r="A8" s="175" t="s">
+        <v>252</v>
       </c>
       <c r="B8" s="102"/>
       <c r="C8" s="102"/>
@@ -32407,19 +32449,19 @@
         <v>0.21724859954203968</v>
       </c>
       <c r="AE8" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="AF8">
         <v>83.3333333333333</v>
       </c>
       <c r="AH8" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="AI8">
         <v>83.3</v>
       </c>
       <c r="AJ8" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -32428,13 +32470,13 @@
         <v>3</v>
       </c>
       <c r="AM8" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AN8">
         <v>51.1</v>
       </c>
       <c r="AO8" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AP8">
         <v>3.7</v>
@@ -32443,7 +32485,7 @@
         <v>32.4</v>
       </c>
       <c r="AS8" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="AT8">
         <v>44.5724369425714</v>
@@ -32545,19 +32587,19 @@
         <v>0.12780422738436692</v>
       </c>
       <c r="AE9" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AF9">
         <v>59.375</v>
       </c>
       <c r="AH9" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AI9">
         <v>59.4</v>
       </c>
       <c r="AJ9" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AK9">
         <v>8</v>
@@ -32566,13 +32608,13 @@
         <v>1</v>
       </c>
       <c r="AM9" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AN9">
         <v>45.6</v>
       </c>
       <c r="AO9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AP9">
         <v>1.1000000000000001</v>
@@ -32581,7 +32623,7 @@
         <v>28.4</v>
       </c>
       <c r="AS9" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AT9">
         <v>28.571278521519002</v>
@@ -32683,19 +32725,19 @@
         <v>0.21268691268480011</v>
       </c>
       <c r="AE10" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AF10">
         <v>54</v>
       </c>
       <c r="AH10" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="AI10">
         <v>54</v>
       </c>
       <c r="AJ10" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AK10">
         <v>8</v>
@@ -32704,13 +32746,13 @@
         <v>3</v>
       </c>
       <c r="AM10" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="AN10">
         <v>44.8</v>
       </c>
       <c r="AO10" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AP10">
         <v>1.8</v>
@@ -32719,7 +32761,7 @@
         <v>25</v>
       </c>
       <c r="AS10" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AT10">
         <v>24.369253736000001</v>
@@ -32762,7 +32804,7 @@
       </c>
       <c r="I11" s="43">
         <f>'Watchlist Ratings'!BC7</f>
-        <v>6.1111111111111116E-2</v>
+        <v>6.3333333333333339E-2</v>
       </c>
       <c r="J11" s="44">
         <f ca="1">'Watchlist Ratings'!AW7</f>
@@ -32786,7 +32828,7 @@
       </c>
       <c r="T11" s="23">
         <f>'Watchlist Ratings'!BC7</f>
-        <v>6.1111111111111116E-2</v>
+        <v>6.3333333333333339E-2</v>
       </c>
       <c r="V11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -32821,19 +32863,19 @@
         <v>0.21900244611200459</v>
       </c>
       <c r="AE11" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AF11">
         <v>41.6666666666667</v>
       </c>
       <c r="AH11" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AI11">
         <v>41.7</v>
       </c>
       <c r="AJ11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AK11">
         <v>8</v>
@@ -32842,13 +32884,13 @@
         <v>2</v>
       </c>
       <c r="AM11" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AN11">
         <v>43.6</v>
       </c>
       <c r="AO11" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AP11">
         <v>0.6</v>
@@ -32857,7 +32899,7 @@
         <v>23.3</v>
       </c>
       <c r="AS11" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="AT11">
         <v>51.179748126470599</v>
@@ -32959,19 +33001,19 @@
         <v>8.4916787387159243E-2</v>
       </c>
       <c r="AE12" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AF12">
         <v>38.3333333333333</v>
       </c>
       <c r="AH12" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AI12">
         <v>38.299999999999997</v>
       </c>
       <c r="AJ12" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AK12">
         <v>7</v>
@@ -32980,13 +33022,13 @@
         <v>3</v>
       </c>
       <c r="AM12" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="AN12">
         <v>40.299999999999997</v>
       </c>
       <c r="AO12" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AP12">
         <v>-0.1</v>
@@ -32995,7 +33037,7 @@
         <v>20.8</v>
       </c>
       <c r="AS12" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AT12">
         <v>25.7039266520833</v>
@@ -33045,10 +33087,10 @@
         <v>22.249565544483985</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="M13" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="O13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -33103,19 +33145,19 @@
         <v>0.19745985531708032</v>
       </c>
       <c r="AE13" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AF13">
         <v>37.5</v>
       </c>
       <c r="AH13" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="AI13">
         <v>37.5</v>
       </c>
       <c r="AJ13" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AK13">
         <v>7</v>
@@ -33124,13 +33166,13 @@
         <v>3</v>
       </c>
       <c r="AM13" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="AN13">
         <v>38.9</v>
       </c>
       <c r="AO13" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="AP13">
         <v>4.7</v>
@@ -33139,7 +33181,7 @@
         <v>32.9</v>
       </c>
       <c r="AS13" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AT13">
         <v>29.589673076923098</v>
@@ -33189,7 +33231,7 @@
         <v>26.703442307692306</v>
       </c>
       <c r="L14" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="M14">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&gt;=8")</f>
@@ -33248,19 +33290,19 @@
         <v>0.12867081613737774</v>
       </c>
       <c r="AE14" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AF14">
         <v>37.142857142857103</v>
       </c>
       <c r="AH14" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="AI14">
         <v>37.1</v>
       </c>
       <c r="AJ14" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AK14">
         <v>7</v>
@@ -33269,13 +33311,13 @@
         <v>2</v>
       </c>
       <c r="AM14" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AN14">
         <v>38.5</v>
       </c>
       <c r="AO14" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AP14">
         <v>-4.2</v>
@@ -33284,7 +33326,7 @@
         <v>13.7</v>
       </c>
       <c r="AS14" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="AT14">
         <v>26.244954871232899</v>
@@ -33334,7 +33376,7 @@
         <v>26.560800363447559</v>
       </c>
       <c r="L15" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="M15">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN71,"&gt;=7",'Watchlist Ratings'!AN4:AN71,"&lt;8")</f>
@@ -33393,19 +33435,19 @@
         <v>0.25949207403006769</v>
       </c>
       <c r="AE15" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AF15">
         <v>36.1111111111111</v>
       </c>
       <c r="AH15" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AI15">
         <v>36.1</v>
       </c>
       <c r="AJ15" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AK15">
         <v>7</v>
@@ -33414,13 +33456,13 @@
         <v>2</v>
       </c>
       <c r="AM15" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AN15">
         <v>37.700000000000003</v>
       </c>
       <c r="AO15" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AP15">
         <v>-8</v>
@@ -33429,7 +33471,7 @@
         <v>13.5</v>
       </c>
       <c r="AS15" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AT15">
         <v>27.905545425233299</v>
@@ -33479,7 +33521,7 @@
         <v>36.235240624476425</v>
       </c>
       <c r="L16" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="M16">
         <f>COUNTIFS('Watchlist Ratings'!AN4:AN71,"&gt;=6",'Watchlist Ratings'!AN4:AN71,"&lt;7")</f>
@@ -33538,19 +33580,19 @@
         <v>2.2808301254799268E-2</v>
       </c>
       <c r="AE16" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="AF16">
         <v>32.142857142857103</v>
       </c>
       <c r="AH16" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="AI16">
         <v>32.1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="AK16">
         <v>7</v>
@@ -33559,13 +33601,13 @@
         <v>3</v>
       </c>
       <c r="AM16" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AN16">
         <v>29.6</v>
       </c>
       <c r="AO16" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AP16">
         <v>-7.9</v>
@@ -33574,7 +33616,7 @@
         <v>12.3</v>
       </c>
       <c r="AS16" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="AT16">
         <v>52.2229498644231</v>
@@ -33624,7 +33666,7 @@
         <v>37.159060432515382</v>
       </c>
       <c r="L17" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="M17">
         <f>COUNTIF('Watchlist Ratings'!AN4:AN71,"&lt;6")</f>
@@ -33683,7 +33725,7 @@
         <v>0.11301923910271405</v>
       </c>
       <c r="AS17" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AT17">
         <v>37.736707694444398</v>
@@ -33777,7 +33819,7 @@
         <v>9.4174490275463096E-2</v>
       </c>
       <c r="AS18" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="AT18">
         <v>24.612029698461502</v>
@@ -33871,7 +33913,7 @@
         <v>0.10741088468091919</v>
       </c>
       <c r="AS19" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AT19">
         <v>45.617441111111098</v>
@@ -33898,11 +33940,11 @@
       </c>
       <c r="E20" s="47">
         <f>'Watchlist Ratings'!AM16</f>
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="F20" s="47">
         <f>'Watchlist Ratings'!AN16</f>
-        <v>7.9</v>
+        <v>7.84</v>
       </c>
       <c r="G20" s="48">
         <f>'Watchlist Ratings'!K16</f>
@@ -33914,11 +33956,11 @@
       </c>
       <c r="I20" s="49">
         <f>'Watchlist Ratings'!BC16</f>
-        <v>0.20625000000000002</v>
+        <v>0.14514896867838048</v>
       </c>
       <c r="J20" s="50">
         <f ca="1">'Watchlist Ratings'!AW16</f>
-        <v>59.942949999999996</v>
+        <v>59.15153551912568</v>
       </c>
       <c r="O20" t="str">
         <f ca="1">'Watchlist Ratings'!B16</f>
@@ -33926,11 +33968,11 @@
       </c>
       <c r="P20" s="37">
         <f>'Watchlist Ratings'!AN16</f>
-        <v>7.9</v>
+        <v>7.84</v>
       </c>
       <c r="Q20" s="23">
         <f ca="1">'Watchlist Ratings'!BM16</f>
-        <v>-2.6426000842472375E-2</v>
+        <v>-6.630657915443261E-3</v>
       </c>
       <c r="V20" t="str">
         <f ca="1">'Watchlist Ratings'!B16</f>
@@ -33950,7 +33992,7 @@
       </c>
       <c r="Z20">
         <f ca="1">'Watchlist Ratings'!AW16</f>
-        <v>59.942949999999996</v>
+        <v>59.15153551912568</v>
       </c>
       <c r="AA20" t="str">
         <f ca="1">'Watchlist Ratings'!B16</f>
@@ -33958,14 +34000,14 @@
       </c>
       <c r="AB20">
         <f ca="1">'Watchlist Ratings'!BL16</f>
-        <v>-0.19206539792849897</v>
+        <v>-0.19083965708991213</v>
       </c>
       <c r="AC20">
         <f ca="1">'Watchlist Ratings'!BM16</f>
-        <v>-2.6426000842472375E-2</v>
+        <v>-6.630657915443261E-3</v>
       </c>
       <c r="AS20" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AT20">
         <v>43.630936634999998</v>
@@ -34059,7 +34101,7 @@
         <v>8.4171531047791737E-2</v>
       </c>
       <c r="AS21" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AT21">
         <v>38.120501266027397</v>
@@ -34168,8 +34210,8 @@
       </c>
     </row>
     <row r="24" spans="1:47" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="168" t="s">
-        <v>285</v>
+      <c r="A24" s="146" t="s">
+        <v>279</v>
       </c>
       <c r="B24" s="102"/>
       <c r="C24" s="102"/>
@@ -34196,11 +34238,11 @@
       </c>
       <c r="P25" s="37">
         <f>'Watchlist Ratings'!AN21</f>
-        <v>7.54</v>
+        <v>7.58</v>
       </c>
       <c r="Q25">
         <f ca="1">'Watchlist Ratings'!BM21</f>
-        <v>-5.6932641321074229E-2</v>
+        <v>-5.9816951414956021E-3</v>
       </c>
     </row>
     <row r="26" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -34244,7 +34286,7 @@
     <row r="38" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="39" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="40" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="L40" s="176"/>
+      <c r="L40" s="115"/>
       <c r="M40" s="102"/>
       <c r="N40" s="102"/>
       <c r="O40" s="102"/>
@@ -34261,7 +34303,7 @@
       <c r="Q41" s="57"/>
     </row>
     <row r="42" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="J42" s="178"/>
+      <c r="J42" s="119"/>
       <c r="K42" s="102"/>
       <c r="L42" s="102"/>
       <c r="M42" s="102"/>
@@ -34346,8 +34388,8 @@
     <row r="60" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="61" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="62" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="147" t="s">
-        <v>286</v>
+      <c r="A62" s="149" t="s">
+        <v>280</v>
       </c>
       <c r="B62" s="102"/>
       <c r="C62" s="102"/>
@@ -34357,7 +34399,7 @@
       <c r="G62" s="102"/>
       <c r="H62" s="102"/>
       <c r="J62" s="154" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K62" s="102"/>
       <c r="L62" s="102"/>
@@ -34369,52 +34411,52 @@
     </row>
     <row r="63" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="61" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B63" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="C63" s="61" t="s">
+        <v>283</v>
+      </c>
+      <c r="D63" s="61" t="s">
+        <v>284</v>
+      </c>
+      <c r="E63" s="61" t="s">
+        <v>248</v>
+      </c>
+      <c r="F63" s="61" t="s">
+        <v>247</v>
+      </c>
+      <c r="G63" s="61" t="s">
+        <v>285</v>
+      </c>
+      <c r="H63" s="61" t="s">
+        <v>286</v>
+      </c>
+      <c r="J63" s="62" t="s">
+        <v>234</v>
+      </c>
+      <c r="K63" s="62" t="s">
+        <v>287</v>
+      </c>
+      <c r="L63" s="62" t="s">
         <v>288</v>
       </c>
-      <c r="C63" s="61" t="s">
+      <c r="M63" s="62" t="s">
         <v>289</v>
       </c>
-      <c r="D63" s="61" t="s">
+      <c r="N63" s="62" t="s">
         <v>290</v>
       </c>
-      <c r="E63" s="61" t="s">
-        <v>254</v>
-      </c>
-      <c r="F63" s="61" t="s">
-        <v>253</v>
-      </c>
-      <c r="G63" s="61" t="s">
+      <c r="O63" s="62" t="s">
+        <v>236</v>
+      </c>
+      <c r="P63" s="62" t="s">
         <v>291</v>
       </c>
-      <c r="H63" s="61" t="s">
+      <c r="Q63" s="62" t="s">
         <v>292</v>
-      </c>
-      <c r="J63" s="62" t="s">
-        <v>240</v>
-      </c>
-      <c r="K63" s="62" t="s">
-        <v>293</v>
-      </c>
-      <c r="L63" s="62" t="s">
-        <v>294</v>
-      </c>
-      <c r="M63" s="62" t="s">
-        <v>295</v>
-      </c>
-      <c r="N63" s="62" t="s">
-        <v>296</v>
-      </c>
-      <c r="O63" s="62" t="s">
-        <v>242</v>
-      </c>
-      <c r="P63" s="62" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q63" s="62" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="4.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -34946,29 +34988,29 @@
       </c>
     </row>
     <row r="72" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="165" t="str">
+      <c r="A72" s="145" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="B72" s="166"/>
-      <c r="C72" s="166"/>
-      <c r="D72" s="166"/>
-      <c r="E72" s="166"/>
-      <c r="F72" s="166"/>
-      <c r="G72" s="166"/>
-      <c r="H72" s="166"/>
-      <c r="I72" s="167"/>
-      <c r="J72" s="175" t="str">
+      <c r="B72" s="113"/>
+      <c r="C72" s="113"/>
+      <c r="D72" s="113"/>
+      <c r="E72" s="113"/>
+      <c r="F72" s="113"/>
+      <c r="G72" s="113"/>
+      <c r="H72" s="113"/>
+      <c r="I72" s="114"/>
+      <c r="J72" s="112" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
         <v>NTO</v>
       </c>
-      <c r="K72" s="166"/>
-      <c r="L72" s="166"/>
-      <c r="M72" s="166"/>
-      <c r="N72" s="166"/>
-      <c r="O72" s="166"/>
-      <c r="P72" s="166"/>
-      <c r="Q72" s="167"/>
+      <c r="K72" s="113"/>
+      <c r="L72" s="113"/>
+      <c r="M72" s="113"/>
+      <c r="N72" s="113"/>
+      <c r="O72" s="113"/>
+      <c r="P72" s="113"/>
+      <c r="Q72" s="114"/>
     </row>
     <row r="73" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="68" t="str">
@@ -35038,7 +35080,7 @@
     </row>
     <row r="74" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="75" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B74" s="76" t="str">
         <f ca="1">VLOOKUP(A74,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35069,7 +35111,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J74" s="78" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="K74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35102,7 +35144,7 @@
     </row>
     <row r="75" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="79" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B75" s="80" t="str">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35133,7 +35175,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J75" s="79" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="K75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35165,8 +35207,8 @@
       </c>
     </row>
     <row r="76" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A76" s="140" t="s">
-        <v>299</v>
+      <c r="A76" s="165" t="s">
+        <v>293</v>
       </c>
       <c r="B76" s="102"/>
       <c r="C76" s="102"/>
@@ -35187,7 +35229,7 @@
     </row>
     <row r="77" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="79" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B77" s="80" t="str">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35218,7 +35260,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J77" s="79" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="K77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35251,129 +35293,129 @@
     </row>
     <row r="78" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="132" t="s">
-        <v>300</v>
-      </c>
-      <c r="B78" s="117"/>
-      <c r="C78" s="116" t="s">
-        <v>301</v>
-      </c>
-      <c r="D78" s="117"/>
-      <c r="E78" s="135" t="s">
-        <v>302</v>
-      </c>
-      <c r="F78" s="117"/>
-      <c r="G78" s="135" t="s">
-        <v>303</v>
-      </c>
-      <c r="H78" s="117"/>
-      <c r="I78" s="112" t="s">
-        <v>304</v>
+        <v>294</v>
+      </c>
+      <c r="B78" s="121"/>
+      <c r="C78" s="171" t="s">
+        <v>295</v>
+      </c>
+      <c r="D78" s="121"/>
+      <c r="E78" s="161" t="s">
+        <v>296</v>
+      </c>
+      <c r="F78" s="121"/>
+      <c r="G78" s="161" t="s">
+        <v>297</v>
+      </c>
+      <c r="H78" s="121"/>
+      <c r="I78" s="168" t="s">
+        <v>298</v>
       </c>
       <c r="J78" s="102"/>
       <c r="K78" s="132" t="s">
-        <v>305</v>
-      </c>
-      <c r="L78" s="117"/>
+        <v>299</v>
+      </c>
+      <c r="L78" s="121"/>
       <c r="M78" s="132" t="s">
-        <v>306</v>
-      </c>
-      <c r="N78" s="117"/>
+        <v>300</v>
+      </c>
+      <c r="N78" s="121"/>
       <c r="O78" s="132" t="s">
-        <v>307</v>
-      </c>
-      <c r="P78" s="117"/>
+        <v>301</v>
+      </c>
+      <c r="P78" s="121"/>
       <c r="Q78" s="82" t="str">
         <f>IF(K78&gt;=8.5,"🟢 ALTO",IF(K78&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="141" t="str">
+      <c r="A79" s="120" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AN:AN),'Watchlist Ratings'!AN:AN,0))</f>
         <v>CSU</v>
       </c>
-      <c r="B79" s="117"/>
-      <c r="C79" s="169" t="str">
+      <c r="B79" s="121"/>
+      <c r="C79" s="122" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM:BM),'Watchlist Ratings'!BM:BM,0))</f>
         <v>KSPI</v>
       </c>
-      <c r="D79" s="117"/>
-      <c r="E79" s="142" t="str">
+      <c r="D79" s="121"/>
+      <c r="E79" s="123" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BC:BC),'Watchlist Ratings'!BC:BC,0))</f>
         <v>NVDA</v>
       </c>
-      <c r="F79" s="117"/>
-      <c r="G79" s="142" t="str">
+      <c r="F79" s="121"/>
+      <c r="G79" s="123" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!K:K),'Watchlist Ratings'!K:K,0))</f>
         <v>VEEV</v>
       </c>
-      <c r="H79" s="117"/>
+      <c r="H79" s="121"/>
       <c r="I79" s="153" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!L:L),'Watchlist Ratings'!L:L,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J79" s="102"/>
-      <c r="K79" s="141" t="str">
+      <c r="K79" s="120" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!AM:AM),'Watchlist Ratings'!AM:AM,0))</f>
         <v>DSGX</v>
       </c>
-      <c r="L79" s="117"/>
-      <c r="M79" s="141" t="str">
+      <c r="L79" s="121"/>
+      <c r="M79" s="120" t="str">
         <f t="array" aca="1" ref="M79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MIN('Watchlist Ratings'!AW4:AW64),'Watchlist Ratings'!AW4:AW64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="N79" s="117"/>
-      <c r="O79" s="141" t="str">
+      <c r="N79" s="121"/>
+      <c r="O79" s="120" t="str">
         <f t="array" aca="1" ref="O79" ca="1">INDEX('Watchlist Ratings'!B:B,MATCH(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),'Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64,0)+3)</f>
         <v>OTLY</v>
       </c>
-      <c r="P79" s="117"/>
+      <c r="P79" s="121"/>
       <c r="Q79" s="79" t="str">
         <f ca="1">IF(K79&gt;=8.5,"🟢 ALTO",IF(K79&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="133">
+      <c r="A80" s="159">
         <f>MAX('Watchlist Ratings'!AN:AN)</f>
         <v>8.4499999999999993</v>
       </c>
-      <c r="B80" s="117"/>
-      <c r="C80" s="134">
+      <c r="B80" s="121"/>
+      <c r="C80" s="160">
         <f ca="1">MAX('Watchlist Ratings'!BM:BM)</f>
         <v>0.34861805110601995</v>
       </c>
-      <c r="D80" s="117"/>
-      <c r="E80" s="138">
+      <c r="D80" s="121"/>
+      <c r="E80" s="163">
         <f>MAX('Watchlist Ratings'!BC:BC)</f>
         <v>0.63420845122686575</v>
       </c>
-      <c r="F80" s="117"/>
-      <c r="G80" s="138" t="str">
+      <c r="F80" s="121"/>
+      <c r="G80" s="163" t="str">
         <f>MAX('Watchlist Ratings'!K:K)&amp;"/8"</f>
         <v>8/8</v>
       </c>
-      <c r="H80" s="117"/>
-      <c r="I80" s="171" t="str">
+      <c r="H80" s="121"/>
+      <c r="I80" s="125" t="str">
         <f>MAX('Watchlist Ratings'!L:L)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J80" s="102"/>
-      <c r="K80" s="172">
+      <c r="K80" s="126">
         <f>MAX('Watchlist Ratings'!AM:AM)</f>
         <v>8.7100000000000009</v>
       </c>
-      <c r="L80" s="117"/>
-      <c r="M80" s="172" t="str">
+      <c r="L80" s="121"/>
+      <c r="M80" s="126" t="str">
         <f ca="1">MIN('Watchlist Ratings'!AW4:AW64)&amp;"x"</f>
-        <v>-19.522744352x</v>
-      </c>
-      <c r="N80" s="117"/>
-      <c r="O80" s="172" t="str">
+        <v>-45.9971332237443x</v>
+      </c>
+      <c r="N80" s="121"/>
+      <c r="O80" s="126" t="str">
         <f t="array" aca="1" ref="O80" ca="1">TEXT(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),"0.0%")</f>
-        <v>238.2%</v>
-      </c>
-      <c r="P80" s="117"/>
+        <v>221.3%</v>
+      </c>
+      <c r="P80" s="121"/>
       <c r="Q80" s="82" t="str">
         <f>IF(K80&gt;=8.5,"🟢 ALTO",IF(K80&gt;=7.5,"🟡 MEDIO","🔴 BAJO"))</f>
         <v>🟢 ALTO</v>
@@ -35381,7 +35423,7 @@
     </row>
     <row r="81" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="79" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B81" s="80" t="str">
         <f ca="1">VLOOKUP(A81,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35412,7 +35454,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J81" s="79" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="K81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35444,8 +35486,8 @@
       </c>
     </row>
     <row r="82" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="173" t="s">
-        <v>308</v>
+      <c r="A82" s="127" t="s">
+        <v>302</v>
       </c>
       <c r="B82" s="102"/>
       <c r="C82" s="102"/>
@@ -35466,7 +35508,7 @@
     </row>
     <row r="83" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="83" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B83" s="84" t="str">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$71,4,FALSE())</f>
@@ -35497,7 +35539,7 @@
         <v>🟢 BUY</v>
       </c>
       <c r="J83" s="83" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="K83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$71,36,FALSE())</f>
@@ -35531,7 +35573,7 @@
     <row r="84" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="85" spans="1:17" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="152" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B85" s="102"/>
       <c r="C85" s="102"/>
@@ -35552,41 +35594,41 @@
     </row>
     <row r="86" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="87" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="174" t="s">
+      <c r="A87" s="128" t="s">
+        <v>294</v>
+      </c>
+      <c r="B87" s="102"/>
+      <c r="C87" s="173" t="s">
+        <v>295</v>
+      </c>
+      <c r="D87" s="102"/>
+      <c r="E87" s="124" t="s">
+        <v>296</v>
+      </c>
+      <c r="F87" s="102"/>
+      <c r="G87" s="150" t="s">
+        <v>297</v>
+      </c>
+      <c r="H87" s="102"/>
+      <c r="I87" s="151" t="s">
+        <v>298</v>
+      </c>
+      <c r="J87" s="102"/>
+      <c r="K87" s="172" t="s">
+        <v>299</v>
+      </c>
+      <c r="L87" s="102"/>
+      <c r="M87" s="148" t="s">
         <v>300</v>
-      </c>
-      <c r="B87" s="102"/>
-      <c r="C87" s="119" t="s">
-        <v>301</v>
-      </c>
-      <c r="D87" s="102"/>
-      <c r="E87" s="170" t="s">
-        <v>302</v>
-      </c>
-      <c r="F87" s="102"/>
-      <c r="G87" s="148" t="s">
-        <v>303</v>
-      </c>
-      <c r="H87" s="102"/>
-      <c r="I87" s="149" t="s">
-        <v>304</v>
-      </c>
-      <c r="J87" s="102"/>
-      <c r="K87" s="118" t="s">
-        <v>305</v>
-      </c>
-      <c r="L87" s="102"/>
-      <c r="M87" s="145" t="s">
-        <v>306</v>
       </c>
       <c r="N87" s="102"/>
       <c r="O87" s="155" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="P87" s="102"/>
     </row>
     <row r="88" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A88" s="146" t="str">
+      <c r="A88" s="118" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AN$4:AN$71),'Watchlist Ratings'!AN$4:AN$71,0))</f>
         <v>CSU</v>
       </c>
@@ -35596,83 +35638,83 @@
         <v>KSPI</v>
       </c>
       <c r="D88" s="102"/>
-      <c r="E88" s="146" t="str">
+      <c r="E88" s="118" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!BC$4:BC$71),'Watchlist Ratings'!BC$4:BC$71,0))</f>
         <v>NVDA</v>
       </c>
       <c r="F88" s="102"/>
-      <c r="G88" s="146" t="str">
+      <c r="G88" s="118" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!K$4:K$71),'Watchlist Ratings'!K$4:K$71,0))</f>
         <v>VEEV</v>
       </c>
       <c r="H88" s="102"/>
-      <c r="I88" s="146" t="str">
+      <c r="I88" s="118" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!L$4:L$71),'Watchlist Ratings'!L$4:L$71,0))</f>
         <v>MSFT</v>
       </c>
       <c r="J88" s="102"/>
-      <c r="K88" s="146" t="str">
+      <c r="K88" s="118" t="str">
         <f ca="1">INDEX('Watchlist Ratings'!B$4:B$71,MATCH(MAX('Watchlist Ratings'!AM$4:AM$71),'Watchlist Ratings'!AM$4:AM$71,0))</f>
         <v>DSGX</v>
       </c>
       <c r="L88" s="102"/>
-      <c r="M88" s="146" t="str">
+      <c r="M88" s="118" t="str">
         <f t="array" aca="1" ref="M88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64)),IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64),0))</f>
         <v>KSPI</v>
       </c>
       <c r="N88" s="102"/>
-      <c r="O88" s="146" t="str">
+      <c r="O88" s="118" t="str">
         <f t="array" aca="1" ref="O88" ca="1">INDEX('Watchlist Ratings'!B$4:B$64,MATCH(MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64),'Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64,0))</f>
         <v>OTLY</v>
       </c>
       <c r="P88" s="102"/>
     </row>
     <row r="89" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="144">
+      <c r="A89" s="147">
         <f>MAX('Watchlist Ratings'!AN$4:AN$71)</f>
         <v>8.4499999999999993</v>
       </c>
       <c r="B89" s="102"/>
-      <c r="C89" s="151">
+      <c r="C89" s="117">
         <f ca="1">MAX('Watchlist Ratings'!BM$4:BM$64)</f>
         <v>0.34861805110601995</v>
       </c>
       <c r="D89" s="102"/>
-      <c r="E89" s="151">
+      <c r="E89" s="117">
         <f>MAX('Watchlist Ratings'!BC$4:BC$71)</f>
         <v>0.63420845122686575</v>
       </c>
       <c r="F89" s="102"/>
-      <c r="G89" s="150" t="str">
+      <c r="G89" s="111" t="str">
         <f>MAX('Watchlist Ratings'!K$4:K$71)&amp;"/8"</f>
         <v>8/8</v>
       </c>
       <c r="H89" s="102"/>
-      <c r="I89" s="150" t="str">
+      <c r="I89" s="111" t="str">
         <f>MAX('Watchlist Ratings'!L$4:L$71)&amp;"/3"</f>
         <v>3/3</v>
       </c>
       <c r="J89" s="102"/>
-      <c r="K89" s="177">
+      <c r="K89" s="116">
         <f>MAX('Watchlist Ratings'!AM$4:AM$71)</f>
         <v>8.7100000000000009</v>
       </c>
       <c r="L89" s="102"/>
-      <c r="M89" s="150" t="str">
+      <c r="M89" s="111" t="str">
         <f t="array" aca="1" ref="M89" ca="1">MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64))&amp;"x"</f>
         <v>9.1219709975982x</v>
       </c>
       <c r="N89" s="102"/>
-      <c r="O89" s="150">
+      <c r="O89" s="111">
         <f t="array" aca="1" ref="O89" ca="1">MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64)</f>
-        <v>2.382151208725046</v>
+        <v>2.213371296902098</v>
       </c>
       <c r="P89" s="102"/>
     </row>
     <row r="90" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="91" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="111" t="s">
-        <v>308</v>
+      <c r="A91" s="167" t="s">
+        <v>302</v>
       </c>
       <c r="B91" s="102"/>
       <c r="C91" s="102"/>
@@ -35693,44 +35735,38 @@
     </row>
   </sheetData>
   <mergeCells count="86">
-    <mergeCell ref="I89:J89"/>
-    <mergeCell ref="J72:Q72"/>
-    <mergeCell ref="L40:R40"/>
-    <mergeCell ref="K89:L89"/>
-    <mergeCell ref="C89:D89"/>
-    <mergeCell ref="O88:P88"/>
-    <mergeCell ref="J42:Q42"/>
-    <mergeCell ref="O89:P89"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="M79:N79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="K88:L88"/>
-    <mergeCell ref="E79:F79"/>
-    <mergeCell ref="M88:N88"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="I80:J80"/>
-    <mergeCell ref="K80:L80"/>
-    <mergeCell ref="A82:Q82"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="K79:L79"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="M80:N80"/>
-    <mergeCell ref="O80:P80"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="K78:L78"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A24:R24"/>
-    <mergeCell ref="O78:P78"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A91:Q91"/>
+    <mergeCell ref="I78:J78"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G78:H78"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E80:F80"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G80:H80"/>
+    <mergeCell ref="A76:Q76"/>
+    <mergeCell ref="O79:P79"/>
+    <mergeCell ref="G79:H79"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="M87:N87"/>
     <mergeCell ref="G88:H88"/>
@@ -35747,38 +35783,44 @@
     <mergeCell ref="O87:P87"/>
     <mergeCell ref="C88:D88"/>
     <mergeCell ref="E88:F88"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="M78:N78"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G78:H78"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="E80:F80"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G80:H80"/>
-    <mergeCell ref="A76:Q76"/>
-    <mergeCell ref="O79:P79"/>
-    <mergeCell ref="G79:H79"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A91:Q91"/>
-    <mergeCell ref="I78:J78"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A24:R24"/>
+    <mergeCell ref="O78:P78"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="E79:F79"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="I80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="A82:Q82"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="O80:P80"/>
+    <mergeCell ref="I89:J89"/>
+    <mergeCell ref="J72:Q72"/>
+    <mergeCell ref="L40:R40"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="O88:P88"/>
+    <mergeCell ref="J42:Q42"/>
+    <mergeCell ref="O89:P89"/>
   </mergeCells>
   <conditionalFormatting sqref="F9:F22">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -35821,7 +35863,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E212"/>
+  <dimension ref="A1:E222"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -35832,3606 +35874,3776 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B1" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D1" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="E1" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D2" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="D3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E4" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D5" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="E5" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B6" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C6" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D6" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="E6" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B7" t="s">
         <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D7" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="E7" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="E8" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B9" t="s">
         <v>91</v>
       </c>
       <c r="C9" t="s">
+        <v>325</v>
+      </c>
+      <c r="D9" t="s">
         <v>331</v>
       </c>
-      <c r="D9" t="s">
-        <v>337</v>
-      </c>
       <c r="E9" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B10" t="s">
         <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E10" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B11" t="s">
         <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E11" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B12" t="s">
         <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D12" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="E12" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
         <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D13" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="E13" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B14" t="s">
         <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D14" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E14" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B15" t="s">
         <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D15" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="E15" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B16" t="s">
         <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D16" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E16" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B17" t="s">
         <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D17" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="E17" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B18" t="s">
         <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D18" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E18" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B19" t="s">
         <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D19" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E19" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B20" t="s">
         <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D20" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="E20" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s">
         <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D21" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E21" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B22" t="s">
         <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D22" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E22" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B23" t="s">
         <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D23" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E23" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s">
         <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D24" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E24" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B25" t="s">
         <v>97</v>
       </c>
       <c r="C25" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D25" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E25" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B26" t="s">
         <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D26" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E26" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s">
         <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D27" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E27" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s">
         <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D28" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E28" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B29" t="s">
         <v>97</v>
       </c>
       <c r="C29" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D29" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E29" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B30" t="s">
         <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D30" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E30" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B31" t="s">
         <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D31" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E31" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B32" t="s">
         <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D32" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E32" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B33" t="s">
         <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D33" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E33" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B34" t="s">
         <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D34" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E34" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B35" t="s">
         <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D35" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E35" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B36" t="s">
         <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D36" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E36" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B37" t="s">
         <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D37" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E37" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s">
         <v>97</v>
       </c>
       <c r="C38" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D38" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E38" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B39" t="s">
         <v>97</v>
       </c>
       <c r="C39" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D39" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E39" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s">
         <v>97</v>
       </c>
       <c r="C40" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D40" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E40" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B41" t="s">
         <v>97</v>
       </c>
       <c r="C41" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D41" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E41" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B42" t="s">
         <v>97</v>
       </c>
       <c r="C42" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D42" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E42" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s">
         <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D43" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E43" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s">
         <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D44" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E44" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B45" t="s">
         <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D45" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E45" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B46" t="s">
         <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D46" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E46" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B47" t="s">
         <v>97</v>
       </c>
       <c r="C47" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="D47" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="E47" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B48" t="s">
         <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D48" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E48" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B49" t="s">
         <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D49" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E49" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B50" t="s">
         <v>105</v>
       </c>
       <c r="C50" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D50" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="E50" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B51" t="s">
         <v>105</v>
       </c>
       <c r="C51" t="s">
+        <v>390</v>
+      </c>
+      <c r="D51" t="s">
         <v>396</v>
       </c>
-      <c r="D51" t="s">
-        <v>402</v>
-      </c>
       <c r="E51" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s">
         <v>105</v>
       </c>
       <c r="C52" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D52" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E52" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s">
         <v>105</v>
       </c>
       <c r="C53" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D53" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="E53" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="B54" t="s">
         <v>105</v>
       </c>
       <c r="C54" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D54" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="E54" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s">
         <v>105</v>
       </c>
       <c r="C55" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D55" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="E55" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B56" t="s">
         <v>105</v>
       </c>
       <c r="C56" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="D56" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="E56" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B57" t="s">
         <v>105</v>
       </c>
       <c r="C57" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D57" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="E57" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s">
         <v>105</v>
       </c>
       <c r="C58" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D58" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E58" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B59" t="s">
         <v>105</v>
       </c>
       <c r="C59" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E59" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B60" t="s">
         <v>105</v>
       </c>
       <c r="C60" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D60" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E60" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B61" t="s">
         <v>105</v>
       </c>
       <c r="C61" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D61" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E61" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B62" t="s">
         <v>105</v>
       </c>
       <c r="C62" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D62" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E62" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B63" t="s">
         <v>105</v>
       </c>
       <c r="C63" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="E63" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B64" t="s">
         <v>105</v>
       </c>
       <c r="C64" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E64" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B65" t="s">
         <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="E65" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B66" t="s">
         <v>105</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E66" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B67" t="s">
         <v>105</v>
       </c>
       <c r="C67" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D67" t="s">
+        <v>423</v>
+      </c>
+      <c r="E67" t="s">
         <v>429</v>
-      </c>
-      <c r="E67" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s">
         <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D68" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E68" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B69" t="s">
         <v>105</v>
       </c>
       <c r="C69" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D69" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="E69" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B70" t="s">
         <v>105</v>
       </c>
       <c r="C70" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D70" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="E70" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B71" t="s">
         <v>105</v>
       </c>
       <c r="C71" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E71" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B72" t="s">
         <v>105</v>
       </c>
       <c r="C72" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="E72" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B73" t="s">
         <v>105</v>
       </c>
       <c r="C73" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D73" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E73" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B74" t="s">
         <v>105</v>
       </c>
       <c r="C74" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="E74" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B75" t="s">
         <v>105</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D75" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E75" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B76" t="s">
         <v>105</v>
       </c>
       <c r="C76" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D76" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="E76" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B77" t="s">
         <v>105</v>
       </c>
       <c r="C77" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D77" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="E77" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B78" t="s">
         <v>105</v>
       </c>
       <c r="C78" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D78" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="E78" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B79" t="s">
         <v>105</v>
       </c>
       <c r="C79" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D79" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="E79" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B80" t="s">
         <v>105</v>
       </c>
       <c r="C80" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D80" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="E80" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B81" t="s">
         <v>105</v>
       </c>
       <c r="C81" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D81" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E81" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B82" t="s">
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D82" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="E82" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B83" t="s">
         <v>105</v>
       </c>
       <c r="C83" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="D83" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="E83" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B84" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C84" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D84" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="E84" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B85" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C85" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D85" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="E85" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B86" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C86" t="s">
+        <v>457</v>
+      </c>
+      <c r="D86" t="s">
         <v>463</v>
       </c>
-      <c r="D86" t="s">
-        <v>469</v>
-      </c>
       <c r="E86" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B87" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C87" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D87" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="E87" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B88" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C88" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D88" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="E88" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B89" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C89" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D89" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="E89" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B90" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C90" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D90" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="E90" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="B91" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C91" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D91" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="E91" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B92" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C92" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D92" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="E92" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C93" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D93" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="E93" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B94" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C94" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="D94" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E94" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B95" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C95" t="s">
+        <v>479</v>
+      </c>
+      <c r="D95" t="s">
+        <v>484</v>
+      </c>
+      <c r="E95" t="s">
         <v>485</v>
-      </c>
-      <c r="D95" t="s">
-        <v>490</v>
-      </c>
-      <c r="E95" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B96" t="s">
         <v>83</v>
       </c>
       <c r="C96" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D96" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="E96" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B97" t="s">
         <v>83</v>
       </c>
       <c r="C97" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D97" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="E97" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B98" t="s">
         <v>83</v>
       </c>
       <c r="C98" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D98" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="E98" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B99" t="s">
         <v>83</v>
       </c>
       <c r="C99" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D99" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="E99" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B100" t="s">
         <v>83</v>
       </c>
       <c r="C100" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D100" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
       <c r="E100" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B101" t="s">
         <v>83</v>
       </c>
       <c r="C101" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D101" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="E101" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="B102" t="s">
         <v>83</v>
       </c>
       <c r="C102" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D102" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="E102" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B103" t="s">
         <v>79</v>
       </c>
       <c r="C103" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="D103" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="E103" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B104" t="s">
         <v>79</v>
       </c>
       <c r="C104" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="D104" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="E104" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B105" t="s">
         <v>79</v>
       </c>
       <c r="C105" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D105" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="E105" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B106" t="s">
         <v>79</v>
       </c>
       <c r="C106" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="D106" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="E106" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="B107" t="s">
         <v>79</v>
       </c>
       <c r="C107" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="D107" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="E107" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B108" t="s">
         <v>79</v>
       </c>
       <c r="C108" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D108" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="E108" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B109" t="s">
         <v>79</v>
       </c>
       <c r="C109" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="D109" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="E109" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B110" t="s">
         <v>79</v>
       </c>
       <c r="C110" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="D110" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="E110" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B111" s="97">
         <v>46254</v>
       </c>
       <c r="C111" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="D111" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="E111" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B112" s="97">
         <v>46254</v>
       </c>
       <c r="C112" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="D112" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="E112" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B113" s="97">
         <v>46254</v>
       </c>
       <c r="C113" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D113" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="E113" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B114" s="97">
         <v>46254</v>
       </c>
       <c r="C114" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="D114" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="E114" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B115" s="97">
         <v>46255</v>
       </c>
       <c r="C115" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D115" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="E115" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B116" s="97">
         <v>46255</v>
       </c>
       <c r="C116" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="D116" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="E116" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B117" s="97">
         <v>46255</v>
       </c>
       <c r="C117" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="D117" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="E117" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B118" s="97">
         <v>46255</v>
       </c>
       <c r="C118" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="D118" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="E118" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B119" s="97">
         <v>46255</v>
       </c>
       <c r="C119" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="D119" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E119" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B120" s="97">
         <v>46255</v>
       </c>
       <c r="C120" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D120" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E120" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B121" s="97">
         <v>46255</v>
       </c>
       <c r="C121" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="D121" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E121" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B122" s="97">
         <v>46255</v>
       </c>
       <c r="C122" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D122" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E122" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B123" s="97">
         <v>46255</v>
       </c>
       <c r="C123" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="D123" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E123" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B124" s="97">
         <v>46255</v>
       </c>
       <c r="C124" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="D124" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E124" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B125" s="97">
         <v>46255</v>
       </c>
       <c r="C125" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D125" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E125" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B126" s="97">
         <v>46255</v>
       </c>
       <c r="C126" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D126" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E126" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B127" s="97">
         <v>46255</v>
       </c>
       <c r="C127" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D127" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E127" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B128" s="97">
         <v>46255</v>
       </c>
       <c r="C128" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D128" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E128" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B129" s="97">
         <v>46255</v>
       </c>
       <c r="C129" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D129" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E129" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B130" s="97">
         <v>46255</v>
       </c>
       <c r="C130" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="D130" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E130" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B131" s="97">
         <v>46255</v>
       </c>
       <c r="C131" t="s">
+        <v>575</v>
+      </c>
+      <c r="D131" t="s">
+        <v>562</v>
+      </c>
+      <c r="E131" t="s">
         <v>581</v>
-      </c>
-      <c r="D131" t="s">
-        <v>568</v>
-      </c>
-      <c r="E131" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B132" s="97">
         <v>46255</v>
       </c>
       <c r="C132" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D132" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E132" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B133" s="97">
         <v>46255</v>
       </c>
       <c r="C133" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D133" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E133" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B134" s="97">
         <v>46255</v>
       </c>
       <c r="C134" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D134" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E134" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B135" s="97">
         <v>46255</v>
       </c>
       <c r="C135" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="D135" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E135" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B136" s="97">
         <v>46255</v>
       </c>
       <c r="C136" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D136" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E136" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B137" s="97">
         <v>46255</v>
       </c>
       <c r="C137" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D137" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E137" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B138" s="97">
         <v>46255</v>
       </c>
       <c r="C138" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="D138" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="E138" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B139" s="97">
         <v>46255</v>
       </c>
       <c r="C139" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="D139" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="E139" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B140" s="97">
         <v>46255</v>
       </c>
       <c r="C140" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D140" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E140" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B141" s="97">
         <v>46255</v>
       </c>
       <c r="C141" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="D141" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E141" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B142" s="97">
         <v>46255</v>
       </c>
       <c r="C142" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="D142" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E142" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B143" s="97">
         <v>46255</v>
       </c>
       <c r="C143" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="D143" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E143" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B144" s="97">
         <v>46255</v>
       </c>
       <c r="C144" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="D144" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E144" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B145" s="97">
         <v>46255</v>
       </c>
       <c r="C145" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D145" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E145" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B146" s="97">
         <v>46256</v>
       </c>
       <c r="C146" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="D146" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="E146" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B147" s="97">
         <v>46256</v>
       </c>
       <c r="C147" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="D147" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="E147" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B148" s="97">
         <v>46256</v>
       </c>
       <c r="C148" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D148" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="E148" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B149" s="97">
         <v>46256</v>
       </c>
       <c r="C149" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="D149" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="E149" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B150" s="97">
         <v>46256</v>
       </c>
       <c r="C150" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D150" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="E150" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B151" s="97">
         <v>46256</v>
       </c>
       <c r="C151" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D151" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="E151" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B152" s="97">
         <v>46256</v>
       </c>
       <c r="C152" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D152" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="E152" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B153" s="97">
         <v>46256</v>
       </c>
       <c r="C153" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D153" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="E153" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B154" s="97">
         <v>46256</v>
       </c>
       <c r="C154" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D154" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="E154" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B155" s="97">
         <v>46256</v>
       </c>
       <c r="C155" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="D155" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="E155" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B156" s="97">
         <v>46256</v>
       </c>
       <c r="C156" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="D156" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="E156" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B157" s="97">
         <v>46256</v>
       </c>
       <c r="C157" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D157" t="s">
+        <v>647</v>
+      </c>
+      <c r="E157" t="s">
         <v>653</v>
-      </c>
-      <c r="E157" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B158" s="97">
         <v>46256</v>
       </c>
       <c r="C158" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="D158" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E158" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B159" s="97">
         <v>46256</v>
       </c>
       <c r="C159" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="D159" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E159" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B160" s="97">
         <v>46256</v>
       </c>
       <c r="C160" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="D160" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E160" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B161" s="97">
         <v>46256</v>
       </c>
       <c r="C161" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D161" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E161" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B162" s="97">
         <v>46256</v>
       </c>
       <c r="C162" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="D162" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E162" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="B163" s="97">
         <v>46256</v>
       </c>
       <c r="C163" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D163" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E163" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B164" s="97">
         <v>46256</v>
       </c>
       <c r="C164" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="D164" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="E164" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B165">
         <v>46259</v>
       </c>
       <c r="C165" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="D165" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E165" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B166">
         <v>46259</v>
       </c>
       <c r="C166" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D166" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="E166" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B167">
         <v>46259</v>
       </c>
       <c r="C167" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D167" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="E167" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B168">
         <v>46259</v>
       </c>
       <c r="C168" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D168" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E168" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B169">
         <v>46259</v>
       </c>
       <c r="C169" t="s">
+        <v>693</v>
+      </c>
+      <c r="D169" t="s">
+        <v>698</v>
+      </c>
+      <c r="E169" t="s">
         <v>699</v>
-      </c>
-      <c r="D169" t="s">
-        <v>704</v>
-      </c>
-      <c r="E169" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B170">
         <v>46259</v>
       </c>
       <c r="C170" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D170" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E170" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B171">
         <v>46259</v>
       </c>
       <c r="C171" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D171" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="E171" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="B172">
         <v>46259</v>
       </c>
       <c r="C172" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D172" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="E172" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="B173">
         <v>46259</v>
       </c>
       <c r="C173" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="D173" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="E173" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="B174">
         <v>46259</v>
       </c>
       <c r="C174" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="D174" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="E174" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B175">
         <v>46259</v>
       </c>
       <c r="C175" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D175" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="E175" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B176">
         <v>46259</v>
       </c>
       <c r="C176" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D176" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="E176" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B177">
         <v>46259</v>
       </c>
       <c r="C177" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="D177" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="E177" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B178">
         <v>46259</v>
       </c>
       <c r="C178" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="D178" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="E178" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B179">
         <v>46259</v>
       </c>
       <c r="C179" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D179" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="E179" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B180">
         <v>46259</v>
       </c>
       <c r="C180" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="D180" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="E180" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B181">
         <v>46259</v>
       </c>
       <c r="C181" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="D181" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="E181" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="B182">
         <v>46259</v>
       </c>
       <c r="C182" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="D182" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="E182" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="B183">
         <v>46259</v>
       </c>
       <c r="C183" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="D183" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="E183" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B184">
         <v>46259</v>
       </c>
       <c r="C184" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="D184" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="E184" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B185">
         <v>46259</v>
       </c>
       <c r="C185" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="D185" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="E185" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B186">
         <v>46259</v>
       </c>
       <c r="C186" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="D186" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="E186" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B187">
         <v>46259</v>
       </c>
       <c r="C187" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="D187" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E187" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B188">
         <v>46259</v>
       </c>
       <c r="C188" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D188" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E188" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B189">
         <v>46259</v>
       </c>
       <c r="C189" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D189" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E189" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B190">
         <v>46259</v>
       </c>
       <c r="C190" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D190" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E190" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="B191">
         <v>46259</v>
       </c>
       <c r="C191" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D191" t="s">
+        <v>744</v>
+      </c>
+      <c r="E191" t="s">
         <v>750</v>
-      </c>
-      <c r="E191" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B192">
         <v>46259</v>
       </c>
       <c r="C192" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D192" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E192" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B193">
         <v>46259</v>
       </c>
       <c r="C193" t="s">
+        <v>746</v>
+      </c>
+      <c r="D193" t="s">
+        <v>744</v>
+      </c>
+      <c r="E193" t="s">
         <v>752</v>
-      </c>
-      <c r="D193" t="s">
-        <v>750</v>
-      </c>
-      <c r="E193" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B194">
         <v>46259</v>
       </c>
       <c r="C194" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D194" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E194" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="B195">
         <v>46259</v>
       </c>
       <c r="C195" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D195" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E195" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="B196">
         <v>46259</v>
       </c>
       <c r="C196" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D196" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E196" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B197">
         <v>46259</v>
       </c>
       <c r="C197" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D197" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E197" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B198">
         <v>46259</v>
       </c>
       <c r="C198" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D198" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E198" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="B199">
         <v>46259</v>
       </c>
       <c r="C199" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D199" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E199" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="B200">
         <v>46259</v>
       </c>
       <c r="C200" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D200" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E200" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B201">
         <v>46259</v>
       </c>
       <c r="C201" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D201" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E201" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B202">
         <v>46259</v>
       </c>
       <c r="C202" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D202" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E202" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B203">
         <v>46259</v>
       </c>
       <c r="C203" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D203" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E203" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="B204">
         <v>46259</v>
       </c>
       <c r="C204" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D204" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E204" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B205">
         <v>46259</v>
       </c>
       <c r="C205" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D205" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E205" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B206">
         <v>46259</v>
       </c>
       <c r="C206" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D206" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E206" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B207">
         <v>46259</v>
       </c>
       <c r="C207" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="D207" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E207" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B208">
         <v>46259</v>
       </c>
       <c r="C208" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="D208" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E208" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="B209">
         <v>46259</v>
       </c>
       <c r="C209" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="D209" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E209" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B210">
         <v>46259</v>
       </c>
       <c r="C210" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="D210" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="E210" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="B211">
         <v>46259</v>
       </c>
       <c r="C211" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="D211" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="E211" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="B212">
         <v>46259</v>
       </c>
       <c r="C212" t="s">
+        <v>776</v>
+      </c>
+      <c r="D212" t="s">
+        <v>774</v>
+      </c>
+      <c r="E212" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>375</v>
+      </c>
+      <c r="B213">
+        <v>46259</v>
+      </c>
+      <c r="C213" t="s">
+        <v>779</v>
+      </c>
+      <c r="D213" t="s">
+        <v>780</v>
+      </c>
+      <c r="E213" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>328</v>
+      </c>
+      <c r="B214">
+        <v>46259</v>
+      </c>
+      <c r="C214" t="s">
+        <v>667</v>
+      </c>
+      <c r="D214" t="s">
+        <v>780</v>
+      </c>
+      <c r="E214" t="s">
         <v>782</v>
       </c>
-      <c r="D212" t="s">
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>336</v>
+      </c>
+      <c r="B215">
+        <v>46259</v>
+      </c>
+      <c r="C215" t="s">
+        <v>783</v>
+      </c>
+      <c r="D215" t="s">
         <v>780</v>
       </c>
-      <c r="E212" t="s">
-        <v>783</v>
+      <c r="E215" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>272</v>
+      </c>
+      <c r="B216">
+        <v>46259</v>
+      </c>
+      <c r="C216" t="s">
+        <v>785</v>
+      </c>
+      <c r="D216" t="s">
+        <v>780</v>
+      </c>
+      <c r="E216" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>258</v>
+      </c>
+      <c r="B217">
+        <v>46259</v>
+      </c>
+      <c r="C217" t="s">
+        <v>787</v>
+      </c>
+      <c r="D217" t="s">
+        <v>780</v>
+      </c>
+      <c r="E217" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>257</v>
+      </c>
+      <c r="B218">
+        <v>46259</v>
+      </c>
+      <c r="C218" t="s">
+        <v>789</v>
+      </c>
+      <c r="D218" t="s">
+        <v>780</v>
+      </c>
+      <c r="E218" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>405</v>
+      </c>
+      <c r="B219">
+        <v>46259</v>
+      </c>
+      <c r="C219" t="s">
+        <v>791</v>
+      </c>
+      <c r="D219" t="s">
+        <v>780</v>
+      </c>
+      <c r="E219" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>389</v>
+      </c>
+      <c r="B220">
+        <v>46259</v>
+      </c>
+      <c r="C220" t="s">
+        <v>793</v>
+      </c>
+      <c r="D220" t="s">
+        <v>780</v>
+      </c>
+      <c r="E220" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>261</v>
+      </c>
+      <c r="B221">
+        <v>46259</v>
+      </c>
+      <c r="C221" t="s">
+        <v>795</v>
+      </c>
+      <c r="D221" t="s">
+        <v>796</v>
+      </c>
+      <c r="E221" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>453</v>
+      </c>
+      <c r="B222">
+        <v>46259</v>
+      </c>
+      <c r="C222" t="s">
+        <v>770</v>
+      </c>
+      <c r="D222" t="s">
+        <v>780</v>
+      </c>
+      <c r="E222" t="s">
+        <v>798</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Cosas Roger\BOLSA E INVERSIÓN\repos\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1A780B-12A6-4BD2-8FAF-83690C08BF3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8953462F-95FD-4E3B-952E-48E297AE4D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2463,7 +2463,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1743" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="816">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -4419,9 +4419,6 @@
     <t>Precision: el objetivo es estar aproximadamente acertado, no exactamente equivocado. Un error del 10% en el capex de mantenimiento mueve el FCF normalizado mucho menos que la diferencia entre usar el FCF reportado o no usarlo.</t>
   </si>
   <si>
-    <t>OJO: el FCF normalizado NO sustituye a las columnas FCF@5y, que siguen siendo la vision forward y la base de la valoracion. El normalizado solo sirve para que el EV/FCF de cribado signifique algo durante el ciclo de inversion.</t>
-  </si>
-  <si>
     <t>AS (FCF); AF (R3 Capital Intensity)</t>
   </si>
   <si>
@@ -4899,7 +4896,58 @@
     <t>Se anade LOTB (16) a la lista de filas con FCF normalizado: capex LTM 101,8 frente a un D&amp;A de 37,7, con un compromiso publicado de al menos 500 M EUR de capacidad Biscoff a cinco anos. Con ella son trece.</t>
   </si>
   <si>
-    <t>Filas normalizadas a 25-ago-2026 (trece): MSFT (5), COST (8), AMZN (13), LOTB (16), DNP (23), META (28), GOOG (32), NVDA (38), TSM (40), CPR (44), NFLX (50), TREX (55) e IPCO (63). El resto usa FCF reportado. NVDA y NFLX cumplen el disparador por poco (efecto del 2,8% y el 3,7%) y se aplican igual para no elegir a dedo. EXCEPCIONES documentadas: TFPM (49) lo activa mecanicamente pero NO se normaliza, porque ese capex son compras de streams -M&amp;A de crecimiento- y en una royalty el capex de sostenimiento es cero; EVD (20) tampoco, porque el D&amp;A de la fuente es implausible y el capex derivado no es fiable.</t>
+    <t>Filas normalizadas a 25-ago-2026 (doce): MSFT (5), COST (8), AMZN (13), DNP (23), META (28), GOOG (32), NVDA (38), TSM (40), CPR (44), NFLX (50), TREX (55) e IPCO (63). CONDICION ANADIDA EL 25-AGO: la normalizacion solo vale si el capex elevado es TEMPORAL. Si el capex lleva TRES O MAS EJERCICIOS SEGUIDOS por encima del doble del D&amp;A, no es una fase de inversion, es como funciona el negocio, y entonces se usa el FCF reportado. Por eso sale LOTB (16): capex sobre D&amp;A de 1,9x-5,1x-2,1x-3,3x-2,9x-2,7x en seis ejercicios seguidos y 500 M EUR mas comprometidos hasta 2030. Normalizarlo inflaba su FCF un 39% y su EV/FCF pasaba de 81,9x a 59,2x. PENDIENTE: pasar este mismo test a las doce restantes. EXCEPCIONES ya documentadas: TFPM (49), capex que son compras de streams; EVD (20), D&amp;A de la fuente no fiable.</t>
+  </si>
+  <si>
+    <t>OJO: el FCF normalizado NO sustituye a las columnas FCF@5y, que siguen siendo la vision forward y la base de la valoracion. El normalizado solo sirve para que el EV/FCF de cribado signifique algo durante el ciclo de inversion. Y ADVERTENCIA DEL 25-AGO: hay negocios cuyo FCF a traves del ciclo no existe porque el beneficio se reinvierte en circulante, no en activo fijo. TFF Group es el caso extremo del libro: FCF acumulado de -25,3 M EUR en cinco ejercicios (18,0 / -29,2 / -55,7 / -17,5 / +59,1), y el unico ano bueno es el de desalmacenamiento de madera. En esos casos el EV/FCF da falsos positivos en el suelo y falsos negativos en la recuperacion: la metrica honesta es EV/EBITDA.</t>
+  </si>
+  <si>
+    <t>AS; BD; BF</t>
+  </si>
+  <si>
+    <t>Deep dive 2a version - se retira la normalizacion del FCF</t>
+  </si>
+  <si>
+    <t>Lotus Bakeries. RECTIFICA LA ENTRADA DE ESTA MANANA. Se retira el FCF normalizado: AS vuelve de 182,6 a 131,7 M EUR (el reportado) y el EV/FCF pasa de 59,2x a 82,2x. Motivo: la regla del libro se escribio para un PICO temporal de capex (caso Amazon/Microsoft), y en Lotus no hay pico sino REGIMEN - el capex supera el doble del D&amp;A en cinco de los ultimos seis ejercicios (1,90x - 5,09x - 2,07x - 3,33x - 2,89x - 2,70x) y hay 500 M EUR mas comprometidos hasta 2030. El dato que lo cierra: en cinco ejercicios el FCF acumulado es 302,9 M EUR contra un beneficio neto acumulado de 648,2, o sea una CONVERSION DE CAJA DEL 47% sostenida. BD/BF rebasados sobre el FCF reportado: 185 (+7,0%/a) y 243 (+13,0%/a, el organico de Biscoff en 2025). Resultado: bajista -75% y alcista -44%. TAMBIEN SE RETIRA la recomendacion de subir los multiplos de 15x/25x a 17x/28x: era contar dos veces el mismo argumento, porque yo habia subido el FCF por normalizacion Y ademas pedia mas multiplo. A 13.100 EUR Lotus cotiza a 56 veces beneficio y 82 veces caja libre. El negocio sigue siendo de los mejores del libro; el precio no.</t>
+  </si>
+  <si>
+    <t>Deep dive 2a version - FCF de ciclo completo</t>
+  </si>
+  <si>
+    <t>TFF Group. RECTIFICA LA ENTRADA DE ESTA MANANA, que decia que TFF era la unica del grupo con asimetria positiva (+180%). Estaba construida sobre UN ano anomalo. El historico de cinco ejercicios: FCF de +18,0 / -29,2 / -55,7 / -17,5 / +59,1, o sea un ACUMULADO DE -25,3 M EUR en cinco anos. El unico ano positivo de verdad es el ultimo y es el del desalmacenamiento de madera. A traves del ciclo TFF no genera caja libre: el beneficio se reinvierte en roble secandose tres anos. BD/BF pasan a 12 y 42 (antes 59 y 104), que es lo que se puede defender sobre el ciclo completo y no sobre el ano de destocking. Resultado: bajista -100% (topado) y alcista -34%. SE RETIRA la recomendacion de subir el multiplo bajista de 6x a 8x: Roger tiene razon en que en un ciclico el multiplo es alto en el suelo y bajo en el pico, asi que lo que debe crecer es el FCF, no el multiplo. AVISO METODOLOGICO: para esta fila el EV/FCF da falsos positivos en el suelo y falsos negativos en la recuperacion. La metrica honesta es EV/EBITDA (14,6x hoy, unas 8x a mitad de ciclo).</t>
+  </si>
+  <si>
+    <t>Deep dive 2a version - pico de ciclo</t>
+  </si>
+  <si>
+    <t>Mips AB. El historico dice que hoy es MAXIMO HISTORICO de ingresos y que el ciclo es violento: 608 (2021) - 563 - 357 (2023, un -41% desde el pico) - 483 - 533 - 664 LTM. Y el margen EBIT del 46,7% de hoy tampoco es record: en 2021 fue del 52%. Rebasar el caso alcista al 18% anual desde este punto era anclar la valoracion en el mejor momento del ciclo, que es justo lo que el paso 4 del framework prohibe. BD pasa de 121 a 90 (el bajista repite la caida de 2023) y BF de 384 a 270 (+10,0%/a, el recorrido de volumen que da la propia guia de Safety). Resultado: bajista -85% y alcista -39%. SE RETIRA la recomendacion de subir el multiplo alcista de 22,5x a 25x, por la misma razon que en TFF: no se sube el multiplo de salida de un negocio que esta en pico de ciclo.</t>
+  </si>
+  <si>
+    <t>AE (R3 Risk of Disappearance)</t>
+  </si>
+  <si>
+    <t>Revertido por indicacion de Roger</t>
+  </si>
+  <si>
+    <t>Oatly. R3 Risk of Disappearance vuelve de -12 a -10. Roger no ve tanto riesgo de desaparicion: la distribucion es buena y muchos consumidores perciben el producto como unico, y ademas la mejora financiera es real - estan reduciendo gastos y creciendo a la vez, con apalancamiento operativo. Se mantiene el resto de la fila como estaba, incluido BD=0 (en el escenario malo la accion vale cero) y BF=114. La asimetria a 15,57 $ es exigente; a 8 $ el planteamiento era razonable.</t>
+  </si>
+  <si>
+    <t>BL4:BM71 (Worst IRR y Best IRR)</t>
+  </si>
+  <si>
+    <t>Suelo de -99% en las TIR</t>
+  </si>
+  <si>
+    <t>Se anade suelo: =IF($BJn&lt;=0,-0,99,MAX(-0,99,($BJn/Gn)^(1/5)-1)) y la equivalente en BM. Antes, cuando el FVE salia negativo la formula devolvia disparates (-188% anual en TFF, -216% en Oatly) que contaminaban cualquier media por categoria; y cuando el FVE era negativo con exponente fraccionario podia dar error. Una accion no puede perder mas del 100%. El pipeline de Python ya hacia esto (devuelve -0,99); ahora el Excel coincide. BL y BM son columnas protegidas: se tocan por indicacion expresa de Roger. AVISO: en la primera pasada la plantilla de BL se escribio con comillas dobles y PowerShell interpolo $BJ como variable vacia, dejando =IF(57&lt;=0,...) en las 68 filas; detectado y corregido en el mismo turno con comillas simples.</t>
+  </si>
+  <si>
+    <t>Framework Notes filas 58 y 59</t>
+  </si>
+  <si>
+    <t>Condicion nueva para normalizar el FCF</t>
+  </si>
+  <si>
+    <t>Fila 58: la normalizacion solo vale si el capex elevado es TEMPORAL. Si lleva TRES O MAS EJERCICIOS SEGUIDOS por encima del doble del D&amp;A, no es una fase de inversion sino como funciona el negocio, y se usa el FCF reportado. Sale LOTB y quedan doce filas normalizadas. PENDIENTE: pasar este test a las doce restantes, empezando por META, GOOG, MSFT y AMZN, que tambien llevan varios ejercicios de capex alto. Fila 59: advertencia nueva sobre los negocios cuyo FCF a traves del ciclo no existe porque el beneficio se reinvierte en circulante y no en activo fijo, con TFF como caso extremo del libro.</t>
   </si>
 </sst>
 </file>
@@ -7073,34 +7121,34 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.21724859954203968</c:v>
+                  <c:v>0.21535056770391781</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12780422738436692</c:v>
+                  <c:v>0.12725933974662795</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.21268691268480011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21900244611200459</c:v>
+                  <c:v>0.21874186412022789</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.4916787387159243E-2</c:v>
+                  <c:v>8.5040896509370301E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.19745985531708032</c:v>
+                  <c:v>0.19690295456465767</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.12867081613737774</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.25949207403006769</c:v>
+                  <c:v>0.25943228470250812</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.2808301254799268E-2</c:v>
+                  <c:v>1.423921438264375E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.11301923910271405</c:v>
+                  <c:v>0.11256640658534334</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.4174490275463096E-2</c:v>
@@ -7109,13 +7157,13 @@
                   <c:v>0.10741088468091919</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-6.630657915443261E-3</c:v>
+                  <c:v>-0.11087272348127619</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>8.4171531047791737E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.10791391779857418</c:v>
+                  <c:v>0.10909212414512681</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9164,31 +9212,31 @@
     <v>2007</v>
     <v>244.17</v>
     <v>0.94240000000000002</v>
-    <v>-4.62</v>
-    <v>-1.8595E-2</v>
-    <v>39610174272</v>
+    <v>-2.71</v>
+    <v>-1.0907E-2</v>
+    <v>39920440975</v>
     <v>248.46</v>
     <v>Veeva Systems Inc. Es un proveedor de soluciones en la nube para la industria global de las ciencias de la vida. Ofrece software SPAN Cloud, datos y consultoría empresarial, y está diseñado para satisfacer las necesidades de sus clientes y las funciones estratégicas de negocio, desde la investigación y el desarrollo (I+D) hasta la comercialización. Sus cuatro categorías de productos incluyen Veeva Development Cloud, Veeva Quality Cloud, Veeva Commercial Cloud y Veeva Data Cloud. Veeva Development Cloud incluye paquetes de aplicaciones para las funciones clínicas, regulatorias y de seguridad de las empresas de ciencias de la vida, todo construido en su plataforma Veeva Vault. Veeva Quality Cloud unifica aplicaciones, procesos y socios en las soluciones de gestión de contenido, capacitación, gestión de calidad, garantía y laboratorio de control en la plataforma Veeva Vault. Veeva Commercial Cloud es una categoría de producto compuesta por soluciones de software y análisis. Veeva Data Cloud es una plataforma de datos compuesta por datos de referencia conectados, datos profundos y datos de transacciones.</v>
     <v>7928</v>
     <v>XNYS</v>
-    <v>46259.736814907032</v>
+    <v>46259.828987187502</v>
     <v>New York Stock Exchange</v>
     <v>0</v>
     <v>247.35</v>
     <v>310.5</v>
-    <v>243.09</v>
+    <v>242.53</v>
     <v>148.05000000000001</v>
     <v>USD</v>
     <v>VEEVA SYSTEMS INC.</v>
     <v>VEEVA SYSTEMS INC.</v>
-    <v>43.136899999999997</v>
-    <v>243.84</v>
+    <v>43.474800000000002</v>
+    <v>245.75</v>
     <v>Healthcare Equipment &amp; Supplies</v>
     <v>4280 Hacienda Drive, PLEASANTON, CA, 94588 US</v>
     <v>VEEV</v>
     <v>Acciones</v>
     <v>VEEVA SYSTEMS INC. (XNYS:VEEV)</v>
-    <v>782256</v>
+    <v>1190369</v>
     <v>1649889</v>
   </rv>
   <rv s="2">
@@ -9236,32 +9284,32 @@
     <v>1993</v>
     <v>485.75</v>
     <v>1.1020000000000001</v>
-    <v>2.52</v>
-    <v>5.1710000000000002E-3</v>
-    <v>3637254707350</v>
+    <v>3.7050000000000001</v>
+    <v>7.6029999999999995E-3</v>
+    <v>3646053978175</v>
     <v>487.31</v>
     <v>Microsoft Corporation es una empresa de tecnología. La Compañía desarrolla y apoya software, servicios, dispositivos y soluciones. Los segmentos de la compañía incluyen Productividad y Procesos de Negocio, Nube Inteligente y más Informática Personal. El segmento Productividad y Procesos de Negocio está formado por productos y servicios en su cartera de servicios de productividad, comunicación e información. Este segmento comprende principalmente: Office Commercial, Office Consumer, LinkedIn y soluciones empresariales de Dynamics. El segmento de la nube inteligente consiste en productos de servidor y servicios en la nube, incluidos Azure y otros servicios en la nube, SQL Server, Windows Server, Visual Studio, System Center y Windows Server. licencias de acceso de clientes (CAL) relacionadas, Nuance y GitHub; y Servicios empresariales, incluidos los servicios de soporte empresarial, las soluciones de la industria y los servicios profesionales de Nuance. El segmento más personal de Computación comprende principalmente Windows, dispositivos, juegos y publicidad de búsqueda y noticias.</v>
     <v>223000</v>
     <v>XNAS</v>
-    <v>46259.736870601562</v>
+    <v>46259.829026874999</v>
     <v>6</v>
     <v>Nasdaq Stock Market</v>
     <v>7</v>
-    <v>490.76499999999999</v>
+    <v>491.62</v>
     <v>553.72</v>
     <v>484.3</v>
     <v>349.2</v>
     <v>USD</v>
     <v>MICROSOFT CORPORATION</v>
     <v>MICROSOFT CORPORATION</v>
-    <v>27.293600000000001</v>
-    <v>489.83</v>
+    <v>27.3596</v>
+    <v>491.01499999999999</v>
     <v>Software &amp; IT Services</v>
     <v>One Microsoft Way, REDMOND, WA, 98052 US</v>
     <v>MSFT</v>
     <v>Acciones</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>9638027</v>
+    <v>12138578</v>
     <v>34423023</v>
   </rv>
   <rv s="2">
@@ -9341,14 +9389,14 @@
     <v>2005</v>
     <v>42.21</v>
     <v>1.5463</v>
-    <v>0.105</v>
-    <v>2.5019999999999999E-3</v>
-    <v>103164323625</v>
+    <v>0.15</v>
+    <v>3.5739999999999999E-3</v>
+    <v>103274659800</v>
     <v>41.97</v>
     <v>Brookfield Corporation es una firma de inversión global con sede en Canadá enfocada en la construcción de riqueza a largo plazo para instituciones e individuos de todo el mundo. La Compañía tiene tres negocios principales: Gestión de activos alternativos, Soluciones de patrimonio y sus negocios operativos, que se encuentran en energía renovable, infraestructura, servicios empresariales e industriales, y bienes raíces. Su negocio de gestión de activos incluye la gestión de fondos privados a largo plazo, estrategias perpetuas y estrategias líquidas en nombre de sus inversores y de sí mismo. El negocio de Wealth Solutions de la Compañía incluye su participación contabilizada en Brookfield Wealth Solutions Ltd. Su negocio de energía renovable y transición incluye la propiedad, operación y desarrollo de activos de generación de energía solar hidroeléctrica, eólica, a escala de servicios públicos, energía distribuida y soluciones sostenibles. El negocio de infraestructura de la Compañía incluye la propiedad, operación y desarrollo de servicios públicos, transporte, midstream y activos de datos.</v>
     <v>250000</v>
     <v>XNYS</v>
-    <v>46259.736837823439</v>
+    <v>46259.828978460158</v>
     <v>New York Stock Exchange</v>
     <v>13</v>
     <v>42.301499999999997</v>
@@ -9358,14 +9406,14 @@
     <v>USD</v>
     <v>Brookfield Corporation</v>
     <v>Brookfield Corporation</v>
-    <v>82.274100000000004</v>
-    <v>42.075000000000003</v>
+    <v>82.362099999999998</v>
+    <v>42.12</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>Brookfield Place, 181 Bay St, Ste 100, Po Box 762, TORONTO, ON, M5J 2T3 CA</v>
     <v>BN</v>
     <v>Acciones</v>
     <v>Brookfield Corporation (XNYS:BN)</v>
-    <v>1265132</v>
+    <v>1947163</v>
     <v>4358850</v>
   </rv>
   <rv s="2">
@@ -9393,14 +9441,14 @@
     <v>1987</v>
     <v>966.56</v>
     <v>0.8669</v>
-    <v>-9.49</v>
-    <v>-9.7689999999999999E-3</v>
-    <v>426586692508</v>
+    <v>-10.039999999999999</v>
+    <v>-1.0336000000000001E-2</v>
+    <v>426342779168</v>
     <v>971.4</v>
     <v>Costco Wholesale Corporation (Costco) opera almacenes de membresía y sitios de comercio electrónico que ofrecen una selección de productos de marca nacional y de marca privada en una amplia gama de categorías. La Compañía compra la mayoría de sus mercancías directamente a los proveedores y la dirige a puntos de consolidación de cross-docking (depósitos) o directamente a sus almacenes. Opera 891 almacenes, incluyendo 614 en los Estados Unidos y Puerto Rico, 108 en Canadá, 40 en México, 35 en Japón, 29 en el Reino Unido, 19 en Corea, 15 en Australia, 14 en Taiwán, siete en China, y más. cinco en España, dos en Francia, y uno en Islandia, Nueva Zelanda y Suecia. También opera sitios de comercio electrónico en los Estados Unidos, Canadá, el Reino Unido, México, Corea, Taiwán, Japón y Australia. La Compañía ofrece una amplia selección de mercancías, además de la conveniencia de departamentos especializados y servicios exclusivos para miembros.</v>
     <v>341000</v>
     <v>XNAS</v>
-    <v>46259.736856029689</v>
+    <v>46259.828993390627</v>
     <v>Nasdaq Stock Market</v>
     <v>16</v>
     <v>968.76</v>
@@ -9410,14 +9458,14 @@
     <v>USD</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
-    <v>48.380499999999998</v>
-    <v>961.91</v>
+    <v>48.352800000000002</v>
+    <v>961.36</v>
     <v>Diversified Retail</v>
     <v>999 Lake Dr, ISSAQUAH, WA, 98027- US</v>
     <v>COST</v>
     <v>Acciones</v>
     <v>COSTCO WHOLESALE CORPORATION (XNAS:COST)</v>
-    <v>432862</v>
+    <v>641406</v>
     <v>1860725</v>
   </rv>
   <rv s="2">
@@ -9445,14 +9493,14 @@
     <v>2023</v>
     <v>77.709999999999994</v>
     <v>0.19470000000000001</v>
-    <v>-1.17</v>
-    <v>-1.4910000000000001E-2</v>
+    <v>-0.99</v>
+    <v>-1.2616E-2</v>
     <v>9370206000</v>
     <v>78.47</v>
     <v>Descartes Systems Group Inc. Se centra en los procesos de negocio de logística y gestión de la cadena de suministro. Proporciona soluciones de software como servicio (SaaS) bajo demanda enfocadas en mejorar la productividad, seguridad y sostenibilidad de las empresas con un uso intensivo de logística. Permite a los clientes utilizar sus soluciones modulares SaaS para enrutar, rastrear y ayudar a mejorar la seguridad y el cumplimiento de los recursos de entrega; planificar, asignar y ejecutar envíos; clasificar, auditar y pagar facturas de transporte; acceder a datos comerciales globales; archivar documentos aduaneros y de seguridad para importaciones y exportaciones; y completar otros procesos logísticos participando en la comunidad logística multimodal. Sus soluciones incluyen soluciones basadas en la nube y consisten en conectividad y mensajería de servicios B2B, sistemas empresariales de corredores y forwarder, inteligencia comercial global, cumplimiento normativo, envío de comercio electrónico, gestión de transporte y enrutamiento. También proporciona software de declaración de aduanas para proveedores de servicios logísticos y expedidores.</v>
     <v>2403</v>
     <v>XNAS</v>
-    <v>46259.736787094531</v>
+    <v>46259.828948750001</v>
     <v>Nasdaq Stock Market</v>
     <v>19</v>
     <v>79.209999999999994</v>
@@ -9462,14 +9510,14 @@
     <v>USD</v>
     <v>The Descartes Systems Group Inc.</v>
     <v>The Descartes Systems Group Inc.</v>
-    <v>38.444299999999998</v>
-    <v>77.3</v>
+    <v>38.533799999999999</v>
+    <v>77.48</v>
     <v>Software &amp; IT Services</v>
     <v>120 Randall Drive, WATERLOO, ON, N2V 1C6 CA</v>
     <v>DSGX</v>
     <v>Acciones</v>
     <v>The Descartes Systems Group Inc. (XNAS:DSGX)</v>
-    <v>177395</v>
+    <v>246721</v>
     <v>477978</v>
   </rv>
   <rv s="2">
@@ -9504,7 +9552,7 @@
     <v>Rational AG is a Germany-based company that provides technology products for thermal food preparation for industrial and commercial kitchens. It operates through two segments: Through the RATIONAL segment, the Company offers the SelfCookingCenter 5 Senses, a steamer that works as hot air oven, stove or boiling pan. The FRIMA segment provides the complementary steamer VarioCookingCenter. The Company markets its products around the globe through a network of subsidiaries, including sales companies. It also offers related accessories, such as granite enameled containers, roasting and baking trays, grilling and roasting plates, potato bakers and muffin and timbale molds, among others.</v>
     <v>2912</v>
     <v>XFRA</v>
-    <v>46259.652777777781</v>
+    <v>46259.765972222223</v>
     <v>Deutsche Boerse AG</v>
     <v>22</v>
     <v>633.5</v>
@@ -9549,31 +9597,31 @@
     <v>2007</v>
     <v>175</v>
     <v>0.93230000000000002</v>
-    <v>-7.56</v>
-    <v>-4.2939999999999999E-2</v>
-    <v>27248050750</v>
+    <v>-7.52</v>
+    <v>-4.2713000000000001E-2</v>
+    <v>27254519130</v>
     <v>176.06</v>
     <v>Zscaler, Inc. Es una compañía de seguridad en la nube. La Compañía ha desarrollado una plataforma que incorpora funcionalidades de seguridad básicas necesarias para permitir un acceso rápido y seguro a los recursos de la nube basado en la identidad, el contexto y las políticas de una organización. Su plataforma Zscaler Zero Trust Exchange protege a miles de clientes de ciberataques y pérdida de datos conectando de forma segura a usuarios, dispositivos y aplicaciones en cualquier ubicación. Su solución es una plataforma en la nube distribuida, multiusuario y diseñada específicamente que incorpora la funcionalidad de seguridad necesaria para permitir que los usuarios, aplicaciones y dispositivos utilicen de manera segura y eficiente aplicaciones y servicios autorizados basados en las políticas de negocio de una organización. Ofrece sus soluciones utilizando un modelo de negocio de software como servicio (SaaS) y vende suscripciones a los clientes para acceder a su plataforma en la nube, junto con los servicios de soporte relacionados. Ofrece una plataforma de seguridad que combina su plataforma con operaciones de seguridad automatizadas.</v>
     <v>7923</v>
     <v>XNAS</v>
-    <v>46259.736836365628</v>
+    <v>46259.82901887656</v>
     <v>Nasdaq Stock Market</v>
     <v>25</v>
     <v>176.81</v>
     <v>336.99</v>
-    <v>168.18</v>
+    <v>166.66</v>
     <v>114.625</v>
     <v>USD</v>
     <v>ZSCALER, INC.</v>
     <v>ZSCALER, INC.</v>
     <v>0</v>
-    <v>168.5</v>
+    <v>168.54</v>
     <v>Software &amp; IT Services</v>
     <v>120 Holger Way, SAN JOSE, CA, 95134 US</v>
     <v>ZS</v>
     <v>Acciones</v>
     <v>ZSCALER, INC. (XNAS:ZS)</v>
-    <v>825529</v>
+    <v>1528902</v>
     <v>2141928</v>
   </rv>
   <rv s="2">
@@ -9601,31 +9649,31 @@
     <v>1947</v>
     <v>47.5</v>
     <v>0.1275</v>
-    <v>0.505</v>
-    <v>1.0632999999999998E-2</v>
+    <v>2.605</v>
+    <v>5.4848000000000001E-2</v>
     <v>11318880000000</v>
     <v>47.494999999999997</v>
     <v>Nintendo Co Ltd es una empresa con sede en Japón dedicada principalmente al desarrollo, fabricación y venta de productos de entretenimiento en el campo del entretenimiento en el hogar. La Compañía desarrolla, fabrica y vende hardware y software para juegos de consola portátiles y domésticos. Sus productos principales son las consolas de juegos, que son dispositivos de entretenimiento basados en computadora, y los bienes de carácter y las cartas de juego. Las consolas de juegos son hardware y software para juegos de consola portátil y doméstica, que son desarrollados por la Compañía y sus afiliados, fabricados por la Compañía y vendidos principalmente por sus afiliados en Japón y en el extranjero. La Compañía también desarrolla negocios que utilizan su propiedad intelectual (IP), como contenido de video y aplicaciones móviles.</v>
     <v>8666</v>
     <v>XFRA</v>
-    <v>46259.725694444445</v>
+    <v>46259.815972222219</v>
     <v>Deutsche Boerse AG</v>
     <v>28</v>
-    <v>48.454999999999998</v>
+    <v>50.1</v>
     <v>546.1</v>
     <v>47.5</v>
     <v>34.6</v>
     <v>EUR</v>
     <v>Nintendo Co., Ltd.</v>
     <v>Nintendo Co., Ltd.</v>
-    <v>21.7195</v>
-    <v>48</v>
+    <v>22.669699999999999</v>
+    <v>50.1</v>
     <v>Leisure Products</v>
     <v>11-1, Kamitoba Hokotate-cho, Minami-ku, KYOTO-SHI, KYOTO-FU, 601-8501 JP</v>
     <v>NTO</v>
     <v>Acciones</v>
     <v>Nintendo Co., Ltd. (XFRA:NTO)</v>
-    <v>818</v>
+    <v>851</v>
     <v>12187950</v>
   </rv>
   <rv s="2">
@@ -9653,31 +9701,31 @@
     <v>1996</v>
     <v>262.73</v>
     <v>1.4475</v>
-    <v>-1.85</v>
-    <v>-7.0589999999999993E-3</v>
-    <v>2806813588200</v>
+    <v>-1.32</v>
+    <v>-5.0370000000000007E-3</v>
+    <v>2812530332500</v>
     <v>262.07</v>
     <v>Amazon.com, Inc. Ofrece una gama de productos y servicios a los clientes. Los productos ofrecidos a través de sus tiendas incluyen mercancía y contenido que ha adquirido para su reventa y productos ofrecidos por terceros vendedores. Los segmentos de la compañía incluyen Norteamérica, International y Amazon Web Services (AWS). Sirve a los consumidores a través de sus tiendas en línea y físicas y se centra en la selección, el precio y la conveniencia. Los clientes acceden a sus ofertas a través de sus sitios web, aplicaciones móviles, Alexa, dispositivos, streaming, y visitando físicamente sus tiendas. También fabrica y vende dispositivos electrónicos, incluyendo Kindle, tableta de fuego, Fire TV, Echo, Ring, Blink y eero, y desarrolla y produce contenido multimedia. Presta servicios a desarrolladores y empresas de todos los tamaños, incluidas empresas emergentes, agencias gubernamentales e instituciones académicas, a través de AWS, que ofrece un conjunto de servicios de tecnología bajo demanda, incluyendo computación, almacenamiento, base de datos, análisis, y el aprendizaje automático, y otros servicios.</v>
     <v>1595000</v>
     <v>XNAS</v>
-    <v>46259.73687836797</v>
+    <v>46259.828995474221</v>
     <v>Nasdaq Stock Market</v>
     <v>31</v>
     <v>263.87189999999998</v>
     <v>287.2</v>
-    <v>260.08</v>
+    <v>259.83</v>
     <v>196</v>
     <v>USD</v>
     <v>AMAZON.COM, INC.</v>
     <v>AMAZON.COM, INC.</v>
-    <v>20.930499999999999</v>
-    <v>260.22000000000003</v>
+    <v>20.973099999999999</v>
+    <v>260.75</v>
     <v>Diversified Retail</v>
     <v>410 Terry Avenue North, SEATTLE, WA, 98109 US</v>
     <v>AMZN</v>
     <v>Acciones</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>11114718</v>
+    <v>16235193</v>
     <v>45276854</v>
   </rv>
   <rv s="2">
@@ -9913,31 +9961,31 @@
     <v>1987</v>
     <v>1157.24</v>
     <v>1.3213999999999999</v>
-    <v>-23.07</v>
-    <v>-1.9779000000000001E-2</v>
-    <v>24693229741</v>
+    <v>-29.13</v>
+    <v>-2.4974E-2</v>
+    <v>24562348042</v>
     <v>1166.4000000000001</v>
     <v>Fair Isaac Corporation es una empresa de software de análisis aplicado. La compañía se centra en el uso de análisis predictivos y ciencia de datos para mejorar las decisiones operativas. La Compañía opera a través de dos segmentos: Puntajes y Software. El segmento de puntajes incluye las soluciones y servicios de puntaje de negocios a negocios de la Compañía que dan a sus clientes acceso a crédito predictivo y otros puntajes. Este segmento incluye sus soluciones de puntuación entre empresas y consumidores, incluidas sus ofertas de suscripción de myFICO.com. El segmento de software de la compañía incluye soluciones de análisis y gestión de decisiones preconfiguradas diseñadas para un tipo específico de necesidad o proceso de negocio, como originación de cuentas, gestión de clientes, participación de clientes, detección de fraude y marketing, así como servicios profesionales asociados. Este segmento incluye FICO Platform, una oferta de software modular diseñada para soportar casos de uso analítico y de decisión avanzados, así como software analítico y de toma de decisiones independiente.</v>
     <v>3876</v>
     <v>XNYS</v>
-    <v>46259.73682334453</v>
+    <v>46259.829016608594</v>
     <v>New York Stock Exchange</v>
     <v>46</v>
     <v>1169.2663</v>
     <v>1998.01</v>
-    <v>1134.67</v>
+    <v>1133.1600000000001</v>
     <v>870.01</v>
     <v>USD</v>
     <v>FAIR ISAAC CORPORATION</v>
     <v>FAIR ISAAC CORPORATION</v>
-    <v>33.030500000000004</v>
-    <v>1143.33</v>
+    <v>32.855400000000003</v>
+    <v>1137.27</v>
     <v>Software &amp; IT Services</v>
     <v>5 West Mendenhall, Suites 105, BOZEMAN, MT, 59715 US</v>
     <v>FICO</v>
     <v>Acciones</v>
     <v>FAIR ISAAC CORPORATION (XNYS:FICO)</v>
-    <v>100223</v>
+    <v>138611</v>
     <v>368737</v>
   </rv>
   <rv s="2">
@@ -10020,31 +10068,31 @@
     <v>2014</v>
     <v>61.45</v>
     <v>1.3953</v>
-    <v>-0.5</v>
-    <v>-8.319E-3</v>
+    <v>-1</v>
+    <v>-1.6639000000000001E-2</v>
     <v>5836800000</v>
     <v>60.1</v>
     <v>Cts Eventim AG &amp; Co KgaA is a Germany-based company. The Company provides e ticketing and live entertainment sectors and operates in the leisure events market. The Company operates in two segments namely Ticketing and Live Entertainment. The objects of the Ticketing segment are to promote, sell, broker, distribute, and market tickets for cinema, concert, theatre, art, sports and other events in Germany and abroad, using data processing and data transmission technologies. Its tickets are marketed through its network platform (eventim.net), its in-house ticketing product (eventim.inhouse), the sports ticketing product (eventim.tixx) and a solution for ticket sales and admission control in stadiums and arenas. The objects of the Live Entertainment segment are to plan, prepare and execute tours and events, especially music events and concerts, and to market music productions. Internationally venues are also operated. The Company operates kinoheld GmbH as a majority owned subsidiary.</v>
     <v>5280</v>
     <v>XFRA</v>
-    <v>46259.722222222219</v>
+    <v>46259.81527777778</v>
     <v>Deutsche Boerse AG</v>
     <v>52</v>
     <v>61.5</v>
     <v>113.8</v>
-    <v>59.5</v>
+    <v>59.1</v>
     <v>25.98</v>
     <v>EUR</v>
     <v>Eventim</v>
     <v>Eventim</v>
-    <v>18.625</v>
-    <v>59.6</v>
+    <v>18.468800000000002</v>
+    <v>59.1</v>
     <v>Software &amp; IT Services</v>
     <v>Contrescarpe 75 A, BREMEN, BREMEN, 28195 DE</v>
     <v>EVD</v>
     <v>Acciones</v>
     <v>Eventim (XFRA:EVD)</v>
-    <v>565</v>
+    <v>603</v>
     <v>219770</v>
   </rv>
   <rv s="2">
@@ -10072,31 +10120,31 @@
     <v>2014</v>
     <v>48.82</v>
     <v>0.52370000000000005</v>
-    <v>-0.31</v>
-    <v>-6.3370000000000006E-3</v>
-    <v>95081937760</v>
+    <v>-7.4999999999999997E-2</v>
+    <v>-1.5329999999999999E-3</v>
+    <v>95541601520</v>
     <v>48.92</v>
     <v>Monster Beverage Corporation es una sociedad holding. La Compañía, a través de sus subsidiarias, desarrolla, comercializa, vende y distribuye bebidas de bebidas energéticas y concentrados para bebidas energéticas bajo diversas marcas. Su segmento de bebidas Monster Energy consiste principalmente en sus bebidas energéticas Monster Energy, bebidas energéticas de alto rendimiento Reign Total Body Fuel, bebidas energéticas de bienestar total Reign Storm y bebidas energéticas Bang Energy. Su segmento de Marcas Estratégicas consiste principalmente en varias marcas de bebidas energéticas adquiridas de The Coca-Cola Company, así como sus marcas de energía asequibles, Predator y Fury. Su segmento de marcas de alcohol consiste en varias cervezas artesanales, seltzers duros y bebidas de malta con sabor. Su otro segmento consiste en ciertos productos vendidos por American Fruits and Flavors LLC, una subsidiaria de propiedad total de la Compañía, a clientes independientes de terceros. También desarrolla, comercializa, vende y distribuye aguas tranquilas y chispeantes bajo la marca Monster Tour Water.</v>
     <v>6891</v>
     <v>XNAS</v>
-    <v>46259.736860601559</v>
+    <v>46259.829009710156</v>
     <v>Nasdaq Stock Market</v>
     <v>55</v>
     <v>49.24</v>
     <v>50.17</v>
-    <v>48.5</v>
+    <v>48.34</v>
     <v>30.484999999999999</v>
     <v>USD</v>
     <v>MONSTER BEVERAGE CORPORATION</v>
     <v>MONSTER BEVERAGE CORPORATION</v>
-    <v>45.113700000000001</v>
-    <v>48.61</v>
+    <v>45.331800000000001</v>
+    <v>48.844999999999999</v>
     <v>Beverages</v>
     <v>1 Monster Way, CORONA, CA, 92879-7101 US</v>
     <v>MNST</v>
     <v>Acciones</v>
     <v>MONSTER BEVERAGE CORPORATION (XNAS:MNST)</v>
-    <v>2845312</v>
+    <v>4476151</v>
     <v>11028559</v>
   </rv>
   <rv s="2">
@@ -10124,14 +10172,14 @@
     <v>2008</v>
     <v>190.13</v>
     <v>1.1597999999999999</v>
-    <v>-0.26</v>
-    <v>-1.3669999999999999E-3</v>
-    <v>111991803715</v>
+    <v>-0.1</v>
+    <v>-5.2570000000000004E-4</v>
+    <v>112086137427</v>
     <v>190.21</v>
     <v>Airbnb, Inc. Opera una plataforma global para estancias y experiencias. El modelo de mercado de la Compañía conecta a anfitriones y huéspedes en línea o a través de dispositivos móviles para reservar espacios y experiencias en todo el mundo. La Compañía ha construido su plataforma para incorporar nuevos hosts, especialmente aquellos que anteriormente no habían considerado hosting. Se asocia con los anfitriones durante todo el proceso de configuración de su listado y les proporciona un conjunto de herramientas para administrar sus listados, incluyendo programación, merchandising, pagos integrados, soporte comunitario, etc. protección del anfitrión, orientación de precios y comentarios de las revisiones. Su sitio web y aplicaciones móviles ofrecen a sus huéspedes una manera de explorar una variedad de hogares y experiencias y una manera fácil de reservarlos. Su plataforma tecnológica impulsa su mercado de dos caras y permite su red global de anfitriones e invitados. Posee una cartera de marcas con protección en 220 países en los que opera para sus marcas principales, AIRBNB, y su logotipo de Belo.</v>
     <v>8200</v>
     <v>XNAS</v>
-    <v>46259.736880763281</v>
+    <v>46259.828997175784</v>
     <v>Nasdaq Stock Market</v>
     <v>58</v>
     <v>191.3595</v>
@@ -10141,14 +10189,14 @@
     <v>USD</v>
     <v>AIRBNB, INC.</v>
     <v>AIRBNB, INC.</v>
-    <v>43.191099999999999</v>
-    <v>189.95</v>
+    <v>43.227400000000003</v>
+    <v>190.11</v>
     <v>Software &amp; IT Services</v>
     <v>888 Brannan St., SAN FRANCISCO, CA, 94103 US</v>
     <v>ABNB</v>
     <v>Acciones</v>
     <v>AIRBNB, INC. (XNAS:ABNB)</v>
-    <v>1594049</v>
+    <v>2482826</v>
     <v>4988542</v>
   </rv>
   <rv s="2">
@@ -10224,14 +10272,14 @@
     <v>2022</v>
     <v>99.11</v>
     <v>0.68899999999999995</v>
-    <v>-1.175</v>
-    <v>-1.1823999999999999E-2</v>
-    <v>23939283093</v>
+    <v>-0.52500000000000002</v>
+    <v>-5.2829999999999995E-3</v>
+    <v>24097748738</v>
     <v>99.37</v>
     <v>Veralto Corporation proporciona soluciones tecnológicas esenciales que monitorean, mejoran y protegen los recursos clave en todo el mundo. Sus segmentos incluyen Calidad del Agua (WQ) y Calidad e Innovación del Producto (PQI). WQ Segment ofrece carteras de análisis de agua y soluciones de tratamiento de agua diferenciadas que permiten el suministro de agua potable segura por parte de empresas públicas y privadas. Bajo sus marcas Hach, Trojan Technologies, ChemTreat y otras marcas WQ reconocidas mundialmente, proporciona instrumentación de precisión y tecnologías avanzadas de tratamiento de agua en las que sus clientes confían para medir, analizar y tratar el agua en aplicaciones residenciales, comerciales, municipales, industriales, de investigación y de recursos naturales. El segmento PQI proporciona un conjunto de soluciones esenciales para los propietarios de marcas y las empresas de bienes de consumo envasados. Bajo sus marcas Videojet, Linx, Esko, X-Rite, Pantone y otras marcas PQI reconocidas a nivel mundial, proporciona marcado y codificación, así como embalaje e instrumentación de color y consumibles relacionados.</v>
     <v>17000</v>
     <v>XNYS</v>
-    <v>46259.736862858597</v>
+    <v>46259.828968414062</v>
     <v>New York Stock Exchange</v>
     <v>99.69</v>
     <v>109.86</v>
@@ -10240,14 +10288,14 @@
     <v>USD</v>
     <v>VERALTO CORPORATION</v>
     <v>VERALTO CORPORATION</v>
-    <v>24.753</v>
-    <v>98.194999999999993</v>
+    <v>24.916799999999999</v>
+    <v>98.844999999999999</v>
     <v>Professional &amp; Commercial Services</v>
     <v>225 Wyman Street, Suite 250, WALTHAM, MA, 02451 US</v>
     <v>VLTO</v>
     <v>Acciones</v>
     <v>VERALTO CORPORATION (XNYS:VLTO)</v>
-    <v>438934</v>
+    <v>801832</v>
     <v>1598214</v>
   </rv>
   <rv s="2">
@@ -10434,31 +10482,31 @@
     <v>2004</v>
     <v>563.29999999999995</v>
     <v>1.2408999999999999</v>
-    <v>6.04</v>
-    <v>1.0805E-2</v>
-    <v>1439493740359</v>
+    <v>9.68</v>
+    <v>1.7316000000000002E-2</v>
+    <v>1448766662200</v>
     <v>559.02</v>
     <v>Meta Platforms, Inc. Está construyendo conexiones humanas, impulsadas por inteligencia artificial y tecnologías inmersivas. Los productos de la Compañía permiten a las personas conectarse y compartir con amigos y familiares a través de dispositivos móviles, computadoras personales, auriculares de realidad virtual (VR) y realidad mixta (MR), realidad aumentada (AR) y wearables. También ayuda a las personas a descubrir y aprender sobre lo que está sucediendo en el mundo que les rodea, permitiendo a las personas compartir sus experiencias, ideas, fotos, videos y otros contenidos con audiencias que van desde sus familiares y amigos más cercanos hasta el público en general. Los segmentos de la compañía incluyen Family of Apps (FOA) y Reality Labs (RL). El segmento FOA incluye Facebook, Instagram, Messenger, WhatsApp e hilos. El segmento de RL incluye su hardware, software y contenido de consumo relacionado con la realidad virtual, aumentada y mixta. Sus ofertas de productos en realidad virtual incluyen sus dispositivos Meta Quest, así como software y contenido disponible a través de la Tienda Meta Horizon.</v>
     <v>75472</v>
     <v>XNAS</v>
-    <v>46259.736876469535</v>
+    <v>46259.829016318748</v>
     <v>Nasdaq Stock Market</v>
     <v>75</v>
-    <v>568.64</v>
+    <v>570.79999999999995</v>
     <v>790.8</v>
     <v>561.40009999999995</v>
     <v>520.26</v>
     <v>USD</v>
     <v>META PLATFORMS, INC.</v>
     <v>META PLATFORMS, INC.</v>
-    <v>19.5669</v>
-    <v>565.05999999999995</v>
+    <v>19.693000000000001</v>
+    <v>568.70000000000005</v>
     <v>Software &amp; IT Services</v>
     <v>1 Meta Way, MENLO PARK, CA, 94025 US</v>
     <v>META</v>
     <v>Acciones</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>4752126</v>
+    <v>7154819</v>
     <v>16293971</v>
   </rv>
   <rv s="2">
@@ -10486,31 +10534,31 @@
     <v>2021</v>
     <v>106.78</v>
     <v>1.7875000000000001</v>
-    <v>0.26</v>
-    <v>2.4229999999999998E-3</v>
-    <v>96567637848</v>
+    <v>0.40500000000000003</v>
+    <v>3.774E-3</v>
+    <v>96697795010</v>
     <v>107.32</v>
     <v>KKR &amp; Co. Inc. Es una empresa de inversión global que ofrece gestión alternativa de activos, mercados de capital y soluciones de seguros. Los segmentos de la Compañía incluyen Gestión de Activos, Seguros y Holdings Estratégicos. El segmento de gestión de activos ofrece una gama de servicios de gestión de inversiones a fondos de inversión, vehículos y cuentas y proporciona servicios de mercados de capitales a empresas de cartera y terceros. El segmento de Gestión de Activos incluye cinco líneas de negocio: Capital Privado, Activos Inmobiliarios, Estrategias de Crédito y Líquido, Mercados de Capitales y Actividades Principales. El segmento de seguros es operado por Global Atlantic, que es una compañía de seguros de vida y jubilación de los Estados Unidos que ofrece un conjunto de productos de protección, herencia y ahorro y soluciones de reaseguro a clientes en los mercados individuales e institucionales. Global Atlantic ofrece anualidades de tasa fija a individuos y otras. El segmento Estratégico Holdings representa su participación en su estrategia básica de capital riesgo.</v>
     <v>5043</v>
     <v>XNYS</v>
-    <v>46259.736887337502</v>
+    <v>46259.828982707812</v>
     <v>New York Stock Exchange</v>
     <v>78</v>
-    <v>107.85</v>
+    <v>108.02</v>
     <v>152.095</v>
     <v>105.92</v>
     <v>82.67</v>
     <v>USD</v>
     <v>KKR &amp; CO. INC.</v>
     <v>KKR &amp; CO. INC.</v>
-    <v>34.296100000000003</v>
-    <v>107.58</v>
+    <v>34.342300000000002</v>
+    <v>107.72499999999999</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>30 Hudson Yards, NEW YORK, NY, 10001 US</v>
     <v>KKR</v>
     <v>Acciones</v>
     <v>KKR &amp; CO. INC. (XNYS:KKR)</v>
-    <v>847320</v>
+    <v>1407436</v>
     <v>4782292</v>
   </rv>
   <rv s="2">
@@ -10538,31 +10586,31 @@
     <v>2009</v>
     <v>285.42</v>
     <v>1.6548</v>
-    <v>-4.54</v>
-    <v>-1.6194E-2</v>
-    <v>98210342057</v>
+    <v>-2.96</v>
+    <v>-1.0558000000000001E-2</v>
+    <v>98772947983</v>
     <v>280.35000000000002</v>
     <v>Cloudflare, Inc. Es una compañía de conectividad en la nube. Su conjunto completo de productos consiste en sus servicios de sitio web y aplicaciones para ofrecer seguridad, rendimiento y confiabilidad para los sitios web, aplicaciones e interfaces de programación de aplicaciones (API) de una organización; su plataforma Secure Access Service Edge (SASE), que contiene su conjunto de soluciones Zero Trust y servicios de red para ayudar a garantizar que el tráfico de entrada y salida de la red interna y los dispositivos de una organización se verifique y autorice, así como para conectar de forma segura centros de datos, servicios en la nube y sucursales a una organización con su Connectivity Cloud; sus soluciones basadas en desarrolladores para crear e implementar aplicaciones sin servidor con escala, rendimiento, seguridad y confiabilidad, y sus ofertas para consumidores. Sus ofertas de productos de seguridad de sitios web y aplicaciones incluyen firewall de aplicaciones web, gestión de bots, protección de denegación de servicio distribuida, seguridad de API, cifrado SSL/TLS, administración de scripts y centro de seguridad.</v>
     <v>5483</v>
     <v>XNYS</v>
-    <v>46259.736867974221</v>
+    <v>46259.828989062502</v>
     <v>New York Stock Exchange</v>
     <v>81</v>
     <v>287</v>
     <v>332.22</v>
-    <v>275.59440000000001</v>
+    <v>273.21010000000001</v>
     <v>158.83000000000001</v>
     <v>USD</v>
     <v>CLOUDFLARE, INC.</v>
     <v>CLOUDFLARE, INC.</v>
     <v>0</v>
-    <v>275.81</v>
+    <v>277.39</v>
     <v>Software &amp; IT Services</v>
     <v>101 Townsend St, SAN FRANCISCO, CA, 94107-1934 US</v>
     <v>NET</v>
     <v>Acciones</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
-    <v>856157</v>
+    <v>1385138</v>
     <v>3817041</v>
   </rv>
   <rv s="2">
@@ -10590,31 +10638,31 @@
     <v>2011</v>
     <v>191.25</v>
     <v>1.2294</v>
-    <v>-7.38</v>
-    <v>-3.8704000000000002E-2</v>
-    <v>186658422600</v>
+    <v>-5.4749999999999996</v>
+    <v>-2.8713000000000002E-2</v>
+    <v>188598326010</v>
     <v>190.68</v>
     <v>CrowdStrike Holdings, Inc. Es una compañía global de ciberseguridad que proporciona protección en la nube para endpoints, cargas de trabajo en la nube, identidad y datos. Su plataforma Falcon está diseñada para la consolidación de la ciberseguridad, diseñada específicamente para detener las brechas. Las plataformas recopilan e integran datos de toda la empresa, incluidos puntos finales, cargas de trabajo en la nube, identidades y fuentes de terceros. Ofrece 29 módulos en la nube en su plataforma Falcon a través de un modelo basado en suscripción de software como servicio (SaaS) que abarca múltiples mercados grandes, incluyendo seguridad de endpoints corporativos y cargas de trabajo en la nube, servicios de seguridad gestionada, gestión de operaciones de tecnología de la información (TI), protección de identidades, gestión de información de seguridad de próxima generación y gestión de eventos (SIEM) y gestión de registros, servicios de inteligencia contra amenazas, protección de datos, gestión de posturas de seguridad SaaS, automatización y respuesta (SOAR) y automatización de flujo de trabajo impulsada por inteligencia artificial, entre otros.</v>
     <v>11157</v>
     <v>XNAS</v>
-    <v>46259.736866828127</v>
+    <v>46259.829008263281</v>
     <v>Nasdaq Stock Market</v>
     <v>84</v>
     <v>194.45</v>
     <v>227.5</v>
-    <v>183.3</v>
+    <v>182.35</v>
     <v>85.68</v>
     <v>USD</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>0</v>
-    <v>183.3</v>
+    <v>185.20500000000001</v>
     <v>Software &amp; IT Services</v>
     <v>206 E. 9TH STREET, SUITE 1400, AUSTIN, TX, 78701 US</v>
     <v>CRWD</v>
     <v>Acciones</v>
     <v>CROWDSTRIKE HOLDINGS, INC. (XNAS:CRWD)</v>
-    <v>4138776</v>
+    <v>6664502</v>
     <v>7663469</v>
   </rv>
   <rv s="2">
@@ -10642,14 +10690,14 @@
     <v>2015</v>
     <v>345.61</v>
     <v>1.2306999999999999</v>
-    <v>-1.2648999999999999</v>
-    <v>-3.6709999999999998E-3</v>
-    <v>4198865973000</v>
+    <v>-0.82489999999999997</v>
+    <v>-2.3939999999999999E-3</v>
+    <v>4204247173000</v>
     <v>344.59</v>
     <v>Alphabet Inc. Es una compañía holding. Los segmentos de la Compañía incluyen Google Services, Google Cloud y otras apuestas. El segmento de Servicios de Google incluye productos y servicios como anuncios, Android, Chrome, dispositivos, Google Maps, Google Maps, etc. Google Play, Búsqueda y YouTube. El segmento de Google Cloud incluye servicios de infraestructura y plataforma, herramientas de colaboración y otros servicios para clientes empresariales. Su otro segmento de apuestas se dedica a la venta de servicios relacionados con la salud y servicios de Internet. Google Cloud ofrece servicios en la nube listos para la empresa, incluidos Google Cloud Platform y Google Workspace. Google Cloud Platform proporciona acceso a soluciones como las ofertas de inteligencia artificial (IA), incluida su infraestructura de IA, la plataforma Vertex AI y Gemini para Google Cloud; ciberseguridad y datos y análisis. Google Workspace incluye herramientas de comunicación y colaboración basadas en la nube para empresas, como Calendar, Gmail, Docs, Drive, y reunirse.</v>
     <v>198933</v>
     <v>XNAS</v>
-    <v>46259.736882638281</v>
+    <v>46259.829016642965</v>
     <v>Nasdaq Stock Market</v>
     <v>87</v>
     <v>346.7</v>
@@ -10659,14 +10707,14 @@
     <v>USD</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
-    <v>17.2578</v>
-    <v>343.32510000000002</v>
+    <v>17.279900000000001</v>
+    <v>343.76510000000002</v>
     <v>Software &amp; IT Services</v>
     <v>1600 Amphitheatre Parkway, MOUNTAIN VIEW, CA, 94043 US</v>
     <v>GOOG</v>
     <v>Acciones</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>4957789</v>
+    <v>7457351</v>
     <v>19444835</v>
   </rv>
   <rv s="2">
@@ -10738,14 +10786,14 @@
     <v>2010</v>
     <v>292.01</v>
     <v>0.87039999999999995</v>
-    <v>-2.1800000000000002</v>
-    <v>-7.4850000000000003E-3</v>
-    <v>55747872175</v>
+    <v>-2.2349999999999999</v>
+    <v>-7.6739999999999994E-3</v>
+    <v>55737265287</v>
     <v>291.25</v>
     <v>Garmin Ltd. (Garmin) es una entidad con sede en Suiza. La Compañía y sus filiales ofrecen sistemas de posicionamiento global (GPS) y dispositivos y aplicaciones inalámbricas. La Compañía opera a través de cinco segmentos: Fitness, outdoor, aviación, marina y auto. Ofrece una gama de productos de navegación automática, así como una gama de productos y aplicaciones diseñados para el mercado de GPS móvil. Ofrece Handhelds al aire libre, dispositivos portables, dispositivos de golf y dispositivos de seguimiento de perros y entrenamiento / obediencia de mascotas. Garmin ofrece varios productos diseñados para su uso en el seguimiento de fitness y actividad. El segmento de negocios de aviación de la compañía es un proveedor de soluciones para fabricantes de aeronaves, propietarios y operadores de aeronaves existentes, así como clientes militares y gubernamentales, y sirve a una gama de aeronaves, incluyendo aviones de transporte, aviación de negocios, aviación general, deportes experimentales / ligeros, etc. helicópteros, vehículos pilotados opcionalmente y vehículos aéreos no tripulados. La compañía opera en todo el mundo.</v>
     <v>23000</v>
     <v>XNYS</v>
-    <v>46259.736895022659</v>
+    <v>46259.82903050859</v>
     <v>New York Stock Exchange</v>
     <v>92</v>
     <v>294.99</v>
@@ -10755,14 +10803,14 @@
     <v>USD</v>
     <v>Garmin Ltd.</v>
     <v>Garmin Ltd.</v>
-    <v>29.8109</v>
-    <v>289.07</v>
+    <v>29.805199999999999</v>
+    <v>289.01499999999999</v>
     <v>Communications &amp; Networking</v>
     <v>Muehlentalstrasse 2, SCHAFFHAUSEN, SCHAFFHAUSEN, 8200 CH</v>
     <v>GRMN</v>
     <v>Acciones</v>
     <v>Garmin Ltd. (XNYS:GRMN)</v>
-    <v>173797</v>
+    <v>382888</v>
     <v>1036306</v>
   </rv>
   <rv s="2">
@@ -10797,7 +10845,7 @@
     <v>Kingspan Group PLC es una empresa con sede en Irlanda, que participa en la fabricación de soluciones de aislamiento y envolvente de edificios de alto rendimiento. Sus segmentos incluyen paneles aislados; Aislamiento; Luz, aire + agua; Datos + pisos, y techos + impermeabilización. El segmento de paneles aislados fabrica paneles aislados, marcos estructurales y fachadas metálicas. El segmento de aislamiento fabrica placas de aislamiento rígido, aislamiento técnico y sistemas de madera de ingeniería. El segmento Luz, Aire + Agua fabrica soluciones de energía y agua, iluminación diurna, gestión de humos y sistemas de ventilación y actividades de servicio relacionadas. El segmento Data + Flooring se dedica a la fabricación de soluciones de almacenamiento de centros de datos y pisos de acceso elevados. El segmento Roofing + Waterproofing se dedica a la fabricación de soluciones de techos e impermeabilización para la renovación y nueva construcción de edificios. También ofrece soluciones de membrana de cloruro de polivinilo (PVC) para techos no residenciales.</v>
     <v>27955</v>
     <v>XFRA</v>
-    <v>46259.688194444447</v>
+    <v>46259.754861111112</v>
     <v>Deutsche Boerse AG</v>
     <v>95</v>
     <v>102.2</v>
@@ -10842,31 +10890,31 @@
     <v>2008</v>
     <v>106.5</v>
     <v>0.20369999999999999</v>
-    <v>1.71</v>
-    <v>1.6062E-2</v>
-    <v>20480204695</v>
+    <v>2.33</v>
+    <v>2.1886000000000003E-2</v>
+    <v>20597591465</v>
     <v>106.46</v>
     <v>Kaspi.kz AO (Joint Stock Company Kaspi.kz), formerly Aktsionernoe obshchestvo kaspi, is a Kazakhstan-based financial technology company, which provide a range of services such as online payments, e-commerce, and digital banking. The Company operates as holding company for Kaspi Group AO and Kaspi Magazin TOO. The Company operates through two segments. Mass retail offers a wide range of products and financial services to retail customers through a network of branches, offices, and automated teller machine (ATM). These products include savings and current accounts, credit cards, car loans and commodity loans, as well as a wide range of insurance policies. Financial services for corporate, middle, and small, and other businesses segment, including deposits, overdrafts, loans and other credit services and currency exchange.</v>
     <v>7700</v>
     <v>XNAS</v>
-    <v>46259.736895242968</v>
+    <v>46259.828997939061</v>
     <v>Nasdaq Stock Market</v>
     <v>98</v>
-    <v>108.3</v>
-    <v>108.3</v>
+    <v>108.79</v>
+    <v>108.79</v>
     <v>105.1</v>
     <v>68.59</v>
     <v>USD</v>
     <v>Kaspi.kz AO</v>
     <v>Kaspi.kz AO</v>
-    <v>9.2832000000000008</v>
-    <v>108.17</v>
+    <v>9.3363999999999994</v>
+    <v>108.79</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Bostandykskiy Rayon, Ul. Nauryzbay Batyra, 154A, ALMATY, ALMATY, 050013 KZ</v>
     <v>KSPI</v>
     <v>Acciones</v>
     <v>Kaspi.kz AO (XNAS:KSPI)</v>
-    <v>535581</v>
+    <v>643071</v>
     <v>542477</v>
   </rv>
   <rv s="2">
@@ -10945,14 +10993,14 @@
     <v>1998</v>
     <v>210.8</v>
     <v>2.2109999999999999</v>
-    <v>3.7866</v>
-    <v>1.8162999999999999E-2</v>
-    <v>5136851720000</v>
+    <v>4.2350000000000003</v>
+    <v>2.0314000000000002E-2</v>
+    <v>5147703000000</v>
     <v>208.48</v>
     <v>NVIDIA Corporation es una empresa de infraestructura de computación completa. La Compañía se dedica a la computación acelerada para ayudar a resolver los problemas computacionales desafiantes. Los segmentos de la Compañía incluyen Compute &amp; Networking y Gráficos. El segmento Compute &amp; Networking incluye sus plataformas de computación acelerada de centros de datos y soluciones y software de inteligencia artificial (IA); redes; plataformas automotrices y soluciones de vehículos autónomos y eléctricos; Jetson para robótica y otras plataformas integradas, y servicios de computación en la nube DGX. El segmento de gráficos incluye GPU GeForce para juegos y PC, el servicio de streaming de juegos GeForce NOW e infraestructura relacionada, y soluciones para plataformas de juegos; GPU Quadro/NVIDIA RTX para gráficos de estaciones de trabajo empresariales; software de GPU virtual para computación visual y virtual basada en la nube; plataformas automotrices para sistemas de infoentretenimiento y software Omniverse Enterprise para construir y operar aplicaciones industriales de IA y gemelas digitales.</v>
     <v>42000</v>
     <v>XNAS</v>
-    <v>46259.736876724222</v>
+    <v>46259.829004640625</v>
     <v>Nasdaq Stock Market</v>
     <v>104</v>
     <v>214.72909999999999</v>
@@ -10962,14 +11010,14 @@
     <v>USD</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>32.506399999999999</v>
-    <v>212.26660000000001</v>
+    <v>32.575000000000003</v>
+    <v>212.715</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
     <v>NVDA</v>
     <v>Acciones</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>68379799</v>
+    <v>88410411</v>
     <v>117539452</v>
   </rv>
   <rv s="2">
@@ -11049,14 +11097,14 @@
     <v>1987</v>
     <v>414.91</v>
     <v>1.3940999999999999</v>
-    <v>5.5250000000000004</v>
-    <v>1.3472E-2</v>
-    <v>2155731985730</v>
+    <v>6.35</v>
+    <v>1.5483E-2</v>
+    <v>2160010826780</v>
     <v>410.12</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd es una empresa con sede en Taiwán dedicada principalmente a la prestación de servicios de fabricación de circuitos integrados. Los servicios integrados de fabricación de circuitos incluyen tecnología de proceso, tecnología de proceso especial, soporte del ecosistema de diseño, tecnología de máscara, embalaje avanzado 3DFabricTM y servicios de tecnología de apilamiento de silicio. La compañía ha completado la transferencia y la producción en masa de la tecnología 5nm, y se dedica a la investigación y desarrollo de la tecnología de proceso 3nm y la tecnología de proceso 2nm. La gama de aplicaciones de productos cubre toda la industria de aplicaciones electrónicas, incluyendo computadoras personales y productos periféricos, productos de aplicaciones de información, productos de sistemas de comunicación cableados e inalámbricos, servidores y centros de datos.</v>
     <v>52045</v>
     <v>XNYS</v>
-    <v>46259.736848159373</v>
+    <v>46259.829015207812</v>
     <v>New York Stock Exchange</v>
     <v>110</v>
     <v>419.76949999999999</v>
@@ -11066,14 +11114,14 @@
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
-    <v>30.231400000000001</v>
-    <v>415.64499999999998</v>
+    <v>30.291399999999999</v>
+    <v>416.47</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>No.8, Li-Hsin 6th Road, Hsinchu Science Park, HSINCHU, HSINCHU, 300 TW</v>
     <v>TSM</v>
     <v>Acciones</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>4304845</v>
+    <v>5714738</v>
     <v>12203006</v>
   </rv>
   <rv s="2">
@@ -11101,14 +11149,14 @@
     <v>2007</v>
     <v>532.49</v>
     <v>1.5842000000000001</v>
-    <v>13.98</v>
-    <v>2.5992999999999999E-2</v>
-    <v>113417882244</v>
+    <v>12.88</v>
+    <v>2.3948000000000001E-2</v>
+    <v>113191794624</v>
     <v>537.84</v>
     <v>Spotify Technology SA es una empresa con sede en Luxemburgo que ofrece servicios de música digital en streaming. La Compañía permite a los usuarios descubrir nuevos lanzamientos, que incluyen los últimos singles y álbumes; listas de reproducción, que incluye listas de reproducción preparadas por fanáticos de la música y expertos, y más de millones de canciones para que los usuarios puedan reproducir sus favoritos, descubrir nuevas pistas y construir una colección personalizada. Sus usuarios pueden seleccionar Spotify Free, que incluye solo reproducción aleatoria o Spotify Premium, que abarca una gama de características, como reproducción aleatoria, publicidad gratuita, saltos ilimitados, escuchar sin conexión, reproducir cualquier pista y audio. La Compañía opera a través de una serie de subsidiarias, incluyendo Spotify LTD y está presente en más de 20 países. Su servicio ofrece una experiencia de escucha de música sin pausas comerciales.</v>
     <v>7287</v>
     <v>XNYS</v>
-    <v>46259.736869872657</v>
+    <v>46259.82901400391</v>
     <v>New York Stock Exchange</v>
     <v>113</v>
     <v>554.21</v>
@@ -11118,14 +11166,14 @@
     <v>USD</v>
     <v>Spotify Technology S.A.</v>
     <v>Spotify Technology S.A.</v>
-    <v>30.489799999999999</v>
-    <v>551.82000000000005</v>
+    <v>30.428999999999998</v>
+    <v>550.72</v>
     <v>Software &amp; IT Services</v>
     <v>33, Boulevard Prince Henri, LUXEMBOURG, 1724 LU</v>
     <v>SPOT</v>
     <v>Acciones</v>
     <v>Spotify Technology S.A. (XNYS:SPOT)</v>
-    <v>773242</v>
+    <v>1051649</v>
     <v>2048995</v>
   </rv>
   <rv s="2">
@@ -11169,7 +11217,7 @@
     <v>EUR</v>
     <v>Prysmian S.p.A.</v>
     <v>Prysmian S.p.A.</v>
-    <v>25.245100000000001</v>
+    <v>24.757000000000001</v>
     <v>121</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>Via Chiese 6, MILANO, MILANO, 20126 IT</v>
@@ -11177,7 +11225,7 @@
     <v>Acciones</v>
     <v>Prysmian S.p.A. (XMIL:PRY)</v>
     <v>1043254</v>
-    <v>1022350</v>
+    <v>1037820</v>
   </rv>
   <rv s="2">
     <v>117</v>
@@ -11320,7 +11368,7 @@
     <v>Sika AG es una compañía con base en Suiza activa en la industria química. La Compañía produce productos principalmente para las industrias de automóviles y autopartes, energía renovable y equipos y componentes. Las actividades de la Compañía se dividen en dos áreas de negocio: la División de Construcción ofrece una gama de productos, que incluyen mezclas de hormigón, morteros listos para usar, sistemas de techado, sistemas de impermeabilización, sistemas de pisos y soluciones de protección de acero, entre otros y la División Industria desarrolla soluciones de unión, sellado, amortiguación, acristalamiento y refuerzo, entre otros. Las marcas de la Compañía incluye Sarnafil, Sika, Sikadur, Sikaflex, SikaGrout, SikaPower, SikaHydroPrep, SikaReinforcer, Sika ViscoCrete, Sikaplan y SikaRapid, entre otros. La Compañía tiene una actividad global, con actividades divididas en regiones geográficas, a saber, Europa, Medio Oriente y África (EMEA), América del Norte, América Latina y Asia/ Pacifico. La Compañía opera a través de numerosas filiales.</v>
     <v>33856</v>
     <v>XSWX</v>
-    <v>46259.725555555553</v>
+    <v>46259.818414351852</v>
     <v>SIX Swiss Exchange</v>
     <v>125</v>
     <v>191.5</v>
@@ -11366,14 +11414,14 @@
     <v>1993</v>
     <v>129.80000000000001</v>
     <v>0.49270000000000003</v>
-    <v>-2.25</v>
-    <v>-1.7240999999999999E-2</v>
-    <v>13094401950</v>
+    <v>-0.89</v>
+    <v>-6.8200000000000005E-3</v>
+    <v>13233258766</v>
     <v>130.5</v>
     <v>Check Point Software Technologies Ltd es una empresa con sede en Israel dedicada principalmente a la industria de la ciberseguridad. La compañía se centra en proporcionar soluciones de seguridad basadas en IA y entregadas en la nube para proteger a las empresas corporativas y los gobiernos de todo el mundo. Su producto clave es Check Point Infinity Architecture, que es una plataforma integral de ciberseguridad. La Plataforma tiene como objetivo defenderse contra los ciberataques de quinta generación en varias redes, endpoints, entornos de nube, cargas de trabajo, Internet de las Cosas (IoT) y dispositivos móviles. Aparte de eso, la Compañía ofrece una gama de productos y servicios diseñados para proteger la infraestructura de TI. Integra tecnologías avanzadas de prevención de amenazas, incluyendo firewall, sistema de prevención de intrusiones (IPS), antivirus, anti-bot y capacidades de sandboxing.</v>
     <v>6825</v>
     <v>XNAS</v>
-    <v>46259.736859478908</v>
+    <v>46259.828961157029</v>
     <v>Nasdaq Stock Market</v>
     <v>128</v>
     <v>130.35</v>
@@ -11383,14 +11431,14 @@
     <v>USD</v>
     <v>CHECK POINT SOFTWARE TECHNOLOGIES LTD.</v>
     <v>CHECK POINT SOFTWARE TECHNOLOGIES LTD.</v>
-    <v>13.1381</v>
-    <v>128.25</v>
+    <v>13.2774</v>
+    <v>129.61000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>5 Shlomo Kaplan Street, TEL AVIV, TEL AVIV, 6789159 IL</v>
     <v>CHKP</v>
     <v>Acciones</v>
     <v>CHECK POINT SOFTWARE TECHNOLOGIES LTD. (XNAS:CHKP)</v>
-    <v>274926</v>
+    <v>584269</v>
     <v>1187282</v>
   </rv>
   <rv s="2">
@@ -11520,31 +11568,31 @@
     <v>2019</v>
     <v>47.25</v>
     <v>0.3654</v>
-    <v>1.01</v>
-    <v>2.1006999999999998E-2</v>
-    <v>10112687270</v>
+    <v>1.2</v>
+    <v>2.4958000000000001E-2</v>
+    <v>10151827840</v>
     <v>48.08</v>
     <v>Triple Flag Precious Metals Corp. is a precious metal streaming and royalty company. It offers investors exposure to gold and silver from a total of 242 assets, consisting of 17 streams and 225 royalties, from the Americas and Australia. These streams and royalties are tied to mining assets at various stages of the mine life cycle, including 36 producing mines and 206 development and exploration stage projects and other assets. It has a diversified portfolio of properties in Australia, Peru, South Africa, Colombia, Canada, Mexico, the United States, Mongolia, Cote d’Ivoire, and others. Its diversified portfolio of streams and royalties provides exposure to production from a suite of mining assets, including the Northparkes copper-gold mine in Australia (Evolution Mining), the Cerro Lindo polymetallic mine in Peru (Nexa), the Fosterville gold mine in Australia (Agnico Eagle), the Buritica gold mine in Colombia (Zijin) and the Impala Bafokeng Operations in South Africa (Implats).</v>
     <v>19</v>
     <v>XTSE</v>
-    <v>46259.724988425929</v>
+    <v>46259.818495370368</v>
     <v>Toronto Stock Exchange</v>
     <v>137</v>
-    <v>49.2</v>
+    <v>49.365000000000002</v>
     <v>57.26</v>
     <v>47.15</v>
     <v>35.950000000000003</v>
     <v>CAD</v>
     <v>Triple Flag Prec</v>
     <v>Triple Flag Prec</v>
-    <v>17.3689</v>
-    <v>49.09</v>
+    <v>17.436199999999999</v>
+    <v>49.28</v>
     <v>Metals &amp; Mining</v>
     <v>TD Canada Trust Tower, 161 Bay Street, Suite 4535, Toronto, ON, M5J 2S1 CA</v>
     <v>TFPM</v>
     <v>Acciones</v>
     <v>Triple Flag Prec (XTSE:TFPM)</v>
-    <v>86672</v>
+    <v>126600</v>
     <v>238650</v>
   </rv>
   <rv s="2">
@@ -11572,31 +11620,31 @@
     <v>1997</v>
     <v>79.510000000000005</v>
     <v>1.5216000000000001</v>
-    <v>1.98</v>
-    <v>2.4746999999999998E-2</v>
-    <v>341401358610</v>
+    <v>2.335</v>
+    <v>2.9184000000000002E-2</v>
+    <v>342879556955</v>
     <v>80.010000000000005</v>
     <v>Netflix, Inc. Es un proveedor de servicios de entretenimiento. La Compañía adquiere, concede licencias y produce contenido, incluida la programación original. Ofrece membresías pagadas en más de 190 países que ofrecen series de televisión (TV), películas y juegos en una variedad de géneros e idiomas. Permite a los miembros jugar, pausar y reanudar la mirada tanto como quieran, en cualquier momento y en cualquier lugar, y puede cambiar sus planes en cualquier momento. La Compañía ofrece a los miembros la posibilidad de recibir contenido en streaming a través de una serie de dispositivos conectados a Internet, incluidos televisores, reproductores de video digital, decodificadores de TV y dispositivos móviles. Se dedica a escalar su servicio de streaming, como la introducción de juegos y publicidad en su servicio, así como ofrecer programación en vivo. Está desarrollando tecnología y utilizando computación en la nube de terceros, tecnología y otros servicios. La Compañía también se dedica a escalar sus propias operaciones de estudio para producir contenido original.</v>
     <v>16000</v>
     <v>XNAS</v>
-    <v>46259.736888321095</v>
+    <v>46259.829037823438</v>
     <v>Nasdaq Stock Market</v>
     <v>140</v>
-    <v>82.325000000000003</v>
+    <v>82.454999999999998</v>
     <v>126.71</v>
     <v>79.400000000000006</v>
     <v>65.08</v>
     <v>USD</v>
     <v>NETFLIX, INC.</v>
     <v>NETFLIX, INC.</v>
-    <v>25.830100000000002</v>
-    <v>81.99</v>
+    <v>25.942</v>
+    <v>82.344999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>121 Albright Way, LOS GATOS, CA, 95032 US</v>
     <v>NFLX</v>
     <v>Acciones</v>
     <v>NETFLIX, INC. (XNAS:NFLX)</v>
-    <v>15188105</v>
+    <v>22268965</v>
     <v>35113398</v>
   </rv>
   <rv s="2">
@@ -11624,14 +11672,14 @@
     <v>1969</v>
     <v>39.6</v>
     <v>1.1161000000000001</v>
-    <v>-1.08</v>
-    <v>-2.6503000000000002E-2</v>
-    <v>58850405330</v>
+    <v>-1.28</v>
+    <v>-3.1410999999999994E-2</v>
+    <v>58553705530</v>
     <v>40.75</v>
     <v>NIKE, Inc. Se dedica al diseño, comercialización y distribución de calzado deportivo, ropa, equipos y accesorios y servicios para actividades deportivas y de fitness. Los segmentos operativos de la compañía incluyen América del Norte, Europa, Oriente Medio y África (EMEA), Gran China y Asia Pacífico y América Latina (APLA). Vende una línea de equipos y accesorios bajo la marca NIKE, incluyendo bolsos, calcetines, bolas deportivas, gafas, relojes, dispositivos digitales, murciélagos, guantes, equipos de protección y otros equipos diseñados para actividades deportivas. También diseña productos específicamente para la marca Jordan y Converse. La marca Jordan diseña, distribuye y otorga licencias de calzado deportivo y casual, ropa y accesorios principalmente centrados en el rendimiento y la cultura del baloncesto utilizando la marca Jumpman. La Compañía también diseña, distribuye y otorga licencias de zapatillas de deporte casuales, ropa y accesorios bajo las marcas registradas Chuck Taylor, All Star, One Star, Star Chevron y Jack Purcell.</v>
     <v>73000</v>
     <v>XNYS</v>
-    <v>46259.736870532033</v>
+    <v>46259.829026145315</v>
     <v>New York Stock Exchange</v>
     <v>143</v>
     <v>39.865000000000002</v>
@@ -11641,14 +11689,14 @@
     <v>USD</v>
     <v>NIKE, INC.</v>
     <v>NIKE, INC.</v>
-    <v>18.906700000000001</v>
-    <v>39.67</v>
+    <v>18.811399999999999</v>
+    <v>39.47</v>
     <v>Textiles &amp; Apparel</v>
     <v>One Bowerman Dr, BEAVERTON, OR, 97005-6453 US</v>
     <v>NKE</v>
     <v>Acciones</v>
     <v>NIKE, INC. (XNYS:NKE)</v>
-    <v>24289581</v>
+    <v>33114441</v>
     <v>23006900</v>
   </rv>
   <rv s="2">
@@ -11729,31 +11777,31 @@
     <v>2024</v>
     <v>237.21</v>
     <v>1.1198999999999999</v>
-    <v>-2.06</v>
-    <v>-8.7119999999999993E-3</v>
-    <v>45343378353</v>
+    <v>-3.9950000000000001</v>
+    <v>-1.6896000000000001E-2</v>
+    <v>44969047378</v>
     <v>236.45</v>
     <v>Ferguson Enterprises Inc. Es un distribuidor de valor agregado que sirve a profesionales especializados en el mercado de la construcción residencial y no residencial de América del Norte. Los segmentos geográficos de la Compañía incluyen Estados Unidos y Canadá. La Compañía ofrece una amplia gama de productos y servicios, tales como plomería, calefacción, ventilación y aire acondicionado (HVAC), electrodomésticos e iluminación para tuberías, válvulas y accesorios (PVF), soluciones de agua y aguas residuales, y más. Se vende a través de una red común de centros de distribución, sucursales, servicio de mostrador y asociados de ventas especializados, consultores de showroom y canales de comercio electrónico. La compañía sirve a diversas industrias, tales como plomería, HVAC, comercial / mecánica, suministro de instalaciones, fuego y fabricación, industrial, constructor, obras de agua. Las marcas de la compañía incluyen Armateck, Durastar, FNW, National Fire Products, Pollardwater, PROFLO, PROSELECT, Raptor, Hardware de firma y Westcraft.</v>
     <v>35000</v>
     <v>XNYS</v>
-    <v>46259.736896110939</v>
+    <v>46259.828951863281</v>
     <v>New York Stock Exchange</v>
     <v>149</v>
     <v>237.76499999999999</v>
     <v>271.64</v>
-    <v>233.34</v>
+    <v>232.1901</v>
     <v>207.64</v>
     <v>USD</v>
     <v>FERGUSON ENTERPRISES INC.</v>
     <v>FERGUSON ENTERPRISES INC.</v>
-    <v>23.065100000000001</v>
-    <v>234.39</v>
+    <v>22.874700000000001</v>
+    <v>232.45500000000001</v>
     <v>Homebuilding &amp; Construction Supplies</v>
     <v>751 Lakefront Commons, NEWPORT NEWS, VA, 23606 US</v>
     <v>FERG</v>
     <v>Acciones</v>
     <v>FERGUSON ENTERPRISES INC. (XNYS:FERG)</v>
-    <v>813653</v>
+    <v>1241057</v>
     <v>3782353</v>
   </rv>
   <rv s="2">
@@ -11781,31 +11829,31 @@
     <v>2013</v>
     <v>20.76</v>
     <v>0.76</v>
-    <v>-0.6139</v>
-    <v>-2.9485999999999998E-2</v>
-    <v>6926725842</v>
+    <v>-0.56499999999999995</v>
+    <v>-2.7136999999999998E-2</v>
+    <v>6943488943</v>
     <v>20.82</v>
     <v>SentinelOne, Inc. Es un proveedor de ciberseguridad impulsado por inteligencia artificial (IA). La Plataforma Singularity de la compañía ofrece capacidades autónomas de prevención, detección, respuesta y administración de exposición de amenazas impulsadas por IA en los endpoints, cargas de trabajo en la nube y credenciales de identidad de una organización. La plataforma Singularity de la compañía ingiere, correlaciona y consulta petabytes de datos estructurados y no estructurados de una miríada de fuentes externas e internas dispares en constante expansión en tiempo real. Sus modelos de IA distribuida se ejecutan tanto localmente en cada endpoint y cada carga de trabajo en la nube, así como en su plataforma en la nube. La compañía a través de PingSafe Pte. Ltd. (PingSafe), que es una plataforma de protección de aplicaciones nativa en la nube (CNAPP) para reforzar su paquete de productos de seguridad en la nube. Al agregar CNAPP de PingSafe a su Cloud Workload Security (CWS), proporciona a las empresas una cobertura de seguridad en la nube integral que impulsa la seguridad, la postura mejorada y la protección autónoma.</v>
     <v>2700</v>
     <v>XNYS</v>
-    <v>46259.736888587497</v>
+    <v>46259.829034039059</v>
     <v>New York Stock Exchange</v>
     <v>152</v>
     <v>20.91</v>
     <v>23.95</v>
-    <v>20.18</v>
+    <v>19.934999999999999</v>
     <v>11.81</v>
     <v>USD</v>
     <v>SENTINELONE, INC.</v>
     <v>SENTINELONE, INC.</v>
     <v>0</v>
-    <v>20.206099999999999</v>
+    <v>20.254999999999999</v>
     <v>Software &amp; IT Services</v>
     <v>444 Castro Street, Suite 400, MOUNTAIN VIEW, CA, 94041 US</v>
     <v>S</v>
     <v>Acciones</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
-    <v>1980784</v>
+    <v>3458387</v>
     <v>6492375</v>
   </rv>
   <rv s="2">
@@ -11833,31 +11881,31 @@
     <v>1998</v>
     <v>47.75</v>
     <v>1.4733000000000001</v>
-    <v>-0.42</v>
-    <v>-8.8849999999999988E-3</v>
-    <v>4772384620</v>
+    <v>-0.49</v>
+    <v>-1.0366E-2</v>
+    <v>4765254056</v>
     <v>47.27</v>
     <v>Trex Company, Inc. Es un fabricante de terrazas alternativas de madera y barandillas residenciales y productos y accesorios para vivir al aire libre, comercializados bajo la marca Trex. El segmento de la compañía es Trex Residential. Sus categorías de productos incluyen cubiertas y accesorios, barandillas y cercas. Sus productos de terrazas están hechos en un proceso patentado que combina fibras de madera recuperadas y película de polietileno reciclado. Sus cubiertas y accesorios incluyen cubiertas Trex Signature, cubiertas Trex Transcend Lineage, cubiertas Trex Transcend, cubiertas Trex Select, cubiertas Trex Enhance, colección de sujetadores Trex Hideaway y sistema de iluminación exterior Trex DeckLighting. Su producto de decking Trex Transcend también se puede utilizar como revestimiento. Sus productos de barandilla incluyen barandilla Trex Signature X-Series, barandilla de aluminio Trex Signature, barandilla Trex Transcend, barandilla Trex Select, carril T Trex Select y barandilla Trex Enhance. Su producto compuesto de esgrima Trex Seclusions se ofrece a través de dos distribuidores especializados.</v>
     <v>1839</v>
     <v>XNYS</v>
-    <v>46259.736879664066</v>
+    <v>46259.82898721016</v>
     <v>New York Stock Exchange</v>
     <v>155</v>
     <v>48</v>
     <v>66.055000000000007</v>
-    <v>46.82</v>
+    <v>46.486800000000002</v>
     <v>29.77</v>
     <v>USD</v>
     <v>TREX COMPANY, INC.</v>
     <v>TREX COMPANY, INC.</v>
-    <v>27.649899999999999</v>
-    <v>46.85</v>
+    <v>27.608599999999999</v>
+    <v>46.78</v>
     <v>Homebuilding &amp; Construction Supplies</v>
     <v>2500 TREX WAY, WINCHESTER, VA, 22601 US</v>
     <v>TREX</v>
     <v>Acciones</v>
     <v>TREX COMPANY, INC. (XNYS:TREX)</v>
-    <v>595089</v>
+    <v>856422</v>
     <v>2039791</v>
   </rv>
   <rv s="2">
@@ -11989,14 +12037,14 @@
     <v>2005</v>
     <v>35</v>
     <v>0.93210000000000004</v>
-    <v>0.35499999999999998</v>
-    <v>1.0134000000000001E-2</v>
-    <v>8953643475</v>
+    <v>0.47</v>
+    <v>1.3416999999999998E-2</v>
+    <v>8982742500</v>
     <v>35.03</v>
     <v>Celsius Holdings, Inc. Se dedica al desarrollo, procesamiento, comercialización, venta y distribución de bebidas energéticas funcionales a una amplia gama de consumidores. El activo insignia de la Compañía, CELSIUS, se comercializa como un estilo de vida y bebida energética. Esta línea de productos viene en dos versiones: Una forma lista para beber y una forma de polvo en movimiento. También ofrece una nueva línea CELSIUS Essentials, disponible en latas de 16 onzas y una línea de hidratación de polvos con cero azúcar que se infunden con electrolitos y están disponibles en una variedad de sabores frutales. Los productos Celsius se ofrecen en canales minoristas a través de los Estados Unidos, incluyendo comestibles convencionales, naturales, conveniencia, fitness, etc. mercado masivo, especialidad de vitaminas y plataformas de comercio electrónico. Sus productos también se ofrecen en mercados seleccionados de Europa, Oriente Medio y la región de Asia-Pacífico. La formulación de su producto incluye ingredientes y suplementos como el té verde (EGCG), jengibre (de la raíz), calcio, cromo, vitaminas B y vitamina C.</v>
     <v>1497</v>
     <v>XNAS</v>
-    <v>46259.736849872657</v>
+    <v>46259.829011515627</v>
     <v>Nasdaq Stock Market</v>
     <v>164</v>
     <v>35.65</v>
@@ -12006,14 +12054,14 @@
     <v>USD</v>
     <v>CELSIUS HOLDINGS, INC.</v>
     <v>CELSIUS HOLDINGS, INC.</v>
-    <v>152.12809999999999</v>
-    <v>35.384999999999998</v>
+    <v>152.6225</v>
+    <v>35.5</v>
     <v>Beverages</v>
     <v>2424 N. Federal Hwy, Suite 208, BOCA RATON, FL, 33431 US</v>
     <v>CELH</v>
     <v>Acciones</v>
     <v>CELSIUS HOLDINGS, INC. (XNAS:CELH)</v>
-    <v>4511589</v>
+    <v>6020025</v>
     <v>12600191</v>
   </rv>
   <rv s="2">
@@ -12242,14 +12290,14 @@
     <v>2017</v>
     <v>34.56</v>
     <v>0.3357</v>
-    <v>-0.13</v>
-    <v>-3.6909999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-7.6659999999999992E-3</v>
     <v>27016750000</v>
     <v>35.22</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION es una compañía spin-off con sede en Canadá para activos no noruegos de Lundin Petroleum AB. La Compañía se dedica a la producción y exploración de petróleo y gas natural, así como a líquidos de gas natural. La Compañía es propietaria directa o indirecta de varias subsidiarias de Lundin Petroleum AB. La Compañía tiene una cartera de activos en tres jurisdicciones: Malasia (Bertam), Francia (París y Cuenca de Aquitania) y los Países Bajos. La cartera está orientada hacia el petróleo ligero, con líquidos que representan el 94% de las reservas 2P y con la producción de gas generada principalmente a partir de los activos de petróleo y gas en los Países Bajos. La Compañía opera la mayoría de sus volúmenes producidos en la Cuenca de París y Malasia y posee intereses no operados en la Cuenca de Aquitania y los Países Bajos.</v>
     <v>131</v>
     <v>XTSE</v>
-    <v>46259.72215277778</v>
+    <v>46259.817511574074</v>
     <v>Toronto Stock Exchange</v>
     <v>178</v>
     <v>35.35</v>
@@ -12259,14 +12307,14 @@
     <v>CAD</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION</v>
-    <v>134.1874</v>
-    <v>35.090000000000003</v>
+    <v>133.65199999999999</v>
+    <v>34.950000000000003</v>
     <v>Oil &amp; Gas</v>
     <v>Suite 2800, 1055 Dunsmuir Street, VANCOUVER, BC, V7X 1L2 CA</v>
     <v>IPCO</v>
     <v>Acciones</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION (XTSE:IPCO)</v>
-    <v>109640</v>
+    <v>121836</v>
     <v>159030</v>
   </rv>
   <rv s="2">
@@ -12294,14 +12342,14 @@
     <v>2016</v>
     <v>15.9</v>
     <v>1.8165</v>
-    <v>-0.13500000000000001</v>
-    <v>-8.4930000000000005E-3</v>
-    <v>502937217</v>
+    <v>-0.32</v>
+    <v>-2.0131999999999997E-2</v>
+    <v>497033449</v>
     <v>15.895</v>
     <v>Oatly Group AB (publ) is a Sweden-based company that is primarily focused on manufacture, distribution and sale oat-based products. The Company's scope of activity concentrates on developing the know-how around oats, and what follows - the alternatives to milk, ice cream, yogurt, cooking creams, spreads and on-the-go drinks. Moreover, the Company distributes their oat-based dairy substitute products primarily under its own brand, Oatly. Apart from oatmilk production, Oatly Group AB (publ) also handles the administration of Oatly Group and its financing. The major operations in the Group take place in underlying companies, primarily in Oatly AB. Oatly Group AB (publ) products are available in over 20 countries.</v>
     <v>1404</v>
     <v>XNAS</v>
-    <v>46259.736454363279</v>
+    <v>46259.828983517968</v>
     <v>Nasdaq Stock Market</v>
     <v>181</v>
     <v>16.2</v>
@@ -12312,13 +12360,13 @@
     <v>Oatly Group</v>
     <v>Oatly Group</v>
     <v>0</v>
-    <v>15.76</v>
+    <v>15.574999999999999</v>
     <v>Food &amp; Tobacco</v>
     <v>Angfarjekajen 8, MALMO, SKANE, 211 36 SE</v>
     <v>OTLY</v>
     <v>Acciones</v>
     <v>Oatly Group (XNAS:OTLY)</v>
-    <v>76627</v>
+    <v>109722</v>
     <v>207028</v>
   </rv>
   <rv s="2">
@@ -12346,14 +12394,14 @@
     <v>2002</v>
     <v>3106.02</v>
     <v>0.69550000000000001</v>
-    <v>-46.38</v>
-    <v>-1.4967999999999999E-2</v>
-    <v>64682695103</v>
+    <v>-43.69</v>
+    <v>-1.41E-2</v>
+    <v>64739700319</v>
     <v>3098.67</v>
     <v>Constellation Software Inc. Es un proveedor de software y servicios con sede en Canadá para varias industrias. La Compañía adquiere, administra y construye negocios de software de mercado vertical (VMS) que proporcionan soluciones de software de misión crítica. Se dedica principalmente al desarrollo, instalación y personalización de software, así como en el suministro de servicios profesionales relacionados y soporte para clientes de todo el mundo. Sus servicios profesionales incluyen la instalación, implementación, capacitación y personalización de software y otros servicios. La Compañía vende licencias de software en las instalaciones tanto a perpetuo como a plazo especificado. Cuenta con seis grupos operativos, que dan servicio a clientes en más de 100 mercados diferentes en todo el mundo. Los seis grupos operativos incluyen Volaris, Harris, Topicus.com, Vela, Jonas, y Grupo Perseus. Opera oficinas en América del Norte, Europa Continental, Reino Unido, América del Sur, África, y Australia.</v>
     <v>64000</v>
     <v>XTSE</v>
-    <v>46259.726400462961</v>
+    <v>46259.816851851851</v>
     <v>Toronto Stock Exchange</v>
     <v>184</v>
     <v>3106.02</v>
@@ -12363,14 +12411,14 @@
     <v>CAD</v>
     <v>Constellation Software Inc.</v>
     <v>Constellation Software Inc.</v>
-    <v>47.416499999999999</v>
-    <v>3052.29</v>
+    <v>47.458300000000001</v>
+    <v>3054.98</v>
     <v>Software &amp; IT Services</v>
     <v>#66 Wellington Street West, Suite 5300, TD Bank Tower, TORONTO, ON, M5K 1E6 CA</v>
     <v>CSU</v>
     <v>Acciones</v>
     <v>Constellation Software Inc. (XTSE:CSU)</v>
-    <v>14449</v>
+    <v>22539</v>
     <v>53640</v>
   </rv>
   <rv s="2">
@@ -12398,31 +12446,31 @@
     <v>2010</v>
     <v>79.38</v>
     <v>1.1629</v>
-    <v>0.52</v>
-    <v>6.5580000000000005E-3</v>
-    <v>163016713600</v>
+    <v>0.82499999999999996</v>
+    <v>1.0404999999999999E-2</v>
+    <v>163639694400</v>
     <v>79.290000000000006</v>
     <v>Uber Technologies, Inc. Opera una plataforma tecnológica que utiliza redes y tecnología para impulsar el movimiento desde el punto A al punto B. Desarrolla y opera aplicaciones tecnológicas que soportan una variedad de ofertas en su plataforma (plataforma(s)). Sus segmentos incluyen Movilidad, Entrega y Carga. Los productos de movilidad conectan a los consumidores con conductores que ofrecen viajes en una variedad de vehículos, como automóviles, rickshaws de automóviles, motos, minibuses, etc. o taxis. Las ofertas de entrega permiten a los consumidores buscar y descubrir restaurantes locales, pedir una comida y recoger en el restaurante o hacer que se les entregue la comida. En ciertos mercados, el segmento de Entrega ofrece ofertas para la entrega de comestibles, alcohol y tiendas de conveniencia, así como otros productos seleccionados. El segmento de carga conecta a los transportistas con los transportistas en su plataforma, y ofrece a los transportistas por adelantado, precios y la capacidad de reservar un envío. El segmento de carga también incluye la gestión del transporte y otras ofertas de servicios logísticos.</v>
     <v>34000</v>
     <v>XNYS</v>
-    <v>46259.736892303124</v>
+    <v>46259.829024513281</v>
     <v>New York Stock Exchange</v>
     <v>187</v>
-    <v>80.19</v>
+    <v>80.290000000000006</v>
     <v>101.99</v>
     <v>78.61</v>
     <v>65.41</v>
     <v>USD</v>
     <v>UBER TECHNOLOGIES, INC.</v>
     <v>UBER TECHNOLOGIES, INC.</v>
-    <v>17.519100000000002</v>
-    <v>79.81</v>
+    <v>17.585999999999999</v>
+    <v>80.114999999999995</v>
     <v>Software &amp; IT Services</v>
     <v>1725 3Rd Street, SAN FRANCISCO, CA, 94158 US</v>
     <v>UBER</v>
     <v>Acciones</v>
     <v>UBER TECHNOLOGIES, INC. (XNYS:UBER)</v>
-    <v>6925648</v>
+    <v>10572650</v>
     <v>19803871</v>
   </rv>
   <rv s="2">
@@ -12570,7 +12618,7 @@
     <v>EUR</v>
     <v>Robertet</v>
     <v>Robertet</v>
-    <v>16.6691</v>
+    <v>16.690000000000001</v>
     <v>798</v>
     <v>Chemicals</v>
     <v>37 Avenue Sidi Brahim, Bp 52100, GRASSE, PACA, 06130 FR</v>
@@ -12653,14 +12701,14 @@
     <v>1992</v>
     <v>78.254999999999995</v>
     <v>1.1266</v>
-    <v>0.18</v>
-    <v>2.3259999999999999E-3</v>
-    <v>1157404612</v>
+    <v>0.28000000000000003</v>
+    <v>3.6189999999999998E-3</v>
+    <v>1158896882</v>
     <v>77.38</v>
     <v>U.S. Physical Therapy, Inc. is an operator of outpatient physical therapy clinics and provider of industrial injury prevention services. It owns and/or manages 795 outpatient physical therapy clinics in 45 states. Its reportable segments include the Physical Therapy Operations segment and the Industrial Injury Prevention Services (IIP) segment. The Physical Therapy Operations segment consists of physical therapy, speech therapy and occupational therapy clinics and home-care physical and speech therapy practices that provide pre- and post-operative care and treatment for a variety of orthopedic-related disorders, sports-related injuries, and rehabilitation of injured workers. The IIP segment includes onsite services for clients’ employees, including injury prevention and rehabilitation, performance optimization, post-offer employment testing, functional capacity evaluations and ergonomic assessments. The majority of these services are contracted with and paid for directly by employers.</v>
     <v>4200</v>
     <v>XNYS</v>
-    <v>46259.736806550784</v>
+    <v>46259.828895381252</v>
     <v>New York Stock Exchange</v>
     <v>201</v>
     <v>78.499899999999997</v>
@@ -12670,14 +12718,14 @@
     <v>USD</v>
     <v>US Physical</v>
     <v>US Physical</v>
-    <v>441.43430000000001</v>
-    <v>77.56</v>
+    <v>442.0034</v>
+    <v>77.66</v>
     <v>Healthcare Providers &amp; Services</v>
     <v>1300 West Sam Houston Parkway South, Suite 300, HOUSTON, TX, 77043 US</v>
     <v>USPH</v>
     <v>Acciones</v>
     <v>US Physical (XNYS:USPH)</v>
-    <v>71017</v>
+    <v>92360</v>
     <v>237137</v>
   </rv>
   <rv s="2">
@@ -12697,18 +12745,18 @@
     <v>Finance</v>
     <v>51</v>
     <v>185.52</v>
-    <v>0.34</v>
-    <v>1.833E-3</v>
+    <v>0.2</v>
+    <v>1.078E-3</v>
     <v>185.52</v>
     <v>EUR</v>
-    <v>46259.736840277779</v>
+    <v>46259.829027777778</v>
     <v>185.94</v>
     <v>187.93</v>
     <v>185.53</v>
     <v>171.06</v>
     <v>JPY</v>
     <v>Euro/Japanese Yen FX Cross Rate</v>
-    <v>185.86</v>
+    <v>185.72</v>
     <v>EURJPY</v>
     <v>Par de divisa</v>
     <v>EUR/JPY</v>
@@ -12730,18 +12778,18 @@
     <v>Finance</v>
     <v>51</v>
     <v>1.2458</v>
-    <v>0</v>
-    <v>0</v>
+    <v>1.4E-3</v>
+    <v>1.124E-3</v>
     <v>1.2461</v>
     <v>CHF</v>
-    <v>46259.736886574072</v>
-    <v>1.2472000000000001</v>
+    <v>46259.829027777778</v>
+    <v>1.2478</v>
     <v>1.3149</v>
     <v>1.2435</v>
     <v>1.2181999999999999</v>
     <v>USD</v>
     <v>Swiss Franc/US Dollar FX Cross Rate</v>
-    <v>1.2461</v>
+    <v>1.2475000000000001</v>
     <v>CHFUSD</v>
     <v>Par de divisa</v>
     <v>CHF/USD</v>
@@ -12763,18 +12811,18 @@
     <v>Finance</v>
     <v>51</v>
     <v>457.19</v>
-    <v>0.63</v>
-    <v>1.3780000000000001E-3</v>
+    <v>0.66</v>
+    <v>1.444E-3</v>
     <v>457.15</v>
     <v>USD</v>
-    <v>46259.736875000002</v>
+    <v>46259.77611111111</v>
     <v>459.69</v>
     <v>549.66</v>
     <v>456.73</v>
     <v>453.81</v>
     <v>KZT</v>
     <v>US Dollar/Kazakhstan Tenge FX Spot Rate</v>
-    <v>457.78</v>
+    <v>457.81</v>
     <v>USDKZT</v>
     <v>Par de divisa</v>
     <v>USD/KZT</v>
@@ -12796,18 +12844,18 @@
     <v>Finance</v>
     <v>51</v>
     <v>0.72209999999999996</v>
-    <v>4.0000000000000002E-4</v>
-    <v>5.5380000000000002E-4</v>
+    <v>6.9999999999999999E-4</v>
+    <v>9.6909999999999997E-4</v>
     <v>0.72230000000000005</v>
     <v>CAD</v>
-    <v>46259.736828703702</v>
-    <v>0.72319999999999995</v>
+    <v>46259.829016203701</v>
+    <v>0.72330000000000005</v>
     <v>0.74170000000000003</v>
     <v>0.72109999999999996</v>
     <v>0.70169999999999999</v>
     <v>USD</v>
     <v>Canadian Dollar/US Dollar FX Cross Rate</v>
-    <v>0.72270000000000001</v>
+    <v>0.72299999999999998</v>
     <v>CADUSD</v>
     <v>Par de divisa</v>
     <v>CAD/USD</v>
@@ -12829,18 +12877,18 @@
     <v>Finance</v>
     <v>51</v>
     <v>0.85729999999999995</v>
-    <v>-5.0000000000000001E-4</v>
-    <v>-5.8319999999999997E-4</v>
+    <v>-8.0000000000000004E-4</v>
+    <v>-9.3320000000000002E-4</v>
     <v>0.85729999999999995</v>
     <v>USD</v>
-    <v>46259.736840277779</v>
+    <v>46259.828981481478</v>
     <v>0.85819999999999996</v>
     <v>0.88300000000000001</v>
-    <v>0.85650000000000004</v>
+    <v>0.85629999999999995</v>
     <v>0.82779999999999998</v>
     <v>EUR</v>
     <v>US Dollar/Euro FX Cross Rate</v>
-    <v>0.85680000000000001</v>
+    <v>0.85650000000000004</v>
     <v>USDEUR</v>
     <v>Par de divisa</v>
     <v>USD/EUR</v>
@@ -15883,7 +15931,7 @@
       </c>
       <c r="G4" s="12">
         <f t="array" aca="1" ref="G4" ca="1">_FV(A4,"Precio")</f>
-        <v>243.84</v>
+        <v>245.75</v>
       </c>
       <c r="H4" s="13" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">_FV(A4,"Acciones en circulación",TRUE)/1000000</f>
@@ -15891,7 +15939,7 @@
       </c>
       <c r="I4" s="14">
         <f t="shared" ref="I4:I16" ca="1" si="0">G4*H4</f>
-        <v>39610.174271999997</v>
+        <v>39920.440974999998</v>
       </c>
       <c r="J4" s="90">
         <v>1.5</v>
@@ -16004,7 +16052,7 @@
       </c>
       <c r="AR4" s="19">
         <f t="shared" ref="AR4:AR11" ca="1" si="8">I4-AP4+AQ4</f>
-        <v>32397.174271999997</v>
+        <v>32707.440974999998</v>
       </c>
       <c r="AS4" s="19">
         <v>1640</v>
@@ -16020,15 +16068,15 @@
       </c>
       <c r="AW4" s="20">
         <f t="shared" ref="AW4:AW35" ca="1" si="9">AR4/AS4</f>
-        <v>19.754374556097559</v>
+        <v>19.94356157012195</v>
       </c>
       <c r="AX4" s="20">
         <f t="shared" ref="AX4:AX35" ca="1" si="10">AR4/AU4</f>
-        <v>30.854451687619044</v>
+        <v>31.149943785714285</v>
       </c>
       <c r="AY4" s="20">
         <f t="shared" ref="AY4:AY35" ca="1" si="11">AR4/AV4</f>
-        <v>9.7611251196143414</v>
+        <v>9.8546071030430848</v>
       </c>
       <c r="AZ4" s="21">
         <v>1500</v>
@@ -16074,12 +16122,12 @@
         <v>651.6304458232504</v>
       </c>
       <c r="BL4" s="23">
-        <f t="shared" ref="BL4:BL35" ca="1" si="18">($BJ4/G4)^(1/5)-1</f>
-        <v>-2.9177844379771334E-2</v>
+        <f t="shared" ref="BL4:BL35" ca="1" si="18">IF($BJ4&lt;=0,-0.99,MAX(-0.99,($BJ4/G4)^(1/5)-1))</f>
+        <v>-3.0691628302968677E-2</v>
       </c>
       <c r="BM4" s="23">
-        <f t="shared" ref="BM4:BM35" ca="1" si="19">(BK4/G4)^(1/5)-1</f>
-        <v>0.21724859954203968</v>
+        <f t="shared" ref="BM4:BM35" ca="1" si="19">IF(BK4&lt;=0,-0.99,MAX(-0.99,(BK4/G4)^(1/5)-1))</f>
+        <v>0.21535056770391781</v>
       </c>
       <c r="BN4" t="s">
         <v>79</v>
@@ -16115,7 +16163,7 @@
       </c>
       <c r="G5" s="12">
         <f t="array" aca="1" ref="G5" ca="1">_FV(A5,"Precio")</f>
-        <v>489.83</v>
+        <v>491.01499999999999</v>
       </c>
       <c r="H5" s="13">
         <f t="array" aca="1" ref="H5" ca="1">_FV(A5,"Acciones en circulación",TRUE())/1000000</f>
@@ -16123,7 +16171,7 @@
       </c>
       <c r="I5" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>3637254.7073499998</v>
+        <v>3646053.9781749998</v>
       </c>
       <c r="J5" s="91">
         <v>1</v>
@@ -16236,7 +16284,7 @@
       </c>
       <c r="AR5" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>3600705.7073499998</v>
+        <v>3609504.9781749998</v>
       </c>
       <c r="AS5" s="19">
         <v>124961</v>
@@ -16252,15 +16300,15 @@
       </c>
       <c r="AW5" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>28.814635825177454</v>
+        <v>28.885051961612021</v>
       </c>
       <c r="AX5" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>18.582273443136486</v>
+        <v>18.627684112560701</v>
       </c>
       <c r="AY5" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>10.850761083989525</v>
+        <v>10.877277770771368</v>
       </c>
       <c r="AZ5" s="21">
         <v>589551</v>
@@ -16307,11 +16355,11 @@
       </c>
       <c r="BL5" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-4.1895880509692951E-2</v>
+        <v>-4.2358779191663531E-2</v>
       </c>
       <c r="BM5" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.12780422738436692</v>
+        <v>0.12725933974662795</v>
       </c>
       <c r="BN5" s="99">
         <v>46256</v>
@@ -16579,7 +16627,7 @@
       </c>
       <c r="G7" s="12">
         <f t="array" aca="1" ref="G7" ca="1">_FV(A7,"Precio")</f>
-        <v>42.075000000000003</v>
+        <v>42.12</v>
       </c>
       <c r="H7" s="13">
         <f t="array" aca="1" ref="H7" ca="1">_FV(A7,"Acciones en circulación",TRUE())/1000000</f>
@@ -16587,7 +16635,7 @@
       </c>
       <c r="I7" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>103164.323625</v>
+        <v>103274.65979999999</v>
       </c>
       <c r="J7" s="91">
         <v>1</v>
@@ -16700,7 +16748,7 @@
       </c>
       <c r="AR7" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>110979.323625</v>
+        <v>111089.65979999999</v>
       </c>
       <c r="AS7" s="19">
         <v>6200</v>
@@ -16716,15 +16764,15 @@
       </c>
       <c r="AW7" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>17.899890907258065</v>
+        <v>17.917687064516127</v>
       </c>
       <c r="AX7" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>19.47005677631579</v>
+        <v>19.489414</v>
       </c>
       <c r="AY7" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>1.3753789022803322</v>
+        <v>1.3767463105713222</v>
       </c>
       <c r="AZ7" s="21">
         <v>90000</v>
@@ -16771,20 +16819,20 @@
       </c>
       <c r="BL7" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>1.6521030185501884E-2</v>
+        <v>1.6303731954826928E-2</v>
       </c>
       <c r="BM7" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.21900244611200459</v>
+        <v>0.21874186412022789</v>
       </c>
       <c r="BN7" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO7" t="s">
         <v>88</v>
       </c>
       <c r="BP7" s="96" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -16811,7 +16859,7 @@
       </c>
       <c r="G8" s="12">
         <f t="array" aca="1" ref="G8" ca="1">_FV(A8,"Precio")</f>
-        <v>961.91</v>
+        <v>961.36</v>
       </c>
       <c r="H8" s="13">
         <f t="array" aca="1" ref="H8" ca="1">_FV(A8,"Acciones en circulación",TRUE())/1000000</f>
@@ -16819,7 +16867,7 @@
       </c>
       <c r="I8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>426586.69250799995</v>
+        <v>426342.77916799998</v>
       </c>
       <c r="J8" s="90">
         <v>1.5</v>
@@ -16932,7 +16980,7 @@
       </c>
       <c r="AR8" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>414816.69250799995</v>
+        <v>414572.77916799998</v>
       </c>
       <c r="AS8" s="19">
         <v>11905</v>
@@ -16948,15 +16996,15 @@
       </c>
       <c r="AW8" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>34.843905292566141</v>
+        <v>34.823416981772361</v>
       </c>
       <c r="AX8" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>30.080978426976067</v>
+        <v>30.06329073009427</v>
       </c>
       <c r="AY8" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>1.4129115177901153</v>
+        <v>1.4120807219864435</v>
       </c>
       <c r="AZ8" s="21">
         <v>44305</v>
@@ -17003,14 +17051,14 @@
       </c>
       <c r="BL8" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-4.9816250558583963E-2</v>
+        <v>-4.9707554230484341E-2</v>
       </c>
       <c r="BM8" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>8.4916787387159243E-2</v>
+        <v>8.5040896509370301E-2</v>
       </c>
       <c r="BN8" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO8" t="s">
         <v>92</v>
@@ -17043,7 +17091,7 @@
       </c>
       <c r="G9" s="12">
         <f t="array" aca="1" ref="G9" ca="1">_FV(A9,"Precio")</f>
-        <v>77.3</v>
+        <v>77.48</v>
       </c>
       <c r="H9" s="13">
         <f t="array" aca="1" ref="H9" ca="1">_FV(A9,"Acciones en circulación",TRUE())/1000000</f>
@@ -17051,7 +17099,7 @@
       </c>
       <c r="I9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>6621.0279179999998</v>
+        <v>6636.4455768000007</v>
       </c>
       <c r="J9" s="91">
         <v>1</v>
@@ -17164,7 +17212,7 @@
       </c>
       <c r="AR9" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>6252.1279180000001</v>
+        <v>6267.5455768000011</v>
       </c>
       <c r="AS9" s="19">
         <v>281</v>
@@ -17180,15 +17228,15 @@
       </c>
       <c r="AW9" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>22.249565544483985</v>
+        <v>22.304432657651251</v>
       </c>
       <c r="AX9" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>19.53789974375</v>
+        <v>19.586079927500002</v>
       </c>
       <c r="AY9" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>8.2919468408488068</v>
+        <v>8.3123946641909825</v>
       </c>
       <c r="AZ9" s="21">
         <v>1676</v>
@@ -17235,20 +17283,20 @@
       </c>
       <c r="BL9" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.6669624209512586E-2</v>
+        <v>-3.7117638736870018E-2</v>
       </c>
       <c r="BM9" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.19745985531708032</v>
+        <v>0.19690295456465767</v>
       </c>
       <c r="BN9" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO9" t="s">
         <v>80</v>
       </c>
       <c r="BP9" s="96" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -17474,7 +17522,7 @@
         <v>0.12867081613737774</v>
       </c>
       <c r="BN10" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO10" s="95" t="s">
         <v>125</v>
@@ -17507,7 +17555,7 @@
       </c>
       <c r="G11" s="12">
         <f t="array" aca="1" ref="G11" ca="1">_FV(A11,"Precio")</f>
-        <v>168.5</v>
+        <v>168.54</v>
       </c>
       <c r="H11" s="13">
         <f t="array" aca="1" ref="H11" ca="1">_FV(A11,"Acciones en circulación",TRUE())/1000000</f>
@@ -17515,7 +17563,7 @@
       </c>
       <c r="I11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>27248.050749999999</v>
+        <v>27254.519129999997</v>
       </c>
       <c r="J11" s="91">
         <v>1</v>
@@ -17628,7 +17676,7 @@
       </c>
       <c r="AR11" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>25578.050749999999</v>
+        <v>25584.519129999997</v>
       </c>
       <c r="AS11" s="19">
         <v>963</v>
@@ -17644,15 +17692,15 @@
       </c>
       <c r="AW11" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>26.560800363447559</v>
+        <v>26.567517268951192</v>
       </c>
       <c r="AX11" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>-419.31230737704914</v>
+        <v>-419.41834639344256</v>
       </c>
       <c r="AY11" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>8.0687857255520505</v>
+        <v>8.0708262239747626</v>
       </c>
       <c r="AZ11" s="21">
         <v>4597</v>
@@ -17699,14 +17747,14 @@
       </c>
       <c r="BL11" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-2.4255031214933664E-2</v>
+        <v>-2.430135078832063E-2</v>
       </c>
       <c r="BM11" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.25949207403006769</v>
+        <v>0.25943228470250812</v>
       </c>
       <c r="BN11" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO11" t="s">
         <v>92</v>
@@ -17739,7 +17787,7 @@
       </c>
       <c r="G12" s="12">
         <f t="array" aca="1" ref="G12" ca="1">_FV(A12,"Precio")</f>
-        <v>48</v>
+        <v>50.1</v>
       </c>
       <c r="H12" s="13">
         <f t="array" aca="1" ref="H12" ca="1">_FV(A12,"Acciones en circulación",TRUE())/1000000</f>
@@ -17747,7 +17795,7 @@
       </c>
       <c r="I12" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>61788.479999999996</v>
+        <v>64491.726000000002</v>
       </c>
       <c r="J12" s="90">
         <v>1</v>
@@ -17860,7 +17908,7 @@
       </c>
       <c r="AR12" s="19">
         <f ca="1">I12*'Framework Notes'!E4-AP12+AQ12</f>
-        <v>9516098.8927999996</v>
+        <v>10009495.35272</v>
       </c>
       <c r="AS12" s="19">
         <v>262620</v>
@@ -17876,15 +17924,15 @@
       </c>
       <c r="AW12" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>36.235240624476425</v>
+        <v>38.113987330439414</v>
       </c>
       <c r="AX12" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>20.615465538994801</v>
+        <v>21.684348684402078</v>
       </c>
       <c r="AY12" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>4.2134579053983146</v>
+        <v>4.431919823245595</v>
       </c>
       <c r="AZ12" s="21">
         <v>1600000</v>
@@ -17923,22 +17971,22 @@
       </c>
       <c r="BJ12" s="25">
         <f ca="1">((BD12*BH12+$AP12-$AQ12)/$H12)/'Framework Notes'!E4</f>
-        <v>24.690509736438038</v>
+        <v>24.709122009554029</v>
       </c>
       <c r="BK12" s="25">
         <f ca="1">((BF12*BI12+$AP12-$AQ12)/$H12)/'Framework Notes'!E4</f>
-        <v>53.729457824241827</v>
+        <v>53.76996032314014</v>
       </c>
       <c r="BL12" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.12449674769032804</v>
+        <v>-0.13183171301735208</v>
       </c>
       <c r="BM12" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>2.2808301254799268E-2</v>
+        <v>1.423921438264375E-2</v>
       </c>
       <c r="BN12" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO12" s="100" t="s">
         <v>125</v>
@@ -17971,7 +18019,7 @@
       </c>
       <c r="G13" s="12">
         <f t="array" aca="1" ref="G13" ca="1">_FV(A13,"Precio")</f>
-        <v>260.22000000000003</v>
+        <v>260.75</v>
       </c>
       <c r="H13" s="13">
         <f t="array" aca="1" ref="H13" ca="1">_FV(A13,"Acciones en circulación",TRUE())/1000000</f>
@@ -17979,7 +18027,7 @@
       </c>
       <c r="I13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>2806813.5882000001</v>
+        <v>2812530.3325</v>
       </c>
       <c r="J13" s="91">
         <v>1.5</v>
@@ -18092,7 +18140,7 @@
       </c>
       <c r="AR13" s="19">
         <f t="shared" ref="AR13:AR32" ca="1" si="21">I13-AP13+AQ13</f>
-        <v>2857494.5882000001</v>
+        <v>2863211.3325</v>
       </c>
       <c r="AS13" s="19">
         <v>76899</v>
@@ -18108,15 +18156,15 @@
       </c>
       <c r="AW13" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>37.159060432515382</v>
+        <v>37.233401377131045</v>
       </c>
       <c r="AX13" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>20.706482523188406</v>
+        <v>20.747908206521739</v>
       </c>
       <c r="AY13" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>3.6839714876182228</v>
+        <v>3.6913416933537548</v>
       </c>
       <c r="AZ13" s="21">
         <v>300000</v>
@@ -18163,14 +18211,14 @@
       </c>
       <c r="BL13" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-6.0627169269325321E-2</v>
+        <v>-6.1009353645609887E-2</v>
       </c>
       <c r="BM13" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.11301923910271405</v>
+        <v>0.11256640658534334</v>
       </c>
       <c r="BN13" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO13" s="93" t="s">
         <v>106</v>
@@ -18402,7 +18450,7 @@
         <v>9.4174490275463096E-2</v>
       </c>
       <c r="BN14" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO14" s="93" t="s">
         <v>106</v>
@@ -18634,7 +18682,7 @@
         <v>0.10741088468091919</v>
       </c>
       <c r="BN15" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO15" t="s">
         <v>110</v>
@@ -18791,7 +18839,7 @@
         <v>10824.731</v>
       </c>
       <c r="AS16" s="19">
-        <v>183</v>
+        <v>131.69999999999999</v>
       </c>
       <c r="AT16" s="19">
         <v>190</v>
@@ -18804,7 +18852,7 @@
       </c>
       <c r="AW16" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>59.15153551912568</v>
+        <v>82.192338648443439</v>
       </c>
       <c r="AX16" s="20">
         <f t="shared" ca="1" si="10"/>
@@ -18830,18 +18878,18 @@
         <v>0.14514896867838048</v>
       </c>
       <c r="BD16" s="98">
-        <v>256.2</v>
+        <v>185</v>
       </c>
       <c r="BE16" s="23">
         <f t="shared" si="15"/>
-        <v>6.9610375725068785E-2</v>
+        <v>7.0328748919836093E-2</v>
       </c>
       <c r="BF16">
-        <v>419</v>
+        <v>243</v>
       </c>
       <c r="BG16" s="23">
         <f t="shared" si="16"/>
-        <v>0.18019178321090878</v>
+        <v>0.13032699494236311</v>
       </c>
       <c r="BH16" s="24">
         <v>15</v>
@@ -18851,28 +18899,28 @@
       </c>
       <c r="BJ16" s="25">
         <f ca="1">(BD16*BH16+$AP16-$AQ16)/$H16</f>
-        <v>4544.0619600249993</v>
+        <v>3235.2544699207119</v>
       </c>
       <c r="BK16" s="25">
         <f ca="1">(BF16*BI16+$AP16-$AQ16)/$H16</f>
-        <v>12671.413340522788</v>
+        <v>7279.3225573216014</v>
       </c>
       <c r="BL16" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.19083965708991213</v>
+        <v>-0.24399019156889146</v>
       </c>
       <c r="BM16" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-6.630657915443261E-3</v>
+        <v>-0.11087272348127619</v>
       </c>
       <c r="BN16" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO16" s="95" t="s">
         <v>104</v>
       </c>
       <c r="BP16" s="95" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19131,7 +19179,7 @@
       </c>
       <c r="G18" s="12">
         <f t="array" aca="1" ref="G18" ca="1">_FV(A18,"Precio")</f>
-        <v>1143.33</v>
+        <v>1137.27</v>
       </c>
       <c r="H18" s="13">
         <f t="array" aca="1" ref="H18" ca="1">_FV(A18,"Acciones en circulación",TRUE())/1000000</f>
@@ -19139,7 +19187,7 @@
       </c>
       <c r="I18" s="14">
         <f t="shared" ref="I18:I25" ca="1" si="22">G18*H18</f>
-        <v>24693.229741199997</v>
+        <v>24562.348042799997</v>
       </c>
       <c r="J18" s="90">
         <v>0</v>
@@ -19252,7 +19300,7 @@
       </c>
       <c r="AR18" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>26893.229741199997</v>
+        <v>26762.348042799997</v>
       </c>
       <c r="AS18" s="19">
         <v>730</v>
@@ -19268,15 +19316,15 @@
       </c>
       <c r="AW18" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>36.840040741369862</v>
+        <v>36.660750743561643</v>
       </c>
       <c r="AX18" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>30.73511970422857</v>
+        <v>30.585540620342854</v>
       </c>
       <c r="AY18" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>15.635598686744185</v>
+        <v>15.55950467604651</v>
       </c>
       <c r="AZ18" s="21">
         <v>2200</v>
@@ -19323,11 +19371,11 @@
       </c>
       <c r="BL18" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-7.07025913355247E-2</v>
+        <v>-6.9714333956378272E-2</v>
       </c>
       <c r="BM18" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.10791391779857418</v>
+        <v>0.10909212414512681</v>
       </c>
       <c r="BN18" s="93" t="s">
         <v>83</v>
@@ -19595,7 +19643,7 @@
       </c>
       <c r="G20" s="12">
         <f t="array" aca="1" ref="G20" ca="1">_FV(A20,"Precio")</f>
-        <v>59.6</v>
+        <v>59.1</v>
       </c>
       <c r="H20" s="13">
         <f t="array" aca="1" ref="H20" ca="1">_FV(A20,"Acciones en circulación",TRUE())/1000000</f>
@@ -19603,7 +19651,7 @@
       </c>
       <c r="I20" s="14">
         <f t="shared" ca="1" si="22"/>
-        <v>5721.6</v>
+        <v>5673.6</v>
       </c>
       <c r="J20" s="90">
         <v>0.5</v>
@@ -19716,7 +19764,7 @@
       </c>
       <c r="AR20" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>4481.6000000000004</v>
+        <v>4433.6000000000004</v>
       </c>
       <c r="AS20" s="19">
         <v>274</v>
@@ -19732,15 +19780,15 @@
       </c>
       <c r="AW20" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>16.356204379562044</v>
+        <v>16.181021897810222</v>
       </c>
       <c r="AX20" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>8.4718336483931953</v>
+        <v>8.3810964083175818</v>
       </c>
       <c r="AY20" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>1.3580606060606062</v>
+        <v>1.3435151515151516</v>
       </c>
       <c r="AZ20" s="21">
         <v>1573</v>
@@ -19787,14 +19835,14 @@
       </c>
       <c r="BL20" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.9229015671845779E-2</v>
+        <v>-3.7608819307332841E-2</v>
       </c>
       <c r="BM20" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.15549957158625838</v>
+        <v>0.15744814854748856</v>
       </c>
       <c r="BN20" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO20" t="s">
         <v>92</v>
@@ -19827,7 +19875,7 @@
       </c>
       <c r="G21" s="12">
         <f t="array" aca="1" ref="G21" ca="1">_FV(A21,"Precio")</f>
-        <v>48.61</v>
+        <v>48.844999999999999</v>
       </c>
       <c r="H21" s="13">
         <f t="array" aca="1" ref="H21" ca="1">_FV(A21,"Acciones en circulación",TRUE())/1000000</f>
@@ -19835,7 +19883,7 @@
       </c>
       <c r="I21" s="14">
         <f t="shared" ca="1" si="22"/>
-        <v>95081.937760000001</v>
+        <v>95541.601519999997</v>
       </c>
       <c r="J21" s="91">
         <v>0</v>
@@ -19948,7 +19996,7 @@
       </c>
       <c r="AR21" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>91755.937760000001</v>
+        <v>92215.601519999997</v>
       </c>
       <c r="AS21" s="19">
         <v>2100</v>
@@ -19964,15 +20012,15 @@
       </c>
       <c r="AW21" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>43.693303695238093</v>
+        <v>43.912191199999995</v>
       </c>
       <c r="AX21" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>31.316019713310581</v>
+        <v>31.472901542662115</v>
       </c>
       <c r="AY21" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>9.9518370672451191</v>
+        <v>10.001692138828632</v>
       </c>
       <c r="AZ21" s="21">
         <v>9665</v>
@@ -20007,7 +20055,7 @@
         <v>18</v>
       </c>
       <c r="BI21" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BJ21" s="25">
         <f t="shared" ca="1" si="23"/>
@@ -20015,18 +20063,18 @@
       </c>
       <c r="BK21" s="25">
         <f t="shared" ca="1" si="24"/>
-        <v>47.173438254083813</v>
+        <v>51.307351269110271</v>
       </c>
       <c r="BL21" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.12304367658880577</v>
+        <v>-0.12388913665846968</v>
       </c>
       <c r="BM21" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-5.9816951414956021E-3</v>
+        <v>9.8849409169941005E-3</v>
       </c>
       <c r="BN21" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO21" s="93" t="s">
         <v>125</v>
@@ -20059,7 +20107,7 @@
       </c>
       <c r="G22" s="12">
         <f t="array" aca="1" ref="G22" ca="1">_FV(A22,"Precio")</f>
-        <v>189.95</v>
+        <v>190.11</v>
       </c>
       <c r="H22" s="13">
         <f t="array" aca="1" ref="H22" ca="1">_FV(A22,"Acciones en circulación",TRUE())/1000000</f>
@@ -20067,7 +20115,7 @@
       </c>
       <c r="I22" s="14">
         <f t="shared" ca="1" si="22"/>
-        <v>111991.80371499999</v>
+        <v>112086.13742700001</v>
       </c>
       <c r="J22" s="90">
         <v>1.5</v>
@@ -20180,7 +20228,7 @@
       </c>
       <c r="AR22" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>102418.80371499999</v>
+        <v>102513.13742700001</v>
       </c>
       <c r="AS22" s="19">
         <v>4800</v>
@@ -20196,15 +20244,15 @@
       </c>
       <c r="AW22" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>21.337250773958331</v>
+        <v>21.356903630625002</v>
       </c>
       <c r="AX22" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>35.636326971120383</v>
+        <v>35.669150113778706</v>
       </c>
       <c r="AY22" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>7.783175295615167</v>
+        <v>7.7903440555513344</v>
       </c>
       <c r="AZ22" s="21">
         <v>10662</v>
@@ -20251,14 +20299,14 @@
       </c>
       <c r="BL22" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-4.029888100678769E-2</v>
+        <v>-4.0460475765684678E-2</v>
       </c>
       <c r="BM22" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.16592790507589994</v>
+        <v>0.1657315857896311</v>
       </c>
       <c r="BN22" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO22" s="95" t="s">
         <v>125</v>
@@ -20490,13 +20538,13 @@
         <v>0.13746109747208712</v>
       </c>
       <c r="BN23" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO23" s="96" t="s">
         <v>88</v>
       </c>
       <c r="BP23" s="96" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="24" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -20523,7 +20571,7 @@
       </c>
       <c r="G24" s="12">
         <f t="array" aca="1" ref="G24" ca="1">_FV(A24,"Precio")</f>
-        <v>98.194999999999993</v>
+        <v>98.844999999999999</v>
       </c>
       <c r="H24" s="13">
         <f t="array" aca="1" ref="H24" ca="1">_FV(A24,"Acciones en circulación",TRUE())/1000000</f>
@@ -20531,7 +20579,7 @@
       </c>
       <c r="I24" s="14">
         <f t="shared" ca="1" si="22"/>
-        <v>23939.283093499998</v>
+        <v>24097.748738499999</v>
       </c>
       <c r="J24" s="90">
         <v>2</v>
@@ -20644,7 +20692,7 @@
       </c>
       <c r="AR24" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>25409.283093499998</v>
+        <v>25567.748738499999</v>
       </c>
       <c r="AS24" s="19">
         <v>1050</v>
@@ -20660,15 +20708,15 @@
       </c>
       <c r="AW24" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>24.199317231904761</v>
+        <v>24.350236893809523</v>
       </c>
       <c r="AX24" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>18.280059779496401</v>
+        <v>18.39406384064748</v>
       </c>
       <c r="AY24" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>4.4577689637719295</v>
+        <v>4.4855699541228065</v>
       </c>
       <c r="AZ24" s="21">
         <v>6501</v>
@@ -20715,14 +20763,14 @@
       </c>
       <c r="BL24" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-9.5473248221805362E-2</v>
+        <v>-9.6666014737439077E-2</v>
       </c>
       <c r="BM24" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>8.2282923728493218E-2</v>
+        <v>8.0855756616710517E-2</v>
       </c>
       <c r="BN24" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO24" s="93" t="s">
         <v>128</v>
@@ -20954,7 +21002,7 @@
         <v>0.10491795222211375</v>
       </c>
       <c r="BN25" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO25" s="95" t="s">
         <v>125</v>
@@ -21186,13 +21234,13 @@
         <v>0.31684805256802173</v>
       </c>
       <c r="BN26" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO26" s="95" t="s">
         <v>147</v>
       </c>
       <c r="BP26" s="95" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="27" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -21418,7 +21466,7 @@
         <v>6.6237833093061527E-2</v>
       </c>
       <c r="BN27" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO27" s="100" t="s">
         <v>131</v>
@@ -21451,7 +21499,7 @@
       </c>
       <c r="G28" s="12">
         <f t="array" aca="1" ref="G28" ca="1">_FV(A28,"Precio")</f>
-        <v>565.05999999999995</v>
+        <v>568.70000000000005</v>
       </c>
       <c r="H28" s="13">
         <f t="array" aca="1" ref="H28" ca="1">_FV(A28,"Acciones en circulación",TRUE())/1000000</f>
@@ -21459,7 +21507,7 @@
       </c>
       <c r="I28" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>1439493.7403599997</v>
+        <v>1448766.6622000001</v>
       </c>
       <c r="J28" s="90">
         <v>-0.5</v>
@@ -21572,7 +21620,7 @@
       </c>
       <c r="AR28" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>1461553.7403599997</v>
+        <v>1470826.6622000001</v>
       </c>
       <c r="AS28" s="19">
         <v>85640</v>
@@ -21588,15 +21636,15 @@
       </c>
       <c r="AW28" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>17.066251055114428</v>
+        <v>17.174528984119572</v>
       </c>
       <c r="AX28" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>13.328047969724601</v>
+        <v>13.412608628488055</v>
       </c>
       <c r="AY28" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>6.4033022578751355</v>
+        <v>6.4439284214676897</v>
       </c>
       <c r="AZ28" s="21">
         <v>393577</v>
@@ -21643,14 +21691,14 @@
       </c>
       <c r="BL28" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-4.4126189439631758E-2</v>
+        <v>-4.5352960331777936E-2</v>
       </c>
       <c r="BM28" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.26454787038117189</v>
+        <v>0.26292494641153241</v>
       </c>
       <c r="BN28" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO28" s="93" t="s">
         <v>84</v>
@@ -21683,7 +21731,7 @@
       </c>
       <c r="G29" s="12">
         <f t="array" aca="1" ref="G29" ca="1">_FV(A29,"Precio")</f>
-        <v>107.58</v>
+        <v>107.72499999999999</v>
       </c>
       <c r="H29" s="13">
         <f t="array" aca="1" ref="H29" ca="1">_FV(A29,"Acciones en circulación",TRUE())/1000000</f>
@@ -21691,7 +21739,7 @@
       </c>
       <c r="I29" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>96567.637847999998</v>
+        <v>96697.795009999987</v>
       </c>
       <c r="J29" s="91">
         <v>0</v>
@@ -21804,7 +21852,7 @@
       </c>
       <c r="AR29" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>131651.63784799998</v>
+        <v>131781.79501</v>
       </c>
       <c r="AS29" s="19">
         <v>5000</v>
@@ -21820,15 +21868,15 @@
       </c>
       <c r="AW29" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>26.330327569599998</v>
+        <v>26.356359002000001</v>
       </c>
       <c r="AX29" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>19.498169112559239</v>
+        <v>19.517445943424171</v>
       </c>
       <c r="AY29" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>5.0962581909960125</v>
+        <v>5.101296597762552</v>
       </c>
       <c r="AZ29" s="21">
         <v>80000</v>
@@ -21875,14 +21923,14 @@
       </c>
       <c r="BL29" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-6.2025761416033554E-2</v>
+        <v>-6.2278403886486977E-2</v>
       </c>
       <c r="BM29" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.23368644814706618</v>
+        <v>0.23335415587377817</v>
       </c>
       <c r="BN29" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO29" s="95" t="s">
         <v>106</v>
@@ -21915,7 +21963,7 @@
       </c>
       <c r="G30" s="12">
         <f t="array" aca="1" ref="G30" ca="1">_FV(A30,"Precio")</f>
-        <v>275.81</v>
+        <v>277.39</v>
       </c>
       <c r="H30" s="13">
         <f t="array" aca="1" ref="H30" ca="1">_FV(A30,"Acciones en circulación",TRUE())/1000000</f>
@@ -21923,7 +21971,7 @@
       </c>
       <c r="I30" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>98210.342057000002</v>
+        <v>98772.947982999991</v>
       </c>
       <c r="J30" s="90">
         <v>1</v>
@@ -22036,7 +22084,7 @@
       </c>
       <c r="AR30" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>97576.342057000002</v>
+        <v>98138.947982999991</v>
       </c>
       <c r="AS30" s="19">
         <v>342</v>
@@ -22052,15 +22100,15 @@
       </c>
       <c r="AW30" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>285.31094168713452</v>
+        <v>286.95598825438594</v>
       </c>
       <c r="AX30" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>-48788.171028500001</v>
+        <v>-49069.473991499995</v>
       </c>
       <c r="AY30" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>38.844085213773887</v>
+        <v>39.068052541003183</v>
       </c>
       <c r="AZ30" s="21">
         <v>3846</v>
@@ -22107,14 +22155,14 @@
       </c>
       <c r="BL30" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.32468468389562533</v>
+        <v>-0.325455755361031</v>
       </c>
       <c r="BM30" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-0.18238523641727311</v>
+        <v>-0.18331878464113061</v>
       </c>
       <c r="BN30" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO30" s="95" t="s">
         <v>125</v>
@@ -22147,7 +22195,7 @@
       </c>
       <c r="G31" s="12">
         <f t="array" aca="1" ref="G31" ca="1">_FV(A31,"Precio")</f>
-        <v>183.3</v>
+        <v>185.20500000000001</v>
       </c>
       <c r="H31" s="13">
         <f t="array" aca="1" ref="H31" ca="1">_FV(A31,"Acciones en circulación",TRUE())/1000000</f>
@@ -22155,7 +22203,7 @@
       </c>
       <c r="I31" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>186658.42260000002</v>
+        <v>188598.32601000002</v>
       </c>
       <c r="J31" s="91">
         <v>1</v>
@@ -22268,7 +22316,7 @@
       </c>
       <c r="AR31" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>182929.42260000002</v>
+        <v>184869.32601000002</v>
       </c>
       <c r="AS31" s="19">
         <v>1510</v>
@@ -22284,15 +22332,15 @@
       </c>
       <c r="AW31" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>121.14531298013246</v>
+        <v>122.43001722516557</v>
       </c>
       <c r="AX31" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>3100.4986881355935</v>
+        <v>3133.378406949153</v>
       </c>
       <c r="AY31" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>35.938982829076622</v>
+        <v>36.32010334184676</v>
       </c>
       <c r="AZ31" s="21">
         <v>7154</v>
@@ -22339,14 +22387,14 @@
       </c>
       <c r="BL31" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.21132167938899171</v>
+        <v>-0.21295084941557374</v>
       </c>
       <c r="BM31" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-4.5877313596097258E-2</v>
+        <v>-4.784824146586153E-2</v>
       </c>
       <c r="BN31" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO31" t="s">
         <v>80</v>
@@ -22379,7 +22427,7 @@
       </c>
       <c r="G32" s="12">
         <f t="array" aca="1" ref="G32" ca="1">_FV(A32,"Precio")</f>
-        <v>343.32510000000002</v>
+        <v>343.76510000000002</v>
       </c>
       <c r="H32" s="13">
         <f t="array" aca="1" ref="H32" ca="1">_FV(A32,"Acciones en circulación",TRUE())/1000000</f>
@@ -22387,7 +22435,7 @@
       </c>
       <c r="I32" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>4198865.9730000002</v>
+        <v>4204247.1730000004</v>
       </c>
       <c r="J32" s="90">
         <v>1</v>
@@ -22500,7 +22548,7 @@
       </c>
       <c r="AR32" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>4077185.9730000002</v>
+        <v>4082567.1730000004</v>
       </c>
       <c r="AS32" s="19">
         <v>119475</v>
@@ -22516,15 +22564,15 @@
       </c>
       <c r="AW32" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>34.125850370370372</v>
+        <v>34.170890755388157</v>
       </c>
       <c r="AX32" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>23.54577253984754</v>
+        <v>23.576849000924003</v>
       </c>
       <c r="AY32" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>9.1443379751945635</v>
+        <v>9.1564069639132484</v>
       </c>
       <c r="AZ32" s="21">
         <v>795872</v>
@@ -22571,14 +22619,14 @@
       </c>
       <c r="BL32" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-5.4585002792887805E-2</v>
+        <v>-5.4827142402877116E-2</v>
       </c>
       <c r="BM32" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.11790528475856199</v>
+        <v>0.11761896695055585</v>
       </c>
       <c r="BN32" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO32" s="93" t="s">
         <v>133</v>
@@ -22732,7 +22780,7 @@
       </c>
       <c r="AR33" s="19">
         <f ca="1">I33*'Framework Notes'!E5-AP33+AQ33</f>
-        <v>184718.519444084</v>
+        <v>184922.35535390003</v>
       </c>
       <c r="AS33" s="19">
         <v>4870</v>
@@ -22748,15 +22796,15 @@
       </c>
       <c r="AW33" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>37.929880789339627</v>
+        <v>37.971736212299803</v>
       </c>
       <c r="AX33" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>25.834757964207551</v>
+        <v>25.86326648306294</v>
       </c>
       <c r="AY33" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>5.1669515928415102</v>
+        <v>5.1726532966125882</v>
       </c>
       <c r="AZ33" s="21">
         <v>27296</v>
@@ -22795,22 +22843,22 @@
       </c>
       <c r="BJ33" s="25">
         <f ca="1">((BD33*BH33+$AP33-$AQ33)/$H33)/'Framework Notes'!E5</f>
-        <v>35.065441902372577</v>
+        <v>35.02608990344406</v>
       </c>
       <c r="BK33" s="25">
         <f ca="1">((BF33*BI33+$AP33-$AQ33)/$H33)/'Framework Notes'!E5</f>
-        <v>92.99982633215599</v>
+        <v>92.895457789578813</v>
       </c>
       <c r="BL33" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.15177708262240708</v>
+        <v>-0.15196755084126234</v>
       </c>
       <c r="BM33" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>3.0933296240593267E-2</v>
+        <v>3.0701800457267003E-2</v>
       </c>
       <c r="BN33" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO33" s="93" t="s">
         <v>134</v>
@@ -22843,7 +22891,7 @@
       </c>
       <c r="G34" s="12">
         <f t="array" aca="1" ref="G34" ca="1">_FV(A34,"Precio")</f>
-        <v>289.07</v>
+        <v>289.01499999999999</v>
       </c>
       <c r="H34" s="13">
         <f t="array" aca="1" ref="H34" ca="1">_FV(A34,"Acciones en circulación",TRUE())/1000000</f>
@@ -22851,7 +22899,7 @@
       </c>
       <c r="I34" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>55747.872174999997</v>
+        <v>55737.265287499999</v>
       </c>
       <c r="J34" s="90">
         <v>0</v>
@@ -22964,7 +23012,7 @@
       </c>
       <c r="AR34" s="19">
         <f ca="1">I34-AP34+AQ34</f>
-        <v>53304.872174999997</v>
+        <v>53294.265287499999</v>
       </c>
       <c r="AS34" s="19">
         <v>1600</v>
@@ -22980,15 +23028,15 @@
       </c>
       <c r="AW34" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>33.315545109374995</v>
+        <v>33.308915804687501</v>
       </c>
       <c r="AX34" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>23.075702240259737</v>
+        <v>23.071110514069264</v>
       </c>
       <c r="AY34" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>6.9497877672750974</v>
+        <v>6.9484048614732723</v>
       </c>
       <c r="AZ34" s="21">
         <v>9341</v>
@@ -23035,14 +23083,14 @@
       </c>
       <c r="BL34" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-7.628226402961813E-2</v>
+        <v>-7.6247109723681095E-2</v>
       </c>
       <c r="BM34" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>7.2435514956375791E-2</v>
+        <v>7.2476329076016865E-2</v>
       </c>
       <c r="BN34" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO34" s="93" t="s">
         <v>84</v>
@@ -23273,13 +23321,13 @@
         <v>5.7941616311690369E-2</v>
       </c>
       <c r="BN35" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO35" s="95" t="s">
         <v>104</v>
       </c>
       <c r="BP35" s="95" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="36" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -23306,7 +23354,7 @@
       </c>
       <c r="G36" s="12">
         <f t="array" aca="1" ref="G36" ca="1">_FV(A36,"Precio")</f>
-        <v>108.17</v>
+        <v>108.79</v>
       </c>
       <c r="H36" s="13">
         <f t="array" aca="1" ref="H36" ca="1">_FV(A36,"Acciones en circulación",TRUE())/1000000</f>
@@ -23314,7 +23362,7 @@
       </c>
       <c r="I36" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>20480.204695</v>
+        <v>20597.591465000001</v>
       </c>
       <c r="J36" s="90">
         <v>1</v>
@@ -23427,7 +23475,7 @@
       </c>
       <c r="AR36" s="19">
         <f ca="1">I36*'Framework Notes'!E6-AP36+AQ36</f>
-        <v>8575428.1052770987</v>
+        <v>8629783.3485916499</v>
       </c>
       <c r="AS36" s="19">
         <v>940085</v>
@@ -23443,15 +23491,15 @@
       </c>
       <c r="AW36" s="20">
         <f t="shared" ref="AW36:AW66" ca="1" si="35">AR36/AS36</f>
-        <v>9.1219709975981953</v>
+        <v>9.1797904961696553</v>
       </c>
       <c r="AX36" s="20">
         <f t="shared" ref="AX36:AX66" ca="1" si="36">AR36/AU36</f>
-        <v>5.3394461108837685</v>
+        <v>5.3732901229796104</v>
       </c>
       <c r="AY36" s="20">
         <f t="shared" ref="AY36:AY66" ca="1" si="37">AR36/AV36</f>
-        <v>1.9272773111962813</v>
+        <v>1.9394933342214435</v>
       </c>
       <c r="AZ36" s="21">
         <v>2601577</v>
@@ -23490,28 +23538,28 @@
       </c>
       <c r="BJ36" s="25">
         <f ca="1">((BD36*BH36+$AP36-$AQ36)/$H36)/'Framework Notes'!E6</f>
-        <v>81.68625383292455</v>
+        <v>81.680900984330179</v>
       </c>
       <c r="BK36" s="25">
         <f ca="1">((BF36*BI36+$AP36-$AQ36)/$H36)/'Framework Notes'!E6</f>
-        <v>482.56039075735447</v>
+        <v>482.52876887988839</v>
       </c>
       <c r="BL36" s="23">
-        <f t="shared" ref="BL36:BL64" ca="1" si="43">($BJ36/G36)^(1/5)-1</f>
-        <v>-5.4615603614305841E-2</v>
+        <f t="shared" ref="BL36:BL71" ca="1" si="43">IF($BJ36&lt;=0,-0.99,MAX(-0.99,($BJ36/G36)^(1/5)-1))</f>
+        <v>-5.5708003930611705E-2</v>
       </c>
       <c r="BM36" s="23">
-        <f t="shared" ref="BM36:BM71" ca="1" si="44">(BK36/G36)^(1/5)-1</f>
-        <v>0.34861805110601995</v>
+        <f t="shared" ref="BM36:BM71" ca="1" si="44">IF(BK36&lt;=0,-0.99,MAX(-0.99,(BK36/G36)^(1/5)-1))</f>
+        <v>0.34705971061379648</v>
       </c>
       <c r="BN36" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO36" t="s">
         <v>138</v>
       </c>
       <c r="BP36" s="96" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="37" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -23737,13 +23785,13 @@
         <v>9.2815334580940823E-2</v>
       </c>
       <c r="BN37" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO37" s="100" t="s">
         <v>84</v>
       </c>
       <c r="BP37" s="95" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="38" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -23770,7 +23818,7 @@
       </c>
       <c r="G38" s="12">
         <f t="array" aca="1" ref="G38" ca="1">_FV(A38,"Precio")</f>
-        <v>212.26660000000001</v>
+        <v>212.715</v>
       </c>
       <c r="H38" s="13">
         <f t="array" aca="1" ref="H38" ca="1">_FV(A38,"Acciones en circulación",TRUE())/1000000</f>
@@ -23778,7 +23826,7 @@
       </c>
       <c r="I38" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>5136851.7200000007</v>
+        <v>5147703</v>
       </c>
       <c r="J38" s="90">
         <v>1</v>
@@ -23891,7 +23939,7 @@
       </c>
       <c r="AR38" s="19">
         <f ca="1">I38-AP38+AQ38</f>
-        <v>5096491.7200000007</v>
+        <v>5107343</v>
       </c>
       <c r="AS38" s="19">
         <v>122365</v>
@@ -23907,15 +23955,15 @@
       </c>
       <c r="AW38" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>41.649913945981289</v>
+        <v>41.738593552077802</v>
       </c>
       <c r="AX38" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>30.792651320161927</v>
+        <v>30.858214005196061</v>
       </c>
       <c r="AY38" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>20.105296934790331</v>
+        <v>20.148104461714468</v>
       </c>
       <c r="AZ38" s="21">
         <v>215590</v>
@@ -23962,14 +24010,14 @@
       </c>
       <c r="BL38" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-6.6763793169846597E-2</v>
+        <v>-6.715757490375629E-2</v>
       </c>
       <c r="BM38" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.1043703183777529</v>
+        <v>0.10390432610734335</v>
       </c>
       <c r="BN38" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO38" t="s">
         <v>141</v>
@@ -24234,7 +24282,7 @@
       </c>
       <c r="G40" s="12">
         <f t="array" aca="1" ref="G40" ca="1">_FV(A40,"Precio")</f>
-        <v>415.64499999999998</v>
+        <v>416.47</v>
       </c>
       <c r="H40" s="13">
         <f t="array" aca="1" ref="H40" ca="1">_FV(A40,"Acciones en circulación",TRUE())/1000000</f>
@@ -24242,7 +24290,7 @@
       </c>
       <c r="I40" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>2155731.9857299998</v>
+        <v>2160010.8267800002</v>
       </c>
       <c r="J40" s="90">
         <v>2</v>
@@ -24355,7 +24403,7 @@
       </c>
       <c r="AR40" s="19">
         <f ca="1">I40-AP40+AQ40</f>
-        <v>2078741.9857299998</v>
+        <v>2083020.8267800002</v>
       </c>
       <c r="AS40" s="19">
         <v>59255</v>
@@ -24371,15 +24419,15 @@
       </c>
       <c r="AW40" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>35.081292477090535</v>
+        <v>35.153503109948531</v>
       </c>
       <c r="AX40" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>20.879288727701887</v>
+        <v>20.922266239252714</v>
       </c>
       <c r="AY40" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>14.893902598910939</v>
+        <v>14.924559911012397</v>
       </c>
       <c r="AZ40" s="21">
         <v>244100</v>
@@ -24426,14 +24474,14 @@
       </c>
       <c r="BL40" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-9.6777819288964562E-2</v>
+        <v>-9.7135948059777655E-2</v>
       </c>
       <c r="BM40" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>5.4817197673405094E-2</v>
+        <v>5.4398961280961888E-2</v>
       </c>
       <c r="BN40" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO40" s="93" t="s">
         <v>134</v>
@@ -24466,7 +24514,7 @@
       </c>
       <c r="G41" s="12">
         <f t="array" aca="1" ref="G41" ca="1">_FV(A41,"Precio")</f>
-        <v>551.82000000000005</v>
+        <v>550.72</v>
       </c>
       <c r="H41" s="13">
         <f t="array" aca="1" ref="H41" ca="1">_FV(A41,"Acciones en circulación",TRUE())/1000000</f>
@@ -24474,7 +24522,7 @@
       </c>
       <c r="I41" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>113417.88224400001</v>
+        <v>113191.794624</v>
       </c>
       <c r="J41" s="91">
         <v>1</v>
@@ -24587,7 +24635,7 @@
       </c>
       <c r="AR41" s="19">
         <f ca="1">I41*'Framework Notes'!E8-AP41+AQ41</f>
-        <v>90657.441506659205</v>
+        <v>90429.772095456006</v>
       </c>
       <c r="AS41" s="19">
         <v>3267</v>
@@ -24603,15 +24651,15 @@
       </c>
       <c r="AW41" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>27.749446436075669</v>
+        <v>27.679758829340681</v>
       </c>
       <c r="AX41" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>32.966342366057894</v>
+        <v>32.883553489256727</v>
       </c>
       <c r="AY41" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>5.0051035999922266</v>
+        <v>4.9925342072244252</v>
       </c>
       <c r="AZ41" s="21">
         <v>8834</v>
@@ -24650,22 +24698,22 @@
       </c>
       <c r="BJ41" s="25">
         <f ca="1">((BD41*BH41+$AP41-$AQ41)/$H41)/'Framework Notes'!E8</f>
-        <v>424.10152153159288</v>
+        <v>424.25006847433599</v>
       </c>
       <c r="BK41" s="25">
         <f ca="1">((BF41*BI41+$AP41-$AQ41)/$H41)/'Framework Notes'!E8</f>
-        <v>784.02989859202648</v>
+        <v>784.30451501885375</v>
       </c>
       <c r="BL41" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-5.1287814644433882E-2</v>
+        <v>-5.0842651420662355E-2</v>
       </c>
       <c r="BM41" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>7.2771031468262803E-2</v>
+        <v>7.3274406694289196E-2</v>
       </c>
       <c r="BN41" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO41" s="95" t="s">
         <v>84</v>
@@ -25361,7 +25409,7 @@
         <v>0.11502649565910006</v>
       </c>
       <c r="BN44" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO44" s="95" t="s">
         <v>84</v>
@@ -25593,7 +25641,7 @@
         <v>7.8644748935160935E-2</v>
       </c>
       <c r="BN45" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO45" s="93" t="s">
         <v>128</v>
@@ -25626,7 +25674,7 @@
       </c>
       <c r="G46" s="12">
         <f t="array" aca="1" ref="G46" ca="1">_FV(A46,"Precio")</f>
-        <v>128.25</v>
+        <v>129.61000000000001</v>
       </c>
       <c r="H46" s="13">
         <f t="array" aca="1" ref="H46" ca="1">_FV(A46,"Acciones en circulación",TRUE())/1000000</f>
@@ -25634,7 +25682,7 @@
       </c>
       <c r="I46" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>13094.401949999999</v>
+        <v>13233.258766000001</v>
       </c>
       <c r="J46" s="90">
         <v>1</v>
@@ -25747,7 +25795,7 @@
       </c>
       <c r="AR46" s="19">
         <f t="shared" ca="1" si="45"/>
-        <v>12784.401949999999</v>
+        <v>12923.258766000001</v>
       </c>
       <c r="AS46" s="19">
         <v>1100</v>
@@ -25763,15 +25811,15 @@
       </c>
       <c r="AW46" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>11.62218359090909</v>
+        <v>11.748417060000001</v>
       </c>
       <c r="AX46" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>15.111586229314421</v>
+        <v>15.275719581560285</v>
       </c>
       <c r="AY46" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>4.6320296920289854</v>
+        <v>4.6823401326086955</v>
       </c>
       <c r="AZ46" s="21">
         <v>5759</v>
@@ -25818,14 +25866,14 @@
       </c>
       <c r="BL46" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.10321009824795069</v>
+        <v>-0.10510005394753019</v>
       </c>
       <c r="BM46" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.15475894702900495</v>
+        <v>0.15232532991387693</v>
       </c>
       <c r="BN46" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO46" s="93" t="s">
         <v>106</v>
@@ -26322,7 +26370,7 @@
       </c>
       <c r="G49" s="12">
         <f t="array" aca="1" ref="G49" ca="1">_FV(A49,"Precio")</f>
-        <v>49.09</v>
+        <v>49.28</v>
       </c>
       <c r="H49" s="13">
         <f t="array" aca="1" ref="H49" ca="1">_FV(A49,"Acciones en circulación",TRUE())/1000000</f>
@@ -26330,7 +26378,7 @@
       </c>
       <c r="I49" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>10112.68727</v>
+        <v>10151.82784</v>
       </c>
       <c r="J49" s="91">
         <v>0</v>
@@ -26443,7 +26491,7 @@
       </c>
       <c r="AR49" s="19">
         <f ca="1">I49*'Framework Notes'!E7-AP49+AQ49</f>
-        <v>7509.439090029</v>
+        <v>7540.7715283199996</v>
       </c>
       <c r="AS49" s="19">
         <v>395</v>
@@ -26459,15 +26507,15 @@
       </c>
       <c r="AW49" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>19.011238202605064</v>
+        <v>19.090560831189872</v>
       </c>
       <c r="AX49" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>19.91893657832626</v>
+        <v>20.002046494217506</v>
       </c>
       <c r="AY49" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>15.356726155478528</v>
+        <v>15.420800671411042</v>
       </c>
       <c r="AZ49" s="21">
         <v>2539</v>
@@ -26506,22 +26554,22 @@
       </c>
       <c r="BJ49" s="25">
         <f ca="1">((BD49*BH49+$AP49-$AQ49)/$H49)/'Framework Notes'!E7</f>
-        <v>38.548246284814027</v>
+        <v>38.532251161874271</v>
       </c>
       <c r="BK49" s="25">
         <f ca="1">((BF49*BI49+$AP49-$AQ49)/$H49)/'Framework Notes'!E7</f>
-        <v>88.495059209343935</v>
+        <v>88.458339267763293</v>
       </c>
       <c r="BL49" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-4.7198749230701886E-2</v>
+        <v>-4.8013616383375313E-2</v>
       </c>
       <c r="BM49" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.12508464727548008</v>
+        <v>0.12412243766219344</v>
       </c>
       <c r="BN49" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO49" s="95" t="s">
         <v>98</v>
@@ -26554,7 +26602,7 @@
       </c>
       <c r="G50" s="12">
         <f t="array" aca="1" ref="G50" ca="1">_FV(A50,"Precio")</f>
-        <v>81.99</v>
+        <v>82.344999999999999</v>
       </c>
       <c r="H50" s="13">
         <f t="array" aca="1" ref="H50" ca="1">_FV(A50,"Acciones en circulación",TRUE())/1000000</f>
@@ -26562,7 +26610,7 @@
       </c>
       <c r="I50" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>341401.35861</v>
+        <v>342879.55695500004</v>
       </c>
       <c r="J50" s="90">
         <v>0.5</v>
@@ -26677,7 +26725,7 @@
       </c>
       <c r="AR50" s="19">
         <f t="shared" ref="AR50:AR62" ca="1" si="48">I50-AP50+AQ50</f>
-        <v>346631.35861</v>
+        <v>348109.55695500004</v>
       </c>
       <c r="AS50" s="19">
         <v>11560</v>
@@ -26693,15 +26741,15 @@
       </c>
       <c r="AW50" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>29.985411644463667</v>
+        <v>30.113283473615919</v>
       </c>
       <c r="AX50" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>23.532339348947726</v>
+        <v>23.632692257637476</v>
       </c>
       <c r="AY50" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>7.1662468184825308</v>
+        <v>7.1968070488939428</v>
       </c>
       <c r="AZ50" s="21">
         <v>46315</v>
@@ -26748,14 +26796,14 @@
       </c>
       <c r="BL50" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-7.2584595960507148E-2</v>
+        <v>-7.3385620156376619E-2</v>
       </c>
       <c r="BM50" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>7.0737265216964884E-2</v>
+        <v>6.9812451532479836E-2</v>
       </c>
       <c r="BN50" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO50" s="93" t="s">
         <v>134</v>
@@ -26788,7 +26836,7 @@
       </c>
       <c r="G51" s="12">
         <f t="array" aca="1" ref="G51" ca="1">_FV(A51,"Precio")</f>
-        <v>39.67</v>
+        <v>39.47</v>
       </c>
       <c r="H51" s="13">
         <f t="array" aca="1" ref="H51" ca="1">_FV(A51,"Acciones en circulación",TRUE())/1000000</f>
@@ -26796,7 +26844,7 @@
       </c>
       <c r="I51" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>58850.405330000001</v>
+        <v>58553.705529999999</v>
       </c>
       <c r="J51" s="91">
         <v>0</v>
@@ -26909,7 +26957,7 @@
       </c>
       <c r="AR51" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>60860.405330000001</v>
+        <v>60563.705529999999</v>
       </c>
       <c r="AS51" s="19">
         <v>2180</v>
@@ -26925,15 +26973,15 @@
       </c>
       <c r="AW51" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>27.917617123853212</v>
+        <v>27.781516298165137</v>
       </c>
       <c r="AX51" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>12.344909803245436</v>
+        <v>12.284727288032455</v>
       </c>
       <c r="AY51" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>1.3116466665948276</v>
+        <v>1.3052522743534483</v>
       </c>
       <c r="AZ51" s="21">
         <v>25863</v>
@@ -26980,14 +27028,14 @@
       </c>
       <c r="BL51" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.13493338517207842</v>
+        <v>-0.13405847403815352</v>
       </c>
       <c r="BM51" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>3.0610269988418981E-2</v>
+        <v>3.165260867597719E-2</v>
       </c>
       <c r="BN51" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO51" s="93" t="s">
         <v>156</v>
@@ -27183,18 +27231,18 @@
         <v>0.16118143459915613</v>
       </c>
       <c r="BD52" s="98">
-        <v>172.3</v>
+        <v>90</v>
       </c>
       <c r="BE52" s="23">
         <f t="shared" si="41"/>
-        <v>5.0674290335872563E-3</v>
+        <v>-0.11735382086685286</v>
       </c>
       <c r="BF52">
-        <v>384</v>
+        <v>270</v>
       </c>
       <c r="BG52" s="23">
         <f t="shared" si="42"/>
-        <v>0.17978912471277986</v>
+        <v>9.9539654079581652E-2</v>
       </c>
       <c r="BH52" s="24">
         <v>17.5</v>
@@ -27204,22 +27252,22 @@
       </c>
       <c r="BJ52" s="25">
         <f t="shared" ca="1" si="49"/>
-        <v>108.38537592974552</v>
+        <v>54.01810115993586</v>
       </c>
       <c r="BK52" s="25">
         <f t="shared" ca="1" si="50"/>
-        <v>320.71124210678903</v>
+        <v>223.88634380124358</v>
       </c>
       <c r="BL52" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.21628953585513977</v>
+        <v>-0.31818057414402756</v>
       </c>
       <c r="BM52" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>-2.6391527282287108E-2</v>
+        <v>-9.391898935410159E-2</v>
       </c>
       <c r="BN52" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO52" s="93" t="s">
         <v>134</v>
@@ -27252,7 +27300,7 @@
       </c>
       <c r="G53" s="12">
         <f t="array" aca="1" ref="G53" ca="1">_FV(A53,"Precio")</f>
-        <v>234.39</v>
+        <v>232.45500000000001</v>
       </c>
       <c r="H53" s="13">
         <f t="array" aca="1" ref="H53" ca="1">_FV(A53,"Acciones en circulación",TRUE())/1000000</f>
@@ -27260,7 +27308,7 @@
       </c>
       <c r="I53" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>45343.378352999993</v>
+        <v>44969.047378499999</v>
       </c>
       <c r="J53" s="91">
         <v>0</v>
@@ -27373,7 +27421,7 @@
       </c>
       <c r="AR53" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>51793.378352999993</v>
+        <v>51419.047378499999</v>
       </c>
       <c r="AS53" s="19">
         <v>1118</v>
@@ -27389,15 +27437,15 @@
       </c>
       <c r="AW53" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>46.326814269230766</v>
+        <v>45.991992288461539</v>
       </c>
       <c r="AX53" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>16.865313693585151</v>
+        <v>16.743421484369911</v>
       </c>
       <c r="AY53" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>1.6470577610188892</v>
+        <v>1.635153831282198</v>
       </c>
       <c r="AZ53" s="21">
         <v>12926</v>
@@ -27444,20 +27492,20 @@
       </c>
       <c r="BL53" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.12084855359515034</v>
+        <v>-0.1193897578117874</v>
       </c>
       <c r="BM53" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>7.9083214732629026E-2</v>
+        <v>8.0873761799334032E-2</v>
       </c>
       <c r="BN53" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO53" s="95" t="s">
         <v>132</v>
       </c>
       <c r="BP53" s="95" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="54" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -27484,7 +27532,7 @@
       </c>
       <c r="G54" s="12">
         <f t="array" aca="1" ref="G54" ca="1">_FV(A54,"Precio")</f>
-        <v>20.206099999999999</v>
+        <v>20.254999999999999</v>
       </c>
       <c r="H54" s="13">
         <f t="array" aca="1" ref="H54" ca="1">_FV(A54,"Acciones en circulación",TRUE())/1000000</f>
@@ -27492,7 +27540,7 @@
       </c>
       <c r="I54" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>6926.7258425699993</v>
+        <v>6943.4889434999996</v>
       </c>
       <c r="J54" s="90">
         <v>1</v>
@@ -27605,7 +27653,7 @@
       </c>
       <c r="AR54" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>6269.7258425699993</v>
+        <v>6286.4889434999996</v>
       </c>
       <c r="AS54" s="19">
         <v>62</v>
@@ -27621,15 +27669,15 @@
       </c>
       <c r="AW54" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>101.12461036403225</v>
+        <v>101.39498295967741</v>
       </c>
       <c r="AX54" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>-24.207435685598451</v>
+        <v>-24.272158083011583</v>
       </c>
       <c r="AY54" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>5.9711674691142846</v>
+        <v>5.9871323271428567</v>
       </c>
       <c r="AZ54" s="21">
         <v>1684</v>
@@ -27676,14 +27724,14 @@
       </c>
       <c r="BL54" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.19885773220635861</v>
+        <v>-0.19924493283260303</v>
       </c>
       <c r="BM54" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>-8.043374446389806E-3</v>
+        <v>-8.5227976924998616E-3</v>
       </c>
       <c r="BN54" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO54" t="s">
         <v>92</v>
@@ -27716,7 +27764,7 @@
       </c>
       <c r="G55" s="12">
         <f t="array" aca="1" ref="G55" ca="1">_FV(A55,"Precio")</f>
-        <v>46.85</v>
+        <v>46.78</v>
       </c>
       <c r="H55" s="13">
         <f t="array" aca="1" ref="H55" ca="1">_FV(A55,"Acciones en circulación",TRUE())/1000000</f>
@@ -27724,7 +27772,7 @@
       </c>
       <c r="I55" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>4772.3846199999998</v>
+        <v>4765.2540559999998</v>
       </c>
       <c r="J55" s="91">
         <v>1</v>
@@ -27837,7 +27885,7 @@
       </c>
       <c r="AR55" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>5068.8846199999998</v>
+        <v>5061.7540559999998</v>
       </c>
       <c r="AS55" s="19">
         <v>283</v>
@@ -27853,15 +27901,15 @@
       </c>
       <c r="AW55" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>17.911253074204947</v>
+        <v>17.886056734982333</v>
       </c>
       <c r="AX55" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>16.194519552715654</v>
+        <v>16.171738198083066</v>
       </c>
       <c r="AY55" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>4.1960965397350991</v>
+        <v>4.1901937549668871</v>
       </c>
       <c r="AZ55" s="21">
         <v>1176</v>
@@ -27908,20 +27956,20 @@
       </c>
       <c r="BL55" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-8.2700322857376607E-2</v>
+        <v>-8.2425963820944581E-2</v>
       </c>
       <c r="BM55" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.14794472574933581</v>
+        <v>0.14828806938793271</v>
       </c>
       <c r="BN55" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO55" s="95" t="s">
         <v>132</v>
       </c>
       <c r="BP55" s="95" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="56" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28147,7 +28195,7 @@
         <v>0.12247003636339482</v>
       </c>
       <c r="BN56" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO56" s="95" t="s">
         <v>106</v>
@@ -28343,43 +28391,43 @@
         <v>3.3653846153846152E-2</v>
       </c>
       <c r="BD57" s="98">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="BE57" s="23">
         <f t="shared" si="41"/>
-        <v>0</v>
+        <v>-0.27277994551431728</v>
       </c>
       <c r="BF57">
-        <v>103.8</v>
+        <v>42</v>
       </c>
       <c r="BG57" s="23">
         <f t="shared" si="42"/>
-        <v>0.11961592833339973</v>
+        <v>-6.5714829037020306E-2</v>
       </c>
       <c r="BH57" s="24">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="BI57" s="24">
         <v>12.5</v>
       </c>
       <c r="BJ57" s="25">
         <f t="shared" ca="1" si="49"/>
-        <v>3.1826568265682655</v>
+        <v>-9.547970479704798</v>
       </c>
       <c r="BK57" s="25">
         <f t="shared" ca="1" si="50"/>
-        <v>46.702029520295206</v>
+        <v>11.07011070110701</v>
       </c>
       <c r="BL57" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.28200940850053402</v>
+        <v>-0.99</v>
       </c>
       <c r="BM57" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.22864931127815757</v>
+        <v>-7.8720975150120442E-2</v>
       </c>
       <c r="BN57" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO57" s="93" t="s">
         <v>160</v>
@@ -28412,7 +28460,7 @@
       </c>
       <c r="G58" s="12">
         <f t="array" aca="1" ref="G58" ca="1">_FV(A58,"Precio")</f>
-        <v>35.384999999999998</v>
+        <v>35.5</v>
       </c>
       <c r="H58" s="13">
         <f t="array" aca="1" ref="H58" ca="1">_FV(A58,"Acciones en circulación",TRUE())/1000000</f>
@@ -28420,7 +28468,7 @@
       </c>
       <c r="I58" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>8953.6434749999989</v>
+        <v>8982.7425000000003</v>
       </c>
       <c r="J58" s="90">
         <v>0</v>
@@ -28533,7 +28581,7 @@
       </c>
       <c r="AR58" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>8990.6434749999989</v>
+        <v>9019.7425000000003</v>
       </c>
       <c r="AS58" s="19">
         <v>447</v>
@@ -28549,15 +28597,15 @@
       </c>
       <c r="AW58" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>20.113296364653241</v>
+        <v>20.178394854586131</v>
       </c>
       <c r="AX58" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>12.504372009735743</v>
+        <v>12.544843532684284</v>
       </c>
       <c r="AY58" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>2.9506542418772561</v>
+        <v>2.9602042993107975</v>
       </c>
       <c r="AZ58" s="21">
         <v>3400</v>
@@ -28604,14 +28652,14 @@
       </c>
       <c r="BL58" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-5.3680187428046922E-2</v>
+        <v>-5.4294092037257102E-2</v>
       </c>
       <c r="BM58" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.29785192981163666</v>
+        <v>0.29700997630797055</v>
       </c>
       <c r="BN58" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO58" t="s">
         <v>125</v>
@@ -29573,7 +29621,7 @@
       </c>
       <c r="G63" s="12">
         <f t="array" aca="1" ref="G63" ca="1">_FV(A63,"Precio")</f>
-        <v>35.090000000000003</v>
+        <v>34.950000000000003</v>
       </c>
       <c r="H63" s="13">
         <f t="array" aca="1" ref="H63" ca="1">_FV(A63,"Acciones en circulación",TRUE())/1000000</f>
@@ -29581,7 +29629,7 @@
       </c>
       <c r="I63" s="14">
         <f ca="1">G63*H63</f>
-        <v>3959.0924120000004</v>
+        <v>3943.2966600000004</v>
       </c>
       <c r="J63" s="91">
         <v>0</v>
@@ -29694,7 +29742,7 @@
       </c>
       <c r="AR63" s="19">
         <f ca="1">I63*'Framework Notes'!E7-AP63+AQ63</f>
-        <v>3366.9360861524001</v>
+        <v>3356.7034851799999</v>
       </c>
       <c r="AS63" s="19">
         <v>18.600000000000001</v>
@@ -29710,15 +29758,15 @@
       </c>
       <c r="AW63" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>181.01806914797848</v>
+        <v>180.46792931075268</v>
       </c>
       <c r="AX63" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>13.30804777135336</v>
+        <v>13.267602708221343</v>
       </c>
       <c r="AY63" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>4.7622858361420084</v>
+        <v>4.7478125674398868</v>
       </c>
       <c r="AZ63" s="21">
         <v>1833</v>
@@ -29757,28 +29805,28 @@
       </c>
       <c r="BJ63" s="25">
         <f ca="1">((BD63*BH63+$AP63-$AQ63)/$H63)/'Framework Notes'!$E$7</f>
-        <v>15.627926411388863</v>
+        <v>15.621441794620653</v>
       </c>
       <c r="BK63" s="25">
         <f ca="1">((BF63*BI63+$AP63-$AQ63)/$H63)/'Framework Notes'!$E$7</f>
-        <v>68.301507151336423</v>
+        <v>68.273166276999774</v>
       </c>
       <c r="BL63" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.14936431494277813</v>
+        <v>-0.14875458252908824</v>
       </c>
       <c r="BM63" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.14248204562663958</v>
+        <v>0.14330097239812867</v>
       </c>
       <c r="BN63" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO63" s="95" t="s">
         <v>132</v>
       </c>
       <c r="BP63" s="95" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="64" spans="1:68" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29805,7 +29853,7 @@
       </c>
       <c r="G64" s="12">
         <f t="array" aca="1" ref="G64" ca="1">_FV(A64,"Precio")</f>
-        <v>15.76</v>
+        <v>15.574999999999999</v>
       </c>
       <c r="H64" s="13">
         <f t="array" aca="1" ref="H64" ca="1">_FV(A64,"Acciones en circulación",TRUE())/1000000</f>
@@ -29813,7 +29861,7 @@
       </c>
       <c r="I64" s="14">
         <f ca="1">G64*H64</f>
-        <v>502.9372176</v>
+        <v>497.03344949999996</v>
       </c>
       <c r="J64" s="90">
         <v>1</v>
@@ -29883,7 +29931,7 @@
         <v>8</v>
       </c>
       <c r="AE64" s="90">
-        <v>-12</v>
+        <v>-10</v>
       </c>
       <c r="AF64" s="90">
         <v>4</v>
@@ -29905,15 +29953,15 @@
       </c>
       <c r="AL64" s="15">
         <f t="shared" si="32"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM64" s="16">
         <f t="shared" si="33"/>
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AN64" s="17">
         <f t="shared" si="34"/>
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AO64" s="18" t="s">
         <v>78</v>
@@ -29926,7 +29974,7 @@
       </c>
       <c r="AR64" s="19">
         <f t="shared" ref="AR64:AR71" ca="1" si="51">I64-AP64+AQ64</f>
-        <v>1007.3372176</v>
+        <v>1001.4334494999999</v>
       </c>
       <c r="AS64" s="19">
         <v>-21.9</v>
@@ -29942,15 +29990,15 @@
       </c>
       <c r="AW64" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>-45.997133223744299</v>
+        <v>-45.727554771689498</v>
       </c>
       <c r="AX64" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>-71.952658400000004</v>
+        <v>-71.530960678571418</v>
       </c>
       <c r="AY64" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>1.0890132082162163</v>
+        <v>1.0826307562162161</v>
       </c>
       <c r="AZ64" s="21">
         <v>169</v>
@@ -29997,14 +30045,14 @@
       </c>
       <c r="BL64" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-2.0005810202640713</v>
+        <v>-0.99</v>
       </c>
       <c r="BM64" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.21279027663802674</v>
+        <v>0.21565779158195664</v>
       </c>
       <c r="BN64" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO64" s="93" t="s">
         <v>133</v>
@@ -30037,7 +30085,7 @@
       </c>
       <c r="G65" s="12">
         <f t="array" aca="1" ref="G65" ca="1">_FV(A65,"Precio")</f>
-        <v>3052.29</v>
+        <v>3054.98</v>
       </c>
       <c r="H65" s="13">
         <f t="array" aca="1" ref="H65" ca="1">_FV(A65,"Acciones en circulación",TRUE())/1000000</f>
@@ -30045,7 +30093,7 @@
       </c>
       <c r="I65" s="14">
         <f ca="1">G65*H65</f>
-        <v>64682.695103699996</v>
+        <v>64739.700319399999</v>
       </c>
       <c r="J65" s="90">
         <v>2</v>
@@ -30158,7 +30206,7 @@
       </c>
       <c r="AR65" s="19">
         <f ca="1">I65*'Framework Notes'!$E$7-AP65+AQ65</f>
-        <v>47788.18375144399</v>
+        <v>47848.803330926195</v>
       </c>
       <c r="AS65" s="19">
         <v>2700</v>
@@ -30174,15 +30222,15 @@
       </c>
       <c r="AW65" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>17.699327315349628</v>
+        <v>17.721779011454146</v>
       </c>
       <c r="AX65" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>13.940543684785295</v>
+        <v>13.958227342743932</v>
       </c>
       <c r="AY65" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>3.7804116566287469</v>
+        <v>3.7852071300471635</v>
       </c>
       <c r="AZ65" s="21">
         <v>5000</v>
@@ -30221,25 +30269,25 @@
       </c>
       <c r="BJ65" s="25">
         <f ca="1">((BD65*BH65+$AP65-$AQ65)/$H65)/'Framework Notes'!$E$7</f>
-        <v>2360.9350103705701</v>
+        <v>2359.9553692874292</v>
       </c>
       <c r="BK65" s="25">
         <f ca="1">((BF65*BI65+$AP65-$AQ65)/$H65)/'Framework Notes'!$E$7</f>
-        <v>7401.7055950436161</v>
+        <v>7398.6343479087436</v>
       </c>
       <c r="BL65" s="23">
-        <f ca="1">(BJ65/G65)^(1/5)-1</f>
-        <v>-5.0069903219847944E-2</v>
+        <f t="shared" ca="1" si="43"/>
+        <v>-5.0316082036399479E-2</v>
       </c>
       <c r="BM65" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.19382646615642507</v>
+        <v>0.19351708045783256</v>
       </c>
       <c r="BN65" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO65" s="95" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="BP65" s="95" t="s">
         <v>144</v>
@@ -30269,7 +30317,7 @@
       </c>
       <c r="G66" s="12">
         <f t="array" aca="1" ref="G66" ca="1">_FV(A66,"Precio")</f>
-        <v>79.81</v>
+        <v>80.114999999999995</v>
       </c>
       <c r="H66" s="13">
         <f t="array" aca="1" ref="H66" ca="1">_FV(A66,"Acciones en circulación",TRUE())/1000000</f>
@@ -30277,7 +30325,7 @@
       </c>
       <c r="I66" s="14">
         <f ca="1">G66*H66</f>
-        <v>163016.71359999999</v>
+        <v>163639.69439999998</v>
       </c>
       <c r="J66" s="90">
         <v>1</v>
@@ -30390,7 +30438,7 @@
       </c>
       <c r="AR66" s="19">
         <f t="shared" ca="1" si="51"/>
-        <v>172356.71359999999</v>
+        <v>172979.69439999998</v>
       </c>
       <c r="AS66" s="19">
         <v>10116</v>
@@ -30406,15 +30454,15 @@
       </c>
       <c r="AW66" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>17.038030209568998</v>
+        <v>17.099613918544879</v>
       </c>
       <c r="AX66" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>23.057754327759195</v>
+        <v>23.141096240802671</v>
       </c>
       <c r="AY66" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>3.120877715610118</v>
+        <v>3.1321580820975243</v>
       </c>
       <c r="AZ66" s="21">
         <v>37739</v>
@@ -30460,21 +30508,21 @@
         <v>311.50125332915559</v>
       </c>
       <c r="BL66" s="23">
-        <f ca="1">(BJ66/G66)^(1/5)-1</f>
-        <v>-6.5402330914239526E-2</v>
+        <f t="shared" ca="1" si="43"/>
+        <v>-6.6115024826753577E-2</v>
       </c>
       <c r="BM66" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.31304768252822446</v>
+        <v>0.31204639489277164</v>
       </c>
       <c r="BN66" s="95" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO66" s="95" t="s">
         <v>98</v>
       </c>
       <c r="BP66" s="95" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="67" spans="1:68" x14ac:dyDescent="0.35">
@@ -30692,7 +30740,7 @@
         <v>872.3210177435401</v>
       </c>
       <c r="BL67" s="23">
-        <f ca="1">(BJ67/G67)^(1/5)-1</f>
+        <f t="shared" ca="1" si="43"/>
         <v>4.7818617486187209E-2</v>
       </c>
       <c r="BM67" s="23">
@@ -30924,7 +30972,7 @@
         <v>100.54666038448079</v>
       </c>
       <c r="BL68" s="23">
-        <f ca="1">($BJ68/G68)^(1/5)-1</f>
+        <f t="shared" ca="1" si="43"/>
         <v>-4.3241288682237089E-2</v>
       </c>
       <c r="BM68" s="23">
@@ -30932,7 +30980,7 @@
         <v>0.21585925378268067</v>
       </c>
       <c r="BN68" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO68" s="96" t="s">
         <v>125</v>
@@ -31156,7 +31204,7 @@
         <v>1704.6973678145025</v>
       </c>
       <c r="BL69" s="23">
-        <f ca="1">($BJ69/G69)^(1/5)-1</f>
+        <f t="shared" ca="1" si="43"/>
         <v>-4.0775624735993499E-2</v>
       </c>
       <c r="BM69" s="23">
@@ -31164,7 +31212,7 @@
         <v>0.16393540749423563</v>
       </c>
       <c r="BN69" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO69" s="96" t="s">
         <v>125</v>
@@ -31388,7 +31436,7 @@
         <v>4483.5825814691225</v>
       </c>
       <c r="BL70" s="23">
-        <f ca="1">($BJ70/G70)^(1/5)-1</f>
+        <f t="shared" ca="1" si="43"/>
         <v>-1.3169556271558358E-3</v>
       </c>
       <c r="BM70" s="23">
@@ -31396,7 +31444,7 @@
         <v>0.18934774904737917</v>
       </c>
       <c r="BN70" s="96" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="BO70" s="96" t="s">
         <v>547</v>
@@ -31429,7 +31477,7 @@
       </c>
       <c r="G71" s="12">
         <f t="shared" ca="1" si="54"/>
-        <v>77.56</v>
+        <v>77.66</v>
       </c>
       <c r="H71" s="13">
         <f t="shared" ca="1" si="55"/>
@@ -31437,7 +31485,7 @@
       </c>
       <c r="I71" s="14">
         <f ca="1">G71*H71</f>
-        <v>1157.404612</v>
+        <v>1158.896882</v>
       </c>
       <c r="J71" s="90">
         <v>2</v>
@@ -31550,7 +31598,7 @@
       </c>
       <c r="AR71" s="19">
         <f t="shared" ca="1" si="51"/>
-        <v>1518.3046119999999</v>
+        <v>1519.7968819999999</v>
       </c>
       <c r="AS71" s="19">
         <v>62</v>
@@ -31566,15 +31614,15 @@
       </c>
       <c r="AW71" s="20">
         <f ca="1">AR71/AS71</f>
-        <v>24.488784064516128</v>
+        <v>24.51285293548387</v>
       </c>
       <c r="AX71" s="20">
         <f ca="1">AR71/AU71</f>
-        <v>15.815673041666665</v>
+        <v>15.831217520833333</v>
       </c>
       <c r="AY71" s="20">
         <f ca="1">AR71/AV71</f>
-        <v>1.887734193708815</v>
+        <v>1.8895895586224045</v>
       </c>
       <c r="AZ71" s="21">
         <v>1127.5999999999999</v>
@@ -31620,12 +31668,12 @@
         <v>158.75813358172448</v>
       </c>
       <c r="BL71" s="23">
-        <f ca="1">($BJ71/G71)^(1/5)-1</f>
-        <v>-7.6107164828045581E-2</v>
+        <f t="shared" ca="1" si="43"/>
+        <v>-7.6345220215282117E-2</v>
       </c>
       <c r="BM71" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.15403674413348489</v>
+        <v>0.15373938858146485</v>
       </c>
       <c r="BN71" s="96" t="s">
         <v>542</v>
@@ -31689,7 +31737,7 @@
       </c>
       <c r="E4" s="29">
         <f t="array" aca="1" ref="E4" ca="1">_FV(D4,"Precio")</f>
-        <v>185.86</v>
+        <v>185.72</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31701,7 +31749,7 @@
       </c>
       <c r="E5" s="30">
         <f t="array" aca="1" ref="E5" ca="1">_FV(D5,"Precio")</f>
-        <v>1.2461</v>
+        <v>1.2475000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31713,7 +31761,7 @@
       </c>
       <c r="E6" s="31">
         <f t="array" aca="1" ref="E6" ca="1">_FV(D6,"Precio")</f>
-        <v>457.78</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31722,7 +31770,7 @@
       </c>
       <c r="E7" s="30">
         <f t="array" aca="1" ref="E7" ca="1">_FV(D7,"Precio")</f>
-        <v>0.72270000000000001</v>
+        <v>0.72299999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31734,7 +31782,7 @@
       </c>
       <c r="E8" s="87">
         <f t="array" aca="1" ref="E8" ca="1">_FV(D8,"Precio")</f>
-        <v>0.85680000000000001</v>
+        <v>0.85650000000000004</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31968,67 +32016,67 @@
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>639</v>
+        <v>799</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
   </sheetData>
@@ -32138,7 +32186,7 @@
       <c r="F4" s="136"/>
       <c r="G4" s="138" t="str">
         <f ca="1">TEXT(AVERAGE('Watchlist Ratings'!AW4:AW71),"0.0x")</f>
-        <v>34.0x</v>
+        <v>34.4x</v>
       </c>
       <c r="H4" s="136"/>
       <c r="I4" s="138">
@@ -32406,7 +32454,7 @@
       </c>
       <c r="Q8" s="23">
         <f ca="1">'Watchlist Ratings'!BM4</f>
-        <v>0.21724859954203968</v>
+        <v>0.21535056770391781</v>
       </c>
       <c r="S8" t="str">
         <f ca="1">'Watchlist Ratings'!B4</f>
@@ -32434,7 +32482,7 @@
       </c>
       <c r="Z8">
         <f ca="1">'Watchlist Ratings'!AW4</f>
-        <v>19.754374556097559</v>
+        <v>19.94356157012195</v>
       </c>
       <c r="AA8" t="str">
         <f ca="1">'Watchlist Ratings'!B4</f>
@@ -32442,11 +32490,11 @@
       </c>
       <c r="AB8">
         <f ca="1">'Watchlist Ratings'!BL4</f>
-        <v>-2.9177844379771334E-2</v>
+        <v>-3.0691628302968677E-2</v>
       </c>
       <c r="AC8">
         <f ca="1">'Watchlist Ratings'!BM4</f>
-        <v>0.21724859954203968</v>
+        <v>0.21535056770391781</v>
       </c>
       <c r="AE8" t="s">
         <v>253</v>
@@ -32532,7 +32580,7 @@
       </c>
       <c r="J9" s="44">
         <f ca="1">'Watchlist Ratings'!AW5</f>
-        <v>28.814635825177454</v>
+        <v>28.885051961612021</v>
       </c>
       <c r="O9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32544,7 +32592,7 @@
       </c>
       <c r="Q9" s="23">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>0.12780422738436692</v>
+        <v>0.12725933974662795</v>
       </c>
       <c r="S9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32572,7 +32620,7 @@
       </c>
       <c r="Z9">
         <f ca="1">'Watchlist Ratings'!AW5</f>
-        <v>28.814635825177454</v>
+        <v>28.885051961612021</v>
       </c>
       <c r="AA9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -32580,11 +32628,11 @@
       </c>
       <c r="AB9">
         <f ca="1">'Watchlist Ratings'!BL5</f>
-        <v>-4.1895880509692951E-2</v>
+        <v>-4.2358779191663531E-2</v>
       </c>
       <c r="AC9">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>0.12780422738436692</v>
+        <v>0.12725933974662795</v>
       </c>
       <c r="AE9" t="s">
         <v>257</v>
@@ -32808,7 +32856,7 @@
       </c>
       <c r="J11" s="44">
         <f ca="1">'Watchlist Ratings'!AW7</f>
-        <v>17.899890907258065</v>
+        <v>17.917687064516127</v>
       </c>
       <c r="O11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -32820,7 +32868,7 @@
       </c>
       <c r="Q11" s="23">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.21900244611200459</v>
+        <v>0.21874186412022789</v>
       </c>
       <c r="S11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -32848,7 +32896,7 @@
       </c>
       <c r="Z11">
         <f ca="1">'Watchlist Ratings'!AW7</f>
-        <v>17.899890907258065</v>
+        <v>17.917687064516127</v>
       </c>
       <c r="AA11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -32856,11 +32904,11 @@
       </c>
       <c r="AB11">
         <f ca="1">'Watchlist Ratings'!BL7</f>
-        <v>1.6521030185501884E-2</v>
+        <v>1.6303731954826928E-2</v>
       </c>
       <c r="AC11">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.21900244611200459</v>
+        <v>0.21874186412022789</v>
       </c>
       <c r="AE11" t="s">
         <v>262</v>
@@ -32946,7 +32994,7 @@
       </c>
       <c r="J12" s="50">
         <f ca="1">'Watchlist Ratings'!AW8</f>
-        <v>34.843905292566141</v>
+        <v>34.823416981772361</v>
       </c>
       <c r="O12" t="str">
         <f ca="1">'Watchlist Ratings'!B8</f>
@@ -32958,7 +33006,7 @@
       </c>
       <c r="Q12" s="23">
         <f ca="1">'Watchlist Ratings'!BM8</f>
-        <v>8.4916787387159243E-2</v>
+        <v>8.5040896509370301E-2</v>
       </c>
       <c r="S12" t="str">
         <f ca="1">'Watchlist Ratings'!B8</f>
@@ -32986,7 +33034,7 @@
       </c>
       <c r="Z12">
         <f ca="1">'Watchlist Ratings'!AW8</f>
-        <v>34.843905292566141</v>
+        <v>34.823416981772361</v>
       </c>
       <c r="AA12" t="str">
         <f ca="1">'Watchlist Ratings'!B8</f>
@@ -32994,11 +33042,11 @@
       </c>
       <c r="AB12">
         <f ca="1">'Watchlist Ratings'!BL8</f>
-        <v>-4.9816250558583963E-2</v>
+        <v>-4.9707554230484341E-2</v>
       </c>
       <c r="AC12">
         <f ca="1">'Watchlist Ratings'!BM8</f>
-        <v>8.4916787387159243E-2</v>
+        <v>8.5040896509370301E-2</v>
       </c>
       <c r="AE12" t="s">
         <v>265</v>
@@ -33084,7 +33132,7 @@
       </c>
       <c r="J13" s="44">
         <f ca="1">'Watchlist Ratings'!AW9</f>
-        <v>22.249565544483985</v>
+        <v>22.304432657651251</v>
       </c>
       <c r="L13" s="36" t="s">
         <v>267</v>
@@ -33102,7 +33150,7 @@
       </c>
       <c r="Q13" s="23">
         <f ca="1">'Watchlist Ratings'!BM9</f>
-        <v>0.19745985531708032</v>
+        <v>0.19690295456465767</v>
       </c>
       <c r="S13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -33130,7 +33178,7 @@
       </c>
       <c r="Z13">
         <f ca="1">'Watchlist Ratings'!AW9</f>
-        <v>22.249565544483985</v>
+        <v>22.304432657651251</v>
       </c>
       <c r="AA13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -33138,11 +33186,11 @@
       </c>
       <c r="AB13">
         <f ca="1">'Watchlist Ratings'!BL9</f>
-        <v>-3.6669624209512586E-2</v>
+        <v>-3.7117638736870018E-2</v>
       </c>
       <c r="AC13">
         <f ca="1">'Watchlist Ratings'!BM9</f>
-        <v>0.19745985531708032</v>
+        <v>0.19690295456465767</v>
       </c>
       <c r="AE13" t="s">
         <v>260</v>
@@ -33373,7 +33421,7 @@
       </c>
       <c r="J15" s="44">
         <f ca="1">'Watchlist Ratings'!AW11</f>
-        <v>26.560800363447559</v>
+        <v>26.567517268951192</v>
       </c>
       <c r="L15" t="s">
         <v>274</v>
@@ -33392,7 +33440,7 @@
       </c>
       <c r="Q15" s="23">
         <f ca="1">'Watchlist Ratings'!BM11</f>
-        <v>0.25949207403006769</v>
+        <v>0.25943228470250812</v>
       </c>
       <c r="S15" t="str">
         <f ca="1">'Watchlist Ratings'!B11</f>
@@ -33420,7 +33468,7 @@
       </c>
       <c r="Z15">
         <f ca="1">'Watchlist Ratings'!AW11</f>
-        <v>26.560800363447559</v>
+        <v>26.567517268951192</v>
       </c>
       <c r="AA15" t="str">
         <f ca="1">'Watchlist Ratings'!B11</f>
@@ -33428,11 +33476,11 @@
       </c>
       <c r="AB15">
         <f ca="1">'Watchlist Ratings'!BL11</f>
-        <v>-2.4255031214933664E-2</v>
+        <v>-2.430135078832063E-2</v>
       </c>
       <c r="AC15">
         <f ca="1">'Watchlist Ratings'!BM11</f>
-        <v>0.25949207403006769</v>
+        <v>0.25943228470250812</v>
       </c>
       <c r="AE15" t="s">
         <v>273</v>
@@ -33518,7 +33566,7 @@
       </c>
       <c r="J16" s="50">
         <f ca="1">'Watchlist Ratings'!AW12</f>
-        <v>36.235240624476425</v>
+        <v>38.113987330439414</v>
       </c>
       <c r="L16" t="s">
         <v>277</v>
@@ -33537,7 +33585,7 @@
       </c>
       <c r="Q16" s="23">
         <f ca="1">'Watchlist Ratings'!BM12</f>
-        <v>2.2808301254799268E-2</v>
+        <v>1.423921438264375E-2</v>
       </c>
       <c r="S16" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
@@ -33565,7 +33613,7 @@
       </c>
       <c r="Z16">
         <f ca="1">'Watchlist Ratings'!AW12</f>
-        <v>36.235240624476425</v>
+        <v>38.113987330439414</v>
       </c>
       <c r="AA16" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
@@ -33573,11 +33621,11 @@
       </c>
       <c r="AB16">
         <f ca="1">'Watchlist Ratings'!BL12</f>
-        <v>-0.12449674769032804</v>
+        <v>-0.13183171301735208</v>
       </c>
       <c r="AC16">
         <f ca="1">'Watchlist Ratings'!BM12</f>
-        <v>2.2808301254799268E-2</v>
+        <v>1.423921438264375E-2</v>
       </c>
       <c r="AE16" t="s">
         <v>254</v>
@@ -33663,7 +33711,7 @@
       </c>
       <c r="J17" s="44">
         <f ca="1">'Watchlist Ratings'!AW13</f>
-        <v>37.159060432515382</v>
+        <v>37.233401377131045</v>
       </c>
       <c r="L17" t="s">
         <v>278</v>
@@ -33682,7 +33730,7 @@
       </c>
       <c r="Q17" s="23">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>0.11301923910271405</v>
+        <v>0.11256640658534334</v>
       </c>
       <c r="S17" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
@@ -33710,7 +33758,7 @@
       </c>
       <c r="Z17">
         <f ca="1">'Watchlist Ratings'!AW13</f>
-        <v>37.159060432515382</v>
+        <v>37.233401377131045</v>
       </c>
       <c r="AA17" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
@@ -33718,11 +33766,11 @@
       </c>
       <c r="AB17">
         <f ca="1">'Watchlist Ratings'!BL13</f>
-        <v>-6.0627169269325321E-2</v>
+        <v>-6.1009353645609887E-2</v>
       </c>
       <c r="AC17">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>0.11301923910271405</v>
+        <v>0.11256640658534334</v>
       </c>
       <c r="AS17" t="s">
         <v>275</v>
@@ -33960,7 +34008,7 @@
       </c>
       <c r="J20" s="50">
         <f ca="1">'Watchlist Ratings'!AW16</f>
-        <v>59.15153551912568</v>
+        <v>82.192338648443439</v>
       </c>
       <c r="O20" t="str">
         <f ca="1">'Watchlist Ratings'!B16</f>
@@ -33972,7 +34020,7 @@
       </c>
       <c r="Q20" s="23">
         <f ca="1">'Watchlist Ratings'!BM16</f>
-        <v>-6.630657915443261E-3</v>
+        <v>-0.11087272348127619</v>
       </c>
       <c r="V20" t="str">
         <f ca="1">'Watchlist Ratings'!B16</f>
@@ -33992,7 +34040,7 @@
       </c>
       <c r="Z20">
         <f ca="1">'Watchlist Ratings'!AW16</f>
-        <v>59.15153551912568</v>
+        <v>82.192338648443439</v>
       </c>
       <c r="AA20" t="str">
         <f ca="1">'Watchlist Ratings'!B16</f>
@@ -34000,11 +34048,11 @@
       </c>
       <c r="AB20">
         <f ca="1">'Watchlist Ratings'!BL16</f>
-        <v>-0.19083965708991213</v>
+        <v>-0.24399019156889146</v>
       </c>
       <c r="AC20">
         <f ca="1">'Watchlist Ratings'!BM16</f>
-        <v>-6.630657915443261E-3</v>
+        <v>-0.11087272348127619</v>
       </c>
       <c r="AS20" t="s">
         <v>264</v>
@@ -34148,7 +34196,7 @@
       </c>
       <c r="J22" s="56">
         <f ca="1">'Watchlist Ratings'!AW18</f>
-        <v>36.840040741369862</v>
+        <v>36.660750743561643</v>
       </c>
       <c r="O22" t="str">
         <f ca="1">'Watchlist Ratings'!B18</f>
@@ -34160,7 +34208,7 @@
       </c>
       <c r="Q22" s="23">
         <f ca="1">'Watchlist Ratings'!BM18</f>
-        <v>0.10791391779857418</v>
+        <v>0.10909212414512681</v>
       </c>
       <c r="V22" t="str">
         <f ca="1">'Watchlist Ratings'!B18</f>
@@ -34180,7 +34228,7 @@
       </c>
       <c r="Z22">
         <f ca="1">'Watchlist Ratings'!AW18</f>
-        <v>36.840040741369862</v>
+        <v>36.660750743561643</v>
       </c>
       <c r="AA22" t="str">
         <f ca="1">'Watchlist Ratings'!B18</f>
@@ -34188,11 +34236,11 @@
       </c>
       <c r="AB22">
         <f ca="1">'Watchlist Ratings'!BL18</f>
-        <v>-7.07025913355247E-2</v>
+        <v>-6.9714333956378272E-2</v>
       </c>
       <c r="AC22">
         <f ca="1">'Watchlist Ratings'!BM18</f>
-        <v>0.10791391779857418</v>
+        <v>0.10909212414512681</v>
       </c>
     </row>
     <row r="23" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -34242,7 +34290,7 @@
       </c>
       <c r="Q25">
         <f ca="1">'Watchlist Ratings'!BM21</f>
-        <v>-5.9816951414956021E-3</v>
+        <v>9.8849409169941005E-3</v>
       </c>
     </row>
     <row r="26" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -34256,7 +34304,7 @@
       </c>
       <c r="Q26">
         <f ca="1">'Watchlist Ratings'!BM22</f>
-        <v>0.16592790507589994</v>
+        <v>0.1657315857896311</v>
       </c>
     </row>
     <row r="27" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -34466,7 +34514,7 @@
       </c>
       <c r="B64" s="64">
         <f ca="1">'Watchlist Ratings'!G4</f>
-        <v>243.84</v>
+        <v>245.75</v>
       </c>
       <c r="C64" s="64">
         <f ca="1">'Watchlist Ratings'!BJ4</f>
@@ -34478,15 +34526,15 @@
       </c>
       <c r="E64" s="65">
         <f ca="1">'Watchlist Ratings'!BL4</f>
-        <v>-2.9177844379771334E-2</v>
+        <v>-3.0691628302968677E-2</v>
       </c>
       <c r="F64" s="65">
         <f ca="1">'Watchlist Ratings'!BM4</f>
-        <v>0.21724859954203968</v>
+        <v>0.21535056770391781</v>
       </c>
       <c r="G64" s="65">
         <f t="shared" ref="G64:G71" ca="1" si="0">F64-E64</f>
-        <v>0.24642644392181101</v>
+        <v>0.24604219600688648</v>
       </c>
       <c r="H64" s="63" t="str">
         <f t="shared" ref="H64:H71" ca="1" si="1">IF(E64&gt;0,"🟢 BUY",IF(E64&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -34532,7 +34580,7 @@
       </c>
       <c r="B65" s="64">
         <f ca="1">'Watchlist Ratings'!G5</f>
-        <v>489.83</v>
+        <v>491.01499999999999</v>
       </c>
       <c r="C65" s="64">
         <f ca="1">'Watchlist Ratings'!BJ5</f>
@@ -34544,15 +34592,15 @@
       </c>
       <c r="E65" s="65">
         <f ca="1">'Watchlist Ratings'!BL5</f>
-        <v>-4.1895880509692951E-2</v>
+        <v>-4.2358779191663531E-2</v>
       </c>
       <c r="F65" s="65">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>0.12780422738436692</v>
+        <v>0.12725933974662795</v>
       </c>
       <c r="G65" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.16970010789405987</v>
+        <v>0.16961811893829148</v>
       </c>
       <c r="H65" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -34664,7 +34712,7 @@
       </c>
       <c r="B67" s="64">
         <f ca="1">'Watchlist Ratings'!G7</f>
-        <v>42.075000000000003</v>
+        <v>42.12</v>
       </c>
       <c r="C67" s="64">
         <f ca="1">'Watchlist Ratings'!BJ7</f>
@@ -34676,15 +34724,15 @@
       </c>
       <c r="E67" s="65">
         <f ca="1">'Watchlist Ratings'!BL7</f>
-        <v>1.6521030185501884E-2</v>
+        <v>1.6303731954826928E-2</v>
       </c>
       <c r="F67" s="65">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.21900244611200459</v>
+        <v>0.21874186412022789</v>
       </c>
       <c r="G67" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.20248141592650271</v>
+        <v>0.20243813216540096</v>
       </c>
       <c r="H67" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -34730,7 +34778,7 @@
       </c>
       <c r="B68" s="64">
         <f ca="1">'Watchlist Ratings'!G8</f>
-        <v>961.91</v>
+        <v>961.36</v>
       </c>
       <c r="C68" s="64">
         <f ca="1">'Watchlist Ratings'!BJ8</f>
@@ -34742,15 +34790,15 @@
       </c>
       <c r="E68" s="65">
         <f ca="1">'Watchlist Ratings'!BL8</f>
-        <v>-4.9816250558583963E-2</v>
+        <v>-4.9707554230484341E-2</v>
       </c>
       <c r="F68" s="65">
         <f ca="1">'Watchlist Ratings'!BM8</f>
-        <v>8.4916787387159243E-2</v>
+        <v>8.5040896509370301E-2</v>
       </c>
       <c r="G68" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.13473303794574321</v>
+        <v>0.13474845073985464</v>
       </c>
       <c r="H68" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -34796,7 +34844,7 @@
       </c>
       <c r="B69" s="64">
         <f ca="1">'Watchlist Ratings'!G9</f>
-        <v>77.3</v>
+        <v>77.48</v>
       </c>
       <c r="C69" s="64">
         <f ca="1">'Watchlist Ratings'!BJ9</f>
@@ -34808,15 +34856,15 @@
       </c>
       <c r="E69" s="65">
         <f ca="1">'Watchlist Ratings'!BL9</f>
-        <v>-3.6669624209512586E-2</v>
+        <v>-3.7117638736870018E-2</v>
       </c>
       <c r="F69" s="65">
         <f ca="1">'Watchlist Ratings'!BM9</f>
-        <v>0.19745985531708032</v>
+        <v>0.19690295456465767</v>
       </c>
       <c r="G69" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.23412947952659291</v>
+        <v>0.23402059330152769</v>
       </c>
       <c r="H69" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -34928,7 +34976,7 @@
       </c>
       <c r="B71" s="64">
         <f ca="1">'Watchlist Ratings'!G11</f>
-        <v>168.5</v>
+        <v>168.54</v>
       </c>
       <c r="C71" s="64">
         <f ca="1">'Watchlist Ratings'!BJ11</f>
@@ -34940,15 +34988,15 @@
       </c>
       <c r="E71" s="65">
         <f ca="1">'Watchlist Ratings'!BL11</f>
-        <v>-2.4255031214933664E-2</v>
+        <v>-2.430135078832063E-2</v>
       </c>
       <c r="F71" s="65">
         <f ca="1">'Watchlist Ratings'!BM11</f>
-        <v>0.25949207403006769</v>
+        <v>0.25943228470250812</v>
       </c>
       <c r="G71" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.28374710524500135</v>
+        <v>0.28373363549082875</v>
       </c>
       <c r="H71" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -35019,7 +35067,7 @@
       </c>
       <c r="B73" s="69">
         <f ca="1">'Watchlist Ratings'!G13</f>
-        <v>260.22000000000003</v>
+        <v>260.75</v>
       </c>
       <c r="C73" s="69">
         <f ca="1">'Watchlist Ratings'!BJ13</f>
@@ -35031,15 +35079,15 @@
       </c>
       <c r="E73" s="70">
         <f ca="1">'Watchlist Ratings'!BL13</f>
-        <v>-6.0627169269325321E-2</v>
+        <v>-6.1009353645609887E-2</v>
       </c>
       <c r="F73" s="70">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>0.11301923910271405</v>
+        <v>0.11256640658534334</v>
       </c>
       <c r="G73" s="70">
         <f ca="1">F73-E73</f>
-        <v>0.17364640837203937</v>
+        <v>0.17357576023095322</v>
       </c>
       <c r="H73" s="71" t="str">
         <f ca="1">IF(E73&gt;0,"🟢 BUY",IF(E73&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -35100,11 +35148,11 @@
       </c>
       <c r="F74" s="77">
         <f ca="1">VLOOKUP(A74,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.21724859954203968</v>
+        <v>0.21535056770391781</v>
       </c>
       <c r="G74" s="77">
         <f ca="1">F74-E74</f>
-        <v>-210.0653546226284</v>
+        <v>-210.06725265446653</v>
       </c>
       <c r="H74" s="75" t="str">
         <f ca="1">IF(E74&gt;0,"🟢 BUY",IF(E74&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -35131,7 +35179,7 @@
       </c>
       <c r="O74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>39610.174271999997</v>
+        <v>39920.440974999998</v>
       </c>
       <c r="P74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -35164,11 +35212,11 @@
       </c>
       <c r="F75" s="81">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.12780422738436692</v>
+        <v>0.12725933974662795</v>
       </c>
       <c r="G75" s="81">
         <f ca="1">F75-E75</f>
-        <v>-395.33798313233132</v>
+        <v>-395.33852801996909</v>
       </c>
       <c r="H75" s="79" t="str">
         <f ca="1">IF(E75&gt;0,"🟢 BUY",IF(E75&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -35195,7 +35243,7 @@
       </c>
       <c r="O75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>3637254.7073499998</v>
+        <v>3646053.9781749998</v>
       </c>
       <c r="P75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -35249,11 +35297,11 @@
       </c>
       <c r="F77" s="81">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.21900244611200459</v>
+        <v>0.21874186412022789</v>
       </c>
       <c r="G77" s="81">
         <f ca="1">F77-E77</f>
-        <v>-45.448363673839133</v>
+        <v>-45.448624255830914</v>
       </c>
       <c r="H77" s="79" t="str">
         <f ca="1">IF(E77&gt;0,"🟢 BUY",IF(E77&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -35280,7 +35328,7 @@
       </c>
       <c r="O77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>103164.323625</v>
+        <v>103274.65979999999</v>
       </c>
       <c r="P77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -35383,7 +35431,7 @@
       <c r="B80" s="121"/>
       <c r="C80" s="160">
         <f ca="1">MAX('Watchlist Ratings'!BM:BM)</f>
-        <v>0.34861805110601995</v>
+        <v>0.34705971061379648</v>
       </c>
       <c r="D80" s="121"/>
       <c r="E80" s="163">
@@ -35408,12 +35456,12 @@
       <c r="L80" s="121"/>
       <c r="M80" s="126" t="str">
         <f ca="1">MIN('Watchlist Ratings'!AW4:AW64)&amp;"x"</f>
-        <v>-45.9971332237443x</v>
+        <v>-45.7275547716895x</v>
       </c>
       <c r="N80" s="121"/>
       <c r="O80" s="126" t="str">
         <f t="array" aca="1" ref="O80" ca="1">TEXT(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),"0.0%")</f>
-        <v>221.3%</v>
+        <v>120.6%</v>
       </c>
       <c r="P80" s="121"/>
       <c r="Q80" s="82" t="str">
@@ -35443,11 +35491,11 @@
       </c>
       <c r="F81" s="81">
         <f ca="1">VLOOKUP(A81,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.25949207403006769</v>
+        <v>0.25943228470250812</v>
       </c>
       <c r="G81" s="81">
         <f ca="1">F81-E81</f>
-        <v>-148.77318689659319</v>
+        <v>-148.77324668592075</v>
       </c>
       <c r="H81" s="79" t="str">
         <f ca="1">IF(E81&gt;0,"🟢 BUY",IF(E81&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -35474,7 +35522,7 @@
       </c>
       <c r="O81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>27248.050749999999</v>
+        <v>27254.519129999997</v>
       </c>
       <c r="P81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -35528,11 +35576,11 @@
       </c>
       <c r="F83" s="85">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.11301923910271405</v>
+        <v>0.11256640658534334</v>
       </c>
       <c r="G83" s="85">
         <f ca="1">F83-E83</f>
-        <v>-190.22723614016971</v>
+        <v>-190.2276889726871</v>
       </c>
       <c r="H83" s="83" t="str">
         <f ca="1">IF(E83&gt;0,"🟢 BUY",IF(E83&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -35559,7 +35607,7 @@
       </c>
       <c r="O83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>2806813.5882000001</v>
+        <v>2812530.3325</v>
       </c>
       <c r="P83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -35677,7 +35725,7 @@
       <c r="B89" s="102"/>
       <c r="C89" s="117">
         <f ca="1">MAX('Watchlist Ratings'!BM$4:BM$64)</f>
-        <v>0.34861805110601995</v>
+        <v>0.34705971061379648</v>
       </c>
       <c r="D89" s="102"/>
       <c r="E89" s="117">
@@ -35702,12 +35750,12 @@
       <c r="L89" s="102"/>
       <c r="M89" s="111" t="str">
         <f t="array" aca="1" ref="M89" ca="1">MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64))&amp;"x"</f>
-        <v>9.1219709975982x</v>
+        <v>9.17979049616966x</v>
       </c>
       <c r="N89" s="102"/>
       <c r="O89" s="111">
         <f t="array" aca="1" ref="O89" ca="1">MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64)</f>
-        <v>2.213371296902098</v>
+        <v>1.2056577915819566</v>
       </c>
       <c r="P89" s="102"/>
     </row>
@@ -35863,7 +35911,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E228"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -38430,13 +38478,13 @@
         <v>46256</v>
       </c>
       <c r="C151" t="s">
+        <v>639</v>
+      </c>
+      <c r="D151" t="s">
         <v>640</v>
       </c>
-      <c r="D151" t="s">
+      <c r="E151" t="s">
         <v>641</v>
-      </c>
-      <c r="E151" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
@@ -38447,13 +38495,13 @@
         <v>46256</v>
       </c>
       <c r="C152" t="s">
+        <v>639</v>
+      </c>
+      <c r="D152" t="s">
         <v>640</v>
       </c>
-      <c r="D152" t="s">
-        <v>641</v>
-      </c>
       <c r="E152" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
@@ -38464,13 +38512,13 @@
         <v>46256</v>
       </c>
       <c r="C153" t="s">
+        <v>643</v>
+      </c>
+      <c r="D153" t="s">
+        <v>640</v>
+      </c>
+      <c r="E153" t="s">
         <v>644</v>
-      </c>
-      <c r="D153" t="s">
-        <v>641</v>
-      </c>
-      <c r="E153" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
@@ -38481,13 +38529,13 @@
         <v>46256</v>
       </c>
       <c r="C154" t="s">
+        <v>645</v>
+      </c>
+      <c r="D154" t="s">
         <v>646</v>
       </c>
-      <c r="D154" t="s">
+      <c r="E154" t="s">
         <v>647</v>
-      </c>
-      <c r="E154" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
@@ -38498,13 +38546,13 @@
         <v>46256</v>
       </c>
       <c r="C155" t="s">
+        <v>648</v>
+      </c>
+      <c r="D155" t="s">
+        <v>646</v>
+      </c>
+      <c r="E155" t="s">
         <v>649</v>
-      </c>
-      <c r="D155" t="s">
-        <v>647</v>
-      </c>
-      <c r="E155" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
@@ -38518,10 +38566,10 @@
         <v>622</v>
       </c>
       <c r="D156" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E156" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
@@ -38532,13 +38580,13 @@
         <v>46256</v>
       </c>
       <c r="C157" t="s">
+        <v>651</v>
+      </c>
+      <c r="D157" t="s">
+        <v>646</v>
+      </c>
+      <c r="E157" t="s">
         <v>652</v>
-      </c>
-      <c r="D157" t="s">
-        <v>647</v>
-      </c>
-      <c r="E157" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
@@ -38549,13 +38597,13 @@
         <v>46256</v>
       </c>
       <c r="C158" t="s">
+        <v>663</v>
+      </c>
+      <c r="D158" t="s">
         <v>664</v>
       </c>
-      <c r="D158" t="s">
+      <c r="E158" t="s">
         <v>665</v>
-      </c>
-      <c r="E158" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
@@ -38566,13 +38614,13 @@
         <v>46256</v>
       </c>
       <c r="C159" t="s">
+        <v>666</v>
+      </c>
+      <c r="D159" t="s">
+        <v>664</v>
+      </c>
+      <c r="E159" t="s">
         <v>667</v>
-      </c>
-      <c r="D159" t="s">
-        <v>665</v>
-      </c>
-      <c r="E159" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
@@ -38583,13 +38631,13 @@
         <v>46256</v>
       </c>
       <c r="C160" t="s">
+        <v>668</v>
+      </c>
+      <c r="D160" t="s">
+        <v>664</v>
+      </c>
+      <c r="E160" t="s">
         <v>669</v>
-      </c>
-      <c r="D160" t="s">
-        <v>665</v>
-      </c>
-      <c r="E160" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
@@ -38600,13 +38648,13 @@
         <v>46256</v>
       </c>
       <c r="C161" t="s">
+        <v>670</v>
+      </c>
+      <c r="D161" t="s">
+        <v>664</v>
+      </c>
+      <c r="E161" t="s">
         <v>671</v>
-      </c>
-      <c r="D161" t="s">
-        <v>665</v>
-      </c>
-      <c r="E161" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
@@ -38617,13 +38665,13 @@
         <v>46256</v>
       </c>
       <c r="C162" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D162" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="E162" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
@@ -38634,13 +38682,13 @@
         <v>46256</v>
       </c>
       <c r="C163" t="s">
+        <v>673</v>
+      </c>
+      <c r="D163" t="s">
+        <v>664</v>
+      </c>
+      <c r="E163" t="s">
         <v>674</v>
-      </c>
-      <c r="D163" t="s">
-        <v>665</v>
-      </c>
-      <c r="E163" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
@@ -38651,13 +38699,13 @@
         <v>46256</v>
       </c>
       <c r="C164" t="s">
+        <v>675</v>
+      </c>
+      <c r="D164" t="s">
+        <v>664</v>
+      </c>
+      <c r="E164" t="s">
         <v>676</v>
-      </c>
-      <c r="D164" t="s">
-        <v>665</v>
-      </c>
-      <c r="E164" t="s">
-        <v>677</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
@@ -38668,13 +38716,13 @@
         <v>46259</v>
       </c>
       <c r="C165" t="s">
+        <v>686</v>
+      </c>
+      <c r="D165" t="s">
         <v>687</v>
       </c>
-      <c r="D165" t="s">
+      <c r="E165" t="s">
         <v>688</v>
-      </c>
-      <c r="E165" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
@@ -38685,13 +38733,13 @@
         <v>46259</v>
       </c>
       <c r="C166" t="s">
+        <v>689</v>
+      </c>
+      <c r="D166" t="s">
         <v>690</v>
       </c>
-      <c r="D166" t="s">
+      <c r="E166" t="s">
         <v>691</v>
-      </c>
-      <c r="E166" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
@@ -38702,13 +38750,13 @@
         <v>46259</v>
       </c>
       <c r="C167" t="s">
+        <v>692</v>
+      </c>
+      <c r="D167" t="s">
         <v>693</v>
       </c>
-      <c r="D167" t="s">
+      <c r="E167" t="s">
         <v>694</v>
-      </c>
-      <c r="E167" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
@@ -38719,13 +38767,13 @@
         <v>46259</v>
       </c>
       <c r="C168" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D168" t="s">
+        <v>695</v>
+      </c>
+      <c r="E168" t="s">
         <v>696</v>
-      </c>
-      <c r="E168" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
@@ -38736,13 +38784,13 @@
         <v>46259</v>
       </c>
       <c r="C169" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D169" t="s">
+        <v>697</v>
+      </c>
+      <c r="E169" t="s">
         <v>698</v>
-      </c>
-      <c r="E169" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
@@ -38753,13 +38801,13 @@
         <v>46259</v>
       </c>
       <c r="C170" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D170" t="s">
+        <v>699</v>
+      </c>
+      <c r="E170" t="s">
         <v>700</v>
-      </c>
-      <c r="E170" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
@@ -38770,13 +38818,13 @@
         <v>46259</v>
       </c>
       <c r="C171" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D171" t="s">
+        <v>701</v>
+      </c>
+      <c r="E171" t="s">
         <v>702</v>
-      </c>
-      <c r="E171" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
@@ -38787,47 +38835,47 @@
         <v>46259</v>
       </c>
       <c r="C172" t="s">
+        <v>692</v>
+      </c>
+      <c r="D172" t="s">
         <v>693</v>
       </c>
-      <c r="D172" t="s">
-        <v>694</v>
-      </c>
       <c r="E172" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B173">
         <v>46259</v>
       </c>
       <c r="C173" t="s">
+        <v>705</v>
+      </c>
+      <c r="D173" t="s">
         <v>706</v>
       </c>
-      <c r="D173" t="s">
+      <c r="E173" t="s">
         <v>707</v>
-      </c>
-      <c r="E173" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B174">
         <v>46259</v>
       </c>
       <c r="C174" t="s">
+        <v>709</v>
+      </c>
+      <c r="D174" t="s">
         <v>710</v>
       </c>
-      <c r="D174" t="s">
+      <c r="E174" t="s">
         <v>711</v>
-      </c>
-      <c r="E174" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
@@ -38838,13 +38886,13 @@
         <v>46259</v>
       </c>
       <c r="C175" t="s">
+        <v>712</v>
+      </c>
+      <c r="D175" t="s">
         <v>713</v>
       </c>
-      <c r="D175" t="s">
+      <c r="E175" t="s">
         <v>714</v>
-      </c>
-      <c r="E175" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
@@ -38855,13 +38903,13 @@
         <v>46259</v>
       </c>
       <c r="C176" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D176" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E176" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
@@ -38872,13 +38920,13 @@
         <v>46259</v>
       </c>
       <c r="C177" t="s">
+        <v>716</v>
+      </c>
+      <c r="D177" t="s">
         <v>717</v>
       </c>
-      <c r="D177" t="s">
+      <c r="E177" t="s">
         <v>718</v>
-      </c>
-      <c r="E177" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
@@ -38889,13 +38937,13 @@
         <v>46259</v>
       </c>
       <c r="C178" t="s">
+        <v>719</v>
+      </c>
+      <c r="D178" t="s">
         <v>720</v>
       </c>
-      <c r="D178" t="s">
+      <c r="E178" t="s">
         <v>721</v>
-      </c>
-      <c r="E178" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
@@ -38906,13 +38954,13 @@
         <v>46259</v>
       </c>
       <c r="C179" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D179" t="s">
+        <v>722</v>
+      </c>
+      <c r="E179" t="s">
         <v>723</v>
-      </c>
-      <c r="E179" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
@@ -38923,13 +38971,13 @@
         <v>46259</v>
       </c>
       <c r="C180" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D180" t="s">
+        <v>724</v>
+      </c>
+      <c r="E180" t="s">
         <v>725</v>
-      </c>
-      <c r="E180" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
@@ -38940,30 +38988,30 @@
         <v>46259</v>
       </c>
       <c r="C181" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D181" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E181" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B182">
         <v>46259</v>
       </c>
       <c r="C182" t="s">
+        <v>728</v>
+      </c>
+      <c r="D182" t="s">
         <v>729</v>
       </c>
-      <c r="D182" t="s">
+      <c r="E182" t="s">
         <v>730</v>
-      </c>
-      <c r="E182" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
@@ -38974,13 +39022,13 @@
         <v>46259</v>
       </c>
       <c r="C183" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D183" t="s">
+        <v>731</v>
+      </c>
+      <c r="E183" t="s">
         <v>732</v>
-      </c>
-      <c r="E183" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
@@ -38991,13 +39039,13 @@
         <v>46259</v>
       </c>
       <c r="C184" t="s">
+        <v>733</v>
+      </c>
+      <c r="D184" t="s">
         <v>734</v>
       </c>
-      <c r="D184" t="s">
+      <c r="E184" t="s">
         <v>735</v>
-      </c>
-      <c r="E184" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
@@ -39008,13 +39056,13 @@
         <v>46259</v>
       </c>
       <c r="C185" t="s">
+        <v>736</v>
+      </c>
+      <c r="D185" t="s">
         <v>737</v>
       </c>
-      <c r="D185" t="s">
+      <c r="E185" t="s">
         <v>738</v>
-      </c>
-      <c r="E185" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
@@ -39025,13 +39073,13 @@
         <v>46259</v>
       </c>
       <c r="C186" t="s">
+        <v>739</v>
+      </c>
+      <c r="D186" t="s">
         <v>740</v>
       </c>
-      <c r="D186" t="s">
+      <c r="E186" t="s">
         <v>741</v>
-      </c>
-      <c r="E186" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
@@ -39042,13 +39090,13 @@
         <v>46259</v>
       </c>
       <c r="C187" t="s">
+        <v>742</v>
+      </c>
+      <c r="D187" t="s">
         <v>743</v>
       </c>
-      <c r="D187" t="s">
+      <c r="E187" t="s">
         <v>744</v>
-      </c>
-      <c r="E187" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
@@ -39059,13 +39107,13 @@
         <v>46259</v>
       </c>
       <c r="C188" t="s">
+        <v>745</v>
+      </c>
+      <c r="D188" t="s">
+        <v>743</v>
+      </c>
+      <c r="E188" t="s">
         <v>746</v>
-      </c>
-      <c r="D188" t="s">
-        <v>744</v>
-      </c>
-      <c r="E188" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
@@ -39076,13 +39124,13 @@
         <v>46259</v>
       </c>
       <c r="C189" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D189" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E189" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
@@ -39093,13 +39141,13 @@
         <v>46259</v>
       </c>
       <c r="C190" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D190" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E190" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
@@ -39110,13 +39158,13 @@
         <v>46259</v>
       </c>
       <c r="C191" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D191" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E191" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
@@ -39127,13 +39175,13 @@
         <v>46259</v>
       </c>
       <c r="C192" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D192" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E192" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
@@ -39144,13 +39192,13 @@
         <v>46259</v>
       </c>
       <c r="C193" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D193" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E193" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
@@ -39161,30 +39209,30 @@
         <v>46259</v>
       </c>
       <c r="C194" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D194" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E194" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B195">
         <v>46259</v>
       </c>
       <c r="C195" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D195" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E195" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
@@ -39195,13 +39243,13 @@
         <v>46259</v>
       </c>
       <c r="C196" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D196" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E196" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
@@ -39212,13 +39260,13 @@
         <v>46259</v>
       </c>
       <c r="C197" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D197" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E197" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
@@ -39229,13 +39277,13 @@
         <v>46259</v>
       </c>
       <c r="C198" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D198" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E198" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
@@ -39246,13 +39294,13 @@
         <v>46259</v>
       </c>
       <c r="C199" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D199" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E199" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
@@ -39263,13 +39311,13 @@
         <v>46259</v>
       </c>
       <c r="C200" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D200" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E200" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
@@ -39280,13 +39328,13 @@
         <v>46259</v>
       </c>
       <c r="C201" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D201" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E201" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
@@ -39297,13 +39345,13 @@
         <v>46259</v>
       </c>
       <c r="C202" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D202" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E202" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
@@ -39314,13 +39362,13 @@
         <v>46259</v>
       </c>
       <c r="C203" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D203" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E203" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
@@ -39331,13 +39379,13 @@
         <v>46259</v>
       </c>
       <c r="C204" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D204" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E204" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
@@ -39348,13 +39396,13 @@
         <v>46259</v>
       </c>
       <c r="C205" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D205" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E205" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
@@ -39365,13 +39413,13 @@
         <v>46259</v>
       </c>
       <c r="C206" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D206" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E206" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
@@ -39382,13 +39430,13 @@
         <v>46259</v>
       </c>
       <c r="C207" t="s">
+        <v>765</v>
+      </c>
+      <c r="D207" t="s">
+        <v>743</v>
+      </c>
+      <c r="E207" t="s">
         <v>766</v>
-      </c>
-      <c r="D207" t="s">
-        <v>744</v>
-      </c>
-      <c r="E207" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
@@ -39399,13 +39447,13 @@
         <v>46259</v>
       </c>
       <c r="C208" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D208" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E208" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
@@ -39416,13 +39464,13 @@
         <v>46259</v>
       </c>
       <c r="C209" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D209" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E209" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
@@ -39433,13 +39481,13 @@
         <v>46259</v>
       </c>
       <c r="C210" t="s">
+        <v>769</v>
+      </c>
+      <c r="D210" t="s">
         <v>770</v>
       </c>
-      <c r="D210" t="s">
+      <c r="E210" t="s">
         <v>771</v>
-      </c>
-      <c r="E210" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
@@ -39450,13 +39498,13 @@
         <v>46259</v>
       </c>
       <c r="C211" t="s">
+        <v>772</v>
+      </c>
+      <c r="D211" t="s">
         <v>773</v>
       </c>
-      <c r="D211" t="s">
+      <c r="E211" t="s">
         <v>774</v>
-      </c>
-      <c r="E211" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
@@ -39467,13 +39515,13 @@
         <v>46259</v>
       </c>
       <c r="C212" t="s">
+        <v>775</v>
+      </c>
+      <c r="D212" t="s">
+        <v>773</v>
+      </c>
+      <c r="E212" t="s">
         <v>776</v>
-      </c>
-      <c r="D212" t="s">
-        <v>774</v>
-      </c>
-      <c r="E212" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
@@ -39484,13 +39532,13 @@
         <v>46259</v>
       </c>
       <c r="C213" t="s">
+        <v>778</v>
+      </c>
+      <c r="D213" t="s">
         <v>779</v>
       </c>
-      <c r="D213" t="s">
+      <c r="E213" t="s">
         <v>780</v>
-      </c>
-      <c r="E213" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
@@ -39501,13 +39549,13 @@
         <v>46259</v>
       </c>
       <c r="C214" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D214" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E214" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
@@ -39518,13 +39566,13 @@
         <v>46259</v>
       </c>
       <c r="C215" t="s">
+        <v>782</v>
+      </c>
+      <c r="D215" t="s">
+        <v>779</v>
+      </c>
+      <c r="E215" t="s">
         <v>783</v>
-      </c>
-      <c r="D215" t="s">
-        <v>780</v>
-      </c>
-      <c r="E215" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
@@ -39535,13 +39583,13 @@
         <v>46259</v>
       </c>
       <c r="C216" t="s">
+        <v>784</v>
+      </c>
+      <c r="D216" t="s">
+        <v>779</v>
+      </c>
+      <c r="E216" t="s">
         <v>785</v>
-      </c>
-      <c r="D216" t="s">
-        <v>780</v>
-      </c>
-      <c r="E216" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
@@ -39552,13 +39600,13 @@
         <v>46259</v>
       </c>
       <c r="C217" t="s">
+        <v>786</v>
+      </c>
+      <c r="D217" t="s">
+        <v>779</v>
+      </c>
+      <c r="E217" t="s">
         <v>787</v>
-      </c>
-      <c r="D217" t="s">
-        <v>780</v>
-      </c>
-      <c r="E217" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
@@ -39569,13 +39617,13 @@
         <v>46259</v>
       </c>
       <c r="C218" t="s">
+        <v>788</v>
+      </c>
+      <c r="D218" t="s">
+        <v>779</v>
+      </c>
+      <c r="E218" t="s">
         <v>789</v>
-      </c>
-      <c r="D218" t="s">
-        <v>780</v>
-      </c>
-      <c r="E218" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
@@ -39586,13 +39634,13 @@
         <v>46259</v>
       </c>
       <c r="C219" t="s">
+        <v>790</v>
+      </c>
+      <c r="D219" t="s">
+        <v>779</v>
+      </c>
+      <c r="E219" t="s">
         <v>791</v>
-      </c>
-      <c r="D219" t="s">
-        <v>780</v>
-      </c>
-      <c r="E219" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
@@ -39603,13 +39651,13 @@
         <v>46259</v>
       </c>
       <c r="C220" t="s">
+        <v>792</v>
+      </c>
+      <c r="D220" t="s">
+        <v>779</v>
+      </c>
+      <c r="E220" t="s">
         <v>793</v>
-      </c>
-      <c r="D220" t="s">
-        <v>780</v>
-      </c>
-      <c r="E220" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
@@ -39620,13 +39668,13 @@
         <v>46259</v>
       </c>
       <c r="C221" t="s">
+        <v>794</v>
+      </c>
+      <c r="D221" t="s">
         <v>795</v>
       </c>
-      <c r="D221" t="s">
+      <c r="E221" t="s">
         <v>796</v>
-      </c>
-      <c r="E221" t="s">
-        <v>797</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
@@ -39637,13 +39685,115 @@
         <v>46259</v>
       </c>
       <c r="C222" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D222" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E222" t="s">
-        <v>798</v>
+        <v>797</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>258</v>
+      </c>
+      <c r="B223">
+        <v>46259</v>
+      </c>
+      <c r="C223" t="s">
+        <v>800</v>
+      </c>
+      <c r="D223" t="s">
+        <v>801</v>
+      </c>
+      <c r="E223" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>405</v>
+      </c>
+      <c r="B224">
+        <v>46259</v>
+      </c>
+      <c r="C224" t="s">
+        <v>673</v>
+      </c>
+      <c r="D224" t="s">
+        <v>803</v>
+      </c>
+      <c r="E224" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>272</v>
+      </c>
+      <c r="B225">
+        <v>46259</v>
+      </c>
+      <c r="C225" t="s">
+        <v>673</v>
+      </c>
+      <c r="D225" t="s">
+        <v>805</v>
+      </c>
+      <c r="E225" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>389</v>
+      </c>
+      <c r="B226">
+        <v>46259</v>
+      </c>
+      <c r="C226" t="s">
+        <v>807</v>
+      </c>
+      <c r="D226" t="s">
+        <v>808</v>
+      </c>
+      <c r="E226" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>453</v>
+      </c>
+      <c r="B227">
+        <v>46259</v>
+      </c>
+      <c r="C227" t="s">
+        <v>810</v>
+      </c>
+      <c r="D227" t="s">
+        <v>811</v>
+      </c>
+      <c r="E227" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>453</v>
+      </c>
+      <c r="B228">
+        <v>46259</v>
+      </c>
+      <c r="C228" t="s">
+        <v>813</v>
+      </c>
+      <c r="D228" t="s">
+        <v>814</v>
+      </c>
+      <c r="E228" t="s">
+        <v>815</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Cosas Roger\BOLSA E INVERSIÓN\repos\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8953462F-95FD-4E3B-952E-48E297AE4D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1838A2-3038-4449-AF3B-196C7ECCE318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2463,7 +2463,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1807" uniqueCount="837">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -4948,6 +4948,69 @@
   </si>
   <si>
     <t>Fila 58: la normalizacion solo vale si el capex elevado es TEMPORAL. Si lleva TRES O MAS EJERCICIOS SEGUIDOS por encima del doble del D&amp;A, no es una fase de inversion sino como funciona el negocio, y se usa el FCF reportado. Sale LOTB y quedan doce filas normalizadas. PENDIENTE: pasar este test a las doce restantes, empezando por META, GOOG, MSFT y AMZN, que tambien llevan varios ejercicios de capex alto. Fila 59: advertencia nueva sobre los negocios cuyo FCF a traves del ciclo no existe porque el beneficio se reinvierte en circulante y no en activo fijo, con TFF como caso extremo del libro.</t>
+  </si>
+  <si>
+    <t>AH (R3 Financing Source); AI (R3 Incentives)</t>
+  </si>
+  <si>
+    <t>Correccion de un error propio</t>
+  </si>
+  <si>
+    <t>SentinelOne. CORRIGE UN ERROR MIO DEL 25-AGO: el mapa de columnas del script tenia AH en la posicion 35, que es AI, asi que el cambio previsto -Financing Source de 0 a 1- se escribio en Incentives y lo bajo de 6 a 1. Efecto real: el R3 cayo 5 puntos en vez de subir 1. Restaurado: AH=1 (que era la intencion, por 657 M$ de caja e inversiones a corto mas 156 a largo, sin deuda y FCF LTM positivo de 62 M$) y AI=6 (valor original). El R3 pasa de 2,86 a 3,71.</t>
+  </si>
+  <si>
+    <t>Deep dive completo del 25-ago-2026</t>
+  </si>
+  <si>
+    <t>Costco. R2 Potential 11 -&gt; 13. El 11 estaba calibrado como el de un retailer americano maduro y el deep dive muestra que el motor no son las aperturas: el parque solo ha crecido un 17% en seis anos (795 a 931 almacenes) mientras la FACTURACION POR ALMACEN subia de 209,8 a 315,3 M$ (+50%) y el BENEFICIO POR ALMACEN de 5,03 a 9,50 M$ (+89%). O sea apalancamiento operativo sobre una base de costes ya pagada, mas subidas de cuota cada cinco anos, mas penetracion de Kirkland, mas comercio electronico apalancando los mismos almacenes. Y Europa sigue practicamente sin ejecutar. FLYWHEEL confirmado con el indicador que la tesis de 2021 eligio como senal de alarma: la renovacion EE.UU./Canada ha subido del 91% al 92,2% y la mundial del 88% al 89,7%. Las cuotas son el 49% del beneficio operativo. NO se sube Optionality (sigue en 1 sobre 3): Europa lleva cinco anos prometida y sin ejecutar, y una opcion no ejercida no se premia.</t>
+  </si>
+  <si>
+    <t>AD (R3 Durability); L (R1 Optionality); BF</t>
+  </si>
+  <si>
+    <t>Inditex. R3 Durability 14 -&gt; 15 y R1 Optionality 2 -&gt; 1,5. Durability al maximo porque el deep dive responde la pregunta que la tesis de 2021 dejo abierta: el online iba a comprimir el margen y ha hecho lo contrario. Es el 26,7% de las ventas (10.700 M EUR) y el margen bruto SUBIO 42 pb hasta el 58,3%, con el EBIT en 20,2% frente al 16-16,5% que se esperaba. Ademas han cerrado casi 2.000 tiendas desde 2019 (7.400 a 5.460) y venden mas que nunca. Absorber un cambio de canal que ha matado a media industria textil expandiendo margen ES antifragilidad demostrada. Optionality baja porque la palanca online ya esta ejercida y esta en la base, no en el futuro; Asia, que era la otra palanca de la tesis, lleva cinco anos sin arrancar; y no lanzan una marca organica desde Uterque en 2008 ni compran una desde Stradivarius en 1998. BF pasa de 12.407 a 10.832 (+12,0%/a a +9,0%/a): con el parque de tiendas ENCOGIENDO y Asia sin ejecutar, un 12% anual de FCF durante cinco anos exige que el margen siga expandiendo por encima del 20,2%. El +9%/a es lo que da el historial real (beneficio neto +9,5% anual entre 2019 y 2025). Alcista pasa de +67% a +46%, asimetria 2,3:1. AVISO ya recogido: la hoja tenia DEUDA CERO y son 6.040 M EUR, casi todo arrendamientos NIIF 16 de 5.460 tiendas; la caja neta excluyendo arrendamientos ronda los 10.000 M EUR.</t>
+  </si>
+  <si>
+    <t>Ninguno - nota de proceso</t>
+  </si>
+  <si>
+    <t>Revision de las tesis del Drive</t>
+  </si>
+  <si>
+    <t>Revisadas las 36 tesis de la carpeta de Drive (2020-2021). Once son de empresas de la watchlist: COST, ITX, AMZN, MSFT, NTO, ABNB, GOOG, META, VID, SIKA y SPOT, mas Brookfield Asset Management que no es la matriz que seguimos. PATRON QUE CONVIENE ANOTAR: en Costco e Inditex el analisis del NEGOCIO fue solido -las dos identificaron la metrica correcta a vigilar- y la estimacion del RECORRIDO se quedo corta por un factor de dos o tres. Costco con precio de venta en 450 $ y hoy 947; Inditex con techo en 35-40 EUR y hoy 58,28. Es un sesgo consistente, no mala suerte, y hay que tenerlo delante al fijar los multiplos de salida del escenario alcista. Indice completo en Inversion Roger/00_Tesis_en_Drive_indice.md.</t>
+  </si>
+  <si>
+    <t>Ninguno - deep dive sin cambio de rating</t>
+  </si>
+  <si>
+    <t>Nintendo. SIN CAMBIO DE RATING, y se explica por que. El deep dive confirma la tesis del Drive en lo esencial -las IP tienen efecto Lindy, la explotacion fuera de la consola ya esta ocurriendo (Osaka, cine, series) y la caja neta sigue siendo el 19% de la capitalizacion, igual proporcion que en 2021- y no aparece ningun hecho nuevo que mueva R1, R2 ni R3. LO QUE SI APARECE ES UN PROBLEMA DE MEDICION: en el ano de lanzamiento Nintendo fabrica e inventaria millones de consolas antes de venderlas, asi que el circulante absorbe caja justo cuando el beneficio hace maximo y el FCF se deprime en el PICO de ventas. Por eso el EV/FCF sale en 38,1x en el mejor ejercicio de su historia. La tesis de 2021 decia que en la parte alta del ciclo la empresa PARECERIA BARATA y es justo al reves. Mismo mecanismo que TFF Group: negocios donde el circulante se mueve al reves que el beneficio. Para Nintendo la metrica honesta es EV/EBIT sobre beneficio medio de ciclo. Contexto: FY2026 cerro con ventas de 2.313 mm JPY (+98,6%) y la propia guia FY2027 es de 2.050 mm (-11,4%); el +150% de resultado operativo del Q1 incluye unos 300 M$ de devoluciones de aranceles que no se repiten.</t>
+  </si>
+  <si>
+    <t>U (R2 MOAT)</t>
+  </si>
+  <si>
+    <t>Airbnb. R2 MOAT 16 -&gt; 17. Hecho de largo plazo que las ratings no recogian: la marca se ha convertido en CATEGORIA -la gente dice un airbnb- y eso hace que el trafico directo sustituya al comprado. Consecuencia medible: margen operativo del 20,8% frente al 11% que proyectaba la tesis del Drive para este momento, y margen FCF del 37%. Un foso de marca que reduce estructuralmente el coste de adquisicion es exactamente lo que mide esta columna. NO se sube MOAT del R1 (sigue en 6 sobre 8): la observacion del 21-ago de que el anfitrion tiene Booking a un clic y de que la oferta es legislable ciudad a ciudad sigue siendo cierta. PENDIENTE: Experiencias lleva cinco anos sin monetizar; si sigue asi hay que sacarla del caso alcista. AVISO: de los 12.069 M$ de caja, una parte son fondos de anfitriones pendientes de pago -flotacion, no caja propia- y la fila no lo distingue.</t>
+  </si>
+  <si>
+    <t>AF (R3 Capital Intensity)</t>
+  </si>
+  <si>
+    <t>Alphabet. R3 Capital Intensity 6 -&gt; 5. El capex LTM es de 132.410 M$, el 29,7% de las ventas y CINCO VECES el D&amp;A. La tesis del Drive describia Alphabet como un negocio donde para cada dolar extra ganado no hace falta invertir practicamente nada; eso ha dejado de ser cierto. Precedente del libro: a Microsoft se le bajo esta misma columna de 5 a 4 con el capex al 35% de las ventas. El capital empleado sube a 795.872 M$ y el ROIC baja al 15,1%, bajo para Alphabet. RIESGO ESTRUCTURAL QUE HAY QUE VIGILAR y que no estaba en la tesis de 2021: si el usuario deja de teclear una consulta y pasa a preguntar a un asistente que da la respuesta directa SIN ensenar diez enlaces con anuncios encima, el inventario publicitario se encoge aunque la busqueda siga existiendo. Es lo que decide el valor terminal. AVISO: toda la asimetria de esta fila descansa en la normalizacion del FCF; con el reportado (53.270) el EV/FCF seria 76,5x.</t>
+  </si>
+  <si>
+    <t>AF (R3 Capital Intensity); AH (R3 Financing Source)</t>
+  </si>
+  <si>
+    <t>Meta. R3 Capital Intensity 7 -&gt; 5 y R3 Financing Source 4 -&gt; 3. Capex LTM de 89.320 M$, el 39,1% de las ventas y casi CUATRO VECES el D&amp;A: mas intensivo que Microsoft cuando se le bajo esta columna. Y por primera vez en su historia la DEUDA (112.320) SUPERA A LA CAJA (90.260), o sea que la apuesta se esta financiando con apalancamiento. Meta ha pasado de ser el negocio mas ligero en capital de las grandes tecnologicas a uno de los mas pesados. El negocio publicitario sigue siendo extraordinario -38,1% de margen operativo sobre 228.250 M$- y el bucle de la subasta que describia la tesis de 2021 sigue funcionando: el ARPU sube sin necesidad de anadir usuarios. AVISO SOBRE LA ASIMETRIA: 10,5:1 sobre el papel es la mas alta del libro, pero el rango entre el bajista (-5,4% anual de FCF) y el alcista (+16%) es enorme porque la incertidumbre es enorme. Un 10,5:1 no es senal de compra, es senal de resultado BINARIO, y un binario se penaliza por el divisor de riesgo terminal, no se premia por el numerador. WhatsApp sigue sin monetizar cinco anos despues: opcionalidad no ejercida que no se debe pagar.</t>
+  </si>
+  <si>
+    <t>Sika. R2 Potential 11 -&gt; 10. La tesis del Drive es la mejor documentada del lote y su parte cualitativa no necesita correccion: el foso de la ESPECIFICACION es real -el prescriptor escribe el producto en el pliego y cambiarlo puede exigir una nueva homologacion, asi que el coste de cambio es regulatorio y no economico- y ademas se ensancha con la regulacion climatica. Cultura solida (promocion interna, el CEO llevaba 32 anos dentro, compromiso 86/100) y retribucion bien disenada, con el ROCE relativo pesando el 40% del incentivo largo. LO QUE BAJA POTENTIAL ES CUANTITATIVO Y DE LARGO PLAZO: la propia tesis reconoce que el crecimiento organico es bajo, y los numeros lo confirman -de 9.250 M CHF en 2021 a 11.760 en 2024 con MBCC aportando 2.100 de esos 2.500, o sea que casi todo el crecimiento de tres anos vino de una compra financiada con 2.250 M EUR de bonos-. Hoy el ROIC es del 9,6%, cerca del coste de capital, y la deuda neta 5.455 M CHF = 2,8x EBITDA, lo que limita la siguiente compra. Un consolidador que reinvierte al 9,6% no compone, administra. Contraste con la tesis: margen FCF 11,9% cumple lo esperado (9-12%), pero el EBITDA esta en 17,5% y no en el 20% previsto. AVISO: el multiplo de salida bajista de 18x es el 66% del actual, blando para un ciclico apalancado; 15x seria mas honesto.</t>
+  </si>
+  <si>
+    <t>T (R2 Financials); AH (R3 Financing Source)</t>
+  </si>
+  <si>
+    <t>Spotify. R2 Financials 13 -&gt; 15 y R3 Financing Source 2 -&gt; 4. Ha demostrado lo que tenia que demostrar: que el apalancamiento operativo existia. De perdidas estructurales a un resultado operativo de 2.653 M EUR (14,6% de margen), un FCF de 3.267 (18% de margen) y un ROIC del 24%, con 6.519 M EUR de CAJA NETA. Ya no depende de nadie para financiarse. LA LECCION QUE HAY QUE LLEVARSE AL RESTO DEL LIBRO: la tesis del Drive fijaba el caso alcista en 380 $ y la accion esta en 550,72 $; fallo en una unica variable, el margen, y ella misma la habia senalado como su punto debil (los margenes operativos me generan dudas, el apalancamiento operativo es poco visible). En negocios con base de costes fija grande y margen bruto creciente, el apalancamiento operativo NO es lineal: es explosivo al cruzar el umbral de rentabilidad. Mismo error que en Airbnb (11% proyectado, 20,8% real). Y es lo que puede estar pasando AHORA con SentinelOne, que acaba de cruzar a operativo no-GAAP positivo. NO se sube MOAT ni Concentration: Spotify no es dueno de lo que vende y tres discograficas pueden decidir su margen; el -2 de concentracion esta bien puesto.</t>
   </si>
 </sst>
 </file>
@@ -7079,7 +7142,7 @@
                   <c:v>7.97</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.0500000000000007</c:v>
+                  <c:v>8.1300000000000008</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>7.92</c:v>
@@ -7154,7 +7217,7 @@
                   <c:v>9.4174490275463096E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.10741088468091919</c:v>
+                  <c:v>7.8247362813344878E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>-0.11087272348127619</c:v>
@@ -16908,7 +16971,7 @@
         <v>19</v>
       </c>
       <c r="V8" s="90">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="W8" s="90">
         <v>10</v>
@@ -16927,11 +16990,11 @@
       </c>
       <c r="AB8" s="15">
         <f t="shared" si="3"/>
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AC8" s="16">
         <f t="shared" si="4"/>
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD8" s="90">
         <v>15</v>
@@ -16967,7 +17030,7 @@
       </c>
       <c r="AN8" s="17">
         <f t="shared" si="7"/>
-        <v>8.0500000000000007</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="AO8" s="18" t="s">
         <v>78</v>
@@ -18500,7 +18563,7 @@
         <v>6.5</v>
       </c>
       <c r="L15" s="91">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M15" s="91">
         <v>1</v>
@@ -18519,11 +18582,11 @@
       </c>
       <c r="R15" s="26">
         <f t="shared" si="1"/>
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="S15" s="16">
         <f t="shared" si="2"/>
-        <v>7.19</v>
+        <v>6.88</v>
       </c>
       <c r="T15" s="91">
         <v>16</v>
@@ -18558,7 +18621,7 @@
         <v>7.7</v>
       </c>
       <c r="AD15" s="91">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE15" s="91">
         <v>-1</v>
@@ -18583,11 +18646,11 @@
       </c>
       <c r="AL15" s="26">
         <f t="shared" si="5"/>
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AM15" s="16">
         <f t="shared" si="6"/>
-        <v>8.14</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="AN15" s="17">
         <f t="shared" si="7"/>
@@ -18653,11 +18716,11 @@
         <v>3.9994258350512402E-2</v>
       </c>
       <c r="BF15">
-        <v>12406.6</v>
+        <v>10832</v>
       </c>
       <c r="BG15" s="23">
         <f t="shared" si="16"/>
-        <v>0.11999484630306445</v>
+        <v>9.0001758126663889E-2</v>
       </c>
       <c r="BH15" s="24">
         <v>16</v>
@@ -18671,7 +18734,7 @@
       </c>
       <c r="BK15" s="25">
         <f ca="1">(BF15*BI15+$AP15-$AQ15)/$H15</f>
-        <v>97.065184050063991</v>
+        <v>84.93986495765327</v>
       </c>
       <c r="BL15" s="23">
         <f t="shared" ca="1" si="18"/>
@@ -18679,7 +18742,7 @@
       </c>
       <c r="BM15" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.10741088468091919</v>
+        <v>7.8247362813344878E-2</v>
       </c>
       <c r="BN15" s="96" t="s">
         <v>678</v>
@@ -20153,7 +20216,7 @@
         <v>14</v>
       </c>
       <c r="U22" s="90">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V22" s="90">
         <v>14</v>
@@ -20175,11 +20238,11 @@
       </c>
       <c r="AB22" s="15">
         <f t="shared" si="3"/>
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AC22" s="16">
         <f t="shared" si="4"/>
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AD22" s="90">
         <v>12</v>
@@ -20215,7 +20278,7 @@
       </c>
       <c r="AN22" s="17">
         <f t="shared" si="7"/>
-        <v>7.26</v>
+        <v>7.3</v>
       </c>
       <c r="AO22" s="18" t="s">
         <v>78</v>
@@ -21580,13 +21643,13 @@
         <v>-3</v>
       </c>
       <c r="AF28" s="90">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG28" s="90">
         <v>12</v>
       </c>
       <c r="AH28" s="90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI28" s="90">
         <v>8</v>
@@ -21599,15 +21662,15 @@
       </c>
       <c r="AL28" s="15">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AM28" s="16">
         <f t="shared" si="6"/>
-        <v>6.86</v>
+        <v>6.43</v>
       </c>
       <c r="AN28" s="17">
         <f t="shared" si="7"/>
-        <v>6.66</v>
+        <v>6.48</v>
       </c>
       <c r="AO28" s="18" t="s">
         <v>78</v>
@@ -22508,7 +22571,7 @@
         <v>-4</v>
       </c>
       <c r="AF32" s="90">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG32" s="90">
         <v>11</v>
@@ -22527,15 +22590,15 @@
       </c>
       <c r="AL32" s="15">
         <f t="shared" si="5"/>
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM32" s="16">
         <f t="shared" si="6"/>
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="AN32" s="17">
         <f t="shared" si="7"/>
-        <v>6.6</v>
+        <v>6.54</v>
       </c>
       <c r="AO32" s="18" t="s">
         <v>78</v>
@@ -24557,7 +24620,7 @@
         <v>4.38</v>
       </c>
       <c r="T41" s="91">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="U41" s="91">
         <v>11</v>
@@ -24582,11 +24645,11 @@
       </c>
       <c r="AB41" s="26">
         <f t="shared" si="30"/>
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AC41" s="16">
         <f t="shared" si="31"/>
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="AD41" s="91">
         <v>10</v>
@@ -24601,7 +24664,7 @@
         <v>9</v>
       </c>
       <c r="AH41" s="91">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI41" s="91">
         <v>8</v>
@@ -24614,15 +24677,15 @@
       </c>
       <c r="AL41" s="26">
         <f t="shared" si="32"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AM41" s="16">
         <f t="shared" si="33"/>
-        <v>5.29</v>
+        <v>5.57</v>
       </c>
       <c r="AN41" s="17">
         <f t="shared" si="34"/>
-        <v>5.35</v>
+        <v>5.54</v>
       </c>
       <c r="AO41" s="18" t="s">
         <v>87</v>
@@ -25491,7 +25554,7 @@
         <v>13</v>
       </c>
       <c r="V45" s="91">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W45" s="91">
         <v>9</v>
@@ -25510,11 +25573,11 @@
       </c>
       <c r="AB45" s="26">
         <f t="shared" si="30"/>
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC45" s="16">
         <f t="shared" si="31"/>
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AD45" s="91">
         <v>12</v>
@@ -25550,7 +25613,7 @@
       </c>
       <c r="AN45" s="17">
         <f t="shared" si="34"/>
-        <v>5.51</v>
+        <v>5.47</v>
       </c>
       <c r="AO45" s="18" t="s">
         <v>130</v>
@@ -27619,10 +27682,10 @@
         <v>7</v>
       </c>
       <c r="AH54" s="90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI54" s="90">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AJ54" s="90">
         <v>9</v>
@@ -27632,15 +27695,15 @@
       </c>
       <c r="AL54" s="15">
         <f t="shared" si="32"/>
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AM54" s="16">
         <f t="shared" si="33"/>
-        <v>2.86</v>
+        <v>3.71</v>
       </c>
       <c r="AN54" s="17">
         <f t="shared" si="34"/>
-        <v>3.7</v>
+        <v>4.04</v>
       </c>
       <c r="AO54" s="18" t="s">
         <v>78</v>
@@ -32970,7 +33033,7 @@
       </c>
       <c r="D12" s="47">
         <f>'Watchlist Ratings'!AC8</f>
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="E12" s="47">
         <f>'Watchlist Ratings'!AM8</f>
@@ -32978,7 +33041,7 @@
       </c>
       <c r="F12" s="47">
         <f>'Watchlist Ratings'!AN8</f>
-        <v>8.0500000000000007</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="G12" s="48">
         <f>'Watchlist Ratings'!K8</f>
@@ -33002,7 +33065,7 @@
       </c>
       <c r="P12" s="37">
         <f>'Watchlist Ratings'!AN8</f>
-        <v>8.0500000000000007</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="Q12" s="23">
         <f ca="1">'Watchlist Ratings'!BM8</f>
@@ -33886,7 +33949,7 @@
       </c>
       <c r="C19" s="41">
         <f>'Watchlist Ratings'!S15</f>
-        <v>7.19</v>
+        <v>6.88</v>
       </c>
       <c r="D19" s="41">
         <f>'Watchlist Ratings'!AC15</f>
@@ -33894,7 +33957,7 @@
       </c>
       <c r="E19" s="41">
         <f>'Watchlist Ratings'!AM15</f>
-        <v>8.14</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="F19" s="41">
         <f>'Watchlist Ratings'!AN15</f>
@@ -33906,7 +33969,7 @@
       </c>
       <c r="H19" s="42">
         <f>'Watchlist Ratings'!L15</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I19" s="43">
         <f>'Watchlist Ratings'!BC15</f>
@@ -33926,7 +33989,7 @@
       </c>
       <c r="Q19" s="23">
         <f ca="1">'Watchlist Ratings'!BM15</f>
-        <v>0.10741088468091919</v>
+        <v>7.8247362813344878E-2</v>
       </c>
       <c r="V19" t="str">
         <f ca="1">'Watchlist Ratings'!B15</f>
@@ -33938,7 +34001,7 @@
       </c>
       <c r="X19" s="38">
         <f>'Watchlist Ratings'!L15</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Y19" t="str">
         <f ca="1">'Watchlist Ratings'!B15</f>
@@ -33958,7 +34021,7 @@
       </c>
       <c r="AC19">
         <f ca="1">'Watchlist Ratings'!BM15</f>
-        <v>0.10741088468091919</v>
+        <v>7.8247362813344878E-2</v>
       </c>
       <c r="AS19" t="s">
         <v>258</v>
@@ -34300,7 +34363,7 @@
       </c>
       <c r="P26" s="37">
         <f>'Watchlist Ratings'!AN22</f>
-        <v>7.26</v>
+        <v>7.3</v>
       </c>
       <c r="Q26">
         <f ca="1">'Watchlist Ratings'!BM22</f>
@@ -35911,7 +35974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E228"/>
+  <dimension ref="A1:E238"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -39796,6 +39859,176 @@
         <v>815</v>
       </c>
     </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>336</v>
+      </c>
+      <c r="B229">
+        <v>46259</v>
+      </c>
+      <c r="C229" t="s">
+        <v>816</v>
+      </c>
+      <c r="D229" t="s">
+        <v>817</v>
+      </c>
+      <c r="E229" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>255</v>
+      </c>
+      <c r="B230">
+        <v>46259</v>
+      </c>
+      <c r="C230" t="s">
+        <v>666</v>
+      </c>
+      <c r="D230" t="s">
+        <v>819</v>
+      </c>
+      <c r="E230" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>273</v>
+      </c>
+      <c r="B231">
+        <v>46259</v>
+      </c>
+      <c r="C231" t="s">
+        <v>821</v>
+      </c>
+      <c r="D231" t="s">
+        <v>819</v>
+      </c>
+      <c r="E231" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>453</v>
+      </c>
+      <c r="B232">
+        <v>46259</v>
+      </c>
+      <c r="C232" t="s">
+        <v>823</v>
+      </c>
+      <c r="D232" t="s">
+        <v>824</v>
+      </c>
+      <c r="E232" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>276</v>
+      </c>
+      <c r="B233">
+        <v>46259</v>
+      </c>
+      <c r="C233" t="s">
+        <v>826</v>
+      </c>
+      <c r="D233" t="s">
+        <v>819</v>
+      </c>
+      <c r="E233" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>260</v>
+      </c>
+      <c r="B234">
+        <v>46259</v>
+      </c>
+      <c r="C234" t="s">
+        <v>828</v>
+      </c>
+      <c r="D234" t="s">
+        <v>819</v>
+      </c>
+      <c r="E234" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>376</v>
+      </c>
+      <c r="B235">
+        <v>46259</v>
+      </c>
+      <c r="C235" t="s">
+        <v>830</v>
+      </c>
+      <c r="D235" t="s">
+        <v>819</v>
+      </c>
+      <c r="E235" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>372</v>
+      </c>
+      <c r="B236">
+        <v>46259</v>
+      </c>
+      <c r="C236" t="s">
+        <v>832</v>
+      </c>
+      <c r="D236" t="s">
+        <v>819</v>
+      </c>
+      <c r="E236" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>469</v>
+      </c>
+      <c r="B237">
+        <v>46259</v>
+      </c>
+      <c r="C237" t="s">
+        <v>666</v>
+      </c>
+      <c r="D237" t="s">
+        <v>819</v>
+      </c>
+      <c r="E237" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>380</v>
+      </c>
+      <c r="B238">
+        <v>46259</v>
+      </c>
+      <c r="C238" t="s">
+        <v>835</v>
+      </c>
+      <c r="D238" t="s">
+        <v>819</v>
+      </c>
+      <c r="E238" t="s">
+        <v>836</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/watchlist_ratings.xlsx
+++ b/data/raw/watchlist_ratings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roger\Cosas Roger\BOLSA E INVERSIÓN\repos\watchlist-dashboard\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C663877-819D-4BC2-B98A-6D13BAD1E559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E93E5ED-46D3-4967-8D6C-E86A7D32171C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2483,7 +2483,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1881" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="878">
   <si>
     <t>WATCHLIST RATINGS — JP Morgan Equity Research Framework | Long-Term Investor View</t>
   </si>
@@ -5124,6 +5124,36 @@
   </si>
   <si>
     <t>Meta. R3 Terminal Risk -5 -&gt; -6. Al hacer el deep dive se anoto que la asimetria de 10,5:1 -la mas alta del libro- no es una senal de compra sino de resultado BINARIO, y que en el framework de sizing un binario se penaliza por el DIVISOR de riesgo terminal, no se premia por el numerador de asimetria. Esto lo aplica. Los hechos: capex de 89.320 M$, el 39,1% de las ventas y casi cuatro veces el D&amp;A, financiado con deuda neta positiva por primera vez en su historia (112.320 de deuda contra 90.260 de caja). Ademas Meta no controla el sistema operativo por el que llega a sus usuarios - Apple ya demostro en 2021 que puede cambiar las reglas y costarle decenas de miles de millones, riesgo que Alphabet no tiene porque se compro el suyo con Android.</t>
+  </si>
+  <si>
+    <t>Correccion del capital empleado</t>
+  </si>
+  <si>
+    <t>KKR. AZ de 80.000 a 34.500 M$. Los 80.000 eran una cifra de relleno sin base publicada y el ROIC resultante -6,5%- no media nada, porque el balance consolidado de KKR incluye los fondos que gestiona y la aseguradora Global Atlantic, o sea dinero de TERCEROS. Se sustituye por el VALOR CONTABLE publicado por la compania a 30-jun-2026: 34.500 M$, que incluye 5.300 M$ de caja e inversiones a corto. Es el capital del accionista, que es el denominador correcto para una gestora. El ROIC pasa del 6,5% al 15,0%, que si es una cifra interpretable. AVISO QUE SIGUE ABIERTO: la deuda de 56.164 M$ que entra en el EV es sobre todo pasivo de la aseguradora respaldado por su cartera, no deuda del accionista, asi que el EV/FCF de esta fila sigue estando inflado. Lo honesto para KKR es el multiplo sobre beneficio ajustado: 5.000 M$ contra 96.846 de capitalizacion, 19,4 veces.</t>
+  </si>
+  <si>
+    <t>Brookfield. AZ de 90.000 a 42.483 M$. Mismo problema y misma solucion que en KKR: los 90.000 no tenian base publicada. El balance de Brookfield a 30-jun-2026 trae 525.515 M$ de activo y 166.636 de patrimonio total, pero de ese patrimonio solo 42.483 M$ son CAPITAL COMUN DE LA MATRIZ; los otros 120.100 son minoritarios de las filiales consolidadas, o sea dinero que no es del accionista de BN. Con el capital comun el ROIC pasa del 6,3% al 13,4% sobre el DE antes de realizaciones de 5.700 M$, que es coherente con lo que la propia compania comunica. Se completa asi la fila que quedo a medias el 25-ago cuando se pasaron NOPAT y EBITDA a metricas non-GAAP.</t>
+  </si>
+  <si>
+    <t>Ninguno - verificacion</t>
+  </si>
+  <si>
+    <t>Verificacion del aviso sobre la flotacion</t>
+  </si>
+  <si>
+    <t>Airbnb. SE COMPRUEBA Y NO HAY QUE CAMBIAR NADA. El 25-ago se aviso de que parte de los 12.069 M$ de caja podian ser fondos de anfitriones pendientes de pago -flotacion, no caja propia- y de que eso afectaria al EV. Revisado el balance a 30-jun-2026: los 12.069 son caja y equivalentes (6.821) mas inversiones a corto (5.248), que son recursos PROPIOS de Airbnb. Los fondos de clientes van en lineas separadas del balance -fondos a cobrar y a pagar por cuenta de clientes- que en la presentacion normalizada quedan dentro de otros activos corrientes (12.308) y otros pasivos corrientes (13.245). El aviso era excesivamente cauteloso y queda retirado. MATIZ QUE SI ES REAL aunque no se ajusta: hay 2.831 M$ de ingresos diferidos, reservas cobradas cuya estancia aun no se ha producido. Es un pasivo genuino contra esa caja, pero es circulante negativo estructural del modelo -igual que en Costco, Inditex y Spotify- y no se neteaba en aquellas, asi que tampoco aqui.</t>
+  </si>
+  <si>
+    <t>Triple Flag. R2 Risks -11 -&gt; -10. La compra del flujo del 5,5% de oro sobre Ravenswood por 440 M$, la mayor de su historia, sube la guia de 2026 a 100.000-110.000 GEO y la perspectiva de 2030 a 150.000-160.000, un +45% de volumen. Mas activos significa menos dependencia de una sola mina, que es el riesgo estructural de una compania de regalias -por eso Customers sigue en 6 sobre 10-. FLYWHEEL: paga por adelantado y recibe metal o dinero durante decadas sin poner un euro mas; no paga costes operativos, ni inflacion de salarios mineros, ni capex de sostenimiento, ni rehabilitacion. Margen bruto del 80%. Y lo que casi nadie valora: si la minera encuentra mas mineral, la regalia lo cubre GRATIS - compra opcionalidad geologica sin pagarla. LO QUE HAY QUE TENER CLARO: es una apuesta apalancada al precio del oro sin admitirlo. Los ingresos pasaron de unos 310 M$ en 2025 a 489 LTM y ese salto es del metal, no del negocio. Por eso el caso bajista asume el FCF CAYENDO un 3,5% anual y el alcista del 9% es solo VOLUMEN, sin sumarle subida de oro. EXCEPCION METODOLOGICA vigente: la regla de FCF normalizado se dispara mecanicamente pero no se aplica, porque ese capex son compras de flujos -M&amp;A de crecimiento- y en una royalty el capex de sostenimiento es cero.</t>
+  </si>
+  <si>
+    <t>AG (R3 Capital Allocation)</t>
+  </si>
+  <si>
+    <t>Campari. R3 Capital Allocation 9 -&gt; 8. El ROIC es del 5,8%, muy por debajo del coste de capital, con 7.090 M EUR de capital empleado llenos de marcas pagadas a multiplos de mercado -Courvoisier en 2024 por mas de mil millones es el ejemplo mas caro- y una deuda neta de 3,2x EBITDA, la mas alta del libro entre las companias de calidad media o alta. Y la propia estrategia lo reconoce: estan VENDIENDO marcas no prioritarias (Bisquit &amp; Dubouche y Cabo Wabo a Cobblestone) y el consejero delegado dice que la simplificacion de cartera termina en 2027. Es una compania deshaciendo compras. EL HECHO DE LARGO PLAZO MAS IMPORTANTE: Aperol crecio un 3,3% organico en el 1S2026 y el grupo un 2,7%, con guia del 3%. Aperol venia de una decada de doble digito. La joya de la corona ha entrado en crecimiento de un digito medio-bajo. Lo que si funciona es el agave: Espolon +8,2% y Sarti Rosa +8,8%. FLYWHEEL: no vende una bebida, vende un RITUAL con nombre -el Spritz tiene copa, proporcion y momento del dia propios- que se aprende viendo a otros en una terraza, y que el bar adopta porque se hace en diez segundos y se cobra como coctel. El foso no es el gusto del consumidor: es el hueco en la carta y la mano del camarero. Y a diferencia de Lotus, el ritual SI tiene sustituto: el siguiente ritual.</t>
+  </si>
+  <si>
+    <t>Check Point. R2 Potential 8 -&gt; 9. Tres hechos nuevos que apuntan en la misma direccion: Gil Shwed dejo de ser consejero delegado en 2024 tras TREINTA Y UN anos y Nadav Zafrir -cofundador de Team8, ex Unidad 8200- lleva el timon; estan contratando cientos de comerciales para preparar un crecimiento mas fuerte en 2027, que es exactamente lo que la tesis bajista decia que nunca harian, gastar margen para comprar crecimiento; y correo, gestion de exposicion y seguridad de IA superaron conjuntamente el 40% de crecimiento en ARR en el Q2 2026. EL FLYWHEEL QUE FUNCIONA es la renovacion: las politicas de seguridad se acumulan durante anos, nadie sabe ya por que esta cada regla, y migrar significa reescribir y auditar la politica de la compania entera. EL QUE SE PARO es el paso cero, ganar clientes nuevos: el sector crece a doble digito y Check Point crecio un 5% en el Q1. Palo Alto y CrowdStrike gastaron el dinero en fuerza comercial y producto; Check Point lo gasto en recomprar acciones. LO QUE HACE INTERESANTE LA FILA: a 11,6x FCF es la mas barata del libro entre las rentables -mediana 26,7x- con un margen de caja libre del 39,9% y CONTABILIDAD LIMPIA, sin la discusion GAAP contra non-GAAP de Cloudflare, CrowdStrike o Zscaler. No hace falta que el despertar funcione para no perder dinero. El multiplo de salida bajista de 6x asume que dentro de cinco anos el mercado paga seis veces el FCF, precio de liquidacion ordenada: para una compania que pierde cuota es el escenario correcto y hay que dejarlo asi.</t>
   </si>
 </sst>
 </file>
@@ -7303,34 +7333,34 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.21440325563515295</c:v>
+                  <c:v>0.21485168962191081</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.12530205264345784</c:v>
+                  <c:v>0.12564775439289733</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0.21440249613313545</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.21981528931254024</c:v>
+                  <c:v>0.21954785350683115</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.5666007165993152E-2</c:v>
+                  <c:v>8.5789611564482282E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.19992256658649676</c:v>
+                  <c:v>0.20036217929528854</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0.12636883264119847</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.26082680899108857</c:v>
+                  <c:v>0.26060125856359373</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.2805303231882901E-2</c:v>
+                  <c:v>2.2838362358715614E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.1137563839946405</c:v>
+                  <c:v>0.1144404281327791</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>9.2008300037514035E-2</c:v>
@@ -7345,7 +7375,7 @@
                   <c:v>9.0703083820528052E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1098005163465392</c:v>
+                  <c:v>0.11022293283992024</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9394,14 +9424,14 @@
     <v>2007</v>
     <v>240.78</v>
     <v>0.9466</v>
-    <v>-7.0000000000000007E-2</v>
-    <v>-2.8370000000000001E-4</v>
-    <v>40076386543</v>
+    <v>-0.52500000000000002</v>
+    <v>-2.127E-3</v>
+    <v>40002474841</v>
     <v>246.78</v>
     <v>Veeva Systems Inc. Es un proveedor de soluciones en la nube para la industria global de las ciencias de la vida. Ofrece software SPAN Cloud, datos y consultoría empresarial, y está diseñado para satisfacer las necesidades de sus clientes y las funciones estratégicas de negocio, desde la investigación y el desarrollo (I+D) hasta la comercialización. Sus cuatro categorías de productos incluyen Veeva Development Cloud, Veeva Quality Cloud, Veeva Commercial Cloud y Veeva Data Cloud. Veeva Development Cloud incluye paquetes de aplicaciones para las funciones clínicas, regulatorias y de seguridad de las empresas de ciencias de la vida, todo construido en su plataforma Veeva Vault. Veeva Quality Cloud unifica aplicaciones, procesos y socios en las soluciones de gestión de contenido, capacitación, gestión de calidad, garantía y laboratorio de control en la plataforma Veeva Vault. Veeva Commercial Cloud es una categoría de producto compuesta por soluciones de software y análisis. Veeva Data Cloud es una plataforma de datos compuesta por datos de referencia conectados, datos profundos y datos de transacciones.</v>
     <v>7928</v>
     <v>XNYS</v>
-    <v>46260.660590856249</v>
+    <v>46260.681129305471</v>
     <v>New York Stock Exchange</v>
     <v>0</v>
     <v>247.7</v>
@@ -9411,14 +9441,14 @@
     <v>USD</v>
     <v>VEEVA SYSTEMS INC.</v>
     <v>VEEVA SYSTEMS INC.</v>
-    <v>43.644599999999997</v>
-    <v>246.71</v>
+    <v>43.564100000000003</v>
+    <v>246.255</v>
     <v>Healthcare Equipment &amp; Supplies</v>
     <v>4280 Hacienda Drive, PLEASANTON, CA, 94588 US</v>
     <v>VEEV</v>
     <v>Acciones</v>
     <v>VEEVA SYSTEMS INC. (XNYS:VEEV)</v>
-    <v>432053</v>
+    <v>482046</v>
     <v>1667135</v>
   </rv>
   <rv s="2">
@@ -9466,14 +9496,14 @@
     <v>1993</v>
     <v>488</v>
     <v>1.1033999999999999</v>
-    <v>3.5901000000000001</v>
-    <v>7.3009999999999993E-3</v>
-    <v>3677873181054</v>
+    <v>2.83</v>
+    <v>5.7549999999999997E-3</v>
+    <v>3672229024300</v>
     <v>491.71</v>
     <v>Microsoft Corporation es una empresa de tecnología. La Compañía desarrolla y apoya software, servicios, dispositivos y soluciones. Los segmentos de la compañía incluyen Productividad y Procesos de Negocio, Nube Inteligente y más Informática Personal. El segmento Productividad y Procesos de Negocio está formado por productos y servicios en su cartera de servicios de productividad, comunicación e información. Este segmento comprende principalmente: Office Commercial, Office Consumer, LinkedIn y soluciones empresariales de Dynamics. El segmento de la nube inteligente consiste en productos de servidor y servicios en la nube, incluidos Azure y otros servicios en la nube, SQL Server, Windows Server, Visual Studio, System Center y Windows Server. licencias de acceso de clientes (CAL) relacionadas, Nuance y GitHub; y Servicios empresariales, incluidos los servicios de soporte empresarial, las soluciones de la industria y los servicios profesionales de Nuance. El segmento más personal de Computación comprende principalmente Windows, dispositivos, juegos y publicidad de búsqueda y noticias.</v>
     <v>223000</v>
     <v>XNAS</v>
-    <v>46260.660629096878</v>
+    <v>46260.681203876564</v>
     <v>6</v>
     <v>Nasdaq Stock Market</v>
     <v>7</v>
@@ -9484,14 +9514,14 @@
     <v>USD</v>
     <v>MICROSOFT CORPORATION</v>
     <v>MICROSOFT CORPORATION</v>
-    <v>27.598400000000002</v>
-    <v>495.30009999999999</v>
+    <v>27.556000000000001</v>
+    <v>494.54</v>
     <v>Software &amp; IT Services</v>
     <v>One Microsoft Way, REDMOND, WA, 98052 US</v>
     <v>MSFT</v>
     <v>Acciones</v>
     <v>MICROSOFT CORPORATION (XNAS:MSFT)</v>
-    <v>8787532</v>
+    <v>9412988</v>
     <v>34238717</v>
   </rv>
   <rv s="2">
@@ -9526,7 +9556,7 @@
     <v>Adyen NV, antes Adyen BV, es un proveedor de soluciones de pago por móvil, en línea y en punto de venta (TPV) con sede en los Países Bajos. Opera una plataforma online que permite a los comerciantes aceptar pagos a nivel internacional y desde todos los canales de venta, como tiendas online, pagos móviles desde aplicaciones y sitios web, y puntos de venta, como mostradores, terminales móviles, tabletas y cajas registradoras, entre otros. La plataforma cubre toda la cadena de pagos, incluidos los procesos técnicos, contractuales, de conciliación y de liquidación. La plataforma está disponible en forma de páginas de pago listas para usar (HPP), interfaz de programación de aplicaciones (API) y solución de cifrado del lado del cliente (EE). Entre los clientes de la Empresa se encuentran Mango, KLM, Netflix, Superdry, Uber, Groupon y Crocs, entre otros. Tiene oficinas en los Países Bajos, el Reino Unido, Francia, Alemania, Bélgica, Brasil, China, Australia, México, Singapur, España, Suecia y Estados Unidos.</v>
     <v>5020</v>
     <v>XAMS</v>
-    <v>46260.649410693753</v>
+    <v>46260.666666666664</v>
     <v>Euronext Amsterdam</v>
     <v>10</v>
     <v>1082</v>
@@ -9543,7 +9573,7 @@
     <v>ADYEN</v>
     <v>Acciones</v>
     <v>Adyen N.V. (XAMS:ADYEN)</v>
-    <v>99960</v>
+    <v>100021</v>
     <v>189000</v>
   </rv>
   <rv s="2">
@@ -9571,14 +9601,14 @@
     <v>2005</v>
     <v>42.06</v>
     <v>1.5449999999999999</v>
-    <v>-0.185</v>
-    <v>-4.3920000000000001E-3</v>
-    <v>102821055525</v>
+    <v>-0.13900000000000001</v>
+    <v>-3.3E-3</v>
+    <v>102933843615</v>
     <v>42.12</v>
     <v>Brookfield Corporation es una firma de inversión global con sede en Canadá enfocada en la construcción de riqueza a largo plazo para instituciones e individuos de todo el mundo. La Compañía tiene tres negocios principales: Gestión de activos alternativos, Soluciones de patrimonio y sus negocios operativos, que se encuentran en energía renovable, infraestructura, servicios empresariales e industriales, y bienes raíces. Su negocio de gestión de activos incluye la gestión de fondos privados a largo plazo, estrategias perpetuas y estrategias líquidas en nombre de sus inversores y de sí mismo. El negocio de Wealth Solutions de la Compañía incluye su participación contabilizada en Brookfield Wealth Solutions Ltd. Su negocio de energía renovable y transición incluye la propiedad, operación y desarrollo de activos de generación de energía solar hidroeléctrica, eólica, a escala de servicios públicos, energía distribuida y soluciones sostenibles. El negocio de infraestructura de la Compañía incluye la propiedad, operación y desarrollo de servicios públicos, transporte, midstream y activos de datos.</v>
     <v>250000</v>
     <v>XNYS</v>
-    <v>46260.660642140625</v>
+    <v>46260.681137233594</v>
     <v>New York Stock Exchange</v>
     <v>13</v>
     <v>42.23</v>
@@ -9588,14 +9618,14 @@
     <v>USD</v>
     <v>Brookfield Corporation</v>
     <v>Brookfield Corporation</v>
-    <v>82.000399999999999</v>
-    <v>41.935000000000002</v>
+    <v>82.090299999999999</v>
+    <v>41.981000000000002</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>Brookfield Place, 181 Bay St, Ste 100, Po Box 762, TORONTO, ON, M5J 2T3 CA</v>
     <v>BN</v>
     <v>Acciones</v>
     <v>Brookfield Corporation (XNYS:BN)</v>
-    <v>803460</v>
+    <v>899795</v>
     <v>4289245</v>
   </rv>
   <rv s="2">
@@ -9623,14 +9653,14 @@
     <v>1987</v>
     <v>960.39</v>
     <v>0.8649</v>
-    <v>-1.4145000000000001</v>
-    <v>-1.4729999999999999E-3</v>
-    <v>425116782025</v>
+    <v>-1.96</v>
+    <v>-2.042E-3</v>
+    <v>424874864340</v>
     <v>960.01</v>
     <v>Costco Wholesale Corporation (Costco) opera almacenes de membresía y sitios de comercio electrónico que ofrecen una selección de productos de marca nacional y de marca privada en una amplia gama de categorías. La Compañía compra la mayoría de sus mercancías directamente a los proveedores y la dirige a puntos de consolidación de cross-docking (depósitos) o directamente a sus almacenes. Opera 891 almacenes, incluyendo 614 en los Estados Unidos y Puerto Rico, 108 en Canadá, 40 en México, 35 en Japón, 29 en el Reino Unido, 19 en Corea, 15 en Australia, 14 en Taiwán, siete en China, y más. cinco en España, dos en Francia, y uno en Islandia, Nueva Zelanda y Suecia. También opera sitios de comercio electrónico en los Estados Unidos, Canadá, el Reino Unido, México, Corea, Taiwán, Japón y Australia. La Compañía ofrece una amplia selección de mercancías, además de la conveniencia de departamentos especializados y servicios exclusivos para miembros.</v>
     <v>341000</v>
     <v>XNAS</v>
-    <v>46260.660623251562</v>
+    <v>46260.681188853909</v>
     <v>Nasdaq Stock Market</v>
     <v>16</v>
     <v>964.45</v>
@@ -9640,14 +9670,14 @@
     <v>USD</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
     <v>COSTCO WHOLESALE CORPORATION</v>
-    <v>48.213799999999999</v>
-    <v>958.59550000000002</v>
+    <v>48.186300000000003</v>
+    <v>958.05</v>
     <v>Diversified Retail</v>
     <v>999 Lake Dr, ISSAQUAH, WA, 98027- US</v>
     <v>COST</v>
     <v>Acciones</v>
     <v>COSTCO WHOLESALE CORPORATION (XNAS:COST)</v>
-    <v>306837</v>
+    <v>343595</v>
     <v>1841810</v>
   </rv>
   <rv s="2">
@@ -9675,14 +9705,14 @@
     <v>2023</v>
     <v>76.19</v>
     <v>0.18970000000000001</v>
-    <v>-1.01</v>
-    <v>-1.3028999999999999E-2</v>
+    <v>-1.1499999999999999</v>
+    <v>-1.4835000000000001E-2</v>
     <v>9188366000</v>
     <v>77.52</v>
     <v>Descartes Systems Group Inc. Se centra en los procesos de negocio de logística y gestión de la cadena de suministro. Proporciona soluciones de software como servicio (SaaS) bajo demanda enfocadas en mejorar la productividad, seguridad y sostenibilidad de las empresas con un uso intensivo de logística. Permite a los clientes utilizar sus soluciones modulares SaaS para enrutar, rastrear y ayudar a mejorar la seguridad y el cumplimiento de los recursos de entrega; planificar, asignar y ejecutar envíos; clasificar, auditar y pagar facturas de transporte; acceder a datos comerciales globales; archivar documentos aduaneros y de seguridad para importaciones y exportaciones; y completar otros procesos logísticos participando en la comunidad logística multimodal. Sus soluciones incluyen soluciones basadas en la nube y consisten en conectividad y mensajería de servicios B2B, sistemas empresariales de corredores y forwarder, inteligencia comercial global, cumplimiento normativo, envío de comercio electrónico, gestión de transporte y enrutamiento. También proporciona software de declaración de aduanas para proveedores de servicios logísticos y expedidores.</v>
     <v>2403</v>
     <v>XNAS</v>
-    <v>46260.660463367967</v>
+    <v>46260.681079339847</v>
     <v>Nasdaq Stock Market</v>
     <v>19</v>
     <v>77.709999999999994</v>
@@ -9692,14 +9722,14 @@
     <v>USD</v>
     <v>The Descartes Systems Group Inc.</v>
     <v>The Descartes Systems Group Inc.</v>
-    <v>38.051400000000001</v>
-    <v>76.510000000000005</v>
+    <v>37.9818</v>
+    <v>76.37</v>
     <v>Software &amp; IT Services</v>
     <v>120 Randall Drive, WATERLOO, ON, N2V 1C6 CA</v>
     <v>DSGX</v>
     <v>Acciones</v>
     <v>The Descartes Systems Group Inc. (XNAS:DSGX)</v>
-    <v>99391</v>
+    <v>106697</v>
     <v>473944</v>
   </rv>
   <rv s="2">
@@ -9734,7 +9764,7 @@
     <v>Rational AG is a Germany-based company that provides technology products for thermal food preparation for industrial and commercial kitchens. It operates through two segments: Through the RATIONAL segment, the Company offers the SelfCookingCenter 5 Senses, a steamer that works as hot air oven, stove or boiling pan. The FRIMA segment provides the complementary steamer VarioCookingCenter. The Company markets its products around the globe through a network of subsidiaries, including sales companies. It also offers related accessories, such as granite enameled containers, roasting and baking trays, grilling and roasting plates, potato bakers and muffin and timbale molds, among others.</v>
     <v>2912</v>
     <v>XFRA</v>
-    <v>46260.645833333336</v>
+    <v>46260.656944444447</v>
     <v>Deutsche Boerse AG</v>
     <v>22</v>
     <v>640</v>
@@ -9779,14 +9809,14 @@
     <v>2007</v>
     <v>161.63</v>
     <v>0.92969999999999997</v>
-    <v>-0.81</v>
-    <v>-4.8089999999999999E-3</v>
-    <v>27104129295</v>
+    <v>-0.66</v>
+    <v>-3.9190000000000006E-3</v>
+    <v>27128385720</v>
     <v>168.42</v>
     <v>Zscaler, Inc. Es una compañía de seguridad en la nube. La Compañía ha desarrollado una plataforma que incorpora funcionalidades de seguridad básicas necesarias para permitir un acceso rápido y seguro a los recursos de la nube basado en la identidad, el contexto y las políticas de una organización. Su plataforma Zscaler Zero Trust Exchange protege a miles de clientes de ciberataques y pérdida de datos conectando de forma segura a usuarios, dispositivos y aplicaciones en cualquier ubicación. Su solución es una plataforma en la nube distribuida, multiusuario y diseñada específicamente que incorpora la funcionalidad de seguridad necesaria para permitir que los usuarios, aplicaciones y dispositivos utilicen de manera segura y eficiente aplicaciones y servicios autorizados basados en las políticas de negocio de una organización. Ofrece sus soluciones utilizando un modelo de negocio de software como servicio (SaaS) y vende suscripciones a los clientes para acceder a su plataforma en la nube, junto con los servicios de soporte relacionados. Ofrece una plataforma de seguridad que combina su plataforma con operaciones de seguridad automatizadas.</v>
     <v>7923</v>
     <v>XNAS</v>
-    <v>46260.660578923438</v>
+    <v>46260.681165439062</v>
     <v>Nasdaq Stock Market</v>
     <v>25</v>
     <v>169.87</v>
@@ -9797,13 +9827,13 @@
     <v>ZSCALER, INC.</v>
     <v>ZSCALER, INC.</v>
     <v>0</v>
-    <v>167.61</v>
+    <v>167.76</v>
     <v>Software &amp; IT Services</v>
     <v>120 Holger Way, SAN JOSE, CA, 95134 US</v>
     <v>ZS</v>
     <v>Acciones</v>
     <v>ZSCALER, INC. (XNAS:ZS)</v>
-    <v>894484</v>
+    <v>958642</v>
     <v>2149269</v>
   </rv>
   <rv s="2">
@@ -9838,7 +9868,7 @@
     <v>Nintendo Co Ltd es una empresa con sede en Japón dedicada principalmente al desarrollo, fabricación y venta de productos de entretenimiento en el campo del entretenimiento en el hogar. La Compañía desarrolla, fabrica y vende hardware y software para juegos de consola portátiles y domésticos. Sus productos principales son las consolas de juegos, que son dispositivos de entretenimiento basados en computadora, y los bienes de carácter y las cartas de juego. Las consolas de juegos son hardware y software para juegos de consola portátil y doméstica, que son desarrollados por la Compañía y sus afiliados, fabricados por la Compañía y vendidos principalmente por sus afiliados en Japón y en el extranjero. La Compañía también desarrolla negocios que utilizan su propiedad intelectual (IP), como contenido de video y aplicaciones móviles.</v>
     <v>8666</v>
     <v>XFRA</v>
-    <v>46260.649305555555</v>
+    <v>46260.670138888891</v>
     <v>Deutsche Boerse AG</v>
     <v>28</v>
     <v>48.354999999999997</v>
@@ -9883,31 +9913,31 @@
     <v>1996</v>
     <v>261.39</v>
     <v>1.4448000000000001</v>
-    <v>-1.7</v>
-    <v>-6.5120000000000004E-3</v>
-    <v>2797537361600</v>
+    <v>-2.4950000000000001</v>
+    <v>-9.5569999999999995E-3</v>
+    <v>2788962245150</v>
     <v>261.06</v>
     <v>Amazon.com, Inc. Ofrece una gama de productos y servicios a los clientes. Los productos ofrecidos a través de sus tiendas incluyen mercancía y contenido que ha adquirido para su reventa y productos ofrecidos por terceros vendedores. Los segmentos de la compañía incluyen Norteamérica, International y Amazon Web Services (AWS). Sirve a los consumidores a través de sus tiendas en línea y físicas y se centra en la selección, el precio y la conveniencia. Los clientes acceden a sus ofertas a través de sus sitios web, aplicaciones móviles, Alexa, dispositivos, streaming, y visitando físicamente sus tiendas. También fabrica y vende dispositivos electrónicos, incluyendo Kindle, tableta de fuego, Fire TV, Echo, Ring, Blink y eero, y desarrolla y produce contenido multimedia. Presta servicios a desarrolladores y empresas de todos los tamaños, incluidas empresas emergentes, agencias gubernamentales e instituciones académicas, a través de AWS, que ofrece un conjunto de servicios de tecnología bajo demanda, incluyendo computación, almacenamiento, base de datos, análisis, y el aprendizaje automático, y otros servicios.</v>
     <v>1595000</v>
     <v>XNAS</v>
-    <v>46260.660631446095</v>
+    <v>46260.681233657029</v>
     <v>Nasdaq Stock Market</v>
     <v>31</v>
     <v>262.05</v>
     <v>287.2</v>
-    <v>258.77999999999997</v>
+    <v>258.35000000000002</v>
     <v>196</v>
     <v>USD</v>
     <v>AMAZON.COM, INC.</v>
     <v>AMAZON.COM, INC.</v>
-    <v>20.8613</v>
-    <v>259.36</v>
+    <v>20.7973</v>
+    <v>258.565</v>
     <v>Diversified Retail</v>
     <v>410 Terry Avenue North, SEATTLE, WA, 98109 US</v>
     <v>AMZN</v>
     <v>Acciones</v>
     <v>AMAZON.COM, INC. (XNAS:AMZN)</v>
-    <v>7684915</v>
+    <v>8732541</v>
     <v>45189580</v>
   </rv>
   <rv s="2">
@@ -9942,7 +9972,7 @@
     <v>Schneider Electric SE es una empresa con sede en Francia. La Compañía está especializada en la transformación digital de la gestión de energía y la automatización en hogares, edificios, centros de datos, infraestructuras y entornos industriales. Ofrece soluciones que abarcan la gestión de energía de media y baja tensión, sistemas energéticos seguros y tecnologías avanzadas de automatización. Sus ofertas integradas de eficiencia combinan gestión de energía, automatización y software, respaldadas por un ecosistema abierto que permite la colaboración con socios, integradores y desarrolladores para proporcionar control operativo en tiempo real y un rendimiento mejorado. Opera en más de 115 países, incluidos Francia, Europa Occidental, Estados Unidos, Norteamérica, China, la región de Asia-Pacífico y otros mercados globales.</v>
     <v>162970</v>
     <v>XPAR</v>
-    <v>46260.649606481478</v>
+    <v>46260.666666666664</v>
     <v>Euronext Paris</v>
     <v>34</v>
     <v>301.89999999999998</v>
@@ -9959,7 +9989,7 @@
     <v>SU</v>
     <v>Acciones</v>
     <v>Schneider Electric SE (XPAR:SU)</v>
-    <v>572228</v>
+    <v>572450</v>
     <v>632080</v>
   </rv>
   <rv s="2">
@@ -9994,7 +10024,7 @@
     <v>Industria de Diseno Textil SA, conocida como Inditex SA, es una empresa con sede en España dedicada principalmente a la industria textil. Las actividades de la Compañía incluyen el diseño, confección, fabricación, distribución y venta al por menor de ropa para hombres, mujeres y niños, calzado y accesorios de moda, así como mobiliario para el hogar y productos textiles para el hogar. El negocio de la Compañía se divide en tres segmentos: Zara, que ofrece moda, con una amplia gama de productos para la ropa y el hogar; Bershka, que se dirige al segmento de consumidores jóvenes con artículos de moda y otros que comercializa ropa al por menor. La compañía opera en todo el mundo a través de ocho marcas: Zara, Pull&amp;Bear, Massimo Dutti, Bershka, Stradivarius, Oysho, Zara Hogar y Uterque. Ofrece sus productos en aproximadamente 215 mercados a través de su plataforma online y a través de sus tiendas físicas en 95 países. La empresa está controlada por Pontegadea Inversiones SL.</v>
     <v>163047</v>
     <v>BMEX</v>
-    <v>46260.650063495312</v>
+    <v>46260.666666666664</v>
     <v>Bolsas y Mercados Espanoles</v>
     <v>37</v>
     <v>58.76</v>
@@ -10046,7 +10076,7 @@
     <v>Lotus Bakeries NV is a Belgium-based company that produces and sells biscuits and cakes. Its product portfolio is divided into six product lines. The Caramelized Biscuits line includes caramelized biscuits, caramelized biscuit spread and caramelized biscuit ice cream sold under the Lotus brand. The Waffles and Galettes line consists of Liege, soft, filled, galettes and vanilla waffles also sold under the Lotus brand. The Cake Specialties line comprises frangipane, madeleine, carre confiture and Zebra in Belgium, Glaces and Enkhuizer cookies in the Netherlands, as well as Breton butter. The Gingerbread line includes the sale of gingerbread products under the Peijnenburg and Snelle Jelle brands. The Pepparkakor Biscuits line encompasses a range of traditional Swedish biscuits sold under the Annas Pepparkakor brand in Sweden, Finland, the United States, Canada as well as other countries. The Dinosaurs Biscuits line includes the sale of children’s biscuit through the Dinosaurs brand.</v>
     <v>4164</v>
     <v>XBRU</v>
-    <v>46260.649386863282</v>
+    <v>46260.666666666664</v>
     <v>Euronext Brussels</v>
     <v>40</v>
     <v>13200</v>
@@ -10098,7 +10128,7 @@
     <v>Halma plc es una compañía global de tecnología que salva vidas. Los segmentos de la Compañía incluyen Seguridad, Medio Ambiente y Salud. Segmento de seguridad ofrece productos que protegen a las personas, los activos y la infraestructura en espacios comerciales, industriales y públicos. Las soluciones de este segmento incluyen soluciones de seguridad contra incendios, tecnologías de seguridad pública, soluciones de seguridad de los trabajadores y tecnologías de seguridad de infraestructura y activos. El segmento de Medio Ambiente y Análisis proporciona soluciones que monitorean el medio ambiente y mejoran la disponibilidad de recursos naturales críticos para la vida, se utilizan en el análisis de materiales y aplicaciones optoelectrónicas. Este segmento incluye análisis óptico, sistemas de análisis y tratamiento de agua y tecnologías de monitoreo ambiental. Los segmentos de atención médica proporcionan tecnologías para ayudar a la calidad de vida de los pacientes y mejorar la calidad de la atención prestada por los proveedores de atención médica. También diseña y fabrica dispositivos de notificación, iniciación y detección de alto rendimiento.</v>
     <v>9625</v>
     <v>XLON</v>
-    <v>46260.650129039066</v>
+    <v>46260.652523842189</v>
     <v>London Stock Exchange</v>
     <v>43</v>
     <v>3662</v>
@@ -10108,14 +10138,14 @@
     <v>GBp</v>
     <v>HALMA PUBLIC LIMITED COMPANY</v>
     <v>HALMA PUBLIC LIMITED COMPANY</v>
-    <v>36.790599999999998</v>
+    <v>36.509399999999999</v>
     <v>3616</v>
     <v>Electronic Equipment &amp; Parts</v>
     <v>Misbourne Court, Rectory Way, AMERSHAM, BUCKINGHAMSHIRE, HP7 0DE GB</v>
     <v>HLMA</v>
     <v>Acciones</v>
     <v>HALMA PUBLIC LIMITED COMPANY (XLON:HLMA)</v>
-    <v>447872</v>
+    <v>495388</v>
     <v>953090</v>
   </rv>
   <rv s="2">
@@ -10143,14 +10173,14 @@
     <v>1987</v>
     <v>1120.655</v>
     <v>1.3177000000000001</v>
-    <v>-3.4950000000000001</v>
-    <v>-3.0739999999999999E-3</v>
-    <v>24484056597</v>
+    <v>-5.65</v>
+    <v>-4.9690000000000003E-3</v>
+    <v>24437513683</v>
     <v>1137.1400000000001</v>
     <v>Fair Isaac Corporation es una empresa de software de análisis aplicado. La compañía se centra en el uso de análisis predictivos y ciencia de datos para mejorar las decisiones operativas. La Compañía opera a través de dos segmentos: Puntajes y Software. El segmento de puntajes incluye las soluciones y servicios de puntaje de negocios a negocios de la Compañía que dan a sus clientes acceso a crédito predictivo y otros puntajes. Este segmento incluye sus soluciones de puntuación entre empresas y consumidores, incluidas sus ofertas de suscripción de myFICO.com. El segmento de software de la compañía incluye soluciones de análisis y gestión de decisiones preconfiguradas diseñadas para un tipo específico de necesidad o proceso de negocio, como originación de cuentas, gestión de clientes, participación de clientes, detección de fraude y marketing, así como servicios profesionales asociados. Este segmento incluye FICO Platform, una oferta de software modular diseñada para soportar casos de uso analítico y de decisión avanzados, así como software analítico y de toma de decisiones independiente.</v>
     <v>3876</v>
     <v>XNYS</v>
-    <v>46260.660463471875</v>
+    <v>46260.681167685158</v>
     <v>New York Stock Exchange</v>
     <v>46</v>
     <v>1145.893</v>
@@ -10160,14 +10190,14 @@
     <v>USD</v>
     <v>FAIR ISAAC CORPORATION</v>
     <v>FAIR ISAAC CORPORATION</v>
-    <v>32.750700000000002</v>
-    <v>1133.645</v>
+    <v>32.688400000000001</v>
+    <v>1131.49</v>
     <v>Software &amp; IT Services</v>
     <v>5 West Mendenhall, Suites 105, BOZEMAN, MT, 59715 US</v>
     <v>FICO</v>
     <v>Acciones</v>
     <v>FAIR ISAAC CORPORATION (XNYS:FICO)</v>
-    <v>36042</v>
+    <v>39694</v>
     <v>367385</v>
   </rv>
   <rv s="2">
@@ -10204,7 +10234,7 @@
     <v>Lifco AB (publ), formerly Lifco AB, is a Sweden-based conglomerate of small and medium-sized companies. The Company offers a safe haven for small and medium-sized businesses. Business concept is to acquire and develop sustainable, niche businesses with the potential to deliver sustainable earnings growth and robust cash flows. Lifco AB (publ) operates in three segments: Dental, Demolition &amp; Tools and Systems Solutions. Systems Solutions consists of a merger of those business areas which have similar economic characteristics and which do not individually meet the defined quantitative limits. The Company is involved in the distribution of dental equipment, such as denture attachments, disinfectants, saliva ejectors, bite registration and dental impression materials, bonding agents, and other consumables, as well as develops and sells medical record systems.</v>
     <v>8140</v>
     <v>XSTO</v>
-    <v>46260.645671296297</v>
+    <v>46260.666666666664</v>
     <v>NASDAQ Stockholm</v>
     <v>49</v>
     <v>320.8</v>
@@ -10257,7 +10287,7 @@
     <v>Cts Eventim AG &amp; Co KgaA is a Germany-based company. The Company provides e ticketing and live entertainment sectors and operates in the leisure events market. The Company operates in two segments namely Ticketing and Live Entertainment. The objects of the Ticketing segment are to promote, sell, broker, distribute, and market tickets for cinema, concert, theatre, art, sports and other events in Germany and abroad, using data processing and data transmission technologies. Its tickets are marketed through its network platform (eventim.net), its in-house ticketing product (eventim.inhouse), the sports ticketing product (eventim.tixx) and a solution for ticket sales and admission control in stadiums and arenas. The objects of the Live Entertainment segment are to plan, prepare and execute tours and events, especially music events and concerts, and to market music productions. Internationally venues are also operated. The Company operates kinoheld GmbH as a majority owned subsidiary.</v>
     <v>5280</v>
     <v>XFRA</v>
-    <v>46260.649305555555</v>
+    <v>46260.670138888891</v>
     <v>Deutsche Boerse AG</v>
     <v>52</v>
     <v>59.5</v>
@@ -10302,31 +10332,31 @@
     <v>2014</v>
     <v>48.73</v>
     <v>0.52290000000000003</v>
-    <v>-0.29499999999999998</v>
-    <v>-6.0540000000000004E-3</v>
-    <v>94739634960</v>
+    <v>-0.61</v>
+    <v>-1.2518E-2</v>
+    <v>94123489920</v>
     <v>48.73</v>
     <v>Monster Beverage Corporation es una sociedad holding. La Compañía, a través de sus subsidiarias, desarrolla, comercializa, vende y distribuye bebidas de bebidas energéticas y concentrados para bebidas energéticas bajo diversas marcas. Su segmento de bebidas Monster Energy consiste principalmente en sus bebidas energéticas Monster Energy, bebidas energéticas de alto rendimiento Reign Total Body Fuel, bebidas energéticas de bienestar total Reign Storm y bebidas energéticas Bang Energy. Su segmento de Marcas Estratégicas consiste principalmente en varias marcas de bebidas energéticas adquiridas de The Coca-Cola Company, así como sus marcas de energía asequibles, Predator y Fury. Su segmento de marcas de alcohol consiste en varias cervezas artesanales, seltzers duros y bebidas de malta con sabor. Su otro segmento consiste en ciertos productos vendidos por American Fruits and Flavors LLC, una subsidiaria de propiedad total de la Compañía, a clientes independientes de terceros. También desarrolla, comercializa, vende y distribuye aguas tranquilas y chispeantes bajo la marca Monster Tour Water.</v>
     <v>6891</v>
     <v>XNAS</v>
-    <v>46260.660623471878</v>
+    <v>46260.681216064062</v>
     <v>Nasdaq Stock Market</v>
     <v>55</v>
     <v>48.77</v>
     <v>50.17</v>
-    <v>48.191000000000003</v>
+    <v>48.110999999999997</v>
     <v>30.484999999999999</v>
     <v>USD</v>
     <v>MONSTER BEVERAGE CORPORATION</v>
     <v>MONSTER BEVERAGE CORPORATION</v>
-    <v>44.951300000000003</v>
-    <v>48.435000000000002</v>
+    <v>44.658900000000003</v>
+    <v>48.12</v>
     <v>Beverages</v>
     <v>1 Monster Way, CORONA, CA, 92879-7101 US</v>
     <v>MNST</v>
     <v>Acciones</v>
     <v>MONSTER BEVERAGE CORPORATION (XNAS:MNST)</v>
-    <v>1864775</v>
+    <v>2108655</v>
     <v>10972968</v>
   </rv>
   <rv s="2">
@@ -10354,31 +10384,31 @@
     <v>2008</v>
     <v>190.76</v>
     <v>1.1657</v>
-    <v>-1.6798999999999999</v>
-    <v>-8.8179999999999994E-3</v>
-    <v>111325630832</v>
+    <v>-1.95</v>
+    <v>-1.0236E-2</v>
+    <v>111166383735</v>
     <v>190.5</v>
     <v>Airbnb, Inc. Opera una plataforma global para estancias y experiencias. El modelo de mercado de la Compañía conecta a anfitriones y huéspedes en línea o a través de dispositivos móviles para reservar espacios y experiencias en todo el mundo. La Compañía ha construido su plataforma para incorporar nuevos hosts, especialmente aquellos que anteriormente no habían considerado hosting. Se asocia con los anfitriones durante todo el proceso de configuración de su listado y les proporciona un conjunto de herramientas para administrar sus listados, incluyendo programación, merchandising, pagos integrados, soporte comunitario, etc. protección del anfitrión, orientación de precios y comentarios de las revisiones. Su sitio web y aplicaciones móviles ofrecen a sus huéspedes una manera de explorar una variedad de hogares y experiencias y una manera fácil de reservarlos. Su plataforma tecnológica impulsa su mercado de dos caras y permite su red global de anfitriones e invitados. Posee una cartera de marcas con protección en 220 países en los que opera para sus marcas principales, AIRBNB, y su logotipo de Belo.</v>
     <v>8200</v>
     <v>XNAS</v>
-    <v>46260.660616330468</v>
+    <v>46260.681211249997</v>
     <v>Nasdaq Stock Market</v>
     <v>58</v>
     <v>192.43</v>
     <v>193.4529</v>
-    <v>188.45</v>
+    <v>188.39</v>
     <v>110.81</v>
     <v>USD</v>
     <v>AIRBNB, INC.</v>
     <v>AIRBNB, INC.</v>
-    <v>42.934199999999997</v>
-    <v>188.8201</v>
+    <v>42.872700000000002</v>
+    <v>188.55</v>
     <v>Software &amp; IT Services</v>
     <v>888 Brannan St., SAN FRANCISCO, CA, 94103 US</v>
     <v>ABNB</v>
     <v>Acciones</v>
     <v>AIRBNB, INC. (XNAS:ABNB)</v>
-    <v>1019988</v>
+    <v>1136542</v>
     <v>5074998</v>
   </rv>
   <rv s="2">
@@ -10454,14 +10484,14 @@
     <v>2022</v>
     <v>98.52</v>
     <v>0.68899999999999995</v>
-    <v>-0.01</v>
-    <v>-1.0120000000000001E-4</v>
-    <v>24077026308</v>
+    <v>0.16</v>
+    <v>1.6200000000000001E-3</v>
+    <v>24118471169</v>
     <v>98.77</v>
     <v>Veralto Corporation proporciona soluciones tecnológicas esenciales que monitorean, mejoran y protegen los recursos clave en todo el mundo. Sus segmentos incluyen Calidad del Agua (WQ) y Calidad e Innovación del Producto (PQI). WQ Segment ofrece carteras de análisis de agua y soluciones de tratamiento de agua diferenciadas que permiten el suministro de agua potable segura por parte de empresas públicas y privadas. Bajo sus marcas Hach, Trojan Technologies, ChemTreat y otras marcas WQ reconocidas mundialmente, proporciona instrumentación de precisión y tecnologías avanzadas de tratamiento de agua en las que sus clientes confían para medir, analizar y tratar el agua en aplicaciones residenciales, comerciales, municipales, industriales, de investigación y de recursos naturales. El segmento PQI proporciona un conjunto de soluciones esenciales para los propietarios de marcas y las empresas de bienes de consumo envasados. Bajo sus marcas Videojet, Linx, Esko, X-Rite, Pantone y otras marcas PQI reconocidas a nivel mundial, proporciona marcado y codificación, así como embalaje e instrumentación de color y consumibles relacionados.</v>
     <v>17000</v>
     <v>XNYS</v>
-    <v>46260.660565358594</v>
+    <v>46260.681169837502</v>
     <v>New York Stock Exchange</v>
     <v>99.66</v>
     <v>109.86</v>
@@ -10470,14 +10500,14 @@
     <v>USD</v>
     <v>VERALTO CORPORATION</v>
     <v>VERALTO CORPORATION</v>
-    <v>24.895399999999999</v>
-    <v>98.76</v>
+    <v>24.938199999999998</v>
+    <v>98.93</v>
     <v>Professional &amp; Commercial Services</v>
     <v>225 Wyman Street, Suite 250, WALTHAM, MA, 02451 US</v>
     <v>VLTO</v>
     <v>Acciones</v>
     <v>VERALTO CORPORATION (XNYS:VLTO)</v>
-    <v>221402</v>
+    <v>268928</v>
     <v>1588745</v>
   </rv>
   <rv s="2">
@@ -10512,7 +10542,7 @@
     <v>Legrand SA, anteriormente Legrand SNC, es una empresa con sede en Francia. La compañía se especializa predominantemente en infraestructura eléctrica y digital de edificios. Su gama de productos es adecuada para los segmentos comercial, industrial y residencial del mercado de baja tensión. La Compañía tiene operaciones comerciales e industriales en más de 90 países. Se beneficia de palancas de crecimiento sólidas y a largo plazo. Sus productos lanzados por la Compañía se utilizan para la eficiencia energética: Dimmer avanzado de diodo emisor de luz radiante (led) y medidor trifásico conectado con Netatmo, entre otros; productos conectados en el programa Eliot: Dispositivo portátil de teleasistencia NOVO GO y sistema de alarma contra incendios T4 inalámbrico, entre otros; y centros de datos: Bandeja de cable CABLOFIL Wiremesh CF 150/900 BS, y UPS Keor SPE RT, entre otros.</v>
     <v>40931</v>
     <v>XPAR</v>
-    <v>46260.649415265623</v>
+    <v>46260.666666666664</v>
     <v>Euronext Paris</v>
     <v>66</v>
     <v>138.75</v>
@@ -10564,7 +10594,7 @@
     <v>Judges Scientific plc is a United Kingdom-based company, which is focused on acquiring and developing companies within the scientific instrument sector. The principal activities of the Company and its subsidiaries comprise the design, manufacture and sale of scientific instruments. The Company’s segments include Materials Sciences and Vacuum. Its subsidiaries are primarily United Kingdom-based with products sold around the world to a diverse range of markets, including higher education institutions, the scientific communities, manufacturers, and regulatory authorities. It is engaged in operating approximately 25 businesses. Its subsidiaries include Fire Testing Technology Limited, PE.fiberoptics Limited, UHV Design Limited, Aitchee Engineering Limited, Quorum Technologies Limited, Deben UK Limited, Oxford Cryosystems Limited, Global Digital Systems Limited, Scientifica Limited, Dia-Stron Limited, Geotek Coring Limited, EWB Solutions Limited, among others.</v>
     <v>791</v>
     <v>XLON</v>
-    <v>46260.650154930467</v>
+    <v>46260.404039351852</v>
     <v>London Stock Exchange</v>
     <v>69</v>
     <v>4050</v>
@@ -10574,14 +10604,14 @@
     <v>GBp</v>
     <v>Judges</v>
     <v>Judges</v>
-    <v>48.4709</v>
+    <v>48.350099999999998</v>
     <v>4000</v>
     <v>Machinery, Equipment &amp; Components</v>
     <v>52c Borough High Street, LONDON, SE1 1XN GB</v>
     <v>JDG</v>
     <v>Acciones</v>
     <v>Judges (XLON:JDG)</v>
-    <v>70659</v>
+    <v>130274</v>
     <v>10180</v>
   </rv>
   <rv s="2">
@@ -10618,7 +10648,7 @@
     <v>Straumann Holding AG es una compañía con sede en Suiza activa en el campo de la implantología y odontología restauradora y la regeneración de tejidos orales. En colaboración con clínicas, institutos de investigación y universidades, el Grupo investiga y desarrolla implantes, instrumentos, diseño/ fabricación de prótesis por ordenador y productos de regeneración de tejidos para usar en soluciones de reemplazo y restauración de dientes o para prevenir la perdida de dientes. Straumann Holding AG también ofrece una serie de servicios profesionales dentales a lo largo del mundo, incluye capacitación y educación, provisto por Equipo Internacional de implantología Sus productos y servicios están disponibles en varios países a través de las sedes del grupo y por una red de subsidiarias y socios tecnológicos ubicados en Europa, Norte América, Asia/la región del pacifico y en Latino América, incluyendo Dental Wings Inc localizado en Canadá y Createch Medical SL en Espana.</v>
     <v>11582</v>
     <v>XSWX</v>
-    <v>46260.646481481483</v>
+    <v>46260.662581018521</v>
     <v>SIX Swiss Exchange</v>
     <v>72</v>
     <v>94</v>
@@ -10664,14 +10694,14 @@
     <v>2004</v>
     <v>590</v>
     <v>1.2422</v>
-    <v>11.185</v>
-    <v>1.9621E-2</v>
-    <v>1480699649910</v>
+    <v>7.53</v>
+    <v>1.3209E-2</v>
+    <v>1471388515480</v>
     <v>570.04999999999995</v>
     <v>Meta Platforms, Inc. Está construyendo conexiones humanas, impulsadas por inteligencia artificial y tecnologías inmersivas. Los productos de la Compañía permiten a las personas conectarse y compartir con amigos y familiares a través de dispositivos móviles, computadoras personales, auriculares de realidad virtual (VR) y realidad mixta (MR), realidad aumentada (AR) y wearables. También ayuda a las personas a descubrir y aprender sobre lo que está sucediendo en el mundo que les rodea, permitiendo a las personas compartir sus experiencias, ideas, fotos, videos y otros contenidos con audiencias que van desde sus familiares y amigos más cercanos hasta el público en general. Los segmentos de la compañía incluyen Family of Apps (FOA) y Reality Labs (RL). El segmento FOA incluye Facebook, Instagram, Messenger, WhatsApp e hilos. El segmento de RL incluye su hardware, software y contenido de consumo relacionado con la realidad virtual, aumentada y mixta. Sus ofertas de productos en realidad virtual incluyen sus dispositivos Meta Quest, así como software y contenido disponible a través de la Tienda Meta Horizon.</v>
     <v>75472</v>
     <v>XNAS</v>
-    <v>46260.660636967186</v>
+    <v>46260.68122465234</v>
     <v>Nasdaq Stock Market</v>
     <v>75</v>
     <v>593.27</v>
@@ -10681,14 +10711,14 @@
     <v>USD</v>
     <v>META PLATFORMS, INC.</v>
     <v>META PLATFORMS, INC.</v>
-    <v>20.127099999999999</v>
-    <v>581.23500000000001</v>
+    <v>20.000499999999999</v>
+    <v>577.58000000000004</v>
     <v>Software &amp; IT Services</v>
     <v>1 Meta Way, MENLO PARK, CA, 94025 US</v>
     <v>META</v>
     <v>Acciones</v>
     <v>META PLATFORMS, INC. (XNAS:META)</v>
-    <v>21569017</v>
+    <v>22888967</v>
     <v>16319116</v>
   </rv>
   <rv s="2">
@@ -10716,14 +10746,14 @@
     <v>2021</v>
     <v>107.74</v>
     <v>1.7877000000000001</v>
-    <v>0.31</v>
-    <v>2.882E-3</v>
-    <v>96845904884</v>
+    <v>0.4</v>
+    <v>3.7180000000000004E-3</v>
+    <v>96926692088</v>
     <v>107.58</v>
     <v>KKR &amp; Co. Inc. Es una empresa de inversión global que ofrece gestión alternativa de activos, mercados de capital y soluciones de seguros. Los segmentos de la Compañía incluyen Gestión de Activos, Seguros y Holdings Estratégicos. El segmento de gestión de activos ofrece una gama de servicios de gestión de inversiones a fondos de inversión, vehículos y cuentas y proporciona servicios de mercados de capitales a empresas de cartera y terceros. El segmento de Gestión de Activos incluye cinco líneas de negocio: Capital Privado, Activos Inmobiliarios, Estrategias de Crédito y Líquido, Mercados de Capitales y Actividades Principales. El segmento de seguros es operado por Global Atlantic, que es una compañía de seguros de vida y jubilación de los Estados Unidos que ofrece un conjunto de productos de protección, herencia y ahorro y soluciones de reaseguro a clientes en los mercados individuales e institucionales. Global Atlantic ofrece anualidades de tasa fija a individuos y otras. El segmento Estratégico Holdings representa su participación en su estrategia básica de capital riesgo.</v>
     <v>5043</v>
     <v>XNYS</v>
-    <v>46260.660644883596</v>
+    <v>46260.681210381248</v>
     <v>New York Stock Exchange</v>
     <v>78</v>
     <v>108.99</v>
@@ -10733,14 +10763,14 @@
     <v>USD</v>
     <v>KKR &amp; CO. INC.</v>
     <v>KKR &amp; CO. INC.</v>
-    <v>34.3949</v>
-    <v>107.89</v>
+    <v>34.4236</v>
+    <v>107.98</v>
     <v>Investment Banking &amp; Investment Services</v>
     <v>30 Hudson Yards, NEW YORK, NY, 10001 US</v>
     <v>KKR</v>
     <v>Acciones</v>
     <v>KKR &amp; CO. INC. (XNYS:KKR)</v>
-    <v>383235</v>
+    <v>476442</v>
     <v>4748653</v>
   </rv>
   <rv s="2">
@@ -10768,14 +10798,14 @@
     <v>2009</v>
     <v>273.81</v>
     <v>1.6516999999999999</v>
-    <v>7.06</v>
-    <v>2.5434000000000002E-2</v>
-    <v>101354525808</v>
+    <v>6.55</v>
+    <v>2.3597E-2</v>
+    <v>101172925161</v>
     <v>277.58</v>
     <v>Cloudflare, Inc. Es una compañía de conectividad en la nube. Su conjunto completo de productos consiste en sus servicios de sitio web y aplicaciones para ofrecer seguridad, rendimiento y confiabilidad para los sitios web, aplicaciones e interfaces de programación de aplicaciones (API) de una organización; su plataforma Secure Access Service Edge (SASE), que contiene su conjunto de soluciones Zero Trust y servicios de red para ayudar a garantizar que el tráfico de entrada y salida de la red interna y los dispositivos de una organización se verifique y autorice, así como para conectar de forma segura centros de datos, servicios en la nube y sucursales a una organización con su Connectivity Cloud; sus soluciones basadas en desarrolladores para crear e implementar aplicaciones sin servidor con escala, rendimiento, seguridad y confiabilidad, y sus ofertas para consumidores. Sus ofertas de productos de seguridad de sitios web y aplicaciones incluyen firewall de aplicaciones web, gestión de bots, protección de denegación de servicio distribuida, seguridad de API, cifrado SSL/TLS, administración de scripts y centro de seguridad.</v>
     <v>5483</v>
     <v>XNYS</v>
-    <v>46260.660615937501</v>
+    <v>46260.681190462499</v>
     <v>New York Stock Exchange</v>
     <v>81</v>
     <v>286.60000000000002</v>
@@ -10786,13 +10816,13 @@
     <v>CLOUDFLARE, INC.</v>
     <v>CLOUDFLARE, INC.</v>
     <v>0</v>
-    <v>284.64</v>
+    <v>284.13</v>
     <v>Software &amp; IT Services</v>
     <v>101 Townsend St, SAN FRANCISCO, CA, 94107-1934 US</v>
     <v>NET</v>
     <v>Acciones</v>
     <v>CLOUDFLARE, INC. (XNYS:NET)</v>
-    <v>809710</v>
+    <v>1037922</v>
     <v>3743504</v>
   </rv>
   <rv s="2">
@@ -10820,14 +10850,14 @@
     <v>2011</v>
     <v>182.01</v>
     <v>1.2242999999999999</v>
-    <v>1.97</v>
-    <v>1.0626999999999999E-2</v>
-    <v>190782626700</v>
+    <v>2.0150000000000001</v>
+    <v>1.0869999999999999E-2</v>
+    <v>190828451190</v>
     <v>185.38</v>
     <v>CrowdStrike Holdings, Inc. Es una compañía global de ciberseguridad que proporciona protección en la nube para endpoints, cargas de trabajo en la nube, identidad y datos. Su plataforma Falcon está diseñada para la consolidación de la ciberseguridad, diseñada específicamente para detener las brechas. Las plataformas recopilan e integran datos de toda la empresa, incluidos puntos finales, cargas de trabajo en la nube, identidades y fuentes de terceros. Ofrece 29 módulos en la nube en su plataforma Falcon a través de un modelo basado en suscripción de software como servicio (SaaS) que abarca múltiples mercados grandes, incluyendo seguridad de endpoints corporativos y cargas de trabajo en la nube, servicios de seguridad gestionada, gestión de operaciones de tecnología de la información (TI), protección de identidades, gestión de información de seguridad de próxima generación y gestión de eventos (SIEM) y gestión de registros, servicios de inteligencia contra amenazas, protección de datos, gestión de posturas de seguridad SaaS, automatización y respuesta (SOAR) y automatización de flujo de trabajo impulsada por inteligencia artificial, entre otros.</v>
     <v>11157</v>
     <v>XNAS</v>
-    <v>46260.660641689065</v>
+    <v>46260.681224895314</v>
     <v>Nasdaq Stock Market</v>
     <v>84</v>
     <v>189.65</v>
@@ -10838,13 +10868,13 @@
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>CROWDSTRIKE HOLDINGS, INC.</v>
     <v>0</v>
-    <v>187.35</v>
+    <v>187.39500000000001</v>
     <v>Software &amp; IT Services</v>
     <v>206 E. 9TH STREET, SUITE 1400, AUSTIN, TX, 78701 US</v>
     <v>CRWD</v>
     <v>Acciones</v>
     <v>CROWDSTRIKE HOLDINGS, INC. (XNAS:CRWD)</v>
-    <v>3629596</v>
+    <v>3962952</v>
     <v>7602119</v>
   </rv>
   <rv s="2">
@@ -10872,14 +10902,14 @@
     <v>2015</v>
     <v>342.94</v>
     <v>1.2282999999999999</v>
-    <v>-4.26</v>
-    <v>-1.2407999999999999E-2</v>
-    <v>4146948400000</v>
+    <v>-5.3</v>
+    <v>-1.5437000000000001E-2</v>
+    <v>4134229200000</v>
     <v>343.34</v>
     <v>Alphabet Inc. Es una compañía holding. Los segmentos de la Compañía incluyen Google Services, Google Cloud y otras apuestas. El segmento de Servicios de Google incluye productos y servicios como anuncios, Android, Chrome, dispositivos, Google Maps, Google Maps, etc. Google Play, Búsqueda y YouTube. El segmento de Google Cloud incluye servicios de infraestructura y plataforma, herramientas de colaboración y otros servicios para clientes empresariales. Su otro segmento de apuestas se dedica a la venta de servicios relacionados con la salud y servicios de Internet. Google Cloud ofrece servicios en la nube listos para la empresa, incluidos Google Cloud Platform y Google Workspace. Google Cloud Platform proporciona acceso a soluciones como las ofertas de inteligencia artificial (IA), incluida su infraestructura de IA, la plataforma Vertex AI y Gemini para Google Cloud; ciberseguridad y datos y análisis. Google Workspace incluye herramientas de comunicación y colaboración basadas en la nube para empresas, como Calendar, Gmail, Docs, Drive, y reunirse.</v>
     <v>198933</v>
     <v>XNAS</v>
-    <v>46260.660658437497</v>
+    <v>46260.681234328127</v>
     <v>Nasdaq Stock Market</v>
     <v>87</v>
     <v>343.19110000000001</v>
@@ -10889,14 +10919,14 @@
     <v>USD</v>
     <v>ALPHABET INC.</v>
     <v>ALPHABET INC.</v>
-    <v>17.0444</v>
-    <v>339.08</v>
+    <v>16.992100000000001</v>
+    <v>338.04</v>
     <v>Software &amp; IT Services</v>
     <v>1600 Amphitheatre Parkway, MOUNTAIN VIEW, CA, 94043 US</v>
     <v>GOOG</v>
     <v>Acciones</v>
     <v>ALPHABET INC. (XNAS:GOOG)</v>
-    <v>5473978</v>
+    <v>6052185</v>
     <v>19309296</v>
   </rv>
   <rv s="2">
@@ -10968,14 +10998,14 @@
     <v>2010</v>
     <v>286.91000000000003</v>
     <v>0.86799999999999999</v>
-    <v>-1.4450000000000001</v>
-    <v>-5.0099999999999997E-3</v>
-    <v>55349631762</v>
+    <v>-1.46</v>
+    <v>-5.0619999999999997E-3</v>
+    <v>55346738975</v>
     <v>288.45</v>
     <v>Garmin Ltd. (Garmin) es una entidad con sede en Suiza. La Compañía y sus filiales ofrecen sistemas de posicionamiento global (GPS) y dispositivos y aplicaciones inalámbricas. La Compañía opera a través de cinco segmentos: Fitness, outdoor, aviación, marina y auto. Ofrece una gama de productos de navegación automática, así como una gama de productos y aplicaciones diseñados para el mercado de GPS móvil. Ofrece Handhelds al aire libre, dispositivos portables, dispositivos de golf y dispositivos de seguimiento de perros y entrenamiento / obediencia de mascotas. Garmin ofrece varios productos diseñados para su uso en el seguimiento de fitness y actividad. El segmento de negocios de aviación de la compañía es un proveedor de soluciones para fabricantes de aeronaves, propietarios y operadores de aeronaves existentes, así como clientes militares y gubernamentales, y sirve a una gama de aeronaves, incluyendo aviones de transporte, aviación de negocios, aviación general, deportes experimentales / ligeros, etc. helicópteros, vehículos pilotados opcionalmente y vehículos aéreos no tripulados. La compañía opera en todo el mundo.</v>
     <v>23000</v>
     <v>XNYS</v>
-    <v>46260.660581203127</v>
+    <v>46260.681156990628</v>
     <v>New York Stock Exchange</v>
     <v>92</v>
     <v>289.14</v>
@@ -10985,14 +11015,14 @@
     <v>USD</v>
     <v>Garmin Ltd.</v>
     <v>Garmin Ltd.</v>
-    <v>29.597899999999999</v>
-    <v>287.005</v>
+    <v>29.596399999999999</v>
+    <v>286.99</v>
     <v>Communications &amp; Networking</v>
     <v>Muehlentalstrasse 2, SCHAFFHAUSEN, SCHAFFHAUSEN, 8200 CH</v>
     <v>GRMN</v>
     <v>Acciones</v>
     <v>Garmin Ltd. (XNYS:GRMN)</v>
-    <v>134299</v>
+    <v>158935</v>
     <v>1023816</v>
   </rv>
   <rv s="2">
@@ -11072,31 +11102,31 @@
     <v>2008</v>
     <v>108.37</v>
     <v>0.2137</v>
-    <v>-0.68</v>
-    <v>-6.2529999999999999E-3</v>
-    <v>20461271345</v>
+    <v>-1.04</v>
+    <v>-9.5630000000000003E-3</v>
+    <v>20393111285</v>
     <v>108.75</v>
     <v>Kaspi.kz AO (Joint Stock Company Kaspi.kz), formerly Aktsionernoe obshchestvo kaspi, is a Kazakhstan-based financial technology company, which provide a range of services such as online payments, e-commerce, and digital banking. The Company operates as holding company for Kaspi Group AO and Kaspi Magazin TOO. The Company operates through two segments. Mass retail offers a wide range of products and financial services to retail customers through a network of branches, offices, and automated teller machine (ATM). These products include savings and current accounts, credit cards, car loans and commodity loans, as well as a wide range of insurance policies. Financial services for corporate, middle, and small, and other businesses segment, including deposits, overdrafts, loans and other credit services and currency exchange.</v>
     <v>7700</v>
     <v>XNAS</v>
-    <v>46260.660579617972</v>
+    <v>46260.681186006252</v>
     <v>Nasdaq Stock Market</v>
     <v>98</v>
     <v>109.94</v>
     <v>109.94</v>
-    <v>107.71</v>
+    <v>107.68</v>
     <v>68.59</v>
     <v>USD</v>
     <v>Kaspi.kz AO</v>
     <v>Kaspi.kz AO</v>
-    <v>9.2745999999999995</v>
-    <v>108.07</v>
+    <v>9.2437000000000005</v>
+    <v>107.71</v>
     <v>Financial Technology (Fintech) &amp; Infrastructure</v>
     <v>Bostandykskiy Rayon, Ul. Nauryzbay Batyra, 154A, ALMATY, ALMATY, 050013 KZ</v>
     <v>KSPI</v>
     <v>Acciones</v>
     <v>Kaspi.kz AO (XNAS:KSPI)</v>
-    <v>532601</v>
+    <v>558536</v>
     <v>564603</v>
   </rv>
   <rv s="2">
@@ -11130,7 +11160,7 @@
     <v>Clínica Baviera SA es una empresa con sede en España dedicada al sector sanitario. La Compañía se centra en la prestación de servicios dentro del campo de la medicina oftálmica. La Compañía está especializada en el diagnóstico y tratamiento de trastornos oculares, incluyendo miopía, hipermetropía, astigmatismo, cataratas, etc. glaucoma, retina vítrea y estrabismo, entre otros. La Compañía opera una red de clínicas ubicadas en varios países europeos, como España, Alemania, Austria e Italia. La Compañía es una matriz del Grupo Baviera, un grupo que comprende varias entidades controladas, entre ellas Clinica Baviera Italia Srl, Clinica Baviera Mallorca SL, Care Visión Germany GmbH y Castellana de INTERMEDIACION Sanitaria SL, entre otras.</v>
     <v>2009</v>
     <v>BMEX</v>
-    <v>46260.650150462963</v>
+    <v>46260.666666666664</v>
     <v>Bolsas y Mercados Espanoles</v>
     <v>101</v>
     <v>60.2</v>
@@ -11175,31 +11205,31 @@
     <v>1998</v>
     <v>212.56</v>
     <v>2.2120000000000002</v>
-    <v>-1.835</v>
-    <v>-8.6129999999999991E-3</v>
-    <v>5111403000000</v>
+    <v>-2.7250000000000001</v>
+    <v>-1.2789999999999999E-2</v>
+    <v>5089865000000</v>
     <v>213.05</v>
     <v>NVIDIA Corporation es una empresa de infraestructura de computación completa. La Compañía se dedica a la computación acelerada para ayudar a resolver los problemas computacionales desafiantes. Los segmentos de la Compañía incluyen Compute &amp; Networking y Gráficos. El segmento Compute &amp; Networking incluye sus plataformas de computación acelerada de centros de datos y soluciones y software de inteligencia artificial (IA); redes; plataformas automotrices y soluciones de vehículos autónomos y eléctricos; Jetson para robótica y otras plataformas integradas, y servicios de computación en la nube DGX. El segmento de gráficos incluye GPU GeForce para juegos y PC, el servicio de streaming de juegos GeForce NOW e infraestructura relacionada, y soluciones para plataformas de juegos; GPU Quadro/NVIDIA RTX para gráficos de estaciones de trabajo empresariales; software de GPU virtual para computación visual y virtual basada en la nube; plataformas automotrices para sistemas de infoentretenimiento y software Omniverse Enterprise para construir y operar aplicaciones industriales de IA y gemelas digitales.</v>
     <v>42000</v>
     <v>XNAS</v>
-    <v>46260.660632858591</v>
+    <v>46260.681221608596</v>
     <v>Nasdaq Stock Market</v>
     <v>104</v>
     <v>213.6</v>
     <v>236.54</v>
-    <v>210.08080000000001</v>
+    <v>209.76</v>
     <v>164.07</v>
     <v>USD</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>32.345300000000002</v>
-    <v>211.215</v>
+    <v>32.209000000000003</v>
+    <v>210.32499999999999</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
     <v>NVDA</v>
     <v>Acciones</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>40425876</v>
+    <v>47024405</v>
     <v>118084391</v>
   </rv>
   <rv s="2">
@@ -11234,7 +11264,7 @@
     <v>Corticeira Amorim SGPS SA (Corticeira Amorim) is a Portugal-based holding company engaged in the cork industry. The Company organizes its activities into five business divisions: Raw Materials, Cork Stoppers, Coverings, Cork Composites and Isolations. In the Raw Materials division, the Company is active in the purchase, storage and initial preparation of cork. The Cork Stoppers division produces and supplies various types of bottle caps, mainly for the wine industry. The Coverings division is active in the production of cork-based laminates. The Cork Composites and the Isolations units produce thermal, acoustic and anti-vibration insulation products, among others. The Company and its subsidiaries operate in Portugal, Spain, Tunisia, the United States, Australia, Germany, China, Italy, Argentina, France and Netherlands, among others. The Company is a subsidiary of Amorim Capital SGPS SA.</v>
     <v>4637</v>
     <v>XLIS</v>
-    <v>46260.649334652342</v>
+    <v>46260.666666666664</v>
     <v>Euronext Lisbon</v>
     <v>107</v>
     <v>7.08</v>
@@ -11279,31 +11309,31 @@
     <v>1987</v>
     <v>417.99</v>
     <v>1.395</v>
-    <v>-0.26300000000000001</v>
-    <v>-6.3009999999999997E-4</v>
-    <v>2163522069678</v>
+    <v>-1.37</v>
+    <v>-3.2819999999999998E-3</v>
+    <v>2157780642960</v>
     <v>417.41</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd es una empresa con sede en Taiwán dedicada principalmente a la prestación de servicios de fabricación de circuitos integrados. Los servicios integrados de fabricación de circuitos incluyen tecnología de proceso, tecnología de proceso especial, soporte del ecosistema de diseño, tecnología de máscara, embalaje avanzado 3DFabricTM y servicios de tecnología de apilamiento de silicio. La compañía ha completado la transferencia y la producción en masa de la tecnología 5nm, y se dedica a la investigación y desarrollo de la tecnología de proceso 3nm y la tecnología de proceso 2nm. La gama de aplicaciones de productos cubre toda la industria de aplicaciones electrónicas, incluyendo computadoras personales y productos periféricos, productos de aplicaciones de información, productos de sistemas de comunicación cableados e inalámbricos, servidores y centros de datos.</v>
     <v>52045</v>
     <v>XNYS</v>
-    <v>46260.660653356252</v>
+    <v>46260.681224814063</v>
     <v>New York Stock Exchange</v>
     <v>110</v>
     <v>420.75</v>
     <v>479</v>
-    <v>415.63</v>
+    <v>414.41</v>
     <v>225.6301</v>
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
-    <v>30.340599999999998</v>
-    <v>417.14699999999999</v>
+    <v>30.260100000000001</v>
+    <v>416.04</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>No.8, Li-Hsin 6th Road, Hsinchu Science Park, HSINCHU, HSINCHU, 300 TW</v>
     <v>TSM</v>
     <v>Acciones</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>2585183</v>
+    <v>3000139</v>
     <v>11756595</v>
   </rv>
   <rv s="2">
@@ -11331,31 +11361,31 @@
     <v>2007</v>
     <v>549.44000000000005</v>
     <v>1.5881000000000001</v>
-    <v>-8.9949999999999992</v>
-    <v>-1.6278000000000001E-2</v>
-    <v>111723252765</v>
+    <v>-7.62</v>
+    <v>-1.379E-2</v>
+    <v>112005862290</v>
     <v>552.57000000000005</v>
     <v>Spotify Technology SA es una empresa con sede en Luxemburgo que ofrece servicios de música digital en streaming. La Compañía permite a los usuarios descubrir nuevos lanzamientos, que incluyen los últimos singles y álbumes; listas de reproducción, que incluye listas de reproducción preparadas por fanáticos de la música y expertos, y más de millones de canciones para que los usuarios puedan reproducir sus favoritos, descubrir nuevas pistas y construir una colección personalizada. Sus usuarios pueden seleccionar Spotify Free, que incluye solo reproducción aleatoria o Spotify Premium, que abarca una gama de características, como reproducción aleatoria, publicidad gratuita, saltos ilimitados, escuchar sin conexión, reproducir cualquier pista y audio. La Compañía opera a través de una serie de subsidiarias, incluyendo Spotify LTD y está presente en más de 20 países. Su servicio ofrece una experiencia de escucha de música sin pausas comerciales.</v>
     <v>7287</v>
     <v>XNYS</v>
-    <v>46260.660633032028</v>
+    <v>46260.681165300783</v>
     <v>New York Stock Exchange</v>
     <v>113</v>
     <v>554.97</v>
     <v>745</v>
-    <v>543.36099999999999</v>
+    <v>543.20000000000005</v>
     <v>405</v>
     <v>USD</v>
     <v>Spotify Technology S.A.</v>
     <v>Spotify Technology S.A.</v>
-    <v>30.034300000000002</v>
-    <v>543.57500000000005</v>
+    <v>30.110199999999999</v>
+    <v>544.95000000000005</v>
     <v>Software &amp; IT Services</v>
     <v>33, Boulevard Prince Henri, LUXEMBOURG, 1724 LU</v>
     <v>SPOT</v>
     <v>Acciones</v>
     <v>Spotify Technology S.A. (XNYS:SPOT)</v>
-    <v>288032</v>
+    <v>603859</v>
     <v>1986802</v>
   </rv>
   <rv s="2">
@@ -11389,7 +11419,7 @@
     <v>PRYSMIAN S.P.A. es una empresa con sede en Italia activa en el desarrollo, diseño, producción, suministro y montaje de cables. Las actividades de negocio de la Empresa se dividen en dos sectores principales: Energía y Telecomunicaciones. El segmento de Energía se divide en cuatro líneas de negocio, que incluyen los Servicios Públicos, que consta de sistemas de transmisión de potencia, transmisión submarina de energía y cables y sistemas para distribución de energía, así como componentes y accesorios; Comercio e Instaladores, ofrece cables de distribución de energía hasta y dentro de edificios; Industrial, que incluye cables para los sectores de energías renovables, automotriz, ascensor y petróleo y gas, y Otros, que está activa en la venta de productos semiacabados, materias primas u otros bienes. El segmento de Telecomunicaciones hace sistemas de cable y productos de conectividad utilizados en las redes de telecomunicaciones, incluyendo fibra óptica, cables ópticos, componentes de conectividad, cables ópticos terrestres y cables de cobre, entre otros.</v>
     <v>33824</v>
     <v>XMIL</v>
-    <v>46260.649429282028</v>
+    <v>46260.666666666664</v>
     <v>Borsa Italiana</v>
     <v>116</v>
     <v>123.05</v>
@@ -11406,7 +11436,7 @@
     <v>PRY</v>
     <v>Acciones</v>
     <v>Prysmian S.p.A. (XMIL:PRY)</v>
-    <v>708554</v>
+    <v>708614</v>
     <v>1042440</v>
   </rv>
   <rv s="2">
@@ -11443,7 +11473,7 @@
     <v>Jungfraubahn Holding AG is a Switzerland-based holding company engaged in the operation of excursion railways and winter sports facilities in the Eiger Monch &amp; Jungfrau Region and the marketing of the Jungfraujoch-Top of Europe experience, as well as the trip to the Jungfraujoch. The Company’s destinations include Jungfraujoch-Top of Europe, Kleine Scheidegg, Harder Kulm, Schynige Platte, Grindelwald First and Murren and Winteregg. The Company owns various restaurants and lodges along the railway trails. Jungfraubahn Holding AG's activities are carried out through a number of subsidiaries, including Jungfraubahn AG, Wengernalpbahn AG, Firstbahn AG, Bergbahn Lauterbrunnen-Muerren AG, Harderbahn AG, Parkhaus Lauterbrunnen AG and Jungfraubahnen Management AG, among others.</v>
     <v>757</v>
     <v>XSWX</v>
-    <v>46260.646481481483</v>
+    <v>46260.652777777781</v>
     <v>SIX Swiss Exchange</v>
     <v>119</v>
     <v>256</v>
@@ -11496,7 +11526,7 @@
     <v>Davide Campari Milano NV, constituida en los Países Bajos, es una empresa activa en la industria de las bebidas espirituosas de marca. Posee una amplia y variada cartera de productos de más de 50 marcas, incluidas Aperol, Appleton Estate, Campari, Grand Marnier, SKYY Vodka y Wild Turkey. Opera a través de cuatro segmentos geográficos: América; Sur de Europa, Medio Oriente y África; Europa del Norte, Central y del Este; Asia-Pacífico. La Compañía es un alcance de distribución global, que opera en más de 190 países de todo el mundo con un enfoque en Europa y las Américas. Cuenta con 21 plantas productivas y red de distribución propia en 20 países.</v>
     <v>4935</v>
     <v>XMIL</v>
-    <v>46260.649363425924</v>
+    <v>46260.666666666664</v>
     <v>Borsa Italiana</v>
     <v>122</v>
     <v>5.9880000000000004</v>
@@ -11550,7 +11580,7 @@
     <v>Sika AG es una compañía con base en Suiza activa en la industria química. La Compañía produce productos principalmente para las industrias de automóviles y autopartes, energía renovable y equipos y componentes. Las actividades de la Compañía se dividen en dos áreas de negocio: la División de Construcción ofrece una gama de productos, que incluyen mezclas de hormigón, morteros listos para usar, sistemas de techado, sistemas de impermeabilización, sistemas de pisos y soluciones de protección de acero, entre otros y la División Industria desarrolla soluciones de unión, sellado, amortiguación, acristalamiento y refuerzo, entre otros. Las marcas de la Compañía incluye Sarnafil, Sika, Sikadur, Sikaflex, SikaGrout, SikaPower, SikaHydroPrep, SikaReinforcer, Sika ViscoCrete, Sikaplan y SikaRapid, entre otros. La Compañía tiene una actividad global, con actividades divididas en regiones geográficas, a saber, Europa, Medio Oriente y África (EMEA), América del Norte, América Latina y Asia/ Pacifico. La Compañía opera a través de numerosas filiales.</v>
     <v>33856</v>
     <v>XSWX</v>
-    <v>46260.646481481483</v>
+    <v>46260.652777777781</v>
     <v>SIX Swiss Exchange</v>
     <v>125</v>
     <v>194.05</v>
@@ -11596,14 +11626,14 @@
     <v>1993</v>
     <v>126.82</v>
     <v>0.49199999999999999</v>
-    <v>-1.395</v>
-    <v>-1.0770999999999999E-2</v>
-    <v>13081639375</v>
+    <v>-1.33</v>
+    <v>-1.0268999999999999E-2</v>
+    <v>13088275914</v>
     <v>129.52000000000001</v>
     <v>Check Point Software Technologies Ltd es una empresa con sede en Israel dedicada principalmente a la industria de la ciberseguridad. La compañía se centra en proporcionar soluciones de seguridad basadas en IA y entregadas en la nube para proteger a las empresas corporativas y los gobiernos de todo el mundo. Su producto clave es Check Point Infinity Architecture, que es una plataforma integral de ciberseguridad. La Plataforma tiene como objetivo defenderse contra los ciberataques de quinta generación en varias redes, endpoints, entornos de nube, cargas de trabajo, Internet de las Cosas (IoT) y dispositivos móviles. Aparte de eso, la Compañía ofrece una gama de productos y servicios diseñados para proteger la infraestructura de TI. Integra tecnologías avanzadas de prevención de amenazas, incluyendo firewall, sistema de prevención de intrusiones (IPS), antivirus, anti-bot y capacidades de sandboxing.</v>
     <v>6825</v>
     <v>XNAS</v>
-    <v>46260.660564224221</v>
+    <v>46260.68117928203</v>
     <v>Nasdaq Stock Market</v>
     <v>128</v>
     <v>129.65</v>
@@ -11613,14 +11643,14 @@
     <v>USD</v>
     <v>CHECK POINT SOFTWARE TECHNOLOGIES LTD.</v>
     <v>CHECK POINT SOFTWARE TECHNOLOGIES LTD.</v>
-    <v>13.125299999999999</v>
-    <v>128.125</v>
+    <v>13.1319</v>
+    <v>128.19</v>
     <v>Software &amp; IT Services</v>
     <v>5 Shlomo Kaplan Street, TEL AVIV, TEL AVIV, 6789159 IL</v>
     <v>CHKP</v>
     <v>Acciones</v>
     <v>CHECK POINT SOFTWARE TECHNOLOGIES LTD. (XNAS:CHKP)</v>
-    <v>226979</v>
+    <v>247077</v>
     <v>1169905</v>
   </rv>
   <rv s="2">
@@ -11654,7 +11684,7 @@
     <v>Technogym SpA es una empresa con sede en Italia que se dedica a la industria de productos recreativos. La Empresa fabrica equipos fitness. Diseña y fabrica equipos fitness para particulares, empresas, centros de fitness, hoteles y spas, y centros médicos. La oferta de productos de la Empresa incluye cintas de correr, bicicletas estáticas, entrenadores de cross, entrenamiento en circuito, equipos para ejercicios de core, accesorios de fitness, bancos de gimnasio, kinesis, equipos para ejercicios de piernas, multigimnasios, equipos de carga de placas, software y hardware, steppers, máquinas de estiramiento, equipos para la parte superior del cuerpo y pesas, mancuernas y barras para entrenamiento cardiovascular, fitness en grupo, entrenamiento de resistencia y funcional, y entrenamiento de fuerza, entre otros.</v>
     <v>2800</v>
     <v>XMIL</v>
-    <v>46260.649502997658</v>
+    <v>46260.666666666664</v>
     <v>Borsa Italiana</v>
     <v>131</v>
     <v>12.99</v>
@@ -11706,7 +11736,7 @@
     <v>VIDRALA, S.A. es una empresa española dedicada principalmente a la industria del vidrio. La empresa opera a través de dos segmentos: España y la Unión Europea. Las actividades de la empresa incluyen la producción, distribución y venta de botellas y envases de vidrio en las industrias de alimentos y bebidas. La empresa realiza sus propias operaciones de investigación y desarrollo (I+D). Opera plantas de producción y hornos de fusión situados en países como Portugal, Francia, Bélgica e Italia. La empresa posee las siguientes subsidiarias: Crisnova Vidrio, S. A., Inverbeira Sociedad de Promoción de Empresas, S. A., Gallo Vidro, S. A., Castellar Vidrio, S. A., Corsico Vetro SRL, MD Verre, S. A., Omega Immobiliere et Financiere, S. A., Investverre, S. A. y CD Verre, S. A.</v>
     <v>4771</v>
     <v>BMEX</v>
-    <v>46260.649548611109</v>
+    <v>46260.666666666664</v>
     <v>Bolsas y Mercados Espanoles</v>
     <v>134</v>
     <v>91.7</v>
@@ -11751,14 +11781,14 @@
     <v>2019</v>
     <v>48.67</v>
     <v>0.38369999999999999</v>
-    <v>-0.35</v>
-    <v>-7.0860000000000003E-3</v>
-    <v>10102387120</v>
+    <v>-0.24</v>
+    <v>-4.8589999999999996E-3</v>
+    <v>10125047450</v>
     <v>49.39</v>
     <v>Triple Flag Precious Metals Corp. is a precious metal streaming and royalty company. It offers investors exposure to gold and silver from a total of 242 assets, consisting of 17 streams and 225 royalties, from the Americas and Australia. These streams and royalties are tied to mining assets at various stages of the mine life cycle, including 36 producing mines and 206 development and exploration stage projects and other assets. It has a diversified portfolio of properties in Australia, Peru, South Africa, Colombia, Canada, Mexico, the United States, Mongolia, Cote d’Ivoire, and others. Its diversified portfolio of streams and royalties provides exposure to production from a suite of mining assets, including the Northparkes copper-gold mine in Australia (Evolution Mining), the Cerro Lindo polymetallic mine in Peru (Nexa), the Fosterville gold mine in Australia (Agnico Eagle), the Buritica gold mine in Colombia (Zijin) and the Impala Bafokeng Operations in South Africa (Implats).</v>
     <v>19</v>
     <v>XTSE</v>
-    <v>46260.64980324074</v>
+    <v>46260.668379629627</v>
     <v>Toronto Stock Exchange</v>
     <v>137</v>
     <v>49.84</v>
@@ -11768,14 +11798,14 @@
     <v>CAD</v>
     <v>Triple Flag Prec</v>
     <v>Triple Flag Prec</v>
-    <v>17.351199999999999</v>
-    <v>49.04</v>
+    <v>17.3902</v>
+    <v>49.15</v>
     <v>Metals &amp; Mining</v>
     <v>TD Canada Trust Tower, 161 Bay Street, Suite 4535, Toronto, ON, M5J 2S1 CA</v>
     <v>TFPM</v>
     <v>Acciones</v>
     <v>Triple Flag Prec (XTSE:TFPM)</v>
-    <v>48937</v>
+    <v>55338</v>
     <v>230150</v>
   </rv>
   <rv s="2">
@@ -11803,14 +11833,14 @@
     <v>1997</v>
     <v>81.84</v>
     <v>1.5269999999999999</v>
-    <v>-0.56499999999999995</v>
-    <v>-6.8710000000000004E-3</v>
-    <v>340048078435</v>
+    <v>-0.76500000000000001</v>
+    <v>-9.3030000000000005E-3</v>
+    <v>339215290635</v>
     <v>82.23</v>
     <v>Netflix, Inc. Es un proveedor de servicios de entretenimiento. La Compañía adquiere, concede licencias y produce contenido, incluida la programación original. Ofrece membresías pagadas en más de 190 países que ofrecen series de televisión (TV), películas y juegos en una variedad de géneros e idiomas. Permite a los miembros jugar, pausar y reanudar la mirada tanto como quieran, en cualquier momento y en cualquier lugar, y puede cambiar sus planes en cualquier momento. La Compañía ofrece a los miembros la posibilidad de recibir contenido en streaming a través de una serie de dispositivos conectados a Internet, incluidos televisores, reproductores de video digital, decodificadores de TV y dispositivos móviles. Se dedica a escalar su servicio de streaming, como la introducción de juegos y publicidad en su servicio, así como ofrecer programación en vivo. Está desarrollando tecnología y utilizando computación en la nube de terceros, tecnología y otros servicios. La Compañía también se dedica a escalar sus propias operaciones de estudio para producir contenido original.</v>
     <v>16000</v>
     <v>XNAS</v>
-    <v>46260.660662534377</v>
+    <v>46260.681235532029</v>
     <v>Nasdaq Stock Market</v>
     <v>140</v>
     <v>82.42</v>
@@ -11820,14 +11850,14 @@
     <v>USD</v>
     <v>NETFLIX, INC.</v>
     <v>NETFLIX, INC.</v>
-    <v>25.727699999999999</v>
-    <v>81.665000000000006</v>
+    <v>25.6647</v>
+    <v>81.465000000000003</v>
     <v>Software &amp; IT Services</v>
     <v>121 Albright Way, LOS GATOS, CA, 95032 US</v>
     <v>NFLX</v>
     <v>Acciones</v>
     <v>NETFLIX, INC. (XNAS:NFLX)</v>
-    <v>9967784</v>
+    <v>10892296</v>
     <v>34029245</v>
   </rv>
   <rv s="2">
@@ -11855,14 +11885,14 @@
     <v>1969</v>
     <v>39.36</v>
     <v>1.1114999999999999</v>
-    <v>-0.88500000000000001</v>
-    <v>-2.2416000000000002E-2</v>
-    <v>57255643905</v>
+    <v>-0.94499999999999995</v>
+    <v>-2.3936000000000002E-2</v>
+    <v>57166633964</v>
     <v>39.479999999999997</v>
     <v>NIKE, Inc. Se dedica al diseño, comercialización y distribución de calzado deportivo, ropa, equipos y accesorios y servicios para actividades deportivas y de fitness. Los segmentos operativos de la compañía incluyen América del Norte, Europa, Oriente Medio y África (EMEA), Gran China y Asia Pacífico y América Latina (APLA). Vende una línea de equipos y accesorios bajo la marca NIKE, incluyendo bolsos, calcetines, bolas deportivas, gafas, relojes, dispositivos digitales, murciélagos, guantes, equipos de protección y otros equipos diseñados para actividades deportivas. También diseña productos específicamente para la marca Jordan y Converse. La marca Jordan diseña, distribuye y otorga licencias de calzado deportivo y casual, ropa y accesorios principalmente centrados en el rendimiento y la cultura del baloncesto utilizando la marca Jumpman. La Compañía también diseña, distribuye y otorga licencias de zapatillas de deporte casuales, ropa y accesorios bajo las marcas registradas Chuck Taylor, All Star, One Star, Star Chevron y Jack Purcell.</v>
     <v>73000</v>
     <v>XNYS</v>
-    <v>46260.660633437503</v>
+    <v>46260.681191990625</v>
     <v>New York Stock Exchange</v>
     <v>143</v>
     <v>39.480699999999999</v>
@@ -11872,14 +11902,14 @@
     <v>USD</v>
     <v>NIKE, INC.</v>
     <v>NIKE, INC.</v>
-    <v>18.394300000000001</v>
-    <v>38.594999999999999</v>
+    <v>18.3657</v>
+    <v>38.534999999999997</v>
     <v>Textiles &amp; Apparel</v>
     <v>One Bowerman Dr, BEAVERTON, OR, 97005-6453 US</v>
     <v>NKE</v>
     <v>Acciones</v>
     <v>NIKE, INC. (XNYS:NKE)</v>
-    <v>20081618</v>
+    <v>21634552</v>
     <v>24193538</v>
   </rv>
   <rv s="2">
@@ -11916,7 +11946,7 @@
     <v>Mips AB is a Sweden-based company, which specializes in helmet safety and brain protection. The Company offers its MIPS Brain Protection System (BPS) that implies solutions protecting against rotational motion transferred to the brain from angled impacts to the head. BPS is designed to add protection in helmets due to the low friction layer, which enables a relative movement between the head and the helmet, mimicking the brain’s own protection system. The technology implements into bicycle, snow, motorcycle and equestrian helmets. More than 40 helmet brands use BPS, including Bell, Fox Head, Giro, Scott, Smith and Trek, among others. The Company determines only one segment as operations solely comprise sales of the component kit included in consumer products.</v>
     <v>127</v>
     <v>XSTO</v>
-    <v>46260.645694444444</v>
+    <v>46260.666666666664</v>
     <v>NASDAQ Stockholm</v>
     <v>146</v>
     <v>366.8</v>
@@ -11960,14 +11990,14 @@
     <v>2024</v>
     <v>233.255</v>
     <v>1.117</v>
-    <v>3.28</v>
-    <v>1.4097E-2</v>
-    <v>45645164565</v>
+    <v>2.95</v>
+    <v>1.2679000000000001E-2</v>
+    <v>45581325174</v>
     <v>232.67</v>
     <v>Ferguson Enterprises Inc. Es un distribuidor de valor agregado que sirve a profesionales especializados en el mercado de la construcción residencial y no residencial de América del Norte. Los segmentos geográficos de la Compañía incluyen Estados Unidos y Canadá. La Compañía ofrece una amplia gama de productos y servicios, tales como plomería, calefacción, ventilación y aire acondicionado (HVAC), electrodomésticos e iluminación para tuberías, válvulas y accesorios (PVF), soluciones de agua y aguas residuales, y más. Se vende a través de una red común de centros de distribución, sucursales, servicio de mostrador y asociados de ventas especializados, consultores de showroom y canales de comercio electrónico. La compañía sirve a diversas industrias, tales como plomería, HVAC, comercial / mecánica, suministro de instalaciones, fuego y fabricación, industrial, constructor, obras de agua. Las marcas de la compañía incluyen Armateck, Durastar, FNW, National Fire Products, Pollardwater, PROFLO, PROSELECT, Raptor, Hardware de firma y Westcraft.</v>
     <v>35000</v>
     <v>XNYS</v>
-    <v>46260.660660312496</v>
+    <v>46260.681221423438</v>
     <v>New York Stock Exchange</v>
     <v>149</v>
     <v>240.48</v>
@@ -11977,14 +12007,14 @@
     <v>USD</v>
     <v>FERGUSON ENTERPRISES INC.</v>
     <v>FERGUSON ENTERPRISES INC.</v>
-    <v>23.218599999999999</v>
-    <v>235.95</v>
+    <v>23.186199999999999</v>
+    <v>235.62</v>
     <v>Homebuilding &amp; Construction Supplies</v>
     <v>751 Lakefront Commons, NEWPORT NEWS, VA, 23606 US</v>
     <v>FERG</v>
     <v>Acciones</v>
     <v>FERGUSON ENTERPRISES INC. (XNYS:FERG)</v>
-    <v>377465</v>
+    <v>470989</v>
     <v>3789521</v>
   </rv>
   <rv s="2">
@@ -12012,14 +12042,14 @@
     <v>2013</v>
     <v>20.07</v>
     <v>0.75890000000000002</v>
-    <v>0.08</v>
-    <v>3.9389999999999998E-3</v>
-    <v>6989767443</v>
+    <v>9.5000000000000001E-2</v>
+    <v>4.6769999999999997E-3</v>
+    <v>6994909498</v>
     <v>20.309999999999999</v>
     <v>SentinelOne, Inc. Es un proveedor de ciberseguridad impulsado por inteligencia artificial (IA). La Plataforma Singularity de la compañía ofrece capacidades autónomas de prevención, detección, respuesta y administración de exposición de amenazas impulsadas por IA en los endpoints, cargas de trabajo en la nube y credenciales de identidad de una organización. La plataforma Singularity de la compañía ingiere, correlaciona y consulta petabytes de datos estructurados y no estructurados de una miríada de fuentes externas e internas dispares en constante expansión en tiempo real. Sus modelos de IA distribuida se ejecutan tanto localmente en cada endpoint y cada carga de trabajo en la nube, así como en su plataforma en la nube. La compañía a través de PingSafe Pte. Ltd. (PingSafe), que es una plataforma de protección de aplicaciones nativa en la nube (CNAPP) para reforzar su paquete de productos de seguridad en la nube. Al agregar CNAPP de PingSafe a su Cloud Workload Security (CWS), proporciona a las empresas una cobertura de seguridad en la nube integral que impulsa la seguridad, la postura mejorada y la protección autónoma.</v>
     <v>2700</v>
     <v>XNYS</v>
-    <v>46260.660583471872</v>
+    <v>46260.681148251562</v>
     <v>New York Stock Exchange</v>
     <v>152</v>
     <v>20.605</v>
@@ -12030,13 +12060,13 @@
     <v>SENTINELONE, INC.</v>
     <v>SENTINELONE, INC.</v>
     <v>0</v>
-    <v>20.39</v>
+    <v>20.405000000000001</v>
     <v>Software &amp; IT Services</v>
     <v>444 Castro Street, Suite 400, MOUNTAIN VIEW, CA, 94041 US</v>
     <v>S</v>
     <v>Acciones</v>
     <v>SENTINELONE, INC. (XNYS:S)</v>
-    <v>1528709</v>
+    <v>1718482</v>
     <v>6410105</v>
   </rv>
   <rv s="2">
@@ -12064,14 +12094,14 @@
     <v>1998</v>
     <v>47.2</v>
     <v>1.4735</v>
-    <v>0.28499999999999998</v>
-    <v>6.0850000000000001E-3</v>
-    <v>4800397550</v>
+    <v>0.245</v>
+    <v>5.2310000000000004E-3</v>
+    <v>4796322942</v>
     <v>46.84</v>
     <v>Trex Company, Inc. Es un fabricante de terrazas alternativas de madera y barandillas residenciales y productos y accesorios para vivir al aire libre, comercializados bajo la marca Trex. El segmento de la compañía es Trex Residential. Sus categorías de productos incluyen cubiertas y accesorios, barandillas y cercas. Sus productos de terrazas están hechos en un proceso patentado que combina fibras de madera recuperadas y película de polietileno reciclado. Sus cubiertas y accesorios incluyen cubiertas Trex Signature, cubiertas Trex Transcend Lineage, cubiertas Trex Transcend, cubiertas Trex Select, cubiertas Trex Enhance, colección de sujetadores Trex Hideaway y sistema de iluminación exterior Trex DeckLighting. Su producto de decking Trex Transcend también se puede utilizar como revestimiento. Sus productos de barandilla incluyen barandilla Trex Signature X-Series, barandilla de aluminio Trex Signature, barandilla Trex Transcend, barandilla Trex Select, carril T Trex Select y barandilla Trex Enhance. Su producto compuesto de esgrima Trex Seclusions se ofrece a través de dos distribuidores especializados.</v>
     <v>1839</v>
     <v>XNYS</v>
-    <v>46260.660524154686</v>
+    <v>46260.681206735935</v>
     <v>New York Stock Exchange</v>
     <v>155</v>
     <v>47.54</v>
@@ -12081,14 +12111,14 @@
     <v>USD</v>
     <v>TREX COMPANY, INC.</v>
     <v>TREX COMPANY, INC.</v>
-    <v>27.812200000000001</v>
-    <v>47.125</v>
+    <v>27.788599999999999</v>
+    <v>47.085000000000001</v>
     <v>Homebuilding &amp; Construction Supplies</v>
     <v>2500 TREX WAY, WINCHESTER, VA, 22601 US</v>
     <v>TREX</v>
     <v>Acciones</v>
     <v>TREX COMPANY, INC. (XNYS:TREX)</v>
-    <v>137668</v>
+    <v>163938</v>
     <v>2005414</v>
   </rv>
   <rv s="2">
@@ -12098,32 +12128,34 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=aea12w&amp;q=XPAR%3aSGO&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="12">
+  <rv s="6">
     <v>es-ES</v>
     <v>aea12w</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
-    <v>45</v>
-    <v>46</v>
+    <v>18</v>
+    <v>19</v>
     <v>Compagnie de Saint Gobain SA (XPAR:SGO)</v>
     <v>3</v>
-    <v>47</v>
+    <v>45</v>
     <v>Finance</v>
-    <v>48</v>
+    <v>28</v>
     <v>XPAR</v>
     <v>494834000</v>
     <v>1981</v>
     <v>81.88</v>
     <v>1.4025000000000001</v>
     <v>1.04</v>
+    <v>-1.944E-3</v>
     <v>1.2798E-2</v>
+    <v>-0.16</v>
     <v>40210210000</v>
     <v>81.260000000000005</v>
     <v>Compagnie de Saint Gobain SA es un grupo con sede en Francia especializado en el diseño, fabricación, distribución de materiales para la construcción, la movilidad, la salud y soluciones industriales con el objetivo de mejorar el bienestar de la vida en todo el mundo. El Grupo, a través de sus filiales, opera a través de tres sectores: Distribución de Edificios (BD), Productos de Construcción (CP) y Materiales (IM). El sector BD cubre las actividades de distribución de la Compañía a los proveedores. El sector CP ofrece tanto soluciones interiores (aislantes y yeso) como soluciones exteriores (morteros industriales, tuberías y productos exteriores). El sector IM proporciona vidrio plano y materiales de alto rendimiento. Sus soluciones abarcan desde ventanas autolimpiables y vidrio fotovoltaico hasta sistemas de aislamiento inteligentes, sistemas de suministro de agua con muchas aplicaciones industriales.</v>
     <v>161688</v>
     <v>XPAR</v>
-    <v>46260.649548611109</v>
+    <v>46260.666666666664</v>
     <v>Euronext Paris</v>
     <v>158</v>
     <v>83.14</v>
@@ -12176,7 +12208,7 @@
     <v>Tonnellerie Francois Freres SA, formerly Tonnellerie Francois Freres SA, is a France-based company that manufactures and distributes oak barrels that are used to conserve and transport liquids. The Company has four core businesses: stave milling, cooperage, cask manufacturing and oak wine-aging products. Tonnellerie Francois Freres SA also offers oak products for oenology, where the wine is put in contact with wood in varied forms and has developed products for the alcohol maturing and aging market, especially the whisky market. The Company offers four brands of barrels: Exclusif, Privilege, Classique and Horizon. The Company operated through its subsidiaries, including Sogibois, Bouyoud, Treuil, Francois Inc, Classic Oak New Zealand, Demptos Napa, among others. The Company has operating units in France, the United States, Spain, Hungary, South Africa, China, New Zealand, Australia and Ireland.</v>
     <v>1613</v>
     <v>XPAR</v>
-    <v>46260.649340277778</v>
+    <v>46260.666666666664</v>
     <v>Euronext Paris</v>
     <v>161</v>
     <v>16.68</v>
@@ -12221,14 +12253,14 @@
     <v>2005</v>
     <v>35.26</v>
     <v>0.93740000000000001</v>
-    <v>-0.47770000000000001</v>
-    <v>-1.3517E-2</v>
-    <v>8821382080</v>
+    <v>-0.52</v>
+    <v>-1.4714E-2</v>
+    <v>8810678700</v>
     <v>35.340000000000003</v>
     <v>Celsius Holdings, Inc. Se dedica al desarrollo, procesamiento, comercialización, venta y distribución de bebidas energéticas funcionales a una amplia gama de consumidores. El activo insignia de la Compañía, CELSIUS, se comercializa como un estilo de vida y bebida energética. Esta línea de productos viene en dos versiones: Una forma lista para beber y una forma de polvo en movimiento. También ofrece una nueva línea CELSIUS Essentials, disponible en latas de 16 onzas y una línea de hidratación de polvos con cero azúcar que se infunden con electrolitos y están disponibles en una variedad de sabores frutales. Los productos Celsius se ofrecen en canales minoristas a través de los Estados Unidos, incluyendo comestibles convencionales, naturales, conveniencia, fitness, etc. mercado masivo, especialidad de vitaminas y plataformas de comercio electrónico. Sus productos también se ofrecen en mercados seleccionados de Europa, Oriente Medio y la región de Asia-Pacífico. La formulación de su producto incluye ingredientes y suplementos como el té verde (EGCG), jengibre (de la raíz), calcio, cromo, vitaminas B y vitamina C.</v>
     <v>1497</v>
     <v>XNAS</v>
-    <v>46260.660645346878</v>
+    <v>46260.681216700781</v>
     <v>Nasdaq Stock Market</v>
     <v>164</v>
     <v>36.130000000000003</v>
@@ -12238,14 +12270,14 @@
     <v>USD</v>
     <v>CELSIUS HOLDINGS, INC.</v>
     <v>CELSIUS HOLDINGS, INC.</v>
-    <v>149.8809</v>
-    <v>34.862299999999998</v>
+    <v>149.69909999999999</v>
+    <v>34.82</v>
     <v>Beverages</v>
     <v>2424 N. Federal Hwy, Suite 208, BOCA RATON, FL, 33431 US</v>
     <v>CELH</v>
     <v>Acciones</v>
     <v>CELSIUS HOLDINGS, INC. (XNAS:CELH)</v>
-    <v>3009229</v>
+    <v>3304558</v>
     <v>12453304</v>
   </rv>
   <rv s="2">
@@ -12280,7 +12312,7 @@
     <v>Basic-Fit N.V. es una compañía con sede en Holanda que es propietario de una red de gimnasios en la industria del fitness. La compañía ofrece una variedad de opciones de membresía, adaptadas a las necesidades individuales. Basic-Fit desarrolló una aplicación de fitness que ofrece consejos de nutrición, lecciones grupales virtuales y programas de entrenamiento para diversas necesidades o poblaciones. La aplicación ofrece seguimiento de los servicios de progreso de la capacitación.</v>
     <v>9432</v>
     <v>XAMS</v>
-    <v>46260.649357071095</v>
+    <v>46260.666666666664</v>
     <v>Euronext Amsterdam</v>
     <v>167</v>
     <v>33.96</v>
@@ -12307,17 +12339,17 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=bscvur&amp;q=XWBO%3aVRLA&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="13">
+  <rv s="12">
     <v>es-ES</v>
     <v>bscvur</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
-    <v>49</v>
-    <v>50</v>
+    <v>46</v>
+    <v>47</v>
     <v>Verallia SA (XWBO:VRLA)</v>
     <v>3</v>
-    <v>51</v>
+    <v>48</v>
     <v>Finance</v>
     <v>13</v>
     <v>XWBO</v>
@@ -12466,7 +12498,7 @@
     <v>1</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION (XTSE:IPCO)</v>
     <v>3</v>
-    <v>52</v>
+    <v>49</v>
     <v>Finance</v>
     <v>41</v>
     <v>XTSE</v>
@@ -12474,31 +12506,31 @@
     <v>2017</v>
     <v>34.4</v>
     <v>0.3357</v>
-    <v>0.18</v>
-    <v>5.1739999999999998E-3</v>
+    <v>0.56000000000000005</v>
+    <v>1.6097E-2</v>
     <v>26955180000</v>
     <v>34.79</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION es una compañía spin-off con sede en Canadá para activos no noruegos de Lundin Petroleum AB. La Compañía se dedica a la producción y exploración de petróleo y gas natural, así como a líquidos de gas natural. La Compañía es propietaria directa o indirecta de varias subsidiarias de Lundin Petroleum AB. La Compañía tiene una cartera de activos en tres jurisdicciones: Malasia (Bertam), Francia (París y Cuenca de Aquitania) y los Países Bajos. La cartera está orientada hacia el petróleo ligero, con líquidos que representan el 94% de las reservas 2P y con la producción de gas generada principalmente a partir de los activos de petróleo y gas en los Países Bajos. La Compañía opera la mayoría de sus volúmenes producidos en la Cuenca de París y Malasia y posee intereses no operados en la Cuenca de Aquitania y los Países Bajos.</v>
     <v>131</v>
     <v>XTSE</v>
-    <v>46260.649988425925</v>
+    <v>46260.666585648149</v>
     <v>Toronto Stock Exchange</v>
     <v>178</v>
-    <v>35.06</v>
+    <v>35.35</v>
     <v>39.47</v>
     <v>34.369999999999997</v>
     <v>20.74</v>
     <v>CAD</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION</v>
-    <v>133.7285</v>
-    <v>34.97</v>
+    <v>135.1816</v>
+    <v>35.35</v>
     <v>Oil &amp; Gas</v>
     <v>Suite 2800, 1055 Dunsmuir Street, VANCOUVER, BC, V7X 1L2 CA</v>
     <v>IPCO</v>
     <v>Acciones</v>
     <v>INTERNATIONAL PETROLEUM CORPORATION (XTSE:IPCO)</v>
-    <v>49593</v>
+    <v>53873</v>
     <v>151110</v>
   </rv>
   <rv s="2">
@@ -12526,31 +12558,31 @@
     <v>2016</v>
     <v>15.31</v>
     <v>1.8140000000000001</v>
-    <v>-0.28000000000000003</v>
-    <v>-1.8134999999999998E-2</v>
-    <v>483789861</v>
+    <v>-0.375</v>
+    <v>-2.4287999999999997E-2</v>
+    <v>480758196</v>
     <v>15.44</v>
     <v>Oatly Group AB (publ) is a Sweden-based company that is primarily focused on manufacture, distribution and sale oat-based products. The Company's scope of activity concentrates on developing the know-how around oats, and what follows - the alternatives to milk, ice cream, yogurt, cooking creams, spreads and on-the-go drinks. Moreover, the Company distributes their oat-based dairy substitute products primarily under its own brand, Oatly. Apart from oatmilk production, Oatly Group AB (publ) also handles the administration of Oatly Group and its financing. The major operations in the Group take place in underlying companies, primarily in Oatly AB. Oatly Group AB (publ) products are available in over 20 countries.</v>
     <v>1404</v>
     <v>XNAS</v>
-    <v>46260.659979189062</v>
+    <v>46260.681092303123</v>
     <v>Nasdaq Stock Market</v>
     <v>181</v>
     <v>15.48</v>
     <v>18.84</v>
-    <v>15.03</v>
+    <v>15.02</v>
     <v>8.01</v>
     <v>USD</v>
     <v>Oatly Group</v>
     <v>Oatly Group</v>
     <v>0</v>
-    <v>15.16</v>
+    <v>15.065</v>
     <v>Food &amp; Tobacco</v>
     <v>Angfarjekajen 8, MALMO, SKANE, 211 36 SE</v>
     <v>OTLY</v>
     <v>Acciones</v>
     <v>Oatly Group (XNAS:OTLY)</v>
-    <v>23926</v>
+    <v>25215</v>
     <v>205032</v>
   </rv>
   <rv s="2">
@@ -12578,31 +12610,31 @@
     <v>2002</v>
     <v>3078.66</v>
     <v>0.69210000000000005</v>
-    <v>-13.11</v>
-    <v>-4.2580000000000005E-3</v>
-    <v>64963694791</v>
+    <v>-18</v>
+    <v>-5.8469999999999998E-3</v>
+    <v>64860068209</v>
     <v>3078.66</v>
     <v>Constellation Software Inc. Es un proveedor de software y servicios con sede en Canadá para varias industrias. La Compañía adquiere, administra y construye negocios de software de mercado vertical (VMS) que proporcionan soluciones de software de misión crítica. Se dedica principalmente al desarrollo, instalación y personalización de software, así como en el suministro de servicios profesionales relacionados y soporte para clientes de todo el mundo. Sus servicios profesionales incluyen la instalación, implementación, capacitación y personalización de software y otros servicios. La Compañía vende licencias de software en las instalaciones tanto a perpetuo como a plazo especificado. Cuenta con seis grupos operativos, que dan servicio a clientes en más de 100 mercados diferentes en todo el mundo. Los seis grupos operativos incluyen Volaris, Harris, Topicus.com, Vela, Jonas, y Grupo Perseus. Opera oficinas en América del Norte, Europa Continental, Reino Unido, América del Sur, África, y Australia.</v>
     <v>64000</v>
     <v>XTSE</v>
-    <v>46260.647662037038</v>
+    <v>46260.669479166667</v>
     <v>Toronto Stock Exchange</v>
     <v>184</v>
     <v>3114.97</v>
     <v>4634.9799999999996</v>
-    <v>3065.14</v>
+    <v>3060.66</v>
     <v>2196</v>
     <v>CAD</v>
     <v>Constellation Software Inc.</v>
     <v>Constellation Software Inc.</v>
-    <v>47.622500000000002</v>
-    <v>3065.55</v>
+    <v>47.546500000000002</v>
+    <v>3060.66</v>
     <v>Software &amp; IT Services</v>
     <v>#66 Wellington Street West, Suite 5300, TD Bank Tower, TORONTO, ON, M5K 1E6 CA</v>
     <v>CSU</v>
     <v>Acciones</v>
     <v>Constellation Software Inc. (XTSE:CSU)</v>
-    <v>18776</v>
+    <v>20034</v>
     <v>51380</v>
   </rv>
   <rv s="2">
@@ -12630,31 +12662,31 @@
     <v>2010</v>
     <v>81.59</v>
     <v>1.1668000000000001</v>
-    <v>-0.64</v>
-    <v>-7.9649999999999999E-3</v>
-    <v>162812457600</v>
+    <v>-0.82</v>
+    <v>-1.0204999999999999E-2</v>
+    <v>162444796800</v>
     <v>80.349999999999994</v>
     <v>Uber Technologies, Inc. Opera una plataforma tecnológica que utiliza redes y tecnología para impulsar el movimiento desde el punto A al punto B. Desarrolla y opera aplicaciones tecnológicas que soportan una variedad de ofertas en su plataforma (plataforma(s)). Sus segmentos incluyen Movilidad, Entrega y Carga. Los productos de movilidad conectan a los consumidores con conductores que ofrecen viajes en una variedad de vehículos, como automóviles, rickshaws de automóviles, motos, minibuses, etc. o taxis. Las ofertas de entrega permiten a los consumidores buscar y descubrir restaurantes locales, pedir una comida y recoger en el restaurante o hacer que se les entregue la comida. En ciertos mercados, el segmento de Entrega ofrece ofertas para la entrega de comestibles, alcohol y tiendas de conveniencia, así como otros productos seleccionados. El segmento de carga conecta a los transportistas con los transportistas en su plataforma, y ofrece a los transportistas por adelantado, precios y la capacidad de reservar un envío. El segmento de carga también incluye la gestión del transporte y otras ofertas de servicios logísticos.</v>
     <v>34000</v>
     <v>XNYS</v>
-    <v>46260.660665416406</v>
+    <v>46260.681210242969</v>
     <v>New York Stock Exchange</v>
     <v>187</v>
     <v>82.364999999999995</v>
     <v>101.99</v>
-    <v>79.599999999999994</v>
+    <v>79.48</v>
     <v>65.41</v>
     <v>USD</v>
     <v>UBER TECHNOLOGIES, INC.</v>
     <v>UBER TECHNOLOGIES, INC.</v>
-    <v>17.4971</v>
-    <v>79.709999999999994</v>
+    <v>17.457599999999999</v>
+    <v>79.53</v>
     <v>Software &amp; IT Services</v>
     <v>1725 3Rd Street, SAN FRANCISCO, CA, 94158 US</v>
     <v>UBER</v>
     <v>Acciones</v>
     <v>UBER TECHNOLOGIES, INC. (XNYS:UBER)</v>
-    <v>6032279</v>
+    <v>6554391</v>
     <v>19900197</v>
   </rv>
   <rv s="2">
@@ -12664,17 +12696,17 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=aodtkr&amp;q=XLON%3aSOM&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="14">
+  <rv s="13">
     <v>es-ES</v>
     <v>aodtkr</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
-    <v>53</v>
-    <v>54</v>
+    <v>50</v>
+    <v>51</v>
     <v>Somero (XLON:SOM)</v>
     <v>3</v>
-    <v>55</v>
+    <v>52</v>
     <v>Finance</v>
     <v>17</v>
     <v>XLON</v>
@@ -12738,7 +12770,7 @@
     <v>Interpump Group SpA es una empresa con sede en Italia que fabrica y comercializa bombas de émbolo de alta y muy alta presión, sistemas de muy alta presión, tomas de fuerza, bombas de engranajes, cilindros hidráulicos, controles direccionales, válvulas, mangueras y accesorios hidráulicos, y otros productos hidráulicos. Opera a través de dos segmentos: el Sector Hidráulico y el Sector de Chorro de Agua. El Sector Hidráulico incluye la producción y venta de tomas de fuerza para vehículos industriales, cilindros, bombas, válvulas, mangueras y otros accesorios hidráulicos bajo marcas como Hydrocar, PZB, Muncie, Penta entre otras. El Sector de Chorro de Agua está formado por bombas y sistemas de bombeo de alta y muy alta presión utilizados en diversos sectores industriales para el transporte de fluidos. Este sector además fabrica componentes y sistemas para la industria alimentaria, cosmética y farmacéutica bajo las marcas Bertoli, Inoxpa y Mariotti &amp; Pecini. La Empresa opera a través del sistema de fluido 80.</v>
     <v>9712</v>
     <v>XMIL</v>
-    <v>46260.649488541407</v>
+    <v>46260.666666666664</v>
     <v>Borsa Italiana</v>
     <v>193</v>
     <v>37.94</v>
@@ -12790,7 +12822,7 @@
     <v>Robertet SA is a France-based holding company engaged in the production and distribution of flavor and perfume additives and ingredients. The Company's operations are conducted through three divisions: Raw Materials, which supplies ingredients to the cosmetics industry for products such as soaps, shampoos, and other beauty products, as well as air fresheners; Fragrance, providing ingredients that go into the creations of a number of perfumes and scents, and flavours, including products for food and beverage industries. The Company operates globally through a network of subsidiaries, including Bionov, Robertet GmbH, Robertet Argentina, Robertet Do Brasil, Robertet Hiyoki, Robertet Turkey, Robertet de Mexico, Robertet USA, Robertet Italia, Robertet Savoury, and Aroma Esencial Sl, among others.</v>
     <v>2750</v>
     <v>XPAR</v>
-    <v>46260.649421399998</v>
+    <v>46260.666666666664</v>
     <v>Euronext Paris</v>
     <v>196</v>
     <v>813</v>
@@ -12813,14 +12845,14 @@
   <rv s="2">
     <v>197</v>
   </rv>
-  <rv s="15">
+  <rv s="14">
     <v>es-ES</v>
     <v>cg32pr</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
-    <v>56</v>
-    <v>57</v>
+    <v>53</v>
+    <v>54</v>
     <v>Roko (XSTO:ROKO B)</v>
     <v>26</v>
     <v>44</v>
@@ -12840,7 +12872,7 @@
     <v>Roko AB (publ) is a Sweden-based company primarily engaged in the investment and risk capital industry. The Company focuses on acquiring and managing small- and medium-sized profitable businesses across Europe. Their key product is equity capital investment, which is a financial service.</v>
     <v>1829</v>
     <v>XSTO</v>
-    <v>46260.645555555559</v>
+    <v>46260.666666666664</v>
     <v>NASDAQ Stockholm</v>
     <v>1904</v>
     <v>1870</v>
@@ -12883,14 +12915,14 @@
     <v>1992</v>
     <v>77.17</v>
     <v>1.1251</v>
-    <v>1.23</v>
-    <v>1.5907999999999999E-2</v>
-    <v>1172178085</v>
+    <v>0.96</v>
+    <v>1.2416E-2</v>
+    <v>1168148956</v>
     <v>77.319999999999993</v>
     <v>U.S. Physical Therapy, Inc. is an operator of outpatient physical therapy clinics and provider of industrial injury prevention services. It owns and/or manages 795 outpatient physical therapy clinics in 45 states. Its reportable segments include the Physical Therapy Operations segment and the Industrial Injury Prevention Services (IIP) segment. The Physical Therapy Operations segment consists of physical therapy, speech therapy and occupational therapy clinics and home-care physical and speech therapy practices that provide pre- and post-operative care and treatment for a variety of orthopedic-related disorders, sports-related injuries, and rehabilitation of injured workers. The IIP segment includes onsite services for clients’ employees, including injury prevention and rehabilitation, performance optimization, post-offer employment testing, functional capacity evaluations and ergonomic assessments. The majority of these services are contracted with and paid for directly by employers.</v>
     <v>4200</v>
     <v>XNYS</v>
-    <v>46260.660501435159</v>
+    <v>46260.681174814061</v>
     <v>New York Stock Exchange</v>
     <v>201</v>
     <v>79</v>
@@ -12900,14 +12932,14 @@
     <v>USD</v>
     <v>US Physical</v>
     <v>US Physical</v>
-    <v>447.06889999999999</v>
-    <v>78.55</v>
+    <v>445.53219999999999</v>
+    <v>78.28</v>
     <v>Healthcare Providers &amp; Services</v>
     <v>1300 West Sam Houston Parkway South, Suite 300, HOUSTON, TX, 77043 US</v>
     <v>USPH</v>
     <v>Acciones</v>
     <v>US Physical (XNYS:USPH)</v>
-    <v>67004</v>
+    <v>78257</v>
     <v>236554</v>
   </rv>
   <rv s="2">
@@ -12942,7 +12974,7 @@
     <v>SAP SE (SAP) es una empresa alemana de software de aplicaciones. La compañía opera a través de dos segmentos: el segmento de Aplicaciones, Tecnología y Soporte (ATS) y su segmento de Servicios Centrales. El segmento ATS abarca el portafolio integrado de productos de la compañía e incluye ofertas de suscripción en la nube, servicios de soporte y soluciones de capacitación. También comprende actividades relacionadas con la operación de tecnologías en la nube y la prestación de soporte al cliente asociado con sus productos de software. El segmento de Servicios Centrales complementa el portafolio de productos de la compañía mediante la entrega de servicios de consultoría y soporte premium para ayudar a los clientes a adoptar sus innovaciones. Los ingresos de este segmento provienen principalmente de servicios profesionales y ofertas de soporte mejoradas, mientras que los costos surgen de la ejecución de estas actividades de servicio.</v>
     <v>112019</v>
     <v>XETR</v>
-    <v>46260.650231481479</v>
+    <v>46260.670752314814</v>
     <v>Xetra</v>
     <v>204</v>
     <v>182.16</v>
@@ -12959,7 +12991,7 @@
     <v>SAP</v>
     <v>Acciones</v>
     <v>SAP SE (XETR:SAP)</v>
-    <v>3642348</v>
+    <v>3647747</v>
     <v>1895750</v>
   </rv>
   <rv s="2">
@@ -12987,14 +13019,14 @@
     <v>2018</v>
     <v>83.295000000000002</v>
     <v>0.57399999999999995</v>
-    <v>-0.38</v>
-    <v>-4.5760000000000002E-3</v>
-    <v>55157093320</v>
+    <v>0.03</v>
+    <v>3.612E-4</v>
+    <v>55430643680</v>
     <v>83.05</v>
     <v>Corteva, Inc. Es una compañía global de agricultura de juego puro. Es un proveedor global de soluciones de protección de semillas y cultivos enfocadas en la industria agrícola y contribuyendo a un suministro de alimentos más saludable, seguro y sostenible. El segmento de semillas se dedica al desarrollo y suministro de semillas comerciales que combinan germoplasma avanzado y rasgos que producen un rendimiento óptimo para las granjas de todo el mundo. Opera en varios mercados clave de semillas, incluyendo maíz y soja de América del Norte, maíz y girasol europeos, así como maíz de Brasil, India, Sudáfrica y Argentina. El segmento de protección de cultivos sirve a la industria mundial de insumos agrícolas con productos que protegen contra malezas, insectos y otras plagas, y enfermedades, y que apoyan la salud general de los cultivos tanto en el suelo como en el subsuelo a través de la gestión del nitrógeno y las tecnologías aplicadas a las semillas. Sus soluciones de protección de cultivos y soluciones digitales proporcionan a los agricultores herramientas para mejorar la productividad y ayudar a mantener los campos libres de malezas, insectos y enfermedades.</v>
     <v>21500</v>
     <v>XNYS</v>
-    <v>46260.660743193752</v>
+    <v>46260.681177476559</v>
     <v>New York Stock Exchange</v>
     <v>207</v>
     <v>84.6</v>
@@ -13004,45 +13036,45 @@
     <v>USD</v>
     <v>CORTEVA, INC.</v>
     <v>CORTEVA, INC.</v>
-    <v>50.842599999999997</v>
-    <v>82.67</v>
+    <v>51.094700000000003</v>
+    <v>83.08</v>
     <v>Chemicals</v>
     <v>9330 ZIONSVILLE ROAD, INDIANAPOLIS, IN, 46268 US</v>
     <v>CTVA</v>
     <v>Acciones</v>
     <v>CORTEVA, INC. (XNYS:CTVA)</v>
-    <v>911147</v>
+    <v>1113450</v>
     <v>4814695</v>
   </rv>
   <rv s="2">
     <v>208</v>
   </rv>
-  <rv s="16">
+  <rv s="15">
     <v>es-ES</v>
     <v>av8wim</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
+    <v>55</v>
+    <v>56</v>
+    <v>EUR/JPY</v>
+    <v>57</v>
     <v>58</v>
+    <v>Finance</v>
     <v>59</v>
-    <v>EUR/JPY</v>
-    <v>60</v>
-    <v>61</v>
-    <v>Finance</v>
-    <v>62</v>
     <v>185.8</v>
-    <v>-0.12</v>
-    <v>-6.4600000000000009E-4</v>
+    <v>-0.15</v>
+    <v>-8.0750000000000006E-4</v>
     <v>185.77</v>
     <v>EUR</v>
-    <v>46260.66064814815</v>
+    <v>46260.681168981479</v>
     <v>185.91</v>
     <v>187.93</v>
     <v>185.37</v>
     <v>171.07</v>
     <v>JPY</v>
     <v>Euro/Japanese Yen FX Cross Rate</v>
-    <v>185.65</v>
+    <v>185.62</v>
     <v>EURJPY</v>
     <v>Par de divisa</v>
     <v>EUR/JPY</v>
@@ -13050,32 +13082,32 @@
   <rv s="2">
     <v>210</v>
   </rv>
-  <rv s="16">
+  <rv s="15">
     <v>es-ES</v>
     <v>avv7r7</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
-    <v>58</v>
+    <v>55</v>
+    <v>56</v>
+    <v>CHF/USD</v>
+    <v>57</v>
+    <v>60</v>
+    <v>Finance</v>
     <v>59</v>
-    <v>CHF/USD</v>
-    <v>60</v>
-    <v>63</v>
-    <v>Finance</v>
-    <v>62</v>
     <v>1.2472000000000001</v>
-    <v>-6.1999999999999998E-3</v>
-    <v>-4.9690000000000003E-3</v>
+    <v>-6.1000000000000004E-3</v>
+    <v>-4.8890000000000001E-3</v>
     <v>1.2477</v>
     <v>CHF</v>
-    <v>46260.660601851851</v>
+    <v>46260.681238425925</v>
     <v>1.2484</v>
     <v>1.3149</v>
     <v>1.2403999999999999</v>
     <v>1.2181999999999999</v>
     <v>USD</v>
     <v>Swiss Franc/US Dollar FX Cross Rate</v>
-    <v>1.2415</v>
+    <v>1.2416</v>
     <v>CHFUSD</v>
     <v>Par de divisa</v>
     <v>CHF/USD</v>
@@ -13083,32 +13115,32 @@
   <rv s="2">
     <v>212</v>
   </rv>
-  <rv s="16">
+  <rv s="15">
     <v>es-ES</v>
     <v>avyosm</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
-    <v>58</v>
+    <v>55</v>
+    <v>56</v>
+    <v>USD/KZT</v>
+    <v>57</v>
+    <v>61</v>
+    <v>Finance</v>
     <v>59</v>
-    <v>USD/KZT</v>
-    <v>60</v>
-    <v>64</v>
-    <v>Finance</v>
-    <v>62</v>
     <v>457.82</v>
-    <v>1.43</v>
-    <v>3.1230000000000003E-3</v>
+    <v>1.4</v>
+    <v>3.058E-3</v>
     <v>457.83</v>
     <v>USD</v>
-    <v>46260.660613425927</v>
+    <v>46260.681157407409</v>
     <v>460.65</v>
     <v>549.66</v>
     <v>457.34</v>
     <v>453.81</v>
     <v>KZT</v>
     <v>US Dollar/Kazakhstan Tenge FX Spot Rate</v>
-    <v>459.26</v>
+    <v>459.23</v>
     <v>USDKZT</v>
     <v>Par de divisa</v>
     <v>USD/KZT</v>
@@ -13116,32 +13148,32 @@
   <rv s="2">
     <v>214</v>
   </rv>
-  <rv s="16">
+  <rv s="15">
     <v>es-ES</v>
     <v>av3wnm</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
-    <v>58</v>
+    <v>55</v>
+    <v>56</v>
+    <v>CAD/USD</v>
+    <v>57</v>
+    <v>60</v>
+    <v>Finance</v>
     <v>59</v>
-    <v>CAD/USD</v>
-    <v>60</v>
-    <v>63</v>
-    <v>Finance</v>
-    <v>62</v>
     <v>0.72250000000000003</v>
-    <v>-2.2000000000000001E-3</v>
-    <v>-3.045E-3</v>
+    <v>-1.6999999999999999E-3</v>
+    <v>-2.3530000000000001E-3</v>
     <v>0.72250000000000003</v>
     <v>CAD</v>
-    <v>46260.660636574074</v>
+    <v>46260.681180555555</v>
     <v>0.72299999999999998</v>
     <v>0.74170000000000003</v>
     <v>0.7198</v>
     <v>0.70169999999999999</v>
     <v>USD</v>
     <v>Canadian Dollar/US Dollar FX Cross Rate</v>
-    <v>0.72030000000000005</v>
+    <v>0.7208</v>
     <v>CADUSD</v>
     <v>Par de divisa</v>
     <v>CAD/USD</v>
@@ -13149,25 +13181,25 @@
   <rv s="2">
     <v>216</v>
   </rv>
-  <rv s="16">
+  <rv s="15">
     <v>es-ES</v>
     <v>avyn9c</v>
     <v>268435456</v>
     <v>1</v>
     <v>Con tecnología de Refinitiv</v>
-    <v>58</v>
+    <v>55</v>
+    <v>56</v>
+    <v>USD/EUR</v>
+    <v>57</v>
+    <v>62</v>
+    <v>Finance</v>
     <v>59</v>
-    <v>USD/EUR</v>
-    <v>60</v>
-    <v>65</v>
-    <v>Finance</v>
-    <v>62</v>
     <v>0.85650000000000004</v>
     <v>1.6000000000000001E-3</v>
     <v>1.8679999999999999E-3</v>
     <v>0.85650000000000004</v>
     <v>USD</v>
-    <v>46260.660590277781</v>
+    <v>46260.681168981479</v>
     <v>0.8589</v>
     <v>0.88300000000000001</v>
     <v>0.85640000000000005</v>
@@ -13186,7 +13218,7 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="17">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="16">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -13594,52 +13626,6 @@
     <k n="Intercambio" t="s"/>
     <k n="LearnMoreOnLink" t="r"/>
     <k n="Máximo"/>
-    <k n="Máximo en 52 semanas"/>
-    <k n="Mínimo"/>
-    <k n="Mínimo en 52 semanas"/>
-    <k n="Moneda" t="s"/>
-    <k n="Nombre" t="s"/>
-    <k n="Nombre oficial" t="s"/>
-    <k n="P/I"/>
-    <k n="Precio"/>
-    <k n="Precio (horario ampliado)"/>
-    <k n="Sector" t="s"/>
-    <k n="Sede central" t="s"/>
-    <k n="Símbolo bursátil" t="s"/>
-    <k n="Tipo de instrumento" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volumen"/>
-    <k n="Volumen promedio"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_CanonicalPropertyNames" t="spb"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="Abreviatura de intercambio" t="s"/>
-    <k n="Acciones en circulación"/>
-    <k n="Año de constitución"/>
-    <k n="Apertura"/>
-    <k n="Beta"/>
-    <k n="Cambio"/>
-    <k n="Cambio (%)"/>
-    <k n="Capitalización de mercado"/>
-    <k n="Cierre anterior"/>
-    <k n="Descripción" t="s"/>
-    <k n="Empleados"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Hora de la última operación"/>
-    <k n="Intercambio" t="s"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Máximo"/>
     <k n="Mínimo"/>
     <k n="Moneda" t="s"/>
     <k n="Nombre" t="s"/>
@@ -13777,7 +13763,7 @@
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="13">
+  <spbArrays count="12">
     <a count="43">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
@@ -14137,52 +14123,6 @@
       <v t="s">ExchangeID</v>
       <v t="s">%ProviderInfo</v>
     </a>
-    <a count="44">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">_CanonicalPropertyNames</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Nombre</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Precio</v>
-      <v t="s">Precio (horario ampliado)</v>
-      <v t="s">Intercambio</v>
-      <v t="s">Nombre oficial</v>
-      <v t="s">Hora de la última operación</v>
-      <v t="s">Símbolo bursátil</v>
-      <v t="s">Abreviatura de intercambio</v>
-      <v t="s">Cambio</v>
-      <v t="s">Cambio (%)</v>
-      <v t="s">Moneda</v>
-      <v t="s">Cierre anterior</v>
-      <v t="s">Apertura</v>
-      <v t="s">Máximo</v>
-      <v t="s">Mínimo</v>
-      <v t="s">Máximo en 52 semanas</v>
-      <v t="s">Mínimo en 52 semanas</v>
-      <v t="s">Volumen</v>
-      <v t="s">Volumen promedio</v>
-      <v t="s">Capitalización de mercado</v>
-      <v t="s">Beta</v>
-      <v t="s">P/I</v>
-      <v t="s">Acciones en circulación</v>
-      <v t="s">Descripción</v>
-      <v t="s">Empleados</v>
-      <v t="s">Sede central</v>
-      <v t="s">Sector</v>
-      <v t="s">Tipo de instrumento</v>
-      <v t="s">Año de constitución</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
     <a count="41">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
@@ -14345,7 +14285,7 @@
       <v t="s">%ProviderInfo</v>
     </a>
   </spbArrays>
-  <spbData count="66">
+  <spbData count="63">
     <spb s="0">
       <v>P/E</v>
       <v>Beta</v>
@@ -15063,47 +15003,7 @@
       <v>5</v>
       <v>9</v>
     </spb>
-    <spb s="28">
-      <v>P/E</v>
-      <v>Beta</v>
-      <v>Change</v>
-      <v>Currency</v>
-      <v>High</v>
-      <v>Low</v>
-      <v>Name</v>
-      <v>Price</v>
-      <v>Industry</v>
-      <v>Volume</v>
-      <v>Open</v>
-      <v>Employees</v>
-      <v>Change (%)</v>
-      <v>ExchangeID</v>
-      <v>UniqueName</v>
-      <v>Description</v>
-      <v>Exchange</v>
-      <v>Headquarters</v>
-      <v>%ProviderInfo</v>
-      <v>Official name</v>
-      <v>Previous close</v>
-      <v>LearnMoreOnLink</v>
-      <v>Ticker symbol</v>
-      <v>Volume average</v>
-      <v>Year incorporated</v>
-      <v>Instrument type</v>
-      <v>52 week high</v>
-      <v>52 week low</v>
-      <v>Shares outstanding</v>
-      <v>Market cap</v>
-      <v>Price (Extended hours)</v>
-      <v>Exchange abbreviation</v>
-      <v>Last trade time</v>
-    </spb>
-    <spb s="1">
-      <v>8</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="29">
+    <spb s="13">
       <v>1</v>
       <v>1</v>
       <v>11</v>
@@ -15122,18 +15022,13 @@
       <v>11</v>
       <v>11</v>
       <v>4</v>
+      <v>11</v>
       <v>12</v>
       <v>11</v>
+      <v>5</v>
       <v>9</v>
     </spb>
-    <spb s="30">
-      <v xml:space="preserve">desde el cierre anterior </v>
-      <v xml:space="preserve">al cierre </v>
-      <v xml:space="preserve">desde el cierre anterior </v>
-      <v>Retrasado 15 minutos</v>
-      <v>GMT</v>
-    </spb>
-    <spb s="31">
+    <spb s="28">
       <v>P/E</v>
       <v>Beta</v>
       <v>Change</v>
@@ -15166,11 +15061,11 @@
       <v>Last trade time</v>
     </spb>
     <spb s="1">
-      <v>9</v>
+      <v>8</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="32">
+    <spb s="29">
       <v>1</v>
       <v>1</v>
       <v>11</v>
@@ -15212,7 +15107,7 @@
       <v>18</v>
       <v>9</v>
     </spb>
-    <spb s="33">
+    <spb s="30">
       <v>P/E</v>
       <v>Beta</v>
       <v>Change</v>
@@ -15245,11 +15140,11 @@
       <v>Last trade time</v>
     </spb>
     <spb s="1">
-      <v>10</v>
+      <v>9</v>
       <v>Name</v>
       <v>LearnMoreOnLink</v>
     </spb>
-    <spb s="34">
+    <spb s="31">
       <v>1</v>
       <v>1</v>
       <v>15</v>
@@ -15269,7 +15164,7 @@
       <v>16</v>
       <v>9</v>
     </spb>
-    <spb s="35">
+    <spb s="32">
       <v>P/E</v>
       <v>Beta</v>
       <v>Change</v>
@@ -15304,10 +15199,10 @@
       <v>Last trade time</v>
     </spb>
     <spb s="16">
-      <v>11</v>
+      <v>10</v>
       <v>Name</v>
     </spb>
-    <spb s="36">
+    <spb s="33">
       <v>Change</v>
       <v>Currency</v>
       <v>High</v>
@@ -15327,14 +15222,14 @@
       <v>Last trade time</v>
     </spb>
     <spb s="16">
-      <v>12</v>
+      <v>11</v>
       <v>Name</v>
     </spb>
-    <spb s="37">
+    <spb s="34">
       <v>2</v>
       <v>2</v>
     </spb>
-    <spb s="38">
+    <spb s="35">
       <v>25</v>
       <v>25</v>
       <v>25</v>
@@ -15348,10 +15243,10 @@
       <v>25</v>
       <v>9</v>
     </spb>
-    <spb s="39">
+    <spb s="36">
       <v>GMT</v>
     </spb>
-    <spb s="38">
+    <spb s="35">
       <v>2</v>
       <v>2</v>
       <v>2</v>
@@ -15365,7 +15260,7 @@
       <v>2</v>
       <v>9</v>
     </spb>
-    <spb s="38">
+    <spb s="35">
       <v>26</v>
       <v>26</v>
       <v>26</v>
@@ -15379,7 +15274,7 @@
       <v>26</v>
       <v>9</v>
     </spb>
-    <spb s="38">
+    <spb s="35">
       <v>11</v>
       <v>11</v>
       <v>11</v>
@@ -15398,7 +15293,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="40">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="37">
   <s>
     <k n="P/I" t="s"/>
     <k n="Beta" t="s"/>
@@ -15931,71 +15826,6 @@
     <k n="Volumen promedio" t="s"/>
     <k n="Año de constitución" t="s"/>
     <k n="Tipo de instrumento" t="s"/>
-    <k n="Máximo en 52 semanas" t="s"/>
-    <k n="Mínimo en 52 semanas" t="s"/>
-    <k n="Acciones en circulación" t="s"/>
-    <k n="Capitalización de mercado" t="s"/>
-    <k n="Precio (horario ampliado)" t="s"/>
-    <k n="Abreviatura de intercambio" t="s"/>
-    <k n="Hora de la última operación" t="s"/>
-  </s>
-  <s>
-    <k n="P/I" t="i"/>
-    <k n="Beta" t="i"/>
-    <k n="Cambio" t="i"/>
-    <k n="Máximo" t="i"/>
-    <k n="Mínimo" t="i"/>
-    <k n="Nombre" t="i"/>
-    <k n="Precio" t="i"/>
-    <k n="Volumen" t="i"/>
-    <k n="Apertura" t="i"/>
-    <k n="Empleados" t="i"/>
-    <k n="Cambio (%)" t="i"/>
-    <k n="Cierre anterior" t="i"/>
-    <k n="Volumen promedio" t="i"/>
-    <k n="`%EntityServiceId" t="i"/>
-    <k n="Año de constitución" t="i"/>
-    <k n="Máximo en 52 semanas" t="i"/>
-    <k n="Mínimo en 52 semanas" t="i"/>
-    <k n="Acciones en circulación" t="i"/>
-    <k n="Capitalización de mercado" t="i"/>
-    <k n="Precio (horario ampliado)" t="i"/>
-    <k n="Hora de la última operación" t="i"/>
-  </s>
-  <s>
-    <k n="Cambio" t="s"/>
-    <k n="Precio" t="s"/>
-    <k n="Cambio (%)" t="s"/>
-    <k n="Precio (horario ampliado)" t="s"/>
-    <k n="Hora de la última operación" t="s"/>
-  </s>
-  <s>
-    <k n="P/I" t="s"/>
-    <k n="Beta" t="s"/>
-    <k n="Cambio" t="s"/>
-    <k n="Moneda" t="s"/>
-    <k n="Máximo" t="s"/>
-    <k n="Mínimo" t="s"/>
-    <k n="Nombre" t="s"/>
-    <k n="Precio" t="s"/>
-    <k n="Sector" t="s"/>
-    <k n="Volumen" t="s"/>
-    <k n="Apertura" t="s"/>
-    <k n="Empleados" t="s"/>
-    <k n="Cambio (%)" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Descripción" t="s"/>
-    <k n="Intercambio" t="s"/>
-    <k n="Sede central" t="s"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="Nombre oficial" t="s"/>
-    <k n="Cierre anterior" t="s"/>
-    <k n="LearnMoreOnLink" t="s"/>
-    <k n="Símbolo bursátil" t="s"/>
-    <k n="Volumen promedio" t="s"/>
-    <k n="Año de constitución" t="s"/>
-    <k n="Tipo de instrumento" t="s"/>
     <k n="Acciones en circulación" t="s"/>
     <k n="Capitalización de mercado" t="s"/>
     <k n="Abreviatura de intercambio" t="s"/>
@@ -16862,7 +16692,7 @@
       </c>
       <c r="G4" s="12">
         <f t="array" aca="1" ref="G4" ca="1">_FV(A4,"Precio")</f>
-        <v>246.71</v>
+        <v>246.255</v>
       </c>
       <c r="H4" s="13" cm="1">
         <f t="array" aca="1" ref="H4" ca="1">_FV(A4,"Acciones en circulación",TRUE)/1000000</f>
@@ -16870,7 +16700,7 @@
       </c>
       <c r="I4" s="14">
         <f t="shared" ref="I4:I16" ca="1" si="0">G4*H4</f>
-        <v>40076.386543000001</v>
+        <v>40002.474841499999</v>
       </c>
       <c r="J4" s="90">
         <v>1.5</v>
@@ -16983,7 +16813,7 @@
       </c>
       <c r="AR4" s="19">
         <f t="shared" ref="AR4:AR11" ca="1" si="8">I4-AP4+AQ4</f>
-        <v>32863.386543000001</v>
+        <v>32789.474841499999</v>
       </c>
       <c r="AS4" s="19">
         <v>1640</v>
@@ -16999,15 +16829,15 @@
       </c>
       <c r="AW4" s="20">
         <f t="shared" ref="AW4:AW35" ca="1" si="9">AR4/AS4</f>
-        <v>20.038650331097561</v>
+        <v>19.993582220426831</v>
       </c>
       <c r="AX4" s="20">
         <f t="shared" ref="AX4:AX35" ca="1" si="10">AR4/AU4</f>
-        <v>31.298463374285713</v>
+        <v>31.228071277619048</v>
       </c>
       <c r="AY4" s="20">
         <f t="shared" ref="AY4:AY35" ca="1" si="11">AR4/AV4</f>
-        <v>9.9015928119915646</v>
+        <v>9.8793235436878568</v>
       </c>
       <c r="AZ4" s="21">
         <v>1500</v>
@@ -17054,11 +16884,11 @@
       </c>
       <c r="BL4" s="23">
         <f t="shared" ref="BL4:BL35" ca="1" si="18">IF($BJ4&lt;=0,-0.99,MAX(-0.99,($BJ4/G4)^(1/5)-1))</f>
-        <v>-3.1447161351016106E-2</v>
+        <v>-3.1089510785764829E-2</v>
       </c>
       <c r="BM4" s="23">
         <f t="shared" ref="BM4:BM35" ca="1" si="19">IF(BK4&lt;=0,-0.99,MAX(-0.99,(BK4/G4)^(1/5)-1))</f>
-        <v>0.21440325563515295</v>
+        <v>0.21485168962191081</v>
       </c>
       <c r="BN4" t="s">
         <v>79</v>
@@ -17094,7 +16924,7 @@
       </c>
       <c r="G5" s="12">
         <f t="array" aca="1" ref="G5" ca="1">_FV(A5,"Precio")</f>
-        <v>495.30009999999999</v>
+        <v>494.54</v>
       </c>
       <c r="H5" s="13">
         <f t="array" aca="1" ref="H5" ca="1">_FV(A5,"Acciones en circulación",TRUE())/1000000</f>
@@ -17102,7 +16932,7 @@
       </c>
       <c r="I5" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>3677873.1810544999</v>
+        <v>3672229.0243000002</v>
       </c>
       <c r="J5" s="91">
         <v>1</v>
@@ -17215,7 +17045,7 @@
       </c>
       <c r="AR5" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>3641324.1810544999</v>
+        <v>3635680.0243000002</v>
       </c>
       <c r="AS5" s="19">
         <v>124961</v>
@@ -17231,15 +17061,15 @@
       </c>
       <c r="AW5" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>29.13968503016541</v>
+        <v>29.094517683917385</v>
       </c>
       <c r="AX5" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>18.791894458172276</v>
+        <v>18.762766483632742</v>
       </c>
       <c r="AY5" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>10.973165242947633</v>
+        <v>10.956156522590774</v>
       </c>
       <c r="AZ5" s="21">
         <v>589551</v>
@@ -17286,11 +17116,11 @@
       </c>
       <c r="BL5" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-4.4021554335645474E-2</v>
+        <v>-4.3727870146306191E-2</v>
       </c>
       <c r="BM5" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.12530205264345784</v>
+        <v>0.12564775439289733</v>
       </c>
       <c r="BN5" s="99">
         <v>46256</v>
@@ -17558,7 +17388,7 @@
       </c>
       <c r="G7" s="12">
         <f t="array" aca="1" ref="G7" ca="1">_FV(A7,"Precio")</f>
-        <v>41.935000000000002</v>
+        <v>41.981000000000002</v>
       </c>
       <c r="H7" s="13">
         <f t="array" aca="1" ref="H7" ca="1">_FV(A7,"Acciones en circulación",TRUE())/1000000</f>
@@ -17566,7 +17396,7 @@
       </c>
       <c r="I7" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>102821.055525</v>
+        <v>102933.84361500001</v>
       </c>
       <c r="J7" s="91">
         <v>1</v>
@@ -17679,7 +17509,7 @@
       </c>
       <c r="AR7" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>110636.055525</v>
+        <v>110748.84361500001</v>
       </c>
       <c r="AS7" s="19">
         <v>6200</v>
@@ -17695,18 +17525,18 @@
       </c>
       <c r="AW7" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>17.844525084677421</v>
+        <v>17.862716712096773</v>
       </c>
       <c r="AX7" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>19.40983430263158</v>
+        <v>19.429621686842108</v>
       </c>
       <c r="AY7" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>1.3711247431528071</v>
+        <v>1.3725225382947082</v>
       </c>
       <c r="AZ7" s="21">
-        <v>90000</v>
+        <v>42483</v>
       </c>
       <c r="BA7" s="22">
         <f t="shared" si="12"/>
@@ -17714,11 +17544,11 @@
       </c>
       <c r="BB7" s="22">
         <f t="shared" si="13"/>
-        <v>0.89655555555555555</v>
+        <v>1.8993479744839112</v>
       </c>
       <c r="BC7" s="23">
         <f t="shared" si="14"/>
-        <v>6.3333333333333339E-2</v>
+        <v>0.13417131558505757</v>
       </c>
       <c r="BD7" s="98">
         <v>6845</v>
@@ -17750,14 +17580,14 @@
       </c>
       <c r="BL7" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>1.7198856723277256E-2</v>
+        <v>1.6975843125892842E-2</v>
       </c>
       <c r="BM7" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.21981528931254024</v>
+        <v>0.21954785350683115</v>
       </c>
       <c r="BN7" s="96" t="s">
-        <v>677</v>
+        <v>836</v>
       </c>
       <c r="BO7" t="s">
         <v>88</v>
@@ -17790,7 +17620,7 @@
       </c>
       <c r="G8" s="12">
         <f t="array" aca="1" ref="G8" ca="1">_FV(A8,"Precio")</f>
-        <v>958.59550000000002</v>
+        <v>958.05</v>
       </c>
       <c r="H8" s="13">
         <f t="array" aca="1" ref="H8" ca="1">_FV(A8,"Acciones en circulación",TRUE())/1000000</f>
@@ -17798,7 +17628,7 @@
       </c>
       <c r="I8" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>425116.78202539997</v>
+        <v>424874.86433999997</v>
       </c>
       <c r="J8" s="90">
         <v>1.5</v>
@@ -17911,7 +17741,7 @@
       </c>
       <c r="AR8" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>413346.78202539997</v>
+        <v>413104.86433999997</v>
       </c>
       <c r="AS8" s="19">
         <v>11905</v>
@@ -17927,15 +17757,15 @@
       </c>
       <c r="AW8" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>34.720435281427967</v>
+        <v>34.700114602267952</v>
       </c>
       <c r="AX8" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>29.974385933676576</v>
+        <v>29.95684295431472</v>
       </c>
       <c r="AY8" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>1.4079048401696241</v>
+        <v>1.4070808417861642</v>
       </c>
       <c r="AZ8" s="21">
         <v>44305</v>
@@ -17982,11 +17812,11 @@
       </c>
       <c r="BL8" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-4.9160074465740333E-2</v>
+        <v>-4.905182018101617E-2</v>
       </c>
       <c r="BM8" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>8.5666007165993152E-2</v>
+        <v>8.5789611564482282E-2</v>
       </c>
       <c r="BN8" s="96" t="s">
         <v>677</v>
@@ -18022,7 +17852,7 @@
       </c>
       <c r="G9" s="12">
         <f t="array" aca="1" ref="G9" ca="1">_FV(A9,"Precio")</f>
-        <v>76.510000000000005</v>
+        <v>76.37</v>
       </c>
       <c r="H9" s="13">
         <f t="array" aca="1" ref="H9" ca="1">_FV(A9,"Acciones en circulación",TRUE())/1000000</f>
@@ -18030,7 +17860,7 @@
       </c>
       <c r="I9" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>6553.3615266000006</v>
+        <v>6541.3700142000007</v>
       </c>
       <c r="J9" s="91">
         <v>1</v>
@@ -18143,7 +17973,7 @@
       </c>
       <c r="AR9" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>6184.461526600001</v>
+        <v>6172.4700142000011</v>
       </c>
       <c r="AS9" s="19">
         <v>281</v>
@@ -18159,15 +17989,15 @@
       </c>
       <c r="AW9" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>22.008759881138793</v>
+        <v>21.966085459786481</v>
       </c>
       <c r="AX9" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>19.326442270625002</v>
+        <v>19.288968794375002</v>
       </c>
       <c r="AY9" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>8.2022036161803733</v>
+        <v>8.1862997535809026</v>
       </c>
       <c r="AZ9" s="21">
         <v>1676</v>
@@ -18214,11 +18044,11 @@
       </c>
       <c r="BL9" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.4688426625229307E-2</v>
+        <v>-3.4334767774719888E-2</v>
       </c>
       <c r="BM9" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.19992256658649676</v>
+        <v>0.20036217929528854</v>
       </c>
       <c r="BN9" s="96" t="s">
         <v>677</v>
@@ -18486,7 +18316,7 @@
       </c>
       <c r="G11" s="12">
         <f t="array" aca="1" ref="G11" ca="1">_FV(A11,"Precio")</f>
-        <v>167.61</v>
+        <v>167.76</v>
       </c>
       <c r="H11" s="13">
         <f t="array" aca="1" ref="H11" ca="1">_FV(A11,"Acciones en circulación",TRUE())/1000000</f>
@@ -18494,7 +18324,7 @@
       </c>
       <c r="I11" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>27104.129295000002</v>
+        <v>27128.385719999998</v>
       </c>
       <c r="J11" s="91">
         <v>1</v>
@@ -18607,7 +18437,7 @@
       </c>
       <c r="AR11" s="19">
         <f t="shared" ca="1" si="8"/>
-        <v>25434.129295000002</v>
+        <v>25458.385719999998</v>
       </c>
       <c r="AS11" s="19">
         <v>963</v>
@@ -18623,15 +18453,15 @@
       </c>
       <c r="AW11" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>26.411349215991695</v>
+        <v>26.436537611630321</v>
       </c>
       <c r="AX11" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>-416.9529392622951</v>
+        <v>-417.35058557377045</v>
       </c>
       <c r="AY11" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>8.0233846356466891</v>
+        <v>8.0310365047318601</v>
       </c>
       <c r="AZ11" s="21">
         <v>4597</v>
@@ -18678,11 +18508,11 @@
       </c>
       <c r="BL11" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-2.3220994598323275E-2</v>
+        <v>-2.3395731461994917E-2</v>
       </c>
       <c r="BM11" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.26082680899108857</v>
+        <v>0.26060125856359373</v>
       </c>
       <c r="BN11" s="96" t="s">
         <v>677</v>
@@ -18839,7 +18669,7 @@
       </c>
       <c r="AR12" s="19">
         <f ca="1">I12*'Framework Notes'!E4-AP12+AQ12</f>
-        <v>9516267.2020450011</v>
+        <v>9514411.4236660004</v>
       </c>
       <c r="AS12" s="19">
         <v>262620</v>
@@ -18855,15 +18685,15 @@
       </c>
       <c r="AW12" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>36.235881509576579</v>
+        <v>36.228815108011574</v>
       </c>
       <c r="AX12" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>20.615830160409448</v>
+        <v>20.611809843297227</v>
       </c>
       <c r="AY12" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>4.2135324279444646</v>
+        <v>4.2127107420656449</v>
       </c>
       <c r="AZ12" s="21">
         <v>1600000</v>
@@ -18902,19 +18732,19 @@
       </c>
       <c r="BJ12" s="25">
         <f ca="1">((BD12*BH12+$AP12-$AQ12)/$H12)/'Framework Notes'!E4</f>
-        <v>24.718438672848769</v>
+        <v>24.722433679637831</v>
       </c>
       <c r="BK12" s="25">
         <f ca="1">((BF12*BI12+$AP12-$AQ12)/$H12)/'Framework Notes'!E4</f>
-        <v>53.790234480008543</v>
+        <v>53.798928085408825</v>
       </c>
       <c r="BL12" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.12449931393740532</v>
+        <v>-0.12447101599239929</v>
       </c>
       <c r="BM12" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>2.2805303231882901E-2</v>
+        <v>2.2838362358715614E-2</v>
       </c>
       <c r="BN12" s="95" t="s">
         <v>677</v>
@@ -18950,7 +18780,7 @@
       </c>
       <c r="G13" s="12">
         <f t="array" aca="1" ref="G13" ca="1">_FV(A13,"Precio")</f>
-        <v>259.36</v>
+        <v>258.565</v>
       </c>
       <c r="H13" s="13">
         <f t="array" aca="1" ref="H13" ca="1">_FV(A13,"Acciones en circulación",TRUE())/1000000</f>
@@ -18958,7 +18788,7 @@
       </c>
       <c r="I13" s="14">
         <f t="shared" ca="1" si="0"/>
-        <v>2797537.3615999999</v>
+        <v>2788962.2451499999</v>
       </c>
       <c r="J13" s="91">
         <v>1.5</v>
@@ -19071,7 +18901,7 @@
       </c>
       <c r="AR13" s="19">
         <f t="shared" ref="AR13:AR32" ca="1" si="21">I13-AP13+AQ13</f>
-        <v>2848218.3615999999</v>
+        <v>2839643.2451499999</v>
       </c>
       <c r="AS13" s="19">
         <v>76899</v>
@@ -19087,15 +18917,15 @@
       </c>
       <c r="AW13" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>37.038431729931467</v>
+        <v>36.926920313007969</v>
       </c>
       <c r="AX13" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>20.639263489855072</v>
+        <v>20.57712496485507</v>
       </c>
       <c r="AY13" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>3.6720122858586794</v>
+        <v>3.6609569772553812</v>
       </c>
       <c r="AZ13" s="21">
         <v>300000</v>
@@ -19142,11 +18972,11 @@
       </c>
       <c r="BL13" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-6.0005029184535763E-2</v>
+        <v>-5.9427705400891262E-2</v>
       </c>
       <c r="BM13" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.1137563839946405</v>
+        <v>0.1144404281327791</v>
       </c>
       <c r="BN13" s="95" t="s">
         <v>677</v>
@@ -20110,7 +19940,7 @@
       </c>
       <c r="G18" s="12">
         <f t="array" aca="1" ref="G18" ca="1">_FV(A18,"Precio")</f>
-        <v>1133.645</v>
+        <v>1131.49</v>
       </c>
       <c r="H18" s="13">
         <f t="array" aca="1" ref="H18" ca="1">_FV(A18,"Acciones en circulación",TRUE())/1000000</f>
@@ -20118,7 +19948,7 @@
       </c>
       <c r="I18" s="14">
         <f t="shared" ref="I18:I25" ca="1" si="22">G18*H18</f>
-        <v>24484.056597799998</v>
+        <v>24437.513683599998</v>
       </c>
       <c r="J18" s="90">
         <v>0</v>
@@ -20231,7 +20061,7 @@
       </c>
       <c r="AR18" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>26684.056597799998</v>
+        <v>26637.513683599998</v>
       </c>
       <c r="AS18" s="19">
         <v>730</v>
@@ -20247,15 +20077,15 @@
       </c>
       <c r="AW18" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>36.553502188767119</v>
+        <v>36.489744772054792</v>
       </c>
       <c r="AX18" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>30.496064683199997</v>
+        <v>30.44287278125714</v>
       </c>
       <c r="AY18" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>15.513986394069766</v>
+        <v>15.486926560232558</v>
       </c>
       <c r="AZ18" s="21">
         <v>2200</v>
@@ -20302,11 +20132,11 @@
       </c>
       <c r="BL18" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.1488094577400273</v>
+        <v>-0.14848547435854165</v>
       </c>
       <c r="BM18" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.1098005163465392</v>
+        <v>0.11022293283992024</v>
       </c>
       <c r="BN18" s="95" t="s">
         <v>836</v>
@@ -20806,7 +20636,7 @@
       </c>
       <c r="G21" s="12">
         <f t="array" aca="1" ref="G21" ca="1">_FV(A21,"Precio")</f>
-        <v>48.435000000000002</v>
+        <v>48.12</v>
       </c>
       <c r="H21" s="13">
         <f t="array" aca="1" ref="H21" ca="1">_FV(A21,"Acciones en circulación",TRUE())/1000000</f>
@@ -20814,7 +20644,7 @@
       </c>
       <c r="I21" s="14">
         <f t="shared" ca="1" si="22"/>
-        <v>94739.63496000001</v>
+        <v>94123.489919999993</v>
       </c>
       <c r="J21" s="91">
         <v>0</v>
@@ -20927,7 +20757,7 @@
       </c>
       <c r="AR21" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>91413.63496000001</v>
+        <v>90797.489919999993</v>
       </c>
       <c r="AS21" s="19">
         <v>2100</v>
@@ -20943,15 +20773,15 @@
       </c>
       <c r="AW21" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>43.530302361904766</v>
+        <v>43.236899961904761</v>
       </c>
       <c r="AX21" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>31.199192819112632</v>
+        <v>30.988904409556312</v>
       </c>
       <c r="AY21" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>9.9147109501084607</v>
+        <v>9.8478839392624717</v>
       </c>
       <c r="AZ21" s="21">
         <v>9665</v>
@@ -20998,11 +20828,11 @@
       </c>
       <c r="BL21" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.12241088608740791</v>
+        <v>-0.12126491952848262</v>
       </c>
       <c r="BM21" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>1.1588906765475082E-2</v>
+        <v>1.2909851886780066E-2</v>
       </c>
       <c r="BN21" s="95" t="s">
         <v>677</v>
@@ -21038,7 +20868,7 @@
       </c>
       <c r="G22" s="12">
         <f t="array" aca="1" ref="G22" ca="1">_FV(A22,"Precio")</f>
-        <v>188.8201</v>
+        <v>188.55</v>
       </c>
       <c r="H22" s="13">
         <f t="array" aca="1" ref="H22" ca="1">_FV(A22,"Acciones en circulación",TRUE())/1000000</f>
@@ -21046,7 +20876,7 @@
       </c>
       <c r="I22" s="14">
         <f t="shared" ca="1" si="22"/>
-        <v>111325.63083256999</v>
+        <v>111166.383735</v>
       </c>
       <c r="J22" s="90">
         <v>1.5</v>
@@ -21159,7 +20989,7 @@
       </c>
       <c r="AR22" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>101752.63083256999</v>
+        <v>101593.383735</v>
       </c>
       <c r="AS22" s="19">
         <v>4800</v>
@@ -21175,15 +21005,15 @@
       </c>
       <c r="AW22" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>21.198464756785416</v>
+        <v>21.165288278125001</v>
       </c>
       <c r="AX22" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>35.404534040560193</v>
+        <v>35.349124472860126</v>
       </c>
       <c r="AY22" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>7.73255040904096</v>
+        <v>7.720448646173721</v>
       </c>
       <c r="AZ22" s="21">
         <v>10662</v>
@@ -21230,11 +21060,11 @@
       </c>
       <c r="BL22" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-3.915304956811827E-2</v>
+        <v>-3.8877922355027072E-2</v>
       </c>
       <c r="BM22" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.16731996018807838</v>
+        <v>0.16765420851689705</v>
       </c>
       <c r="BN22" s="95" t="s">
         <v>677</v>
@@ -21502,7 +21332,7 @@
       </c>
       <c r="G24" s="12">
         <f t="array" aca="1" ref="G24" ca="1">_FV(A24,"Precio")</f>
-        <v>98.76</v>
+        <v>98.93</v>
       </c>
       <c r="H24" s="13">
         <f t="array" aca="1" ref="H24" ca="1">_FV(A24,"Acciones en circulación",TRUE())/1000000</f>
@@ -21510,7 +21340,7 @@
       </c>
       <c r="I24" s="14">
         <f t="shared" ca="1" si="22"/>
-        <v>24077.026308</v>
+        <v>24118.471169</v>
       </c>
       <c r="J24" s="90">
         <v>2</v>
@@ -21623,7 +21453,7 @@
       </c>
       <c r="AR24" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>25547.026308</v>
+        <v>25588.471169</v>
       </c>
       <c r="AS24" s="19">
         <v>1050</v>
@@ -21639,15 +21469,15 @@
       </c>
       <c r="AW24" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>24.330501245714284</v>
+        <v>24.369972541904762</v>
       </c>
       <c r="AX24" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>18.379155617266186</v>
+        <v>18.408972064028777</v>
       </c>
       <c r="AY24" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>4.4819344399999999</v>
+        <v>4.489205468245614</v>
       </c>
       <c r="AZ24" s="21">
         <v>6501</v>
@@ -21694,11 +21524,11 @@
       </c>
       <c r="BL24" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-9.6510573327446503E-2</v>
+        <v>-9.6821295827241416E-2</v>
       </c>
       <c r="BM24" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>8.1041745127657938E-2</v>
+        <v>8.0669959931824575E-2</v>
       </c>
       <c r="BN24" s="95" t="s">
         <v>836</v>
@@ -22430,7 +22260,7 @@
       </c>
       <c r="G28" s="12">
         <f t="array" aca="1" ref="G28" ca="1">_FV(A28,"Precio")</f>
-        <v>581.23500000000001</v>
+        <v>577.58000000000004</v>
       </c>
       <c r="H28" s="13">
         <f t="array" aca="1" ref="H28" ca="1">_FV(A28,"Acciones en circulación",TRUE())/1000000</f>
@@ -22438,7 +22268,7 @@
       </c>
       <c r="I28" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>1480699.6499099999</v>
+        <v>1471388.5154800001</v>
       </c>
       <c r="J28" s="90">
         <v>-0.5</v>
@@ -22551,7 +22381,7 @@
       </c>
       <c r="AR28" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>1502759.6499099999</v>
+        <v>1493448.5154800001</v>
       </c>
       <c r="AS28" s="19">
         <v>85640</v>
@@ -22567,15 +22397,15 @@
       </c>
       <c r="AW28" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>17.547403665460063</v>
+        <v>17.438679536198038</v>
       </c>
       <c r="AX28" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>13.703808589367133</v>
+        <v>13.618899466350539</v>
       </c>
       <c r="AY28" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>6.5838319820810511</v>
+        <v>6.5430384029791897</v>
       </c>
       <c r="AZ28" s="21">
         <v>393577</v>
@@ -22622,11 +22452,11 @@
       </c>
       <c r="BL28" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-4.9506559278054252E-2</v>
+        <v>-4.8306624008308319E-2</v>
       </c>
       <c r="BM28" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.25743005300206456</v>
+        <v>0.25901747549778387</v>
       </c>
       <c r="BN28" s="95" t="s">
         <v>836</v>
@@ -22662,7 +22492,7 @@
       </c>
       <c r="G29" s="12">
         <f t="array" aca="1" ref="G29" ca="1">_FV(A29,"Precio")</f>
-        <v>107.89</v>
+        <v>107.98</v>
       </c>
       <c r="H29" s="13">
         <f t="array" aca="1" ref="H29" ca="1">_FV(A29,"Acciones en circulación",TRUE())/1000000</f>
@@ -22670,7 +22500,7 @@
       </c>
       <c r="I29" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>96845.904883999989</v>
+        <v>96926.692087999996</v>
       </c>
       <c r="J29" s="91">
         <v>0</v>
@@ -22783,7 +22613,7 @@
       </c>
       <c r="AR29" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>131929.90488399999</v>
+        <v>132010.69208800001</v>
       </c>
       <c r="AS29" s="19">
         <v>5000</v>
@@ -22799,18 +22629,18 @@
       </c>
       <c r="AW29" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>26.385980976799999</v>
+        <v>26.402138417600003</v>
       </c>
       <c r="AX29" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>19.539381647511846</v>
+        <v>19.551346577014218</v>
       </c>
       <c r="AY29" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>5.1070299571865441</v>
+        <v>5.1101572441450864</v>
       </c>
       <c r="AZ29" s="21">
-        <v>80000</v>
+        <v>34500</v>
       </c>
       <c r="BA29" s="22">
         <f t="shared" si="12"/>
@@ -22818,11 +22648,11 @@
       </c>
       <c r="BB29" s="22">
         <f t="shared" si="13"/>
-        <v>0.32291249999999999</v>
+        <v>0.74878260869565216</v>
       </c>
       <c r="BC29" s="23">
         <f t="shared" si="14"/>
-        <v>6.4699999999999994E-2</v>
+        <v>0.15002898550724636</v>
       </c>
       <c r="BD29" s="98">
         <v>7013</v>
@@ -22854,11 +22684,11 @@
       </c>
       <c r="BL29" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-6.2565397677014079E-2</v>
+        <v>-6.2721717840990787E-2</v>
       </c>
       <c r="BM29" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.23297668244699166</v>
+        <v>0.23277107971299626</v>
       </c>
       <c r="BN29" s="95" t="s">
         <v>836</v>
@@ -22894,7 +22724,7 @@
       </c>
       <c r="G30" s="12">
         <f t="array" aca="1" ref="G30" ca="1">_FV(A30,"Precio")</f>
-        <v>284.64</v>
+        <v>284.13</v>
       </c>
       <c r="H30" s="13">
         <f t="array" aca="1" ref="H30" ca="1">_FV(A30,"Acciones en circulación",TRUE())/1000000</f>
@@ -22902,7 +22732,7 @@
       </c>
       <c r="I30" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>101354.52580799999</v>
+        <v>101172.92516099999</v>
       </c>
       <c r="J30" s="90">
         <v>1</v>
@@ -23015,7 +22845,7 @@
       </c>
       <c r="AR30" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>100720.52580799999</v>
+        <v>100538.92516099999</v>
       </c>
       <c r="AS30" s="19">
         <v>342</v>
@@ -23031,15 +22861,15 @@
       </c>
       <c r="AW30" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>294.50446142690055</v>
+        <v>293.97346538304089</v>
       </c>
       <c r="AX30" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>-50360.262903999996</v>
+        <v>-50269.462580499996</v>
       </c>
       <c r="AY30" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>40.095750719745219</v>
+        <v>40.023457468550951</v>
       </c>
       <c r="AZ30" s="21">
         <v>3846</v>
@@ -23086,11 +22916,11 @@
       </c>
       <c r="BL30" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.32892754178639116</v>
+        <v>-0.32868680586190779</v>
       </c>
       <c r="BM30" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-0.18752213050000333</v>
+        <v>-0.18723066776950026</v>
       </c>
       <c r="BN30" s="95" t="s">
         <v>677</v>
@@ -23126,7 +22956,7 @@
       </c>
       <c r="G31" s="12">
         <f t="array" aca="1" ref="G31" ca="1">_FV(A31,"Precio")</f>
-        <v>187.35</v>
+        <v>187.39500000000001</v>
       </c>
       <c r="H31" s="13">
         <f t="array" aca="1" ref="H31" ca="1">_FV(A31,"Acciones en circulación",TRUE())/1000000</f>
@@ -23134,7 +22964,7 @@
       </c>
       <c r="I31" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>190782.62669999999</v>
+        <v>190828.45119000002</v>
       </c>
       <c r="J31" s="91">
         <v>1</v>
@@ -23247,7 +23077,7 @@
       </c>
       <c r="AR31" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>187053.62669999999</v>
+        <v>187099.45119000002</v>
       </c>
       <c r="AS31" s="19">
         <v>1510</v>
@@ -23263,15 +23093,15 @@
       </c>
       <c r="AW31" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>123.87657397350993</v>
+        <v>123.90692131788082</v>
       </c>
       <c r="AX31" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>3170.4004525423729</v>
+        <v>3171.1771388135598</v>
       </c>
       <c r="AY31" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>36.749239037328095</v>
+        <v>36.758241884086445</v>
       </c>
       <c r="AZ31" s="21">
         <v>7154</v>
@@ -23318,11 +23148,11 @@
       </c>
       <c r="BL31" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.21476137031297726</v>
+        <v>-0.21479908650920088</v>
       </c>
       <c r="BM31" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>-5.0038562940759923E-2</v>
+        <v>-5.0084191021970481E-2</v>
       </c>
       <c r="BN31" s="96" t="s">
         <v>677</v>
@@ -23358,7 +23188,7 @@
       </c>
       <c r="G32" s="12">
         <f t="array" aca="1" ref="G32" ca="1">_FV(A32,"Precio")</f>
-        <v>339.08</v>
+        <v>338.04</v>
       </c>
       <c r="H32" s="13">
         <f t="array" aca="1" ref="H32" ca="1">_FV(A32,"Acciones en circulación",TRUE())/1000000</f>
@@ -23366,7 +23196,7 @@
       </c>
       <c r="I32" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>4146948.4</v>
+        <v>4134229.2</v>
       </c>
       <c r="J32" s="90">
         <v>1</v>
@@ -23479,7 +23309,7 @@
       </c>
       <c r="AR32" s="19">
         <f t="shared" ca="1" si="21"/>
-        <v>4025268.4</v>
+        <v>4012549.2</v>
       </c>
       <c r="AS32" s="19">
         <v>119475</v>
@@ -23495,15 +23325,15 @@
       </c>
       <c r="AW32" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>33.691302783009</v>
+        <v>33.584843691148777</v>
       </c>
       <c r="AX32" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>23.245948255948257</v>
+        <v>23.172494802494803</v>
       </c>
       <c r="AY32" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>9.0278969206270876</v>
+        <v>8.9993702200192889</v>
       </c>
       <c r="AZ32" s="21">
         <v>795872</v>
@@ -23550,11 +23380,11 @@
       </c>
       <c r="BL32" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-5.2229551152197962E-2</v>
+        <v>-5.1647093159953639E-2</v>
       </c>
       <c r="BM32" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>0.12069048686017769</v>
+        <v>0.12137921389497563</v>
       </c>
       <c r="BN32" s="95" t="s">
         <v>677</v>
@@ -23711,7 +23541,7 @@
       </c>
       <c r="AR33" s="19">
         <f ca="1">I33*'Framework Notes'!E5-AP33+AQ33</f>
-        <v>183958.23505562</v>
+        <v>183972.78747084798</v>
       </c>
       <c r="AS33" s="19">
         <v>4870</v>
@@ -23727,15 +23557,15 @@
       </c>
       <c r="AW33" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>37.7737648984846</v>
+        <v>37.776753074096092</v>
       </c>
       <c r="AX33" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>25.728424483303495</v>
+        <v>25.730459786132585</v>
       </c>
       <c r="AY33" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>5.1456848966606996</v>
+        <v>5.1460919572265169</v>
       </c>
       <c r="AZ33" s="21">
         <v>27296</v>
@@ -23774,19 +23604,19 @@
       </c>
       <c r="BJ33" s="25">
         <f ca="1">((BD33*BH33+$AP33-$AQ33)/$H33)/'Framework Notes'!E5</f>
-        <v>35.195366213891631</v>
+        <v>35.192531535556107</v>
       </c>
       <c r="BK33" s="25">
         <f ca="1">((BF33*BI33+$AP33-$AQ33)/$H33)/'Framework Notes'!E5</f>
-        <v>93.344408854208282</v>
+        <v>93.336890780041543</v>
       </c>
       <c r="BL33" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-0.15106438639403141</v>
+        <v>-0.15107806169951887</v>
       </c>
       <c r="BM33" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>3.1799509893731814E-2</v>
+        <v>3.1782888876456417E-2</v>
       </c>
       <c r="BN33" s="95" t="s">
         <v>677</v>
@@ -23822,7 +23652,7 @@
       </c>
       <c r="G34" s="12">
         <f t="array" aca="1" ref="G34" ca="1">_FV(A34,"Precio")</f>
-        <v>287.005</v>
+        <v>286.99</v>
       </c>
       <c r="H34" s="13">
         <f t="array" aca="1" ref="H34" ca="1">_FV(A34,"Acciones en circulación",TRUE())/1000000</f>
@@ -23830,7 +23660,7 @@
       </c>
       <c r="I34" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>55349.631762499994</v>
+        <v>55346.738975</v>
       </c>
       <c r="J34" s="90">
         <v>0</v>
@@ -23943,7 +23773,7 @@
       </c>
       <c r="AR34" s="19">
         <f ca="1">I34-AP34+AQ34</f>
-        <v>52906.631762499994</v>
+        <v>52903.738975</v>
       </c>
       <c r="AS34" s="19">
         <v>1600</v>
@@ -23959,15 +23789,15 @@
       </c>
       <c r="AW34" s="20">
         <f t="shared" ca="1" si="9"/>
-        <v>33.066644851562494</v>
+        <v>33.064836859374999</v>
       </c>
       <c r="AX34" s="20">
         <f t="shared" ca="1" si="10"/>
-        <v>22.903303793290039</v>
+        <v>22.902051504329005</v>
       </c>
       <c r="AY34" s="20">
         <f t="shared" ca="1" si="11"/>
-        <v>6.8978659403520197</v>
+        <v>6.89748878422425</v>
       </c>
       <c r="AZ34" s="21">
         <v>9341</v>
@@ -24014,11 +23844,11 @@
       </c>
       <c r="BL34" s="23">
         <f t="shared" ca="1" si="18"/>
-        <v>-7.4956843922937333E-2</v>
+        <v>-7.4947174347511858E-2</v>
       </c>
       <c r="BM34" s="23">
         <f t="shared" ca="1" si="19"/>
-        <v>7.3974326586043748E-2</v>
+        <v>7.3985552954984213E-2</v>
       </c>
       <c r="BN34" s="95" t="s">
         <v>677</v>
@@ -24285,7 +24115,7 @@
       </c>
       <c r="G36" s="12">
         <f t="array" aca="1" ref="G36" ca="1">_FV(A36,"Precio")</f>
-        <v>108.07</v>
+        <v>107.71</v>
       </c>
       <c r="H36" s="13">
         <f t="array" aca="1" ref="H36" ca="1">_FV(A36,"Acciones en circulación",TRUE())/1000000</f>
@@ -24293,7 +24123,7 @@
       </c>
       <c r="I36" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>20461.271344999997</v>
+        <v>20393.111284999999</v>
       </c>
       <c r="J36" s="90">
         <v>1</v>
@@ -24406,7 +24236,7 @@
       </c>
       <c r="AR36" s="19">
         <f ca="1">I36*'Framework Notes'!E6-AP36+AQ36</f>
-        <v>8597043.4779046979</v>
+        <v>8565128.4954105504</v>
       </c>
       <c r="AS36" s="19">
         <v>940085</v>
@@ -24422,15 +24252,15 @@
       </c>
       <c r="AW36" s="20">
         <f t="shared" ref="AW36:AW66" ca="1" si="35">AR36/AS36</f>
-        <v>9.1449639957075135</v>
+        <v>9.1110149565311112</v>
       </c>
       <c r="AX36" s="20">
         <f t="shared" ref="AX36:AX66" ca="1" si="36">AR36/AU36</f>
-        <v>5.3529048112419133</v>
+        <v>5.3330331118858858</v>
       </c>
       <c r="AY36" s="20">
         <f t="shared" ref="AY36:AY66" ca="1" si="37">AR36/AV36</f>
-        <v>1.932135239771601</v>
+        <v>1.9249625341185332</v>
       </c>
       <c r="AZ36" s="21">
         <v>2601577</v>
@@ -24469,19 +24299,19 @@
       </c>
       <c r="BJ36" s="25">
         <f ca="1">((BD36*BH36+$AP36-$AQ36)/$H36)/'Framework Notes'!E6</f>
-        <v>81.42301371692767</v>
+        <v>81.428332817185719</v>
       </c>
       <c r="BK36" s="25">
         <f ca="1">((BF36*BI36+$AP36-$AQ36)/$H36)/'Framework Notes'!E6</f>
-        <v>481.00530349018362</v>
+        <v>481.03672599982951</v>
       </c>
       <c r="BL36" s="23">
         <f t="shared" ref="BL36:BL71" ca="1" si="43">IF($BJ36&lt;=0,-0.99,MAX(-0.99,($BJ36/G36)^(1/5)-1))</f>
-        <v>-5.5050924872154572E-2</v>
+        <v>-5.4407751478355082E-2</v>
       </c>
       <c r="BM36" s="23">
         <f t="shared" ref="BM36:BM71" ca="1" si="44">IF(BK36&lt;=0,-0.99,MAX(-0.99,(BK36/G36)^(1/5)-1))</f>
-        <v>0.34799705280246274</v>
+        <v>0.34891455816026773</v>
       </c>
       <c r="BN36" s="96" t="s">
         <v>677</v>
@@ -24749,7 +24579,7 @@
       </c>
       <c r="G38" s="12">
         <f t="array" aca="1" ref="G38" ca="1">_FV(A38,"Precio")</f>
-        <v>211.215</v>
+        <v>210.32499999999999</v>
       </c>
       <c r="H38" s="13">
         <f t="array" aca="1" ref="H38" ca="1">_FV(A38,"Acciones en circulación",TRUE())/1000000</f>
@@ -24757,7 +24587,7 @@
       </c>
       <c r="I38" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>5111403</v>
+        <v>5089865</v>
       </c>
       <c r="J38" s="90">
         <v>1</v>
@@ -24870,7 +24700,7 @@
       </c>
       <c r="AR38" s="19">
         <f ca="1">I38-AP38+AQ38</f>
-        <v>5071043</v>
+        <v>5049505</v>
       </c>
       <c r="AS38" s="19">
         <v>122365</v>
@@ -24886,15 +24716,15 @@
       </c>
       <c r="AW38" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>41.441940097250033</v>
+        <v>41.265925714052223</v>
       </c>
       <c r="AX38" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>30.63889190985439</v>
+        <v>30.508760799951663</v>
       </c>
       <c r="AY38" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>20.004903546490986</v>
+        <v>19.919937670125055</v>
       </c>
       <c r="AZ38" s="21">
         <v>215590</v>
@@ -24941,11 +24771,11 @@
       </c>
       <c r="BL38" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-6.5836356625981307E-2</v>
+        <v>-6.5047100044652861E-2</v>
       </c>
       <c r="BM38" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.10546782550802436</v>
+        <v>0.10640181364052959</v>
       </c>
       <c r="BN38" s="96" t="s">
         <v>677</v>
@@ -25213,7 +25043,7 @@
       </c>
       <c r="G40" s="12">
         <f t="array" aca="1" ref="G40" ca="1">_FV(A40,"Precio")</f>
-        <v>417.14699999999999</v>
+        <v>416.04</v>
       </c>
       <c r="H40" s="13">
         <f t="array" aca="1" ref="H40" ca="1">_FV(A40,"Acciones en circulación",TRUE())/1000000</f>
@@ -25221,7 +25051,7 @@
       </c>
       <c r="I40" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>2163522.0696780002</v>
+        <v>2157780.6429600003</v>
       </c>
       <c r="J40" s="90">
         <v>2</v>
@@ -25334,7 +25164,7 @@
       </c>
       <c r="AR40" s="19">
         <f ca="1">I40-AP40+AQ40</f>
-        <v>2086532.0696780002</v>
+        <v>2080790.6429600003</v>
       </c>
       <c r="AS40" s="19">
         <v>59255</v>
@@ -25350,15 +25180,15 @@
       </c>
       <c r="AW40" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>35.212759592911993</v>
+        <v>35.115866052822554</v>
       </c>
       <c r="AX40" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>20.957533845701086</v>
+        <v>20.899865839292893</v>
       </c>
       <c r="AY40" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>14.949717487124742</v>
+        <v>14.908580948341337</v>
       </c>
       <c r="AZ40" s="21">
         <v>244100</v>
@@ -25405,11 +25235,11 @@
       </c>
       <c r="BL40" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-9.7429195355808074E-2</v>
+        <v>-9.6949393335030942E-2</v>
       </c>
       <c r="BM40" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>5.4056495941170679E-2</v>
+        <v>5.4616826980202315E-2</v>
       </c>
       <c r="BN40" s="95" t="s">
         <v>677</v>
@@ -25445,7 +25275,7 @@
       </c>
       <c r="G41" s="12">
         <f t="array" aca="1" ref="G41" ca="1">_FV(A41,"Precio")</f>
-        <v>543.57500000000005</v>
+        <v>544.95000000000005</v>
       </c>
       <c r="H41" s="13">
         <f t="array" aca="1" ref="H41" ca="1">_FV(A41,"Acciones en circulación",TRUE())/1000000</f>
@@ -25453,7 +25283,7 @@
       </c>
       <c r="I41" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>111723.25276500001</v>
+        <v>112005.86229</v>
       </c>
       <c r="J41" s="91">
         <v>1</v>
@@ -25566,7 +25396,7 @@
       </c>
       <c r="AR41" s="19">
         <f ca="1">I41*'Framework Notes'!E8-AP41+AQ41</f>
-        <v>89350.723197646512</v>
+        <v>89593.230431049</v>
       </c>
       <c r="AS41" s="19">
         <v>3267</v>
@@ -25582,15 +25412,15 @@
       </c>
       <c r="AW41" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>27.349471440969243</v>
+        <v>27.423700774731863</v>
       </c>
       <c r="AX41" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>32.491172071871461</v>
+        <v>32.579356520381452</v>
       </c>
       <c r="AY41" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>4.9329610333819085</v>
+        <v>4.9463496069700765</v>
       </c>
       <c r="AZ41" s="21">
         <v>8834</v>
@@ -25637,11 +25467,11 @@
       </c>
       <c r="BL41" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-4.8715583537403684E-2</v>
+        <v>-4.9196118710194803E-2</v>
       </c>
       <c r="BM41" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>7.5679621724041413E-2</v>
+        <v>7.5136249117544684E-2</v>
       </c>
       <c r="BN41" s="95" t="s">
         <v>677</v>
@@ -26225,7 +26055,7 @@
         <v>6</v>
       </c>
       <c r="AG44" s="90">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH44" s="90">
         <v>0</v>
@@ -26241,15 +26071,15 @@
       </c>
       <c r="AL44" s="15">
         <f t="shared" si="32"/>
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AM44" s="16">
         <f t="shared" si="33"/>
-        <v>5.86</v>
+        <v>5.71</v>
       </c>
       <c r="AN44" s="17">
         <f t="shared" si="34"/>
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="AO44" s="18" t="s">
         <v>87</v>
@@ -26340,7 +26170,7 @@
         <v>0.11374623762627367</v>
       </c>
       <c r="BN44" s="95" t="s">
-        <v>677</v>
+        <v>836</v>
       </c>
       <c r="BO44" s="95" t="s">
         <v>84</v>
@@ -26605,7 +26435,7 @@
       </c>
       <c r="G46" s="12">
         <f t="array" aca="1" ref="G46" ca="1">_FV(A46,"Precio")</f>
-        <v>128.125</v>
+        <v>128.19</v>
       </c>
       <c r="H46" s="13">
         <f t="array" aca="1" ref="H46" ca="1">_FV(A46,"Acciones en circulación",TRUE())/1000000</f>
@@ -26613,7 +26443,7 @@
       </c>
       <c r="I46" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>13081.639375000001</v>
+        <v>13088.275914</v>
       </c>
       <c r="J46" s="90">
         <v>1</v>
@@ -26654,7 +26484,7 @@
         <v>11</v>
       </c>
       <c r="V46" s="90">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W46" s="90">
         <v>7</v>
@@ -26673,11 +26503,11 @@
       </c>
       <c r="AB46" s="15">
         <f t="shared" si="30"/>
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AC46" s="16">
         <f t="shared" si="31"/>
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AD46" s="90">
         <v>11</v>
@@ -26713,7 +26543,7 @@
       </c>
       <c r="AN46" s="17">
         <f t="shared" si="34"/>
-        <v>5.25</v>
+        <v>5.29</v>
       </c>
       <c r="AO46" s="18" t="s">
         <v>78</v>
@@ -26726,7 +26556,7 @@
       </c>
       <c r="AR46" s="19">
         <f t="shared" ca="1" si="45"/>
-        <v>12771.639375000001</v>
+        <v>12778.275914</v>
       </c>
       <c r="AS46" s="19">
         <v>1100</v>
@@ -26742,15 +26572,15 @@
       </c>
       <c r="AW46" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>11.610581250000001</v>
+        <v>11.616614467272727</v>
       </c>
       <c r="AX46" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>15.096500443262412</v>
+        <v>15.104345052009457</v>
       </c>
       <c r="AY46" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>4.6274055706521739</v>
+        <v>4.6298101137681158</v>
       </c>
       <c r="AZ46" s="21">
         <v>5759</v>
@@ -26797,14 +26627,14 @@
       </c>
       <c r="BL46" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.10303518309874493</v>
+        <v>-0.10312616451989021</v>
       </c>
       <c r="BM46" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.15498417797007802</v>
+        <v>0.15486702498934557</v>
       </c>
       <c r="BN46" s="95" t="s">
-        <v>677</v>
+        <v>836</v>
       </c>
       <c r="BO46" s="93" t="s">
         <v>106</v>
@@ -27301,7 +27131,7 @@
       </c>
       <c r="G49" s="12">
         <f t="array" aca="1" ref="G49" ca="1">_FV(A49,"Precio")</f>
-        <v>49.04</v>
+        <v>49.15</v>
       </c>
       <c r="H49" s="13">
         <f t="array" aca="1" ref="H49" ca="1">_FV(A49,"Acciones en circulación",TRUE())/1000000</f>
@@ -27309,7 +27139,7 @@
       </c>
       <c r="I49" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>10102.387119999999</v>
+        <v>10125.047449999998</v>
       </c>
       <c r="J49" s="91">
         <v>0</v>
@@ -27365,15 +27195,15 @@
         <v>5</v>
       </c>
       <c r="AA49" s="91">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="AB49" s="26">
         <f t="shared" si="30"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AC49" s="16">
         <f t="shared" si="31"/>
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AD49" s="91">
         <v>11</v>
@@ -27409,7 +27239,7 @@
       </c>
       <c r="AN49" s="17">
         <f t="shared" si="34"/>
-        <v>5.52</v>
+        <v>5.56</v>
       </c>
       <c r="AO49" s="18" t="s">
         <v>78</v>
@@ -27422,7 +27252,7 @@
       </c>
       <c r="AR49" s="19">
         <f ca="1">I49*'Framework Notes'!E7-AP49+AQ49</f>
-        <v>7477.7494425360001</v>
+        <v>7499.1342019599988</v>
       </c>
       <c r="AS49" s="19">
         <v>395</v>
@@ -27438,15 +27268,15 @@
       </c>
       <c r="AW49" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>18.931011246926584</v>
+        <v>18.985149878379744</v>
       </c>
       <c r="AX49" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>19.834879157920426</v>
+        <v>19.891602657718831</v>
       </c>
       <c r="AY49" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>15.291921150380368</v>
+        <v>15.335652764744374</v>
       </c>
       <c r="AZ49" s="21">
         <v>2539</v>
@@ -27485,22 +27315,22 @@
       </c>
       <c r="BJ49" s="25">
         <f ca="1">((BD49*BH49+$AP49-$AQ49)/$H49)/'Framework Notes'!E7</f>
-        <v>38.676686922164507</v>
+        <v>38.649857921802301</v>
       </c>
       <c r="BK49" s="25">
         <f ca="1">((BF49*BI49+$AP49-$AQ49)/$H49)/'Framework Notes'!E7</f>
-        <v>88.789919881428375</v>
+        <v>88.728328649546143</v>
       </c>
       <c r="BL49" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-4.6370316805624201E-2</v>
+        <v>-4.6929832019531381E-2</v>
       </c>
       <c r="BM49" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.12606287500346403</v>
+        <v>0.12540218949683202</v>
       </c>
       <c r="BN49" s="95" t="s">
-        <v>677</v>
+        <v>836</v>
       </c>
       <c r="BO49" s="95" t="s">
         <v>98</v>
@@ -27533,7 +27363,7 @@
       </c>
       <c r="G50" s="12">
         <f t="array" aca="1" ref="G50" ca="1">_FV(A50,"Precio")</f>
-        <v>81.665000000000006</v>
+        <v>81.465000000000003</v>
       </c>
       <c r="H50" s="13">
         <f t="array" aca="1" ref="H50" ca="1">_FV(A50,"Acciones en circulación",TRUE())/1000000</f>
@@ -27541,7 +27371,7 @@
       </c>
       <c r="I50" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>340048.07843500003</v>
+        <v>339215.29063500004</v>
       </c>
       <c r="J50" s="90">
         <v>0.5</v>
@@ -27656,7 +27486,7 @@
       </c>
       <c r="AR50" s="19">
         <f t="shared" ref="AR50:AR62" ca="1" si="48">I50-AP50+AQ50</f>
-        <v>345278.07843500003</v>
+        <v>344445.29063500004</v>
       </c>
       <c r="AS50" s="19">
         <v>11560</v>
@@ -27672,15 +27502,15 @@
       </c>
       <c r="AW50" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>29.868345885380627</v>
+        <v>29.796305418252597</v>
       </c>
       <c r="AX50" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>23.440466967752887</v>
+        <v>23.383930117786832</v>
       </c>
       <c r="AY50" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>7.1382691427537734</v>
+        <v>7.121052111536077</v>
       </c>
       <c r="AZ50" s="21">
         <v>46315</v>
@@ -27727,11 +27557,11 @@
       </c>
       <c r="BL50" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-7.1847606201125291E-2</v>
+        <v>-7.1392322448425638E-2</v>
       </c>
       <c r="BM50" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>7.1588148646349659E-2</v>
+        <v>7.2113791500824531E-2</v>
       </c>
       <c r="BN50" s="95" t="s">
         <v>677</v>
@@ -27767,7 +27597,7 @@
       </c>
       <c r="G51" s="12">
         <f t="array" aca="1" ref="G51" ca="1">_FV(A51,"Precio")</f>
-        <v>38.594999999999999</v>
+        <v>38.534999999999997</v>
       </c>
       <c r="H51" s="13">
         <f t="array" aca="1" ref="H51" ca="1">_FV(A51,"Acciones en circulación",TRUE())/1000000</f>
@@ -27775,7 +27605,7 @@
       </c>
       <c r="I51" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>57255.643904999997</v>
+        <v>57166.633964999994</v>
       </c>
       <c r="J51" s="91">
         <v>0</v>
@@ -27888,7 +27718,7 @@
       </c>
       <c r="AR51" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>59265.643904999997</v>
+        <v>59176.633964999994</v>
       </c>
       <c r="AS51" s="19">
         <v>2180</v>
@@ -27904,15 +27734,15 @@
       </c>
       <c r="AW51" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>27.186075185779814</v>
+        <v>27.145244938073393</v>
       </c>
       <c r="AX51" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>12.021428783975658</v>
+        <v>12.003374029411763</v>
       </c>
       <c r="AY51" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>1.2772768082974137</v>
+        <v>1.275358490625</v>
       </c>
       <c r="AZ51" s="21">
         <v>25863</v>
@@ -27959,11 +27789,11 @@
       </c>
       <c r="BL51" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.13016719470932003</v>
+        <v>-0.12989649278019666</v>
       </c>
       <c r="BM51" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>3.6288543494115144E-2</v>
+        <v>3.6611048354987297E-2</v>
       </c>
       <c r="BN51" s="95" t="s">
         <v>677</v>
@@ -28231,7 +28061,7 @@
       </c>
       <c r="G53" s="12">
         <f t="array" aca="1" ref="G53" ca="1">_FV(A53,"Precio")</f>
-        <v>235.95</v>
+        <v>235.62</v>
       </c>
       <c r="H53" s="13">
         <f t="array" aca="1" ref="H53" ca="1">_FV(A53,"Acciones en circulación",TRUE())/1000000</f>
@@ -28239,7 +28069,7 @@
       </c>
       <c r="I53" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>45645.164564999999</v>
+        <v>45581.325173999998</v>
       </c>
       <c r="J53" s="91">
         <v>0</v>
@@ -28352,7 +28182,7 @@
       </c>
       <c r="AR53" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>52095.164564999999</v>
+        <v>52031.325173999998</v>
       </c>
       <c r="AS53" s="19">
         <v>1118</v>
@@ -28368,15 +28198,15 @@
       </c>
       <c r="AW53" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>46.596748269230766</v>
+        <v>46.539646846153843</v>
       </c>
       <c r="AX53" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>16.963583381634646</v>
+        <v>16.94279556300879</v>
       </c>
       <c r="AY53" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>1.6566547276283152</v>
+        <v>1.6546246000763212</v>
       </c>
       <c r="AZ53" s="21">
         <v>12926</v>
@@ -28423,11 +28253,11 @@
       </c>
       <c r="BL53" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.12201415457522202</v>
+        <v>-0.12176835782745332</v>
       </c>
       <c r="BM53" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>7.7652539212711869E-2</v>
+        <v>7.7954233699864872E-2</v>
       </c>
       <c r="BN53" s="95" t="s">
         <v>677</v>
@@ -28463,7 +28293,7 @@
       </c>
       <c r="G54" s="12">
         <f t="array" aca="1" ref="G54" ca="1">_FV(A54,"Precio")</f>
-        <v>20.39</v>
+        <v>20.405000000000001</v>
       </c>
       <c r="H54" s="13">
         <f t="array" aca="1" ref="H54" ca="1">_FV(A54,"Acciones en circulación",TRUE())/1000000</f>
@@ -28471,7 +28301,7 @@
       </c>
       <c r="I54" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>6989.7674429999997</v>
+        <v>6994.9094985000002</v>
       </c>
       <c r="J54" s="90">
         <v>1</v>
@@ -28584,7 +28414,7 @@
       </c>
       <c r="AR54" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>6332.7674429999997</v>
+        <v>6337.9094985000002</v>
       </c>
       <c r="AS54" s="19">
         <v>62</v>
@@ -28600,15 +28430,15 @@
       </c>
       <c r="AW54" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>102.14141037096773</v>
+        <v>102.22434675000001</v>
       </c>
       <c r="AX54" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>-24.450839548262547</v>
+        <v>-24.470693044401546</v>
       </c>
       <c r="AY54" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>6.0312070885714286</v>
+        <v>6.036104284285714</v>
       </c>
       <c r="AZ54" s="21">
         <v>1684</v>
@@ -28655,11 +28485,11 @@
       </c>
       <c r="BL54" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.20030809486487711</v>
+        <v>-0.20042570238579438</v>
       </c>
       <c r="BM54" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>-9.8391813915595927E-3</v>
+        <v>-9.9848004211360308E-3</v>
       </c>
       <c r="BN54" s="96" t="s">
         <v>677</v>
@@ -28695,7 +28525,7 @@
       </c>
       <c r="G55" s="12">
         <f t="array" aca="1" ref="G55" ca="1">_FV(A55,"Precio")</f>
-        <v>47.125</v>
+        <v>47.085000000000001</v>
       </c>
       <c r="H55" s="13">
         <f t="array" aca="1" ref="H55" ca="1">_FV(A55,"Acciones en circulación",TRUE())/1000000</f>
@@ -28703,7 +28533,7 @@
       </c>
       <c r="I55" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>4800.3975499999997</v>
+        <v>4796.3229419999998</v>
       </c>
       <c r="J55" s="91">
         <v>1</v>
@@ -28816,7 +28646,7 @@
       </c>
       <c r="AR55" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>5096.8975499999997</v>
+        <v>5092.8229419999998</v>
       </c>
       <c r="AS55" s="19">
         <v>283</v>
@@ -28832,15 +28662,15 @@
       </c>
       <c r="AW55" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>18.010238692579506</v>
+        <v>17.995840784452295</v>
       </c>
       <c r="AX55" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>16.28401773162939</v>
+        <v>16.270999814696484</v>
       </c>
       <c r="AY55" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>4.2192860513245032</v>
+        <v>4.2159130314569531</v>
       </c>
       <c r="AZ55" s="21">
         <v>1176</v>
@@ -28887,11 +28717,11 @@
       </c>
       <c r="BL55" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-8.3773419112029512E-2</v>
+        <v>-8.3617800057869895E-2</v>
       </c>
       <c r="BM55" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.14660181108748027</v>
+        <v>0.14679655886391596</v>
       </c>
       <c r="BN55" s="95" t="s">
         <v>677</v>
@@ -29391,7 +29221,7 @@
       </c>
       <c r="G58" s="12">
         <f t="array" aca="1" ref="G58" ca="1">_FV(A58,"Precio")</f>
-        <v>34.862299999999998</v>
+        <v>34.82</v>
       </c>
       <c r="H58" s="13">
         <f t="array" aca="1" ref="H58" ca="1">_FV(A58,"Acciones en circulación",TRUE())/1000000</f>
@@ -29399,7 +29229,7 @@
       </c>
       <c r="I58" s="14">
         <f t="shared" ca="1" si="25"/>
-        <v>8821.3820804999996</v>
+        <v>8810.6787000000004</v>
       </c>
       <c r="J58" s="90">
         <v>0</v>
@@ -29512,7 +29342,7 @@
       </c>
       <c r="AR58" s="19">
         <f t="shared" ca="1" si="48"/>
-        <v>8858.3820804999996</v>
+        <v>8847.6787000000004</v>
       </c>
       <c r="AS58" s="19">
         <v>447</v>
@@ -29528,15 +29358,15 @@
       </c>
       <c r="AW58" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>19.817409576062637</v>
+        <v>19.793464653243849</v>
       </c>
       <c r="AX58" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>12.320420139777468</v>
+        <v>12.305533657858136</v>
       </c>
       <c r="AY58" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>2.9072471547423695</v>
+        <v>2.90373439448638</v>
       </c>
       <c r="AZ58" s="21">
         <v>3400</v>
@@ -29583,11 +29413,11 @@
       </c>
       <c r="BL58" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-5.0859368041703101E-2</v>
+        <v>-5.0628873190454948E-2</v>
       </c>
       <c r="BM58" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.30172060701312775</v>
+        <v>0.30203672444354601</v>
       </c>
       <c r="BN58" s="96" t="s">
         <v>677</v>
@@ -30552,7 +30382,7 @@
       </c>
       <c r="G63" s="12">
         <f t="array" aca="1" ref="G63" ca="1">_FV(A63,"Precio")</f>
-        <v>34.97</v>
+        <v>35.35</v>
       </c>
       <c r="H63" s="13">
         <f t="array" aca="1" ref="H63" ca="1">_FV(A63,"Acciones en circulación",TRUE())/1000000</f>
@@ -30560,7 +30390,7 @@
       </c>
       <c r="I63" s="14">
         <f ca="1">G63*H63</f>
-        <v>3945.5531960000003</v>
+        <v>3988.4273800000005</v>
       </c>
       <c r="J63" s="91">
         <v>0</v>
@@ -30673,7 +30503,7 @@
       </c>
       <c r="AR63" s="19">
         <f ca="1">I63*'Framework Notes'!E7-AP63+AQ63</f>
-        <v>3347.6819670788004</v>
+        <v>3380.558455504</v>
       </c>
       <c r="AS63" s="19">
         <v>18.600000000000001</v>
@@ -30689,15 +30519,15 @@
       </c>
       <c r="AW63" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>179.98290145584946</v>
+        <v>181.75045459698924</v>
       </c>
       <c r="AX63" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>13.231944533908303</v>
+        <v>13.361891128474308</v>
       </c>
       <c r="AY63" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>4.7350522872401699</v>
+        <v>4.7815536852956155</v>
       </c>
       <c r="AZ63" s="21">
         <v>1833</v>
@@ -30736,19 +30566,19 @@
       </c>
       <c r="BJ63" s="25">
         <f ca="1">((BD63*BH63+$AP63-$AQ63)/$H63)/'Framework Notes'!$E$7</f>
-        <v>15.679997803013649</v>
+        <v>15.669121000986031</v>
       </c>
       <c r="BK63" s="25">
         <f ca="1">((BF63*BI63+$AP63-$AQ63)/$H63)/'Framework Notes'!$E$7</f>
-        <v>68.529084018146378</v>
+        <v>68.481547195159322</v>
       </c>
       <c r="BL63" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-0.14821483291193238</v>
+        <v>-0.15017198595365444</v>
       </c>
       <c r="BM63" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.14402590583034525</v>
+        <v>0.14139726909432526</v>
       </c>
       <c r="BN63" s="95" t="s">
         <v>677</v>
@@ -30784,7 +30614,7 @@
       </c>
       <c r="G64" s="12">
         <f t="array" aca="1" ref="G64" ca="1">_FV(A64,"Precio")</f>
-        <v>15.16</v>
+        <v>15.065</v>
       </c>
       <c r="H64" s="13">
         <f t="array" aca="1" ref="H64" ca="1">_FV(A64,"Acciones en circulación",TRUE())/1000000</f>
@@ -30792,7 +30622,7 @@
       </c>
       <c r="I64" s="14">
         <f ca="1">G64*H64</f>
-        <v>483.78986159999999</v>
+        <v>480.75819689999997</v>
       </c>
       <c r="J64" s="90">
         <v>1</v>
@@ -30905,7 +30735,7 @@
       </c>
       <c r="AR64" s="19">
         <f t="shared" ref="AR64:AR71" ca="1" si="51">I64-AP64+AQ64</f>
-        <v>988.18986159999997</v>
+        <v>985.15819689999989</v>
       </c>
       <c r="AS64" s="19">
         <v>-21.9</v>
@@ -30921,15 +30751,15 @@
       </c>
       <c r="AW64" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>-45.122824730593607</v>
+        <v>-44.984392552511416</v>
       </c>
       <c r="AX64" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>-70.584990114285716</v>
+        <v>-70.368442635714274</v>
       </c>
       <c r="AY64" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>1.0683133638918918</v>
+        <v>1.0650358885405404</v>
       </c>
       <c r="AZ64" s="21">
         <v>169</v>
@@ -30980,7 +30810,7 @@
       </c>
       <c r="BM64" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.22224173389787061</v>
+        <v>0.22377935333798527</v>
       </c>
       <c r="BN64" s="95" t="s">
         <v>677</v>
@@ -31016,7 +30846,7 @@
       </c>
       <c r="G65" s="12">
         <f t="array" aca="1" ref="G65" ca="1">_FV(A65,"Precio")</f>
-        <v>3065.55</v>
+        <v>3060.66</v>
       </c>
       <c r="H65" s="13">
         <f t="array" aca="1" ref="H65" ca="1">_FV(A65,"Acciones en circulación",TRUE())/1000000</f>
@@ -31024,7 +30854,7 @@
       </c>
       <c r="I65" s="14">
         <f ca="1">G65*H65</f>
-        <v>64963.694791500006</v>
+        <v>64860.068209799996</v>
       </c>
       <c r="J65" s="90">
         <v>2</v>
@@ -31137,7 +30967,7 @@
       </c>
       <c r="AR65" s="19">
         <f ca="1">I65*'Framework Notes'!$E$7-AP65+AQ65</f>
-        <v>47835.349358317457</v>
+        <v>47793.137165623833</v>
       </c>
       <c r="AS65" s="19">
         <v>2700</v>
@@ -31153,15 +30983,15 @@
       </c>
       <c r="AW65" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>17.716796058636096</v>
+        <v>17.701161913194014</v>
       </c>
       <c r="AX65" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>13.954302613278138</v>
+        <v>13.941988671418855</v>
       </c>
       <c r="AY65" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>3.784142817681944</v>
+        <v>3.7808035096609314</v>
       </c>
       <c r="AZ65" s="21">
         <v>5000</v>
@@ -31200,19 +31030,19 @@
       </c>
       <c r="BJ65" s="25">
         <f ca="1">((BD65*BH65+$AP65-$AQ65)/$H65)/'Framework Notes'!$E$7</f>
-        <v>2368.8015160277814</v>
+        <v>2367.1583407253206</v>
       </c>
       <c r="BK65" s="25">
         <f ca="1">((BF65*BI65+$AP65-$AQ65)/$H65)/'Framework Notes'!$E$7</f>
-        <v>7426.3676711620456</v>
+        <v>7421.2161952525275</v>
       </c>
       <c r="BL65" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-5.0261477899727125E-2</v>
+        <v>-5.0090033624921482E-2</v>
       </c>
       <c r="BM65" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.19358570431104249</v>
+        <v>0.19380116723134355</v>
       </c>
       <c r="BN65" s="95" t="s">
         <v>677</v>
@@ -31248,7 +31078,7 @@
       </c>
       <c r="G66" s="12">
         <f t="array" aca="1" ref="G66" ca="1">_FV(A66,"Precio")</f>
-        <v>79.709999999999994</v>
+        <v>79.53</v>
       </c>
       <c r="H66" s="13">
         <f t="array" aca="1" ref="H66" ca="1">_FV(A66,"Acciones en circulación",TRUE())/1000000</f>
@@ -31256,7 +31086,7 @@
       </c>
       <c r="I66" s="14">
         <f ca="1">G66*H66</f>
-        <v>162812.45759999999</v>
+        <v>162444.79680000001</v>
       </c>
       <c r="J66" s="90">
         <v>1</v>
@@ -31369,7 +31199,7 @@
       </c>
       <c r="AR66" s="19">
         <f t="shared" ca="1" si="51"/>
-        <v>172152.45759999999</v>
+        <v>171784.79680000001</v>
       </c>
       <c r="AS66" s="19">
         <v>10116</v>
@@ -31385,15 +31215,15 @@
       </c>
       <c r="AW66" s="20">
         <f t="shared" ca="1" si="35"/>
-        <v>17.017838829576906</v>
+        <v>16.981494345591145</v>
       </c>
       <c r="AX66" s="20">
         <f t="shared" ca="1" si="36"/>
-        <v>23.030429110367891</v>
+        <v>22.981243719063546</v>
       </c>
       <c r="AY66" s="20">
         <f t="shared" ca="1" si="37"/>
-        <v>3.117179234794575</v>
+        <v>3.1105219693265975</v>
       </c>
       <c r="AZ66" s="21">
         <v>37739</v>
@@ -31440,11 +31270,11 @@
       </c>
       <c r="BL66" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-6.5167949024175775E-2</v>
+        <v>-6.4745171109066635E-2</v>
       </c>
       <c r="BM66" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.31337697352450511</v>
+        <v>0.31397094842945128</v>
       </c>
       <c r="BN66" s="95" t="s">
         <v>677</v>
@@ -32353,26 +32183,26 @@
         <v>0.10563340590814718</v>
       </c>
       <c r="BH70" s="24">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BI70" s="24">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BJ70" s="25">
         <f t="shared" ca="1" si="72"/>
-        <v>1871.6269105590575</v>
+        <v>1587.3604416429778</v>
       </c>
       <c r="BK70" s="25">
         <f t="shared" ca="1" si="73"/>
-        <v>4483.5825814691225</v>
+        <v>3857.3723890742799</v>
       </c>
       <c r="BL70" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-1.1047858513933972E-3</v>
+        <v>-3.3479239811330386E-2</v>
       </c>
       <c r="BM70" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.18960042545621669</v>
+        <v>0.15434171348505243</v>
       </c>
       <c r="BN70" s="96" t="s">
         <v>677</v>
@@ -32408,7 +32238,7 @@
       </c>
       <c r="G71" s="12">
         <f t="shared" ca="1" si="63"/>
-        <v>78.55</v>
+        <v>78.28</v>
       </c>
       <c r="H71" s="13">
         <f t="shared" ca="1" si="64"/>
@@ -32416,7 +32246,7 @@
       </c>
       <c r="I71" s="14">
         <f t="shared" ca="1" si="65"/>
-        <v>1172.178085</v>
+        <v>1168.148956</v>
       </c>
       <c r="J71" s="90">
         <v>2</v>
@@ -32529,7 +32359,7 @@
       </c>
       <c r="AR71" s="19">
         <f t="shared" ca="1" si="51"/>
-        <v>1533.0780849999999</v>
+        <v>1529.0489559999999</v>
       </c>
       <c r="AS71" s="19">
         <v>62</v>
@@ -32545,15 +32375,15 @@
       </c>
       <c r="AW71" s="20">
         <f t="shared" ca="1" si="56"/>
-        <v>24.727065887096771</v>
+        <v>24.66207993548387</v>
       </c>
       <c r="AX71" s="20">
         <f t="shared" ca="1" si="57"/>
-        <v>15.969563385416665</v>
+        <v>15.927593291666666</v>
       </c>
       <c r="AY71" s="20">
         <f t="shared" ca="1" si="58"/>
-        <v>1.9061023063533507</v>
+        <v>1.9010928210866591</v>
       </c>
       <c r="AZ71" s="21">
         <v>1127.5999999999999</v>
@@ -32600,11 +32430,11 @@
       </c>
       <c r="BL71" s="23">
         <f t="shared" ca="1" si="43"/>
-        <v>-7.8447840067314756E-2</v>
+        <v>-7.7812999736502353E-2</v>
       </c>
       <c r="BM71" s="23">
         <f t="shared" ca="1" si="44"/>
-        <v>0.15111300110900605</v>
+        <v>0.15190598168047975</v>
       </c>
       <c r="BN71" s="96" t="s">
         <v>541</v>
@@ -32870,7 +32700,7 @@
       </c>
       <c r="G73" s="12">
         <f t="shared" ca="1" si="76"/>
-        <v>82.67</v>
+        <v>83.08</v>
       </c>
       <c r="H73" s="13">
         <f t="shared" ca="1" si="77"/>
@@ -32878,7 +32708,7 @@
       </c>
       <c r="I73" s="14">
         <f t="shared" ca="1" si="78"/>
-        <v>55157.09332</v>
+        <v>55430.643680000001</v>
       </c>
       <c r="J73" s="90">
         <v>1</v>
@@ -32991,7 +32821,7 @@
       </c>
       <c r="AR73" s="19">
         <f t="shared" ref="AR73" ca="1" si="90">I73-AP73+AQ73</f>
-        <v>57667.09332</v>
+        <v>57940.643680000001</v>
       </c>
       <c r="AS73" s="19">
         <v>2200</v>
@@ -33007,15 +32837,15 @@
       </c>
       <c r="AW73" s="20">
         <f t="shared" ref="AW73" ca="1" si="91">AR73/AS73</f>
-        <v>26.212315145454546</v>
+        <v>26.336656218181819</v>
       </c>
       <c r="AX73" s="20">
         <f t="shared" ref="AX73" ca="1" si="92">AR73/AU73</f>
-        <v>13.473619934579439</v>
+        <v>13.537533570093458</v>
       </c>
       <c r="AY73" s="20">
         <f t="shared" ref="AY73" ca="1" si="93">AR73/AV73</f>
-        <v>3.2379052959011791</v>
+        <v>3.2532646647950592</v>
       </c>
       <c r="AZ73" s="21">
         <v>30853</v>
@@ -33062,11 +32892,11 @@
       </c>
       <c r="BL73" s="23">
         <f t="shared" ref="BL73" ca="1" si="96">IF($BJ73&lt;=0,-0.99,MAX(-0.99,($BJ73/G73)^(1/5)-1))</f>
-        <v>-0.12500350133508487</v>
+        <v>-0.12586883315652864</v>
       </c>
       <c r="BM73" s="23">
         <f t="shared" ref="BM73" ca="1" si="97">IF(BK73&lt;=0,-0.99,MAX(-0.99,(BK73/G73)^(1/5)-1))</f>
-        <v>6.4622048043704305E-2</v>
+        <v>6.3569185160951669E-2</v>
       </c>
       <c r="BN73" s="96" t="s">
         <v>836</v>
@@ -33130,7 +32960,7 @@
       </c>
       <c r="E4" s="29">
         <f t="array" aca="1" ref="E4" ca="1">_FV(D4,"Precio")</f>
-        <v>185.65</v>
+        <v>185.62</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33142,7 +32972,7 @@
       </c>
       <c r="E5" s="30">
         <f t="array" aca="1" ref="E5" ca="1">_FV(D5,"Precio")</f>
-        <v>1.2415</v>
+        <v>1.2416</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33154,7 +32984,7 @@
       </c>
       <c r="E6" s="31">
         <f t="array" aca="1" ref="E6" ca="1">_FV(D6,"Precio")</f>
-        <v>459.26</v>
+        <v>459.23</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33163,7 +32993,7 @@
       </c>
       <c r="E7" s="30">
         <f t="array" aca="1" ref="E7" ca="1">_FV(D7,"Precio")</f>
-        <v>0.72030000000000005</v>
+        <v>0.7208</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -33574,7 +33404,7 @@
       <c r="D4" s="138"/>
       <c r="E4" s="140" t="str">
         <f>TEXT(AVERAGE('Watchlist Ratings'!BC4:BC71),"0.0%")</f>
-        <v>15.5%</v>
+        <v>15.8%</v>
       </c>
       <c r="F4" s="138"/>
       <c r="G4" s="140" t="str">
@@ -33847,7 +33677,7 @@
       </c>
       <c r="Q8" s="23">
         <f ca="1">'Watchlist Ratings'!BM4</f>
-        <v>0.21440325563515295</v>
+        <v>0.21485168962191081</v>
       </c>
       <c r="S8" t="str">
         <f ca="1">'Watchlist Ratings'!B4</f>
@@ -33875,7 +33705,7 @@
       </c>
       <c r="Z8">
         <f ca="1">'Watchlist Ratings'!AW4</f>
-        <v>20.038650331097561</v>
+        <v>19.993582220426831</v>
       </c>
       <c r="AA8" t="str">
         <f ca="1">'Watchlist Ratings'!B4</f>
@@ -33883,11 +33713,11 @@
       </c>
       <c r="AB8">
         <f ca="1">'Watchlist Ratings'!BL4</f>
-        <v>-3.1447161351016106E-2</v>
+        <v>-3.1089510785764829E-2</v>
       </c>
       <c r="AC8">
         <f ca="1">'Watchlist Ratings'!BM4</f>
-        <v>0.21440325563515295</v>
+        <v>0.21485168962191081</v>
       </c>
       <c r="AE8" t="s">
         <v>252</v>
@@ -33973,7 +33803,7 @@
       </c>
       <c r="J9" s="44">
         <f ca="1">'Watchlist Ratings'!AW5</f>
-        <v>29.13968503016541</v>
+        <v>29.094517683917385</v>
       </c>
       <c r="O9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -33985,7 +33815,7 @@
       </c>
       <c r="Q9" s="23">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>0.12530205264345784</v>
+        <v>0.12564775439289733</v>
       </c>
       <c r="S9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -34013,7 +33843,7 @@
       </c>
       <c r="Z9">
         <f ca="1">'Watchlist Ratings'!AW5</f>
-        <v>29.13968503016541</v>
+        <v>29.094517683917385</v>
       </c>
       <c r="AA9" t="str">
         <f ca="1">'Watchlist Ratings'!B5</f>
@@ -34021,11 +33851,11 @@
       </c>
       <c r="AB9">
         <f ca="1">'Watchlist Ratings'!BL5</f>
-        <v>-4.4021554335645474E-2</v>
+        <v>-4.3727870146306191E-2</v>
       </c>
       <c r="AC9">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>0.12530205264345784</v>
+        <v>0.12564775439289733</v>
       </c>
       <c r="AE9" t="s">
         <v>256</v>
@@ -34245,11 +34075,11 @@
       </c>
       <c r="I11" s="43">
         <f>'Watchlist Ratings'!BC7</f>
-        <v>6.3333333333333339E-2</v>
+        <v>0.13417131558505757</v>
       </c>
       <c r="J11" s="44">
         <f ca="1">'Watchlist Ratings'!AW7</f>
-        <v>17.844525084677421</v>
+        <v>17.862716712096773</v>
       </c>
       <c r="O11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -34261,7 +34091,7 @@
       </c>
       <c r="Q11" s="23">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.21981528931254024</v>
+        <v>0.21954785350683115</v>
       </c>
       <c r="S11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -34269,7 +34099,7 @@
       </c>
       <c r="T11" s="23">
         <f>'Watchlist Ratings'!BC7</f>
-        <v>6.3333333333333339E-2</v>
+        <v>0.13417131558505757</v>
       </c>
       <c r="V11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -34289,7 +34119,7 @@
       </c>
       <c r="Z11">
         <f ca="1">'Watchlist Ratings'!AW7</f>
-        <v>17.844525084677421</v>
+        <v>17.862716712096773</v>
       </c>
       <c r="AA11" t="str">
         <f ca="1">'Watchlist Ratings'!B7</f>
@@ -34297,11 +34127,11 @@
       </c>
       <c r="AB11">
         <f ca="1">'Watchlist Ratings'!BL7</f>
-        <v>1.7198856723277256E-2</v>
+        <v>1.6975843125892842E-2</v>
       </c>
       <c r="AC11">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.21981528931254024</v>
+        <v>0.21954785350683115</v>
       </c>
       <c r="AE11" t="s">
         <v>261</v>
@@ -34387,7 +34217,7 @@
       </c>
       <c r="J12" s="50">
         <f ca="1">'Watchlist Ratings'!AW8</f>
-        <v>34.720435281427967</v>
+        <v>34.700114602267952</v>
       </c>
       <c r="O12" t="str">
         <f ca="1">'Watchlist Ratings'!B8</f>
@@ -34399,7 +34229,7 @@
       </c>
       <c r="Q12" s="23">
         <f ca="1">'Watchlist Ratings'!BM8</f>
-        <v>8.5666007165993152E-2</v>
+        <v>8.5789611564482282E-2</v>
       </c>
       <c r="S12" t="str">
         <f ca="1">'Watchlist Ratings'!B8</f>
@@ -34427,7 +34257,7 @@
       </c>
       <c r="Z12">
         <f ca="1">'Watchlist Ratings'!AW8</f>
-        <v>34.720435281427967</v>
+        <v>34.700114602267952</v>
       </c>
       <c r="AA12" t="str">
         <f ca="1">'Watchlist Ratings'!B8</f>
@@ -34435,11 +34265,11 @@
       </c>
       <c r="AB12">
         <f ca="1">'Watchlist Ratings'!BL8</f>
-        <v>-4.9160074465740333E-2</v>
+        <v>-4.905182018101617E-2</v>
       </c>
       <c r="AC12">
         <f ca="1">'Watchlist Ratings'!BM8</f>
-        <v>8.5666007165993152E-2</v>
+        <v>8.5789611564482282E-2</v>
       </c>
       <c r="AE12" t="s">
         <v>264</v>
@@ -34525,7 +34355,7 @@
       </c>
       <c r="J13" s="44">
         <f ca="1">'Watchlist Ratings'!AW9</f>
-        <v>22.008759881138793</v>
+        <v>21.966085459786481</v>
       </c>
       <c r="L13" s="36" t="s">
         <v>266</v>
@@ -34543,7 +34373,7 @@
       </c>
       <c r="Q13" s="23">
         <f ca="1">'Watchlist Ratings'!BM9</f>
-        <v>0.19992256658649676</v>
+        <v>0.20036217929528854</v>
       </c>
       <c r="S13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -34571,7 +34401,7 @@
       </c>
       <c r="Z13">
         <f ca="1">'Watchlist Ratings'!AW9</f>
-        <v>22.008759881138793</v>
+        <v>21.966085459786481</v>
       </c>
       <c r="AA13" t="str">
         <f ca="1">'Watchlist Ratings'!B9</f>
@@ -34579,11 +34409,11 @@
       </c>
       <c r="AB13">
         <f ca="1">'Watchlist Ratings'!BL9</f>
-        <v>-3.4688426625229307E-2</v>
+        <v>-3.4334767774719888E-2</v>
       </c>
       <c r="AC13">
         <f ca="1">'Watchlist Ratings'!BM9</f>
-        <v>0.19992256658649676</v>
+        <v>0.20036217929528854</v>
       </c>
       <c r="AE13" t="s">
         <v>259</v>
@@ -34814,7 +34644,7 @@
       </c>
       <c r="J15" s="44">
         <f ca="1">'Watchlist Ratings'!AW11</f>
-        <v>26.411349215991695</v>
+        <v>26.436537611630321</v>
       </c>
       <c r="L15" t="s">
         <v>273</v>
@@ -34833,7 +34663,7 @@
       </c>
       <c r="Q15" s="23">
         <f ca="1">'Watchlist Ratings'!BM11</f>
-        <v>0.26082680899108857</v>
+        <v>0.26060125856359373</v>
       </c>
       <c r="S15" t="str">
         <f ca="1">'Watchlist Ratings'!B11</f>
@@ -34861,7 +34691,7 @@
       </c>
       <c r="Z15">
         <f ca="1">'Watchlist Ratings'!AW11</f>
-        <v>26.411349215991695</v>
+        <v>26.436537611630321</v>
       </c>
       <c r="AA15" t="str">
         <f ca="1">'Watchlist Ratings'!B11</f>
@@ -34869,11 +34699,11 @@
       </c>
       <c r="AB15">
         <f ca="1">'Watchlist Ratings'!BL11</f>
-        <v>-2.3220994598323275E-2</v>
+        <v>-2.3395731461994917E-2</v>
       </c>
       <c r="AC15">
         <f ca="1">'Watchlist Ratings'!BM11</f>
-        <v>0.26082680899108857</v>
+        <v>0.26060125856359373</v>
       </c>
       <c r="AE15" t="s">
         <v>272</v>
@@ -34959,7 +34789,7 @@
       </c>
       <c r="J16" s="50">
         <f ca="1">'Watchlist Ratings'!AW12</f>
-        <v>36.235881509576579</v>
+        <v>36.228815108011574</v>
       </c>
       <c r="L16" t="s">
         <v>276</v>
@@ -34978,7 +34808,7 @@
       </c>
       <c r="Q16" s="23">
         <f ca="1">'Watchlist Ratings'!BM12</f>
-        <v>2.2805303231882901E-2</v>
+        <v>2.2838362358715614E-2</v>
       </c>
       <c r="S16" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
@@ -35006,7 +34836,7 @@
       </c>
       <c r="Z16">
         <f ca="1">'Watchlist Ratings'!AW12</f>
-        <v>36.235881509576579</v>
+        <v>36.228815108011574</v>
       </c>
       <c r="AA16" t="str">
         <f ca="1">'Watchlist Ratings'!B12</f>
@@ -35014,11 +34844,11 @@
       </c>
       <c r="AB16">
         <f ca="1">'Watchlist Ratings'!BL12</f>
-        <v>-0.12449931393740532</v>
+        <v>-0.12447101599239929</v>
       </c>
       <c r="AC16">
         <f ca="1">'Watchlist Ratings'!BM12</f>
-        <v>2.2805303231882901E-2</v>
+        <v>2.2838362358715614E-2</v>
       </c>
       <c r="AE16" t="s">
         <v>253</v>
@@ -35104,7 +34934,7 @@
       </c>
       <c r="J17" s="44">
         <f ca="1">'Watchlist Ratings'!AW13</f>
-        <v>37.038431729931467</v>
+        <v>36.926920313007969</v>
       </c>
       <c r="L17" t="s">
         <v>277</v>
@@ -35123,7 +34953,7 @@
       </c>
       <c r="Q17" s="23">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>0.1137563839946405</v>
+        <v>0.1144404281327791</v>
       </c>
       <c r="S17" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
@@ -35151,7 +34981,7 @@
       </c>
       <c r="Z17">
         <f ca="1">'Watchlist Ratings'!AW13</f>
-        <v>37.038431729931467</v>
+        <v>36.926920313007969</v>
       </c>
       <c r="AA17" t="str">
         <f ca="1">'Watchlist Ratings'!B13</f>
@@ -35159,11 +34989,11 @@
       </c>
       <c r="AB17">
         <f ca="1">'Watchlist Ratings'!BL13</f>
-        <v>-6.0005029184535763E-2</v>
+        <v>-5.9427705400891262E-2</v>
       </c>
       <c r="AC17">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>0.1137563839946405</v>
+        <v>0.1144404281327791</v>
       </c>
       <c r="AS17" t="s">
         <v>274</v>
@@ -35589,7 +35419,7 @@
       </c>
       <c r="J22" s="56">
         <f ca="1">'Watchlist Ratings'!AW18</f>
-        <v>36.553502188767119</v>
+        <v>36.489744772054792</v>
       </c>
       <c r="O22" t="str">
         <f ca="1">'Watchlist Ratings'!B18</f>
@@ -35601,7 +35431,7 @@
       </c>
       <c r="Q22" s="23">
         <f ca="1">'Watchlist Ratings'!BM18</f>
-        <v>0.1098005163465392</v>
+        <v>0.11022293283992024</v>
       </c>
       <c r="V22" t="str">
         <f ca="1">'Watchlist Ratings'!B18</f>
@@ -35621,7 +35451,7 @@
       </c>
       <c r="Z22">
         <f ca="1">'Watchlist Ratings'!AW18</f>
-        <v>36.553502188767119</v>
+        <v>36.489744772054792</v>
       </c>
       <c r="AA22" t="str">
         <f ca="1">'Watchlist Ratings'!B18</f>
@@ -35629,11 +35459,11 @@
       </c>
       <c r="AB22">
         <f ca="1">'Watchlist Ratings'!BL18</f>
-        <v>-0.1488094577400273</v>
+        <v>-0.14848547435854165</v>
       </c>
       <c r="AC22">
         <f ca="1">'Watchlist Ratings'!BM18</f>
-        <v>0.1098005163465392</v>
+        <v>0.11022293283992024</v>
       </c>
     </row>
     <row r="23" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -35683,7 +35513,7 @@
       </c>
       <c r="Q25">
         <f ca="1">'Watchlist Ratings'!BM21</f>
-        <v>1.1588906765475082E-2</v>
+        <v>1.2909851886780066E-2</v>
       </c>
     </row>
     <row r="26" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -35697,7 +35527,7 @@
       </c>
       <c r="Q26">
         <f ca="1">'Watchlist Ratings'!BM22</f>
-        <v>0.16731996018807838</v>
+        <v>0.16765420851689705</v>
       </c>
     </row>
     <row r="27" spans="1:47" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -35907,7 +35737,7 @@
       </c>
       <c r="B64" s="64">
         <f ca="1">'Watchlist Ratings'!G4</f>
-        <v>246.71</v>
+        <v>246.255</v>
       </c>
       <c r="C64" s="64">
         <f ca="1">'Watchlist Ratings'!BJ4</f>
@@ -35919,15 +35749,15 @@
       </c>
       <c r="E64" s="65">
         <f ca="1">'Watchlist Ratings'!BL4</f>
-        <v>-3.1447161351016106E-2</v>
+        <v>-3.1089510785764829E-2</v>
       </c>
       <c r="F64" s="65">
         <f ca="1">'Watchlist Ratings'!BM4</f>
-        <v>0.21440325563515295</v>
+        <v>0.21485168962191081</v>
       </c>
       <c r="G64" s="65">
         <f t="shared" ref="G64:G71" ca="1" si="0">F64-E64</f>
-        <v>0.24585041698616905</v>
+        <v>0.24594120040767564</v>
       </c>
       <c r="H64" s="63" t="str">
         <f t="shared" ref="H64:H71" ca="1" si="1">IF(E64&gt;0,"🟢 BUY",IF(E64&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -35973,7 +35803,7 @@
       </c>
       <c r="B65" s="64">
         <f ca="1">'Watchlist Ratings'!G5</f>
-        <v>495.30009999999999</v>
+        <v>494.54</v>
       </c>
       <c r="C65" s="64">
         <f ca="1">'Watchlist Ratings'!BJ5</f>
@@ -35985,15 +35815,15 @@
       </c>
       <c r="E65" s="65">
         <f ca="1">'Watchlist Ratings'!BL5</f>
-        <v>-4.4021554335645474E-2</v>
+        <v>-4.3727870146306191E-2</v>
       </c>
       <c r="F65" s="65">
         <f ca="1">'Watchlist Ratings'!BM5</f>
-        <v>0.12530205264345784</v>
+        <v>0.12564775439289733</v>
       </c>
       <c r="G65" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.16932360697910331</v>
+        <v>0.16937562453920352</v>
       </c>
       <c r="H65" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -36105,7 +35935,7 @@
       </c>
       <c r="B67" s="64">
         <f ca="1">'Watchlist Ratings'!G7</f>
-        <v>41.935000000000002</v>
+        <v>41.981000000000002</v>
       </c>
       <c r="C67" s="64">
         <f ca="1">'Watchlist Ratings'!BJ7</f>
@@ -36117,15 +35947,15 @@
       </c>
       <c r="E67" s="65">
         <f ca="1">'Watchlist Ratings'!BL7</f>
-        <v>1.7198856723277256E-2</v>
+        <v>1.6975843125892842E-2</v>
       </c>
       <c r="F67" s="65">
         <f ca="1">'Watchlist Ratings'!BM7</f>
-        <v>0.21981528931254024</v>
+        <v>0.21954785350683115</v>
       </c>
       <c r="G67" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.20261643258926298</v>
+        <v>0.20257201038093831</v>
       </c>
       <c r="H67" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -36171,7 +36001,7 @@
       </c>
       <c r="B68" s="64">
         <f ca="1">'Watchlist Ratings'!G8</f>
-        <v>958.59550000000002</v>
+        <v>958.05</v>
       </c>
       <c r="C68" s="64">
         <f ca="1">'Watchlist Ratings'!BJ8</f>
@@ -36183,15 +36013,15 @@
       </c>
       <c r="E68" s="65">
         <f ca="1">'Watchlist Ratings'!BL8</f>
-        <v>-4.9160074465740333E-2</v>
+        <v>-4.905182018101617E-2</v>
       </c>
       <c r="F68" s="65">
         <f ca="1">'Watchlist Ratings'!BM8</f>
-        <v>8.5666007165993152E-2</v>
+        <v>8.5789611564482282E-2</v>
       </c>
       <c r="G68" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.13482608163173349</v>
+        <v>0.13484143174549845</v>
       </c>
       <c r="H68" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -36237,7 +36067,7 @@
       </c>
       <c r="B69" s="64">
         <f ca="1">'Watchlist Ratings'!G9</f>
-        <v>76.510000000000005</v>
+        <v>76.37</v>
       </c>
       <c r="C69" s="64">
         <f ca="1">'Watchlist Ratings'!BJ9</f>
@@ -36249,15 +36079,15 @@
       </c>
       <c r="E69" s="65">
         <f ca="1">'Watchlist Ratings'!BL9</f>
-        <v>-3.4688426625229307E-2</v>
+        <v>-3.4334767774719888E-2</v>
       </c>
       <c r="F69" s="65">
         <f ca="1">'Watchlist Ratings'!BM9</f>
-        <v>0.19992256658649676</v>
+        <v>0.20036217929528854</v>
       </c>
       <c r="G69" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.23461099321172607</v>
+        <v>0.23469694707000843</v>
       </c>
       <c r="H69" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -36369,7 +36199,7 @@
       </c>
       <c r="B71" s="64">
         <f ca="1">'Watchlist Ratings'!G11</f>
-        <v>167.61</v>
+        <v>167.76</v>
       </c>
       <c r="C71" s="64">
         <f ca="1">'Watchlist Ratings'!BJ11</f>
@@ -36381,15 +36211,15 @@
       </c>
       <c r="E71" s="65">
         <f ca="1">'Watchlist Ratings'!BL11</f>
-        <v>-2.3220994598323275E-2</v>
+        <v>-2.3395731461994917E-2</v>
       </c>
       <c r="F71" s="65">
         <f ca="1">'Watchlist Ratings'!BM11</f>
-        <v>0.26082680899108857</v>
+        <v>0.26060125856359373</v>
       </c>
       <c r="G71" s="65">
         <f t="shared" ca="1" si="0"/>
-        <v>0.28404780358941184</v>
+        <v>0.28399699002558865</v>
       </c>
       <c r="H71" s="63" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -36460,7 +36290,7 @@
       </c>
       <c r="B73" s="69">
         <f ca="1">'Watchlist Ratings'!G13</f>
-        <v>259.36</v>
+        <v>258.565</v>
       </c>
       <c r="C73" s="69">
         <f ca="1">'Watchlist Ratings'!BJ13</f>
@@ -36472,15 +36302,15 @@
       </c>
       <c r="E73" s="70">
         <f ca="1">'Watchlist Ratings'!BL13</f>
-        <v>-6.0005029184535763E-2</v>
+        <v>-5.9427705400891262E-2</v>
       </c>
       <c r="F73" s="70">
         <f ca="1">'Watchlist Ratings'!BM13</f>
-        <v>0.1137563839946405</v>
+        <v>0.1144404281327791</v>
       </c>
       <c r="G73" s="70">
         <f ca="1">F73-E73</f>
-        <v>0.17376141317917626</v>
+        <v>0.17386813353367037</v>
       </c>
       <c r="H73" s="71" t="str">
         <f ca="1">IF(E73&gt;0,"🟢 BUY",IF(E73&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -36541,11 +36371,11 @@
       </c>
       <c r="F74" s="77">
         <f ca="1">VLOOKUP(A74,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.21440325563515295</v>
+        <v>0.21485168962191081</v>
       </c>
       <c r="G74" s="77">
         <f ca="1">F74-E74</f>
-        <v>-210.0681999665353</v>
+        <v>-210.06775153254853</v>
       </c>
       <c r="H74" s="75" t="str">
         <f ca="1">IF(E74&gt;0,"🟢 BUY",IF(E74&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -36572,7 +36402,7 @@
       </c>
       <c r="O74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>40076.386543000001</v>
+        <v>40002.474841499999</v>
       </c>
       <c r="P74" s="78">
         <f ca="1">VLOOKUP(J74,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -36605,11 +36435,11 @@
       </c>
       <c r="F75" s="81">
         <f ca="1">VLOOKUP(A75,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.12530205264345784</v>
+        <v>0.12564775439289733</v>
       </c>
       <c r="G75" s="81">
         <f ca="1">F75-E75</f>
-        <v>-395.34048530707224</v>
+        <v>-395.3401396053228</v>
       </c>
       <c r="H75" s="79" t="str">
         <f ca="1">IF(E75&gt;0,"🟢 BUY",IF(E75&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -36636,7 +36466,7 @@
       </c>
       <c r="O75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>3677873.1810544999</v>
+        <v>3672229.0243000002</v>
       </c>
       <c r="P75" s="79">
         <f ca="1">VLOOKUP(J75,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -36690,11 +36520,11 @@
       </c>
       <c r="F77" s="81">
         <f ca="1">VLOOKUP(A77,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.21981528931254024</v>
+        <v>0.21954785350683115</v>
       </c>
       <c r="G77" s="81">
         <f ca="1">F77-E77</f>
-        <v>-45.447550830638598</v>
+        <v>-45.447818266444308</v>
       </c>
       <c r="H77" s="79" t="str">
         <f ca="1">IF(E77&gt;0,"🟢 BUY",IF(E77&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -36721,7 +36551,7 @@
       </c>
       <c r="O77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>102821.055525</v>
+        <v>102933.84361500001</v>
       </c>
       <c r="P77" s="79">
         <f ca="1">VLOOKUP(J77,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -36824,7 +36654,7 @@
       <c r="B80" s="123"/>
       <c r="C80" s="162">
         <f ca="1">MAX('Watchlist Ratings'!BM:BM)</f>
-        <v>0.34799705280246274</v>
+        <v>0.34891455816026773</v>
       </c>
       <c r="D80" s="123"/>
       <c r="E80" s="165">
@@ -36849,12 +36679,12 @@
       <c r="L80" s="123"/>
       <c r="M80" s="128" t="str">
         <f ca="1">MIN('Watchlist Ratings'!AW4:AW64)&amp;"x"</f>
-        <v>-45.1228247305936x</v>
+        <v>-44.9843925525114x</v>
       </c>
       <c r="N80" s="123"/>
       <c r="O80" s="128" t="str">
         <f t="array" aca="1" ref="O80" ca="1">TEXT(MAX('Watchlist Ratings'!BM4:BM64-'Watchlist Ratings'!BL4:BL64),"0.0%")</f>
-        <v>121.2%</v>
+        <v>121.4%</v>
       </c>
       <c r="P80" s="123"/>
       <c r="Q80" s="82" t="str">
@@ -36884,11 +36714,11 @@
       </c>
       <c r="F81" s="81">
         <f ca="1">VLOOKUP(A81,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.26082680899108857</v>
+        <v>0.26060125856359373</v>
       </c>
       <c r="G81" s="81">
         <f ca="1">F81-E81</f>
-        <v>-148.77185216163218</v>
+        <v>-148.77207771205968</v>
       </c>
       <c r="H81" s="79" t="str">
         <f ca="1">IF(E81&gt;0,"🟢 BUY",IF(E81&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -36915,7 +36745,7 @@
       </c>
       <c r="O81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>27104.129295000002</v>
+        <v>27128.385719999998</v>
       </c>
       <c r="P81" s="79">
         <f ca="1">VLOOKUP(J81,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -36969,11 +36799,11 @@
       </c>
       <c r="F83" s="85">
         <f ca="1">VLOOKUP(A83,'Watchlist Ratings'!$B$4:$BM$71,64,FALSE())</f>
-        <v>0.1137563839946405</v>
+        <v>0.1144404281327791</v>
       </c>
       <c r="G83" s="85">
         <f ca="1">F83-E83</f>
-        <v>-190.22649899527781</v>
+        <v>-190.22581495113965</v>
       </c>
       <c r="H83" s="83" t="str">
         <f ca="1">IF(E83&gt;0,"🟢 BUY",IF(E83&gt;-0.05,"🟡 HOLD","🔴 PASS"))</f>
@@ -37000,7 +36830,7 @@
       </c>
       <c r="O83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$71,8,FALSE())</f>
-        <v>2797537.3615999999</v>
+        <v>2788962.2451499999</v>
       </c>
       <c r="P83" s="83">
         <f ca="1">VLOOKUP(J83,'Watchlist Ratings'!$B$4:$BM$71,9,FALSE())</f>
@@ -37118,7 +36948,7 @@
       <c r="B89" s="104"/>
       <c r="C89" s="119">
         <f ca="1">MAX('Watchlist Ratings'!BM$4:BM$64)</f>
-        <v>0.34799705280246274</v>
+        <v>0.34891455816026773</v>
       </c>
       <c r="D89" s="104"/>
       <c r="E89" s="119">
@@ -37143,12 +36973,12 @@
       <c r="L89" s="104"/>
       <c r="M89" s="113" t="str">
         <f t="array" aca="1" ref="M89" ca="1">MIN(IF('Watchlist Ratings'!AW$4:AW$64&gt;0,'Watchlist Ratings'!AW$4:AW$64))&amp;"x"</f>
-        <v>9.14496399570751x</v>
+        <v>9.11101495653111x</v>
       </c>
       <c r="N89" s="104"/>
       <c r="O89" s="113">
         <f t="array" aca="1" ref="O89" ca="1">MAX('Watchlist Ratings'!BM$4:BM$64-'Watchlist Ratings'!BL$4:BL$64)</f>
-        <v>1.2122417338978706</v>
+        <v>1.2137793533379853</v>
       </c>
       <c r="P89" s="104"/>
     </row>
@@ -37304,7 +37134,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E253"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.453125" bestFit="1" customWidth="1"/>
@@ -41614,6 +41444,108 @@
         <v>867</v>
       </c>
     </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>372</v>
+      </c>
+      <c r="B254">
+        <v>46260</v>
+      </c>
+      <c r="C254" t="s">
+        <v>627</v>
+      </c>
+      <c r="D254" t="s">
+        <v>868</v>
+      </c>
+      <c r="E254" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>260</v>
+      </c>
+      <c r="B255">
+        <v>46260</v>
+      </c>
+      <c r="C255" t="s">
+        <v>627</v>
+      </c>
+      <c r="D255" t="s">
+        <v>868</v>
+      </c>
+      <c r="E255" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>259</v>
+      </c>
+      <c r="B256">
+        <v>46260</v>
+      </c>
+      <c r="C256" t="s">
+        <v>871</v>
+      </c>
+      <c r="D256" t="s">
+        <v>872</v>
+      </c>
+      <c r="E256" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>384</v>
+      </c>
+      <c r="B257">
+        <v>46260</v>
+      </c>
+      <c r="C257" t="s">
+        <v>667</v>
+      </c>
+      <c r="D257" t="s">
+        <v>845</v>
+      </c>
+      <c r="E257" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>382</v>
+      </c>
+      <c r="B258">
+        <v>46260</v>
+      </c>
+      <c r="C258" t="s">
+        <v>875</v>
+      </c>
+      <c r="D258" t="s">
+        <v>845</v>
+      </c>
+      <c r="E258" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>252</v>
+      </c>
+      <c r="B259">
+        <v>46260</v>
+      </c>
+      <c r="C259" t="s">
+        <v>665</v>
+      </c>
+      <c r="D259" t="s">
+        <v>845</v>
+      </c>
+      <c r="E259" t="s">
+        <v>877</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
